--- a/master.xlsx
+++ b/master.xlsx
@@ -1430,7 +1430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="82" min="1" max="1"/>
@@ -2177,7 +2177,7 @@
       <c r="A39" s="88" t="n"/>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>염증</t>
+          <t>빈맥</t>
         </is>
       </c>
       <c r="C39" s="130" t="n"/>
@@ -2187,27 +2187,24 @@
       <c r="G39" s="130" t="n"/>
       <c r="H39" s="130" t="n"/>
       <c r="I39" s="130" t="n"/>
-      <c r="J39" s="122">
-        <f>SUM(C38:I38)</f>
-        <v/>
-      </c>
+      <c r="J39" s="122" t="n"/>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="82">
       <c r="A40" s="88" t="n"/>
-      <c r="B40" s="40" t="inlineStr">
-        <is>
-          <t>부정맥</t>
-        </is>
-      </c>
-      <c r="C40" s="136" t="n"/>
-      <c r="D40" s="136" t="n"/>
-      <c r="E40" s="136" t="n"/>
-      <c r="F40" s="136" t="n"/>
-      <c r="G40" s="136" t="n"/>
-      <c r="H40" s="136" t="n"/>
-      <c r="I40" s="136" t="n"/>
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>염증</t>
+        </is>
+      </c>
+      <c r="C40" s="130" t="n"/>
+      <c r="D40" s="130" t="n"/>
+      <c r="E40" s="130" t="n"/>
+      <c r="F40" s="130" t="n"/>
+      <c r="G40" s="130" t="n"/>
+      <c r="H40" s="130" t="n"/>
+      <c r="I40" s="130" t="n"/>
       <c r="J40" s="122">
-        <f>SUM(C39:I39)</f>
+        <f>SUM(C38:I38)</f>
         <v/>
       </c>
     </row>
@@ -2215,42 +2212,42 @@
       <c r="A41" s="88" t="n"/>
       <c r="B41" s="40" t="inlineStr">
         <is>
-          <t>심근병증</t>
-        </is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="C41" s="136" t="n"/>
+      <c r="D41" s="136" t="n"/>
+      <c r="E41" s="136" t="n"/>
+      <c r="F41" s="136" t="n"/>
+      <c r="G41" s="136" t="n"/>
+      <c r="H41" s="136" t="n"/>
+      <c r="I41" s="136" t="n"/>
+      <c r="J41" s="122">
+        <f>SUM(C39:I39)</f>
+        <v/>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="82">
       <c r="A42" s="88" t="n"/>
       <c r="B42" s="40" t="inlineStr">
         <is>
-          <t>심장판막</t>
+          <t>심근병증</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="82">
       <c r="A43" s="88" t="n"/>
-      <c r="B43" s="60" t="inlineStr">
-        <is>
-          <t>산정특례심장</t>
-        </is>
-      </c>
-      <c r="C43" s="121" t="n"/>
-      <c r="D43" s="121" t="n"/>
-      <c r="E43" s="121" t="n"/>
-      <c r="F43" s="121" t="n"/>
-      <c r="G43" s="121" t="n"/>
-      <c r="H43" s="121" t="n"/>
-      <c r="I43" s="121" t="n"/>
-      <c r="J43" s="122">
-        <f>SUM(C40:I40)</f>
-        <v/>
+      <c r="B43" s="40" t="inlineStr">
+        <is>
+          <t>심장판막</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="17.25" customHeight="1" s="82">
       <c r="A44" s="88" t="n"/>
-      <c r="B44" s="69" t="inlineStr">
-        <is>
-          <t>2대 주요치료비</t>
+      <c r="B44" s="60" t="inlineStr">
+        <is>
+          <t>산정특례심장</t>
         </is>
       </c>
       <c r="C44" s="121" t="n"/>
@@ -2261,125 +2258,125 @@
       <c r="H44" s="121" t="n"/>
       <c r="I44" s="121" t="n"/>
       <c r="J44" s="122">
-        <f>SUM(C41:I41)</f>
+        <f>SUM(C40:I40)</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1" s="82">
       <c r="A45" s="88" t="n"/>
-      <c r="B45" s="86" t="inlineStr">
-        <is>
-          <t>허혈성 진단비</t>
-        </is>
-      </c>
-      <c r="C45" s="115" t="n"/>
-      <c r="D45" s="115" t="n"/>
-      <c r="E45" s="115" t="n"/>
-      <c r="F45" s="115" t="n"/>
-      <c r="G45" s="115" t="n"/>
-      <c r="H45" s="115" t="n"/>
-      <c r="I45" s="115" t="n"/>
+      <c r="B45" s="69" t="inlineStr">
+        <is>
+          <t>2대 주요치료비</t>
+        </is>
+      </c>
+      <c r="C45" s="121" t="n"/>
+      <c r="D45" s="121" t="n"/>
+      <c r="E45" s="121" t="n"/>
+      <c r="F45" s="121" t="n"/>
+      <c r="G45" s="121" t="n"/>
+      <c r="H45" s="121" t="n"/>
+      <c r="I45" s="121" t="n"/>
       <c r="J45" s="122">
-        <f>SUM(C42:I42)</f>
+        <f>SUM(C41:I41)</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="82">
       <c r="A46" s="88" t="n"/>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>급성심근경색</t>
-        </is>
-      </c>
-      <c r="C46" s="125" t="n"/>
-      <c r="D46" s="125" t="n"/>
-      <c r="E46" s="125" t="n"/>
-      <c r="F46" s="125" t="n"/>
-      <c r="G46" s="125" t="n"/>
-      <c r="H46" s="125" t="n"/>
-      <c r="I46" s="125" t="n"/>
-      <c r="J46" s="110">
+      <c r="B46" s="86" t="inlineStr">
+        <is>
+          <t>허혈성 진단비</t>
+        </is>
+      </c>
+      <c r="C46" s="115" t="n"/>
+      <c r="D46" s="115" t="n"/>
+      <c r="E46" s="115" t="n"/>
+      <c r="F46" s="115" t="n"/>
+      <c r="G46" s="115" t="n"/>
+      <c r="H46" s="115" t="n"/>
+      <c r="I46" s="115" t="n"/>
+      <c r="J46" s="122">
         <f>SUM(C42:I42)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="82">
       <c r="A47" s="88" t="n"/>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>급성심근경색</t>
+        </is>
+      </c>
+      <c r="C47" s="125" t="n"/>
+      <c r="D47" s="125" t="n"/>
+      <c r="E47" s="125" t="n"/>
+      <c r="F47" s="125" t="n"/>
+      <c r="G47" s="125" t="n"/>
+      <c r="H47" s="125" t="n"/>
+      <c r="I47" s="125" t="n"/>
+      <c r="J47" s="110">
+        <f>SUM(C42:I42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" s="82">
+      <c r="A48" s="88" t="n"/>
+      <c r="B48" s="16" t="inlineStr">
         <is>
           <t>중대한 급성심근</t>
         </is>
       </c>
-      <c r="C47" s="111" t="n"/>
-      <c r="D47" s="111" t="n"/>
-      <c r="E47" s="111" t="n"/>
-      <c r="F47" s="111" t="n"/>
-      <c r="G47" s="111" t="n"/>
-      <c r="H47" s="111" t="n"/>
-      <c r="I47" s="111" t="n"/>
-      <c r="J47" s="133">
+      <c r="C48" s="111" t="n"/>
+      <c r="D48" s="111" t="n"/>
+      <c r="E48" s="111" t="n"/>
+      <c r="F48" s="111" t="n"/>
+      <c r="G48" s="111" t="n"/>
+      <c r="H48" s="111" t="n"/>
+      <c r="I48" s="111" t="n"/>
+      <c r="J48" s="133">
         <f>SUM(C44:I44)</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="82">
-      <c r="A48" s="89" t="n"/>
-      <c r="B48" s="64" t="inlineStr">
+    <row r="49" ht="16.5" customHeight="1" s="82">
+      <c r="A49" s="89" t="n"/>
+      <c r="B49" s="64" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C48" s="113" t="n"/>
-      <c r="D48" s="113" t="n"/>
-      <c r="E48" s="113" t="n"/>
-      <c r="F48" s="113" t="n"/>
-      <c r="G48" s="113" t="n"/>
-      <c r="H48" s="113" t="n"/>
-      <c r="I48" s="113" t="n"/>
-      <c r="J48" s="114">
+      <c r="C49" s="113" t="n"/>
+      <c r="D49" s="113" t="n"/>
+      <c r="E49" s="113" t="n"/>
+      <c r="F49" s="113" t="n"/>
+      <c r="G49" s="113" t="n"/>
+      <c r="H49" s="113" t="n"/>
+      <c r="I49" s="113" t="n"/>
+      <c r="J49" s="114">
         <f>SUM(C45:I45)</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="82">
-      <c r="A49" s="87" t="inlineStr">
+    <row r="50" ht="16.5" customHeight="1" s="82">
+      <c r="A50" s="87" t="inlineStr">
         <is>
           <t>일당</t>
         </is>
       </c>
-      <c r="B49" s="95" t="inlineStr">
+      <c r="B50" s="95" t="inlineStr">
         <is>
           <t>질병일당</t>
         </is>
       </c>
-      <c r="C49" s="119" t="n"/>
-      <c r="D49" s="119" t="n"/>
-      <c r="E49" s="119" t="n"/>
-      <c r="F49" s="119" t="n"/>
-      <c r="G49" s="119" t="n"/>
-      <c r="H49" s="119" t="n"/>
-      <c r="I49" s="119" t="n"/>
-      <c r="J49" s="120">
+      <c r="C50" s="119" t="n"/>
+      <c r="D50" s="119" t="n"/>
+      <c r="E50" s="119" t="n"/>
+      <c r="F50" s="119" t="n"/>
+      <c r="G50" s="119" t="n"/>
+      <c r="H50" s="119" t="n"/>
+      <c r="I50" s="119" t="n"/>
+      <c r="J50" s="120">
         <f>SUM(C46:I46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16.5" customHeight="1" s="82">
-      <c r="A50" s="88" t="n"/>
-      <c r="B50" s="65" t="inlineStr">
-        <is>
-          <t>질병수술일당</t>
-        </is>
-      </c>
-      <c r="C50" s="136" t="n"/>
-      <c r="D50" s="136" t="n"/>
-      <c r="E50" s="136" t="n"/>
-      <c r="F50" s="136" t="n"/>
-      <c r="G50" s="136" t="n"/>
-      <c r="H50" s="136" t="n"/>
-      <c r="I50" s="136" t="n"/>
-      <c r="J50" s="122">
-        <f>SUM(C47:I47)</f>
         <v/>
       </c>
     </row>
@@ -2387,7 +2384,7 @@
       <c r="A51" s="88" t="n"/>
       <c r="B51" s="65" t="inlineStr">
         <is>
-          <t>질병종합병원일당</t>
+          <t>질병수술일당</t>
         </is>
       </c>
       <c r="C51" s="136" t="n"/>
@@ -2398,34 +2395,34 @@
       <c r="H51" s="136" t="n"/>
       <c r="I51" s="136" t="n"/>
       <c r="J51" s="122">
-        <f>SUM(C48:I48)</f>
+        <f>SUM(C47:I47)</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" s="82">
       <c r="A52" s="88" t="n"/>
-      <c r="B52" s="60" t="inlineStr">
-        <is>
-          <t>상해일당</t>
-        </is>
-      </c>
-      <c r="C52" s="121" t="n"/>
-      <c r="D52" s="121" t="n"/>
-      <c r="E52" s="121" t="n"/>
-      <c r="F52" s="121" t="n"/>
-      <c r="G52" s="121" t="n"/>
-      <c r="H52" s="121" t="n"/>
-      <c r="I52" s="121" t="n"/>
+      <c r="B52" s="65" t="inlineStr">
+        <is>
+          <t>질병종합병원일당</t>
+        </is>
+      </c>
+      <c r="C52" s="136" t="n"/>
+      <c r="D52" s="136" t="n"/>
+      <c r="E52" s="136" t="n"/>
+      <c r="F52" s="136" t="n"/>
+      <c r="G52" s="136" t="n"/>
+      <c r="H52" s="136" t="n"/>
+      <c r="I52" s="136" t="n"/>
       <c r="J52" s="122">
-        <f>SUM(C49:I49)</f>
+        <f>SUM(C48:I48)</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" s="82">
       <c r="A53" s="88" t="n"/>
-      <c r="B53" s="31" t="inlineStr">
-        <is>
-          <t>간병인</t>
+      <c r="B53" s="60" t="inlineStr">
+        <is>
+          <t>상해일당</t>
         </is>
       </c>
       <c r="C53" s="121" t="n"/>
@@ -2436,7 +2433,7 @@
       <c r="H53" s="121" t="n"/>
       <c r="I53" s="121" t="n"/>
       <c r="J53" s="122">
-        <f>SUM(C50:I50)</f>
+        <f>SUM(C49:I49)</f>
         <v/>
       </c>
     </row>
@@ -2444,7 +2441,7 @@
       <c r="A54" s="88" t="n"/>
       <c r="B54" s="31" t="inlineStr">
         <is>
-          <t>간호통합병동</t>
+          <t>간병인</t>
         </is>
       </c>
       <c r="C54" s="121" t="n"/>
@@ -2455,15 +2452,15 @@
       <c r="H54" s="121" t="n"/>
       <c r="I54" s="121" t="n"/>
       <c r="J54" s="122">
-        <f>SUM(C51:I51)</f>
+        <f>SUM(C50:I50)</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="17.25" customHeight="1" s="82">
       <c r="A55" s="88" t="n"/>
-      <c r="B55" s="66" t="inlineStr">
-        <is>
-          <t>1인실 종합병원</t>
+      <c r="B55" s="31" t="inlineStr">
+        <is>
+          <t>간호통합병동</t>
         </is>
       </c>
       <c r="C55" s="121" t="n"/>
@@ -2474,7 +2471,7 @@
       <c r="H55" s="121" t="n"/>
       <c r="I55" s="121" t="n"/>
       <c r="J55" s="122">
-        <f>SUM(C52:I52)</f>
+        <f>SUM(C51:I51)</f>
         <v/>
       </c>
     </row>
@@ -2482,7 +2479,7 @@
       <c r="A56" s="88" t="n"/>
       <c r="B56" s="66" t="inlineStr">
         <is>
-          <t>1인실 상급병원</t>
+          <t>1인실 종합병원</t>
         </is>
       </c>
       <c r="C56" s="121" t="n"/>
@@ -2493,15 +2490,15 @@
       <c r="H56" s="121" t="n"/>
       <c r="I56" s="121" t="n"/>
       <c r="J56" s="122">
-        <f>SUM(C53:I53)</f>
+        <f>SUM(C52:I52)</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="16.5" customHeight="1" s="82">
       <c r="A57" s="88" t="n"/>
-      <c r="B57" s="31" t="inlineStr">
-        <is>
-          <t>질병중환자실</t>
+      <c r="B57" s="66" t="inlineStr">
+        <is>
+          <t>1인실 상급병원</t>
         </is>
       </c>
       <c r="C57" s="121" t="n"/>
@@ -2512,115 +2509,115 @@
       <c r="H57" s="121" t="n"/>
       <c r="I57" s="121" t="n"/>
       <c r="J57" s="122">
+        <f>SUM(C53:I53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="16.5" customHeight="1" s="82">
+      <c r="A58" s="88" t="n"/>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>질병중환자실</t>
+        </is>
+      </c>
+      <c r="C58" s="121" t="n"/>
+      <c r="D58" s="121" t="n"/>
+      <c r="E58" s="121" t="n"/>
+      <c r="F58" s="121" t="n"/>
+      <c r="G58" s="121" t="n"/>
+      <c r="H58" s="121" t="n"/>
+      <c r="I58" s="121" t="n"/>
+      <c r="J58" s="122">
         <f>SUM(C54:I54)</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="16.5" customHeight="1" s="82">
-      <c r="A58" s="89" t="n"/>
-      <c r="B58" s="25" t="inlineStr">
+    <row r="59" ht="16.5" customHeight="1" s="82">
+      <c r="A59" s="89" t="n"/>
+      <c r="B59" s="25" t="inlineStr">
         <is>
           <t>상해중환자실</t>
         </is>
       </c>
-      <c r="C58" s="117" t="n"/>
-      <c r="D58" s="117" t="n"/>
-      <c r="E58" s="117" t="n"/>
-      <c r="F58" s="117" t="n"/>
-      <c r="G58" s="117" t="n"/>
-      <c r="H58" s="117" t="n"/>
-      <c r="I58" s="117" t="n"/>
-      <c r="J58" s="118">
+      <c r="C59" s="117" t="n"/>
+      <c r="D59" s="117" t="n"/>
+      <c r="E59" s="117" t="n"/>
+      <c r="F59" s="117" t="n"/>
+      <c r="G59" s="117" t="n"/>
+      <c r="H59" s="117" t="n"/>
+      <c r="I59" s="117" t="n"/>
+      <c r="J59" s="118">
         <f>SUM(C55:I55)</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="16.5" customHeight="1" s="82">
-      <c r="A59" s="92" t="inlineStr">
+    <row r="60" ht="16.5" customHeight="1" s="82">
+      <c r="A60" s="92" t="inlineStr">
         <is>
           <t>수술비</t>
         </is>
       </c>
-      <c r="B59" s="95" t="inlineStr">
+      <c r="B60" s="95" t="inlineStr">
         <is>
           <t>상해수술비</t>
         </is>
       </c>
-      <c r="C59" s="119" t="n"/>
-      <c r="D59" s="119" t="n"/>
-      <c r="E59" s="119" t="n"/>
-      <c r="F59" s="119" t="n"/>
-      <c r="G59" s="119" t="n"/>
-      <c r="H59" s="119" t="n"/>
-      <c r="I59" s="119" t="n"/>
-      <c r="J59" s="120">
+      <c r="C60" s="119" t="n"/>
+      <c r="D60" s="119" t="n"/>
+      <c r="E60" s="119" t="n"/>
+      <c r="F60" s="119" t="n"/>
+      <c r="G60" s="119" t="n"/>
+      <c r="H60" s="119" t="n"/>
+      <c r="I60" s="119" t="n"/>
+      <c r="J60" s="120">
         <f>SUM(C56:I56)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60" ht="16.5" customHeight="1" s="82">
-      <c r="A60" s="88" t="n"/>
-      <c r="B60" s="65" t="inlineStr">
-        <is>
-          <t>중대한상해수술비</t>
-        </is>
-      </c>
-      <c r="C60" s="136" t="n"/>
-      <c r="D60" s="136" t="n"/>
-      <c r="E60" s="136" t="n"/>
-      <c r="F60" s="136" t="n"/>
-      <c r="G60" s="136" t="n"/>
-      <c r="H60" s="136" t="n"/>
-      <c r="I60" s="136" t="n"/>
-      <c r="J60" s="122">
-        <f>SUM(C57:I57)</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1" s="82">
       <c r="A61" s="88" t="n"/>
-      <c r="B61" s="60" t="inlineStr">
-        <is>
-          <t>상해 종수술비(1-5종)</t>
+      <c r="B61" s="65" t="inlineStr">
+        <is>
+          <t>중대한상해수술비</t>
         </is>
       </c>
       <c r="C61" s="136" t="n"/>
       <c r="D61" s="136" t="n"/>
       <c r="E61" s="136" t="n"/>
-      <c r="F61" s="137" t="n"/>
+      <c r="F61" s="136" t="n"/>
       <c r="G61" s="136" t="n"/>
       <c r="H61" s="136" t="n"/>
       <c r="I61" s="136" t="n"/>
-      <c r="J61" s="122" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="J61" s="122">
+        <f>SUM(C57:I57)</f>
+        <v/>
       </c>
     </row>
     <row r="62" ht="17.25" customHeight="1" s="82">
       <c r="A62" s="88" t="n"/>
       <c r="B62" s="60" t="inlineStr">
         <is>
-          <t>창상봉합술</t>
-        </is>
-      </c>
-      <c r="C62" s="121" t="n"/>
-      <c r="D62" s="121" t="n"/>
-      <c r="E62" s="121" t="n"/>
-      <c r="F62" s="121" t="n"/>
-      <c r="G62" s="121" t="n"/>
-      <c r="H62" s="121" t="n"/>
-      <c r="I62" s="121" t="n"/>
-      <c r="J62" s="122">
-        <f>SUM(C59:I59)</f>
-        <v/>
+          <t>상해 종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="C62" s="136" t="n"/>
+      <c r="D62" s="136" t="n"/>
+      <c r="E62" s="136" t="n"/>
+      <c r="F62" s="137" t="n"/>
+      <c r="G62" s="136" t="n"/>
+      <c r="H62" s="136" t="n"/>
+      <c r="I62" s="136" t="n"/>
+      <c r="J62" s="122" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1" s="82">
       <c r="A63" s="88" t="n"/>
       <c r="B63" s="60" t="inlineStr">
         <is>
-          <t>골절수술비</t>
+          <t>창상봉합술</t>
         </is>
       </c>
       <c r="C63" s="121" t="n"/>
@@ -2631,15 +2628,15 @@
       <c r="H63" s="121" t="n"/>
       <c r="I63" s="121" t="n"/>
       <c r="J63" s="122">
-        <f>SUM(C60:I60)</f>
+        <f>SUM(C59:I59)</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="16.5" customHeight="1" s="82">
       <c r="A64" s="88" t="n"/>
-      <c r="B64" s="69" t="inlineStr">
-        <is>
-          <t>5대골절수술비</t>
+      <c r="B64" s="60" t="inlineStr">
+        <is>
+          <t>골절수술비</t>
         </is>
       </c>
       <c r="C64" s="121" t="n"/>
@@ -2650,92 +2647,92 @@
       <c r="H64" s="121" t="n"/>
       <c r="I64" s="121" t="n"/>
       <c r="J64" s="122">
-        <f>SUM(C61:I61)</f>
+        <f>SUM(C60:I60)</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16.5" customHeight="1" s="82">
       <c r="A65" s="88" t="n"/>
-      <c r="B65" s="57" t="inlineStr">
-        <is>
-          <t>화상수술비</t>
-        </is>
-      </c>
-      <c r="C65" s="117" t="n"/>
-      <c r="D65" s="117" t="n"/>
-      <c r="E65" s="117" t="n"/>
-      <c r="F65" s="117" t="n"/>
-      <c r="G65" s="117" t="n"/>
-      <c r="H65" s="117" t="n"/>
-      <c r="I65" s="117" t="n"/>
-      <c r="J65" s="118">
-        <f>SUM(C62:I62)</f>
+      <c r="B65" s="69" t="inlineStr">
+        <is>
+          <t>5대골절수술비</t>
+        </is>
+      </c>
+      <c r="C65" s="121" t="n"/>
+      <c r="D65" s="121" t="n"/>
+      <c r="E65" s="121" t="n"/>
+      <c r="F65" s="121" t="n"/>
+      <c r="G65" s="121" t="n"/>
+      <c r="H65" s="121" t="n"/>
+      <c r="I65" s="121" t="n"/>
+      <c r="J65" s="122">
+        <f>SUM(C61:I61)</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" s="82">
       <c r="A66" s="88" t="n"/>
-      <c r="B66" s="65" t="inlineStr">
-        <is>
-          <t>질병수술비</t>
-        </is>
-      </c>
-      <c r="C66" s="136" t="n"/>
-      <c r="D66" s="136" t="n"/>
-      <c r="E66" s="136" t="n"/>
-      <c r="F66" s="136" t="n"/>
-      <c r="G66" s="136" t="n"/>
-      <c r="H66" s="136" t="n"/>
-      <c r="I66" s="138" t="n"/>
-      <c r="J66" s="116">
-        <f>SUM(C63:I63)</f>
+      <c r="B66" s="57" t="inlineStr">
+        <is>
+          <t>화상수술비</t>
+        </is>
+      </c>
+      <c r="C66" s="117" t="n"/>
+      <c r="D66" s="117" t="n"/>
+      <c r="E66" s="117" t="n"/>
+      <c r="F66" s="117" t="n"/>
+      <c r="G66" s="117" t="n"/>
+      <c r="H66" s="117" t="n"/>
+      <c r="I66" s="117" t="n"/>
+      <c r="J66" s="118">
+        <f>SUM(C62:I62)</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" s="82">
       <c r="A67" s="88" t="n"/>
-      <c r="B67" s="60" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-5종)</t>
-        </is>
-      </c>
-      <c r="C67" s="121" t="n"/>
-      <c r="D67" s="121" t="n"/>
-      <c r="E67" s="121" t="n"/>
-      <c r="F67" s="139" t="n"/>
-      <c r="G67" s="121" t="n"/>
-      <c r="H67" s="121" t="n"/>
-      <c r="I67" s="121" t="n"/>
-      <c r="J67" s="122" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="B67" s="65" t="inlineStr">
+        <is>
+          <t>질병수술비</t>
+        </is>
+      </c>
+      <c r="C67" s="136" t="n"/>
+      <c r="D67" s="136" t="n"/>
+      <c r="E67" s="136" t="n"/>
+      <c r="F67" s="136" t="n"/>
+      <c r="G67" s="136" t="n"/>
+      <c r="H67" s="136" t="n"/>
+      <c r="I67" s="138" t="n"/>
+      <c r="J67" s="116">
+        <f>SUM(C63:I63)</f>
+        <v/>
       </c>
     </row>
     <row r="68" ht="17.25" customHeight="1" s="82">
       <c r="A68" s="88" t="n"/>
-      <c r="B68" s="72" t="inlineStr">
-        <is>
-          <t>뇌혈관수술비</t>
-        </is>
-      </c>
-      <c r="C68" s="140" t="n"/>
-      <c r="D68" s="140" t="n"/>
-      <c r="E68" s="140" t="n"/>
-      <c r="F68" s="140" t="n"/>
-      <c r="G68" s="140" t="n"/>
-      <c r="H68" s="140" t="n"/>
-      <c r="I68" s="140" t="n"/>
-      <c r="J68" s="122">
-        <f>SUM(C65:I65)</f>
-        <v/>
+      <c r="B68" s="60" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="C68" s="121" t="n"/>
+      <c r="D68" s="121" t="n"/>
+      <c r="E68" s="121" t="n"/>
+      <c r="F68" s="139" t="n"/>
+      <c r="G68" s="121" t="n"/>
+      <c r="H68" s="121" t="n"/>
+      <c r="I68" s="121" t="n"/>
+      <c r="J68" s="122" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="82">
       <c r="A69" s="88" t="n"/>
       <c r="B69" s="72" t="inlineStr">
         <is>
-          <t>허혈성수술비</t>
+          <t>뇌혈관수술비</t>
         </is>
       </c>
       <c r="C69" s="140" t="n"/>
@@ -2746,7 +2743,7 @@
       <c r="H69" s="140" t="n"/>
       <c r="I69" s="140" t="n"/>
       <c r="J69" s="122">
-        <f>SUM(C66:I66)</f>
+        <f>SUM(C65:I65)</f>
         <v/>
       </c>
     </row>
@@ -2754,7 +2751,7 @@
       <c r="A70" s="88" t="n"/>
       <c r="B70" s="72" t="inlineStr">
         <is>
-          <t>심장수술비</t>
+          <t>허혈성수술비</t>
         </is>
       </c>
       <c r="C70" s="140" t="n"/>
@@ -2765,15 +2762,15 @@
       <c r="H70" s="140" t="n"/>
       <c r="I70" s="140" t="n"/>
       <c r="J70" s="122">
-        <f>SUM(C67:I67)</f>
+        <f>SUM(C66:I66)</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="82">
       <c r="A71" s="88" t="n"/>
-      <c r="B71" s="61" t="inlineStr">
-        <is>
-          <t>120대수술비</t>
+      <c r="B71" s="72" t="inlineStr">
+        <is>
+          <t>심장수술비</t>
         </is>
       </c>
       <c r="C71" s="140" t="n"/>
@@ -2783,88 +2780,88 @@
       <c r="G71" s="140" t="n"/>
       <c r="H71" s="140" t="n"/>
       <c r="I71" s="140" t="n"/>
-      <c r="J71" s="141">
-        <f>SUM(C68:I68)</f>
+      <c r="J71" s="122">
+        <f>SUM(C67:I67)</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" s="82">
       <c r="A72" s="88" t="n"/>
-      <c r="B72" s="73" t="inlineStr">
-        <is>
-          <t>5대기관 수술비 관혈</t>
-        </is>
-      </c>
-      <c r="C72" s="123" t="n"/>
-      <c r="D72" s="123" t="n"/>
-      <c r="E72" s="123" t="n"/>
-      <c r="F72" s="123" t="n"/>
-      <c r="G72" s="123" t="n"/>
-      <c r="H72" s="123" t="n"/>
-      <c r="I72" s="123" t="n"/>
-      <c r="J72" s="120">
-        <f>SUM(C69:I69)</f>
+      <c r="B72" s="61" t="inlineStr">
+        <is>
+          <t>120대수술비</t>
+        </is>
+      </c>
+      <c r="C72" s="140" t="n"/>
+      <c r="D72" s="140" t="n"/>
+      <c r="E72" s="140" t="n"/>
+      <c r="F72" s="140" t="n"/>
+      <c r="G72" s="140" t="n"/>
+      <c r="H72" s="140" t="n"/>
+      <c r="I72" s="140" t="n"/>
+      <c r="J72" s="141">
+        <f>SUM(C68:I68)</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="82">
       <c r="A73" s="88" t="n"/>
-      <c r="B73" s="74" t="inlineStr">
+      <c r="B73" s="73" t="inlineStr">
+        <is>
+          <t>5대기관 수술비 관혈</t>
+        </is>
+      </c>
+      <c r="C73" s="123" t="n"/>
+      <c r="D73" s="123" t="n"/>
+      <c r="E73" s="123" t="n"/>
+      <c r="F73" s="123" t="n"/>
+      <c r="G73" s="123" t="n"/>
+      <c r="H73" s="123" t="n"/>
+      <c r="I73" s="123" t="n"/>
+      <c r="J73" s="120">
+        <f>SUM(C69:I69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="16.5" customHeight="1" s="82">
+      <c r="A74" s="88" t="n"/>
+      <c r="B74" s="74" t="inlineStr">
         <is>
           <t>5대기관 수술비 비관혈</t>
         </is>
       </c>
-      <c r="C73" s="117" t="n"/>
-      <c r="D73" s="117" t="n"/>
-      <c r="E73" s="117" t="n"/>
-      <c r="F73" s="117" t="n"/>
-      <c r="G73" s="117" t="n"/>
-      <c r="H73" s="117" t="n"/>
-      <c r="I73" s="117" t="n"/>
-      <c r="J73" s="118">
+      <c r="C74" s="117" t="n"/>
+      <c r="D74" s="117" t="n"/>
+      <c r="E74" s="117" t="n"/>
+      <c r="F74" s="117" t="n"/>
+      <c r="G74" s="117" t="n"/>
+      <c r="H74" s="117" t="n"/>
+      <c r="I74" s="117" t="n"/>
+      <c r="J74" s="118">
         <f>SUM(C70:I70)</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="16.5" customHeight="1" s="82">
-      <c r="A74" s="87" t="inlineStr">
+    <row r="75" ht="16.5" customHeight="1" s="82">
+      <c r="A75" s="87" t="inlineStr">
         <is>
           <t>운전자</t>
         </is>
       </c>
-      <c r="B74" s="28" t="inlineStr">
+      <c r="B75" s="28" t="inlineStr">
         <is>
           <t>대인</t>
         </is>
       </c>
-      <c r="C74" s="102" t="n"/>
-      <c r="D74" s="102" t="n"/>
-      <c r="E74" s="102" t="n"/>
-      <c r="F74" s="102" t="n"/>
-      <c r="G74" s="102" t="n"/>
-      <c r="H74" s="102" t="n"/>
-      <c r="I74" s="102" t="n"/>
-      <c r="J74" s="120">
+      <c r="C75" s="102" t="n"/>
+      <c r="D75" s="102" t="n"/>
+      <c r="E75" s="102" t="n"/>
+      <c r="F75" s="102" t="n"/>
+      <c r="G75" s="102" t="n"/>
+      <c r="H75" s="102" t="n"/>
+      <c r="I75" s="102" t="n"/>
+      <c r="J75" s="120">
         <f>SUM(C71:I71)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" ht="16.5" customHeight="1" s="82">
-      <c r="A75" s="88" t="n"/>
-      <c r="B75" s="31" t="inlineStr">
-        <is>
-          <t>대물</t>
-        </is>
-      </c>
-      <c r="C75" s="130" t="n"/>
-      <c r="D75" s="130" t="n"/>
-      <c r="E75" s="130" t="n"/>
-      <c r="F75" s="130" t="n"/>
-      <c r="G75" s="130" t="n"/>
-      <c r="H75" s="130" t="n"/>
-      <c r="I75" s="130" t="n"/>
-      <c r="J75" s="122">
-        <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
@@ -2872,7 +2869,7 @@
       <c r="A76" s="88" t="n"/>
       <c r="B76" s="31" t="inlineStr">
         <is>
-          <t>합의금</t>
+          <t>대물</t>
         </is>
       </c>
       <c r="C76" s="130" t="n"/>
@@ -2883,15 +2880,15 @@
       <c r="H76" s="130" t="n"/>
       <c r="I76" s="130" t="n"/>
       <c r="J76" s="122">
-        <f>SUM(C73:I73)</f>
+        <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="82">
       <c r="A77" s="88" t="n"/>
-      <c r="B77" s="66" t="inlineStr">
-        <is>
-          <t>6주미만</t>
+      <c r="B77" s="31" t="inlineStr">
+        <is>
+          <t>합의금</t>
         </is>
       </c>
       <c r="C77" s="130" t="n"/>
@@ -2902,15 +2899,15 @@
       <c r="H77" s="130" t="n"/>
       <c r="I77" s="130" t="n"/>
       <c r="J77" s="122">
-        <f>SUM(C74:I74)</f>
+        <f>SUM(C73:I73)</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16.5" customHeight="1" s="82">
       <c r="A78" s="88" t="n"/>
-      <c r="B78" s="31" t="inlineStr">
-        <is>
-          <t>변호사</t>
+      <c r="B78" s="66" t="inlineStr">
+        <is>
+          <t>6주미만</t>
         </is>
       </c>
       <c r="C78" s="130" t="n"/>
@@ -2921,320 +2918,339 @@
       <c r="H78" s="130" t="n"/>
       <c r="I78" s="130" t="n"/>
       <c r="J78" s="122">
+        <f>SUM(C74:I74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="17.25" customHeight="1" s="82">
+      <c r="A79" s="88" t="n"/>
+      <c r="B79" s="31" t="inlineStr">
+        <is>
+          <t>변호사</t>
+        </is>
+      </c>
+      <c r="C79" s="130" t="n"/>
+      <c r="D79" s="130" t="n"/>
+      <c r="E79" s="130" t="n"/>
+      <c r="F79" s="130" t="n"/>
+      <c r="G79" s="130" t="n"/>
+      <c r="H79" s="130" t="n"/>
+      <c r="I79" s="130" t="n"/>
+      <c r="J79" s="122">
         <f>SUM(C75:I75)</f>
         <v/>
       </c>
     </row>
-    <row r="79" ht="17.25" customHeight="1" s="82">
-      <c r="A79" s="89" t="n"/>
-      <c r="B79" s="25" t="inlineStr">
+    <row r="80" ht="17.25" customHeight="1" s="82">
+      <c r="A80" s="89" t="n"/>
+      <c r="B80" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C79" s="142" t="n"/>
-      <c r="D79" s="142" t="n"/>
-      <c r="E79" s="142" t="n"/>
-      <c r="F79" s="142" t="n"/>
-      <c r="G79" s="142" t="n"/>
-      <c r="H79" s="142" t="n"/>
-      <c r="I79" s="142" t="n"/>
-      <c r="J79" s="118">
+      <c r="C80" s="142" t="n"/>
+      <c r="D80" s="142" t="n"/>
+      <c r="E80" s="142" t="n"/>
+      <c r="F80" s="142" t="n"/>
+      <c r="G80" s="142" t="n"/>
+      <c r="H80" s="142" t="n"/>
+      <c r="I80" s="142" t="n"/>
+      <c r="J80" s="118">
         <f>SUM(C76:I76)</f>
         <v/>
       </c>
     </row>
-    <row r="80" ht="17.25" customHeight="1" s="82">
-      <c r="A80" s="87" t="inlineStr">
+    <row r="81" ht="17.25" customHeight="1" s="82">
+      <c r="A81" s="87" t="inlineStr">
         <is>
           <t>골 절</t>
         </is>
       </c>
-      <c r="B80" s="65" t="inlineStr">
+      <c r="B81" s="65" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C80" s="136" t="n"/>
-      <c r="D80" s="136" t="n"/>
-      <c r="E80" s="136" t="n"/>
-      <c r="F80" s="136" t="n"/>
-      <c r="G80" s="136" t="n"/>
-      <c r="H80" s="136" t="n"/>
-      <c r="I80" s="136" t="n"/>
-      <c r="J80" s="116">
+      <c r="C81" s="136" t="n"/>
+      <c r="D81" s="136" t="n"/>
+      <c r="E81" s="136" t="n"/>
+      <c r="F81" s="136" t="n"/>
+      <c r="G81" s="136" t="n"/>
+      <c r="H81" s="136" t="n"/>
+      <c r="I81" s="136" t="n"/>
+      <c r="J81" s="116">
         <f>SUM(C77:I77)</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="17.25" customHeight="1" s="82">
-      <c r="A81" s="88" t="n"/>
-      <c r="B81" s="60" t="inlineStr">
+    <row r="82" ht="16.5" customHeight="1" s="82">
+      <c r="A82" s="88" t="n"/>
+      <c r="B82" s="60" t="inlineStr">
         <is>
           <t>골절(치아파절제외)</t>
         </is>
       </c>
-      <c r="C81" s="121" t="n"/>
-      <c r="D81" s="121" t="n"/>
-      <c r="E81" s="121" t="n"/>
-      <c r="F81" s="121" t="n"/>
-      <c r="G81" s="121" t="n"/>
-      <c r="H81" s="121" t="n"/>
-      <c r="I81" s="121" t="n"/>
-      <c r="J81" s="122">
+      <c r="C82" s="121" t="n"/>
+      <c r="D82" s="121" t="n"/>
+      <c r="E82" s="121" t="n"/>
+      <c r="F82" s="121" t="n"/>
+      <c r="G82" s="121" t="n"/>
+      <c r="H82" s="121" t="n"/>
+      <c r="I82" s="121" t="n"/>
+      <c r="J82" s="122">
         <f>SUM(C78:I78)</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="16.5" customHeight="1" s="82">
-      <c r="A82" s="89" t="n"/>
-      <c r="B82" s="74" t="inlineStr">
+    <row r="83" ht="17.25" customHeight="1" s="82">
+      <c r="A83" s="89" t="n"/>
+      <c r="B83" s="74" t="inlineStr">
         <is>
           <t>5대골절진단비</t>
         </is>
       </c>
-      <c r="C82" s="117" t="n"/>
-      <c r="D82" s="117" t="n"/>
-      <c r="E82" s="117" t="n"/>
-      <c r="F82" s="117" t="n"/>
-      <c r="G82" s="117" t="n"/>
-      <c r="H82" s="117" t="n"/>
-      <c r="I82" s="117" t="n"/>
-      <c r="J82" s="118">
+      <c r="C83" s="117" t="n"/>
+      <c r="D83" s="117" t="n"/>
+      <c r="E83" s="117" t="n"/>
+      <c r="F83" s="117" t="n"/>
+      <c r="G83" s="117" t="n"/>
+      <c r="H83" s="117" t="n"/>
+      <c r="I83" s="117" t="n"/>
+      <c r="J83" s="118">
         <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="17.25" customHeight="1" s="82">
-      <c r="A83" s="99" t="inlineStr">
+    <row r="84" ht="16.5" customHeight="1" s="82">
+      <c r="A84" s="99" t="inlineStr">
         <is>
           <t>응급실</t>
         </is>
       </c>
-      <c r="B83" s="64" t="inlineStr">
+      <c r="B84" s="64" t="inlineStr">
         <is>
           <t>응급실(응급)</t>
         </is>
       </c>
-      <c r="C83" s="113" t="n"/>
-      <c r="D83" s="113" t="n"/>
-      <c r="E83" s="113" t="n"/>
-      <c r="F83" s="113" t="n"/>
-      <c r="G83" s="113" t="n"/>
-      <c r="H83" s="113" t="n"/>
-      <c r="I83" s="113" t="n"/>
-      <c r="J83" s="114">
+      <c r="C84" s="113" t="n"/>
+      <c r="D84" s="113" t="n"/>
+      <c r="E84" s="113" t="n"/>
+      <c r="F84" s="113" t="n"/>
+      <c r="G84" s="113" t="n"/>
+      <c r="H84" s="113" t="n"/>
+      <c r="I84" s="113" t="n"/>
+      <c r="J84" s="114">
         <f>SUM(C80:I80)</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="16.5" customHeight="1" s="82">
-      <c r="A84" s="92" t="inlineStr">
+    <row r="85" ht="17.25" customHeight="1" s="82">
+      <c r="A85" s="92" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="B84" s="34" t="inlineStr">
+      <c r="B85" s="34" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="C84" s="123" t="n"/>
-      <c r="D84" s="123" t="n"/>
-      <c r="E84" s="123" t="n"/>
-      <c r="F84" s="123" t="n"/>
-      <c r="G84" s="123" t="n"/>
-      <c r="H84" s="123" t="n"/>
-      <c r="I84" s="123" t="n"/>
-      <c r="J84" s="124" t="n"/>
-    </row>
-    <row r="85" ht="17.25" customHeight="1" s="82">
-      <c r="A85" s="87" t="inlineStr">
+      <c r="C85" s="123" t="n"/>
+      <c r="D85" s="123" t="n"/>
+      <c r="E85" s="123" t="n"/>
+      <c r="F85" s="123" t="n"/>
+      <c r="G85" s="123" t="n"/>
+      <c r="H85" s="123" t="n"/>
+      <c r="I85" s="123" t="n"/>
+      <c r="J85" s="124" t="n"/>
+    </row>
+    <row r="86" ht="16.5" customHeight="1" s="82">
+      <c r="A86" s="87" t="inlineStr">
         <is>
           <t>화상</t>
         </is>
       </c>
-      <c r="B85" s="28" t="inlineStr">
+      <c r="B86" s="28" t="inlineStr">
         <is>
           <t>화상진단비</t>
         </is>
       </c>
-      <c r="C85" s="119" t="n"/>
-      <c r="D85" s="119" t="n"/>
-      <c r="E85" s="119" t="n"/>
-      <c r="F85" s="119" t="n"/>
-      <c r="G85" s="119" t="n"/>
-      <c r="H85" s="119" t="n"/>
-      <c r="I85" s="119" t="n"/>
-      <c r="J85" s="120">
+      <c r="C86" s="119" t="n"/>
+      <c r="D86" s="119" t="n"/>
+      <c r="E86" s="119" t="n"/>
+      <c r="F86" s="119" t="n"/>
+      <c r="G86" s="119" t="n"/>
+      <c r="H86" s="119" t="n"/>
+      <c r="I86" s="119" t="n"/>
+      <c r="J86" s="120">
         <f>SUM(C82:I82)</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="16.5" customHeight="1" s="82">
-      <c r="A86" s="89" t="n"/>
-      <c r="B86" s="25" t="inlineStr">
+    <row r="87" ht="16.5" customHeight="1" s="82">
+      <c r="A87" s="89" t="n"/>
+      <c r="B87" s="25" t="inlineStr">
         <is>
           <t>중증화상진단비</t>
         </is>
       </c>
-      <c r="C86" s="117" t="n"/>
-      <c r="D86" s="117" t="n"/>
-      <c r="E86" s="117" t="n"/>
-      <c r="F86" s="117" t="n"/>
-      <c r="G86" s="117" t="n"/>
-      <c r="H86" s="117" t="n"/>
-      <c r="I86" s="117" t="n"/>
-      <c r="J86" s="118">
+      <c r="C87" s="117" t="n"/>
+      <c r="D87" s="117" t="n"/>
+      <c r="E87" s="117" t="n"/>
+      <c r="F87" s="117" t="n"/>
+      <c r="G87" s="117" t="n"/>
+      <c r="H87" s="117" t="n"/>
+      <c r="I87" s="117" t="n"/>
+      <c r="J87" s="118">
         <f>SUM(C83:I83)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="16.5" customHeight="1" s="82">
-      <c r="A87" s="87" t="inlineStr">
+    <row r="88" ht="17.25" customHeight="1" s="82">
+      <c r="A88" s="87" t="inlineStr">
         <is>
           <t>깁스</t>
         </is>
       </c>
-      <c r="B87" s="95" t="inlineStr">
+      <c r="B88" s="95" t="inlineStr">
         <is>
           <t>반깁스</t>
         </is>
       </c>
-      <c r="C87" s="119" t="n"/>
-      <c r="D87" s="119" t="n"/>
-      <c r="E87" s="119" t="n"/>
-      <c r="F87" s="119" t="n"/>
-      <c r="G87" s="119" t="n"/>
-      <c r="H87" s="119" t="n"/>
-      <c r="I87" s="119" t="n"/>
-      <c r="J87" s="120">
+      <c r="C88" s="119" t="n"/>
+      <c r="D88" s="119" t="n"/>
+      <c r="E88" s="119" t="n"/>
+      <c r="F88" s="119" t="n"/>
+      <c r="G88" s="119" t="n"/>
+      <c r="H88" s="119" t="n"/>
+      <c r="I88" s="119" t="n"/>
+      <c r="J88" s="120">
         <f>SUM(C84:I84)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="17.25" customHeight="1" s="82">
-      <c r="A88" s="89" t="n"/>
-      <c r="B88" s="57" t="inlineStr">
+    <row r="89" ht="17.25" customHeight="1" s="82">
+      <c r="A89" s="89" t="n"/>
+      <c r="B89" s="57" t="inlineStr">
         <is>
           <t>깁스진단비</t>
         </is>
       </c>
-      <c r="C88" s="117" t="n"/>
-      <c r="D88" s="117" t="n"/>
-      <c r="E88" s="117" t="n"/>
-      <c r="F88" s="117" t="n"/>
-      <c r="G88" s="117" t="n"/>
-      <c r="H88" s="117" t="n"/>
-      <c r="I88" s="117" t="n"/>
-      <c r="J88" s="118">
+      <c r="C89" s="117" t="n"/>
+      <c r="D89" s="117" t="n"/>
+      <c r="E89" s="117" t="n"/>
+      <c r="F89" s="117" t="n"/>
+      <c r="G89" s="117" t="n"/>
+      <c r="H89" s="117" t="n"/>
+      <c r="I89" s="117" t="n"/>
+      <c r="J89" s="118">
         <f>SUM(C85:I85)</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="17.25" customHeight="1" s="82">
-      <c r="A89" s="87" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="87" t="inlineStr">
         <is>
           <t>실손</t>
         </is>
       </c>
-      <c r="B89" s="95" t="inlineStr">
+      <c r="B90" s="95" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="C89" s="143" t="n"/>
-      <c r="D89" s="143" t="n"/>
-      <c r="E89" s="143" t="n"/>
-      <c r="F89" s="143" t="n"/>
-      <c r="G89" s="143" t="n"/>
-      <c r="H89" s="143" t="n"/>
-      <c r="I89" s="143" t="n"/>
-      <c r="J89" s="120">
+      <c r="C90" s="143" t="n"/>
+      <c r="D90" s="143" t="n"/>
+      <c r="E90" s="143" t="n"/>
+      <c r="F90" s="143" t="n"/>
+      <c r="G90" s="143" t="n"/>
+      <c r="H90" s="143" t="n"/>
+      <c r="I90" s="143" t="n"/>
+      <c r="J90" s="120">
         <f>SUM(C86:I86)</f>
         <v/>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="88" t="n"/>
-      <c r="B90" s="60" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="88" t="n"/>
+      <c r="B91" s="60" t="inlineStr">
         <is>
           <t>통원</t>
         </is>
       </c>
-      <c r="C90" s="144" t="n"/>
-      <c r="D90" s="144" t="n"/>
-      <c r="E90" s="144" t="n"/>
-      <c r="F90" s="144" t="n"/>
-      <c r="G90" s="144" t="n"/>
-      <c r="H90" s="144" t="n"/>
-      <c r="I90" s="144" t="n"/>
-      <c r="J90" s="122">
+      <c r="C91" s="144" t="n"/>
+      <c r="D91" s="144" t="n"/>
+      <c r="E91" s="144" t="n"/>
+      <c r="F91" s="144" t="n"/>
+      <c r="G91" s="144" t="n"/>
+      <c r="H91" s="144" t="n"/>
+      <c r="I91" s="144" t="n"/>
+      <c r="J91" s="122">
         <f>SUM(C87:I87)</f>
         <v/>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="89" t="n"/>
-      <c r="B91" s="22" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="89" t="n"/>
+      <c r="B92" s="22" t="inlineStr">
         <is>
           <t>약값</t>
         </is>
       </c>
-      <c r="C91" s="115" t="n"/>
-      <c r="D91" s="115" t="n"/>
-      <c r="E91" s="115" t="n"/>
-      <c r="F91" s="115" t="n"/>
-      <c r="G91" s="115" t="n"/>
-      <c r="H91" s="115" t="n"/>
-      <c r="I91" s="145" t="n"/>
-      <c r="J91" s="122">
+      <c r="C92" s="115" t="n"/>
+      <c r="D92" s="115" t="n"/>
+      <c r="E92" s="115" t="n"/>
+      <c r="F92" s="115" t="n"/>
+      <c r="G92" s="115" t="n"/>
+      <c r="H92" s="115" t="n"/>
+      <c r="I92" s="145" t="n"/>
+      <c r="J92" s="122">
         <f>SUM(C88:I88)</f>
         <v/>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="87" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="87" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B92" s="79" t="inlineStr">
+      <c r="B93" s="79" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C92" s="146" t="n"/>
-      <c r="D92" s="146" t="n"/>
-      <c r="E92" s="146" t="n"/>
-      <c r="F92" s="146" t="n"/>
-      <c r="G92" s="146" t="n"/>
-      <c r="H92" s="146" t="n"/>
-      <c r="I92" s="146" t="n"/>
-      <c r="J92" s="147">
+      <c r="C93" s="146" t="n"/>
+      <c r="D93" s="146" t="n"/>
+      <c r="E93" s="146" t="n"/>
+      <c r="F93" s="146" t="n"/>
+      <c r="G93" s="146" t="n"/>
+      <c r="H93" s="146" t="n"/>
+      <c r="I93" s="146" t="n"/>
+      <c r="J93" s="147">
         <f>SUM(C89:I89)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A87:A88"/>
     <mergeCell ref="A74:A79"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A49:A58"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A87:A88"/>
     <mergeCell ref="A59:A73"/>
     <mergeCell ref="A89:A91"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A37:A48"/>
     <mergeCell ref="A29:A36"/>
     <mergeCell ref="A15:A28"/>
+    <mergeCell ref="A11:A14"/>
     <mergeCell ref="A80:A82"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A85:A86"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A49:A58"/>
+    <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>
@@ -3262,7 +3278,7 @@
       </c>
     </row>
     <row r="3" ht="17.1" customHeight="1" s="82">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3274,7 +3290,7 @@
       </c>
     </row>
     <row r="4" ht="17.1" customHeight="1" s="82">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3286,7 +3302,7 @@
       </c>
     </row>
     <row r="5" ht="17.1" customHeight="1" s="82">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3298,7 +3314,7 @@
       </c>
     </row>
     <row r="6" ht="17.1" customHeight="1" s="82">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3310,7 +3326,7 @@
       </c>
     </row>
     <row r="7" ht="17.1" customHeight="1" s="82">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3322,7 +3338,7 @@
       </c>
     </row>
     <row r="8" ht="17.1" customHeight="1" s="82">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -3334,7 +3350,7 @@
       </c>
     </row>
     <row r="9" ht="17.1" customHeight="1" s="82">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -3346,7 +3362,7 @@
       </c>
     </row>
     <row r="10" ht="17.1" customHeight="1" s="82">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -3358,7 +3374,7 @@
       </c>
     </row>
     <row r="11" ht="17.1" customHeight="1" s="82">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -3370,7 +3386,7 @@
       </c>
     </row>
     <row r="12" ht="17.1" customHeight="1" s="82">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -3382,7 +3398,7 @@
       </c>
     </row>
     <row r="13" ht="17.1" customHeight="1" s="82">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>11</t>
         </is>
@@ -3394,7 +3410,7 @@
       </c>
     </row>
     <row r="14" ht="17.1" customHeight="1" s="82">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>12</t>
         </is>

--- a/master.xlsx
+++ b/master.xlsx
@@ -167,7 +167,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -805,13 +805,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1240,6 +1260,14 @@
     <xf numFmtId="164" fontId="5" fillId="6" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1430,7 +1458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="82" min="1" max="1"/>
@@ -2320,7 +2348,7 @@
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="82">
-      <c r="A48" s="88" t="n"/>
+      <c r="A48" s="89" t="n"/>
       <c r="B48" s="16" t="inlineStr">
         <is>
           <t>중대한 급성심근</t>
@@ -2339,7 +2367,11 @@
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="82">
-      <c r="A49" s="89" t="n"/>
+      <c r="A49" s="99" t="inlineStr">
+        <is>
+          <t>일당</t>
+        </is>
+      </c>
       <c r="B49" s="64" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
@@ -2358,11 +2390,7 @@
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="82">
-      <c r="A50" s="87" t="inlineStr">
-        <is>
-          <t>일당</t>
-        </is>
-      </c>
+      <c r="A50" s="88" t="n"/>
       <c r="B50" s="95" t="inlineStr">
         <is>
           <t>질병일당</t>
@@ -2456,11 +2484,11 @@
         <v/>
       </c>
     </row>
-    <row r="55" ht="17.25" customHeight="1" s="82">
+    <row r="55" ht="16.5" customHeight="1" s="82">
       <c r="A55" s="88" t="n"/>
       <c r="B55" s="31" t="inlineStr">
         <is>
-          <t>간호통합병동</t>
+          <t>간병인지원일당</t>
         </is>
       </c>
       <c r="C55" s="121" t="n"/>
@@ -2470,16 +2498,13 @@
       <c r="G55" s="121" t="n"/>
       <c r="H55" s="121" t="n"/>
       <c r="I55" s="121" t="n"/>
-      <c r="J55" s="122">
-        <f>SUM(C51:I51)</f>
-        <v/>
-      </c>
+      <c r="J55" s="122" t="n"/>
     </row>
     <row r="56" ht="16.5" customHeight="1" s="82">
       <c r="A56" s="88" t="n"/>
-      <c r="B56" s="66" t="inlineStr">
-        <is>
-          <t>1인실 종합병원</t>
+      <c r="B56" s="31" t="inlineStr">
+        <is>
+          <t>간호통합병동</t>
         </is>
       </c>
       <c r="C56" s="121" t="n"/>
@@ -2490,7 +2515,7 @@
       <c r="H56" s="121" t="n"/>
       <c r="I56" s="121" t="n"/>
       <c r="J56" s="122">
-        <f>SUM(C52:I52)</f>
+        <f>SUM(C51:I51)</f>
         <v/>
       </c>
     </row>
@@ -2498,7 +2523,7 @@
       <c r="A57" s="88" t="n"/>
       <c r="B57" s="66" t="inlineStr">
         <is>
-          <t>1인실 상급병원</t>
+          <t>1인실 종합병원</t>
         </is>
       </c>
       <c r="C57" s="121" t="n"/>
@@ -2509,15 +2534,15 @@
       <c r="H57" s="121" t="n"/>
       <c r="I57" s="121" t="n"/>
       <c r="J57" s="122">
-        <f>SUM(C53:I53)</f>
+        <f>SUM(C52:I52)</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="16.5" customHeight="1" s="82">
       <c r="A58" s="88" t="n"/>
-      <c r="B58" s="31" t="inlineStr">
-        <is>
-          <t>질병중환자실</t>
+      <c r="B58" s="66" t="inlineStr">
+        <is>
+          <t>1인실 상급병원</t>
         </is>
       </c>
       <c r="C58" s="121" t="n"/>
@@ -2528,134 +2553,131 @@
       <c r="H58" s="121" t="n"/>
       <c r="I58" s="121" t="n"/>
       <c r="J58" s="122">
+        <f>SUM(C53:I53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="16.5" customHeight="1" s="82">
+      <c r="A59" s="88" t="n"/>
+      <c r="B59" s="31" t="inlineStr">
+        <is>
+          <t>질병중환자실</t>
+        </is>
+      </c>
+      <c r="C59" s="121" t="n"/>
+      <c r="D59" s="121" t="n"/>
+      <c r="E59" s="121" t="n"/>
+      <c r="F59" s="121" t="n"/>
+      <c r="G59" s="121" t="n"/>
+      <c r="H59" s="121" t="n"/>
+      <c r="I59" s="121" t="n"/>
+      <c r="J59" s="122">
         <f>SUM(C54:I54)</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="16.5" customHeight="1" s="82">
-      <c r="A59" s="89" t="n"/>
-      <c r="B59" s="25" t="inlineStr">
+    <row r="60" ht="16.5" customHeight="1" s="82">
+      <c r="A60" s="89" t="n"/>
+      <c r="B60" s="25" t="inlineStr">
         <is>
           <t>상해중환자실</t>
         </is>
       </c>
-      <c r="C59" s="117" t="n"/>
-      <c r="D59" s="117" t="n"/>
-      <c r="E59" s="117" t="n"/>
-      <c r="F59" s="117" t="n"/>
-      <c r="G59" s="117" t="n"/>
-      <c r="H59" s="117" t="n"/>
-      <c r="I59" s="117" t="n"/>
-      <c r="J59" s="118">
+      <c r="C60" s="117" t="n"/>
+      <c r="D60" s="117" t="n"/>
+      <c r="E60" s="117" t="n"/>
+      <c r="F60" s="117" t="n"/>
+      <c r="G60" s="117" t="n"/>
+      <c r="H60" s="117" t="n"/>
+      <c r="I60" s="117" t="n"/>
+      <c r="J60" s="118">
         <f>SUM(C55:I55)</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="16.5" customHeight="1" s="82">
-      <c r="A60" s="92" t="inlineStr">
-        <is>
-          <t>수술비</t>
-        </is>
-      </c>
-      <c r="B60" s="95" t="inlineStr">
+    <row r="61" ht="16.5" customHeight="1" s="82">
+      <c r="A61" s="148" t="inlineStr">
+        <is>
+          <t>수술</t>
+        </is>
+      </c>
+      <c r="B61" s="95" t="inlineStr">
         <is>
           <t>상해수술비</t>
         </is>
       </c>
-      <c r="C60" s="119" t="n"/>
-      <c r="D60" s="119" t="n"/>
-      <c r="E60" s="119" t="n"/>
-      <c r="F60" s="119" t="n"/>
-      <c r="G60" s="119" t="n"/>
-      <c r="H60" s="119" t="n"/>
-      <c r="I60" s="119" t="n"/>
-      <c r="J60" s="120">
+      <c r="C61" s="119" t="n"/>
+      <c r="D61" s="119" t="n"/>
+      <c r="E61" s="119" t="n"/>
+      <c r="F61" s="119" t="n"/>
+      <c r="G61" s="119" t="n"/>
+      <c r="H61" s="119" t="n"/>
+      <c r="I61" s="119" t="n"/>
+      <c r="J61" s="120">
         <f>SUM(C56:I56)</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="16.5" customHeight="1" s="82">
-      <c r="A61" s="88" t="n"/>
-      <c r="B61" s="65" t="inlineStr">
+    <row r="62" ht="17.25" customHeight="1" s="82">
+      <c r="A62" s="149" t="n"/>
+      <c r="B62" s="65" t="inlineStr">
         <is>
           <t>중대한상해수술비</t>
-        </is>
-      </c>
-      <c r="C61" s="136" t="n"/>
-      <c r="D61" s="136" t="n"/>
-      <c r="E61" s="136" t="n"/>
-      <c r="F61" s="136" t="n"/>
-      <c r="G61" s="136" t="n"/>
-      <c r="H61" s="136" t="n"/>
-      <c r="I61" s="136" t="n"/>
-      <c r="J61" s="122">
-        <f>SUM(C57:I57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="17.25" customHeight="1" s="82">
-      <c r="A62" s="88" t="n"/>
-      <c r="B62" s="60" t="inlineStr">
-        <is>
-          <t>상해 종수술비(1-5종)</t>
         </is>
       </c>
       <c r="C62" s="136" t="n"/>
       <c r="D62" s="136" t="n"/>
       <c r="E62" s="136" t="n"/>
-      <c r="F62" s="137" t="n"/>
+      <c r="F62" s="136" t="n"/>
       <c r="G62" s="136" t="n"/>
       <c r="H62" s="136" t="n"/>
       <c r="I62" s="136" t="n"/>
-      <c r="J62" s="122" t="inlineStr">
+      <c r="J62" s="122">
+        <f>SUM(C57:I57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="17.25" customHeight="1" s="82">
+      <c r="A63" s="149" t="n"/>
+      <c r="B63" s="60" t="inlineStr">
+        <is>
+          <t>상해 종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="C63" s="136" t="n"/>
+      <c r="D63" s="136" t="n"/>
+      <c r="E63" s="136" t="n"/>
+      <c r="F63" s="137" t="n"/>
+      <c r="G63" s="136" t="n"/>
+      <c r="H63" s="136" t="n"/>
+      <c r="I63" s="136" t="n"/>
+      <c r="J63" s="122" t="inlineStr">
         <is>
           <t>/ / / / /</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="16.5" customHeight="1" s="82">
-      <c r="A63" s="88" t="n"/>
-      <c r="B63" s="60" t="inlineStr">
+    <row r="64" ht="16.5" customHeight="1" s="82">
+      <c r="A64" s="149" t="n"/>
+      <c r="B64" s="60" t="inlineStr">
+        <is>
+          <t>상해 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C64" s="136" t="n"/>
+      <c r="D64" s="136" t="n"/>
+      <c r="E64" s="136" t="n"/>
+      <c r="F64" s="137" t="n"/>
+      <c r="G64" s="136" t="n"/>
+      <c r="H64" s="136" t="n"/>
+      <c r="I64" s="136" t="n"/>
+      <c r="J64" s="122" t="n"/>
+    </row>
+    <row r="65" ht="16.5" customHeight="1" s="82">
+      <c r="A65" s="149" t="n"/>
+      <c r="B65" s="60" t="inlineStr">
         <is>
           <t>창상봉합술</t>
-        </is>
-      </c>
-      <c r="C63" s="121" t="n"/>
-      <c r="D63" s="121" t="n"/>
-      <c r="E63" s="121" t="n"/>
-      <c r="F63" s="121" t="n"/>
-      <c r="G63" s="121" t="n"/>
-      <c r="H63" s="121" t="n"/>
-      <c r="I63" s="121" t="n"/>
-      <c r="J63" s="122">
-        <f>SUM(C59:I59)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="16.5" customHeight="1" s="82">
-      <c r="A64" s="88" t="n"/>
-      <c r="B64" s="60" t="inlineStr">
-        <is>
-          <t>골절수술비</t>
-        </is>
-      </c>
-      <c r="C64" s="121" t="n"/>
-      <c r="D64" s="121" t="n"/>
-      <c r="E64" s="121" t="n"/>
-      <c r="F64" s="121" t="n"/>
-      <c r="G64" s="121" t="n"/>
-      <c r="H64" s="121" t="n"/>
-      <c r="I64" s="121" t="n"/>
-      <c r="J64" s="122">
-        <f>SUM(C60:I60)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="16.5" customHeight="1" s="82">
-      <c r="A65" s="88" t="n"/>
-      <c r="B65" s="69" t="inlineStr">
-        <is>
-          <t>5대골절수술비</t>
         </is>
       </c>
       <c r="C65" s="121" t="n"/>
@@ -2666,130 +2688,127 @@
       <c r="H65" s="121" t="n"/>
       <c r="I65" s="121" t="n"/>
       <c r="J65" s="122">
+        <f>SUM(C59:I59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="16.5" customHeight="1" s="82">
+      <c r="A66" s="149" t="n"/>
+      <c r="B66" s="60" t="inlineStr">
+        <is>
+          <t>골절수술비</t>
+        </is>
+      </c>
+      <c r="C66" s="121" t="n"/>
+      <c r="D66" s="121" t="n"/>
+      <c r="E66" s="121" t="n"/>
+      <c r="F66" s="121" t="n"/>
+      <c r="G66" s="121" t="n"/>
+      <c r="H66" s="121" t="n"/>
+      <c r="I66" s="121" t="n"/>
+      <c r="J66" s="122">
+        <f>SUM(C60:I60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16.5" customHeight="1" s="82">
+      <c r="A67" s="149" t="n"/>
+      <c r="B67" s="69" t="inlineStr">
+        <is>
+          <t>5대골절수술비</t>
+        </is>
+      </c>
+      <c r="C67" s="121" t="n"/>
+      <c r="D67" s="121" t="n"/>
+      <c r="E67" s="121" t="n"/>
+      <c r="F67" s="121" t="n"/>
+      <c r="G67" s="121" t="n"/>
+      <c r="H67" s="121" t="n"/>
+      <c r="I67" s="121" t="n"/>
+      <c r="J67" s="122">
         <f>SUM(C61:I61)</f>
         <v/>
       </c>
     </row>
-    <row r="66" ht="16.5" customHeight="1" s="82">
-      <c r="A66" s="88" t="n"/>
-      <c r="B66" s="57" t="inlineStr">
+    <row r="68" ht="17.25" customHeight="1" s="82">
+      <c r="A68" s="149" t="n"/>
+      <c r="B68" s="57" t="inlineStr">
         <is>
           <t>화상수술비</t>
         </is>
       </c>
-      <c r="C66" s="117" t="n"/>
-      <c r="D66" s="117" t="n"/>
-      <c r="E66" s="117" t="n"/>
-      <c r="F66" s="117" t="n"/>
-      <c r="G66" s="117" t="n"/>
-      <c r="H66" s="117" t="n"/>
-      <c r="I66" s="117" t="n"/>
-      <c r="J66" s="118">
+      <c r="C68" s="117" t="n"/>
+      <c r="D68" s="117" t="n"/>
+      <c r="E68" s="117" t="n"/>
+      <c r="F68" s="117" t="n"/>
+      <c r="G68" s="117" t="n"/>
+      <c r="H68" s="117" t="n"/>
+      <c r="I68" s="117" t="n"/>
+      <c r="J68" s="118">
         <f>SUM(C62:I62)</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="16.5" customHeight="1" s="82">
-      <c r="A67" s="88" t="n"/>
-      <c r="B67" s="65" t="inlineStr">
+    <row r="69" ht="16.5" customHeight="1" s="82">
+      <c r="A69" s="149" t="n"/>
+      <c r="B69" s="65" t="inlineStr">
         <is>
           <t>질병수술비</t>
         </is>
       </c>
-      <c r="C67" s="136" t="n"/>
-      <c r="D67" s="136" t="n"/>
-      <c r="E67" s="136" t="n"/>
-      <c r="F67" s="136" t="n"/>
-      <c r="G67" s="136" t="n"/>
-      <c r="H67" s="136" t="n"/>
-      <c r="I67" s="138" t="n"/>
-      <c r="J67" s="116">
+      <c r="C69" s="136" t="n"/>
+      <c r="D69" s="136" t="n"/>
+      <c r="E69" s="136" t="n"/>
+      <c r="F69" s="136" t="n"/>
+      <c r="G69" s="136" t="n"/>
+      <c r="H69" s="136" t="n"/>
+      <c r="I69" s="138" t="n"/>
+      <c r="J69" s="116">
         <f>SUM(C63:I63)</f>
         <v/>
       </c>
     </row>
-    <row r="68" ht="17.25" customHeight="1" s="82">
-      <c r="A68" s="88" t="n"/>
-      <c r="B68" s="60" t="inlineStr">
+    <row r="70" ht="16.5" customHeight="1" s="82">
+      <c r="A70" s="149" t="n"/>
+      <c r="B70" s="60" t="inlineStr">
         <is>
           <t>질병 종수술비(1-5종)</t>
         </is>
       </c>
-      <c r="C68" s="121" t="n"/>
-      <c r="D68" s="121" t="n"/>
-      <c r="E68" s="121" t="n"/>
-      <c r="F68" s="139" t="n"/>
-      <c r="G68" s="121" t="n"/>
-      <c r="H68" s="121" t="n"/>
-      <c r="I68" s="121" t="n"/>
-      <c r="J68" s="122" t="inlineStr">
+      <c r="C70" s="121" t="n"/>
+      <c r="D70" s="121" t="n"/>
+      <c r="E70" s="121" t="n"/>
+      <c r="F70" s="139" t="n"/>
+      <c r="G70" s="121" t="n"/>
+      <c r="H70" s="121" t="n"/>
+      <c r="I70" s="121" t="n"/>
+      <c r="J70" s="122" t="inlineStr">
         <is>
           <t>/ / / / /</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="16.5" customHeight="1" s="82">
-      <c r="A69" s="88" t="n"/>
-      <c r="B69" s="72" t="inlineStr">
+    <row r="71" ht="16.5" customHeight="1" s="82">
+      <c r="A71" s="149" t="n"/>
+      <c r="B71" s="60" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C71" s="121" t="n"/>
+      <c r="D71" s="121" t="n"/>
+      <c r="E71" s="121" t="n"/>
+      <c r="F71" s="139" t="n"/>
+      <c r="G71" s="121" t="n"/>
+      <c r="H71" s="121" t="n"/>
+      <c r="I71" s="121" t="n"/>
+      <c r="J71" s="122" t="n"/>
+    </row>
+    <row r="72" ht="16.5" customHeight="1" s="82">
+      <c r="A72" s="149" t="n"/>
+      <c r="B72" s="72" t="inlineStr">
         <is>
           <t>뇌혈관수술비</t>
-        </is>
-      </c>
-      <c r="C69" s="140" t="n"/>
-      <c r="D69" s="140" t="n"/>
-      <c r="E69" s="140" t="n"/>
-      <c r="F69" s="140" t="n"/>
-      <c r="G69" s="140" t="n"/>
-      <c r="H69" s="140" t="n"/>
-      <c r="I69" s="140" t="n"/>
-      <c r="J69" s="122">
-        <f>SUM(C65:I65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" ht="17.25" customHeight="1" s="82">
-      <c r="A70" s="88" t="n"/>
-      <c r="B70" s="72" t="inlineStr">
-        <is>
-          <t>허혈성수술비</t>
-        </is>
-      </c>
-      <c r="C70" s="140" t="n"/>
-      <c r="D70" s="140" t="n"/>
-      <c r="E70" s="140" t="n"/>
-      <c r="F70" s="140" t="n"/>
-      <c r="G70" s="140" t="n"/>
-      <c r="H70" s="140" t="n"/>
-      <c r="I70" s="140" t="n"/>
-      <c r="J70" s="122">
-        <f>SUM(C66:I66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="16.5" customHeight="1" s="82">
-      <c r="A71" s="88" t="n"/>
-      <c r="B71" s="72" t="inlineStr">
-        <is>
-          <t>심장수술비</t>
-        </is>
-      </c>
-      <c r="C71" s="140" t="n"/>
-      <c r="D71" s="140" t="n"/>
-      <c r="E71" s="140" t="n"/>
-      <c r="F71" s="140" t="n"/>
-      <c r="G71" s="140" t="n"/>
-      <c r="H71" s="140" t="n"/>
-      <c r="I71" s="140" t="n"/>
-      <c r="J71" s="122">
-        <f>SUM(C67:I67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="16.5" customHeight="1" s="82">
-      <c r="A72" s="88" t="n"/>
-      <c r="B72" s="61" t="inlineStr">
-        <is>
-          <t>120대수술비</t>
         </is>
       </c>
       <c r="C72" s="140" t="n"/>
@@ -2799,134 +2818,134 @@
       <c r="G72" s="140" t="n"/>
       <c r="H72" s="140" t="n"/>
       <c r="I72" s="140" t="n"/>
-      <c r="J72" s="141">
+      <c r="J72" s="122">
+        <f>SUM(C65:I65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="16.5" customHeight="1" s="82">
+      <c r="A73" s="149" t="n"/>
+      <c r="B73" s="72" t="inlineStr">
+        <is>
+          <t>허혈성수술비</t>
+        </is>
+      </c>
+      <c r="C73" s="140" t="n"/>
+      <c r="D73" s="140" t="n"/>
+      <c r="E73" s="140" t="n"/>
+      <c r="F73" s="140" t="n"/>
+      <c r="G73" s="140" t="n"/>
+      <c r="H73" s="140" t="n"/>
+      <c r="I73" s="140" t="n"/>
+      <c r="J73" s="122">
+        <f>SUM(C66:I66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="16.5" customHeight="1" s="82">
+      <c r="A74" s="149" t="n"/>
+      <c r="B74" s="72" t="inlineStr">
+        <is>
+          <t>심장수술비</t>
+        </is>
+      </c>
+      <c r="C74" s="140" t="n"/>
+      <c r="D74" s="140" t="n"/>
+      <c r="E74" s="140" t="n"/>
+      <c r="F74" s="140" t="n"/>
+      <c r="G74" s="140" t="n"/>
+      <c r="H74" s="140" t="n"/>
+      <c r="I74" s="140" t="n"/>
+      <c r="J74" s="122">
+        <f>SUM(C67:I67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="16.5" customHeight="1" s="82">
+      <c r="A75" s="149" t="n"/>
+      <c r="B75" s="61" t="inlineStr">
+        <is>
+          <t>120대수술비</t>
+        </is>
+      </c>
+      <c r="C75" s="140" t="n"/>
+      <c r="D75" s="140" t="n"/>
+      <c r="E75" s="140" t="n"/>
+      <c r="F75" s="140" t="n"/>
+      <c r="G75" s="140" t="n"/>
+      <c r="H75" s="140" t="n"/>
+      <c r="I75" s="140" t="n"/>
+      <c r="J75" s="141">
         <f>SUM(C68:I68)</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="16.5" customHeight="1" s="82">
-      <c r="A73" s="88" t="n"/>
-      <c r="B73" s="73" t="inlineStr">
+    <row r="76" ht="17.25" customHeight="1" s="82">
+      <c r="A76" s="149" t="n"/>
+      <c r="B76" s="73" t="inlineStr">
         <is>
           <t>5대기관 수술비 관혈</t>
         </is>
       </c>
-      <c r="C73" s="123" t="n"/>
-      <c r="D73" s="123" t="n"/>
-      <c r="E73" s="123" t="n"/>
-      <c r="F73" s="123" t="n"/>
-      <c r="G73" s="123" t="n"/>
-      <c r="H73" s="123" t="n"/>
-      <c r="I73" s="123" t="n"/>
-      <c r="J73" s="120">
+      <c r="C76" s="123" t="n"/>
+      <c r="D76" s="123" t="n"/>
+      <c r="E76" s="123" t="n"/>
+      <c r="F76" s="123" t="n"/>
+      <c r="G76" s="123" t="n"/>
+      <c r="H76" s="123" t="n"/>
+      <c r="I76" s="123" t="n"/>
+      <c r="J76" s="120">
         <f>SUM(C69:I69)</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="16.5" customHeight="1" s="82">
-      <c r="A74" s="88" t="n"/>
-      <c r="B74" s="74" t="inlineStr">
+    <row r="77" ht="16.5" customHeight="1" s="82">
+      <c r="A77" s="149" t="n"/>
+      <c r="B77" s="74" t="inlineStr">
         <is>
           <t>5대기관 수술비 비관혈</t>
         </is>
       </c>
-      <c r="C74" s="117" t="n"/>
-      <c r="D74" s="117" t="n"/>
-      <c r="E74" s="117" t="n"/>
-      <c r="F74" s="117" t="n"/>
-      <c r="G74" s="117" t="n"/>
-      <c r="H74" s="117" t="n"/>
-      <c r="I74" s="117" t="n"/>
-      <c r="J74" s="118">
+      <c r="C77" s="117" t="n"/>
+      <c r="D77" s="117" t="n"/>
+      <c r="E77" s="117" t="n"/>
+      <c r="F77" s="117" t="n"/>
+      <c r="G77" s="117" t="n"/>
+      <c r="H77" s="117" t="n"/>
+      <c r="I77" s="117" t="n"/>
+      <c r="J77" s="118">
         <f>SUM(C70:I70)</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="16.5" customHeight="1" s="82">
-      <c r="A75" s="87" t="inlineStr">
-        <is>
-          <t>운전자</t>
-        </is>
-      </c>
-      <c r="B75" s="28" t="inlineStr">
+    <row r="78" ht="16.5" customHeight="1" s="82">
+      <c r="A78" s="150" t="inlineStr">
+        <is>
+          <t>운전</t>
+        </is>
+      </c>
+      <c r="B78" s="28" t="inlineStr">
         <is>
           <t>대인</t>
         </is>
       </c>
-      <c r="C75" s="102" t="n"/>
-      <c r="D75" s="102" t="n"/>
-      <c r="E75" s="102" t="n"/>
-      <c r="F75" s="102" t="n"/>
-      <c r="G75" s="102" t="n"/>
-      <c r="H75" s="102" t="n"/>
-      <c r="I75" s="102" t="n"/>
-      <c r="J75" s="120">
+      <c r="C78" s="102" t="n"/>
+      <c r="D78" s="102" t="n"/>
+      <c r="E78" s="102" t="n"/>
+      <c r="F78" s="102" t="n"/>
+      <c r="G78" s="102" t="n"/>
+      <c r="H78" s="102" t="n"/>
+      <c r="I78" s="102" t="n"/>
+      <c r="J78" s="120">
         <f>SUM(C71:I71)</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="17.25" customHeight="1" s="82">
-      <c r="A76" s="88" t="n"/>
-      <c r="B76" s="31" t="inlineStr">
+    <row r="79" ht="17.25" customHeight="1" s="82">
+      <c r="A79" s="149" t="n"/>
+      <c r="B79" s="31" t="inlineStr">
         <is>
           <t>대물</t>
-        </is>
-      </c>
-      <c r="C76" s="130" t="n"/>
-      <c r="D76" s="130" t="n"/>
-      <c r="E76" s="130" t="n"/>
-      <c r="F76" s="130" t="n"/>
-      <c r="G76" s="130" t="n"/>
-      <c r="H76" s="130" t="n"/>
-      <c r="I76" s="130" t="n"/>
-      <c r="J76" s="122">
-        <f>SUM(C72:I72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" ht="16.5" customHeight="1" s="82">
-      <c r="A77" s="88" t="n"/>
-      <c r="B77" s="31" t="inlineStr">
-        <is>
-          <t>합의금</t>
-        </is>
-      </c>
-      <c r="C77" s="130" t="n"/>
-      <c r="D77" s="130" t="n"/>
-      <c r="E77" s="130" t="n"/>
-      <c r="F77" s="130" t="n"/>
-      <c r="G77" s="130" t="n"/>
-      <c r="H77" s="130" t="n"/>
-      <c r="I77" s="130" t="n"/>
-      <c r="J77" s="122">
-        <f>SUM(C73:I73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="16.5" customHeight="1" s="82">
-      <c r="A78" s="88" t="n"/>
-      <c r="B78" s="66" t="inlineStr">
-        <is>
-          <t>6주미만</t>
-        </is>
-      </c>
-      <c r="C78" s="130" t="n"/>
-      <c r="D78" s="130" t="n"/>
-      <c r="E78" s="130" t="n"/>
-      <c r="F78" s="130" t="n"/>
-      <c r="G78" s="130" t="n"/>
-      <c r="H78" s="130" t="n"/>
-      <c r="I78" s="130" t="n"/>
-      <c r="J78" s="122">
-        <f>SUM(C74:I74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="17.25" customHeight="1" s="82">
-      <c r="A79" s="88" t="n"/>
-      <c r="B79" s="31" t="inlineStr">
-        <is>
-          <t>변호사</t>
         </is>
       </c>
       <c r="C79" s="130" t="n"/>
@@ -2937,320 +2956,393 @@
       <c r="H79" s="130" t="n"/>
       <c r="I79" s="130" t="n"/>
       <c r="J79" s="122">
+        <f>SUM(C72:I72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="17.25" customHeight="1" s="82">
+      <c r="A80" s="149" t="n"/>
+      <c r="B80" s="31" t="inlineStr">
+        <is>
+          <t>합의금</t>
+        </is>
+      </c>
+      <c r="C80" s="130" t="n"/>
+      <c r="D80" s="130" t="n"/>
+      <c r="E80" s="130" t="n"/>
+      <c r="F80" s="130" t="n"/>
+      <c r="G80" s="130" t="n"/>
+      <c r="H80" s="130" t="n"/>
+      <c r="I80" s="130" t="n"/>
+      <c r="J80" s="122">
+        <f>SUM(C73:I73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="17.25" customHeight="1" s="82">
+      <c r="A81" s="149" t="n"/>
+      <c r="B81" s="66" t="inlineStr">
+        <is>
+          <t>6주미만</t>
+        </is>
+      </c>
+      <c r="C81" s="130" t="n"/>
+      <c r="D81" s="130" t="n"/>
+      <c r="E81" s="130" t="n"/>
+      <c r="F81" s="130" t="n"/>
+      <c r="G81" s="130" t="n"/>
+      <c r="H81" s="130" t="n"/>
+      <c r="I81" s="130" t="n"/>
+      <c r="J81" s="122">
+        <f>SUM(C74:I74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="16.5" customHeight="1" s="82">
+      <c r="A82" s="149" t="n"/>
+      <c r="B82" s="31" t="inlineStr">
+        <is>
+          <t>변호사</t>
+        </is>
+      </c>
+      <c r="C82" s="130" t="n"/>
+      <c r="D82" s="130" t="n"/>
+      <c r="E82" s="130" t="n"/>
+      <c r="F82" s="130" t="n"/>
+      <c r="G82" s="130" t="n"/>
+      <c r="H82" s="130" t="n"/>
+      <c r="I82" s="130" t="n"/>
+      <c r="J82" s="122">
         <f>SUM(C75:I75)</f>
         <v/>
       </c>
     </row>
-    <row r="80" ht="17.25" customHeight="1" s="82">
-      <c r="A80" s="89" t="n"/>
-      <c r="B80" s="25" t="inlineStr">
+    <row r="83" ht="17.25" customHeight="1" s="82">
+      <c r="A83" s="151" t="n"/>
+      <c r="B83" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C80" s="142" t="n"/>
-      <c r="D80" s="142" t="n"/>
-      <c r="E80" s="142" t="n"/>
-      <c r="F80" s="142" t="n"/>
-      <c r="G80" s="142" t="n"/>
-      <c r="H80" s="142" t="n"/>
-      <c r="I80" s="142" t="n"/>
-      <c r="J80" s="118">
+      <c r="C83" s="142" t="n"/>
+      <c r="D83" s="142" t="n"/>
+      <c r="E83" s="142" t="n"/>
+      <c r="F83" s="142" t="n"/>
+      <c r="G83" s="142" t="n"/>
+      <c r="H83" s="142" t="n"/>
+      <c r="I83" s="142" t="n"/>
+      <c r="J83" s="118">
         <f>SUM(C76:I76)</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="17.25" customHeight="1" s="82">
-      <c r="A81" s="87" t="inlineStr">
-        <is>
-          <t>골 절</t>
-        </is>
-      </c>
-      <c r="B81" s="65" t="inlineStr">
+    <row r="84" ht="16.5" customHeight="1" s="82">
+      <c r="A84" s="150" t="inlineStr">
+        <is>
+          <t>골절</t>
+        </is>
+      </c>
+      <c r="B84" s="65" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C81" s="136" t="n"/>
-      <c r="D81" s="136" t="n"/>
-      <c r="E81" s="136" t="n"/>
-      <c r="F81" s="136" t="n"/>
-      <c r="G81" s="136" t="n"/>
-      <c r="H81" s="136" t="n"/>
-      <c r="I81" s="136" t="n"/>
-      <c r="J81" s="116">
+      <c r="C84" s="136" t="n"/>
+      <c r="D84" s="136" t="n"/>
+      <c r="E84" s="136" t="n"/>
+      <c r="F84" s="136" t="n"/>
+      <c r="G84" s="136" t="n"/>
+      <c r="H84" s="136" t="n"/>
+      <c r="I84" s="136" t="n"/>
+      <c r="J84" s="116">
         <f>SUM(C77:I77)</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="16.5" customHeight="1" s="82">
-      <c r="A82" s="88" t="n"/>
-      <c r="B82" s="60" t="inlineStr">
+    <row r="85" ht="17.25" customHeight="1" s="82">
+      <c r="A85" s="149" t="n"/>
+      <c r="B85" s="60" t="inlineStr">
         <is>
           <t>골절(치아파절제외)</t>
         </is>
       </c>
-      <c r="C82" s="121" t="n"/>
-      <c r="D82" s="121" t="n"/>
-      <c r="E82" s="121" t="n"/>
-      <c r="F82" s="121" t="n"/>
-      <c r="G82" s="121" t="n"/>
-      <c r="H82" s="121" t="n"/>
-      <c r="I82" s="121" t="n"/>
-      <c r="J82" s="122">
+      <c r="C85" s="121" t="n"/>
+      <c r="D85" s="121" t="n"/>
+      <c r="E85" s="121" t="n"/>
+      <c r="F85" s="121" t="n"/>
+      <c r="G85" s="121" t="n"/>
+      <c r="H85" s="121" t="n"/>
+      <c r="I85" s="121" t="n"/>
+      <c r="J85" s="122">
         <f>SUM(C78:I78)</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="17.25" customHeight="1" s="82">
-      <c r="A83" s="89" t="n"/>
-      <c r="B83" s="74" t="inlineStr">
+    <row r="86" ht="16.5" customHeight="1" s="82">
+      <c r="A86" s="151" t="n"/>
+      <c r="B86" s="74" t="inlineStr">
         <is>
           <t>5대골절진단비</t>
         </is>
       </c>
-      <c r="C83" s="117" t="n"/>
-      <c r="D83" s="117" t="n"/>
-      <c r="E83" s="117" t="n"/>
-      <c r="F83" s="117" t="n"/>
-      <c r="G83" s="117" t="n"/>
-      <c r="H83" s="117" t="n"/>
-      <c r="I83" s="117" t="n"/>
-      <c r="J83" s="118">
+      <c r="C86" s="117" t="n"/>
+      <c r="D86" s="117" t="n"/>
+      <c r="E86" s="117" t="n"/>
+      <c r="F86" s="117" t="n"/>
+      <c r="G86" s="117" t="n"/>
+      <c r="H86" s="117" t="n"/>
+      <c r="I86" s="117" t="n"/>
+      <c r="J86" s="118">
         <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="16.5" customHeight="1" s="82">
-      <c r="A84" s="99" t="inlineStr">
+    <row r="87" ht="16.5" customHeight="1" s="82">
+      <c r="A87" s="99" t="inlineStr">
         <is>
           <t>응급실</t>
         </is>
       </c>
-      <c r="B84" s="64" t="inlineStr">
+      <c r="B87" s="64" t="inlineStr">
         <is>
           <t>응급실(응급)</t>
         </is>
       </c>
-      <c r="C84" s="113" t="n"/>
-      <c r="D84" s="113" t="n"/>
-      <c r="E84" s="113" t="n"/>
-      <c r="F84" s="113" t="n"/>
-      <c r="G84" s="113" t="n"/>
-      <c r="H84" s="113" t="n"/>
-      <c r="I84" s="113" t="n"/>
-      <c r="J84" s="114">
+      <c r="C87" s="113" t="n"/>
+      <c r="D87" s="113" t="n"/>
+      <c r="E87" s="113" t="n"/>
+      <c r="F87" s="113" t="n"/>
+      <c r="G87" s="113" t="n"/>
+      <c r="H87" s="113" t="n"/>
+      <c r="I87" s="113" t="n"/>
+      <c r="J87" s="114">
         <f>SUM(C80:I80)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="17.25" customHeight="1" s="82">
-      <c r="A85" s="92" t="inlineStr">
-        <is>
-          <t>독감</t>
-        </is>
-      </c>
-      <c r="B85" s="34" t="inlineStr">
-        <is>
-          <t>독감</t>
-        </is>
-      </c>
-      <c r="C85" s="123" t="n"/>
-      <c r="D85" s="123" t="n"/>
-      <c r="E85" s="123" t="n"/>
-      <c r="F85" s="123" t="n"/>
-      <c r="G85" s="123" t="n"/>
-      <c r="H85" s="123" t="n"/>
-      <c r="I85" s="123" t="n"/>
-      <c r="J85" s="124" t="n"/>
-    </row>
-    <row r="86" ht="16.5" customHeight="1" s="82">
-      <c r="A86" s="87" t="inlineStr">
-        <is>
-          <t>화상</t>
-        </is>
-      </c>
-      <c r="B86" s="28" t="inlineStr">
-        <is>
-          <t>화상진단비</t>
-        </is>
-      </c>
-      <c r="C86" s="119" t="n"/>
-      <c r="D86" s="119" t="n"/>
-      <c r="E86" s="119" t="n"/>
-      <c r="F86" s="119" t="n"/>
-      <c r="G86" s="119" t="n"/>
-      <c r="H86" s="119" t="n"/>
-      <c r="I86" s="119" t="n"/>
-      <c r="J86" s="120">
-        <f>SUM(C82:I82)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" ht="16.5" customHeight="1" s="82">
-      <c r="A87" s="89" t="n"/>
-      <c r="B87" s="25" t="inlineStr">
-        <is>
-          <t>중증화상진단비</t>
-        </is>
-      </c>
-      <c r="C87" s="117" t="n"/>
-      <c r="D87" s="117" t="n"/>
-      <c r="E87" s="117" t="n"/>
-      <c r="F87" s="117" t="n"/>
-      <c r="G87" s="117" t="n"/>
-      <c r="H87" s="117" t="n"/>
-      <c r="I87" s="117" t="n"/>
-      <c r="J87" s="118">
-        <f>SUM(C83:I83)</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="17.25" customHeight="1" s="82">
       <c r="A88" s="87" t="inlineStr">
         <is>
+          <t>독감</t>
+        </is>
+      </c>
+      <c r="B88" s="34" t="inlineStr">
+        <is>
+          <t>독감</t>
+        </is>
+      </c>
+      <c r="C88" s="123" t="n"/>
+      <c r="D88" s="123" t="n"/>
+      <c r="E88" s="123" t="n"/>
+      <c r="F88" s="123" t="n"/>
+      <c r="G88" s="123" t="n"/>
+      <c r="H88" s="123" t="n"/>
+      <c r="I88" s="123" t="n"/>
+      <c r="J88" s="124" t="n"/>
+    </row>
+    <row r="89" ht="17.25" customHeight="1" s="82">
+      <c r="A89" s="150" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B89" s="28" t="inlineStr">
+        <is>
+          <t>화상진단비</t>
+        </is>
+      </c>
+      <c r="C89" s="119" t="n"/>
+      <c r="D89" s="119" t="n"/>
+      <c r="E89" s="119" t="n"/>
+      <c r="F89" s="119" t="n"/>
+      <c r="G89" s="119" t="n"/>
+      <c r="H89" s="119" t="n"/>
+      <c r="I89" s="119" t="n"/>
+      <c r="J89" s="120">
+        <f>SUM(C82:I82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="151" t="n"/>
+      <c r="B90" s="25" t="inlineStr">
+        <is>
+          <t>중증화상진단비</t>
+        </is>
+      </c>
+      <c r="C90" s="117" t="n"/>
+      <c r="D90" s="117" t="n"/>
+      <c r="E90" s="117" t="n"/>
+      <c r="F90" s="117" t="n"/>
+      <c r="G90" s="117" t="n"/>
+      <c r="H90" s="117" t="n"/>
+      <c r="I90" s="117" t="n"/>
+      <c r="J90" s="118">
+        <f>SUM(C83:I83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="150" t="inlineStr">
+        <is>
           <t>깁스</t>
         </is>
       </c>
-      <c r="B88" s="95" t="inlineStr">
+      <c r="B91" s="95" t="inlineStr">
         <is>
           <t>반깁스</t>
         </is>
       </c>
-      <c r="C88" s="119" t="n"/>
-      <c r="D88" s="119" t="n"/>
-      <c r="E88" s="119" t="n"/>
-      <c r="F88" s="119" t="n"/>
-      <c r="G88" s="119" t="n"/>
-      <c r="H88" s="119" t="n"/>
-      <c r="I88" s="119" t="n"/>
-      <c r="J88" s="120">
+      <c r="C91" s="119" t="n"/>
+      <c r="D91" s="119" t="n"/>
+      <c r="E91" s="119" t="n"/>
+      <c r="F91" s="119" t="n"/>
+      <c r="G91" s="119" t="n"/>
+      <c r="H91" s="119" t="n"/>
+      <c r="I91" s="119" t="n"/>
+      <c r="J91" s="120">
         <f>SUM(C84:I84)</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="17.25" customHeight="1" s="82">
-      <c r="A89" s="89" t="n"/>
-      <c r="B89" s="57" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="151" t="n"/>
+      <c r="B92" s="57" t="inlineStr">
         <is>
           <t>깁스진단비</t>
         </is>
       </c>
-      <c r="C89" s="117" t="n"/>
-      <c r="D89" s="117" t="n"/>
-      <c r="E89" s="117" t="n"/>
-      <c r="F89" s="117" t="n"/>
-      <c r="G89" s="117" t="n"/>
-      <c r="H89" s="117" t="n"/>
-      <c r="I89" s="117" t="n"/>
-      <c r="J89" s="118">
+      <c r="C92" s="117" t="n"/>
+      <c r="D92" s="117" t="n"/>
+      <c r="E92" s="117" t="n"/>
+      <c r="F92" s="117" t="n"/>
+      <c r="G92" s="117" t="n"/>
+      <c r="H92" s="117" t="n"/>
+      <c r="I92" s="117" t="n"/>
+      <c r="J92" s="118">
         <f>SUM(C85:I85)</f>
         <v/>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="87" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="150" t="inlineStr">
         <is>
           <t>실손</t>
         </is>
       </c>
-      <c r="B90" s="95" t="inlineStr">
+      <c r="B93" s="95" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="C90" s="143" t="n"/>
-      <c r="D90" s="143" t="n"/>
-      <c r="E90" s="143" t="n"/>
-      <c r="F90" s="143" t="n"/>
-      <c r="G90" s="143" t="n"/>
-      <c r="H90" s="143" t="n"/>
-      <c r="I90" s="143" t="n"/>
-      <c r="J90" s="120">
+      <c r="C93" s="143" t="n"/>
+      <c r="D93" s="143" t="n"/>
+      <c r="E93" s="143" t="n"/>
+      <c r="F93" s="143" t="n"/>
+      <c r="G93" s="143" t="n"/>
+      <c r="H93" s="143" t="n"/>
+      <c r="I93" s="143" t="n"/>
+      <c r="J93" s="120">
         <f>SUM(C86:I86)</f>
         <v/>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="88" t="n"/>
-      <c r="B91" s="60" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="149" t="n"/>
+      <c r="B94" s="60" t="inlineStr">
         <is>
           <t>통원</t>
         </is>
       </c>
-      <c r="C91" s="144" t="n"/>
-      <c r="D91" s="144" t="n"/>
-      <c r="E91" s="144" t="n"/>
-      <c r="F91" s="144" t="n"/>
-      <c r="G91" s="144" t="n"/>
-      <c r="H91" s="144" t="n"/>
-      <c r="I91" s="144" t="n"/>
-      <c r="J91" s="122">
+      <c r="C94" s="144" t="n"/>
+      <c r="D94" s="144" t="n"/>
+      <c r="E94" s="144" t="n"/>
+      <c r="F94" s="144" t="n"/>
+      <c r="G94" s="144" t="n"/>
+      <c r="H94" s="144" t="n"/>
+      <c r="I94" s="144" t="n"/>
+      <c r="J94" s="122">
         <f>SUM(C87:I87)</f>
         <v/>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="89" t="n"/>
-      <c r="B92" s="22" t="inlineStr">
+    <row r="95" s="82">
+      <c r="A95" s="149" t="n"/>
+      <c r="B95" s="22" t="inlineStr">
         <is>
           <t>약값</t>
         </is>
       </c>
-      <c r="C92" s="115" t="n"/>
-      <c r="D92" s="115" t="n"/>
-      <c r="E92" s="115" t="n"/>
-      <c r="F92" s="115" t="n"/>
-      <c r="G92" s="115" t="n"/>
-      <c r="H92" s="115" t="n"/>
-      <c r="I92" s="145" t="n"/>
-      <c r="J92" s="122">
+      <c r="C95" s="115" t="n"/>
+      <c r="D95" s="115" t="n"/>
+      <c r="E95" s="115" t="n"/>
+      <c r="F95" s="115" t="n"/>
+      <c r="G95" s="115" t="n"/>
+      <c r="H95" s="115" t="n"/>
+      <c r="I95" s="145" t="n"/>
+      <c r="J95" s="122">
         <f>SUM(C88:I88)</f>
         <v/>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="87" t="inlineStr">
+    <row r="96" s="82">
+      <c r="A96" s="151" t="n"/>
+      <c r="B96" s="22" t="inlineStr">
+        <is>
+          <t>MRI/도수치료/비급여주사</t>
+        </is>
+      </c>
+      <c r="C96" s="115" t="n"/>
+      <c r="D96" s="115" t="n"/>
+      <c r="E96" s="115" t="n"/>
+      <c r="F96" s="115" t="n"/>
+      <c r="G96" s="115" t="n"/>
+      <c r="H96" s="115" t="n"/>
+      <c r="I96" s="145" t="n"/>
+      <c r="J96" s="122" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="87" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B93" s="79" t="inlineStr">
+      <c r="B97" s="79" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C93" s="146" t="n"/>
-      <c r="D93" s="146" t="n"/>
-      <c r="E93" s="146" t="n"/>
-      <c r="F93" s="146" t="n"/>
-      <c r="G93" s="146" t="n"/>
-      <c r="H93" s="146" t="n"/>
-      <c r="I93" s="146" t="n"/>
-      <c r="J93" s="147">
+      <c r="C97" s="146" t="n"/>
+      <c r="D97" s="146" t="n"/>
+      <c r="E97" s="146" t="n"/>
+      <c r="F97" s="146" t="n"/>
+      <c r="G97" s="146" t="n"/>
+      <c r="H97" s="146" t="n"/>
+      <c r="I97" s="146" t="n"/>
+      <c r="J97" s="147">
         <f>SUM(C89:I89)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A84:A86"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A61:A77"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A6:A10"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A87:A88"/>
-    <mergeCell ref="A74:A79"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A59:A73"/>
-    <mergeCell ref="A89:A91"/>
-    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A93:A96"/>
+    <mergeCell ref="A49:A60"/>
+    <mergeCell ref="A78:A83"/>
     <mergeCell ref="A37:A48"/>
     <mergeCell ref="A29:A36"/>
     <mergeCell ref="A15:A28"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A80:A82"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A85:A86"/>
+    <mergeCell ref="A89:A90"/>
+    <mergeCell ref="A91:A92"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A49:A58"/>
-    <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>

--- a/master.xlsx
+++ b/master.xlsx
@@ -1458,7 +1458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="82" min="1" max="1"/>
@@ -1824,17 +1824,17 @@
     </row>
     <row r="19" ht="16.5" customHeight="1" s="82">
       <c r="A19" s="88" t="n"/>
-      <c r="B19" s="42" t="inlineStr">
-        <is>
-          <t>암주요치료비</t>
-        </is>
-      </c>
-      <c r="C19" s="128" t="n"/>
-      <c r="D19" s="128" t="n"/>
-      <c r="E19" s="128" t="n"/>
-      <c r="F19" s="128" t="n"/>
-      <c r="G19" s="128" t="n"/>
-      <c r="H19" s="128" t="n"/>
+      <c r="B19" s="40" t="inlineStr">
+        <is>
+          <t>통합전이암</t>
+        </is>
+      </c>
+      <c r="C19" s="127" t="n"/>
+      <c r="D19" s="127" t="n"/>
+      <c r="E19" s="127" t="n"/>
+      <c r="F19" s="127" t="n"/>
+      <c r="G19" s="127" t="n"/>
+      <c r="H19" s="127" t="n"/>
       <c r="I19" s="127" t="n"/>
       <c r="J19" s="116" t="n"/>
     </row>
@@ -1842,37 +1842,34 @@
       <c r="A20" s="88" t="n"/>
       <c r="B20" s="42" t="inlineStr">
         <is>
-          <t>하이클래스(암)</t>
-        </is>
-      </c>
-      <c r="C20" s="127" t="n"/>
-      <c r="D20" s="127" t="n"/>
-      <c r="E20" s="127" t="n"/>
-      <c r="F20" s="127" t="n"/>
-      <c r="G20" s="127" t="n"/>
-      <c r="H20" s="127" t="n"/>
+          <t>암주요치료비</t>
+        </is>
+      </c>
+      <c r="C20" s="128" t="n"/>
+      <c r="D20" s="128" t="n"/>
+      <c r="E20" s="128" t="n"/>
+      <c r="F20" s="128" t="n"/>
+      <c r="G20" s="128" t="n"/>
+      <c r="H20" s="128" t="n"/>
       <c r="I20" s="127" t="n"/>
-      <c r="J20" s="122">
-        <f>SUM(C20:I20)</f>
-        <v/>
-      </c>
+      <c r="J20" s="116" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" s="82">
       <c r="A21" s="88" t="n"/>
       <c r="B21" s="42" t="inlineStr">
         <is>
-          <t>중입자치료비</t>
-        </is>
-      </c>
-      <c r="C21" s="128" t="n"/>
-      <c r="D21" s="128" t="n"/>
-      <c r="E21" s="128" t="n"/>
-      <c r="F21" s="128" t="n"/>
-      <c r="G21" s="128" t="n"/>
-      <c r="H21" s="128" t="n"/>
+          <t>하이클래스(암)</t>
+        </is>
+      </c>
+      <c r="C21" s="127" t="n"/>
+      <c r="D21" s="127" t="n"/>
+      <c r="E21" s="127" t="n"/>
+      <c r="F21" s="127" t="n"/>
+      <c r="G21" s="127" t="n"/>
+      <c r="H21" s="127" t="n"/>
       <c r="I21" s="127" t="n"/>
-      <c r="J21" s="116">
-        <f>SUM(C21:I21)</f>
+      <c r="J21" s="122">
+        <f>SUM(C20:I20)</f>
         <v/>
       </c>
     </row>
@@ -1880,7 +1877,7 @@
       <c r="A22" s="88" t="n"/>
       <c r="B22" s="42" t="inlineStr">
         <is>
-          <t>표적항암치료비</t>
+          <t>중입자치료비</t>
         </is>
       </c>
       <c r="C22" s="128" t="n"/>
@@ -1890,32 +1887,32 @@
       <c r="G22" s="128" t="n"/>
       <c r="H22" s="128" t="n"/>
       <c r="I22" s="127" t="n"/>
-      <c r="J22" s="116" t="n"/>
+      <c r="J22" s="116">
+        <f>SUM(C21:I21)</f>
+        <v/>
+      </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" s="82">
       <c r="A23" s="88" t="n"/>
-      <c r="B23" s="44" t="inlineStr">
-        <is>
-          <t>양성자치료</t>
-        </is>
-      </c>
-      <c r="C23" s="129" t="n"/>
-      <c r="D23" s="129" t="n"/>
-      <c r="E23" s="129" t="n"/>
-      <c r="F23" s="129" t="n"/>
-      <c r="G23" s="129" t="n"/>
-      <c r="H23" s="129" t="n"/>
-      <c r="I23" s="130" t="n"/>
-      <c r="J23" s="122">
-        <f>SUM(C23:I23)</f>
-        <v/>
-      </c>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>표적항암치료비</t>
+        </is>
+      </c>
+      <c r="C23" s="128" t="n"/>
+      <c r="D23" s="128" t="n"/>
+      <c r="E23" s="128" t="n"/>
+      <c r="F23" s="128" t="n"/>
+      <c r="G23" s="128" t="n"/>
+      <c r="H23" s="128" t="n"/>
+      <c r="I23" s="127" t="n"/>
+      <c r="J23" s="116" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="82">
       <c r="A24" s="88" t="n"/>
       <c r="B24" s="44" t="inlineStr">
         <is>
-          <t>세기조절치료</t>
+          <t>양성자치료</t>
         </is>
       </c>
       <c r="C24" s="129" t="n"/>
@@ -1926,7 +1923,7 @@
       <c r="H24" s="129" t="n"/>
       <c r="I24" s="130" t="n"/>
       <c r="J24" s="122">
-        <f>SUM(C24:I24)</f>
+        <f>SUM(C23:I23)</f>
         <v/>
       </c>
     </row>
@@ -1934,7 +1931,7 @@
       <c r="A25" s="88" t="n"/>
       <c r="B25" s="44" t="inlineStr">
         <is>
-          <t>다빈치로봇수술비</t>
+          <t>세기조절치료</t>
         </is>
       </c>
       <c r="C25" s="129" t="n"/>
@@ -1945,7 +1942,7 @@
       <c r="H25" s="129" t="n"/>
       <c r="I25" s="130" t="n"/>
       <c r="J25" s="122">
-        <f>SUM(C25:I25)</f>
+        <f>SUM(C24:I24)</f>
         <v/>
       </c>
     </row>
@@ -1953,174 +1950,174 @@
       <c r="A26" s="88" t="n"/>
       <c r="B26" s="44" t="inlineStr">
         <is>
-          <t>암수술</t>
-        </is>
-      </c>
-      <c r="C26" s="130" t="n"/>
-      <c r="D26" s="130" t="n"/>
-      <c r="E26" s="130" t="n"/>
-      <c r="F26" s="130" t="n"/>
-      <c r="G26" s="130" t="n"/>
-      <c r="H26" s="130" t="n"/>
+          <t>다빈치로봇수술비</t>
+        </is>
+      </c>
+      <c r="C26" s="129" t="n"/>
+      <c r="D26" s="129" t="n"/>
+      <c r="E26" s="129" t="n"/>
+      <c r="F26" s="129" t="n"/>
+      <c r="G26" s="129" t="n"/>
+      <c r="H26" s="129" t="n"/>
       <c r="I26" s="130" t="n"/>
       <c r="J26" s="122">
-        <f>SUM(C26:I26)</f>
+        <f>SUM(C25:I25)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="82">
       <c r="A27" s="88" t="n"/>
-      <c r="B27" s="31" t="inlineStr">
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>암수술</t>
+        </is>
+      </c>
+      <c r="C27" s="130" t="n"/>
+      <c r="D27" s="130" t="n"/>
+      <c r="E27" s="130" t="n"/>
+      <c r="F27" s="130" t="n"/>
+      <c r="G27" s="130" t="n"/>
+      <c r="H27" s="130" t="n"/>
+      <c r="I27" s="130" t="n"/>
+      <c r="J27" s="122">
+        <f>SUM(C26:I26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="17.25" customHeight="1" s="82">
+      <c r="A28" s="88" t="n"/>
+      <c r="B28" s="31" t="inlineStr">
         <is>
           <t>암일당</t>
         </is>
       </c>
-      <c r="C27" s="121" t="n"/>
-      <c r="D27" s="121" t="n"/>
-      <c r="E27" s="121" t="n"/>
-      <c r="F27" s="121" t="n"/>
-      <c r="G27" s="121" t="n"/>
-      <c r="H27" s="121" t="n"/>
-      <c r="I27" s="121" t="n"/>
-      <c r="J27" s="122">
+      <c r="C28" s="121" t="n"/>
+      <c r="D28" s="121" t="n"/>
+      <c r="E28" s="121" t="n"/>
+      <c r="F28" s="121" t="n"/>
+      <c r="G28" s="121" t="n"/>
+      <c r="H28" s="121" t="n"/>
+      <c r="I28" s="121" t="n"/>
+      <c r="J28" s="122">
         <f>SUM(C27:I27)</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1" s="82">
-      <c r="A28" s="89" t="n"/>
-      <c r="B28" s="25" t="inlineStr">
+    <row r="29" ht="17.25" customHeight="1" s="82">
+      <c r="A29" s="89" t="n"/>
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>항암방사선약물</t>
         </is>
       </c>
-      <c r="C28" s="117" t="n"/>
-      <c r="D28" s="117" t="n"/>
-      <c r="E28" s="117" t="n"/>
-      <c r="F28" s="117" t="n"/>
-      <c r="G28" s="117" t="n"/>
-      <c r="H28" s="117" t="n"/>
-      <c r="I28" s="117" t="n"/>
-      <c r="J28" s="118">
+      <c r="C29" s="117" t="n"/>
+      <c r="D29" s="117" t="n"/>
+      <c r="E29" s="117" t="n"/>
+      <c r="F29" s="117" t="n"/>
+      <c r="G29" s="117" t="n"/>
+      <c r="H29" s="117" t="n"/>
+      <c r="I29" s="117" t="n"/>
+      <c r="J29" s="118">
         <f>SUM(C28:I28)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="17.25" customHeight="1" s="82">
-      <c r="A29" s="87" t="inlineStr">
+    <row r="30" ht="16.5" customHeight="1" s="82">
+      <c r="A30" s="87" t="inlineStr">
         <is>
           <t>뇌혈관</t>
         </is>
       </c>
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B30" s="34" t="inlineStr">
         <is>
           <t>뇌혈관진단비</t>
         </is>
       </c>
-      <c r="C29" s="123" t="n"/>
-      <c r="D29" s="123" t="n"/>
-      <c r="E29" s="123" t="n"/>
-      <c r="F29" s="123" t="n"/>
-      <c r="G29" s="123" t="n"/>
-      <c r="H29" s="123" t="n"/>
-      <c r="I29" s="123" t="n"/>
-      <c r="J29" s="124">
+      <c r="C30" s="123" t="n"/>
+      <c r="D30" s="123" t="n"/>
+      <c r="E30" s="123" t="n"/>
+      <c r="F30" s="123" t="n"/>
+      <c r="G30" s="123" t="n"/>
+      <c r="H30" s="123" t="n"/>
+      <c r="I30" s="123" t="n"/>
+      <c r="J30" s="124">
         <f>SUM(C29:I29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16.5" customHeight="1" s="82">
-      <c r="A30" s="88" t="n"/>
-      <c r="B30" s="47" t="inlineStr">
-        <is>
-          <t>뇌졸증진단비</t>
-        </is>
-      </c>
-      <c r="C30" s="131" t="n"/>
-      <c r="D30" s="131" t="n"/>
-      <c r="E30" s="131" t="n"/>
-      <c r="F30" s="131" t="n"/>
-      <c r="G30" s="131" t="n"/>
-      <c r="H30" s="131" t="n"/>
-      <c r="I30" s="131" t="n"/>
-      <c r="J30" s="132">
-        <f>SUM(C30:I30)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1" s="82">
       <c r="A31" s="88" t="n"/>
-      <c r="B31" s="50" t="inlineStr">
-        <is>
-          <t>중대한 뇌졸증</t>
-        </is>
-      </c>
-      <c r="C31" s="126" t="n"/>
-      <c r="D31" s="126" t="n"/>
-      <c r="E31" s="126" t="n"/>
-      <c r="F31" s="126" t="n"/>
-      <c r="G31" s="126" t="n"/>
-      <c r="H31" s="126" t="n"/>
-      <c r="I31" s="126" t="n"/>
-      <c r="J31" s="133">
-        <f>SUM(C31:I31)</f>
+      <c r="B31" s="47" t="inlineStr">
+        <is>
+          <t>뇌졸증진단비</t>
+        </is>
+      </c>
+      <c r="C31" s="131" t="n"/>
+      <c r="D31" s="131" t="n"/>
+      <c r="E31" s="131" t="n"/>
+      <c r="F31" s="131" t="n"/>
+      <c r="G31" s="131" t="n"/>
+      <c r="H31" s="131" t="n"/>
+      <c r="I31" s="131" t="n"/>
+      <c r="J31" s="132">
+        <f>SUM(C30:I30)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1" s="82">
       <c r="A32" s="88" t="n"/>
-      <c r="B32" s="52" t="inlineStr">
-        <is>
-          <t>뇌출혈진단비</t>
-        </is>
-      </c>
-      <c r="C32" s="127" t="n"/>
-      <c r="D32" s="127" t="n"/>
-      <c r="E32" s="127" t="n"/>
-      <c r="F32" s="127" t="n"/>
-      <c r="G32" s="127" t="n"/>
-      <c r="H32" s="127" t="n"/>
-      <c r="I32" s="127" t="n"/>
-      <c r="J32" s="116">
-        <f>SUM(C32:I32)</f>
+      <c r="B32" s="50" t="inlineStr">
+        <is>
+          <t>중대한 뇌졸증</t>
+        </is>
+      </c>
+      <c r="C32" s="126" t="n"/>
+      <c r="D32" s="126" t="n"/>
+      <c r="E32" s="126" t="n"/>
+      <c r="F32" s="126" t="n"/>
+      <c r="G32" s="126" t="n"/>
+      <c r="H32" s="126" t="n"/>
+      <c r="I32" s="126" t="n"/>
+      <c r="J32" s="133">
+        <f>SUM(C31:I31)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" s="82">
       <c r="A33" s="88" t="n"/>
-      <c r="B33" s="53" t="inlineStr">
-        <is>
-          <t>외상성뇌출혈</t>
-        </is>
-      </c>
-      <c r="C33" s="134" t="n"/>
-      <c r="D33" s="134" t="n"/>
-      <c r="E33" s="134" t="n"/>
-      <c r="F33" s="134" t="n"/>
-      <c r="G33" s="134" t="n"/>
-      <c r="H33" s="134" t="n"/>
-      <c r="I33" s="134" t="n"/>
+      <c r="B33" s="52" t="inlineStr">
+        <is>
+          <t>뇌출혈진단비</t>
+        </is>
+      </c>
+      <c r="C33" s="127" t="n"/>
+      <c r="D33" s="127" t="n"/>
+      <c r="E33" s="127" t="n"/>
+      <c r="F33" s="127" t="n"/>
+      <c r="G33" s="127" t="n"/>
+      <c r="H33" s="127" t="n"/>
+      <c r="I33" s="127" t="n"/>
       <c r="J33" s="116">
-        <f>SUM(C33:I33)</f>
+        <f>SUM(C32:I32)</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="82">
       <c r="A34" s="88" t="n"/>
-      <c r="B34" s="55" t="inlineStr">
-        <is>
-          <t>산정특례뇌혈관</t>
-        </is>
-      </c>
-      <c r="C34" s="135" t="n"/>
-      <c r="D34" s="135" t="n"/>
-      <c r="E34" s="135" t="n"/>
-      <c r="F34" s="135" t="n"/>
-      <c r="G34" s="135" t="n"/>
-      <c r="H34" s="135" t="n"/>
-      <c r="I34" s="135" t="n"/>
-      <c r="J34" s="122">
-        <f>SUM(C34:I34)</f>
+      <c r="B34" s="53" t="inlineStr">
+        <is>
+          <t>외상성뇌출혈</t>
+        </is>
+      </c>
+      <c r="C34" s="134" t="n"/>
+      <c r="D34" s="134" t="n"/>
+      <c r="E34" s="134" t="n"/>
+      <c r="F34" s="134" t="n"/>
+      <c r="G34" s="134" t="n"/>
+      <c r="H34" s="134" t="n"/>
+      <c r="I34" s="134" t="n"/>
+      <c r="J34" s="116">
+        <f>SUM(C33:I33)</f>
         <v/>
       </c>
     </row>
@@ -2128,7 +2125,7 @@
       <c r="A35" s="88" t="n"/>
       <c r="B35" s="55" t="inlineStr">
         <is>
-          <t>2대 주요치료비</t>
+          <t>산정특례뇌혈관</t>
         </is>
       </c>
       <c r="C35" s="135" t="n"/>
@@ -2138,66 +2135,66 @@
       <c r="G35" s="135" t="n"/>
       <c r="H35" s="135" t="n"/>
       <c r="I35" s="135" t="n"/>
-      <c r="J35" s="122" t="n"/>
+      <c r="J35" s="122">
+        <f>SUM(C34:I34)</f>
+        <v/>
+      </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="82">
-      <c r="A36" s="89" t="n"/>
-      <c r="B36" s="57" t="inlineStr">
+      <c r="A36" s="88" t="n"/>
+      <c r="B36" s="55" t="inlineStr">
+        <is>
+          <t>2대 주요치료비</t>
+        </is>
+      </c>
+      <c r="C36" s="135" t="n"/>
+      <c r="D36" s="135" t="n"/>
+      <c r="E36" s="135" t="n"/>
+      <c r="F36" s="135" t="n"/>
+      <c r="G36" s="135" t="n"/>
+      <c r="H36" s="135" t="n"/>
+      <c r="I36" s="135" t="n"/>
+      <c r="J36" s="122" t="n"/>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" s="82">
+      <c r="A37" s="89" t="n"/>
+      <c r="B37" s="57" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C36" s="117" t="n"/>
-      <c r="D36" s="117" t="n"/>
-      <c r="E36" s="117" t="n"/>
-      <c r="F36" s="117" t="n"/>
-      <c r="G36" s="117" t="n"/>
-      <c r="H36" s="117" t="n"/>
-      <c r="I36" s="117" t="n"/>
-      <c r="J36" s="118">
+      <c r="C37" s="117" t="n"/>
+      <c r="D37" s="117" t="n"/>
+      <c r="E37" s="117" t="n"/>
+      <c r="F37" s="117" t="n"/>
+      <c r="G37" s="117" t="n"/>
+      <c r="H37" s="117" t="n"/>
+      <c r="I37" s="117" t="n"/>
+      <c r="J37" s="118">
         <f>SUM(C35:I35)</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="82">
-      <c r="A37" s="99" t="inlineStr">
+    <row r="38" ht="16.5" customHeight="1" s="82">
+      <c r="A38" s="99" t="inlineStr">
         <is>
           <t>심장</t>
         </is>
       </c>
-      <c r="B37" s="40" t="inlineStr">
+      <c r="B38" s="40" t="inlineStr">
         <is>
           <t>협심증</t>
         </is>
       </c>
-      <c r="C37" s="127" t="n"/>
-      <c r="D37" s="127" t="n"/>
-      <c r="E37" s="127" t="n"/>
-      <c r="F37" s="127" t="n"/>
-      <c r="G37" s="127" t="n"/>
-      <c r="H37" s="127" t="n"/>
-      <c r="I37" s="127" t="n"/>
-      <c r="J37" s="122">
+      <c r="C38" s="127" t="n"/>
+      <c r="D38" s="127" t="n"/>
+      <c r="E38" s="127" t="n"/>
+      <c r="F38" s="127" t="n"/>
+      <c r="G38" s="127" t="n"/>
+      <c r="H38" s="127" t="n"/>
+      <c r="I38" s="127" t="n"/>
+      <c r="J38" s="122">
         <f>SUM(C36:I36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" s="82">
-      <c r="A38" s="88" t="n"/>
-      <c r="B38" s="31" t="inlineStr">
-        <is>
-          <t>심부전</t>
-        </is>
-      </c>
-      <c r="C38" s="130" t="n"/>
-      <c r="D38" s="130" t="n"/>
-      <c r="E38" s="130" t="n"/>
-      <c r="F38" s="130" t="n"/>
-      <c r="G38" s="130" t="n"/>
-      <c r="H38" s="130" t="n"/>
-      <c r="I38" s="130" t="n"/>
-      <c r="J38" s="122">
-        <f>SUM(C37:I37)</f>
         <v/>
       </c>
     </row>
@@ -2205,7 +2202,7 @@
       <c r="A39" s="88" t="n"/>
       <c r="B39" s="31" t="inlineStr">
         <is>
-          <t>빈맥</t>
+          <t>심부전</t>
         </is>
       </c>
       <c r="C39" s="130" t="n"/>
@@ -2215,13 +2212,16 @@
       <c r="G39" s="130" t="n"/>
       <c r="H39" s="130" t="n"/>
       <c r="I39" s="130" t="n"/>
-      <c r="J39" s="122" t="n"/>
+      <c r="J39" s="122">
+        <f>SUM(C37:I37)</f>
+        <v/>
+      </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" s="82">
       <c r="A40" s="88" t="n"/>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>염증</t>
+          <t>빈맥</t>
         </is>
       </c>
       <c r="C40" s="130" t="n"/>
@@ -2231,27 +2231,24 @@
       <c r="G40" s="130" t="n"/>
       <c r="H40" s="130" t="n"/>
       <c r="I40" s="130" t="n"/>
-      <c r="J40" s="122">
-        <f>SUM(C38:I38)</f>
-        <v/>
-      </c>
+      <c r="J40" s="122" t="n"/>
     </row>
     <row r="41" ht="17.25" customHeight="1" s="82">
       <c r="A41" s="88" t="n"/>
-      <c r="B41" s="40" t="inlineStr">
-        <is>
-          <t>부정맥</t>
-        </is>
-      </c>
-      <c r="C41" s="136" t="n"/>
-      <c r="D41" s="136" t="n"/>
-      <c r="E41" s="136" t="n"/>
-      <c r="F41" s="136" t="n"/>
-      <c r="G41" s="136" t="n"/>
-      <c r="H41" s="136" t="n"/>
-      <c r="I41" s="136" t="n"/>
+      <c r="B41" s="31" t="inlineStr">
+        <is>
+          <t>염증</t>
+        </is>
+      </c>
+      <c r="C41" s="130" t="n"/>
+      <c r="D41" s="130" t="n"/>
+      <c r="E41" s="130" t="n"/>
+      <c r="F41" s="130" t="n"/>
+      <c r="G41" s="130" t="n"/>
+      <c r="H41" s="130" t="n"/>
+      <c r="I41" s="130" t="n"/>
       <c r="J41" s="122">
-        <f>SUM(C39:I39)</f>
+        <f>SUM(C38:I38)</f>
         <v/>
       </c>
     </row>
@@ -2259,42 +2256,42 @@
       <c r="A42" s="88" t="n"/>
       <c r="B42" s="40" t="inlineStr">
         <is>
-          <t>심근병증</t>
-        </is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="C42" s="136" t="n"/>
+      <c r="D42" s="136" t="n"/>
+      <c r="E42" s="136" t="n"/>
+      <c r="F42" s="136" t="n"/>
+      <c r="G42" s="136" t="n"/>
+      <c r="H42" s="136" t="n"/>
+      <c r="I42" s="136" t="n"/>
+      <c r="J42" s="122">
+        <f>SUM(C39:I39)</f>
+        <v/>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" s="82">
       <c r="A43" s="88" t="n"/>
       <c r="B43" s="40" t="inlineStr">
         <is>
-          <t>심장판막</t>
+          <t>심근병증</t>
         </is>
       </c>
     </row>
     <row r="44" ht="17.25" customHeight="1" s="82">
       <c r="A44" s="88" t="n"/>
-      <c r="B44" s="60" t="inlineStr">
-        <is>
-          <t>산정특례심장</t>
-        </is>
-      </c>
-      <c r="C44" s="121" t="n"/>
-      <c r="D44" s="121" t="n"/>
-      <c r="E44" s="121" t="n"/>
-      <c r="F44" s="121" t="n"/>
-      <c r="G44" s="121" t="n"/>
-      <c r="H44" s="121" t="n"/>
-      <c r="I44" s="121" t="n"/>
-      <c r="J44" s="122">
-        <f>SUM(C40:I40)</f>
-        <v/>
+      <c r="B44" s="40" t="inlineStr">
+        <is>
+          <t>심장판막</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1" s="82">
       <c r="A45" s="88" t="n"/>
-      <c r="B45" s="69" t="inlineStr">
-        <is>
-          <t>2대 주요치료비</t>
+      <c r="B45" s="60" t="inlineStr">
+        <is>
+          <t>산정특례심장</t>
         </is>
       </c>
       <c r="C45" s="121" t="n"/>
@@ -2305,125 +2302,125 @@
       <c r="H45" s="121" t="n"/>
       <c r="I45" s="121" t="n"/>
       <c r="J45" s="122">
-        <f>SUM(C41:I41)</f>
+        <f>SUM(C40:I40)</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="82">
       <c r="A46" s="88" t="n"/>
-      <c r="B46" s="86" t="inlineStr">
-        <is>
-          <t>허혈성 진단비</t>
-        </is>
-      </c>
-      <c r="C46" s="115" t="n"/>
-      <c r="D46" s="115" t="n"/>
-      <c r="E46" s="115" t="n"/>
-      <c r="F46" s="115" t="n"/>
-      <c r="G46" s="115" t="n"/>
-      <c r="H46" s="115" t="n"/>
-      <c r="I46" s="115" t="n"/>
+      <c r="B46" s="69" t="inlineStr">
+        <is>
+          <t>2대 주요치료비</t>
+        </is>
+      </c>
+      <c r="C46" s="121" t="n"/>
+      <c r="D46" s="121" t="n"/>
+      <c r="E46" s="121" t="n"/>
+      <c r="F46" s="121" t="n"/>
+      <c r="G46" s="121" t="n"/>
+      <c r="H46" s="121" t="n"/>
+      <c r="I46" s="121" t="n"/>
       <c r="J46" s="122">
-        <f>SUM(C42:I42)</f>
+        <f>SUM(C41:I41)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="82">
       <c r="A47" s="88" t="n"/>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B47" s="86" t="inlineStr">
+        <is>
+          <t>허혈성 진단비</t>
+        </is>
+      </c>
+      <c r="C47" s="115" t="n"/>
+      <c r="D47" s="115" t="n"/>
+      <c r="E47" s="115" t="n"/>
+      <c r="F47" s="115" t="n"/>
+      <c r="G47" s="115" t="n"/>
+      <c r="H47" s="115" t="n"/>
+      <c r="I47" s="115" t="n"/>
+      <c r="J47" s="122">
+        <f>SUM(C42:I42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" s="82">
+      <c r="A48" s="88" t="n"/>
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>급성심근경색</t>
         </is>
       </c>
-      <c r="C47" s="125" t="n"/>
-      <c r="D47" s="125" t="n"/>
-      <c r="E47" s="125" t="n"/>
-      <c r="F47" s="125" t="n"/>
-      <c r="G47" s="125" t="n"/>
-      <c r="H47" s="125" t="n"/>
-      <c r="I47" s="125" t="n"/>
-      <c r="J47" s="110">
+      <c r="C48" s="125" t="n"/>
+      <c r="D48" s="125" t="n"/>
+      <c r="E48" s="125" t="n"/>
+      <c r="F48" s="125" t="n"/>
+      <c r="G48" s="125" t="n"/>
+      <c r="H48" s="125" t="n"/>
+      <c r="I48" s="125" t="n"/>
+      <c r="J48" s="110">
         <f>SUM(C42:I42)</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="82">
-      <c r="A48" s="89" t="n"/>
-      <c r="B48" s="16" t="inlineStr">
+    <row r="49" ht="16.5" customHeight="1" s="82">
+      <c r="A49" s="89" t="n"/>
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>중대한 급성심근</t>
         </is>
       </c>
-      <c r="C48" s="111" t="n"/>
-      <c r="D48" s="111" t="n"/>
-      <c r="E48" s="111" t="n"/>
-      <c r="F48" s="111" t="n"/>
-      <c r="G48" s="111" t="n"/>
-      <c r="H48" s="111" t="n"/>
-      <c r="I48" s="111" t="n"/>
-      <c r="J48" s="133">
+      <c r="C49" s="111" t="n"/>
+      <c r="D49" s="111" t="n"/>
+      <c r="E49" s="111" t="n"/>
+      <c r="F49" s="111" t="n"/>
+      <c r="G49" s="111" t="n"/>
+      <c r="H49" s="111" t="n"/>
+      <c r="I49" s="111" t="n"/>
+      <c r="J49" s="133">
         <f>SUM(C44:I44)</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="82">
-      <c r="A49" s="99" t="inlineStr">
+    <row r="50" ht="16.5" customHeight="1" s="82">
+      <c r="A50" s="99" t="inlineStr">
         <is>
           <t>일당</t>
         </is>
       </c>
-      <c r="B49" s="64" t="inlineStr">
+      <c r="B50" s="64" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C49" s="113" t="n"/>
-      <c r="D49" s="113" t="n"/>
-      <c r="E49" s="113" t="n"/>
-      <c r="F49" s="113" t="n"/>
-      <c r="G49" s="113" t="n"/>
-      <c r="H49" s="113" t="n"/>
-      <c r="I49" s="113" t="n"/>
-      <c r="J49" s="114">
+      <c r="C50" s="113" t="n"/>
+      <c r="D50" s="113" t="n"/>
+      <c r="E50" s="113" t="n"/>
+      <c r="F50" s="113" t="n"/>
+      <c r="G50" s="113" t="n"/>
+      <c r="H50" s="113" t="n"/>
+      <c r="I50" s="113" t="n"/>
+      <c r="J50" s="114">
         <f>SUM(C45:I45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16.5" customHeight="1" s="82">
-      <c r="A50" s="88" t="n"/>
-      <c r="B50" s="95" t="inlineStr">
-        <is>
-          <t>질병일당</t>
-        </is>
-      </c>
-      <c r="C50" s="119" t="n"/>
-      <c r="D50" s="119" t="n"/>
-      <c r="E50" s="119" t="n"/>
-      <c r="F50" s="119" t="n"/>
-      <c r="G50" s="119" t="n"/>
-      <c r="H50" s="119" t="n"/>
-      <c r="I50" s="119" t="n"/>
-      <c r="J50" s="120">
-        <f>SUM(C46:I46)</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" s="82">
       <c r="A51" s="88" t="n"/>
-      <c r="B51" s="65" t="inlineStr">
-        <is>
-          <t>질병수술일당</t>
-        </is>
-      </c>
-      <c r="C51" s="136" t="n"/>
-      <c r="D51" s="136" t="n"/>
-      <c r="E51" s="136" t="n"/>
-      <c r="F51" s="136" t="n"/>
-      <c r="G51" s="136" t="n"/>
-      <c r="H51" s="136" t="n"/>
-      <c r="I51" s="136" t="n"/>
-      <c r="J51" s="122">
-        <f>SUM(C47:I47)</f>
+      <c r="B51" s="95" t="inlineStr">
+        <is>
+          <t>질병일당</t>
+        </is>
+      </c>
+      <c r="C51" s="119" t="n"/>
+      <c r="D51" s="119" t="n"/>
+      <c r="E51" s="119" t="n"/>
+      <c r="F51" s="119" t="n"/>
+      <c r="G51" s="119" t="n"/>
+      <c r="H51" s="119" t="n"/>
+      <c r="I51" s="119" t="n"/>
+      <c r="J51" s="120">
+        <f>SUM(C46:I46)</f>
         <v/>
       </c>
     </row>
@@ -2431,7 +2428,7 @@
       <c r="A52" s="88" t="n"/>
       <c r="B52" s="65" t="inlineStr">
         <is>
-          <t>질병종합병원일당</t>
+          <t>질병수술일당</t>
         </is>
       </c>
       <c r="C52" s="136" t="n"/>
@@ -2442,34 +2439,34 @@
       <c r="H52" s="136" t="n"/>
       <c r="I52" s="136" t="n"/>
       <c r="J52" s="122">
-        <f>SUM(C48:I48)</f>
+        <f>SUM(C47:I47)</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" s="82">
       <c r="A53" s="88" t="n"/>
-      <c r="B53" s="60" t="inlineStr">
-        <is>
-          <t>상해일당</t>
-        </is>
-      </c>
-      <c r="C53" s="121" t="n"/>
-      <c r="D53" s="121" t="n"/>
-      <c r="E53" s="121" t="n"/>
-      <c r="F53" s="121" t="n"/>
-      <c r="G53" s="121" t="n"/>
-      <c r="H53" s="121" t="n"/>
-      <c r="I53" s="121" t="n"/>
+      <c r="B53" s="65" t="inlineStr">
+        <is>
+          <t>질병종합병원일당</t>
+        </is>
+      </c>
+      <c r="C53" s="136" t="n"/>
+      <c r="D53" s="136" t="n"/>
+      <c r="E53" s="136" t="n"/>
+      <c r="F53" s="136" t="n"/>
+      <c r="G53" s="136" t="n"/>
+      <c r="H53" s="136" t="n"/>
+      <c r="I53" s="136" t="n"/>
       <c r="J53" s="122">
-        <f>SUM(C49:I49)</f>
+        <f>SUM(C48:I48)</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="82">
       <c r="A54" s="88" t="n"/>
-      <c r="B54" s="31" t="inlineStr">
-        <is>
-          <t>간병인</t>
+      <c r="B54" s="60" t="inlineStr">
+        <is>
+          <t>상해일당</t>
         </is>
       </c>
       <c r="C54" s="121" t="n"/>
@@ -2480,15 +2477,15 @@
       <c r="H54" s="121" t="n"/>
       <c r="I54" s="121" t="n"/>
       <c r="J54" s="122">
-        <f>SUM(C50:I50)</f>
+        <f>SUM(C49:I49)</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="82">
       <c r="A55" s="88" t="n"/>
-      <c r="B55" s="31" t="inlineStr">
-        <is>
-          <t>간병인지원일당</t>
+      <c r="B55" s="60" t="inlineStr">
+        <is>
+          <t>상해수술일당</t>
         </is>
       </c>
       <c r="C55" s="121" t="n"/>
@@ -2504,7 +2501,7 @@
       <c r="A56" s="88" t="n"/>
       <c r="B56" s="31" t="inlineStr">
         <is>
-          <t>간호통합병동</t>
+          <t>간병인</t>
         </is>
       </c>
       <c r="C56" s="121" t="n"/>
@@ -2515,15 +2512,15 @@
       <c r="H56" s="121" t="n"/>
       <c r="I56" s="121" t="n"/>
       <c r="J56" s="122">
-        <f>SUM(C51:I51)</f>
+        <f>SUM(C50:I50)</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="16.5" customHeight="1" s="82">
       <c r="A57" s="88" t="n"/>
-      <c r="B57" s="66" t="inlineStr">
-        <is>
-          <t>1인실 종합병원</t>
+      <c r="B57" s="31" t="inlineStr">
+        <is>
+          <t>간병인지원일당</t>
         </is>
       </c>
       <c r="C57" s="121" t="n"/>
@@ -2533,16 +2530,13 @@
       <c r="G57" s="121" t="n"/>
       <c r="H57" s="121" t="n"/>
       <c r="I57" s="121" t="n"/>
-      <c r="J57" s="122">
-        <f>SUM(C52:I52)</f>
-        <v/>
-      </c>
+      <c r="J57" s="122" t="n"/>
     </row>
     <row r="58" ht="16.5" customHeight="1" s="82">
       <c r="A58" s="88" t="n"/>
-      <c r="B58" s="66" t="inlineStr">
-        <is>
-          <t>1인실 상급병원</t>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>간호통합병동</t>
         </is>
       </c>
       <c r="C58" s="121" t="n"/>
@@ -2553,15 +2547,15 @@
       <c r="H58" s="121" t="n"/>
       <c r="I58" s="121" t="n"/>
       <c r="J58" s="122">
-        <f>SUM(C53:I53)</f>
+        <f>SUM(C51:I51)</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="16.5" customHeight="1" s="82">
       <c r="A59" s="88" t="n"/>
-      <c r="B59" s="31" t="inlineStr">
-        <is>
-          <t>질병중환자실</t>
+      <c r="B59" s="66" t="inlineStr">
+        <is>
+          <t>1인실 종합병원</t>
         </is>
       </c>
       <c r="C59" s="121" t="n"/>
@@ -2572,150 +2566,150 @@
       <c r="H59" s="121" t="n"/>
       <c r="I59" s="121" t="n"/>
       <c r="J59" s="122">
+        <f>SUM(C52:I52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" ht="16.5" customHeight="1" s="82">
+      <c r="A60" s="88" t="n"/>
+      <c r="B60" s="66" t="inlineStr">
+        <is>
+          <t>1인실 상급병원</t>
+        </is>
+      </c>
+      <c r="C60" s="121" t="n"/>
+      <c r="D60" s="121" t="n"/>
+      <c r="E60" s="121" t="n"/>
+      <c r="F60" s="121" t="n"/>
+      <c r="G60" s="121" t="n"/>
+      <c r="H60" s="121" t="n"/>
+      <c r="I60" s="121" t="n"/>
+      <c r="J60" s="122">
+        <f>SUM(C53:I53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="16.5" customHeight="1" s="82">
+      <c r="A61" s="88" t="n"/>
+      <c r="B61" s="31" t="inlineStr">
+        <is>
+          <t>질병중환자실</t>
+        </is>
+      </c>
+      <c r="C61" s="121" t="n"/>
+      <c r="D61" s="121" t="n"/>
+      <c r="E61" s="121" t="n"/>
+      <c r="F61" s="121" t="n"/>
+      <c r="G61" s="121" t="n"/>
+      <c r="H61" s="121" t="n"/>
+      <c r="I61" s="121" t="n"/>
+      <c r="J61" s="122">
         <f>SUM(C54:I54)</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="16.5" customHeight="1" s="82">
-      <c r="A60" s="89" t="n"/>
-      <c r="B60" s="25" t="inlineStr">
+    <row r="62" ht="17.25" customHeight="1" s="82">
+      <c r="A62" s="89" t="n"/>
+      <c r="B62" s="25" t="inlineStr">
         <is>
           <t>상해중환자실</t>
         </is>
       </c>
-      <c r="C60" s="117" t="n"/>
-      <c r="D60" s="117" t="n"/>
-      <c r="E60" s="117" t="n"/>
-      <c r="F60" s="117" t="n"/>
-      <c r="G60" s="117" t="n"/>
-      <c r="H60" s="117" t="n"/>
-      <c r="I60" s="117" t="n"/>
-      <c r="J60" s="118">
+      <c r="C62" s="117" t="n"/>
+      <c r="D62" s="117" t="n"/>
+      <c r="E62" s="117" t="n"/>
+      <c r="F62" s="117" t="n"/>
+      <c r="G62" s="117" t="n"/>
+      <c r="H62" s="117" t="n"/>
+      <c r="I62" s="117" t="n"/>
+      <c r="J62" s="118">
         <f>SUM(C55:I55)</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="16.5" customHeight="1" s="82">
-      <c r="A61" s="148" t="inlineStr">
+    <row r="63" ht="17.25" customHeight="1" s="82">
+      <c r="A63" s="148" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B61" s="95" t="inlineStr">
+      <c r="B63" s="95" t="inlineStr">
         <is>
           <t>상해수술비</t>
         </is>
       </c>
-      <c r="C61" s="119" t="n"/>
-      <c r="D61" s="119" t="n"/>
-      <c r="E61" s="119" t="n"/>
-      <c r="F61" s="119" t="n"/>
-      <c r="G61" s="119" t="n"/>
-      <c r="H61" s="119" t="n"/>
-      <c r="I61" s="119" t="n"/>
-      <c r="J61" s="120">
+      <c r="C63" s="119" t="n"/>
+      <c r="D63" s="119" t="n"/>
+      <c r="E63" s="119" t="n"/>
+      <c r="F63" s="119" t="n"/>
+      <c r="G63" s="119" t="n"/>
+      <c r="H63" s="119" t="n"/>
+      <c r="I63" s="119" t="n"/>
+      <c r="J63" s="120">
         <f>SUM(C56:I56)</f>
         <v/>
-      </c>
-    </row>
-    <row r="62" ht="17.25" customHeight="1" s="82">
-      <c r="A62" s="149" t="n"/>
-      <c r="B62" s="65" t="inlineStr">
-        <is>
-          <t>중대한상해수술비</t>
-        </is>
-      </c>
-      <c r="C62" s="136" t="n"/>
-      <c r="D62" s="136" t="n"/>
-      <c r="E62" s="136" t="n"/>
-      <c r="F62" s="136" t="n"/>
-      <c r="G62" s="136" t="n"/>
-      <c r="H62" s="136" t="n"/>
-      <c r="I62" s="136" t="n"/>
-      <c r="J62" s="122">
-        <f>SUM(C57:I57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="17.25" customHeight="1" s="82">
-      <c r="A63" s="149" t="n"/>
-      <c r="B63" s="60" t="inlineStr">
-        <is>
-          <t>상해 종수술비(1-5종)</t>
-        </is>
-      </c>
-      <c r="C63" s="136" t="n"/>
-      <c r="D63" s="136" t="n"/>
-      <c r="E63" s="136" t="n"/>
-      <c r="F63" s="137" t="n"/>
-      <c r="G63" s="136" t="n"/>
-      <c r="H63" s="136" t="n"/>
-      <c r="I63" s="136" t="n"/>
-      <c r="J63" s="122" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
       </c>
     </row>
     <row r="64" ht="16.5" customHeight="1" s="82">
       <c r="A64" s="149" t="n"/>
-      <c r="B64" s="60" t="inlineStr">
-        <is>
-          <t>상해 종수술비(1-8종)</t>
+      <c r="B64" s="65" t="inlineStr">
+        <is>
+          <t>중대한상해수술비</t>
         </is>
       </c>
       <c r="C64" s="136" t="n"/>
       <c r="D64" s="136" t="n"/>
       <c r="E64" s="136" t="n"/>
-      <c r="F64" s="137" t="n"/>
+      <c r="F64" s="136" t="n"/>
       <c r="G64" s="136" t="n"/>
       <c r="H64" s="136" t="n"/>
       <c r="I64" s="136" t="n"/>
-      <c r="J64" s="122" t="n"/>
+      <c r="J64" s="122">
+        <f>SUM(C57:I57)</f>
+        <v/>
+      </c>
     </row>
     <row r="65" ht="16.5" customHeight="1" s="82">
       <c r="A65" s="149" t="n"/>
       <c r="B65" s="60" t="inlineStr">
         <is>
-          <t>창상봉합술</t>
-        </is>
-      </c>
-      <c r="C65" s="121" t="n"/>
-      <c r="D65" s="121" t="n"/>
-      <c r="E65" s="121" t="n"/>
-      <c r="F65" s="121" t="n"/>
-      <c r="G65" s="121" t="n"/>
-      <c r="H65" s="121" t="n"/>
-      <c r="I65" s="121" t="n"/>
-      <c r="J65" s="122">
-        <f>SUM(C59:I59)</f>
-        <v/>
+          <t>상해 종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="C65" s="136" t="n"/>
+      <c r="D65" s="136" t="n"/>
+      <c r="E65" s="136" t="n"/>
+      <c r="F65" s="137" t="n"/>
+      <c r="G65" s="136" t="n"/>
+      <c r="H65" s="136" t="n"/>
+      <c r="I65" s="136" t="n"/>
+      <c r="J65" s="122" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" s="82">
       <c r="A66" s="149" t="n"/>
       <c r="B66" s="60" t="inlineStr">
         <is>
-          <t>골절수술비</t>
-        </is>
-      </c>
-      <c r="C66" s="121" t="n"/>
-      <c r="D66" s="121" t="n"/>
-      <c r="E66" s="121" t="n"/>
-      <c r="F66" s="121" t="n"/>
-      <c r="G66" s="121" t="n"/>
-      <c r="H66" s="121" t="n"/>
-      <c r="I66" s="121" t="n"/>
-      <c r="J66" s="122">
-        <f>SUM(C60:I60)</f>
-        <v/>
-      </c>
+          <t>상해 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C66" s="136" t="n"/>
+      <c r="D66" s="136" t="n"/>
+      <c r="E66" s="136" t="n"/>
+      <c r="F66" s="137" t="n"/>
+      <c r="G66" s="136" t="n"/>
+      <c r="H66" s="136" t="n"/>
+      <c r="I66" s="136" t="n"/>
+      <c r="J66" s="122" t="n"/>
     </row>
     <row r="67" ht="16.5" customHeight="1" s="82">
       <c r="A67" s="149" t="n"/>
-      <c r="B67" s="69" t="inlineStr">
-        <is>
-          <t>5대골절수술비</t>
+      <c r="B67" s="60" t="inlineStr">
+        <is>
+          <t>창상봉합술</t>
         </is>
       </c>
       <c r="C67" s="121" t="n"/>
@@ -2726,127 +2720,127 @@
       <c r="H67" s="121" t="n"/>
       <c r="I67" s="121" t="n"/>
       <c r="J67" s="122">
-        <f>SUM(C61:I61)</f>
+        <f>SUM(C59:I59)</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="17.25" customHeight="1" s="82">
       <c r="A68" s="149" t="n"/>
-      <c r="B68" s="57" t="inlineStr">
-        <is>
-          <t>화상수술비</t>
-        </is>
-      </c>
-      <c r="C68" s="117" t="n"/>
-      <c r="D68" s="117" t="n"/>
-      <c r="E68" s="117" t="n"/>
-      <c r="F68" s="117" t="n"/>
-      <c r="G68" s="117" t="n"/>
-      <c r="H68" s="117" t="n"/>
-      <c r="I68" s="117" t="n"/>
-      <c r="J68" s="118">
-        <f>SUM(C62:I62)</f>
+      <c r="B68" s="60" t="inlineStr">
+        <is>
+          <t>골절수술비</t>
+        </is>
+      </c>
+      <c r="C68" s="121" t="n"/>
+      <c r="D68" s="121" t="n"/>
+      <c r="E68" s="121" t="n"/>
+      <c r="F68" s="121" t="n"/>
+      <c r="G68" s="121" t="n"/>
+      <c r="H68" s="121" t="n"/>
+      <c r="I68" s="121" t="n"/>
+      <c r="J68" s="122">
+        <f>SUM(C60:I60)</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="82">
       <c r="A69" s="149" t="n"/>
-      <c r="B69" s="65" t="inlineStr">
-        <is>
-          <t>질병수술비</t>
-        </is>
-      </c>
-      <c r="C69" s="136" t="n"/>
-      <c r="D69" s="136" t="n"/>
-      <c r="E69" s="136" t="n"/>
-      <c r="F69" s="136" t="n"/>
-      <c r="G69" s="136" t="n"/>
-      <c r="H69" s="136" t="n"/>
-      <c r="I69" s="138" t="n"/>
-      <c r="J69" s="116">
-        <f>SUM(C63:I63)</f>
+      <c r="B69" s="69" t="inlineStr">
+        <is>
+          <t>5대골절수술비</t>
+        </is>
+      </c>
+      <c r="C69" s="121" t="n"/>
+      <c r="D69" s="121" t="n"/>
+      <c r="E69" s="121" t="n"/>
+      <c r="F69" s="121" t="n"/>
+      <c r="G69" s="121" t="n"/>
+      <c r="H69" s="121" t="n"/>
+      <c r="I69" s="121" t="n"/>
+      <c r="J69" s="122">
+        <f>SUM(C61:I61)</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1" s="82">
       <c r="A70" s="149" t="n"/>
-      <c r="B70" s="60" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-5종)</t>
-        </is>
-      </c>
-      <c r="C70" s="121" t="n"/>
-      <c r="D70" s="121" t="n"/>
-      <c r="E70" s="121" t="n"/>
-      <c r="F70" s="139" t="n"/>
-      <c r="G70" s="121" t="n"/>
-      <c r="H70" s="121" t="n"/>
-      <c r="I70" s="121" t="n"/>
-      <c r="J70" s="122" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="B70" s="57" t="inlineStr">
+        <is>
+          <t>화상수술비</t>
+        </is>
+      </c>
+      <c r="C70" s="117" t="n"/>
+      <c r="D70" s="117" t="n"/>
+      <c r="E70" s="117" t="n"/>
+      <c r="F70" s="117" t="n"/>
+      <c r="G70" s="117" t="n"/>
+      <c r="H70" s="117" t="n"/>
+      <c r="I70" s="117" t="n"/>
+      <c r="J70" s="118">
+        <f>SUM(C62:I62)</f>
+        <v/>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="82">
       <c r="A71" s="149" t="n"/>
-      <c r="B71" s="60" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-8종)</t>
-        </is>
-      </c>
-      <c r="C71" s="121" t="n"/>
-      <c r="D71" s="121" t="n"/>
-      <c r="E71" s="121" t="n"/>
-      <c r="F71" s="139" t="n"/>
-      <c r="G71" s="121" t="n"/>
-      <c r="H71" s="121" t="n"/>
-      <c r="I71" s="121" t="n"/>
-      <c r="J71" s="122" t="n"/>
+      <c r="B71" s="65" t="inlineStr">
+        <is>
+          <t>질병수술비</t>
+        </is>
+      </c>
+      <c r="C71" s="136" t="n"/>
+      <c r="D71" s="136" t="n"/>
+      <c r="E71" s="136" t="n"/>
+      <c r="F71" s="136" t="n"/>
+      <c r="G71" s="136" t="n"/>
+      <c r="H71" s="136" t="n"/>
+      <c r="I71" s="138" t="n"/>
+      <c r="J71" s="116">
+        <f>SUM(C63:I63)</f>
+        <v/>
+      </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" s="82">
       <c r="A72" s="149" t="n"/>
-      <c r="B72" s="72" t="inlineStr">
-        <is>
-          <t>뇌혈관수술비</t>
-        </is>
-      </c>
-      <c r="C72" s="140" t="n"/>
-      <c r="D72" s="140" t="n"/>
-      <c r="E72" s="140" t="n"/>
-      <c r="F72" s="140" t="n"/>
-      <c r="G72" s="140" t="n"/>
-      <c r="H72" s="140" t="n"/>
-      <c r="I72" s="140" t="n"/>
-      <c r="J72" s="122">
-        <f>SUM(C65:I65)</f>
-        <v/>
+      <c r="B72" s="60" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="C72" s="121" t="n"/>
+      <c r="D72" s="121" t="n"/>
+      <c r="E72" s="121" t="n"/>
+      <c r="F72" s="139" t="n"/>
+      <c r="G72" s="121" t="n"/>
+      <c r="H72" s="121" t="n"/>
+      <c r="I72" s="121" t="n"/>
+      <c r="J72" s="122" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="82">
       <c r="A73" s="149" t="n"/>
-      <c r="B73" s="72" t="inlineStr">
-        <is>
-          <t>허혈성수술비</t>
-        </is>
-      </c>
-      <c r="C73" s="140" t="n"/>
-      <c r="D73" s="140" t="n"/>
-      <c r="E73" s="140" t="n"/>
-      <c r="F73" s="140" t="n"/>
-      <c r="G73" s="140" t="n"/>
-      <c r="H73" s="140" t="n"/>
-      <c r="I73" s="140" t="n"/>
-      <c r="J73" s="122">
-        <f>SUM(C66:I66)</f>
-        <v/>
-      </c>
+      <c r="B73" s="60" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C73" s="121" t="n"/>
+      <c r="D73" s="121" t="n"/>
+      <c r="E73" s="121" t="n"/>
+      <c r="F73" s="139" t="n"/>
+      <c r="G73" s="121" t="n"/>
+      <c r="H73" s="121" t="n"/>
+      <c r="I73" s="121" t="n"/>
+      <c r="J73" s="122" t="n"/>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="82">
       <c r="A74" s="149" t="n"/>
       <c r="B74" s="72" t="inlineStr">
         <is>
-          <t>심장수술비</t>
+          <t>뇌혈관수술비</t>
         </is>
       </c>
       <c r="C74" s="140" t="n"/>
@@ -2857,15 +2851,15 @@
       <c r="H74" s="140" t="n"/>
       <c r="I74" s="140" t="n"/>
       <c r="J74" s="122">
-        <f>SUM(C67:I67)</f>
+        <f>SUM(C65:I65)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="82">
       <c r="A75" s="149" t="n"/>
-      <c r="B75" s="61" t="inlineStr">
-        <is>
-          <t>120대수술비</t>
+      <c r="B75" s="72" t="inlineStr">
+        <is>
+          <t>허혈성수술비</t>
         </is>
       </c>
       <c r="C75" s="140" t="n"/>
@@ -2875,115 +2869,115 @@
       <c r="G75" s="140" t="n"/>
       <c r="H75" s="140" t="n"/>
       <c r="I75" s="140" t="n"/>
-      <c r="J75" s="141">
-        <f>SUM(C68:I68)</f>
+      <c r="J75" s="122">
+        <f>SUM(C66:I66)</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="17.25" customHeight="1" s="82">
       <c r="A76" s="149" t="n"/>
-      <c r="B76" s="73" t="inlineStr">
-        <is>
-          <t>5대기관 수술비 관혈</t>
-        </is>
-      </c>
-      <c r="C76" s="123" t="n"/>
-      <c r="D76" s="123" t="n"/>
-      <c r="E76" s="123" t="n"/>
-      <c r="F76" s="123" t="n"/>
-      <c r="G76" s="123" t="n"/>
-      <c r="H76" s="123" t="n"/>
-      <c r="I76" s="123" t="n"/>
-      <c r="J76" s="120">
-        <f>SUM(C69:I69)</f>
+      <c r="B76" s="72" t="inlineStr">
+        <is>
+          <t>심장수술비</t>
+        </is>
+      </c>
+      <c r="C76" s="140" t="n"/>
+      <c r="D76" s="140" t="n"/>
+      <c r="E76" s="140" t="n"/>
+      <c r="F76" s="140" t="n"/>
+      <c r="G76" s="140" t="n"/>
+      <c r="H76" s="140" t="n"/>
+      <c r="I76" s="140" t="n"/>
+      <c r="J76" s="122">
+        <f>SUM(C67:I67)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="82">
       <c r="A77" s="149" t="n"/>
-      <c r="B77" s="74" t="inlineStr">
-        <is>
-          <t>5대기관 수술비 비관혈</t>
-        </is>
-      </c>
-      <c r="C77" s="117" t="n"/>
-      <c r="D77" s="117" t="n"/>
-      <c r="E77" s="117" t="n"/>
-      <c r="F77" s="117" t="n"/>
-      <c r="G77" s="117" t="n"/>
-      <c r="H77" s="117" t="n"/>
-      <c r="I77" s="117" t="n"/>
-      <c r="J77" s="118">
-        <f>SUM(C70:I70)</f>
+      <c r="B77" s="61" t="inlineStr">
+        <is>
+          <t>120대수술비</t>
+        </is>
+      </c>
+      <c r="C77" s="140" t="n"/>
+      <c r="D77" s="140" t="n"/>
+      <c r="E77" s="140" t="n"/>
+      <c r="F77" s="140" t="n"/>
+      <c r="G77" s="140" t="n"/>
+      <c r="H77" s="140" t="n"/>
+      <c r="I77" s="140" t="n"/>
+      <c r="J77" s="141">
+        <f>SUM(C68:I68)</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16.5" customHeight="1" s="82">
-      <c r="A78" s="150" t="inlineStr">
-        <is>
-          <t>운전</t>
-        </is>
-      </c>
-      <c r="B78" s="28" t="inlineStr">
-        <is>
-          <t>대인</t>
-        </is>
-      </c>
-      <c r="C78" s="102" t="n"/>
-      <c r="D78" s="102" t="n"/>
-      <c r="E78" s="102" t="n"/>
-      <c r="F78" s="102" t="n"/>
-      <c r="G78" s="102" t="n"/>
-      <c r="H78" s="102" t="n"/>
-      <c r="I78" s="102" t="n"/>
+      <c r="A78" s="149" t="n"/>
+      <c r="B78" s="73" t="inlineStr">
+        <is>
+          <t>5대기관 수술비 관혈</t>
+        </is>
+      </c>
+      <c r="C78" s="123" t="n"/>
+      <c r="D78" s="123" t="n"/>
+      <c r="E78" s="123" t="n"/>
+      <c r="F78" s="123" t="n"/>
+      <c r="G78" s="123" t="n"/>
+      <c r="H78" s="123" t="n"/>
+      <c r="I78" s="123" t="n"/>
       <c r="J78" s="120">
-        <f>SUM(C71:I71)</f>
+        <f>SUM(C69:I69)</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="17.25" customHeight="1" s="82">
       <c r="A79" s="149" t="n"/>
-      <c r="B79" s="31" t="inlineStr">
-        <is>
-          <t>대물</t>
-        </is>
-      </c>
-      <c r="C79" s="130" t="n"/>
-      <c r="D79" s="130" t="n"/>
-      <c r="E79" s="130" t="n"/>
-      <c r="F79" s="130" t="n"/>
-      <c r="G79" s="130" t="n"/>
-      <c r="H79" s="130" t="n"/>
-      <c r="I79" s="130" t="n"/>
-      <c r="J79" s="122">
-        <f>SUM(C72:I72)</f>
+      <c r="B79" s="74" t="inlineStr">
+        <is>
+          <t>5대기관 수술비 비관혈</t>
+        </is>
+      </c>
+      <c r="C79" s="117" t="n"/>
+      <c r="D79" s="117" t="n"/>
+      <c r="E79" s="117" t="n"/>
+      <c r="F79" s="117" t="n"/>
+      <c r="G79" s="117" t="n"/>
+      <c r="H79" s="117" t="n"/>
+      <c r="I79" s="117" t="n"/>
+      <c r="J79" s="118">
+        <f>SUM(C70:I70)</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="17.25" customHeight="1" s="82">
-      <c r="A80" s="149" t="n"/>
-      <c r="B80" s="31" t="inlineStr">
-        <is>
-          <t>합의금</t>
-        </is>
-      </c>
-      <c r="C80" s="130" t="n"/>
-      <c r="D80" s="130" t="n"/>
-      <c r="E80" s="130" t="n"/>
-      <c r="F80" s="130" t="n"/>
-      <c r="G80" s="130" t="n"/>
-      <c r="H80" s="130" t="n"/>
-      <c r="I80" s="130" t="n"/>
-      <c r="J80" s="122">
-        <f>SUM(C73:I73)</f>
+      <c r="A80" s="150" t="inlineStr">
+        <is>
+          <t>운전</t>
+        </is>
+      </c>
+      <c r="B80" s="28" t="inlineStr">
+        <is>
+          <t>대인</t>
+        </is>
+      </c>
+      <c r="C80" s="102" t="n"/>
+      <c r="D80" s="102" t="n"/>
+      <c r="E80" s="102" t="n"/>
+      <c r="F80" s="102" t="n"/>
+      <c r="G80" s="102" t="n"/>
+      <c r="H80" s="102" t="n"/>
+      <c r="I80" s="102" t="n"/>
+      <c r="J80" s="120">
+        <f>SUM(C71:I71)</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="17.25" customHeight="1" s="82">
       <c r="A81" s="149" t="n"/>
-      <c r="B81" s="66" t="inlineStr">
-        <is>
-          <t>6주미만</t>
+      <c r="B81" s="31" t="inlineStr">
+        <is>
+          <t>대물</t>
         </is>
       </c>
       <c r="C81" s="130" t="n"/>
@@ -2994,7 +2988,7 @@
       <c r="H81" s="130" t="n"/>
       <c r="I81" s="130" t="n"/>
       <c r="J81" s="122">
-        <f>SUM(C74:I74)</f>
+        <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
@@ -3002,7 +2996,7 @@
       <c r="A82" s="149" t="n"/>
       <c r="B82" s="31" t="inlineStr">
         <is>
-          <t>변호사</t>
+          <t>합의금</t>
         </is>
       </c>
       <c r="C82" s="130" t="n"/>
@@ -3013,184 +3007,180 @@
       <c r="H82" s="130" t="n"/>
       <c r="I82" s="130" t="n"/>
       <c r="J82" s="122">
+        <f>SUM(C73:I73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="17.25" customHeight="1" s="82">
+      <c r="A83" s="149" t="n"/>
+      <c r="B83" s="66" t="inlineStr">
+        <is>
+          <t>6주미만</t>
+        </is>
+      </c>
+      <c r="C83" s="130" t="n"/>
+      <c r="D83" s="130" t="n"/>
+      <c r="E83" s="130" t="n"/>
+      <c r="F83" s="130" t="n"/>
+      <c r="G83" s="130" t="n"/>
+      <c r="H83" s="130" t="n"/>
+      <c r="I83" s="130" t="n"/>
+      <c r="J83" s="122">
+        <f>SUM(C74:I74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="16.5" customHeight="1" s="82">
+      <c r="A84" s="149" t="n"/>
+      <c r="B84" s="31" t="inlineStr">
+        <is>
+          <t>변호사</t>
+        </is>
+      </c>
+      <c r="C84" s="130" t="n"/>
+      <c r="D84" s="130" t="n"/>
+      <c r="E84" s="130" t="n"/>
+      <c r="F84" s="130" t="n"/>
+      <c r="G84" s="130" t="n"/>
+      <c r="H84" s="130" t="n"/>
+      <c r="I84" s="130" t="n"/>
+      <c r="J84" s="122">
         <f>SUM(C75:I75)</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="17.25" customHeight="1" s="82">
-      <c r="A83" s="151" t="n"/>
-      <c r="B83" s="25" t="inlineStr">
+    <row r="85" ht="17.25" customHeight="1" s="82">
+      <c r="A85" s="151" t="n"/>
+      <c r="B85" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C83" s="142" t="n"/>
-      <c r="D83" s="142" t="n"/>
-      <c r="E83" s="142" t="n"/>
-      <c r="F83" s="142" t="n"/>
-      <c r="G83" s="142" t="n"/>
-      <c r="H83" s="142" t="n"/>
-      <c r="I83" s="142" t="n"/>
-      <c r="J83" s="118">
+      <c r="C85" s="142" t="n"/>
+      <c r="D85" s="142" t="n"/>
+      <c r="E85" s="142" t="n"/>
+      <c r="F85" s="142" t="n"/>
+      <c r="G85" s="142" t="n"/>
+      <c r="H85" s="142" t="n"/>
+      <c r="I85" s="142" t="n"/>
+      <c r="J85" s="118">
         <f>SUM(C76:I76)</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="16.5" customHeight="1" s="82">
-      <c r="A84" s="150" t="inlineStr">
+    <row r="86" ht="16.5" customHeight="1" s="82">
+      <c r="A86" s="150" t="inlineStr">
         <is>
           <t>골절</t>
         </is>
       </c>
-      <c r="B84" s="65" t="inlineStr">
+      <c r="B86" s="65" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C84" s="136" t="n"/>
-      <c r="D84" s="136" t="n"/>
-      <c r="E84" s="136" t="n"/>
-      <c r="F84" s="136" t="n"/>
-      <c r="G84" s="136" t="n"/>
-      <c r="H84" s="136" t="n"/>
-      <c r="I84" s="136" t="n"/>
-      <c r="J84" s="116">
+      <c r="C86" s="136" t="n"/>
+      <c r="D86" s="136" t="n"/>
+      <c r="E86" s="136" t="n"/>
+      <c r="F86" s="136" t="n"/>
+      <c r="G86" s="136" t="n"/>
+      <c r="H86" s="136" t="n"/>
+      <c r="I86" s="136" t="n"/>
+      <c r="J86" s="116">
         <f>SUM(C77:I77)</f>
         <v/>
       </c>
     </row>
-    <row r="85" ht="17.25" customHeight="1" s="82">
-      <c r="A85" s="149" t="n"/>
-      <c r="B85" s="60" t="inlineStr">
+    <row r="87" ht="16.5" customHeight="1" s="82">
+      <c r="A87" s="149" t="n"/>
+      <c r="B87" s="60" t="inlineStr">
         <is>
           <t>골절(치아파절제외)</t>
         </is>
       </c>
-      <c r="C85" s="121" t="n"/>
-      <c r="D85" s="121" t="n"/>
-      <c r="E85" s="121" t="n"/>
-      <c r="F85" s="121" t="n"/>
-      <c r="G85" s="121" t="n"/>
-      <c r="H85" s="121" t="n"/>
-      <c r="I85" s="121" t="n"/>
-      <c r="J85" s="122">
+      <c r="C87" s="121" t="n"/>
+      <c r="D87" s="121" t="n"/>
+      <c r="E87" s="121" t="n"/>
+      <c r="F87" s="121" t="n"/>
+      <c r="G87" s="121" t="n"/>
+      <c r="H87" s="121" t="n"/>
+      <c r="I87" s="121" t="n"/>
+      <c r="J87" s="122">
         <f>SUM(C78:I78)</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="16.5" customHeight="1" s="82">
-      <c r="A86" s="151" t="n"/>
-      <c r="B86" s="74" t="inlineStr">
+    <row r="88" ht="17.25" customHeight="1" s="82">
+      <c r="A88" s="151" t="n"/>
+      <c r="B88" s="74" t="inlineStr">
         <is>
           <t>5대골절진단비</t>
         </is>
       </c>
-      <c r="C86" s="117" t="n"/>
-      <c r="D86" s="117" t="n"/>
-      <c r="E86" s="117" t="n"/>
-      <c r="F86" s="117" t="n"/>
-      <c r="G86" s="117" t="n"/>
-      <c r="H86" s="117" t="n"/>
-      <c r="I86" s="117" t="n"/>
-      <c r="J86" s="118">
+      <c r="C88" s="117" t="n"/>
+      <c r="D88" s="117" t="n"/>
+      <c r="E88" s="117" t="n"/>
+      <c r="F88" s="117" t="n"/>
+      <c r="G88" s="117" t="n"/>
+      <c r="H88" s="117" t="n"/>
+      <c r="I88" s="117" t="n"/>
+      <c r="J88" s="118">
         <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="16.5" customHeight="1" s="82">
-      <c r="A87" s="99" t="inlineStr">
+    <row r="89" ht="17.25" customHeight="1" s="82">
+      <c r="A89" s="99" t="inlineStr">
         <is>
           <t>응급실</t>
         </is>
       </c>
-      <c r="B87" s="64" t="inlineStr">
+      <c r="B89" s="64" t="inlineStr">
         <is>
           <t>응급실(응급)</t>
         </is>
       </c>
-      <c r="C87" s="113" t="n"/>
-      <c r="D87" s="113" t="n"/>
-      <c r="E87" s="113" t="n"/>
-      <c r="F87" s="113" t="n"/>
-      <c r="G87" s="113" t="n"/>
-      <c r="H87" s="113" t="n"/>
-      <c r="I87" s="113" t="n"/>
-      <c r="J87" s="114">
+      <c r="C89" s="113" t="n"/>
+      <c r="D89" s="113" t="n"/>
+      <c r="E89" s="113" t="n"/>
+      <c r="F89" s="113" t="n"/>
+      <c r="G89" s="113" t="n"/>
+      <c r="H89" s="113" t="n"/>
+      <c r="I89" s="113" t="n"/>
+      <c r="J89" s="114">
         <f>SUM(C80:I80)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="17.25" customHeight="1" s="82">
-      <c r="A88" s="87" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="87" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="B88" s="34" t="inlineStr">
+      <c r="B90" s="34" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="C88" s="123" t="n"/>
-      <c r="D88" s="123" t="n"/>
-      <c r="E88" s="123" t="n"/>
-      <c r="F88" s="123" t="n"/>
-      <c r="G88" s="123" t="n"/>
-      <c r="H88" s="123" t="n"/>
-      <c r="I88" s="123" t="n"/>
-      <c r="J88" s="124" t="n"/>
-    </row>
-    <row r="89" ht="17.25" customHeight="1" s="82">
-      <c r="A89" s="150" t="inlineStr">
-        <is>
-          <t>화상</t>
-        </is>
-      </c>
-      <c r="B89" s="28" t="inlineStr">
-        <is>
-          <t>화상진단비</t>
-        </is>
-      </c>
-      <c r="C89" s="119" t="n"/>
-      <c r="D89" s="119" t="n"/>
-      <c r="E89" s="119" t="n"/>
-      <c r="F89" s="119" t="n"/>
-      <c r="G89" s="119" t="n"/>
-      <c r="H89" s="119" t="n"/>
-      <c r="I89" s="119" t="n"/>
-      <c r="J89" s="120">
-        <f>SUM(C82:I82)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="151" t="n"/>
-      <c r="B90" s="25" t="inlineStr">
-        <is>
-          <t>중증화상진단비</t>
-        </is>
-      </c>
-      <c r="C90" s="117" t="n"/>
-      <c r="D90" s="117" t="n"/>
-      <c r="E90" s="117" t="n"/>
-      <c r="F90" s="117" t="n"/>
-      <c r="G90" s="117" t="n"/>
-      <c r="H90" s="117" t="n"/>
-      <c r="I90" s="117" t="n"/>
-      <c r="J90" s="118">
-        <f>SUM(C83:I83)</f>
-        <v/>
-      </c>
+      <c r="C90" s="123" t="n"/>
+      <c r="D90" s="123" t="n"/>
+      <c r="E90" s="123" t="n"/>
+      <c r="F90" s="123" t="n"/>
+      <c r="G90" s="123" t="n"/>
+      <c r="H90" s="123" t="n"/>
+      <c r="I90" s="123" t="n"/>
+      <c r="J90" s="124" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="150" t="inlineStr">
         <is>
-          <t>깁스</t>
-        </is>
-      </c>
-      <c r="B91" s="95" t="inlineStr">
-        <is>
-          <t>반깁스</t>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B91" s="28" t="inlineStr">
+        <is>
+          <t>화상진단비</t>
         </is>
       </c>
       <c r="C91" s="119" t="n"/>
@@ -3201,15 +3191,15 @@
       <c r="H91" s="119" t="n"/>
       <c r="I91" s="119" t="n"/>
       <c r="J91" s="120">
-        <f>SUM(C84:I84)</f>
+        <f>SUM(C82:I82)</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="151" t="n"/>
-      <c r="B92" s="57" t="inlineStr">
-        <is>
-          <t>깁스진단비</t>
+      <c r="B92" s="25" t="inlineStr">
+        <is>
+          <t>중증화상진단비</t>
         </is>
       </c>
       <c r="C92" s="117" t="n"/>
@@ -3220,129 +3210,171 @@
       <c r="H92" s="117" t="n"/>
       <c r="I92" s="117" t="n"/>
       <c r="J92" s="118">
-        <f>SUM(C85:I85)</f>
+        <f>SUM(C83:I83)</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="150" t="inlineStr">
         <is>
+          <t>깁스</t>
+        </is>
+      </c>
+      <c r="B93" s="95" t="inlineStr">
+        <is>
+          <t>반깁스</t>
+        </is>
+      </c>
+      <c r="C93" s="119" t="n"/>
+      <c r="D93" s="119" t="n"/>
+      <c r="E93" s="119" t="n"/>
+      <c r="F93" s="119" t="n"/>
+      <c r="G93" s="119" t="n"/>
+      <c r="H93" s="119" t="n"/>
+      <c r="I93" s="119" t="n"/>
+      <c r="J93" s="120">
+        <f>SUM(C84:I84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="151" t="n"/>
+      <c r="B94" s="57" t="inlineStr">
+        <is>
+          <t>깁스진단비</t>
+        </is>
+      </c>
+      <c r="C94" s="117" t="n"/>
+      <c r="D94" s="117" t="n"/>
+      <c r="E94" s="117" t="n"/>
+      <c r="F94" s="117" t="n"/>
+      <c r="G94" s="117" t="n"/>
+      <c r="H94" s="117" t="n"/>
+      <c r="I94" s="117" t="n"/>
+      <c r="J94" s="118">
+        <f>SUM(C85:I85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" s="82">
+      <c r="A95" s="150" t="inlineStr">
+        <is>
           <t>실손</t>
         </is>
       </c>
-      <c r="B93" s="95" t="inlineStr">
+      <c r="B95" s="95" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="C93" s="143" t="n"/>
-      <c r="D93" s="143" t="n"/>
-      <c r="E93" s="143" t="n"/>
-      <c r="F93" s="143" t="n"/>
-      <c r="G93" s="143" t="n"/>
-      <c r="H93" s="143" t="n"/>
-      <c r="I93" s="143" t="n"/>
-      <c r="J93" s="120">
+      <c r="C95" s="143" t="n"/>
+      <c r="D95" s="143" t="n"/>
+      <c r="E95" s="143" t="n"/>
+      <c r="F95" s="143" t="n"/>
+      <c r="G95" s="143" t="n"/>
+      <c r="H95" s="143" t="n"/>
+      <c r="I95" s="143" t="n"/>
+      <c r="J95" s="120">
         <f>SUM(C86:I86)</f>
         <v/>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="149" t="n"/>
-      <c r="B94" s="60" t="inlineStr">
+    <row r="96" s="82">
+      <c r="A96" s="149" t="n"/>
+      <c r="B96" s="60" t="inlineStr">
         <is>
           <t>통원</t>
         </is>
       </c>
-      <c r="C94" s="144" t="n"/>
-      <c r="D94" s="144" t="n"/>
-      <c r="E94" s="144" t="n"/>
-      <c r="F94" s="144" t="n"/>
-      <c r="G94" s="144" t="n"/>
-      <c r="H94" s="144" t="n"/>
-      <c r="I94" s="144" t="n"/>
-      <c r="J94" s="122">
+      <c r="C96" s="144" t="n"/>
+      <c r="D96" s="144" t="n"/>
+      <c r="E96" s="144" t="n"/>
+      <c r="F96" s="144" t="n"/>
+      <c r="G96" s="144" t="n"/>
+      <c r="H96" s="144" t="n"/>
+      <c r="I96" s="144" t="n"/>
+      <c r="J96" s="122">
         <f>SUM(C87:I87)</f>
         <v/>
       </c>
     </row>
-    <row r="95" s="82">
-      <c r="A95" s="149" t="n"/>
-      <c r="B95" s="22" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="149" t="n"/>
+      <c r="B97" s="22" t="inlineStr">
         <is>
           <t>약값</t>
         </is>
       </c>
-      <c r="C95" s="115" t="n"/>
-      <c r="D95" s="115" t="n"/>
-      <c r="E95" s="115" t="n"/>
-      <c r="F95" s="115" t="n"/>
-      <c r="G95" s="115" t="n"/>
-      <c r="H95" s="115" t="n"/>
-      <c r="I95" s="145" t="n"/>
-      <c r="J95" s="122">
+      <c r="C97" s="115" t="n"/>
+      <c r="D97" s="115" t="n"/>
+      <c r="E97" s="115" t="n"/>
+      <c r="F97" s="115" t="n"/>
+      <c r="G97" s="115" t="n"/>
+      <c r="H97" s="115" t="n"/>
+      <c r="I97" s="145" t="n"/>
+      <c r="J97" s="122">
         <f>SUM(C88:I88)</f>
         <v/>
       </c>
     </row>
-    <row r="96" s="82">
-      <c r="A96" s="151" t="n"/>
-      <c r="B96" s="22" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="151" t="n"/>
+      <c r="B98" s="22" t="inlineStr">
         <is>
           <t>MRI/도수치료/비급여주사</t>
         </is>
       </c>
-      <c r="C96" s="115" t="n"/>
-      <c r="D96" s="115" t="n"/>
-      <c r="E96" s="115" t="n"/>
-      <c r="F96" s="115" t="n"/>
-      <c r="G96" s="115" t="n"/>
-      <c r="H96" s="115" t="n"/>
-      <c r="I96" s="145" t="n"/>
-      <c r="J96" s="122" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="87" t="inlineStr">
+      <c r="C98" s="115" t="n"/>
+      <c r="D98" s="115" t="n"/>
+      <c r="E98" s="115" t="n"/>
+      <c r="F98" s="115" t="n"/>
+      <c r="G98" s="115" t="n"/>
+      <c r="H98" s="115" t="n"/>
+      <c r="I98" s="145" t="n"/>
+      <c r="J98" s="122" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="87" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B97" s="79" t="inlineStr">
+      <c r="B99" s="79" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C97" s="146" t="n"/>
-      <c r="D97" s="146" t="n"/>
-      <c r="E97" s="146" t="n"/>
-      <c r="F97" s="146" t="n"/>
-      <c r="G97" s="146" t="n"/>
-      <c r="H97" s="146" t="n"/>
-      <c r="I97" s="146" t="n"/>
-      <c r="J97" s="147">
+      <c r="C99" s="146" t="n"/>
+      <c r="D99" s="146" t="n"/>
+      <c r="E99" s="146" t="n"/>
+      <c r="F99" s="146" t="n"/>
+      <c r="G99" s="146" t="n"/>
+      <c r="H99" s="146" t="n"/>
+      <c r="I99" s="146" t="n"/>
+      <c r="J99" s="147">
         <f>SUM(C89:I89)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A30:A37"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A63:A79"/>
+    <mergeCell ref="A93:A94"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A84:A86"/>
+    <mergeCell ref="A15:A29"/>
+    <mergeCell ref="A50:A62"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A61:A77"/>
+    <mergeCell ref="A38:A49"/>
+    <mergeCell ref="A86:A88"/>
     <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A91:A92"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A80:A85"/>
     <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A93:A96"/>
-    <mergeCell ref="A49:A60"/>
-    <mergeCell ref="A78:A83"/>
-    <mergeCell ref="A37:A48"/>
-    <mergeCell ref="A29:A36"/>
-    <mergeCell ref="A15:A28"/>
-    <mergeCell ref="A89:A90"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>

--- a/master.xlsx
+++ b/master.xlsx
@@ -2364,7 +2364,7 @@
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="82">
-      <c r="A49" s="89" t="n"/>
+      <c r="A49" s="88" t="n"/>
       <c r="B49" s="16" t="inlineStr">
         <is>
           <t>중대한 급성심근</t>
@@ -2383,11 +2383,7 @@
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" s="82">
-      <c r="A50" s="99" t="inlineStr">
-        <is>
-          <t>일당</t>
-        </is>
-      </c>
+      <c r="A50" s="89" t="n"/>
       <c r="B50" s="64" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
@@ -2406,7 +2402,11 @@
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" s="82">
-      <c r="A51" s="88" t="n"/>
+      <c r="A51" s="99" t="inlineStr">
+        <is>
+          <t>일당</t>
+        </is>
+      </c>
       <c r="B51" s="95" t="inlineStr">
         <is>
           <t>질병일당</t>
@@ -3358,23 +3358,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A15:A29"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A30:A37"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A80:A85"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A51:A62"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A38:A50"/>
+    <mergeCell ref="A6:A10"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A63:A79"/>
     <mergeCell ref="A93:A94"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A15:A29"/>
-    <mergeCell ref="A50:A62"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A38:A49"/>
     <mergeCell ref="A86:A88"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A95:A98"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A80:A85"/>
-    <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>

--- a/master.xlsx
+++ b/master.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="법칙" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="0.0001"/>
 </workbook>
 </file>
 

--- a/master.xlsx
+++ b/master.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="법칙" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
@@ -1458,7 +1458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="82" min="1" max="1"/>
@@ -3317,8 +3317,8 @@
         <v/>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="151" t="n"/>
+    <row r="98" s="82">
+      <c r="A98" s="149" t="n"/>
       <c r="B98" s="22" t="inlineStr">
         <is>
           <t>MRI/도수치료/비급여주사</t>
@@ -3333,48 +3333,64 @@
       <c r="I98" s="145" t="n"/>
       <c r="J98" s="122" t="n"/>
     </row>
-    <row r="99">
-      <c r="A99" s="87" t="inlineStr">
+    <row r="99" s="82">
+      <c r="A99" s="151" t="n"/>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>상해의료비</t>
+        </is>
+      </c>
+      <c r="C99" s="115" t="n"/>
+      <c r="D99" s="115" t="n"/>
+      <c r="E99" s="115" t="n"/>
+      <c r="F99" s="115" t="n"/>
+      <c r="G99" s="115" t="n"/>
+      <c r="H99" s="115" t="n"/>
+      <c r="I99" s="145" t="n"/>
+      <c r="J99" s="122" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="87" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B99" s="79" t="inlineStr">
+      <c r="B100" s="79" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C99" s="146" t="n"/>
-      <c r="D99" s="146" t="n"/>
-      <c r="E99" s="146" t="n"/>
-      <c r="F99" s="146" t="n"/>
-      <c r="G99" s="146" t="n"/>
-      <c r="H99" s="146" t="n"/>
-      <c r="I99" s="146" t="n"/>
-      <c r="J99" s="147">
+      <c r="C100" s="146" t="n"/>
+      <c r="D100" s="146" t="n"/>
+      <c r="E100" s="146" t="n"/>
+      <c r="F100" s="146" t="n"/>
+      <c r="G100" s="146" t="n"/>
+      <c r="H100" s="146" t="n"/>
+      <c r="I100" s="146" t="n"/>
+      <c r="J100" s="147">
         <f>SUM(C89:I89)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A30:A37"/>
+    <mergeCell ref="A63:A79"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A15:A29"/>
+    <mergeCell ref="A51:A62"/>
+    <mergeCell ref="A95:A99"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A86:A88"/>
     <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A91:A92"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A30:A37"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A95:A98"/>
+    <mergeCell ref="A38:A50"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A80:A85"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A51:A62"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A38:A50"/>
     <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A63:A79"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="A86:A88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>

--- a/master.xlsx
+++ b/master.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="법칙" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" fullCalcOnLoad="0" iterateDelta="0.0001"/>
 </workbook>
 </file>
 

--- a/master.xlsx
+++ b/master.xlsx
@@ -1458,7 +1458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="82" min="1" max="1"/>
@@ -2464,28 +2464,25 @@
     </row>
     <row r="54" ht="16.5" customHeight="1" s="82">
       <c r="A54" s="88" t="n"/>
-      <c r="B54" s="60" t="inlineStr">
-        <is>
-          <t>상해일당</t>
-        </is>
-      </c>
-      <c r="C54" s="121" t="n"/>
-      <c r="D54" s="121" t="n"/>
-      <c r="E54" s="121" t="n"/>
-      <c r="F54" s="121" t="n"/>
-      <c r="G54" s="121" t="n"/>
-      <c r="H54" s="121" t="n"/>
-      <c r="I54" s="121" t="n"/>
-      <c r="J54" s="122">
-        <f>SUM(C49:I49)</f>
-        <v/>
-      </c>
+      <c r="B54" s="65" t="inlineStr">
+        <is>
+          <t>상급병원질병입원일당</t>
+        </is>
+      </c>
+      <c r="C54" s="136" t="n"/>
+      <c r="D54" s="136" t="n"/>
+      <c r="E54" s="136" t="n"/>
+      <c r="F54" s="136" t="n"/>
+      <c r="G54" s="136" t="n"/>
+      <c r="H54" s="136" t="n"/>
+      <c r="I54" s="136" t="n"/>
+      <c r="J54" s="122" t="n"/>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="82">
       <c r="A55" s="88" t="n"/>
       <c r="B55" s="60" t="inlineStr">
         <is>
-          <t>상해수술일당</t>
+          <t>상해일당</t>
         </is>
       </c>
       <c r="C55" s="121" t="n"/>
@@ -2495,13 +2492,16 @@
       <c r="G55" s="121" t="n"/>
       <c r="H55" s="121" t="n"/>
       <c r="I55" s="121" t="n"/>
-      <c r="J55" s="122" t="n"/>
+      <c r="J55" s="122">
+        <f>SUM(C49:I49)</f>
+        <v/>
+      </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" s="82">
       <c r="A56" s="88" t="n"/>
-      <c r="B56" s="31" t="inlineStr">
-        <is>
-          <t>간병인</t>
+      <c r="B56" s="60" t="inlineStr">
+        <is>
+          <t>상해수술일당</t>
         </is>
       </c>
       <c r="C56" s="121" t="n"/>
@@ -2511,16 +2511,13 @@
       <c r="G56" s="121" t="n"/>
       <c r="H56" s="121" t="n"/>
       <c r="I56" s="121" t="n"/>
-      <c r="J56" s="122">
-        <f>SUM(C50:I50)</f>
-        <v/>
-      </c>
+      <c r="J56" s="122" t="n"/>
     </row>
     <row r="57" ht="16.5" customHeight="1" s="82">
       <c r="A57" s="88" t="n"/>
       <c r="B57" s="31" t="inlineStr">
         <is>
-          <t>간병인지원일당</t>
+          <t>간병인</t>
         </is>
       </c>
       <c r="C57" s="121" t="n"/>
@@ -2530,13 +2527,16 @@
       <c r="G57" s="121" t="n"/>
       <c r="H57" s="121" t="n"/>
       <c r="I57" s="121" t="n"/>
-      <c r="J57" s="122" t="n"/>
+      <c r="J57" s="122">
+        <f>SUM(C50:I50)</f>
+        <v/>
+      </c>
     </row>
     <row r="58" ht="16.5" customHeight="1" s="82">
       <c r="A58" s="88" t="n"/>
       <c r="B58" s="31" t="inlineStr">
         <is>
-          <t>간호통합병동</t>
+          <t>간병인지원일당</t>
         </is>
       </c>
       <c r="C58" s="121" t="n"/>
@@ -2546,16 +2546,13 @@
       <c r="G58" s="121" t="n"/>
       <c r="H58" s="121" t="n"/>
       <c r="I58" s="121" t="n"/>
-      <c r="J58" s="122">
-        <f>SUM(C51:I51)</f>
-        <v/>
-      </c>
+      <c r="J58" s="122" t="n"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" s="82">
       <c r="A59" s="88" t="n"/>
-      <c r="B59" s="66" t="inlineStr">
-        <is>
-          <t>1인실 종합병원</t>
+      <c r="B59" s="31" t="inlineStr">
+        <is>
+          <t>간호통합병동</t>
         </is>
       </c>
       <c r="C59" s="121" t="n"/>
@@ -2566,7 +2563,7 @@
       <c r="H59" s="121" t="n"/>
       <c r="I59" s="121" t="n"/>
       <c r="J59" s="122">
-        <f>SUM(C52:I52)</f>
+        <f>SUM(C51:I51)</f>
         <v/>
       </c>
     </row>
@@ -2574,7 +2571,7 @@
       <c r="A60" s="88" t="n"/>
       <c r="B60" s="66" t="inlineStr">
         <is>
-          <t>1인실 상급병원</t>
+          <t>1인실 종합병원</t>
         </is>
       </c>
       <c r="C60" s="121" t="n"/>
@@ -2585,15 +2582,15 @@
       <c r="H60" s="121" t="n"/>
       <c r="I60" s="121" t="n"/>
       <c r="J60" s="122">
-        <f>SUM(C53:I53)</f>
+        <f>SUM(C52:I52)</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1" s="82">
       <c r="A61" s="88" t="n"/>
-      <c r="B61" s="31" t="inlineStr">
-        <is>
-          <t>질병중환자실</t>
+      <c r="B61" s="66" t="inlineStr">
+        <is>
+          <t>1인실 상급병원</t>
         </is>
       </c>
       <c r="C61" s="121" t="n"/>
@@ -2604,96 +2601,95 @@
       <c r="H61" s="121" t="n"/>
       <c r="I61" s="121" t="n"/>
       <c r="J61" s="122">
+        <f>SUM(C53:I53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="17.25" customHeight="1" s="82">
+      <c r="A62" s="88" t="n"/>
+      <c r="B62" s="31" t="inlineStr">
+        <is>
+          <t>질병중환자실</t>
+        </is>
+      </c>
+      <c r="C62" s="121" t="n"/>
+      <c r="D62" s="121" t="n"/>
+      <c r="E62" s="121" t="n"/>
+      <c r="F62" s="121" t="n"/>
+      <c r="G62" s="121" t="n"/>
+      <c r="H62" s="121" t="n"/>
+      <c r="I62" s="121" t="n"/>
+      <c r="J62" s="122">
         <f>SUM(C54:I54)</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="17.25" customHeight="1" s="82">
-      <c r="A62" s="89" t="n"/>
-      <c r="B62" s="25" t="inlineStr">
+    <row r="63" ht="17.25" customHeight="1" s="82">
+      <c r="A63" s="89" t="n"/>
+      <c r="B63" s="25" t="inlineStr">
         <is>
           <t>상해중환자실</t>
         </is>
       </c>
-      <c r="C62" s="117" t="n"/>
-      <c r="D62" s="117" t="n"/>
-      <c r="E62" s="117" t="n"/>
-      <c r="F62" s="117" t="n"/>
-      <c r="G62" s="117" t="n"/>
-      <c r="H62" s="117" t="n"/>
-      <c r="I62" s="117" t="n"/>
-      <c r="J62" s="118">
+      <c r="C63" s="117" t="n"/>
+      <c r="D63" s="117" t="n"/>
+      <c r="E63" s="117" t="n"/>
+      <c r="F63" s="117" t="n"/>
+      <c r="G63" s="117" t="n"/>
+      <c r="H63" s="117" t="n"/>
+      <c r="I63" s="117" t="n"/>
+      <c r="J63" s="118">
         <f>SUM(C55:I55)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="17.25" customHeight="1" s="82">
-      <c r="A63" s="148" t="inlineStr">
+    <row r="64" ht="16.5" customHeight="1" s="82">
+      <c r="A64" s="148" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B63" s="95" t="inlineStr">
+      <c r="B64" s="95" t="inlineStr">
         <is>
           <t>상해수술비</t>
         </is>
       </c>
-      <c r="C63" s="119" t="n"/>
-      <c r="D63" s="119" t="n"/>
-      <c r="E63" s="119" t="n"/>
-      <c r="F63" s="119" t="n"/>
-      <c r="G63" s="119" t="n"/>
-      <c r="H63" s="119" t="n"/>
-      <c r="I63" s="119" t="n"/>
-      <c r="J63" s="120">
+      <c r="C64" s="119" t="n"/>
+      <c r="D64" s="119" t="n"/>
+      <c r="E64" s="119" t="n"/>
+      <c r="F64" s="119" t="n"/>
+      <c r="G64" s="119" t="n"/>
+      <c r="H64" s="119" t="n"/>
+      <c r="I64" s="119" t="n"/>
+      <c r="J64" s="120">
         <f>SUM(C56:I56)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="16.5" customHeight="1" s="82">
-      <c r="A64" s="149" t="n"/>
-      <c r="B64" s="65" t="inlineStr">
-        <is>
-          <t>중대한상해수술비</t>
-        </is>
-      </c>
-      <c r="C64" s="136" t="n"/>
-      <c r="D64" s="136" t="n"/>
-      <c r="E64" s="136" t="n"/>
-      <c r="F64" s="136" t="n"/>
-      <c r="G64" s="136" t="n"/>
-      <c r="H64" s="136" t="n"/>
-      <c r="I64" s="136" t="n"/>
-      <c r="J64" s="122">
-        <f>SUM(C57:I57)</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="16.5" customHeight="1" s="82">
       <c r="A65" s="149" t="n"/>
-      <c r="B65" s="60" t="inlineStr">
-        <is>
-          <t>상해 종수술비(1-5종)</t>
+      <c r="B65" s="65" t="inlineStr">
+        <is>
+          <t>중대한상해수술비</t>
         </is>
       </c>
       <c r="C65" s="136" t="n"/>
       <c r="D65" s="136" t="n"/>
       <c r="E65" s="136" t="n"/>
-      <c r="F65" s="137" t="n"/>
+      <c r="F65" s="136" t="n"/>
       <c r="G65" s="136" t="n"/>
       <c r="H65" s="136" t="n"/>
       <c r="I65" s="136" t="n"/>
-      <c r="J65" s="122" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="J65" s="122">
+        <f>SUM(C57:I57)</f>
+        <v/>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" s="82">
       <c r="A66" s="149" t="n"/>
       <c r="B66" s="60" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-8종)</t>
+          <t>상해 종수술비(1-5종)</t>
         </is>
       </c>
       <c r="C66" s="136" t="n"/>
@@ -2703,32 +2699,33 @@
       <c r="G66" s="136" t="n"/>
       <c r="H66" s="136" t="n"/>
       <c r="I66" s="136" t="n"/>
-      <c r="J66" s="122" t="n"/>
+      <c r="J66" s="122" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" s="82">
       <c r="A67" s="149" t="n"/>
       <c r="B67" s="60" t="inlineStr">
         <is>
-          <t>창상봉합술</t>
-        </is>
-      </c>
-      <c r="C67" s="121" t="n"/>
-      <c r="D67" s="121" t="n"/>
-      <c r="E67" s="121" t="n"/>
-      <c r="F67" s="121" t="n"/>
-      <c r="G67" s="121" t="n"/>
-      <c r="H67" s="121" t="n"/>
-      <c r="I67" s="121" t="n"/>
-      <c r="J67" s="122">
-        <f>SUM(C59:I59)</f>
-        <v/>
-      </c>
+          <t>상해 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C67" s="136" t="n"/>
+      <c r="D67" s="136" t="n"/>
+      <c r="E67" s="136" t="n"/>
+      <c r="F67" s="137" t="n"/>
+      <c r="G67" s="136" t="n"/>
+      <c r="H67" s="136" t="n"/>
+      <c r="I67" s="136" t="n"/>
+      <c r="J67" s="122" t="n"/>
     </row>
     <row r="68" ht="17.25" customHeight="1" s="82">
       <c r="A68" s="149" t="n"/>
       <c r="B68" s="60" t="inlineStr">
         <is>
-          <t>골절수술비</t>
+          <t>창상봉합술</t>
         </is>
       </c>
       <c r="C68" s="121" t="n"/>
@@ -2739,15 +2736,15 @@
       <c r="H68" s="121" t="n"/>
       <c r="I68" s="121" t="n"/>
       <c r="J68" s="122">
-        <f>SUM(C60:I60)</f>
+        <f>SUM(C59:I59)</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="82">
       <c r="A69" s="149" t="n"/>
-      <c r="B69" s="69" t="inlineStr">
-        <is>
-          <t>5대골절수술비</t>
+      <c r="B69" s="60" t="inlineStr">
+        <is>
+          <t>골절수술비</t>
         </is>
       </c>
       <c r="C69" s="121" t="n"/>
@@ -2758,73 +2755,72 @@
       <c r="H69" s="121" t="n"/>
       <c r="I69" s="121" t="n"/>
       <c r="J69" s="122">
-        <f>SUM(C61:I61)</f>
+        <f>SUM(C60:I60)</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1" s="82">
       <c r="A70" s="149" t="n"/>
-      <c r="B70" s="57" t="inlineStr">
-        <is>
-          <t>화상수술비</t>
-        </is>
-      </c>
-      <c r="C70" s="117" t="n"/>
-      <c r="D70" s="117" t="n"/>
-      <c r="E70" s="117" t="n"/>
-      <c r="F70" s="117" t="n"/>
-      <c r="G70" s="117" t="n"/>
-      <c r="H70" s="117" t="n"/>
-      <c r="I70" s="117" t="n"/>
-      <c r="J70" s="118">
-        <f>SUM(C62:I62)</f>
+      <c r="B70" s="69" t="inlineStr">
+        <is>
+          <t>5대골절수술비</t>
+        </is>
+      </c>
+      <c r="C70" s="121" t="n"/>
+      <c r="D70" s="121" t="n"/>
+      <c r="E70" s="121" t="n"/>
+      <c r="F70" s="121" t="n"/>
+      <c r="G70" s="121" t="n"/>
+      <c r="H70" s="121" t="n"/>
+      <c r="I70" s="121" t="n"/>
+      <c r="J70" s="122">
+        <f>SUM(C61:I61)</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="82">
       <c r="A71" s="149" t="n"/>
-      <c r="B71" s="65" t="inlineStr">
-        <is>
-          <t>질병수술비</t>
-        </is>
-      </c>
-      <c r="C71" s="136" t="n"/>
-      <c r="D71" s="136" t="n"/>
-      <c r="E71" s="136" t="n"/>
-      <c r="F71" s="136" t="n"/>
-      <c r="G71" s="136" t="n"/>
-      <c r="H71" s="136" t="n"/>
-      <c r="I71" s="138" t="n"/>
-      <c r="J71" s="116">
-        <f>SUM(C63:I63)</f>
+      <c r="B71" s="57" t="inlineStr">
+        <is>
+          <t>화상수술비</t>
+        </is>
+      </c>
+      <c r="C71" s="117" t="n"/>
+      <c r="D71" s="117" t="n"/>
+      <c r="E71" s="117" t="n"/>
+      <c r="F71" s="117" t="n"/>
+      <c r="G71" s="117" t="n"/>
+      <c r="H71" s="117" t="n"/>
+      <c r="I71" s="117" t="n"/>
+      <c r="J71" s="118">
+        <f>SUM(C62:I62)</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" s="82">
       <c r="A72" s="149" t="n"/>
-      <c r="B72" s="60" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-5종)</t>
-        </is>
-      </c>
-      <c r="C72" s="121" t="n"/>
-      <c r="D72" s="121" t="n"/>
-      <c r="E72" s="121" t="n"/>
-      <c r="F72" s="139" t="n"/>
-      <c r="G72" s="121" t="n"/>
-      <c r="H72" s="121" t="n"/>
-      <c r="I72" s="121" t="n"/>
-      <c r="J72" s="122" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="B72" s="65" t="inlineStr">
+        <is>
+          <t>질병수술비</t>
+        </is>
+      </c>
+      <c r="C72" s="136" t="n"/>
+      <c r="D72" s="136" t="n"/>
+      <c r="E72" s="136" t="n"/>
+      <c r="F72" s="136" t="n"/>
+      <c r="G72" s="136" t="n"/>
+      <c r="H72" s="136" t="n"/>
+      <c r="I72" s="138" t="n"/>
+      <c r="J72" s="116">
+        <f>SUM(C63:I63)</f>
+        <v/>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="82">
       <c r="A73" s="149" t="n"/>
       <c r="B73" s="60" t="inlineStr">
         <is>
-          <t>질병 종수술비(1-8종)</t>
+          <t>질병 종수술비(1-5종)</t>
         </is>
       </c>
       <c r="C73" s="121" t="n"/>
@@ -2834,32 +2830,33 @@
       <c r="G73" s="121" t="n"/>
       <c r="H73" s="121" t="n"/>
       <c r="I73" s="121" t="n"/>
-      <c r="J73" s="122" t="n"/>
+      <c r="J73" s="122" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="82">
       <c r="A74" s="149" t="n"/>
-      <c r="B74" s="72" t="inlineStr">
-        <is>
-          <t>뇌혈관수술비</t>
-        </is>
-      </c>
-      <c r="C74" s="140" t="n"/>
-      <c r="D74" s="140" t="n"/>
-      <c r="E74" s="140" t="n"/>
-      <c r="F74" s="140" t="n"/>
-      <c r="G74" s="140" t="n"/>
-      <c r="H74" s="140" t="n"/>
-      <c r="I74" s="140" t="n"/>
-      <c r="J74" s="122">
-        <f>SUM(C65:I65)</f>
-        <v/>
-      </c>
+      <c r="B74" s="60" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C74" s="121" t="n"/>
+      <c r="D74" s="121" t="n"/>
+      <c r="E74" s="121" t="n"/>
+      <c r="F74" s="139" t="n"/>
+      <c r="G74" s="121" t="n"/>
+      <c r="H74" s="121" t="n"/>
+      <c r="I74" s="121" t="n"/>
+      <c r="J74" s="122" t="n"/>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="82">
       <c r="A75" s="149" t="n"/>
       <c r="B75" s="72" t="inlineStr">
         <is>
-          <t>허혈성수술비</t>
+          <t>뇌혈관수술비</t>
         </is>
       </c>
       <c r="C75" s="140" t="n"/>
@@ -2870,7 +2867,7 @@
       <c r="H75" s="140" t="n"/>
       <c r="I75" s="140" t="n"/>
       <c r="J75" s="122">
-        <f>SUM(C66:I66)</f>
+        <f>SUM(C65:I65)</f>
         <v/>
       </c>
     </row>
@@ -2878,7 +2875,7 @@
       <c r="A76" s="149" t="n"/>
       <c r="B76" s="72" t="inlineStr">
         <is>
-          <t>심장수술비</t>
+          <t>허혈성수술비</t>
         </is>
       </c>
       <c r="C76" s="140" t="n"/>
@@ -2889,15 +2886,15 @@
       <c r="H76" s="140" t="n"/>
       <c r="I76" s="140" t="n"/>
       <c r="J76" s="122">
-        <f>SUM(C67:I67)</f>
+        <f>SUM(C66:I66)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="82">
       <c r="A77" s="149" t="n"/>
-      <c r="B77" s="61" t="inlineStr">
-        <is>
-          <t>120대수술비</t>
+      <c r="B77" s="72" t="inlineStr">
+        <is>
+          <t>심장수술비</t>
         </is>
       </c>
       <c r="C77" s="140" t="n"/>
@@ -2907,88 +2904,88 @@
       <c r="G77" s="140" t="n"/>
       <c r="H77" s="140" t="n"/>
       <c r="I77" s="140" t="n"/>
-      <c r="J77" s="141">
-        <f>SUM(C68:I68)</f>
+      <c r="J77" s="122">
+        <f>SUM(C67:I67)</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16.5" customHeight="1" s="82">
       <c r="A78" s="149" t="n"/>
-      <c r="B78" s="73" t="inlineStr">
-        <is>
-          <t>5대기관 수술비 관혈</t>
-        </is>
-      </c>
-      <c r="C78" s="123" t="n"/>
-      <c r="D78" s="123" t="n"/>
-      <c r="E78" s="123" t="n"/>
-      <c r="F78" s="123" t="n"/>
-      <c r="G78" s="123" t="n"/>
-      <c r="H78" s="123" t="n"/>
-      <c r="I78" s="123" t="n"/>
-      <c r="J78" s="120">
-        <f>SUM(C69:I69)</f>
+      <c r="B78" s="61" t="inlineStr">
+        <is>
+          <t>120대수술비</t>
+        </is>
+      </c>
+      <c r="C78" s="140" t="n"/>
+      <c r="D78" s="140" t="n"/>
+      <c r="E78" s="140" t="n"/>
+      <c r="F78" s="140" t="n"/>
+      <c r="G78" s="140" t="n"/>
+      <c r="H78" s="140" t="n"/>
+      <c r="I78" s="140" t="n"/>
+      <c r="J78" s="141">
+        <f>SUM(C68:I68)</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="17.25" customHeight="1" s="82">
       <c r="A79" s="149" t="n"/>
-      <c r="B79" s="74" t="inlineStr">
+      <c r="B79" s="73" t="inlineStr">
+        <is>
+          <t>5대기관 수술비 관혈</t>
+        </is>
+      </c>
+      <c r="C79" s="123" t="n"/>
+      <c r="D79" s="123" t="n"/>
+      <c r="E79" s="123" t="n"/>
+      <c r="F79" s="123" t="n"/>
+      <c r="G79" s="123" t="n"/>
+      <c r="H79" s="123" t="n"/>
+      <c r="I79" s="123" t="n"/>
+      <c r="J79" s="120">
+        <f>SUM(C69:I69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="17.25" customHeight="1" s="82">
+      <c r="A80" s="149" t="n"/>
+      <c r="B80" s="74" t="inlineStr">
         <is>
           <t>5대기관 수술비 비관혈</t>
         </is>
       </c>
-      <c r="C79" s="117" t="n"/>
-      <c r="D79" s="117" t="n"/>
-      <c r="E79" s="117" t="n"/>
-      <c r="F79" s="117" t="n"/>
-      <c r="G79" s="117" t="n"/>
-      <c r="H79" s="117" t="n"/>
-      <c r="I79" s="117" t="n"/>
-      <c r="J79" s="118">
+      <c r="C80" s="117" t="n"/>
+      <c r="D80" s="117" t="n"/>
+      <c r="E80" s="117" t="n"/>
+      <c r="F80" s="117" t="n"/>
+      <c r="G80" s="117" t="n"/>
+      <c r="H80" s="117" t="n"/>
+      <c r="I80" s="117" t="n"/>
+      <c r="J80" s="118">
         <f>SUM(C70:I70)</f>
         <v/>
       </c>
     </row>
-    <row r="80" ht="17.25" customHeight="1" s="82">
-      <c r="A80" s="150" t="inlineStr">
+    <row r="81" ht="17.25" customHeight="1" s="82">
+      <c r="A81" s="150" t="inlineStr">
         <is>
           <t>운전</t>
         </is>
       </c>
-      <c r="B80" s="28" t="inlineStr">
+      <c r="B81" s="28" t="inlineStr">
         <is>
           <t>대인</t>
         </is>
       </c>
-      <c r="C80" s="102" t="n"/>
-      <c r="D80" s="102" t="n"/>
-      <c r="E80" s="102" t="n"/>
-      <c r="F80" s="102" t="n"/>
-      <c r="G80" s="102" t="n"/>
-      <c r="H80" s="102" t="n"/>
-      <c r="I80" s="102" t="n"/>
-      <c r="J80" s="120">
+      <c r="C81" s="102" t="n"/>
+      <c r="D81" s="102" t="n"/>
+      <c r="E81" s="102" t="n"/>
+      <c r="F81" s="102" t="n"/>
+      <c r="G81" s="102" t="n"/>
+      <c r="H81" s="102" t="n"/>
+      <c r="I81" s="102" t="n"/>
+      <c r="J81" s="120">
         <f>SUM(C71:I71)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="17.25" customHeight="1" s="82">
-      <c r="A81" s="149" t="n"/>
-      <c r="B81" s="31" t="inlineStr">
-        <is>
-          <t>대물</t>
-        </is>
-      </c>
-      <c r="C81" s="130" t="n"/>
-      <c r="D81" s="130" t="n"/>
-      <c r="E81" s="130" t="n"/>
-      <c r="F81" s="130" t="n"/>
-      <c r="G81" s="130" t="n"/>
-      <c r="H81" s="130" t="n"/>
-      <c r="I81" s="130" t="n"/>
-      <c r="J81" s="122">
-        <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
@@ -2996,7 +2993,7 @@
       <c r="A82" s="149" t="n"/>
       <c r="B82" s="31" t="inlineStr">
         <is>
-          <t>합의금</t>
+          <t>대물</t>
         </is>
       </c>
       <c r="C82" s="130" t="n"/>
@@ -3007,15 +3004,15 @@
       <c r="H82" s="130" t="n"/>
       <c r="I82" s="130" t="n"/>
       <c r="J82" s="122">
-        <f>SUM(C73:I73)</f>
+        <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="17.25" customHeight="1" s="82">
       <c r="A83" s="149" t="n"/>
-      <c r="B83" s="66" t="inlineStr">
-        <is>
-          <t>6주미만</t>
+      <c r="B83" s="31" t="inlineStr">
+        <is>
+          <t>합의금</t>
         </is>
       </c>
       <c r="C83" s="130" t="n"/>
@@ -3026,15 +3023,15 @@
       <c r="H83" s="130" t="n"/>
       <c r="I83" s="130" t="n"/>
       <c r="J83" s="122">
-        <f>SUM(C74:I74)</f>
+        <f>SUM(C73:I73)</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="82">
       <c r="A84" s="149" t="n"/>
-      <c r="B84" s="31" t="inlineStr">
-        <is>
-          <t>변호사</t>
+      <c r="B84" s="66" t="inlineStr">
+        <is>
+          <t>6주미만</t>
         </is>
       </c>
       <c r="C84" s="130" t="n"/>
@@ -3045,275 +3042,275 @@
       <c r="H84" s="130" t="n"/>
       <c r="I84" s="130" t="n"/>
       <c r="J84" s="122">
+        <f>SUM(C74:I74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="17.25" customHeight="1" s="82">
+      <c r="A85" s="149" t="n"/>
+      <c r="B85" s="31" t="inlineStr">
+        <is>
+          <t>변호사</t>
+        </is>
+      </c>
+      <c r="C85" s="130" t="n"/>
+      <c r="D85" s="130" t="n"/>
+      <c r="E85" s="130" t="n"/>
+      <c r="F85" s="130" t="n"/>
+      <c r="G85" s="130" t="n"/>
+      <c r="H85" s="130" t="n"/>
+      <c r="I85" s="130" t="n"/>
+      <c r="J85" s="122">
         <f>SUM(C75:I75)</f>
         <v/>
       </c>
     </row>
-    <row r="85" ht="17.25" customHeight="1" s="82">
-      <c r="A85" s="151" t="n"/>
-      <c r="B85" s="25" t="inlineStr">
+    <row r="86" ht="16.5" customHeight="1" s="82">
+      <c r="A86" s="151" t="n"/>
+      <c r="B86" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C85" s="142" t="n"/>
-      <c r="D85" s="142" t="n"/>
-      <c r="E85" s="142" t="n"/>
-      <c r="F85" s="142" t="n"/>
-      <c r="G85" s="142" t="n"/>
-      <c r="H85" s="142" t="n"/>
-      <c r="I85" s="142" t="n"/>
-      <c r="J85" s="118">
+      <c r="C86" s="142" t="n"/>
+      <c r="D86" s="142" t="n"/>
+      <c r="E86" s="142" t="n"/>
+      <c r="F86" s="142" t="n"/>
+      <c r="G86" s="142" t="n"/>
+      <c r="H86" s="142" t="n"/>
+      <c r="I86" s="142" t="n"/>
+      <c r="J86" s="118">
         <f>SUM(C76:I76)</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="16.5" customHeight="1" s="82">
-      <c r="A86" s="150" t="inlineStr">
+    <row r="87" ht="16.5" customHeight="1" s="82">
+      <c r="A87" s="150" t="inlineStr">
         <is>
           <t>골절</t>
         </is>
       </c>
-      <c r="B86" s="65" t="inlineStr">
+      <c r="B87" s="65" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C86" s="136" t="n"/>
-      <c r="D86" s="136" t="n"/>
-      <c r="E86" s="136" t="n"/>
-      <c r="F86" s="136" t="n"/>
-      <c r="G86" s="136" t="n"/>
-      <c r="H86" s="136" t="n"/>
-      <c r="I86" s="136" t="n"/>
-      <c r="J86" s="116">
+      <c r="C87" s="136" t="n"/>
+      <c r="D87" s="136" t="n"/>
+      <c r="E87" s="136" t="n"/>
+      <c r="F87" s="136" t="n"/>
+      <c r="G87" s="136" t="n"/>
+      <c r="H87" s="136" t="n"/>
+      <c r="I87" s="136" t="n"/>
+      <c r="J87" s="116">
         <f>SUM(C77:I77)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="16.5" customHeight="1" s="82">
-      <c r="A87" s="149" t="n"/>
-      <c r="B87" s="60" t="inlineStr">
+    <row r="88" ht="17.25" customHeight="1" s="82">
+      <c r="A88" s="149" t="n"/>
+      <c r="B88" s="60" t="inlineStr">
         <is>
           <t>골절(치아파절제외)</t>
         </is>
       </c>
-      <c r="C87" s="121" t="n"/>
-      <c r="D87" s="121" t="n"/>
-      <c r="E87" s="121" t="n"/>
-      <c r="F87" s="121" t="n"/>
-      <c r="G87" s="121" t="n"/>
-      <c r="H87" s="121" t="n"/>
-      <c r="I87" s="121" t="n"/>
-      <c r="J87" s="122">
+      <c r="C88" s="121" t="n"/>
+      <c r="D88" s="121" t="n"/>
+      <c r="E88" s="121" t="n"/>
+      <c r="F88" s="121" t="n"/>
+      <c r="G88" s="121" t="n"/>
+      <c r="H88" s="121" t="n"/>
+      <c r="I88" s="121" t="n"/>
+      <c r="J88" s="122">
         <f>SUM(C78:I78)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="17.25" customHeight="1" s="82">
-      <c r="A88" s="151" t="n"/>
-      <c r="B88" s="74" t="inlineStr">
+    <row r="89" ht="17.25" customHeight="1" s="82">
+      <c r="A89" s="151" t="n"/>
+      <c r="B89" s="74" t="inlineStr">
         <is>
           <t>5대골절진단비</t>
         </is>
       </c>
-      <c r="C88" s="117" t="n"/>
-      <c r="D88" s="117" t="n"/>
-      <c r="E88" s="117" t="n"/>
-      <c r="F88" s="117" t="n"/>
-      <c r="G88" s="117" t="n"/>
-      <c r="H88" s="117" t="n"/>
-      <c r="I88" s="117" t="n"/>
-      <c r="J88" s="118">
+      <c r="C89" s="117" t="n"/>
+      <c r="D89" s="117" t="n"/>
+      <c r="E89" s="117" t="n"/>
+      <c r="F89" s="117" t="n"/>
+      <c r="G89" s="117" t="n"/>
+      <c r="H89" s="117" t="n"/>
+      <c r="I89" s="117" t="n"/>
+      <c r="J89" s="118">
         <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="17.25" customHeight="1" s="82">
-      <c r="A89" s="99" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="99" t="inlineStr">
         <is>
           <t>응급실</t>
         </is>
       </c>
-      <c r="B89" s="64" t="inlineStr">
+      <c r="B90" s="64" t="inlineStr">
         <is>
           <t>응급실(응급)</t>
         </is>
       </c>
-      <c r="C89" s="113" t="n"/>
-      <c r="D89" s="113" t="n"/>
-      <c r="E89" s="113" t="n"/>
-      <c r="F89" s="113" t="n"/>
-      <c r="G89" s="113" t="n"/>
-      <c r="H89" s="113" t="n"/>
-      <c r="I89" s="113" t="n"/>
-      <c r="J89" s="114">
+      <c r="C90" s="113" t="n"/>
+      <c r="D90" s="113" t="n"/>
+      <c r="E90" s="113" t="n"/>
+      <c r="F90" s="113" t="n"/>
+      <c r="G90" s="113" t="n"/>
+      <c r="H90" s="113" t="n"/>
+      <c r="I90" s="113" t="n"/>
+      <c r="J90" s="114">
         <f>SUM(C80:I80)</f>
         <v/>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="87" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="87" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="B90" s="34" t="inlineStr">
+      <c r="B91" s="34" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="C90" s="123" t="n"/>
-      <c r="D90" s="123" t="n"/>
-      <c r="E90" s="123" t="n"/>
-      <c r="F90" s="123" t="n"/>
-      <c r="G90" s="123" t="n"/>
-      <c r="H90" s="123" t="n"/>
-      <c r="I90" s="123" t="n"/>
-      <c r="J90" s="124" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="150" t="inlineStr">
+      <c r="C91" s="123" t="n"/>
+      <c r="D91" s="123" t="n"/>
+      <c r="E91" s="123" t="n"/>
+      <c r="F91" s="123" t="n"/>
+      <c r="G91" s="123" t="n"/>
+      <c r="H91" s="123" t="n"/>
+      <c r="I91" s="123" t="n"/>
+      <c r="J91" s="124" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="150" t="inlineStr">
         <is>
           <t>화상</t>
         </is>
       </c>
-      <c r="B91" s="28" t="inlineStr">
+      <c r="B92" s="28" t="inlineStr">
         <is>
           <t>화상진단비</t>
         </is>
       </c>
-      <c r="C91" s="119" t="n"/>
-      <c r="D91" s="119" t="n"/>
-      <c r="E91" s="119" t="n"/>
-      <c r="F91" s="119" t="n"/>
-      <c r="G91" s="119" t="n"/>
-      <c r="H91" s="119" t="n"/>
-      <c r="I91" s="119" t="n"/>
-      <c r="J91" s="120">
+      <c r="C92" s="119" t="n"/>
+      <c r="D92" s="119" t="n"/>
+      <c r="E92" s="119" t="n"/>
+      <c r="F92" s="119" t="n"/>
+      <c r="G92" s="119" t="n"/>
+      <c r="H92" s="119" t="n"/>
+      <c r="I92" s="119" t="n"/>
+      <c r="J92" s="120">
         <f>SUM(C82:I82)</f>
         <v/>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="151" t="n"/>
-      <c r="B92" s="25" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="151" t="n"/>
+      <c r="B93" s="25" t="inlineStr">
         <is>
           <t>중증화상진단비</t>
         </is>
       </c>
-      <c r="C92" s="117" t="n"/>
-      <c r="D92" s="117" t="n"/>
-      <c r="E92" s="117" t="n"/>
-      <c r="F92" s="117" t="n"/>
-      <c r="G92" s="117" t="n"/>
-      <c r="H92" s="117" t="n"/>
-      <c r="I92" s="117" t="n"/>
-      <c r="J92" s="118">
+      <c r="C93" s="117" t="n"/>
+      <c r="D93" s="117" t="n"/>
+      <c r="E93" s="117" t="n"/>
+      <c r="F93" s="117" t="n"/>
+      <c r="G93" s="117" t="n"/>
+      <c r="H93" s="117" t="n"/>
+      <c r="I93" s="117" t="n"/>
+      <c r="J93" s="118">
         <f>SUM(C83:I83)</f>
         <v/>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="150" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="150" t="inlineStr">
         <is>
           <t>깁스</t>
         </is>
       </c>
-      <c r="B93" s="95" t="inlineStr">
+      <c r="B94" s="95" t="inlineStr">
         <is>
           <t>반깁스</t>
         </is>
       </c>
-      <c r="C93" s="119" t="n"/>
-      <c r="D93" s="119" t="n"/>
-      <c r="E93" s="119" t="n"/>
-      <c r="F93" s="119" t="n"/>
-      <c r="G93" s="119" t="n"/>
-      <c r="H93" s="119" t="n"/>
-      <c r="I93" s="119" t="n"/>
-      <c r="J93" s="120">
+      <c r="C94" s="119" t="n"/>
+      <c r="D94" s="119" t="n"/>
+      <c r="E94" s="119" t="n"/>
+      <c r="F94" s="119" t="n"/>
+      <c r="G94" s="119" t="n"/>
+      <c r="H94" s="119" t="n"/>
+      <c r="I94" s="119" t="n"/>
+      <c r="J94" s="120">
         <f>SUM(C84:I84)</f>
         <v/>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="151" t="n"/>
-      <c r="B94" s="57" t="inlineStr">
+    <row r="95" s="82">
+      <c r="A95" s="151" t="n"/>
+      <c r="B95" s="57" t="inlineStr">
         <is>
           <t>깁스진단비</t>
         </is>
       </c>
-      <c r="C94" s="117" t="n"/>
-      <c r="D94" s="117" t="n"/>
-      <c r="E94" s="117" t="n"/>
-      <c r="F94" s="117" t="n"/>
-      <c r="G94" s="117" t="n"/>
-      <c r="H94" s="117" t="n"/>
-      <c r="I94" s="117" t="n"/>
-      <c r="J94" s="118">
+      <c r="C95" s="117" t="n"/>
+      <c r="D95" s="117" t="n"/>
+      <c r="E95" s="117" t="n"/>
+      <c r="F95" s="117" t="n"/>
+      <c r="G95" s="117" t="n"/>
+      <c r="H95" s="117" t="n"/>
+      <c r="I95" s="117" t="n"/>
+      <c r="J95" s="118">
         <f>SUM(C85:I85)</f>
         <v/>
       </c>
     </row>
-    <row r="95" s="82">
-      <c r="A95" s="150" t="inlineStr">
+    <row r="96" s="82">
+      <c r="A96" s="150" t="inlineStr">
         <is>
           <t>실손</t>
         </is>
       </c>
-      <c r="B95" s="95" t="inlineStr">
+      <c r="B96" s="95" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="C95" s="143" t="n"/>
-      <c r="D95" s="143" t="n"/>
-      <c r="E95" s="143" t="n"/>
-      <c r="F95" s="143" t="n"/>
-      <c r="G95" s="143" t="n"/>
-      <c r="H95" s="143" t="n"/>
-      <c r="I95" s="143" t="n"/>
-      <c r="J95" s="120">
+      <c r="C96" s="143" t="n"/>
+      <c r="D96" s="143" t="n"/>
+      <c r="E96" s="143" t="n"/>
+      <c r="F96" s="143" t="n"/>
+      <c r="G96" s="143" t="n"/>
+      <c r="H96" s="143" t="n"/>
+      <c r="I96" s="143" t="n"/>
+      <c r="J96" s="120">
         <f>SUM(C86:I86)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" s="82">
-      <c r="A96" s="149" t="n"/>
-      <c r="B96" s="60" t="inlineStr">
-        <is>
-          <t>통원</t>
-        </is>
-      </c>
-      <c r="C96" s="144" t="n"/>
-      <c r="D96" s="144" t="n"/>
-      <c r="E96" s="144" t="n"/>
-      <c r="F96" s="144" t="n"/>
-      <c r="G96" s="144" t="n"/>
-      <c r="H96" s="144" t="n"/>
-      <c r="I96" s="144" t="n"/>
-      <c r="J96" s="122">
-        <f>SUM(C87:I87)</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="149" t="n"/>
-      <c r="B97" s="22" t="inlineStr">
-        <is>
-          <t>약값</t>
-        </is>
-      </c>
-      <c r="C97" s="115" t="n"/>
-      <c r="D97" s="115" t="n"/>
-      <c r="E97" s="115" t="n"/>
-      <c r="F97" s="115" t="n"/>
-      <c r="G97" s="115" t="n"/>
-      <c r="H97" s="115" t="n"/>
-      <c r="I97" s="145" t="n"/>
+      <c r="B97" s="60" t="inlineStr">
+        <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="C97" s="144" t="n"/>
+      <c r="D97" s="144" t="n"/>
+      <c r="E97" s="144" t="n"/>
+      <c r="F97" s="144" t="n"/>
+      <c r="G97" s="144" t="n"/>
+      <c r="H97" s="144" t="n"/>
+      <c r="I97" s="144" t="n"/>
       <c r="J97" s="122">
-        <f>SUM(C88:I88)</f>
+        <f>SUM(C87:I87)</f>
         <v/>
       </c>
     </row>
@@ -3321,7 +3318,7 @@
       <c r="A98" s="149" t="n"/>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>MRI/도수치료/비급여주사</t>
+          <t>약값</t>
         </is>
       </c>
       <c r="C98" s="115" t="n"/>
@@ -3331,13 +3328,16 @@
       <c r="G98" s="115" t="n"/>
       <c r="H98" s="115" t="n"/>
       <c r="I98" s="145" t="n"/>
-      <c r="J98" s="122" t="n"/>
+      <c r="J98" s="122">
+        <f>SUM(C88:I88)</f>
+        <v/>
+      </c>
     </row>
     <row r="99" s="82">
-      <c r="A99" s="151" t="n"/>
+      <c r="A99" s="149" t="n"/>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>상해의료비</t>
+          <t>MRI/도수치료/비급여주사</t>
         </is>
       </c>
       <c r="C99" s="115" t="n"/>
@@ -3350,46 +3350,62 @@
       <c r="J99" s="122" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="87" t="inlineStr">
+      <c r="A100" s="151" t="n"/>
+      <c r="B100" s="22" t="inlineStr">
+        <is>
+          <t>상해의료비</t>
+        </is>
+      </c>
+      <c r="C100" s="115" t="n"/>
+      <c r="D100" s="115" t="n"/>
+      <c r="E100" s="115" t="n"/>
+      <c r="F100" s="115" t="n"/>
+      <c r="G100" s="115" t="n"/>
+      <c r="H100" s="115" t="n"/>
+      <c r="I100" s="145" t="n"/>
+      <c r="J100" s="122" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="87" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B100" s="79" t="inlineStr">
+      <c r="B101" s="79" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C100" s="146" t="n"/>
-      <c r="D100" s="146" t="n"/>
-      <c r="E100" s="146" t="n"/>
-      <c r="F100" s="146" t="n"/>
-      <c r="G100" s="146" t="n"/>
-      <c r="H100" s="146" t="n"/>
-      <c r="I100" s="146" t="n"/>
-      <c r="J100" s="147">
+      <c r="C101" s="146" t="n"/>
+      <c r="D101" s="146" t="n"/>
+      <c r="E101" s="146" t="n"/>
+      <c r="F101" s="146" t="n"/>
+      <c r="G101" s="146" t="n"/>
+      <c r="H101" s="146" t="n"/>
+      <c r="I101" s="146" t="n"/>
+      <c r="J101" s="147">
         <f>SUM(C89:I89)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A94:A95"/>
     <mergeCell ref="A30:A37"/>
-    <mergeCell ref="A63:A79"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A15:A29"/>
-    <mergeCell ref="A51:A62"/>
-    <mergeCell ref="A95:A99"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A96:A100"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="A81:A86"/>
+    <mergeCell ref="A87:A89"/>
     <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A38:A50"/>
+    <mergeCell ref="A51:A63"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A38:A50"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A80:A85"/>
+    <mergeCell ref="A64:A80"/>
     <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/master.xlsx
+++ b/master.xlsx
@@ -1458,7 +1458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="82" min="1" max="1"/>
@@ -2104,39 +2104,36 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" s="82">
       <c r="A34" s="88" t="n"/>
-      <c r="B34" s="53" t="inlineStr">
-        <is>
-          <t>외상성뇌출혈</t>
-        </is>
-      </c>
-      <c r="C34" s="134" t="n"/>
-      <c r="D34" s="134" t="n"/>
-      <c r="E34" s="134" t="n"/>
-      <c r="F34" s="134" t="n"/>
-      <c r="G34" s="134" t="n"/>
-      <c r="H34" s="134" t="n"/>
-      <c r="I34" s="134" t="n"/>
-      <c r="J34" s="116">
-        <f>SUM(C33:I33)</f>
-        <v/>
-      </c>
+      <c r="B34" s="52" t="inlineStr">
+        <is>
+          <t>중대한 뇌출혈</t>
+        </is>
+      </c>
+      <c r="C34" s="127" t="n"/>
+      <c r="D34" s="127" t="n"/>
+      <c r="E34" s="127" t="n"/>
+      <c r="F34" s="127" t="n"/>
+      <c r="G34" s="127" t="n"/>
+      <c r="H34" s="127" t="n"/>
+      <c r="I34" s="127" t="n"/>
+      <c r="J34" s="116" t="n"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="82">
       <c r="A35" s="88" t="n"/>
-      <c r="B35" s="55" t="inlineStr">
-        <is>
-          <t>산정특례뇌혈관</t>
-        </is>
-      </c>
-      <c r="C35" s="135" t="n"/>
-      <c r="D35" s="135" t="n"/>
-      <c r="E35" s="135" t="n"/>
-      <c r="F35" s="135" t="n"/>
-      <c r="G35" s="135" t="n"/>
-      <c r="H35" s="135" t="n"/>
-      <c r="I35" s="135" t="n"/>
-      <c r="J35" s="122">
-        <f>SUM(C34:I34)</f>
+      <c r="B35" s="53" t="inlineStr">
+        <is>
+          <t>외상성뇌출혈</t>
+        </is>
+      </c>
+      <c r="C35" s="134" t="n"/>
+      <c r="D35" s="134" t="n"/>
+      <c r="E35" s="134" t="n"/>
+      <c r="F35" s="134" t="n"/>
+      <c r="G35" s="134" t="n"/>
+      <c r="H35" s="134" t="n"/>
+      <c r="I35" s="134" t="n"/>
+      <c r="J35" s="116">
+        <f>SUM(C33:I33)</f>
         <v/>
       </c>
     </row>
@@ -2144,7 +2141,7 @@
       <c r="A36" s="88" t="n"/>
       <c r="B36" s="55" t="inlineStr">
         <is>
-          <t>2대 주요치료비</t>
+          <t>산정특례뇌혈관</t>
         </is>
       </c>
       <c r="C36" s="135" t="n"/>
@@ -2154,66 +2151,66 @@
       <c r="G36" s="135" t="n"/>
       <c r="H36" s="135" t="n"/>
       <c r="I36" s="135" t="n"/>
-      <c r="J36" s="122" t="n"/>
+      <c r="J36" s="122">
+        <f>SUM(C34:I34)</f>
+        <v/>
+      </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="82">
-      <c r="A37" s="89" t="n"/>
-      <c r="B37" s="57" t="inlineStr">
+      <c r="A37" s="88" t="n"/>
+      <c r="B37" s="55" t="inlineStr">
+        <is>
+          <t>2대 주요치료비</t>
+        </is>
+      </c>
+      <c r="C37" s="135" t="n"/>
+      <c r="D37" s="135" t="n"/>
+      <c r="E37" s="135" t="n"/>
+      <c r="F37" s="135" t="n"/>
+      <c r="G37" s="135" t="n"/>
+      <c r="H37" s="135" t="n"/>
+      <c r="I37" s="135" t="n"/>
+      <c r="J37" s="122" t="n"/>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" s="82">
+      <c r="A38" s="89" t="n"/>
+      <c r="B38" s="57" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C37" s="117" t="n"/>
-      <c r="D37" s="117" t="n"/>
-      <c r="E37" s="117" t="n"/>
-      <c r="F37" s="117" t="n"/>
-      <c r="G37" s="117" t="n"/>
-      <c r="H37" s="117" t="n"/>
-      <c r="I37" s="117" t="n"/>
-      <c r="J37" s="118">
+      <c r="C38" s="117" t="n"/>
+      <c r="D38" s="117" t="n"/>
+      <c r="E38" s="117" t="n"/>
+      <c r="F38" s="117" t="n"/>
+      <c r="G38" s="117" t="n"/>
+      <c r="H38" s="117" t="n"/>
+      <c r="I38" s="117" t="n"/>
+      <c r="J38" s="118">
         <f>SUM(C35:I35)</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="82">
-      <c r="A38" s="99" t="inlineStr">
+    <row r="39" ht="16.5" customHeight="1" s="82">
+      <c r="A39" s="99" t="inlineStr">
         <is>
           <t>심장</t>
         </is>
       </c>
-      <c r="B38" s="40" t="inlineStr">
+      <c r="B39" s="40" t="inlineStr">
         <is>
           <t>협심증</t>
         </is>
       </c>
-      <c r="C38" s="127" t="n"/>
-      <c r="D38" s="127" t="n"/>
-      <c r="E38" s="127" t="n"/>
-      <c r="F38" s="127" t="n"/>
-      <c r="G38" s="127" t="n"/>
-      <c r="H38" s="127" t="n"/>
-      <c r="I38" s="127" t="n"/>
-      <c r="J38" s="122">
+      <c r="C39" s="127" t="n"/>
+      <c r="D39" s="127" t="n"/>
+      <c r="E39" s="127" t="n"/>
+      <c r="F39" s="127" t="n"/>
+      <c r="G39" s="127" t="n"/>
+      <c r="H39" s="127" t="n"/>
+      <c r="I39" s="127" t="n"/>
+      <c r="J39" s="122">
         <f>SUM(C36:I36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" s="82">
-      <c r="A39" s="88" t="n"/>
-      <c r="B39" s="31" t="inlineStr">
-        <is>
-          <t>심부전</t>
-        </is>
-      </c>
-      <c r="C39" s="130" t="n"/>
-      <c r="D39" s="130" t="n"/>
-      <c r="E39" s="130" t="n"/>
-      <c r="F39" s="130" t="n"/>
-      <c r="G39" s="130" t="n"/>
-      <c r="H39" s="130" t="n"/>
-      <c r="I39" s="130" t="n"/>
-      <c r="J39" s="122">
-        <f>SUM(C37:I37)</f>
         <v/>
       </c>
     </row>
@@ -2221,7 +2218,7 @@
       <c r="A40" s="88" t="n"/>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>빈맥</t>
+          <t>심부전</t>
         </is>
       </c>
       <c r="C40" s="130" t="n"/>
@@ -2231,13 +2228,16 @@
       <c r="G40" s="130" t="n"/>
       <c r="H40" s="130" t="n"/>
       <c r="I40" s="130" t="n"/>
-      <c r="J40" s="122" t="n"/>
+      <c r="J40" s="122">
+        <f>SUM(C37:I37)</f>
+        <v/>
+      </c>
     </row>
     <row r="41" ht="17.25" customHeight="1" s="82">
       <c r="A41" s="88" t="n"/>
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>염증</t>
+          <t>빈맥</t>
         </is>
       </c>
       <c r="C41" s="130" t="n"/>
@@ -2247,27 +2247,24 @@
       <c r="G41" s="130" t="n"/>
       <c r="H41" s="130" t="n"/>
       <c r="I41" s="130" t="n"/>
-      <c r="J41" s="122">
-        <f>SUM(C38:I38)</f>
-        <v/>
-      </c>
+      <c r="J41" s="122" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1" s="82">
       <c r="A42" s="88" t="n"/>
-      <c r="B42" s="40" t="inlineStr">
-        <is>
-          <t>부정맥</t>
-        </is>
-      </c>
-      <c r="C42" s="136" t="n"/>
-      <c r="D42" s="136" t="n"/>
-      <c r="E42" s="136" t="n"/>
-      <c r="F42" s="136" t="n"/>
-      <c r="G42" s="136" t="n"/>
-      <c r="H42" s="136" t="n"/>
-      <c r="I42" s="136" t="n"/>
+      <c r="B42" s="31" t="inlineStr">
+        <is>
+          <t>염증</t>
+        </is>
+      </c>
+      <c r="C42" s="130" t="n"/>
+      <c r="D42" s="130" t="n"/>
+      <c r="E42" s="130" t="n"/>
+      <c r="F42" s="130" t="n"/>
+      <c r="G42" s="130" t="n"/>
+      <c r="H42" s="130" t="n"/>
+      <c r="I42" s="130" t="n"/>
       <c r="J42" s="122">
-        <f>SUM(C39:I39)</f>
+        <f>SUM(C38:I38)</f>
         <v/>
       </c>
     </row>
@@ -2275,42 +2272,42 @@
       <c r="A43" s="88" t="n"/>
       <c r="B43" s="40" t="inlineStr">
         <is>
-          <t>심근병증</t>
-        </is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="C43" s="136" t="n"/>
+      <c r="D43" s="136" t="n"/>
+      <c r="E43" s="136" t="n"/>
+      <c r="F43" s="136" t="n"/>
+      <c r="G43" s="136" t="n"/>
+      <c r="H43" s="136" t="n"/>
+      <c r="I43" s="136" t="n"/>
+      <c r="J43" s="122">
+        <f>SUM(C39:I39)</f>
+        <v/>
       </c>
     </row>
     <row r="44" ht="17.25" customHeight="1" s="82">
       <c r="A44" s="88" t="n"/>
       <c r="B44" s="40" t="inlineStr">
         <is>
-          <t>심장판막</t>
+          <t>심근병증</t>
         </is>
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1" s="82">
       <c r="A45" s="88" t="n"/>
-      <c r="B45" s="60" t="inlineStr">
-        <is>
-          <t>산정특례심장</t>
-        </is>
-      </c>
-      <c r="C45" s="121" t="n"/>
-      <c r="D45" s="121" t="n"/>
-      <c r="E45" s="121" t="n"/>
-      <c r="F45" s="121" t="n"/>
-      <c r="G45" s="121" t="n"/>
-      <c r="H45" s="121" t="n"/>
-      <c r="I45" s="121" t="n"/>
-      <c r="J45" s="122">
-        <f>SUM(C40:I40)</f>
-        <v/>
+      <c r="B45" s="40" t="inlineStr">
+        <is>
+          <t>심장판막</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" s="82">
       <c r="A46" s="88" t="n"/>
-      <c r="B46" s="69" t="inlineStr">
-        <is>
-          <t>2대 주요치료비</t>
+      <c r="B46" s="60" t="inlineStr">
+        <is>
+          <t>산정특례심장</t>
         </is>
       </c>
       <c r="C46" s="121" t="n"/>
@@ -2321,125 +2318,125 @@
       <c r="H46" s="121" t="n"/>
       <c r="I46" s="121" t="n"/>
       <c r="J46" s="122">
-        <f>SUM(C41:I41)</f>
+        <f>SUM(C40:I40)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="82">
       <c r="A47" s="88" t="n"/>
-      <c r="B47" s="86" t="inlineStr">
-        <is>
-          <t>허혈성 진단비</t>
-        </is>
-      </c>
-      <c r="C47" s="115" t="n"/>
-      <c r="D47" s="115" t="n"/>
-      <c r="E47" s="115" t="n"/>
-      <c r="F47" s="115" t="n"/>
-      <c r="G47" s="115" t="n"/>
-      <c r="H47" s="115" t="n"/>
-      <c r="I47" s="115" t="n"/>
+      <c r="B47" s="69" t="inlineStr">
+        <is>
+          <t>2대 주요치료비</t>
+        </is>
+      </c>
+      <c r="C47" s="121" t="n"/>
+      <c r="D47" s="121" t="n"/>
+      <c r="E47" s="121" t="n"/>
+      <c r="F47" s="121" t="n"/>
+      <c r="G47" s="121" t="n"/>
+      <c r="H47" s="121" t="n"/>
+      <c r="I47" s="121" t="n"/>
       <c r="J47" s="122">
-        <f>SUM(C42:I42)</f>
+        <f>SUM(C41:I41)</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" s="82">
       <c r="A48" s="88" t="n"/>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>급성심근경색</t>
-        </is>
-      </c>
-      <c r="C48" s="125" t="n"/>
-      <c r="D48" s="125" t="n"/>
-      <c r="E48" s="125" t="n"/>
-      <c r="F48" s="125" t="n"/>
-      <c r="G48" s="125" t="n"/>
-      <c r="H48" s="125" t="n"/>
-      <c r="I48" s="125" t="n"/>
-      <c r="J48" s="110">
+      <c r="B48" s="86" t="inlineStr">
+        <is>
+          <t>허혈성 진단비</t>
+        </is>
+      </c>
+      <c r="C48" s="115" t="n"/>
+      <c r="D48" s="115" t="n"/>
+      <c r="E48" s="115" t="n"/>
+      <c r="F48" s="115" t="n"/>
+      <c r="G48" s="115" t="n"/>
+      <c r="H48" s="115" t="n"/>
+      <c r="I48" s="115" t="n"/>
+      <c r="J48" s="122">
         <f>SUM(C42:I42)</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="82">
       <c r="A49" s="88" t="n"/>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>급성심근경색</t>
+        </is>
+      </c>
+      <c r="C49" s="125" t="n"/>
+      <c r="D49" s="125" t="n"/>
+      <c r="E49" s="125" t="n"/>
+      <c r="F49" s="125" t="n"/>
+      <c r="G49" s="125" t="n"/>
+      <c r="H49" s="125" t="n"/>
+      <c r="I49" s="125" t="n"/>
+      <c r="J49" s="110">
+        <f>SUM(C42:I42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="16.5" customHeight="1" s="82">
+      <c r="A50" s="88" t="n"/>
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>중대한 급성심근</t>
         </is>
       </c>
-      <c r="C49" s="111" t="n"/>
-      <c r="D49" s="111" t="n"/>
-      <c r="E49" s="111" t="n"/>
-      <c r="F49" s="111" t="n"/>
-      <c r="G49" s="111" t="n"/>
-      <c r="H49" s="111" t="n"/>
-      <c r="I49" s="111" t="n"/>
-      <c r="J49" s="133">
+      <c r="C50" s="111" t="n"/>
+      <c r="D50" s="111" t="n"/>
+      <c r="E50" s="111" t="n"/>
+      <c r="F50" s="111" t="n"/>
+      <c r="G50" s="111" t="n"/>
+      <c r="H50" s="111" t="n"/>
+      <c r="I50" s="111" t="n"/>
+      <c r="J50" s="133">
         <f>SUM(C44:I44)</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="82">
-      <c r="A50" s="89" t="n"/>
-      <c r="B50" s="64" t="inlineStr">
+    <row r="51" ht="16.5" customHeight="1" s="82">
+      <c r="A51" s="89" t="n"/>
+      <c r="B51" s="64" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C50" s="113" t="n"/>
-      <c r="D50" s="113" t="n"/>
-      <c r="E50" s="113" t="n"/>
-      <c r="F50" s="113" t="n"/>
-      <c r="G50" s="113" t="n"/>
-      <c r="H50" s="113" t="n"/>
-      <c r="I50" s="113" t="n"/>
-      <c r="J50" s="114">
+      <c r="C51" s="113" t="n"/>
+      <c r="D51" s="113" t="n"/>
+      <c r="E51" s="113" t="n"/>
+      <c r="F51" s="113" t="n"/>
+      <c r="G51" s="113" t="n"/>
+      <c r="H51" s="113" t="n"/>
+      <c r="I51" s="113" t="n"/>
+      <c r="J51" s="114">
         <f>SUM(C45:I45)</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="82">
-      <c r="A51" s="99" t="inlineStr">
+    <row r="52" ht="16.5" customHeight="1" s="82">
+      <c r="A52" s="99" t="inlineStr">
         <is>
           <t>일당</t>
         </is>
       </c>
-      <c r="B51" s="95" t="inlineStr">
+      <c r="B52" s="95" t="inlineStr">
         <is>
           <t>질병일당</t>
         </is>
       </c>
-      <c r="C51" s="119" t="n"/>
-      <c r="D51" s="119" t="n"/>
-      <c r="E51" s="119" t="n"/>
-      <c r="F51" s="119" t="n"/>
-      <c r="G51" s="119" t="n"/>
-      <c r="H51" s="119" t="n"/>
-      <c r="I51" s="119" t="n"/>
-      <c r="J51" s="120">
+      <c r="C52" s="119" t="n"/>
+      <c r="D52" s="119" t="n"/>
+      <c r="E52" s="119" t="n"/>
+      <c r="F52" s="119" t="n"/>
+      <c r="G52" s="119" t="n"/>
+      <c r="H52" s="119" t="n"/>
+      <c r="I52" s="119" t="n"/>
+      <c r="J52" s="120">
         <f>SUM(C46:I46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="16.5" customHeight="1" s="82">
-      <c r="A52" s="88" t="n"/>
-      <c r="B52" s="65" t="inlineStr">
-        <is>
-          <t>질병수술일당</t>
-        </is>
-      </c>
-      <c r="C52" s="136" t="n"/>
-      <c r="D52" s="136" t="n"/>
-      <c r="E52" s="136" t="n"/>
-      <c r="F52" s="136" t="n"/>
-      <c r="G52" s="136" t="n"/>
-      <c r="H52" s="136" t="n"/>
-      <c r="I52" s="136" t="n"/>
-      <c r="J52" s="122">
-        <f>SUM(C47:I47)</f>
         <v/>
       </c>
     </row>
@@ -2447,7 +2444,7 @@
       <c r="A53" s="88" t="n"/>
       <c r="B53" s="65" t="inlineStr">
         <is>
-          <t>질병종합병원일당</t>
+          <t>질병수술일당</t>
         </is>
       </c>
       <c r="C53" s="136" t="n"/>
@@ -2458,7 +2455,7 @@
       <c r="H53" s="136" t="n"/>
       <c r="I53" s="136" t="n"/>
       <c r="J53" s="122">
-        <f>SUM(C48:I48)</f>
+        <f>SUM(C47:I47)</f>
         <v/>
       </c>
     </row>
@@ -2466,7 +2463,7 @@
       <c r="A54" s="88" t="n"/>
       <c r="B54" s="65" t="inlineStr">
         <is>
-          <t>상급병원질병입원일당</t>
+          <t>질병종합병원일당</t>
         </is>
       </c>
       <c r="C54" s="136" t="n"/>
@@ -2476,32 +2473,32 @@
       <c r="G54" s="136" t="n"/>
       <c r="H54" s="136" t="n"/>
       <c r="I54" s="136" t="n"/>
-      <c r="J54" s="122" t="n"/>
+      <c r="J54" s="122">
+        <f>SUM(C48:I48)</f>
+        <v/>
+      </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="82">
       <c r="A55" s="88" t="n"/>
-      <c r="B55" s="60" t="inlineStr">
-        <is>
-          <t>상해일당</t>
-        </is>
-      </c>
-      <c r="C55" s="121" t="n"/>
-      <c r="D55" s="121" t="n"/>
-      <c r="E55" s="121" t="n"/>
-      <c r="F55" s="121" t="n"/>
-      <c r="G55" s="121" t="n"/>
-      <c r="H55" s="121" t="n"/>
-      <c r="I55" s="121" t="n"/>
-      <c r="J55" s="122">
-        <f>SUM(C49:I49)</f>
-        <v/>
-      </c>
+      <c r="B55" s="65" t="inlineStr">
+        <is>
+          <t>상급병원질병입원일당</t>
+        </is>
+      </c>
+      <c r="C55" s="136" t="n"/>
+      <c r="D55" s="136" t="n"/>
+      <c r="E55" s="136" t="n"/>
+      <c r="F55" s="136" t="n"/>
+      <c r="G55" s="136" t="n"/>
+      <c r="H55" s="136" t="n"/>
+      <c r="I55" s="136" t="n"/>
+      <c r="J55" s="122" t="n"/>
     </row>
     <row r="56" ht="16.5" customHeight="1" s="82">
       <c r="A56" s="88" t="n"/>
       <c r="B56" s="60" t="inlineStr">
         <is>
-          <t>상해수술일당</t>
+          <t>상해일당</t>
         </is>
       </c>
       <c r="C56" s="121" t="n"/>
@@ -2511,13 +2508,16 @@
       <c r="G56" s="121" t="n"/>
       <c r="H56" s="121" t="n"/>
       <c r="I56" s="121" t="n"/>
-      <c r="J56" s="122" t="n"/>
+      <c r="J56" s="122">
+        <f>SUM(C49:I49)</f>
+        <v/>
+      </c>
     </row>
     <row r="57" ht="16.5" customHeight="1" s="82">
       <c r="A57" s="88" t="n"/>
-      <c r="B57" s="31" t="inlineStr">
-        <is>
-          <t>간병인</t>
+      <c r="B57" s="60" t="inlineStr">
+        <is>
+          <t>상해수술일당</t>
         </is>
       </c>
       <c r="C57" s="121" t="n"/>
@@ -2527,16 +2527,13 @@
       <c r="G57" s="121" t="n"/>
       <c r="H57" s="121" t="n"/>
       <c r="I57" s="121" t="n"/>
-      <c r="J57" s="122">
-        <f>SUM(C50:I50)</f>
-        <v/>
-      </c>
+      <c r="J57" s="122" t="n"/>
     </row>
     <row r="58" ht="16.5" customHeight="1" s="82">
       <c r="A58" s="88" t="n"/>
       <c r="B58" s="31" t="inlineStr">
         <is>
-          <t>간병인지원일당</t>
+          <t>간병인</t>
         </is>
       </c>
       <c r="C58" s="121" t="n"/>
@@ -2546,13 +2543,16 @@
       <c r="G58" s="121" t="n"/>
       <c r="H58" s="121" t="n"/>
       <c r="I58" s="121" t="n"/>
-      <c r="J58" s="122" t="n"/>
+      <c r="J58" s="122">
+        <f>SUM(C50:I50)</f>
+        <v/>
+      </c>
     </row>
     <row r="59" ht="16.5" customHeight="1" s="82">
       <c r="A59" s="88" t="n"/>
       <c r="B59" s="31" t="inlineStr">
         <is>
-          <t>간호통합병동</t>
+          <t>간병인지원일당</t>
         </is>
       </c>
       <c r="C59" s="121" t="n"/>
@@ -2562,16 +2562,13 @@
       <c r="G59" s="121" t="n"/>
       <c r="H59" s="121" t="n"/>
       <c r="I59" s="121" t="n"/>
-      <c r="J59" s="122">
-        <f>SUM(C51:I51)</f>
-        <v/>
-      </c>
+      <c r="J59" s="122" t="n"/>
     </row>
     <row r="60" ht="16.5" customHeight="1" s="82">
       <c r="A60" s="88" t="n"/>
-      <c r="B60" s="66" t="inlineStr">
-        <is>
-          <t>1인실 종합병원</t>
+      <c r="B60" s="31" t="inlineStr">
+        <is>
+          <t>간호통합병동</t>
         </is>
       </c>
       <c r="C60" s="121" t="n"/>
@@ -2582,7 +2579,7 @@
       <c r="H60" s="121" t="n"/>
       <c r="I60" s="121" t="n"/>
       <c r="J60" s="122">
-        <f>SUM(C52:I52)</f>
+        <f>SUM(C51:I51)</f>
         <v/>
       </c>
     </row>
@@ -2590,7 +2587,7 @@
       <c r="A61" s="88" t="n"/>
       <c r="B61" s="66" t="inlineStr">
         <is>
-          <t>1인실 상급병원</t>
+          <t>1인실 종합병원</t>
         </is>
       </c>
       <c r="C61" s="121" t="n"/>
@@ -2601,15 +2598,15 @@
       <c r="H61" s="121" t="n"/>
       <c r="I61" s="121" t="n"/>
       <c r="J61" s="122">
-        <f>SUM(C53:I53)</f>
+        <f>SUM(C52:I52)</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="17.25" customHeight="1" s="82">
       <c r="A62" s="88" t="n"/>
-      <c r="B62" s="31" t="inlineStr">
-        <is>
-          <t>질병중환자실</t>
+      <c r="B62" s="66" t="inlineStr">
+        <is>
+          <t>1인실 상급병원</t>
         </is>
       </c>
       <c r="C62" s="121" t="n"/>
@@ -2620,96 +2617,95 @@
       <c r="H62" s="121" t="n"/>
       <c r="I62" s="121" t="n"/>
       <c r="J62" s="122">
+        <f>SUM(C53:I53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="17.25" customHeight="1" s="82">
+      <c r="A63" s="88" t="n"/>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>질병중환자실</t>
+        </is>
+      </c>
+      <c r="C63" s="121" t="n"/>
+      <c r="D63" s="121" t="n"/>
+      <c r="E63" s="121" t="n"/>
+      <c r="F63" s="121" t="n"/>
+      <c r="G63" s="121" t="n"/>
+      <c r="H63" s="121" t="n"/>
+      <c r="I63" s="121" t="n"/>
+      <c r="J63" s="122">
         <f>SUM(C54:I54)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="17.25" customHeight="1" s="82">
-      <c r="A63" s="89" t="n"/>
-      <c r="B63" s="25" t="inlineStr">
+    <row r="64" ht="16.5" customHeight="1" s="82">
+      <c r="A64" s="89" t="n"/>
+      <c r="B64" s="25" t="inlineStr">
         <is>
           <t>상해중환자실</t>
         </is>
       </c>
-      <c r="C63" s="117" t="n"/>
-      <c r="D63" s="117" t="n"/>
-      <c r="E63" s="117" t="n"/>
-      <c r="F63" s="117" t="n"/>
-      <c r="G63" s="117" t="n"/>
-      <c r="H63" s="117" t="n"/>
-      <c r="I63" s="117" t="n"/>
-      <c r="J63" s="118">
+      <c r="C64" s="117" t="n"/>
+      <c r="D64" s="117" t="n"/>
+      <c r="E64" s="117" t="n"/>
+      <c r="F64" s="117" t="n"/>
+      <c r="G64" s="117" t="n"/>
+      <c r="H64" s="117" t="n"/>
+      <c r="I64" s="117" t="n"/>
+      <c r="J64" s="118">
         <f>SUM(C55:I55)</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="16.5" customHeight="1" s="82">
-      <c r="A64" s="148" t="inlineStr">
+    <row r="65" ht="16.5" customHeight="1" s="82">
+      <c r="A65" s="148" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B64" s="95" t="inlineStr">
+      <c r="B65" s="95" t="inlineStr">
         <is>
           <t>상해수술비</t>
         </is>
       </c>
-      <c r="C64" s="119" t="n"/>
-      <c r="D64" s="119" t="n"/>
-      <c r="E64" s="119" t="n"/>
-      <c r="F64" s="119" t="n"/>
-      <c r="G64" s="119" t="n"/>
-      <c r="H64" s="119" t="n"/>
-      <c r="I64" s="119" t="n"/>
-      <c r="J64" s="120">
+      <c r="C65" s="119" t="n"/>
+      <c r="D65" s="119" t="n"/>
+      <c r="E65" s="119" t="n"/>
+      <c r="F65" s="119" t="n"/>
+      <c r="G65" s="119" t="n"/>
+      <c r="H65" s="119" t="n"/>
+      <c r="I65" s="119" t="n"/>
+      <c r="J65" s="120">
         <f>SUM(C56:I56)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="16.5" customHeight="1" s="82">
-      <c r="A65" s="149" t="n"/>
-      <c r="B65" s="65" t="inlineStr">
-        <is>
-          <t>중대한상해수술비</t>
-        </is>
-      </c>
-      <c r="C65" s="136" t="n"/>
-      <c r="D65" s="136" t="n"/>
-      <c r="E65" s="136" t="n"/>
-      <c r="F65" s="136" t="n"/>
-      <c r="G65" s="136" t="n"/>
-      <c r="H65" s="136" t="n"/>
-      <c r="I65" s="136" t="n"/>
-      <c r="J65" s="122">
-        <f>SUM(C57:I57)</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" s="82">
       <c r="A66" s="149" t="n"/>
-      <c r="B66" s="60" t="inlineStr">
-        <is>
-          <t>상해 종수술비(1-5종)</t>
+      <c r="B66" s="65" t="inlineStr">
+        <is>
+          <t>중대한상해수술비</t>
         </is>
       </c>
       <c r="C66" s="136" t="n"/>
       <c r="D66" s="136" t="n"/>
       <c r="E66" s="136" t="n"/>
-      <c r="F66" s="137" t="n"/>
+      <c r="F66" s="136" t="n"/>
       <c r="G66" s="136" t="n"/>
       <c r="H66" s="136" t="n"/>
       <c r="I66" s="136" t="n"/>
-      <c r="J66" s="122" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="J66" s="122">
+        <f>SUM(C57:I57)</f>
+        <v/>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" s="82">
       <c r="A67" s="149" t="n"/>
       <c r="B67" s="60" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-8종)</t>
+          <t>상해 종수술비(1-5종)</t>
         </is>
       </c>
       <c r="C67" s="136" t="n"/>
@@ -2719,32 +2715,33 @@
       <c r="G67" s="136" t="n"/>
       <c r="H67" s="136" t="n"/>
       <c r="I67" s="136" t="n"/>
-      <c r="J67" s="122" t="n"/>
+      <c r="J67" s="122" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="17.25" customHeight="1" s="82">
       <c r="A68" s="149" t="n"/>
       <c r="B68" s="60" t="inlineStr">
         <is>
-          <t>창상봉합술</t>
-        </is>
-      </c>
-      <c r="C68" s="121" t="n"/>
-      <c r="D68" s="121" t="n"/>
-      <c r="E68" s="121" t="n"/>
-      <c r="F68" s="121" t="n"/>
-      <c r="G68" s="121" t="n"/>
-      <c r="H68" s="121" t="n"/>
-      <c r="I68" s="121" t="n"/>
-      <c r="J68" s="122">
-        <f>SUM(C59:I59)</f>
-        <v/>
-      </c>
+          <t>상해 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C68" s="136" t="n"/>
+      <c r="D68" s="136" t="n"/>
+      <c r="E68" s="136" t="n"/>
+      <c r="F68" s="137" t="n"/>
+      <c r="G68" s="136" t="n"/>
+      <c r="H68" s="136" t="n"/>
+      <c r="I68" s="136" t="n"/>
+      <c r="J68" s="122" t="n"/>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="82">
       <c r="A69" s="149" t="n"/>
       <c r="B69" s="60" t="inlineStr">
         <is>
-          <t>골절수술비</t>
+          <t>창상봉합술</t>
         </is>
       </c>
       <c r="C69" s="121" t="n"/>
@@ -2755,15 +2752,15 @@
       <c r="H69" s="121" t="n"/>
       <c r="I69" s="121" t="n"/>
       <c r="J69" s="122">
-        <f>SUM(C60:I60)</f>
+        <f>SUM(C59:I59)</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1" s="82">
       <c r="A70" s="149" t="n"/>
-      <c r="B70" s="69" t="inlineStr">
-        <is>
-          <t>5대골절수술비</t>
+      <c r="B70" s="60" t="inlineStr">
+        <is>
+          <t>골절수술비</t>
         </is>
       </c>
       <c r="C70" s="121" t="n"/>
@@ -2774,73 +2771,72 @@
       <c r="H70" s="121" t="n"/>
       <c r="I70" s="121" t="n"/>
       <c r="J70" s="122">
-        <f>SUM(C61:I61)</f>
+        <f>SUM(C60:I60)</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="82">
       <c r="A71" s="149" t="n"/>
-      <c r="B71" s="57" t="inlineStr">
-        <is>
-          <t>화상수술비</t>
-        </is>
-      </c>
-      <c r="C71" s="117" t="n"/>
-      <c r="D71" s="117" t="n"/>
-      <c r="E71" s="117" t="n"/>
-      <c r="F71" s="117" t="n"/>
-      <c r="G71" s="117" t="n"/>
-      <c r="H71" s="117" t="n"/>
-      <c r="I71" s="117" t="n"/>
-      <c r="J71" s="118">
-        <f>SUM(C62:I62)</f>
+      <c r="B71" s="69" t="inlineStr">
+        <is>
+          <t>5대골절수술비</t>
+        </is>
+      </c>
+      <c r="C71" s="121" t="n"/>
+      <c r="D71" s="121" t="n"/>
+      <c r="E71" s="121" t="n"/>
+      <c r="F71" s="121" t="n"/>
+      <c r="G71" s="121" t="n"/>
+      <c r="H71" s="121" t="n"/>
+      <c r="I71" s="121" t="n"/>
+      <c r="J71" s="122">
+        <f>SUM(C61:I61)</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" s="82">
       <c r="A72" s="149" t="n"/>
-      <c r="B72" s="65" t="inlineStr">
-        <is>
-          <t>질병수술비</t>
-        </is>
-      </c>
-      <c r="C72" s="136" t="n"/>
-      <c r="D72" s="136" t="n"/>
-      <c r="E72" s="136" t="n"/>
-      <c r="F72" s="136" t="n"/>
-      <c r="G72" s="136" t="n"/>
-      <c r="H72" s="136" t="n"/>
-      <c r="I72" s="138" t="n"/>
-      <c r="J72" s="116">
-        <f>SUM(C63:I63)</f>
+      <c r="B72" s="57" t="inlineStr">
+        <is>
+          <t>화상수술비</t>
+        </is>
+      </c>
+      <c r="C72" s="117" t="n"/>
+      <c r="D72" s="117" t="n"/>
+      <c r="E72" s="117" t="n"/>
+      <c r="F72" s="117" t="n"/>
+      <c r="G72" s="117" t="n"/>
+      <c r="H72" s="117" t="n"/>
+      <c r="I72" s="117" t="n"/>
+      <c r="J72" s="118">
+        <f>SUM(C62:I62)</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="82">
       <c r="A73" s="149" t="n"/>
-      <c r="B73" s="60" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-5종)</t>
-        </is>
-      </c>
-      <c r="C73" s="121" t="n"/>
-      <c r="D73" s="121" t="n"/>
-      <c r="E73" s="121" t="n"/>
-      <c r="F73" s="139" t="n"/>
-      <c r="G73" s="121" t="n"/>
-      <c r="H73" s="121" t="n"/>
-      <c r="I73" s="121" t="n"/>
-      <c r="J73" s="122" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="B73" s="65" t="inlineStr">
+        <is>
+          <t>질병수술비</t>
+        </is>
+      </c>
+      <c r="C73" s="136" t="n"/>
+      <c r="D73" s="136" t="n"/>
+      <c r="E73" s="136" t="n"/>
+      <c r="F73" s="136" t="n"/>
+      <c r="G73" s="136" t="n"/>
+      <c r="H73" s="136" t="n"/>
+      <c r="I73" s="138" t="n"/>
+      <c r="J73" s="116">
+        <f>SUM(C63:I63)</f>
+        <v/>
       </c>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="82">
       <c r="A74" s="149" t="n"/>
       <c r="B74" s="60" t="inlineStr">
         <is>
-          <t>질병 종수술비(1-8종)</t>
+          <t>질병 종수술비(1-5종)</t>
         </is>
       </c>
       <c r="C74" s="121" t="n"/>
@@ -2850,32 +2846,33 @@
       <c r="G74" s="121" t="n"/>
       <c r="H74" s="121" t="n"/>
       <c r="I74" s="121" t="n"/>
-      <c r="J74" s="122" t="n"/>
+      <c r="J74" s="122" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="82">
       <c r="A75" s="149" t="n"/>
-      <c r="B75" s="72" t="inlineStr">
-        <is>
-          <t>뇌혈관수술비</t>
-        </is>
-      </c>
-      <c r="C75" s="140" t="n"/>
-      <c r="D75" s="140" t="n"/>
-      <c r="E75" s="140" t="n"/>
-      <c r="F75" s="140" t="n"/>
-      <c r="G75" s="140" t="n"/>
-      <c r="H75" s="140" t="n"/>
-      <c r="I75" s="140" t="n"/>
-      <c r="J75" s="122">
-        <f>SUM(C65:I65)</f>
-        <v/>
-      </c>
+      <c r="B75" s="60" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C75" s="121" t="n"/>
+      <c r="D75" s="121" t="n"/>
+      <c r="E75" s="121" t="n"/>
+      <c r="F75" s="139" t="n"/>
+      <c r="G75" s="121" t="n"/>
+      <c r="H75" s="121" t="n"/>
+      <c r="I75" s="121" t="n"/>
+      <c r="J75" s="122" t="n"/>
     </row>
     <row r="76" ht="17.25" customHeight="1" s="82">
       <c r="A76" s="149" t="n"/>
       <c r="B76" s="72" t="inlineStr">
         <is>
-          <t>허혈성수술비</t>
+          <t>뇌혈관수술비</t>
         </is>
       </c>
       <c r="C76" s="140" t="n"/>
@@ -2886,7 +2883,7 @@
       <c r="H76" s="140" t="n"/>
       <c r="I76" s="140" t="n"/>
       <c r="J76" s="122">
-        <f>SUM(C66:I66)</f>
+        <f>SUM(C65:I65)</f>
         <v/>
       </c>
     </row>
@@ -2894,7 +2891,7 @@
       <c r="A77" s="149" t="n"/>
       <c r="B77" s="72" t="inlineStr">
         <is>
-          <t>심장수술비</t>
+          <t>허혈성수술비</t>
         </is>
       </c>
       <c r="C77" s="140" t="n"/>
@@ -2905,15 +2902,15 @@
       <c r="H77" s="140" t="n"/>
       <c r="I77" s="140" t="n"/>
       <c r="J77" s="122">
-        <f>SUM(C67:I67)</f>
+        <f>SUM(C66:I66)</f>
         <v/>
       </c>
     </row>
     <row r="78" ht="16.5" customHeight="1" s="82">
       <c r="A78" s="149" t="n"/>
-      <c r="B78" s="61" t="inlineStr">
-        <is>
-          <t>120대수술비</t>
+      <c r="B78" s="72" t="inlineStr">
+        <is>
+          <t>심장수술비</t>
         </is>
       </c>
       <c r="C78" s="140" t="n"/>
@@ -2923,88 +2920,88 @@
       <c r="G78" s="140" t="n"/>
       <c r="H78" s="140" t="n"/>
       <c r="I78" s="140" t="n"/>
-      <c r="J78" s="141">
-        <f>SUM(C68:I68)</f>
+      <c r="J78" s="122">
+        <f>SUM(C67:I67)</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="17.25" customHeight="1" s="82">
       <c r="A79" s="149" t="n"/>
-      <c r="B79" s="73" t="inlineStr">
-        <is>
-          <t>5대기관 수술비 관혈</t>
-        </is>
-      </c>
-      <c r="C79" s="123" t="n"/>
-      <c r="D79" s="123" t="n"/>
-      <c r="E79" s="123" t="n"/>
-      <c r="F79" s="123" t="n"/>
-      <c r="G79" s="123" t="n"/>
-      <c r="H79" s="123" t="n"/>
-      <c r="I79" s="123" t="n"/>
-      <c r="J79" s="120">
-        <f>SUM(C69:I69)</f>
+      <c r="B79" s="61" t="inlineStr">
+        <is>
+          <t>120대수술비</t>
+        </is>
+      </c>
+      <c r="C79" s="140" t="n"/>
+      <c r="D79" s="140" t="n"/>
+      <c r="E79" s="140" t="n"/>
+      <c r="F79" s="140" t="n"/>
+      <c r="G79" s="140" t="n"/>
+      <c r="H79" s="140" t="n"/>
+      <c r="I79" s="140" t="n"/>
+      <c r="J79" s="141">
+        <f>SUM(C68:I68)</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="17.25" customHeight="1" s="82">
       <c r="A80" s="149" t="n"/>
-      <c r="B80" s="74" t="inlineStr">
+      <c r="B80" s="73" t="inlineStr">
+        <is>
+          <t>5대기관 수술비 관혈</t>
+        </is>
+      </c>
+      <c r="C80" s="123" t="n"/>
+      <c r="D80" s="123" t="n"/>
+      <c r="E80" s="123" t="n"/>
+      <c r="F80" s="123" t="n"/>
+      <c r="G80" s="123" t="n"/>
+      <c r="H80" s="123" t="n"/>
+      <c r="I80" s="123" t="n"/>
+      <c r="J80" s="120">
+        <f>SUM(C69:I69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="17.25" customHeight="1" s="82">
+      <c r="A81" s="149" t="n"/>
+      <c r="B81" s="74" t="inlineStr">
         <is>
           <t>5대기관 수술비 비관혈</t>
         </is>
       </c>
-      <c r="C80" s="117" t="n"/>
-      <c r="D80" s="117" t="n"/>
-      <c r="E80" s="117" t="n"/>
-      <c r="F80" s="117" t="n"/>
-      <c r="G80" s="117" t="n"/>
-      <c r="H80" s="117" t="n"/>
-      <c r="I80" s="117" t="n"/>
-      <c r="J80" s="118">
+      <c r="C81" s="117" t="n"/>
+      <c r="D81" s="117" t="n"/>
+      <c r="E81" s="117" t="n"/>
+      <c r="F81" s="117" t="n"/>
+      <c r="G81" s="117" t="n"/>
+      <c r="H81" s="117" t="n"/>
+      <c r="I81" s="117" t="n"/>
+      <c r="J81" s="118">
         <f>SUM(C70:I70)</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="17.25" customHeight="1" s="82">
-      <c r="A81" s="150" t="inlineStr">
+    <row r="82" ht="16.5" customHeight="1" s="82">
+      <c r="A82" s="150" t="inlineStr">
         <is>
           <t>운전</t>
         </is>
       </c>
-      <c r="B81" s="28" t="inlineStr">
+      <c r="B82" s="28" t="inlineStr">
         <is>
           <t>대인</t>
         </is>
       </c>
-      <c r="C81" s="102" t="n"/>
-      <c r="D81" s="102" t="n"/>
-      <c r="E81" s="102" t="n"/>
-      <c r="F81" s="102" t="n"/>
-      <c r="G81" s="102" t="n"/>
-      <c r="H81" s="102" t="n"/>
-      <c r="I81" s="102" t="n"/>
-      <c r="J81" s="120">
+      <c r="C82" s="102" t="n"/>
+      <c r="D82" s="102" t="n"/>
+      <c r="E82" s="102" t="n"/>
+      <c r="F82" s="102" t="n"/>
+      <c r="G82" s="102" t="n"/>
+      <c r="H82" s="102" t="n"/>
+      <c r="I82" s="102" t="n"/>
+      <c r="J82" s="120">
         <f>SUM(C71:I71)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" ht="16.5" customHeight="1" s="82">
-      <c r="A82" s="149" t="n"/>
-      <c r="B82" s="31" t="inlineStr">
-        <is>
-          <t>대물</t>
-        </is>
-      </c>
-      <c r="C82" s="130" t="n"/>
-      <c r="D82" s="130" t="n"/>
-      <c r="E82" s="130" t="n"/>
-      <c r="F82" s="130" t="n"/>
-      <c r="G82" s="130" t="n"/>
-      <c r="H82" s="130" t="n"/>
-      <c r="I82" s="130" t="n"/>
-      <c r="J82" s="122">
-        <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
@@ -3012,7 +3009,7 @@
       <c r="A83" s="149" t="n"/>
       <c r="B83" s="31" t="inlineStr">
         <is>
-          <t>합의금</t>
+          <t>대물</t>
         </is>
       </c>
       <c r="C83" s="130" t="n"/>
@@ -3023,15 +3020,15 @@
       <c r="H83" s="130" t="n"/>
       <c r="I83" s="130" t="n"/>
       <c r="J83" s="122">
-        <f>SUM(C73:I73)</f>
+        <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="82">
       <c r="A84" s="149" t="n"/>
-      <c r="B84" s="66" t="inlineStr">
-        <is>
-          <t>6주미만</t>
+      <c r="B84" s="31" t="inlineStr">
+        <is>
+          <t>합의금</t>
         </is>
       </c>
       <c r="C84" s="130" t="n"/>
@@ -3042,15 +3039,15 @@
       <c r="H84" s="130" t="n"/>
       <c r="I84" s="130" t="n"/>
       <c r="J84" s="122">
-        <f>SUM(C74:I74)</f>
+        <f>SUM(C73:I73)</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="17.25" customHeight="1" s="82">
       <c r="A85" s="149" t="n"/>
-      <c r="B85" s="31" t="inlineStr">
-        <is>
-          <t>변호사</t>
+      <c r="B85" s="66" t="inlineStr">
+        <is>
+          <t>6주미만</t>
         </is>
       </c>
       <c r="C85" s="130" t="n"/>
@@ -3061,275 +3058,275 @@
       <c r="H85" s="130" t="n"/>
       <c r="I85" s="130" t="n"/>
       <c r="J85" s="122">
+        <f>SUM(C74:I74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16.5" customHeight="1" s="82">
+      <c r="A86" s="149" t="n"/>
+      <c r="B86" s="31" t="inlineStr">
+        <is>
+          <t>변호사</t>
+        </is>
+      </c>
+      <c r="C86" s="130" t="n"/>
+      <c r="D86" s="130" t="n"/>
+      <c r="E86" s="130" t="n"/>
+      <c r="F86" s="130" t="n"/>
+      <c r="G86" s="130" t="n"/>
+      <c r="H86" s="130" t="n"/>
+      <c r="I86" s="130" t="n"/>
+      <c r="J86" s="122">
         <f>SUM(C75:I75)</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="16.5" customHeight="1" s="82">
-      <c r="A86" s="151" t="n"/>
-      <c r="B86" s="25" t="inlineStr">
+    <row r="87" ht="16.5" customHeight="1" s="82">
+      <c r="A87" s="151" t="n"/>
+      <c r="B87" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C86" s="142" t="n"/>
-      <c r="D86" s="142" t="n"/>
-      <c r="E86" s="142" t="n"/>
-      <c r="F86" s="142" t="n"/>
-      <c r="G86" s="142" t="n"/>
-      <c r="H86" s="142" t="n"/>
-      <c r="I86" s="142" t="n"/>
-      <c r="J86" s="118">
+      <c r="C87" s="142" t="n"/>
+      <c r="D87" s="142" t="n"/>
+      <c r="E87" s="142" t="n"/>
+      <c r="F87" s="142" t="n"/>
+      <c r="G87" s="142" t="n"/>
+      <c r="H87" s="142" t="n"/>
+      <c r="I87" s="142" t="n"/>
+      <c r="J87" s="118">
         <f>SUM(C76:I76)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="16.5" customHeight="1" s="82">
-      <c r="A87" s="150" t="inlineStr">
+    <row r="88" ht="17.25" customHeight="1" s="82">
+      <c r="A88" s="150" t="inlineStr">
         <is>
           <t>골절</t>
         </is>
       </c>
-      <c r="B87" s="65" t="inlineStr">
+      <c r="B88" s="65" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C87" s="136" t="n"/>
-      <c r="D87" s="136" t="n"/>
-      <c r="E87" s="136" t="n"/>
-      <c r="F87" s="136" t="n"/>
-      <c r="G87" s="136" t="n"/>
-      <c r="H87" s="136" t="n"/>
-      <c r="I87" s="136" t="n"/>
-      <c r="J87" s="116">
+      <c r="C88" s="136" t="n"/>
+      <c r="D88" s="136" t="n"/>
+      <c r="E88" s="136" t="n"/>
+      <c r="F88" s="136" t="n"/>
+      <c r="G88" s="136" t="n"/>
+      <c r="H88" s="136" t="n"/>
+      <c r="I88" s="136" t="n"/>
+      <c r="J88" s="116">
         <f>SUM(C77:I77)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="17.25" customHeight="1" s="82">
-      <c r="A88" s="149" t="n"/>
-      <c r="B88" s="60" t="inlineStr">
+    <row r="89" ht="17.25" customHeight="1" s="82">
+      <c r="A89" s="149" t="n"/>
+      <c r="B89" s="60" t="inlineStr">
         <is>
           <t>골절(치아파절제외)</t>
         </is>
       </c>
-      <c r="C88" s="121" t="n"/>
-      <c r="D88" s="121" t="n"/>
-      <c r="E88" s="121" t="n"/>
-      <c r="F88" s="121" t="n"/>
-      <c r="G88" s="121" t="n"/>
-      <c r="H88" s="121" t="n"/>
-      <c r="I88" s="121" t="n"/>
-      <c r="J88" s="122">
+      <c r="C89" s="121" t="n"/>
+      <c r="D89" s="121" t="n"/>
+      <c r="E89" s="121" t="n"/>
+      <c r="F89" s="121" t="n"/>
+      <c r="G89" s="121" t="n"/>
+      <c r="H89" s="121" t="n"/>
+      <c r="I89" s="121" t="n"/>
+      <c r="J89" s="122">
         <f>SUM(C78:I78)</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="17.25" customHeight="1" s="82">
-      <c r="A89" s="151" t="n"/>
-      <c r="B89" s="74" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="151" t="n"/>
+      <c r="B90" s="74" t="inlineStr">
         <is>
           <t>5대골절진단비</t>
         </is>
       </c>
-      <c r="C89" s="117" t="n"/>
-      <c r="D89" s="117" t="n"/>
-      <c r="E89" s="117" t="n"/>
-      <c r="F89" s="117" t="n"/>
-      <c r="G89" s="117" t="n"/>
-      <c r="H89" s="117" t="n"/>
-      <c r="I89" s="117" t="n"/>
-      <c r="J89" s="118">
+      <c r="C90" s="117" t="n"/>
+      <c r="D90" s="117" t="n"/>
+      <c r="E90" s="117" t="n"/>
+      <c r="F90" s="117" t="n"/>
+      <c r="G90" s="117" t="n"/>
+      <c r="H90" s="117" t="n"/>
+      <c r="I90" s="117" t="n"/>
+      <c r="J90" s="118">
         <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="99" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="99" t="inlineStr">
         <is>
           <t>응급실</t>
         </is>
       </c>
-      <c r="B90" s="64" t="inlineStr">
+      <c r="B91" s="64" t="inlineStr">
         <is>
           <t>응급실(응급)</t>
         </is>
       </c>
-      <c r="C90" s="113" t="n"/>
-      <c r="D90" s="113" t="n"/>
-      <c r="E90" s="113" t="n"/>
-      <c r="F90" s="113" t="n"/>
-      <c r="G90" s="113" t="n"/>
-      <c r="H90" s="113" t="n"/>
-      <c r="I90" s="113" t="n"/>
-      <c r="J90" s="114">
+      <c r="C91" s="113" t="n"/>
+      <c r="D91" s="113" t="n"/>
+      <c r="E91" s="113" t="n"/>
+      <c r="F91" s="113" t="n"/>
+      <c r="G91" s="113" t="n"/>
+      <c r="H91" s="113" t="n"/>
+      <c r="I91" s="113" t="n"/>
+      <c r="J91" s="114">
         <f>SUM(C80:I80)</f>
         <v/>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="87" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="87" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="B91" s="34" t="inlineStr">
+      <c r="B92" s="34" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="C91" s="123" t="n"/>
-      <c r="D91" s="123" t="n"/>
-      <c r="E91" s="123" t="n"/>
-      <c r="F91" s="123" t="n"/>
-      <c r="G91" s="123" t="n"/>
-      <c r="H91" s="123" t="n"/>
-      <c r="I91" s="123" t="n"/>
-      <c r="J91" s="124" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="150" t="inlineStr">
+      <c r="C92" s="123" t="n"/>
+      <c r="D92" s="123" t="n"/>
+      <c r="E92" s="123" t="n"/>
+      <c r="F92" s="123" t="n"/>
+      <c r="G92" s="123" t="n"/>
+      <c r="H92" s="123" t="n"/>
+      <c r="I92" s="123" t="n"/>
+      <c r="J92" s="124" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="150" t="inlineStr">
         <is>
           <t>화상</t>
         </is>
       </c>
-      <c r="B92" s="28" t="inlineStr">
+      <c r="B93" s="28" t="inlineStr">
         <is>
           <t>화상진단비</t>
         </is>
       </c>
-      <c r="C92" s="119" t="n"/>
-      <c r="D92" s="119" t="n"/>
-      <c r="E92" s="119" t="n"/>
-      <c r="F92" s="119" t="n"/>
-      <c r="G92" s="119" t="n"/>
-      <c r="H92" s="119" t="n"/>
-      <c r="I92" s="119" t="n"/>
-      <c r="J92" s="120">
+      <c r="C93" s="119" t="n"/>
+      <c r="D93" s="119" t="n"/>
+      <c r="E93" s="119" t="n"/>
+      <c r="F93" s="119" t="n"/>
+      <c r="G93" s="119" t="n"/>
+      <c r="H93" s="119" t="n"/>
+      <c r="I93" s="119" t="n"/>
+      <c r="J93" s="120">
         <f>SUM(C82:I82)</f>
         <v/>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="151" t="n"/>
-      <c r="B93" s="25" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="151" t="n"/>
+      <c r="B94" s="25" t="inlineStr">
         <is>
           <t>중증화상진단비</t>
         </is>
       </c>
-      <c r="C93" s="117" t="n"/>
-      <c r="D93" s="117" t="n"/>
-      <c r="E93" s="117" t="n"/>
-      <c r="F93" s="117" t="n"/>
-      <c r="G93" s="117" t="n"/>
-      <c r="H93" s="117" t="n"/>
-      <c r="I93" s="117" t="n"/>
-      <c r="J93" s="118">
+      <c r="C94" s="117" t="n"/>
+      <c r="D94" s="117" t="n"/>
+      <c r="E94" s="117" t="n"/>
+      <c r="F94" s="117" t="n"/>
+      <c r="G94" s="117" t="n"/>
+      <c r="H94" s="117" t="n"/>
+      <c r="I94" s="117" t="n"/>
+      <c r="J94" s="118">
         <f>SUM(C83:I83)</f>
         <v/>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="150" t="inlineStr">
+    <row r="95" s="82">
+      <c r="A95" s="150" t="inlineStr">
         <is>
           <t>깁스</t>
         </is>
       </c>
-      <c r="B94" s="95" t="inlineStr">
+      <c r="B95" s="95" t="inlineStr">
         <is>
           <t>반깁스</t>
         </is>
       </c>
-      <c r="C94" s="119" t="n"/>
-      <c r="D94" s="119" t="n"/>
-      <c r="E94" s="119" t="n"/>
-      <c r="F94" s="119" t="n"/>
-      <c r="G94" s="119" t="n"/>
-      <c r="H94" s="119" t="n"/>
-      <c r="I94" s="119" t="n"/>
-      <c r="J94" s="120">
+      <c r="C95" s="119" t="n"/>
+      <c r="D95" s="119" t="n"/>
+      <c r="E95" s="119" t="n"/>
+      <c r="F95" s="119" t="n"/>
+      <c r="G95" s="119" t="n"/>
+      <c r="H95" s="119" t="n"/>
+      <c r="I95" s="119" t="n"/>
+      <c r="J95" s="120">
         <f>SUM(C84:I84)</f>
         <v/>
       </c>
     </row>
-    <row r="95" s="82">
-      <c r="A95" s="151" t="n"/>
-      <c r="B95" s="57" t="inlineStr">
+    <row r="96" s="82">
+      <c r="A96" s="151" t="n"/>
+      <c r="B96" s="57" t="inlineStr">
         <is>
           <t>깁스진단비</t>
         </is>
       </c>
-      <c r="C95" s="117" t="n"/>
-      <c r="D95" s="117" t="n"/>
-      <c r="E95" s="117" t="n"/>
-      <c r="F95" s="117" t="n"/>
-      <c r="G95" s="117" t="n"/>
-      <c r="H95" s="117" t="n"/>
-      <c r="I95" s="117" t="n"/>
-      <c r="J95" s="118">
+      <c r="C96" s="117" t="n"/>
+      <c r="D96" s="117" t="n"/>
+      <c r="E96" s="117" t="n"/>
+      <c r="F96" s="117" t="n"/>
+      <c r="G96" s="117" t="n"/>
+      <c r="H96" s="117" t="n"/>
+      <c r="I96" s="117" t="n"/>
+      <c r="J96" s="118">
         <f>SUM(C85:I85)</f>
         <v/>
       </c>
     </row>
-    <row r="96" s="82">
-      <c r="A96" s="150" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="150" t="inlineStr">
         <is>
           <t>실손</t>
         </is>
       </c>
-      <c r="B96" s="95" t="inlineStr">
+      <c r="B97" s="95" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="C96" s="143" t="n"/>
-      <c r="D96" s="143" t="n"/>
-      <c r="E96" s="143" t="n"/>
-      <c r="F96" s="143" t="n"/>
-      <c r="G96" s="143" t="n"/>
-      <c r="H96" s="143" t="n"/>
-      <c r="I96" s="143" t="n"/>
-      <c r="J96" s="120">
+      <c r="C97" s="143" t="n"/>
+      <c r="D97" s="143" t="n"/>
+      <c r="E97" s="143" t="n"/>
+      <c r="F97" s="143" t="n"/>
+      <c r="G97" s="143" t="n"/>
+      <c r="H97" s="143" t="n"/>
+      <c r="I97" s="143" t="n"/>
+      <c r="J97" s="120">
         <f>SUM(C86:I86)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="149" t="n"/>
-      <c r="B97" s="60" t="inlineStr">
-        <is>
-          <t>통원</t>
-        </is>
-      </c>
-      <c r="C97" s="144" t="n"/>
-      <c r="D97" s="144" t="n"/>
-      <c r="E97" s="144" t="n"/>
-      <c r="F97" s="144" t="n"/>
-      <c r="G97" s="144" t="n"/>
-      <c r="H97" s="144" t="n"/>
-      <c r="I97" s="144" t="n"/>
-      <c r="J97" s="122">
-        <f>SUM(C87:I87)</f>
         <v/>
       </c>
     </row>
     <row r="98" s="82">
       <c r="A98" s="149" t="n"/>
-      <c r="B98" s="22" t="inlineStr">
-        <is>
-          <t>약값</t>
-        </is>
-      </c>
-      <c r="C98" s="115" t="n"/>
-      <c r="D98" s="115" t="n"/>
-      <c r="E98" s="115" t="n"/>
-      <c r="F98" s="115" t="n"/>
-      <c r="G98" s="115" t="n"/>
-      <c r="H98" s="115" t="n"/>
-      <c r="I98" s="145" t="n"/>
+      <c r="B98" s="60" t="inlineStr">
+        <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="C98" s="144" t="n"/>
+      <c r="D98" s="144" t="n"/>
+      <c r="E98" s="144" t="n"/>
+      <c r="F98" s="144" t="n"/>
+      <c r="G98" s="144" t="n"/>
+      <c r="H98" s="144" t="n"/>
+      <c r="I98" s="144" t="n"/>
       <c r="J98" s="122">
-        <f>SUM(C88:I88)</f>
+        <f>SUM(C87:I87)</f>
         <v/>
       </c>
     </row>
@@ -3337,7 +3334,7 @@
       <c r="A99" s="149" t="n"/>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>MRI/도수치료/비급여주사</t>
+          <t>약값</t>
         </is>
       </c>
       <c r="C99" s="115" t="n"/>
@@ -3347,13 +3344,16 @@
       <c r="G99" s="115" t="n"/>
       <c r="H99" s="115" t="n"/>
       <c r="I99" s="145" t="n"/>
-      <c r="J99" s="122" t="n"/>
+      <c r="J99" s="122">
+        <f>SUM(C88:I88)</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="151" t="n"/>
+      <c r="A100" s="149" t="n"/>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>상해의료비</t>
+          <t>MRI/도수치료/비급여주사</t>
         </is>
       </c>
       <c r="C100" s="115" t="n"/>
@@ -3366,47 +3366,63 @@
       <c r="J100" s="122" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="87" t="inlineStr">
+      <c r="A101" s="151" t="n"/>
+      <c r="B101" s="22" t="inlineStr">
+        <is>
+          <t>상해의료비</t>
+        </is>
+      </c>
+      <c r="C101" s="115" t="n"/>
+      <c r="D101" s="115" t="n"/>
+      <c r="E101" s="115" t="n"/>
+      <c r="F101" s="115" t="n"/>
+      <c r="G101" s="115" t="n"/>
+      <c r="H101" s="115" t="n"/>
+      <c r="I101" s="145" t="n"/>
+      <c r="J101" s="122" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="87" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B101" s="79" t="inlineStr">
+      <c r="B102" s="79" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C101" s="146" t="n"/>
-      <c r="D101" s="146" t="n"/>
-      <c r="E101" s="146" t="n"/>
-      <c r="F101" s="146" t="n"/>
-      <c r="G101" s="146" t="n"/>
-      <c r="H101" s="146" t="n"/>
-      <c r="I101" s="146" t="n"/>
-      <c r="J101" s="147">
+      <c r="C102" s="146" t="n"/>
+      <c r="D102" s="146" t="n"/>
+      <c r="E102" s="146" t="n"/>
+      <c r="F102" s="146" t="n"/>
+      <c r="G102" s="146" t="n"/>
+      <c r="H102" s="146" t="n"/>
+      <c r="I102" s="146" t="n"/>
+      <c r="J102" s="147">
         <f>SUM(C89:I89)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A30:A37"/>
-    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A15:A29"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A96:A100"/>
+    <mergeCell ref="A88:A90"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A81:A86"/>
-    <mergeCell ref="A87:A89"/>
     <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A38:A50"/>
-    <mergeCell ref="A51:A63"/>
+    <mergeCell ref="A82:A87"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A64:A80"/>
     <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A97:A101"/>
+    <mergeCell ref="A30:A38"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="A52:A64"/>
+    <mergeCell ref="A39:A51"/>
+    <mergeCell ref="A65:A81"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>

--- a/master.xlsx
+++ b/master.xlsx
@@ -831,7 +831,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1268,6 +1268,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2085,38 +2094,38 @@
     </row>
     <row r="33" ht="16.5" customHeight="1" s="82">
       <c r="A33" s="88" t="n"/>
-      <c r="B33" s="52" t="inlineStr">
+      <c r="B33" s="152" t="inlineStr">
         <is>
           <t>뇌출혈진단비</t>
         </is>
       </c>
-      <c r="C33" s="127" t="n"/>
-      <c r="D33" s="127" t="n"/>
-      <c r="E33" s="127" t="n"/>
-      <c r="F33" s="127" t="n"/>
-      <c r="G33" s="127" t="n"/>
-      <c r="H33" s="127" t="n"/>
-      <c r="I33" s="127" t="n"/>
-      <c r="J33" s="116">
+      <c r="C33" s="153" t="n"/>
+      <c r="D33" s="153" t="n"/>
+      <c r="E33" s="153" t="n"/>
+      <c r="F33" s="153" t="n"/>
+      <c r="G33" s="153" t="n"/>
+      <c r="H33" s="153" t="n"/>
+      <c r="I33" s="153" t="n"/>
+      <c r="J33" s="154">
         <f>SUM(C32:I32)</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" s="82">
       <c r="A34" s="88" t="n"/>
-      <c r="B34" s="52" t="inlineStr">
+      <c r="B34" s="152" t="inlineStr">
         <is>
           <t>중대한 뇌출혈</t>
         </is>
       </c>
-      <c r="C34" s="127" t="n"/>
-      <c r="D34" s="127" t="n"/>
-      <c r="E34" s="127" t="n"/>
-      <c r="F34" s="127" t="n"/>
-      <c r="G34" s="127" t="n"/>
-      <c r="H34" s="127" t="n"/>
-      <c r="I34" s="127" t="n"/>
-      <c r="J34" s="116" t="n"/>
+      <c r="C34" s="153" t="n"/>
+      <c r="D34" s="153" t="n"/>
+      <c r="E34" s="153" t="n"/>
+      <c r="F34" s="153" t="n"/>
+      <c r="G34" s="153" t="n"/>
+      <c r="H34" s="153" t="n"/>
+      <c r="I34" s="153" t="n"/>
+      <c r="J34" s="154" t="n"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="82">
       <c r="A35" s="88" t="n"/>
@@ -3406,23 +3415,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A97:A101"/>
+    <mergeCell ref="A93:A94"/>
+    <mergeCell ref="A30:A38"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A15:A29"/>
+    <mergeCell ref="A52:A64"/>
     <mergeCell ref="A88:A90"/>
+    <mergeCell ref="A39:A51"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A65:A81"/>
+    <mergeCell ref="A95:A96"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A82:A87"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A97:A101"/>
-    <mergeCell ref="A30:A38"/>
-    <mergeCell ref="A93:A94"/>
-    <mergeCell ref="A52:A64"/>
-    <mergeCell ref="A39:A51"/>
-    <mergeCell ref="A65:A81"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>

--- a/master.xlsx
+++ b/master.xlsx
@@ -1467,7 +1467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="82" min="1" max="1"/>
@@ -2714,7 +2714,7 @@
       <c r="A67" s="149" t="n"/>
       <c r="B67" s="60" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-5종)</t>
+          <t>상해 종수술비(1-3종)</t>
         </is>
       </c>
       <c r="C67" s="136" t="n"/>
@@ -2724,17 +2724,13 @@
       <c r="G67" s="136" t="n"/>
       <c r="H67" s="136" t="n"/>
       <c r="I67" s="136" t="n"/>
-      <c r="J67" s="122" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
-      </c>
+      <c r="J67" s="122" t="n"/>
     </row>
     <row r="68" ht="17.25" customHeight="1" s="82">
       <c r="A68" s="149" t="n"/>
       <c r="B68" s="60" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-8종)</t>
+          <t>상해 종수술비(1-5종)</t>
         </is>
       </c>
       <c r="C68" s="136" t="n"/>
@@ -2744,32 +2740,33 @@
       <c r="G68" s="136" t="n"/>
       <c r="H68" s="136" t="n"/>
       <c r="I68" s="136" t="n"/>
-      <c r="J68" s="122" t="n"/>
+      <c r="J68" s="122" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="82">
       <c r="A69" s="149" t="n"/>
       <c r="B69" s="60" t="inlineStr">
         <is>
-          <t>창상봉합술</t>
-        </is>
-      </c>
-      <c r="C69" s="121" t="n"/>
-      <c r="D69" s="121" t="n"/>
-      <c r="E69" s="121" t="n"/>
-      <c r="F69" s="121" t="n"/>
-      <c r="G69" s="121" t="n"/>
-      <c r="H69" s="121" t="n"/>
-      <c r="I69" s="121" t="n"/>
-      <c r="J69" s="122">
-        <f>SUM(C59:I59)</f>
-        <v/>
-      </c>
+          <t>상해 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C69" s="136" t="n"/>
+      <c r="D69" s="136" t="n"/>
+      <c r="E69" s="136" t="n"/>
+      <c r="F69" s="137" t="n"/>
+      <c r="G69" s="136" t="n"/>
+      <c r="H69" s="136" t="n"/>
+      <c r="I69" s="136" t="n"/>
+      <c r="J69" s="122" t="n"/>
     </row>
     <row r="70" ht="16.5" customHeight="1" s="82">
       <c r="A70" s="149" t="n"/>
       <c r="B70" s="60" t="inlineStr">
         <is>
-          <t>골절수술비</t>
+          <t>창상봉합술</t>
         </is>
       </c>
       <c r="C70" s="121" t="n"/>
@@ -2780,15 +2777,15 @@
       <c r="H70" s="121" t="n"/>
       <c r="I70" s="121" t="n"/>
       <c r="J70" s="122">
-        <f>SUM(C60:I60)</f>
+        <f>SUM(C59:I59)</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="82">
       <c r="A71" s="149" t="n"/>
-      <c r="B71" s="69" t="inlineStr">
-        <is>
-          <t>5대골절수술비</t>
+      <c r="B71" s="60" t="inlineStr">
+        <is>
+          <t>골절수술비</t>
         </is>
       </c>
       <c r="C71" s="121" t="n"/>
@@ -2799,73 +2796,72 @@
       <c r="H71" s="121" t="n"/>
       <c r="I71" s="121" t="n"/>
       <c r="J71" s="122">
-        <f>SUM(C61:I61)</f>
+        <f>SUM(C60:I60)</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" s="82">
       <c r="A72" s="149" t="n"/>
-      <c r="B72" s="57" t="inlineStr">
-        <is>
-          <t>화상수술비</t>
-        </is>
-      </c>
-      <c r="C72" s="117" t="n"/>
-      <c r="D72" s="117" t="n"/>
-      <c r="E72" s="117" t="n"/>
-      <c r="F72" s="117" t="n"/>
-      <c r="G72" s="117" t="n"/>
-      <c r="H72" s="117" t="n"/>
-      <c r="I72" s="117" t="n"/>
-      <c r="J72" s="118">
-        <f>SUM(C62:I62)</f>
+      <c r="B72" s="69" t="inlineStr">
+        <is>
+          <t>5대골절수술비</t>
+        </is>
+      </c>
+      <c r="C72" s="121" t="n"/>
+      <c r="D72" s="121" t="n"/>
+      <c r="E72" s="121" t="n"/>
+      <c r="F72" s="121" t="n"/>
+      <c r="G72" s="121" t="n"/>
+      <c r="H72" s="121" t="n"/>
+      <c r="I72" s="121" t="n"/>
+      <c r="J72" s="122">
+        <f>SUM(C61:I61)</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="82">
       <c r="A73" s="149" t="n"/>
-      <c r="B73" s="65" t="inlineStr">
-        <is>
-          <t>질병수술비</t>
-        </is>
-      </c>
-      <c r="C73" s="136" t="n"/>
-      <c r="D73" s="136" t="n"/>
-      <c r="E73" s="136" t="n"/>
-      <c r="F73" s="136" t="n"/>
-      <c r="G73" s="136" t="n"/>
-      <c r="H73" s="136" t="n"/>
-      <c r="I73" s="138" t="n"/>
-      <c r="J73" s="116">
-        <f>SUM(C63:I63)</f>
+      <c r="B73" s="57" t="inlineStr">
+        <is>
+          <t>화상수술비</t>
+        </is>
+      </c>
+      <c r="C73" s="117" t="n"/>
+      <c r="D73" s="117" t="n"/>
+      <c r="E73" s="117" t="n"/>
+      <c r="F73" s="117" t="n"/>
+      <c r="G73" s="117" t="n"/>
+      <c r="H73" s="117" t="n"/>
+      <c r="I73" s="117" t="n"/>
+      <c r="J73" s="118">
+        <f>SUM(C62:I62)</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="82">
       <c r="A74" s="149" t="n"/>
-      <c r="B74" s="60" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-5종)</t>
-        </is>
-      </c>
-      <c r="C74" s="121" t="n"/>
-      <c r="D74" s="121" t="n"/>
-      <c r="E74" s="121" t="n"/>
-      <c r="F74" s="139" t="n"/>
-      <c r="G74" s="121" t="n"/>
-      <c r="H74" s="121" t="n"/>
-      <c r="I74" s="121" t="n"/>
-      <c r="J74" s="122" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="B74" s="65" t="inlineStr">
+        <is>
+          <t>질병수술비</t>
+        </is>
+      </c>
+      <c r="C74" s="136" t="n"/>
+      <c r="D74" s="136" t="n"/>
+      <c r="E74" s="136" t="n"/>
+      <c r="F74" s="136" t="n"/>
+      <c r="G74" s="136" t="n"/>
+      <c r="H74" s="136" t="n"/>
+      <c r="I74" s="138" t="n"/>
+      <c r="J74" s="116">
+        <f>SUM(C63:I63)</f>
+        <v/>
       </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="82">
       <c r="A75" s="149" t="n"/>
       <c r="B75" s="60" t="inlineStr">
         <is>
-          <t>질병 종수술비(1-8종)</t>
+          <t>질병 종수술비(1-3종)</t>
         </is>
       </c>
       <c r="C75" s="121" t="n"/>
@@ -2879,47 +2875,45 @@
     </row>
     <row r="76" ht="17.25" customHeight="1" s="82">
       <c r="A76" s="149" t="n"/>
-      <c r="B76" s="72" t="inlineStr">
-        <is>
-          <t>뇌혈관수술비</t>
-        </is>
-      </c>
-      <c r="C76" s="140" t="n"/>
-      <c r="D76" s="140" t="n"/>
-      <c r="E76" s="140" t="n"/>
-      <c r="F76" s="140" t="n"/>
-      <c r="G76" s="140" t="n"/>
-      <c r="H76" s="140" t="n"/>
-      <c r="I76" s="140" t="n"/>
-      <c r="J76" s="122">
-        <f>SUM(C65:I65)</f>
-        <v/>
+      <c r="B76" s="60" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="C76" s="121" t="n"/>
+      <c r="D76" s="121" t="n"/>
+      <c r="E76" s="121" t="n"/>
+      <c r="F76" s="139" t="n"/>
+      <c r="G76" s="121" t="n"/>
+      <c r="H76" s="121" t="n"/>
+      <c r="I76" s="121" t="n"/>
+      <c r="J76" s="122" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="82">
       <c r="A77" s="149" t="n"/>
-      <c r="B77" s="72" t="inlineStr">
-        <is>
-          <t>허혈성수술비</t>
-        </is>
-      </c>
-      <c r="C77" s="140" t="n"/>
-      <c r="D77" s="140" t="n"/>
-      <c r="E77" s="140" t="n"/>
-      <c r="F77" s="140" t="n"/>
-      <c r="G77" s="140" t="n"/>
-      <c r="H77" s="140" t="n"/>
-      <c r="I77" s="140" t="n"/>
-      <c r="J77" s="122">
-        <f>SUM(C66:I66)</f>
-        <v/>
-      </c>
+      <c r="B77" s="60" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C77" s="121" t="n"/>
+      <c r="D77" s="121" t="n"/>
+      <c r="E77" s="121" t="n"/>
+      <c r="F77" s="139" t="n"/>
+      <c r="G77" s="121" t="n"/>
+      <c r="H77" s="121" t="n"/>
+      <c r="I77" s="121" t="n"/>
+      <c r="J77" s="122" t="n"/>
     </row>
     <row r="78" ht="16.5" customHeight="1" s="82">
       <c r="A78" s="149" t="n"/>
       <c r="B78" s="72" t="inlineStr">
         <is>
-          <t>심장수술비</t>
+          <t>뇌혈관수술비</t>
         </is>
       </c>
       <c r="C78" s="140" t="n"/>
@@ -2930,15 +2924,15 @@
       <c r="H78" s="140" t="n"/>
       <c r="I78" s="140" t="n"/>
       <c r="J78" s="122">
-        <f>SUM(C67:I67)</f>
+        <f>SUM(C65:I65)</f>
         <v/>
       </c>
     </row>
     <row r="79" ht="17.25" customHeight="1" s="82">
       <c r="A79" s="149" t="n"/>
-      <c r="B79" s="61" t="inlineStr">
-        <is>
-          <t>120대수술비</t>
+      <c r="B79" s="72" t="inlineStr">
+        <is>
+          <t>허혈성수술비</t>
         </is>
       </c>
       <c r="C79" s="140" t="n"/>
@@ -2948,115 +2942,115 @@
       <c r="G79" s="140" t="n"/>
       <c r="H79" s="140" t="n"/>
       <c r="I79" s="140" t="n"/>
-      <c r="J79" s="141">
-        <f>SUM(C68:I68)</f>
+      <c r="J79" s="122">
+        <f>SUM(C66:I66)</f>
         <v/>
       </c>
     </row>
     <row r="80" ht="17.25" customHeight="1" s="82">
       <c r="A80" s="149" t="n"/>
-      <c r="B80" s="73" t="inlineStr">
-        <is>
-          <t>5대기관 수술비 관혈</t>
-        </is>
-      </c>
-      <c r="C80" s="123" t="n"/>
-      <c r="D80" s="123" t="n"/>
-      <c r="E80" s="123" t="n"/>
-      <c r="F80" s="123" t="n"/>
-      <c r="G80" s="123" t="n"/>
-      <c r="H80" s="123" t="n"/>
-      <c r="I80" s="123" t="n"/>
-      <c r="J80" s="120">
-        <f>SUM(C69:I69)</f>
+      <c r="B80" s="72" t="inlineStr">
+        <is>
+          <t>심장수술비</t>
+        </is>
+      </c>
+      <c r="C80" s="140" t="n"/>
+      <c r="D80" s="140" t="n"/>
+      <c r="E80" s="140" t="n"/>
+      <c r="F80" s="140" t="n"/>
+      <c r="G80" s="140" t="n"/>
+      <c r="H80" s="140" t="n"/>
+      <c r="I80" s="140" t="n"/>
+      <c r="J80" s="122">
+        <f>SUM(C67:I67)</f>
         <v/>
       </c>
     </row>
     <row r="81" ht="17.25" customHeight="1" s="82">
       <c r="A81" s="149" t="n"/>
-      <c r="B81" s="74" t="inlineStr">
-        <is>
-          <t>5대기관 수술비 비관혈</t>
-        </is>
-      </c>
-      <c r="C81" s="117" t="n"/>
-      <c r="D81" s="117" t="n"/>
-      <c r="E81" s="117" t="n"/>
-      <c r="F81" s="117" t="n"/>
-      <c r="G81" s="117" t="n"/>
-      <c r="H81" s="117" t="n"/>
-      <c r="I81" s="117" t="n"/>
-      <c r="J81" s="118">
-        <f>SUM(C70:I70)</f>
+      <c r="B81" s="61" t="inlineStr">
+        <is>
+          <t>120대수술비</t>
+        </is>
+      </c>
+      <c r="C81" s="140" t="n"/>
+      <c r="D81" s="140" t="n"/>
+      <c r="E81" s="140" t="n"/>
+      <c r="F81" s="140" t="n"/>
+      <c r="G81" s="140" t="n"/>
+      <c r="H81" s="140" t="n"/>
+      <c r="I81" s="140" t="n"/>
+      <c r="J81" s="141">
+        <f>SUM(C68:I68)</f>
         <v/>
       </c>
     </row>
     <row r="82" ht="16.5" customHeight="1" s="82">
-      <c r="A82" s="150" t="inlineStr">
-        <is>
-          <t>운전</t>
-        </is>
-      </c>
-      <c r="B82" s="28" t="inlineStr">
-        <is>
-          <t>대인</t>
-        </is>
-      </c>
-      <c r="C82" s="102" t="n"/>
-      <c r="D82" s="102" t="n"/>
-      <c r="E82" s="102" t="n"/>
-      <c r="F82" s="102" t="n"/>
-      <c r="G82" s="102" t="n"/>
-      <c r="H82" s="102" t="n"/>
-      <c r="I82" s="102" t="n"/>
+      <c r="A82" s="149" t="n"/>
+      <c r="B82" s="73" t="inlineStr">
+        <is>
+          <t>5대기관 수술비 관혈</t>
+        </is>
+      </c>
+      <c r="C82" s="123" t="n"/>
+      <c r="D82" s="123" t="n"/>
+      <c r="E82" s="123" t="n"/>
+      <c r="F82" s="123" t="n"/>
+      <c r="G82" s="123" t="n"/>
+      <c r="H82" s="123" t="n"/>
+      <c r="I82" s="123" t="n"/>
       <c r="J82" s="120">
-        <f>SUM(C71:I71)</f>
+        <f>SUM(C69:I69)</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="17.25" customHeight="1" s="82">
       <c r="A83" s="149" t="n"/>
-      <c r="B83" s="31" t="inlineStr">
-        <is>
-          <t>대물</t>
-        </is>
-      </c>
-      <c r="C83" s="130" t="n"/>
-      <c r="D83" s="130" t="n"/>
-      <c r="E83" s="130" t="n"/>
-      <c r="F83" s="130" t="n"/>
-      <c r="G83" s="130" t="n"/>
-      <c r="H83" s="130" t="n"/>
-      <c r="I83" s="130" t="n"/>
-      <c r="J83" s="122">
-        <f>SUM(C72:I72)</f>
+      <c r="B83" s="74" t="inlineStr">
+        <is>
+          <t>5대기관 수술비 비관혈</t>
+        </is>
+      </c>
+      <c r="C83" s="117" t="n"/>
+      <c r="D83" s="117" t="n"/>
+      <c r="E83" s="117" t="n"/>
+      <c r="F83" s="117" t="n"/>
+      <c r="G83" s="117" t="n"/>
+      <c r="H83" s="117" t="n"/>
+      <c r="I83" s="117" t="n"/>
+      <c r="J83" s="118">
+        <f>SUM(C70:I70)</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="82">
-      <c r="A84" s="149" t="n"/>
-      <c r="B84" s="31" t="inlineStr">
-        <is>
-          <t>합의금</t>
-        </is>
-      </c>
-      <c r="C84" s="130" t="n"/>
-      <c r="D84" s="130" t="n"/>
-      <c r="E84" s="130" t="n"/>
-      <c r="F84" s="130" t="n"/>
-      <c r="G84" s="130" t="n"/>
-      <c r="H84" s="130" t="n"/>
-      <c r="I84" s="130" t="n"/>
-      <c r="J84" s="122">
-        <f>SUM(C73:I73)</f>
+      <c r="A84" s="150" t="inlineStr">
+        <is>
+          <t>운전</t>
+        </is>
+      </c>
+      <c r="B84" s="28" t="inlineStr">
+        <is>
+          <t>대인</t>
+        </is>
+      </c>
+      <c r="C84" s="102" t="n"/>
+      <c r="D84" s="102" t="n"/>
+      <c r="E84" s="102" t="n"/>
+      <c r="F84" s="102" t="n"/>
+      <c r="G84" s="102" t="n"/>
+      <c r="H84" s="102" t="n"/>
+      <c r="I84" s="102" t="n"/>
+      <c r="J84" s="120">
+        <f>SUM(C71:I71)</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="17.25" customHeight="1" s="82">
       <c r="A85" s="149" t="n"/>
-      <c r="B85" s="66" t="inlineStr">
-        <is>
-          <t>6주미만</t>
+      <c r="B85" s="31" t="inlineStr">
+        <is>
+          <t>대물</t>
         </is>
       </c>
       <c r="C85" s="130" t="n"/>
@@ -3067,7 +3061,7 @@
       <c r="H85" s="130" t="n"/>
       <c r="I85" s="130" t="n"/>
       <c r="J85" s="122">
-        <f>SUM(C74:I74)</f>
+        <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
@@ -3075,7 +3069,7 @@
       <c r="A86" s="149" t="n"/>
       <c r="B86" s="31" t="inlineStr">
         <is>
-          <t>변호사</t>
+          <t>합의금</t>
         </is>
       </c>
       <c r="C86" s="130" t="n"/>
@@ -3086,184 +3080,180 @@
       <c r="H86" s="130" t="n"/>
       <c r="I86" s="130" t="n"/>
       <c r="J86" s="122">
+        <f>SUM(C73:I73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="16.5" customHeight="1" s="82">
+      <c r="A87" s="149" t="n"/>
+      <c r="B87" s="66" t="inlineStr">
+        <is>
+          <t>6주미만</t>
+        </is>
+      </c>
+      <c r="C87" s="130" t="n"/>
+      <c r="D87" s="130" t="n"/>
+      <c r="E87" s="130" t="n"/>
+      <c r="F87" s="130" t="n"/>
+      <c r="G87" s="130" t="n"/>
+      <c r="H87" s="130" t="n"/>
+      <c r="I87" s="130" t="n"/>
+      <c r="J87" s="122">
+        <f>SUM(C74:I74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="17.25" customHeight="1" s="82">
+      <c r="A88" s="149" t="n"/>
+      <c r="B88" s="31" t="inlineStr">
+        <is>
+          <t>변호사</t>
+        </is>
+      </c>
+      <c r="C88" s="130" t="n"/>
+      <c r="D88" s="130" t="n"/>
+      <c r="E88" s="130" t="n"/>
+      <c r="F88" s="130" t="n"/>
+      <c r="G88" s="130" t="n"/>
+      <c r="H88" s="130" t="n"/>
+      <c r="I88" s="130" t="n"/>
+      <c r="J88" s="122">
         <f>SUM(C75:I75)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="16.5" customHeight="1" s="82">
-      <c r="A87" s="151" t="n"/>
-      <c r="B87" s="25" t="inlineStr">
+    <row r="89" ht="17.25" customHeight="1" s="82">
+      <c r="A89" s="151" t="n"/>
+      <c r="B89" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C87" s="142" t="n"/>
-      <c r="D87" s="142" t="n"/>
-      <c r="E87" s="142" t="n"/>
-      <c r="F87" s="142" t="n"/>
-      <c r="G87" s="142" t="n"/>
-      <c r="H87" s="142" t="n"/>
-      <c r="I87" s="142" t="n"/>
-      <c r="J87" s="118">
+      <c r="C89" s="142" t="n"/>
+      <c r="D89" s="142" t="n"/>
+      <c r="E89" s="142" t="n"/>
+      <c r="F89" s="142" t="n"/>
+      <c r="G89" s="142" t="n"/>
+      <c r="H89" s="142" t="n"/>
+      <c r="I89" s="142" t="n"/>
+      <c r="J89" s="118">
         <f>SUM(C76:I76)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="17.25" customHeight="1" s="82">
-      <c r="A88" s="150" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="150" t="inlineStr">
         <is>
           <t>골절</t>
         </is>
       </c>
-      <c r="B88" s="65" t="inlineStr">
+      <c r="B90" s="65" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C88" s="136" t="n"/>
-      <c r="D88" s="136" t="n"/>
-      <c r="E88" s="136" t="n"/>
-      <c r="F88" s="136" t="n"/>
-      <c r="G88" s="136" t="n"/>
-      <c r="H88" s="136" t="n"/>
-      <c r="I88" s="136" t="n"/>
-      <c r="J88" s="116">
+      <c r="C90" s="136" t="n"/>
+      <c r="D90" s="136" t="n"/>
+      <c r="E90" s="136" t="n"/>
+      <c r="F90" s="136" t="n"/>
+      <c r="G90" s="136" t="n"/>
+      <c r="H90" s="136" t="n"/>
+      <c r="I90" s="136" t="n"/>
+      <c r="J90" s="116">
         <f>SUM(C77:I77)</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="17.25" customHeight="1" s="82">
-      <c r="A89" s="149" t="n"/>
-      <c r="B89" s="60" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="149" t="n"/>
+      <c r="B91" s="60" t="inlineStr">
         <is>
           <t>골절(치아파절제외)</t>
         </is>
       </c>
-      <c r="C89" s="121" t="n"/>
-      <c r="D89" s="121" t="n"/>
-      <c r="E89" s="121" t="n"/>
-      <c r="F89" s="121" t="n"/>
-      <c r="G89" s="121" t="n"/>
-      <c r="H89" s="121" t="n"/>
-      <c r="I89" s="121" t="n"/>
-      <c r="J89" s="122">
+      <c r="C91" s="121" t="n"/>
+      <c r="D91" s="121" t="n"/>
+      <c r="E91" s="121" t="n"/>
+      <c r="F91" s="121" t="n"/>
+      <c r="G91" s="121" t="n"/>
+      <c r="H91" s="121" t="n"/>
+      <c r="I91" s="121" t="n"/>
+      <c r="J91" s="122">
         <f>SUM(C78:I78)</f>
         <v/>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="151" t="n"/>
-      <c r="B90" s="74" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="151" t="n"/>
+      <c r="B92" s="74" t="inlineStr">
         <is>
           <t>5대골절진단비</t>
         </is>
       </c>
-      <c r="C90" s="117" t="n"/>
-      <c r="D90" s="117" t="n"/>
-      <c r="E90" s="117" t="n"/>
-      <c r="F90" s="117" t="n"/>
-      <c r="G90" s="117" t="n"/>
-      <c r="H90" s="117" t="n"/>
-      <c r="I90" s="117" t="n"/>
-      <c r="J90" s="118">
+      <c r="C92" s="117" t="n"/>
+      <c r="D92" s="117" t="n"/>
+      <c r="E92" s="117" t="n"/>
+      <c r="F92" s="117" t="n"/>
+      <c r="G92" s="117" t="n"/>
+      <c r="H92" s="117" t="n"/>
+      <c r="I92" s="117" t="n"/>
+      <c r="J92" s="118">
         <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="99" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="99" t="inlineStr">
         <is>
           <t>응급실</t>
         </is>
       </c>
-      <c r="B91" s="64" t="inlineStr">
+      <c r="B93" s="64" t="inlineStr">
         <is>
           <t>응급실(응급)</t>
         </is>
       </c>
-      <c r="C91" s="113" t="n"/>
-      <c r="D91" s="113" t="n"/>
-      <c r="E91" s="113" t="n"/>
-      <c r="F91" s="113" t="n"/>
-      <c r="G91" s="113" t="n"/>
-      <c r="H91" s="113" t="n"/>
-      <c r="I91" s="113" t="n"/>
-      <c r="J91" s="114">
+      <c r="C93" s="113" t="n"/>
+      <c r="D93" s="113" t="n"/>
+      <c r="E93" s="113" t="n"/>
+      <c r="F93" s="113" t="n"/>
+      <c r="G93" s="113" t="n"/>
+      <c r="H93" s="113" t="n"/>
+      <c r="I93" s="113" t="n"/>
+      <c r="J93" s="114">
         <f>SUM(C80:I80)</f>
         <v/>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="87" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="87" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="B92" s="34" t="inlineStr">
+      <c r="B94" s="34" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="C92" s="123" t="n"/>
-      <c r="D92" s="123" t="n"/>
-      <c r="E92" s="123" t="n"/>
-      <c r="F92" s="123" t="n"/>
-      <c r="G92" s="123" t="n"/>
-      <c r="H92" s="123" t="n"/>
-      <c r="I92" s="123" t="n"/>
-      <c r="J92" s="124" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="150" t="inlineStr">
-        <is>
-          <t>화상</t>
-        </is>
-      </c>
-      <c r="B93" s="28" t="inlineStr">
-        <is>
-          <t>화상진단비</t>
-        </is>
-      </c>
-      <c r="C93" s="119" t="n"/>
-      <c r="D93" s="119" t="n"/>
-      <c r="E93" s="119" t="n"/>
-      <c r="F93" s="119" t="n"/>
-      <c r="G93" s="119" t="n"/>
-      <c r="H93" s="119" t="n"/>
-      <c r="I93" s="119" t="n"/>
-      <c r="J93" s="120">
-        <f>SUM(C82:I82)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="151" t="n"/>
-      <c r="B94" s="25" t="inlineStr">
-        <is>
-          <t>중증화상진단비</t>
-        </is>
-      </c>
-      <c r="C94" s="117" t="n"/>
-      <c r="D94" s="117" t="n"/>
-      <c r="E94" s="117" t="n"/>
-      <c r="F94" s="117" t="n"/>
-      <c r="G94" s="117" t="n"/>
-      <c r="H94" s="117" t="n"/>
-      <c r="I94" s="117" t="n"/>
-      <c r="J94" s="118">
-        <f>SUM(C83:I83)</f>
-        <v/>
-      </c>
+      <c r="C94" s="123" t="n"/>
+      <c r="D94" s="123" t="n"/>
+      <c r="E94" s="123" t="n"/>
+      <c r="F94" s="123" t="n"/>
+      <c r="G94" s="123" t="n"/>
+      <c r="H94" s="123" t="n"/>
+      <c r="I94" s="123" t="n"/>
+      <c r="J94" s="124" t="n"/>
     </row>
     <row r="95" s="82">
       <c r="A95" s="150" t="inlineStr">
         <is>
-          <t>깁스</t>
-        </is>
-      </c>
-      <c r="B95" s="95" t="inlineStr">
-        <is>
-          <t>반깁스</t>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B95" s="28" t="inlineStr">
+        <is>
+          <t>화상진단비</t>
         </is>
       </c>
       <c r="C95" s="119" t="n"/>
@@ -3274,15 +3264,15 @@
       <c r="H95" s="119" t="n"/>
       <c r="I95" s="119" t="n"/>
       <c r="J95" s="120">
-        <f>SUM(C84:I84)</f>
+        <f>SUM(C82:I82)</f>
         <v/>
       </c>
     </row>
     <row r="96" s="82">
       <c r="A96" s="151" t="n"/>
-      <c r="B96" s="57" t="inlineStr">
-        <is>
-          <t>깁스진단비</t>
+      <c r="B96" s="25" t="inlineStr">
+        <is>
+          <t>중증화상진단비</t>
         </is>
       </c>
       <c r="C96" s="117" t="n"/>
@@ -3293,92 +3283,99 @@
       <c r="H96" s="117" t="n"/>
       <c r="I96" s="117" t="n"/>
       <c r="J96" s="118">
-        <f>SUM(C85:I85)</f>
+        <f>SUM(C83:I83)</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="150" t="inlineStr">
         <is>
+          <t>깁스</t>
+        </is>
+      </c>
+      <c r="B97" s="95" t="inlineStr">
+        <is>
+          <t>반깁스</t>
+        </is>
+      </c>
+      <c r="C97" s="119" t="n"/>
+      <c r="D97" s="119" t="n"/>
+      <c r="E97" s="119" t="n"/>
+      <c r="F97" s="119" t="n"/>
+      <c r="G97" s="119" t="n"/>
+      <c r="H97" s="119" t="n"/>
+      <c r="I97" s="119" t="n"/>
+      <c r="J97" s="120">
+        <f>SUM(C84:I84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" s="82">
+      <c r="A98" s="151" t="n"/>
+      <c r="B98" s="57" t="inlineStr">
+        <is>
+          <t>깁스진단비</t>
+        </is>
+      </c>
+      <c r="C98" s="117" t="n"/>
+      <c r="D98" s="117" t="n"/>
+      <c r="E98" s="117" t="n"/>
+      <c r="F98" s="117" t="n"/>
+      <c r="G98" s="117" t="n"/>
+      <c r="H98" s="117" t="n"/>
+      <c r="I98" s="117" t="n"/>
+      <c r="J98" s="118">
+        <f>SUM(C85:I85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" s="82">
+      <c r="A99" s="150" t="inlineStr">
+        <is>
           <t>실손</t>
         </is>
       </c>
-      <c r="B97" s="95" t="inlineStr">
+      <c r="B99" s="95" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="C97" s="143" t="n"/>
-      <c r="D97" s="143" t="n"/>
-      <c r="E97" s="143" t="n"/>
-      <c r="F97" s="143" t="n"/>
-      <c r="G97" s="143" t="n"/>
-      <c r="H97" s="143" t="n"/>
-      <c r="I97" s="143" t="n"/>
-      <c r="J97" s="120">
+      <c r="C99" s="143" t="n"/>
+      <c r="D99" s="143" t="n"/>
+      <c r="E99" s="143" t="n"/>
+      <c r="F99" s="143" t="n"/>
+      <c r="G99" s="143" t="n"/>
+      <c r="H99" s="143" t="n"/>
+      <c r="I99" s="143" t="n"/>
+      <c r="J99" s="120">
         <f>SUM(C86:I86)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" s="82">
-      <c r="A98" s="149" t="n"/>
-      <c r="B98" s="60" t="inlineStr">
-        <is>
-          <t>통원</t>
-        </is>
-      </c>
-      <c r="C98" s="144" t="n"/>
-      <c r="D98" s="144" t="n"/>
-      <c r="E98" s="144" t="n"/>
-      <c r="F98" s="144" t="n"/>
-      <c r="G98" s="144" t="n"/>
-      <c r="H98" s="144" t="n"/>
-      <c r="I98" s="144" t="n"/>
-      <c r="J98" s="122">
-        <f>SUM(C87:I87)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" s="82">
-      <c r="A99" s="149" t="n"/>
-      <c r="B99" s="22" t="inlineStr">
-        <is>
-          <t>약값</t>
-        </is>
-      </c>
-      <c r="C99" s="115" t="n"/>
-      <c r="D99" s="115" t="n"/>
-      <c r="E99" s="115" t="n"/>
-      <c r="F99" s="115" t="n"/>
-      <c r="G99" s="115" t="n"/>
-      <c r="H99" s="115" t="n"/>
-      <c r="I99" s="145" t="n"/>
-      <c r="J99" s="122">
-        <f>SUM(C88:I88)</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="149" t="n"/>
-      <c r="B100" s="22" t="inlineStr">
-        <is>
-          <t>MRI/도수치료/비급여주사</t>
-        </is>
-      </c>
-      <c r="C100" s="115" t="n"/>
-      <c r="D100" s="115" t="n"/>
-      <c r="E100" s="115" t="n"/>
-      <c r="F100" s="115" t="n"/>
-      <c r="G100" s="115" t="n"/>
-      <c r="H100" s="115" t="n"/>
-      <c r="I100" s="145" t="n"/>
-      <c r="J100" s="122" t="n"/>
+      <c r="B100" s="60" t="inlineStr">
+        <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="C100" s="144" t="n"/>
+      <c r="D100" s="144" t="n"/>
+      <c r="E100" s="144" t="n"/>
+      <c r="F100" s="144" t="n"/>
+      <c r="G100" s="144" t="n"/>
+      <c r="H100" s="144" t="n"/>
+      <c r="I100" s="144" t="n"/>
+      <c r="J100" s="122">
+        <f>SUM(C87:I87)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="151" t="n"/>
+      <c r="A101" s="149" t="n"/>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>상해의료비</t>
+          <t>약값</t>
         </is>
       </c>
       <c r="C101" s="115" t="n"/>
@@ -3388,50 +3385,85 @@
       <c r="G101" s="115" t="n"/>
       <c r="H101" s="115" t="n"/>
       <c r="I101" s="145" t="n"/>
-      <c r="J101" s="122" t="n"/>
+      <c r="J101" s="122">
+        <f>SUM(C88:I88)</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="87" t="inlineStr">
+      <c r="A102" s="149" t="n"/>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>MRI/도수치료/비급여주사</t>
+        </is>
+      </c>
+      <c r="C102" s="115" t="n"/>
+      <c r="D102" s="115" t="n"/>
+      <c r="E102" s="115" t="n"/>
+      <c r="F102" s="115" t="n"/>
+      <c r="G102" s="115" t="n"/>
+      <c r="H102" s="115" t="n"/>
+      <c r="I102" s="145" t="n"/>
+      <c r="J102" s="122" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="151" t="n"/>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>상해의료비</t>
+        </is>
+      </c>
+      <c r="C103" s="115" t="n"/>
+      <c r="D103" s="115" t="n"/>
+      <c r="E103" s="115" t="n"/>
+      <c r="F103" s="115" t="n"/>
+      <c r="G103" s="115" t="n"/>
+      <c r="H103" s="115" t="n"/>
+      <c r="I103" s="145" t="n"/>
+      <c r="J103" s="122" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="87" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B102" s="79" t="inlineStr">
+      <c r="B104" s="79" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C102" s="146" t="n"/>
-      <c r="D102" s="146" t="n"/>
-      <c r="E102" s="146" t="n"/>
-      <c r="F102" s="146" t="n"/>
-      <c r="G102" s="146" t="n"/>
-      <c r="H102" s="146" t="n"/>
-      <c r="I102" s="146" t="n"/>
-      <c r="J102" s="147">
+      <c r="C104" s="146" t="n"/>
+      <c r="D104" s="146" t="n"/>
+      <c r="E104" s="146" t="n"/>
+      <c r="F104" s="146" t="n"/>
+      <c r="G104" s="146" t="n"/>
+      <c r="H104" s="146" t="n"/>
+      <c r="I104" s="146" t="n"/>
+      <c r="J104" s="147">
         <f>SUM(C89:I89)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A65:A83"/>
+    <mergeCell ref="A15:A29"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A6:A10"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A97:A101"/>
-    <mergeCell ref="A93:A94"/>
     <mergeCell ref="A30:A38"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A15:A29"/>
+    <mergeCell ref="A84:A89"/>
     <mergeCell ref="A52:A64"/>
-    <mergeCell ref="A88:A90"/>
     <mergeCell ref="A39:A51"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A65:A81"/>
+    <mergeCell ref="A90:A92"/>
+    <mergeCell ref="A99:A103"/>
     <mergeCell ref="A95:A96"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A82:A87"/>
-    <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>

--- a/master.xlsx
+++ b/master.xlsx
@@ -2491,7 +2491,7 @@
       <c r="A55" s="88" t="n"/>
       <c r="B55" s="65" t="inlineStr">
         <is>
-          <t>상급병원질병입원일당</t>
+          <t>종합병원 상해입원일당</t>
         </is>
       </c>
       <c r="C55" s="136" t="n"/>
@@ -3447,23 +3447,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A30:A38"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A65:A83"/>
+    <mergeCell ref="A84:A89"/>
     <mergeCell ref="A15:A29"/>
+    <mergeCell ref="A52:A64"/>
+    <mergeCell ref="A39:A51"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A90:A92"/>
+    <mergeCell ref="A99:A103"/>
+    <mergeCell ref="A95:A96"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A30:A38"/>
-    <mergeCell ref="A84:A89"/>
-    <mergeCell ref="A52:A64"/>
-    <mergeCell ref="A39:A51"/>
-    <mergeCell ref="A90:A92"/>
-    <mergeCell ref="A99:A103"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>

--- a/master.xlsx
+++ b/master.xlsx
@@ -8,9 +8,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보장분석" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="법칙" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지침케이스" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="해석원칙" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="0" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
@@ -19,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* \-_-;_-@_-"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -116,8 +118,24 @@
       <family val="3"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFC0392B"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -166,8 +184,37 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFCCFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.7999816888943144"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="53">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -607,17 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -785,6 +821,63 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -805,33 +898,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -988,25 +1061,22 @@
     <xf numFmtId="164" fontId="5" fillId="8" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1015,43 +1085,34 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1075,7 +1136,7 @@
     <xf numFmtId="164" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1086,34 +1147,79 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1218,28 +1324,49 @@
     <xf numFmtId="164" fontId="5" fillId="8" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="11" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1257,24 +1384,7 @@
     <xf numFmtId="164" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1282,74 +1392,7 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <colors/>
 </styleSheet>
 </file>
 
@@ -1470,109 +1513,109 @@
   <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
-    <col width="6.5" customWidth="1" style="82" min="1" max="1"/>
-    <col width="17.3984375" customWidth="1" style="82" min="2" max="2"/>
-    <col width="14.5" customWidth="1" style="82" min="3" max="7"/>
-    <col width="16.5" customWidth="1" style="82" min="8" max="8"/>
-    <col width="14.5" customWidth="1" style="82" min="9" max="9"/>
-    <col width="22.8984375" customWidth="1" style="82" min="10" max="10"/>
-    <col width="1.5" customWidth="1" style="82" min="11" max="11"/>
-    <col width="11.3984375" customWidth="1" style="82" min="12" max="18"/>
+    <col width="6.5" customWidth="1" style="78" min="1" max="1"/>
+    <col width="17.3984375" customWidth="1" style="78" min="2" max="2"/>
+    <col width="14.5" customWidth="1" style="78" min="3" max="7"/>
+    <col width="16.5" customWidth="1" style="78" min="8" max="8"/>
+    <col width="14.5" customWidth="1" style="78" min="9" max="9"/>
+    <col width="22.8984375" customWidth="1" style="78" min="10" max="10"/>
+    <col width="1.5" customWidth="1" style="78" min="11" max="11"/>
+    <col width="11.3984375" customWidth="1" style="78" min="12" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38.25" customHeight="1" s="82">
-      <c r="A1" s="90" t="n"/>
-      <c r="B1" s="91" t="n"/>
-      <c r="C1" s="100" t="n"/>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="100" t="n"/>
-      <c r="G1" s="100" t="n"/>
-      <c r="H1" s="100" t="n"/>
-      <c r="I1" s="101" t="n"/>
+    <row r="1" ht="38.25" customHeight="1" s="78">
+      <c r="A1" s="98" t="n"/>
+      <c r="B1" s="99" t="n"/>
+      <c r="C1" s="115" t="n"/>
+      <c r="D1" s="115" t="n"/>
+      <c r="E1" s="115" t="n"/>
+      <c r="F1" s="115" t="n"/>
+      <c r="G1" s="115" t="n"/>
+      <c r="H1" s="115" t="n"/>
+      <c r="I1" s="116" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="82">
-      <c r="A2" s="95" t="inlineStr">
+    <row r="2" ht="16.5" customHeight="1" s="78">
+      <c r="A2" s="90" t="inlineStr">
         <is>
           <t>보험료</t>
         </is>
       </c>
-      <c r="B2" s="96" t="n"/>
-      <c r="C2" s="102" t="n"/>
-      <c r="D2" s="102" t="n"/>
-      <c r="E2" s="102" t="n"/>
-      <c r="F2" s="102" t="n"/>
-      <c r="G2" s="102" t="n"/>
-      <c r="H2" s="102" t="n"/>
-      <c r="I2" s="102" t="n"/>
-      <c r="J2" s="103">
+      <c r="B2" s="91" t="n"/>
+      <c r="C2" s="117" t="n"/>
+      <c r="D2" s="117" t="n"/>
+      <c r="E2" s="117" t="n"/>
+      <c r="F2" s="117" t="n"/>
+      <c r="G2" s="117" t="n"/>
+      <c r="H2" s="117" t="n"/>
+      <c r="I2" s="117" t="n"/>
+      <c r="J2" s="118">
         <f>SUM(C2:I2)</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="82">
-      <c r="A3" s="93" t="inlineStr">
+    <row r="3" ht="16.5" customHeight="1" s="78">
+      <c r="A3" s="85" t="inlineStr">
         <is>
           <t>가입년일</t>
         </is>
       </c>
-      <c r="B3" s="94" t="n"/>
-      <c r="C3" s="104" t="n"/>
-      <c r="D3" s="104" t="n"/>
-      <c r="E3" s="104" t="n"/>
-      <c r="F3" s="104" t="n"/>
-      <c r="G3" s="104" t="n"/>
-      <c r="H3" s="104" t="n"/>
-      <c r="I3" s="104" t="n"/>
-      <c r="J3" s="105">
+      <c r="B3" s="86" t="n"/>
+      <c r="C3" s="119" t="n"/>
+      <c r="D3" s="119" t="n"/>
+      <c r="E3" s="119" t="n"/>
+      <c r="F3" s="119" t="n"/>
+      <c r="G3" s="119" t="n"/>
+      <c r="H3" s="119" t="n"/>
+      <c r="I3" s="119" t="n"/>
+      <c r="J3" s="120">
         <f>SUM(C3:I3)</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="82">
-      <c r="A4" s="93" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="78">
+      <c r="A4" s="85" t="inlineStr">
         <is>
           <t>만기일자</t>
         </is>
       </c>
-      <c r="B4" s="94" t="n"/>
-      <c r="C4" s="106" t="n"/>
-      <c r="D4" s="106" t="n"/>
-      <c r="E4" s="106" t="n"/>
-      <c r="F4" s="106" t="n"/>
-      <c r="G4" s="106" t="n"/>
-      <c r="H4" s="106" t="n"/>
-      <c r="I4" s="106" t="n"/>
-      <c r="J4" s="105">
+      <c r="B4" s="86" t="n"/>
+      <c r="C4" s="121" t="n"/>
+      <c r="D4" s="121" t="n"/>
+      <c r="E4" s="121" t="n"/>
+      <c r="F4" s="121" t="n"/>
+      <c r="G4" s="121" t="n"/>
+      <c r="H4" s="121" t="n"/>
+      <c r="I4" s="121" t="n"/>
+      <c r="J4" s="120">
         <f>SUM(C4:I4)</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1" s="82">
-      <c r="A5" s="97" t="inlineStr">
+    <row r="5" ht="17.25" customHeight="1" s="78">
+      <c r="A5" s="96" t="inlineStr">
         <is>
           <t>총납입기간</t>
         </is>
       </c>
-      <c r="B5" s="98" t="n"/>
-      <c r="C5" s="107" t="n"/>
-      <c r="D5" s="107" t="n"/>
-      <c r="E5" s="107" t="n"/>
-      <c r="F5" s="107" t="n"/>
-      <c r="G5" s="107" t="n"/>
-      <c r="H5" s="107" t="n"/>
-      <c r="I5" s="107" t="n"/>
-      <c r="J5" s="108">
+      <c r="B5" s="97" t="n"/>
+      <c r="C5" s="122" t="n"/>
+      <c r="D5" s="122" t="n"/>
+      <c r="E5" s="122" t="n"/>
+      <c r="F5" s="122" t="n"/>
+      <c r="G5" s="122" t="n"/>
+      <c r="H5" s="122" t="n"/>
+      <c r="I5" s="122" t="n"/>
+      <c r="J5" s="123">
         <f>SUM(C5:I5)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="82">
+    <row r="6" ht="16.5" customHeight="1" s="78">
       <c r="A6" s="87" t="inlineStr">
         <is>
           <t>사망</t>
@@ -1583,95 +1626,95 @@
           <t>일반사망</t>
         </is>
       </c>
-      <c r="C6" s="109" t="n"/>
-      <c r="D6" s="109" t="n"/>
-      <c r="E6" s="109" t="n"/>
-      <c r="F6" s="109" t="n"/>
-      <c r="G6" s="109" t="n"/>
-      <c r="H6" s="109" t="n"/>
-      <c r="I6" s="109" t="n"/>
-      <c r="J6" s="110">
+      <c r="C6" s="124" t="n"/>
+      <c r="D6" s="124" t="n"/>
+      <c r="E6" s="124" t="n"/>
+      <c r="F6" s="124" t="n"/>
+      <c r="G6" s="124" t="n"/>
+      <c r="H6" s="124" t="n"/>
+      <c r="I6" s="124" t="n"/>
+      <c r="J6" s="125">
         <f>SUM(C6:I6)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="82">
+    <row r="7" ht="17.25" customHeight="1" s="78">
       <c r="A7" s="88" t="n"/>
       <c r="B7" s="16" t="inlineStr">
         <is>
           <t>중대한CI적용</t>
         </is>
       </c>
-      <c r="C7" s="111" t="n"/>
-      <c r="D7" s="111" t="n"/>
-      <c r="E7" s="111" t="n"/>
-      <c r="F7" s="111" t="n"/>
-      <c r="G7" s="111" t="n"/>
-      <c r="H7" s="111" t="n"/>
-      <c r="I7" s="111" t="n"/>
-      <c r="J7" s="112">
+      <c r="C7" s="126" t="n"/>
+      <c r="D7" s="126" t="n"/>
+      <c r="E7" s="126" t="n"/>
+      <c r="F7" s="126" t="n"/>
+      <c r="G7" s="126" t="n"/>
+      <c r="H7" s="126" t="n"/>
+      <c r="I7" s="126" t="n"/>
+      <c r="J7" s="127">
         <f>SUM(C7:I7)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1" s="82">
+    <row r="8" ht="17.25" customHeight="1" s="78">
       <c r="A8" s="88" t="n"/>
       <c r="B8" s="19" t="inlineStr">
         <is>
           <t>질병사망(80세)</t>
         </is>
       </c>
-      <c r="C8" s="113" t="n"/>
-      <c r="D8" s="113" t="n"/>
-      <c r="E8" s="113" t="n"/>
-      <c r="F8" s="113" t="n"/>
-      <c r="G8" s="113" t="n"/>
-      <c r="H8" s="113" t="n"/>
-      <c r="I8" s="113" t="n"/>
-      <c r="J8" s="114">
+      <c r="C8" s="128" t="n"/>
+      <c r="D8" s="128" t="n"/>
+      <c r="E8" s="128" t="n"/>
+      <c r="F8" s="128" t="n"/>
+      <c r="G8" s="128" t="n"/>
+      <c r="H8" s="128" t="n"/>
+      <c r="I8" s="128" t="n"/>
+      <c r="J8" s="129">
         <f>SUM(C8:I8)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="82">
+    <row r="9" ht="16.5" customHeight="1" s="78">
       <c r="A9" s="88" t="n"/>
       <c r="B9" s="22" t="inlineStr">
         <is>
           <t>교통상해사망</t>
         </is>
       </c>
-      <c r="C9" s="115" t="n"/>
-      <c r="D9" s="115" t="n"/>
-      <c r="E9" s="115" t="n"/>
-      <c r="F9" s="115" t="n"/>
-      <c r="G9" s="115" t="n"/>
-      <c r="H9" s="115" t="n"/>
-      <c r="I9" s="115" t="n"/>
-      <c r="J9" s="116">
+      <c r="C9" s="130" t="n"/>
+      <c r="D9" s="130" t="n"/>
+      <c r="E9" s="130" t="n"/>
+      <c r="F9" s="130" t="n"/>
+      <c r="G9" s="130" t="n"/>
+      <c r="H9" s="130" t="n"/>
+      <c r="I9" s="130" t="n"/>
+      <c r="J9" s="131">
         <f>SUM(C9:I9)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1" s="82">
+    <row r="10" ht="17.25" customHeight="1" s="78">
       <c r="A10" s="89" t="n"/>
       <c r="B10" s="25" t="inlineStr">
         <is>
           <t>상해사망</t>
         </is>
       </c>
-      <c r="C10" s="117" t="n"/>
-      <c r="D10" s="117" t="n"/>
-      <c r="E10" s="117" t="n"/>
-      <c r="F10" s="117" t="n"/>
-      <c r="G10" s="117" t="n"/>
-      <c r="H10" s="117" t="n"/>
-      <c r="I10" s="117" t="n"/>
-      <c r="J10" s="118">
+      <c r="C10" s="132" t="n"/>
+      <c r="D10" s="132" t="n"/>
+      <c r="E10" s="132" t="n"/>
+      <c r="F10" s="132" t="n"/>
+      <c r="G10" s="132" t="n"/>
+      <c r="H10" s="132" t="n"/>
+      <c r="I10" s="132" t="n"/>
+      <c r="J10" s="133">
         <f>SUM(C10:I10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="82">
+    <row r="11" ht="16.5" customHeight="1" s="78">
       <c r="A11" s="87" t="inlineStr">
         <is>
           <t>후유장애</t>
@@ -1682,76 +1725,76 @@
           <t>상해후유3%</t>
         </is>
       </c>
-      <c r="C11" s="119" t="n"/>
-      <c r="D11" s="119" t="n"/>
-      <c r="E11" s="119" t="n"/>
-      <c r="F11" s="119" t="n"/>
-      <c r="G11" s="119" t="n"/>
-      <c r="H11" s="119" t="n"/>
-      <c r="I11" s="119" t="n"/>
-      <c r="J11" s="120">
+      <c r="C11" s="134" t="n"/>
+      <c r="D11" s="134" t="n"/>
+      <c r="E11" s="134" t="n"/>
+      <c r="F11" s="134" t="n"/>
+      <c r="G11" s="134" t="n"/>
+      <c r="H11" s="134" t="n"/>
+      <c r="I11" s="134" t="n"/>
+      <c r="J11" s="135">
         <f>SUM(C11:I11)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="82">
+    <row r="12" ht="16.5" customHeight="1" s="78">
       <c r="A12" s="88" t="n"/>
       <c r="B12" s="31" t="inlineStr">
         <is>
           <t>상해후유80%</t>
         </is>
       </c>
-      <c r="C12" s="121" t="n"/>
-      <c r="D12" s="121" t="n"/>
-      <c r="E12" s="121" t="n"/>
-      <c r="F12" s="121" t="n"/>
-      <c r="G12" s="121" t="n"/>
-      <c r="H12" s="121" t="n"/>
-      <c r="I12" s="121" t="n"/>
-      <c r="J12" s="122">
+      <c r="C12" s="136" t="n"/>
+      <c r="D12" s="136" t="n"/>
+      <c r="E12" s="136" t="n"/>
+      <c r="F12" s="136" t="n"/>
+      <c r="G12" s="136" t="n"/>
+      <c r="H12" s="136" t="n"/>
+      <c r="I12" s="136" t="n"/>
+      <c r="J12" s="137">
         <f>SUM(C12:I12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="82">
+    <row r="13" ht="16.5" customHeight="1" s="78">
       <c r="A13" s="88" t="n"/>
       <c r="B13" s="31" t="inlineStr">
         <is>
           <t>질병후유3%</t>
         </is>
       </c>
-      <c r="C13" s="121" t="n"/>
-      <c r="D13" s="121" t="n"/>
-      <c r="E13" s="121" t="n"/>
-      <c r="F13" s="121" t="n"/>
-      <c r="G13" s="121" t="n"/>
-      <c r="H13" s="121" t="n"/>
-      <c r="I13" s="121" t="n"/>
-      <c r="J13" s="122">
+      <c r="C13" s="136" t="n"/>
+      <c r="D13" s="136" t="n"/>
+      <c r="E13" s="136" t="n"/>
+      <c r="F13" s="136" t="n"/>
+      <c r="G13" s="136" t="n"/>
+      <c r="H13" s="136" t="n"/>
+      <c r="I13" s="136" t="n"/>
+      <c r="J13" s="137">
         <f>SUM(C13:I13)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1" s="82">
+    <row r="14" ht="17.25" customHeight="1" s="78">
       <c r="A14" s="89" t="n"/>
       <c r="B14" s="25" t="inlineStr">
         <is>
           <t>질병후유80%</t>
         </is>
       </c>
-      <c r="C14" s="117" t="n"/>
-      <c r="D14" s="117" t="n"/>
-      <c r="E14" s="117" t="n"/>
-      <c r="F14" s="117" t="n"/>
-      <c r="G14" s="117" t="n"/>
-      <c r="H14" s="117" t="n"/>
-      <c r="I14" s="117" t="n"/>
-      <c r="J14" s="122">
+      <c r="C14" s="132" t="n"/>
+      <c r="D14" s="132" t="n"/>
+      <c r="E14" s="132" t="n"/>
+      <c r="F14" s="132" t="n"/>
+      <c r="G14" s="132" t="n"/>
+      <c r="H14" s="132" t="n"/>
+      <c r="I14" s="132" t="n"/>
+      <c r="J14" s="137">
         <f>SUM(C14:I14)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1" s="82">
+    <row r="15" ht="17.25" customHeight="1" s="78">
       <c r="A15" s="87" t="inlineStr">
         <is>
           <t>암</t>
@@ -1762,276 +1805,276 @@
           <t>고액암</t>
         </is>
       </c>
-      <c r="C15" s="123" t="n"/>
-      <c r="D15" s="123" t="n"/>
-      <c r="E15" s="123" t="n"/>
-      <c r="F15" s="123" t="n"/>
-      <c r="G15" s="123" t="n"/>
-      <c r="H15" s="123" t="n"/>
-      <c r="I15" s="123" t="n"/>
-      <c r="J15" s="124">
+      <c r="C15" s="138" t="n"/>
+      <c r="D15" s="138" t="n"/>
+      <c r="E15" s="138" t="n"/>
+      <c r="F15" s="138" t="n"/>
+      <c r="G15" s="138" t="n"/>
+      <c r="H15" s="138" t="n"/>
+      <c r="I15" s="138" t="n"/>
+      <c r="J15" s="139">
         <f>SUM(C15:I15)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="82">
+    <row r="16" ht="16.5" customHeight="1" s="78">
       <c r="A16" s="88" t="n"/>
       <c r="B16" s="13" t="inlineStr">
         <is>
           <t>일반암</t>
         </is>
       </c>
-      <c r="C16" s="125" t="n"/>
-      <c r="D16" s="125" t="n"/>
-      <c r="E16" s="125" t="n"/>
-      <c r="F16" s="125" t="n"/>
-      <c r="G16" s="125" t="n"/>
-      <c r="H16" s="125" t="n"/>
-      <c r="I16" s="125" t="n"/>
-      <c r="J16" s="110">
+      <c r="C16" s="140" t="n"/>
+      <c r="D16" s="140" t="n"/>
+      <c r="E16" s="140" t="n"/>
+      <c r="F16" s="140" t="n"/>
+      <c r="G16" s="140" t="n"/>
+      <c r="H16" s="140" t="n"/>
+      <c r="I16" s="140" t="n"/>
+      <c r="J16" s="125">
         <f>SUM(C16:I16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="17.25" customHeight="1" s="82">
+    <row r="17" ht="17.25" customHeight="1" s="78">
       <c r="A17" s="88" t="n"/>
       <c r="B17" s="38" t="inlineStr">
         <is>
           <t>중대한 암</t>
         </is>
       </c>
-      <c r="C17" s="126" t="n"/>
-      <c r="D17" s="126" t="n"/>
-      <c r="E17" s="126" t="n"/>
-      <c r="F17" s="126" t="n"/>
-      <c r="G17" s="126" t="n"/>
-      <c r="H17" s="126" t="n"/>
-      <c r="I17" s="126" t="n"/>
-      <c r="J17" s="112">
+      <c r="C17" s="141" t="n"/>
+      <c r="D17" s="141" t="n"/>
+      <c r="E17" s="141" t="n"/>
+      <c r="F17" s="141" t="n"/>
+      <c r="G17" s="141" t="n"/>
+      <c r="H17" s="141" t="n"/>
+      <c r="I17" s="141" t="n"/>
+      <c r="J17" s="127">
         <f>SUM(C17:I17)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1" s="82">
+    <row r="18" ht="16.5" customHeight="1" s="78">
       <c r="A18" s="88" t="n"/>
       <c r="B18" s="40" t="inlineStr">
         <is>
           <t>유사암(갑.기.경.제)</t>
         </is>
       </c>
-      <c r="C18" s="127" t="n"/>
-      <c r="D18" s="127" t="n"/>
-      <c r="E18" s="127" t="n"/>
-      <c r="F18" s="127" t="n"/>
-      <c r="G18" s="127" t="n"/>
-      <c r="H18" s="127" t="n"/>
-      <c r="I18" s="127" t="n"/>
-      <c r="J18" s="116">
+      <c r="C18" s="142" t="n"/>
+      <c r="D18" s="142" t="n"/>
+      <c r="E18" s="142" t="n"/>
+      <c r="F18" s="142" t="n"/>
+      <c r="G18" s="142" t="n"/>
+      <c r="H18" s="142" t="n"/>
+      <c r="I18" s="142" t="n"/>
+      <c r="J18" s="131">
         <f>SUM(C18:I18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="82">
+    <row r="19" ht="16.5" customHeight="1" s="78">
       <c r="A19" s="88" t="n"/>
       <c r="B19" s="40" t="inlineStr">
         <is>
           <t>통합전이암</t>
         </is>
       </c>
-      <c r="C19" s="127" t="n"/>
-      <c r="D19" s="127" t="n"/>
-      <c r="E19" s="127" t="n"/>
-      <c r="F19" s="127" t="n"/>
-      <c r="G19" s="127" t="n"/>
-      <c r="H19" s="127" t="n"/>
-      <c r="I19" s="127" t="n"/>
-      <c r="J19" s="116" t="n"/>
-    </row>
-    <row r="20" ht="16.5" customHeight="1" s="82">
+      <c r="C19" s="142" t="n"/>
+      <c r="D19" s="142" t="n"/>
+      <c r="E19" s="142" t="n"/>
+      <c r="F19" s="142" t="n"/>
+      <c r="G19" s="142" t="n"/>
+      <c r="H19" s="142" t="n"/>
+      <c r="I19" s="142" t="n"/>
+      <c r="J19" s="131" t="n"/>
+    </row>
+    <row r="20" ht="16.5" customHeight="1" s="78">
       <c r="A20" s="88" t="n"/>
       <c r="B20" s="42" t="inlineStr">
         <is>
           <t>암주요치료비</t>
         </is>
       </c>
-      <c r="C20" s="128" t="n"/>
-      <c r="D20" s="128" t="n"/>
-      <c r="E20" s="128" t="n"/>
-      <c r="F20" s="128" t="n"/>
-      <c r="G20" s="128" t="n"/>
-      <c r="H20" s="128" t="n"/>
-      <c r="I20" s="127" t="n"/>
-      <c r="J20" s="116" t="n"/>
-    </row>
-    <row r="21" ht="16.5" customHeight="1" s="82">
+      <c r="C20" s="143" t="n"/>
+      <c r="D20" s="143" t="n"/>
+      <c r="E20" s="143" t="n"/>
+      <c r="F20" s="143" t="n"/>
+      <c r="G20" s="143" t="n"/>
+      <c r="H20" s="143" t="n"/>
+      <c r="I20" s="142" t="n"/>
+      <c r="J20" s="131" t="n"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1" s="78">
       <c r="A21" s="88" t="n"/>
       <c r="B21" s="42" t="inlineStr">
         <is>
           <t>하이클래스(암)</t>
         </is>
       </c>
-      <c r="C21" s="127" t="n"/>
-      <c r="D21" s="127" t="n"/>
-      <c r="E21" s="127" t="n"/>
-      <c r="F21" s="127" t="n"/>
-      <c r="G21" s="127" t="n"/>
-      <c r="H21" s="127" t="n"/>
-      <c r="I21" s="127" t="n"/>
-      <c r="J21" s="122">
+      <c r="C21" s="142" t="n"/>
+      <c r="D21" s="142" t="n"/>
+      <c r="E21" s="142" t="n"/>
+      <c r="F21" s="142" t="n"/>
+      <c r="G21" s="142" t="n"/>
+      <c r="H21" s="142" t="n"/>
+      <c r="I21" s="142" t="n"/>
+      <c r="J21" s="137">
         <f>SUM(C20:I20)</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" s="82">
+    <row r="22" ht="16.5" customHeight="1" s="78">
       <c r="A22" s="88" t="n"/>
       <c r="B22" s="42" t="inlineStr">
         <is>
           <t>중입자치료비</t>
         </is>
       </c>
-      <c r="C22" s="128" t="n"/>
-      <c r="D22" s="128" t="n"/>
-      <c r="E22" s="128" t="n"/>
-      <c r="F22" s="128" t="n"/>
-      <c r="G22" s="128" t="n"/>
-      <c r="H22" s="128" t="n"/>
-      <c r="I22" s="127" t="n"/>
-      <c r="J22" s="116">
+      <c r="C22" s="143" t="n"/>
+      <c r="D22" s="143" t="n"/>
+      <c r="E22" s="143" t="n"/>
+      <c r="F22" s="143" t="n"/>
+      <c r="G22" s="143" t="n"/>
+      <c r="H22" s="143" t="n"/>
+      <c r="I22" s="142" t="n"/>
+      <c r="J22" s="131">
         <f>SUM(C21:I21)</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1" s="82">
+    <row r="23" ht="16.5" customHeight="1" s="78">
       <c r="A23" s="88" t="n"/>
       <c r="B23" s="42" t="inlineStr">
         <is>
           <t>표적항암치료비</t>
         </is>
       </c>
-      <c r="C23" s="128" t="n"/>
-      <c r="D23" s="128" t="n"/>
-      <c r="E23" s="128" t="n"/>
-      <c r="F23" s="128" t="n"/>
-      <c r="G23" s="128" t="n"/>
-      <c r="H23" s="128" t="n"/>
-      <c r="I23" s="127" t="n"/>
-      <c r="J23" s="116" t="n"/>
-    </row>
-    <row r="24" ht="16.5" customHeight="1" s="82">
+      <c r="C23" s="143" t="n"/>
+      <c r="D23" s="143" t="n"/>
+      <c r="E23" s="143" t="n"/>
+      <c r="F23" s="143" t="n"/>
+      <c r="G23" s="143" t="n"/>
+      <c r="H23" s="143" t="n"/>
+      <c r="I23" s="142" t="n"/>
+      <c r="J23" s="131" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="78">
       <c r="A24" s="88" t="n"/>
       <c r="B24" s="44" t="inlineStr">
         <is>
           <t>양성자치료</t>
         </is>
       </c>
-      <c r="C24" s="129" t="n"/>
-      <c r="D24" s="129" t="n"/>
-      <c r="E24" s="129" t="n"/>
-      <c r="F24" s="129" t="n"/>
-      <c r="G24" s="129" t="n"/>
-      <c r="H24" s="129" t="n"/>
-      <c r="I24" s="130" t="n"/>
-      <c r="J24" s="122">
+      <c r="C24" s="144" t="n"/>
+      <c r="D24" s="144" t="n"/>
+      <c r="E24" s="144" t="n"/>
+      <c r="F24" s="144" t="n"/>
+      <c r="G24" s="144" t="n"/>
+      <c r="H24" s="144" t="n"/>
+      <c r="I24" s="145" t="n"/>
+      <c r="J24" s="137">
         <f>SUM(C23:I23)</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="82">
+    <row r="25" ht="16.5" customHeight="1" s="78">
       <c r="A25" s="88" t="n"/>
       <c r="B25" s="44" t="inlineStr">
         <is>
           <t>세기조절치료</t>
         </is>
       </c>
-      <c r="C25" s="129" t="n"/>
-      <c r="D25" s="129" t="n"/>
-      <c r="E25" s="129" t="n"/>
-      <c r="F25" s="129" t="n"/>
-      <c r="G25" s="129" t="n"/>
-      <c r="H25" s="129" t="n"/>
-      <c r="I25" s="130" t="n"/>
-      <c r="J25" s="122">
+      <c r="C25" s="144" t="n"/>
+      <c r="D25" s="144" t="n"/>
+      <c r="E25" s="144" t="n"/>
+      <c r="F25" s="144" t="n"/>
+      <c r="G25" s="144" t="n"/>
+      <c r="H25" s="144" t="n"/>
+      <c r="I25" s="145" t="n"/>
+      <c r="J25" s="137">
         <f>SUM(C24:I24)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1" s="82">
+    <row r="26" ht="16.5" customHeight="1" s="78">
       <c r="A26" s="88" t="n"/>
       <c r="B26" s="44" t="inlineStr">
         <is>
           <t>다빈치로봇수술비</t>
         </is>
       </c>
-      <c r="C26" s="129" t="n"/>
-      <c r="D26" s="129" t="n"/>
-      <c r="E26" s="129" t="n"/>
-      <c r="F26" s="129" t="n"/>
-      <c r="G26" s="129" t="n"/>
-      <c r="H26" s="129" t="n"/>
-      <c r="I26" s="130" t="n"/>
-      <c r="J26" s="122">
+      <c r="C26" s="144" t="n"/>
+      <c r="D26" s="144" t="n"/>
+      <c r="E26" s="144" t="n"/>
+      <c r="F26" s="144" t="n"/>
+      <c r="G26" s="144" t="n"/>
+      <c r="H26" s="144" t="n"/>
+      <c r="I26" s="145" t="n"/>
+      <c r="J26" s="137">
         <f>SUM(C25:I25)</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="82">
+    <row r="27" ht="16.5" customHeight="1" s="78">
       <c r="A27" s="88" t="n"/>
       <c r="B27" s="44" t="inlineStr">
         <is>
           <t>암수술</t>
         </is>
       </c>
-      <c r="C27" s="130" t="n"/>
-      <c r="D27" s="130" t="n"/>
-      <c r="E27" s="130" t="n"/>
-      <c r="F27" s="130" t="n"/>
-      <c r="G27" s="130" t="n"/>
-      <c r="H27" s="130" t="n"/>
-      <c r="I27" s="130" t="n"/>
-      <c r="J27" s="122">
+      <c r="C27" s="145" t="n"/>
+      <c r="D27" s="145" t="n"/>
+      <c r="E27" s="145" t="n"/>
+      <c r="F27" s="145" t="n"/>
+      <c r="G27" s="145" t="n"/>
+      <c r="H27" s="145" t="n"/>
+      <c r="I27" s="145" t="n"/>
+      <c r="J27" s="137">
         <f>SUM(C26:I26)</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1" s="82">
+    <row r="28" ht="17.25" customHeight="1" s="78">
       <c r="A28" s="88" t="n"/>
       <c r="B28" s="31" t="inlineStr">
         <is>
           <t>암일당</t>
         </is>
       </c>
-      <c r="C28" s="121" t="n"/>
-      <c r="D28" s="121" t="n"/>
-      <c r="E28" s="121" t="n"/>
-      <c r="F28" s="121" t="n"/>
-      <c r="G28" s="121" t="n"/>
-      <c r="H28" s="121" t="n"/>
-      <c r="I28" s="121" t="n"/>
-      <c r="J28" s="122">
+      <c r="C28" s="136" t="n"/>
+      <c r="D28" s="136" t="n"/>
+      <c r="E28" s="136" t="n"/>
+      <c r="F28" s="136" t="n"/>
+      <c r="G28" s="136" t="n"/>
+      <c r="H28" s="136" t="n"/>
+      <c r="I28" s="136" t="n"/>
+      <c r="J28" s="137">
         <f>SUM(C27:I27)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="17.25" customHeight="1" s="82">
+    <row r="29" ht="17.25" customHeight="1" s="78">
       <c r="A29" s="89" t="n"/>
       <c r="B29" s="25" t="inlineStr">
         <is>
           <t>항암방사선약물</t>
         </is>
       </c>
-      <c r="C29" s="117" t="n"/>
-      <c r="D29" s="117" t="n"/>
-      <c r="E29" s="117" t="n"/>
-      <c r="F29" s="117" t="n"/>
-      <c r="G29" s="117" t="n"/>
-      <c r="H29" s="117" t="n"/>
-      <c r="I29" s="117" t="n"/>
-      <c r="J29" s="118">
+      <c r="C29" s="132" t="n"/>
+      <c r="D29" s="132" t="n"/>
+      <c r="E29" s="132" t="n"/>
+      <c r="F29" s="132" t="n"/>
+      <c r="G29" s="132" t="n"/>
+      <c r="H29" s="132" t="n"/>
+      <c r="I29" s="132" t="n"/>
+      <c r="J29" s="133">
         <f>SUM(C28:I28)</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" s="82">
+    <row r="30" ht="16.5" customHeight="1" s="78">
       <c r="A30" s="87" t="inlineStr">
         <is>
           <t>뇌혈관</t>
@@ -2042,989 +2085,1008 @@
           <t>뇌혈관진단비</t>
         </is>
       </c>
-      <c r="C30" s="123" t="n"/>
-      <c r="D30" s="123" t="n"/>
-      <c r="E30" s="123" t="n"/>
-      <c r="F30" s="123" t="n"/>
-      <c r="G30" s="123" t="n"/>
-      <c r="H30" s="123" t="n"/>
-      <c r="I30" s="123" t="n"/>
-      <c r="J30" s="124">
+      <c r="C30" s="138" t="n"/>
+      <c r="D30" s="138" t="n"/>
+      <c r="E30" s="138" t="n"/>
+      <c r="F30" s="138" t="n"/>
+      <c r="G30" s="138" t="n"/>
+      <c r="H30" s="138" t="n"/>
+      <c r="I30" s="138" t="n"/>
+      <c r="J30" s="139">
         <f>SUM(C29:I29)</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="17.25" customHeight="1" s="82">
+    <row r="31" ht="17.25" customHeight="1" s="78">
       <c r="A31" s="88" t="n"/>
       <c r="B31" s="47" t="inlineStr">
         <is>
           <t>뇌졸증진단비</t>
         </is>
       </c>
-      <c r="C31" s="131" t="n"/>
-      <c r="D31" s="131" t="n"/>
-      <c r="E31" s="131" t="n"/>
-      <c r="F31" s="131" t="n"/>
-      <c r="G31" s="131" t="n"/>
-      <c r="H31" s="131" t="n"/>
-      <c r="I31" s="131" t="n"/>
-      <c r="J31" s="132">
+      <c r="C31" s="146" t="n"/>
+      <c r="D31" s="146" t="n"/>
+      <c r="E31" s="146" t="n"/>
+      <c r="F31" s="146" t="n"/>
+      <c r="G31" s="146" t="n"/>
+      <c r="H31" s="146" t="n"/>
+      <c r="I31" s="146" t="n"/>
+      <c r="J31" s="147">
         <f>SUM(C30:I30)</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="82">
+    <row r="32" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A32" s="88" t="n"/>
       <c r="B32" s="50" t="inlineStr">
         <is>
           <t>중대한 뇌졸증</t>
         </is>
       </c>
-      <c r="C32" s="126" t="n"/>
-      <c r="D32" s="126" t="n"/>
-      <c r="E32" s="126" t="n"/>
-      <c r="F32" s="126" t="n"/>
-      <c r="G32" s="126" t="n"/>
-      <c r="H32" s="126" t="n"/>
-      <c r="I32" s="126" t="n"/>
-      <c r="J32" s="133">
+      <c r="C32" s="141" t="n"/>
+      <c r="D32" s="141" t="n"/>
+      <c r="E32" s="141" t="n"/>
+      <c r="F32" s="141" t="n"/>
+      <c r="G32" s="141" t="n"/>
+      <c r="H32" s="141" t="n"/>
+      <c r="I32" s="141" t="n"/>
+      <c r="J32" s="148">
         <f>SUM(C31:I31)</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" s="82">
+    <row r="33" ht="16.5" customHeight="1" s="78">
       <c r="A33" s="88" t="n"/>
-      <c r="B33" s="152" t="inlineStr">
+      <c r="B33" s="109" t="inlineStr">
         <is>
           <t>뇌출혈진단비</t>
         </is>
       </c>
-      <c r="C33" s="153" t="n"/>
-      <c r="D33" s="153" t="n"/>
-      <c r="E33" s="153" t="n"/>
-      <c r="F33" s="153" t="n"/>
-      <c r="G33" s="153" t="n"/>
-      <c r="H33" s="153" t="n"/>
-      <c r="I33" s="153" t="n"/>
-      <c r="J33" s="154">
+      <c r="C33" s="149" t="n"/>
+      <c r="D33" s="149" t="n"/>
+      <c r="E33" s="149" t="n"/>
+      <c r="F33" s="149" t="n"/>
+      <c r="G33" s="149" t="n"/>
+      <c r="H33" s="149" t="n"/>
+      <c r="I33" s="149" t="n"/>
+      <c r="J33" s="150">
         <f>SUM(C32:I32)</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="82">
+    <row r="34" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A34" s="88" t="n"/>
-      <c r="B34" s="152" t="inlineStr">
+      <c r="B34" s="112" t="inlineStr">
         <is>
           <t>중대한 뇌출혈</t>
         </is>
       </c>
-      <c r="C34" s="153" t="n"/>
-      <c r="D34" s="153" t="n"/>
-      <c r="E34" s="153" t="n"/>
-      <c r="F34" s="153" t="n"/>
-      <c r="G34" s="153" t="n"/>
-      <c r="H34" s="153" t="n"/>
-      <c r="I34" s="153" t="n"/>
-      <c r="J34" s="154" t="n"/>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" s="82">
+      <c r="C34" s="151" t="n"/>
+      <c r="D34" s="151" t="n"/>
+      <c r="E34" s="151" t="n"/>
+      <c r="F34" s="151" t="n"/>
+      <c r="G34" s="151" t="n"/>
+      <c r="H34" s="151" t="n"/>
+      <c r="I34" s="151" t="n"/>
+      <c r="J34" s="152">
+        <f>SUM(C33:I33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" s="78">
       <c r="A35" s="88" t="n"/>
-      <c r="B35" s="53" t="inlineStr">
+      <c r="B35" s="52" t="inlineStr">
         <is>
           <t>외상성뇌출혈</t>
         </is>
       </c>
-      <c r="C35" s="134" t="n"/>
-      <c r="D35" s="134" t="n"/>
-      <c r="E35" s="134" t="n"/>
-      <c r="F35" s="134" t="n"/>
-      <c r="G35" s="134" t="n"/>
-      <c r="H35" s="134" t="n"/>
-      <c r="I35" s="134" t="n"/>
-      <c r="J35" s="116">
+      <c r="C35" s="153" t="n"/>
+      <c r="D35" s="153" t="n"/>
+      <c r="E35" s="153" t="n"/>
+      <c r="F35" s="153" t="n"/>
+      <c r="G35" s="153" t="n"/>
+      <c r="H35" s="153" t="n"/>
+      <c r="I35" s="153" t="n"/>
+      <c r="J35" s="131">
         <f>SUM(C33:I33)</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="82">
+    <row r="36" ht="16.5" customHeight="1" s="78">
       <c r="A36" s="88" t="n"/>
-      <c r="B36" s="55" t="inlineStr">
+      <c r="B36" s="54" t="inlineStr">
         <is>
           <t>산정특례뇌혈관</t>
         </is>
       </c>
-      <c r="C36" s="135" t="n"/>
-      <c r="D36" s="135" t="n"/>
-      <c r="E36" s="135" t="n"/>
-      <c r="F36" s="135" t="n"/>
-      <c r="G36" s="135" t="n"/>
-      <c r="H36" s="135" t="n"/>
-      <c r="I36" s="135" t="n"/>
-      <c r="J36" s="122">
+      <c r="C36" s="154" t="n"/>
+      <c r="D36" s="154" t="n"/>
+      <c r="E36" s="154" t="n"/>
+      <c r="F36" s="154" t="n"/>
+      <c r="G36" s="154" t="n"/>
+      <c r="H36" s="154" t="n"/>
+      <c r="I36" s="154" t="n"/>
+      <c r="J36" s="137">
         <f>SUM(C34:I34)</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="82">
+    <row r="37" ht="16.5" customHeight="1" s="78">
       <c r="A37" s="88" t="n"/>
-      <c r="B37" s="55" t="inlineStr">
+      <c r="B37" s="54" t="inlineStr">
         <is>
           <t>2대 주요치료비</t>
         </is>
       </c>
-      <c r="C37" s="135" t="n"/>
-      <c r="D37" s="135" t="n"/>
-      <c r="E37" s="135" t="n"/>
-      <c r="F37" s="135" t="n"/>
-      <c r="G37" s="135" t="n"/>
-      <c r="H37" s="135" t="n"/>
-      <c r="I37" s="135" t="n"/>
-      <c r="J37" s="122" t="n"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" s="82">
+      <c r="C37" s="154" t="n"/>
+      <c r="D37" s="154" t="n"/>
+      <c r="E37" s="154" t="n"/>
+      <c r="F37" s="154" t="n"/>
+      <c r="G37" s="154" t="n"/>
+      <c r="H37" s="154" t="n"/>
+      <c r="I37" s="154" t="n"/>
+      <c r="J37" s="137" t="n"/>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A38" s="89" t="n"/>
-      <c r="B38" s="57" t="inlineStr">
+      <c r="B38" s="56" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C38" s="117" t="n"/>
-      <c r="D38" s="117" t="n"/>
-      <c r="E38" s="117" t="n"/>
-      <c r="F38" s="117" t="n"/>
-      <c r="G38" s="117" t="n"/>
-      <c r="H38" s="117" t="n"/>
-      <c r="I38" s="117" t="n"/>
-      <c r="J38" s="118">
+      <c r="C38" s="132" t="n"/>
+      <c r="D38" s="132" t="n"/>
+      <c r="E38" s="132" t="n"/>
+      <c r="F38" s="132" t="n"/>
+      <c r="G38" s="132" t="n"/>
+      <c r="H38" s="132" t="n"/>
+      <c r="I38" s="132" t="n"/>
+      <c r="J38" s="133">
         <f>SUM(C35:I35)</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="82">
-      <c r="A39" s="99" t="inlineStr">
+    <row r="39" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A39" s="87" t="inlineStr">
         <is>
           <t>심장</t>
         </is>
       </c>
-      <c r="B39" s="40" t="inlineStr">
+      <c r="B39" s="28" t="inlineStr">
         <is>
           <t>협심증</t>
         </is>
       </c>
-      <c r="C39" s="127" t="n"/>
-      <c r="D39" s="127" t="n"/>
-      <c r="E39" s="127" t="n"/>
-      <c r="F39" s="127" t="n"/>
-      <c r="G39" s="127" t="n"/>
-      <c r="H39" s="127" t="n"/>
-      <c r="I39" s="127" t="n"/>
-      <c r="J39" s="122">
+      <c r="C39" s="117" t="n"/>
+      <c r="D39" s="117" t="n"/>
+      <c r="E39" s="117" t="n"/>
+      <c r="F39" s="117" t="n"/>
+      <c r="G39" s="117" t="n"/>
+      <c r="H39" s="117" t="n"/>
+      <c r="I39" s="117" t="n"/>
+      <c r="J39" s="135">
         <f>SUM(C36:I36)</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="82">
+    <row r="40" ht="16.5" customHeight="1" s="78">
       <c r="A40" s="88" t="n"/>
       <c r="B40" s="31" t="inlineStr">
         <is>
           <t>심부전</t>
         </is>
       </c>
-      <c r="C40" s="130" t="n"/>
-      <c r="D40" s="130" t="n"/>
-      <c r="E40" s="130" t="n"/>
-      <c r="F40" s="130" t="n"/>
-      <c r="G40" s="130" t="n"/>
-      <c r="H40" s="130" t="n"/>
-      <c r="I40" s="130" t="n"/>
-      <c r="J40" s="122">
+      <c r="C40" s="145" t="n"/>
+      <c r="D40" s="145" t="n"/>
+      <c r="E40" s="145" t="n"/>
+      <c r="F40" s="145" t="n"/>
+      <c r="G40" s="145" t="n"/>
+      <c r="H40" s="145" t="n"/>
+      <c r="I40" s="145" t="n"/>
+      <c r="J40" s="137">
         <f>SUM(C37:I37)</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="17.25" customHeight="1" s="82">
+    <row r="41" ht="17.25" customHeight="1" s="78">
       <c r="A41" s="88" t="n"/>
       <c r="B41" s="31" t="inlineStr">
         <is>
           <t>빈맥</t>
         </is>
       </c>
-      <c r="C41" s="130" t="n"/>
-      <c r="D41" s="130" t="n"/>
-      <c r="E41" s="130" t="n"/>
-      <c r="F41" s="130" t="n"/>
-      <c r="G41" s="130" t="n"/>
-      <c r="H41" s="130" t="n"/>
-      <c r="I41" s="130" t="n"/>
-      <c r="J41" s="122" t="n"/>
-    </row>
-    <row r="42" ht="16.5" customHeight="1" s="82">
+      <c r="C41" s="145" t="n"/>
+      <c r="D41" s="145" t="n"/>
+      <c r="E41" s="145" t="n"/>
+      <c r="F41" s="145" t="n"/>
+      <c r="G41" s="145" t="n"/>
+      <c r="H41" s="145" t="n"/>
+      <c r="I41" s="145" t="n"/>
+      <c r="J41" s="137" t="n"/>
+    </row>
+    <row r="42" ht="16.5" customHeight="1" s="78">
       <c r="A42" s="88" t="n"/>
       <c r="B42" s="31" t="inlineStr">
         <is>
           <t>염증</t>
         </is>
       </c>
-      <c r="C42" s="130" t="n"/>
-      <c r="D42" s="130" t="n"/>
-      <c r="E42" s="130" t="n"/>
-      <c r="F42" s="130" t="n"/>
-      <c r="G42" s="130" t="n"/>
-      <c r="H42" s="130" t="n"/>
-      <c r="I42" s="130" t="n"/>
-      <c r="J42" s="122">
+      <c r="C42" s="145" t="n"/>
+      <c r="D42" s="145" t="n"/>
+      <c r="E42" s="145" t="n"/>
+      <c r="F42" s="145" t="n"/>
+      <c r="G42" s="145" t="n"/>
+      <c r="H42" s="145" t="n"/>
+      <c r="I42" s="145" t="n"/>
+      <c r="J42" s="137">
         <f>SUM(C38:I38)</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="16.5" customHeight="1" s="82">
+    <row r="43" ht="16.5" customHeight="1" s="78">
       <c r="A43" s="88" t="n"/>
       <c r="B43" s="40" t="inlineStr">
         <is>
           <t>부정맥</t>
         </is>
       </c>
-      <c r="C43" s="136" t="n"/>
-      <c r="D43" s="136" t="n"/>
-      <c r="E43" s="136" t="n"/>
-      <c r="F43" s="136" t="n"/>
-      <c r="G43" s="136" t="n"/>
-      <c r="H43" s="136" t="n"/>
-      <c r="I43" s="136" t="n"/>
-      <c r="J43" s="122">
+      <c r="C43" s="155" t="n"/>
+      <c r="D43" s="155" t="n"/>
+      <c r="E43" s="155" t="n"/>
+      <c r="F43" s="155" t="n"/>
+      <c r="G43" s="155" t="n"/>
+      <c r="H43" s="155" t="n"/>
+      <c r="I43" s="155" t="n"/>
+      <c r="J43" s="137">
         <f>SUM(C39:I39)</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="17.25" customHeight="1" s="82">
+    <row r="44" ht="17.25" customHeight="1" s="78">
       <c r="A44" s="88" t="n"/>
-      <c r="B44" s="40" t="inlineStr">
+      <c r="B44" s="59" t="inlineStr">
         <is>
           <t>심근병증</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="17.25" customHeight="1" s="82">
+      <c r="C44" s="106" t="n"/>
+      <c r="D44" s="106" t="n"/>
+      <c r="E44" s="106" t="n"/>
+      <c r="F44" s="106" t="n"/>
+      <c r="G44" s="106" t="n"/>
+      <c r="H44" s="106" t="n"/>
+      <c r="I44" s="106" t="n"/>
+      <c r="J44" s="108" t="n"/>
+    </row>
+    <row r="45" ht="17.25" customHeight="1" s="78">
       <c r="A45" s="88" t="n"/>
       <c r="B45" s="40" t="inlineStr">
         <is>
           <t>심장판막</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="16.5" customHeight="1" s="82">
+      <c r="C45" s="107" t="n"/>
+      <c r="D45" s="106" t="n"/>
+      <c r="E45" s="106" t="n"/>
+      <c r="F45" s="106" t="n"/>
+      <c r="G45" s="106" t="n"/>
+      <c r="H45" s="106" t="n"/>
+      <c r="I45" s="106" t="n"/>
+      <c r="J45" s="108" t="n"/>
+    </row>
+    <row r="46" ht="16.5" customHeight="1" s="78">
       <c r="A46" s="88" t="n"/>
-      <c r="B46" s="60" t="inlineStr">
+      <c r="B46" s="59" t="inlineStr">
         <is>
           <t>산정특례심장</t>
         </is>
       </c>
-      <c r="C46" s="121" t="n"/>
-      <c r="D46" s="121" t="n"/>
-      <c r="E46" s="121" t="n"/>
-      <c r="F46" s="121" t="n"/>
-      <c r="G46" s="121" t="n"/>
-      <c r="H46" s="121" t="n"/>
-      <c r="I46" s="121" t="n"/>
-      <c r="J46" s="122">
+      <c r="C46" s="136" t="n"/>
+      <c r="D46" s="136" t="n"/>
+      <c r="E46" s="136" t="n"/>
+      <c r="F46" s="136" t="n"/>
+      <c r="G46" s="136" t="n"/>
+      <c r="H46" s="136" t="n"/>
+      <c r="I46" s="136" t="n"/>
+      <c r="J46" s="137">
         <f>SUM(C40:I40)</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="16.5" customHeight="1" s="82">
+    <row r="47" ht="16.5" customHeight="1" s="78">
       <c r="A47" s="88" t="n"/>
-      <c r="B47" s="69" t="inlineStr">
+      <c r="B47" s="66" t="inlineStr">
         <is>
           <t>2대 주요치료비</t>
         </is>
       </c>
-      <c r="C47" s="121" t="n"/>
-      <c r="D47" s="121" t="n"/>
-      <c r="E47" s="121" t="n"/>
-      <c r="F47" s="121" t="n"/>
-      <c r="G47" s="121" t="n"/>
-      <c r="H47" s="121" t="n"/>
-      <c r="I47" s="121" t="n"/>
-      <c r="J47" s="122">
+      <c r="C47" s="136" t="n"/>
+      <c r="D47" s="136" t="n"/>
+      <c r="E47" s="136" t="n"/>
+      <c r="F47" s="136" t="n"/>
+      <c r="G47" s="136" t="n"/>
+      <c r="H47" s="136" t="n"/>
+      <c r="I47" s="136" t="n"/>
+      <c r="J47" s="137">
         <f>SUM(C41:I41)</f>
         <v/>
       </c>
     </row>
-    <row r="48" ht="16.5" customHeight="1" s="82">
+    <row r="48" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A48" s="88" t="n"/>
-      <c r="B48" s="86" t="inlineStr">
+      <c r="B48" s="82" t="inlineStr">
         <is>
           <t>허혈성 진단비</t>
         </is>
       </c>
-      <c r="C48" s="115" t="n"/>
-      <c r="D48" s="115" t="n"/>
-      <c r="E48" s="115" t="n"/>
-      <c r="F48" s="115" t="n"/>
-      <c r="G48" s="115" t="n"/>
-      <c r="H48" s="115" t="n"/>
-      <c r="I48" s="115" t="n"/>
-      <c r="J48" s="122">
+      <c r="C48" s="130" t="n"/>
+      <c r="D48" s="130" t="n"/>
+      <c r="E48" s="130" t="n"/>
+      <c r="F48" s="130" t="n"/>
+      <c r="G48" s="130" t="n"/>
+      <c r="H48" s="130" t="n"/>
+      <c r="I48" s="130" t="n"/>
+      <c r="J48" s="137">
         <f>SUM(C42:I42)</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="16.5" customHeight="1" s="82">
+    <row r="49" ht="16.5" customHeight="1" s="78">
       <c r="A49" s="88" t="n"/>
       <c r="B49" s="13" t="inlineStr">
         <is>
           <t>급성심근경색</t>
         </is>
       </c>
-      <c r="C49" s="125" t="n"/>
-      <c r="D49" s="125" t="n"/>
-      <c r="E49" s="125" t="n"/>
-      <c r="F49" s="125" t="n"/>
-      <c r="G49" s="125" t="n"/>
-      <c r="H49" s="125" t="n"/>
-      <c r="I49" s="125" t="n"/>
-      <c r="J49" s="110">
+      <c r="C49" s="140" t="n"/>
+      <c r="D49" s="140" t="n"/>
+      <c r="E49" s="140" t="n"/>
+      <c r="F49" s="140" t="n"/>
+      <c r="G49" s="140" t="n"/>
+      <c r="H49" s="140" t="n"/>
+      <c r="I49" s="140" t="n"/>
+      <c r="J49" s="125">
         <f>SUM(C42:I42)</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="16.5" customHeight="1" s="82">
+    <row r="50" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A50" s="88" t="n"/>
       <c r="B50" s="16" t="inlineStr">
         <is>
           <t>중대한 급성심근</t>
         </is>
       </c>
-      <c r="C50" s="111" t="n"/>
-      <c r="D50" s="111" t="n"/>
-      <c r="E50" s="111" t="n"/>
-      <c r="F50" s="111" t="n"/>
-      <c r="G50" s="111" t="n"/>
-      <c r="H50" s="111" t="n"/>
-      <c r="I50" s="111" t="n"/>
-      <c r="J50" s="133">
+      <c r="C50" s="126" t="n"/>
+      <c r="D50" s="126" t="n"/>
+      <c r="E50" s="126" t="n"/>
+      <c r="F50" s="126" t="n"/>
+      <c r="G50" s="126" t="n"/>
+      <c r="H50" s="126" t="n"/>
+      <c r="I50" s="126" t="n"/>
+      <c r="J50" s="148">
         <f>SUM(C44:I44)</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="82">
+    <row r="51" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A51" s="89" t="n"/>
-      <c r="B51" s="64" t="inlineStr">
+      <c r="B51" s="63" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C51" s="113" t="n"/>
-      <c r="D51" s="113" t="n"/>
-      <c r="E51" s="113" t="n"/>
-      <c r="F51" s="113" t="n"/>
-      <c r="G51" s="113" t="n"/>
-      <c r="H51" s="113" t="n"/>
-      <c r="I51" s="113" t="n"/>
-      <c r="J51" s="114">
+      <c r="C51" s="128" t="n"/>
+      <c r="D51" s="128" t="n"/>
+      <c r="E51" s="128" t="n"/>
+      <c r="F51" s="128" t="n"/>
+      <c r="G51" s="128" t="n"/>
+      <c r="H51" s="128" t="n"/>
+      <c r="I51" s="128" t="n"/>
+      <c r="J51" s="129">
         <f>SUM(C45:I45)</f>
         <v/>
       </c>
     </row>
-    <row r="52" ht="16.5" customHeight="1" s="82">
-      <c r="A52" s="99" t="inlineStr">
+    <row r="52" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A52" s="95" t="inlineStr">
         <is>
           <t>일당</t>
         </is>
       </c>
-      <c r="B52" s="95" t="inlineStr">
+      <c r="B52" s="90" t="inlineStr">
         <is>
           <t>질병일당</t>
         </is>
       </c>
-      <c r="C52" s="119" t="n"/>
-      <c r="D52" s="119" t="n"/>
-      <c r="E52" s="119" t="n"/>
-      <c r="F52" s="119" t="n"/>
-      <c r="G52" s="119" t="n"/>
-      <c r="H52" s="119" t="n"/>
-      <c r="I52" s="119" t="n"/>
-      <c r="J52" s="120">
+      <c r="C52" s="134" t="n"/>
+      <c r="D52" s="134" t="n"/>
+      <c r="E52" s="134" t="n"/>
+      <c r="F52" s="134" t="n"/>
+      <c r="G52" s="134" t="n"/>
+      <c r="H52" s="134" t="n"/>
+      <c r="I52" s="134" t="n"/>
+      <c r="J52" s="135">
         <f>SUM(C46:I46)</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="16.5" customHeight="1" s="82">
+    <row r="53" ht="16.5" customHeight="1" s="78">
       <c r="A53" s="88" t="n"/>
-      <c r="B53" s="65" t="inlineStr">
+      <c r="B53" s="64" t="inlineStr">
         <is>
           <t>질병수술일당</t>
         </is>
       </c>
-      <c r="C53" s="136" t="n"/>
-      <c r="D53" s="136" t="n"/>
-      <c r="E53" s="136" t="n"/>
-      <c r="F53" s="136" t="n"/>
-      <c r="G53" s="136" t="n"/>
-      <c r="H53" s="136" t="n"/>
-      <c r="I53" s="136" t="n"/>
-      <c r="J53" s="122">
+      <c r="C53" s="155" t="n"/>
+      <c r="D53" s="155" t="n"/>
+      <c r="E53" s="155" t="n"/>
+      <c r="F53" s="155" t="n"/>
+      <c r="G53" s="155" t="n"/>
+      <c r="H53" s="155" t="n"/>
+      <c r="I53" s="155" t="n"/>
+      <c r="J53" s="137">
         <f>SUM(C47:I47)</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="16.5" customHeight="1" s="82">
+    <row r="54" ht="16.5" customHeight="1" s="78">
       <c r="A54" s="88" t="n"/>
-      <c r="B54" s="65" t="inlineStr">
-        <is>
-          <t>질병종합병원일당</t>
-        </is>
-      </c>
-      <c r="C54" s="136" t="n"/>
-      <c r="D54" s="136" t="n"/>
-      <c r="E54" s="136" t="n"/>
-      <c r="F54" s="136" t="n"/>
-      <c r="G54" s="136" t="n"/>
-      <c r="H54" s="136" t="n"/>
-      <c r="I54" s="136" t="n"/>
-      <c r="J54" s="122">
+      <c r="B54" s="64" t="inlineStr">
+        <is>
+          <t>종합병원 질병입원일당</t>
+        </is>
+      </c>
+      <c r="C54" s="155" t="n"/>
+      <c r="D54" s="155" t="n"/>
+      <c r="E54" s="155" t="n"/>
+      <c r="F54" s="155" t="n"/>
+      <c r="G54" s="155" t="n"/>
+      <c r="H54" s="155" t="n"/>
+      <c r="I54" s="155" t="n"/>
+      <c r="J54" s="137">
         <f>SUM(C48:I48)</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="16.5" customHeight="1" s="82">
+    <row r="55" ht="16.5" customHeight="1" s="78">
       <c r="A55" s="88" t="n"/>
-      <c r="B55" s="65" t="inlineStr">
+      <c r="B55" s="64" t="inlineStr">
         <is>
           <t>종합병원 상해입원일당</t>
         </is>
       </c>
-      <c r="C55" s="136" t="n"/>
-      <c r="D55" s="136" t="n"/>
-      <c r="E55" s="136" t="n"/>
-      <c r="F55" s="136" t="n"/>
-      <c r="G55" s="136" t="n"/>
-      <c r="H55" s="136" t="n"/>
-      <c r="I55" s="136" t="n"/>
-      <c r="J55" s="122" t="n"/>
-    </row>
-    <row r="56" ht="16.5" customHeight="1" s="82">
+      <c r="C55" s="155" t="n"/>
+      <c r="D55" s="155" t="n"/>
+      <c r="E55" s="155" t="n"/>
+      <c r="F55" s="155" t="n"/>
+      <c r="G55" s="155" t="n"/>
+      <c r="H55" s="155" t="n"/>
+      <c r="I55" s="155" t="n"/>
+      <c r="J55" s="137" t="n"/>
+    </row>
+    <row r="56" ht="16.5" customHeight="1" s="78">
       <c r="A56" s="88" t="n"/>
-      <c r="B56" s="60" t="inlineStr">
+      <c r="B56" s="59" t="inlineStr">
         <is>
           <t>상해일당</t>
         </is>
       </c>
-      <c r="C56" s="121" t="n"/>
-      <c r="D56" s="121" t="n"/>
-      <c r="E56" s="121" t="n"/>
-      <c r="F56" s="121" t="n"/>
-      <c r="G56" s="121" t="n"/>
-      <c r="H56" s="121" t="n"/>
-      <c r="I56" s="121" t="n"/>
-      <c r="J56" s="122">
+      <c r="C56" s="136" t="n"/>
+      <c r="D56" s="136" t="n"/>
+      <c r="E56" s="136" t="n"/>
+      <c r="F56" s="136" t="n"/>
+      <c r="G56" s="136" t="n"/>
+      <c r="H56" s="136" t="n"/>
+      <c r="I56" s="136" t="n"/>
+      <c r="J56" s="137">
         <f>SUM(C49:I49)</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="16.5" customHeight="1" s="82">
+    <row r="57" ht="16.5" customHeight="1" s="78">
       <c r="A57" s="88" t="n"/>
-      <c r="B57" s="60" t="inlineStr">
+      <c r="B57" s="59" t="inlineStr">
         <is>
           <t>상해수술일당</t>
         </is>
       </c>
-      <c r="C57" s="121" t="n"/>
-      <c r="D57" s="121" t="n"/>
-      <c r="E57" s="121" t="n"/>
-      <c r="F57" s="121" t="n"/>
-      <c r="G57" s="121" t="n"/>
-      <c r="H57" s="121" t="n"/>
-      <c r="I57" s="121" t="n"/>
-      <c r="J57" s="122" t="n"/>
-    </row>
-    <row r="58" ht="16.5" customHeight="1" s="82">
+      <c r="C57" s="136" t="n"/>
+      <c r="D57" s="136" t="n"/>
+      <c r="E57" s="136" t="n"/>
+      <c r="F57" s="136" t="n"/>
+      <c r="G57" s="136" t="n"/>
+      <c r="H57" s="136" t="n"/>
+      <c r="I57" s="136" t="n"/>
+      <c r="J57" s="137" t="n"/>
+    </row>
+    <row r="58" ht="16.5" customHeight="1" s="78">
       <c r="A58" s="88" t="n"/>
       <c r="B58" s="31" t="inlineStr">
         <is>
           <t>간병인</t>
         </is>
       </c>
-      <c r="C58" s="121" t="n"/>
-      <c r="D58" s="121" t="n"/>
-      <c r="E58" s="121" t="n"/>
-      <c r="F58" s="121" t="n"/>
-      <c r="G58" s="121" t="n"/>
-      <c r="H58" s="121" t="n"/>
-      <c r="I58" s="121" t="n"/>
-      <c r="J58" s="122">
+      <c r="C58" s="136" t="n"/>
+      <c r="D58" s="136" t="n"/>
+      <c r="E58" s="136" t="n"/>
+      <c r="F58" s="136" t="n"/>
+      <c r="G58" s="136" t="n"/>
+      <c r="H58" s="136" t="n"/>
+      <c r="I58" s="136" t="n"/>
+      <c r="J58" s="137">
         <f>SUM(C50:I50)</f>
         <v/>
       </c>
     </row>
-    <row r="59" ht="16.5" customHeight="1" s="82">
+    <row r="59" ht="16.5" customHeight="1" s="78">
       <c r="A59" s="88" t="n"/>
       <c r="B59" s="31" t="inlineStr">
         <is>
           <t>간병인지원일당</t>
         </is>
       </c>
-      <c r="C59" s="121" t="n"/>
-      <c r="D59" s="121" t="n"/>
-      <c r="E59" s="121" t="n"/>
-      <c r="F59" s="121" t="n"/>
-      <c r="G59" s="121" t="n"/>
-      <c r="H59" s="121" t="n"/>
-      <c r="I59" s="121" t="n"/>
-      <c r="J59" s="122" t="n"/>
-    </row>
-    <row r="60" ht="16.5" customHeight="1" s="82">
+      <c r="C59" s="136" t="n"/>
+      <c r="D59" s="136" t="n"/>
+      <c r="E59" s="136" t="n"/>
+      <c r="F59" s="136" t="n"/>
+      <c r="G59" s="136" t="n"/>
+      <c r="H59" s="136" t="n"/>
+      <c r="I59" s="136" t="n"/>
+      <c r="J59" s="137" t="n"/>
+    </row>
+    <row r="60" ht="16.5" customHeight="1" s="78">
       <c r="A60" s="88" t="n"/>
       <c r="B60" s="31" t="inlineStr">
         <is>
           <t>간호통합병동</t>
         </is>
       </c>
-      <c r="C60" s="121" t="n"/>
-      <c r="D60" s="121" t="n"/>
-      <c r="E60" s="121" t="n"/>
-      <c r="F60" s="121" t="n"/>
-      <c r="G60" s="121" t="n"/>
-      <c r="H60" s="121" t="n"/>
-      <c r="I60" s="121" t="n"/>
-      <c r="J60" s="122">
+      <c r="C60" s="136" t="n"/>
+      <c r="D60" s="136" t="n"/>
+      <c r="E60" s="136" t="n"/>
+      <c r="F60" s="136" t="n"/>
+      <c r="G60" s="136" t="n"/>
+      <c r="H60" s="136" t="n"/>
+      <c r="I60" s="136" t="n"/>
+      <c r="J60" s="137">
         <f>SUM(C51:I51)</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="16.5" customHeight="1" s="82">
+    <row r="61" ht="16.5" customHeight="1" s="78">
       <c r="A61" s="88" t="n"/>
-      <c r="B61" s="66" t="inlineStr">
+      <c r="B61" s="65" t="inlineStr">
         <is>
           <t>1인실 종합병원</t>
         </is>
       </c>
-      <c r="C61" s="121" t="n"/>
-      <c r="D61" s="121" t="n"/>
-      <c r="E61" s="121" t="n"/>
-      <c r="F61" s="121" t="n"/>
-      <c r="G61" s="121" t="n"/>
-      <c r="H61" s="121" t="n"/>
-      <c r="I61" s="121" t="n"/>
-      <c r="J61" s="122">
+      <c r="C61" s="136" t="n"/>
+      <c r="D61" s="136" t="n"/>
+      <c r="E61" s="136" t="n"/>
+      <c r="F61" s="136" t="n"/>
+      <c r="G61" s="136" t="n"/>
+      <c r="H61" s="136" t="n"/>
+      <c r="I61" s="136" t="n"/>
+      <c r="J61" s="137">
         <f>SUM(C52:I52)</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="17.25" customHeight="1" s="82">
+    <row r="62" ht="17.25" customHeight="1" s="78">
       <c r="A62" s="88" t="n"/>
-      <c r="B62" s="66" t="inlineStr">
+      <c r="B62" s="65" t="inlineStr">
         <is>
           <t>1인실 상급병원</t>
         </is>
       </c>
-      <c r="C62" s="121" t="n"/>
-      <c r="D62" s="121" t="n"/>
-      <c r="E62" s="121" t="n"/>
-      <c r="F62" s="121" t="n"/>
-      <c r="G62" s="121" t="n"/>
-      <c r="H62" s="121" t="n"/>
-      <c r="I62" s="121" t="n"/>
-      <c r="J62" s="122">
+      <c r="C62" s="136" t="n"/>
+      <c r="D62" s="136" t="n"/>
+      <c r="E62" s="136" t="n"/>
+      <c r="F62" s="136" t="n"/>
+      <c r="G62" s="136" t="n"/>
+      <c r="H62" s="136" t="n"/>
+      <c r="I62" s="136" t="n"/>
+      <c r="J62" s="137">
         <f>SUM(C53:I53)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="17.25" customHeight="1" s="82">
+    <row r="63" ht="17.25" customHeight="1" s="78">
       <c r="A63" s="88" t="n"/>
       <c r="B63" s="31" t="inlineStr">
         <is>
           <t>질병중환자실</t>
         </is>
       </c>
-      <c r="C63" s="121" t="n"/>
-      <c r="D63" s="121" t="n"/>
-      <c r="E63" s="121" t="n"/>
-      <c r="F63" s="121" t="n"/>
-      <c r="G63" s="121" t="n"/>
-      <c r="H63" s="121" t="n"/>
-      <c r="I63" s="121" t="n"/>
-      <c r="J63" s="122">
+      <c r="C63" s="136" t="n"/>
+      <c r="D63" s="136" t="n"/>
+      <c r="E63" s="136" t="n"/>
+      <c r="F63" s="136" t="n"/>
+      <c r="G63" s="136" t="n"/>
+      <c r="H63" s="136" t="n"/>
+      <c r="I63" s="136" t="n"/>
+      <c r="J63" s="137">
         <f>SUM(C54:I54)</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="16.5" customHeight="1" s="82">
+    <row r="64" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A64" s="89" t="n"/>
       <c r="B64" s="25" t="inlineStr">
         <is>
           <t>상해중환자실</t>
         </is>
       </c>
-      <c r="C64" s="117" t="n"/>
-      <c r="D64" s="117" t="n"/>
-      <c r="E64" s="117" t="n"/>
-      <c r="F64" s="117" t="n"/>
-      <c r="G64" s="117" t="n"/>
-      <c r="H64" s="117" t="n"/>
-      <c r="I64" s="117" t="n"/>
-      <c r="J64" s="118">
+      <c r="C64" s="132" t="n"/>
+      <c r="D64" s="132" t="n"/>
+      <c r="E64" s="132" t="n"/>
+      <c r="F64" s="132" t="n"/>
+      <c r="G64" s="132" t="n"/>
+      <c r="H64" s="132" t="n"/>
+      <c r="I64" s="132" t="n"/>
+      <c r="J64" s="133">
         <f>SUM(C55:I55)</f>
         <v/>
       </c>
     </row>
-    <row r="65" ht="16.5" customHeight="1" s="82">
-      <c r="A65" s="148" t="inlineStr">
+    <row r="65" ht="16.5" customHeight="1" s="78">
+      <c r="A65" s="87" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B65" s="95" t="inlineStr">
+      <c r="B65" s="90" t="inlineStr">
         <is>
           <t>상해수술비</t>
         </is>
       </c>
-      <c r="C65" s="119" t="n"/>
-      <c r="D65" s="119" t="n"/>
-      <c r="E65" s="119" t="n"/>
-      <c r="F65" s="119" t="n"/>
-      <c r="G65" s="119" t="n"/>
-      <c r="H65" s="119" t="n"/>
-      <c r="I65" s="119" t="n"/>
-      <c r="J65" s="120">
+      <c r="C65" s="134" t="n"/>
+      <c r="D65" s="134" t="n"/>
+      <c r="E65" s="134" t="n"/>
+      <c r="F65" s="134" t="n"/>
+      <c r="G65" s="134" t="n"/>
+      <c r="H65" s="134" t="n"/>
+      <c r="I65" s="134" t="n"/>
+      <c r="J65" s="135">
         <f>SUM(C56:I56)</f>
         <v/>
       </c>
     </row>
-    <row r="66" ht="16.5" customHeight="1" s="82">
-      <c r="A66" s="149" t="n"/>
-      <c r="B66" s="65" t="inlineStr">
+    <row r="66" ht="16.5" customHeight="1" s="78">
+      <c r="A66" s="88" t="n"/>
+      <c r="B66" s="64" t="inlineStr">
         <is>
           <t>중대한상해수술비</t>
         </is>
       </c>
-      <c r="C66" s="136" t="n"/>
-      <c r="D66" s="136" t="n"/>
-      <c r="E66" s="136" t="n"/>
-      <c r="F66" s="136" t="n"/>
-      <c r="G66" s="136" t="n"/>
-      <c r="H66" s="136" t="n"/>
-      <c r="I66" s="136" t="n"/>
-      <c r="J66" s="122">
+      <c r="C66" s="155" t="n"/>
+      <c r="D66" s="155" t="n"/>
+      <c r="E66" s="155" t="n"/>
+      <c r="F66" s="155" t="n"/>
+      <c r="G66" s="155" t="n"/>
+      <c r="H66" s="155" t="n"/>
+      <c r="I66" s="155" t="n"/>
+      <c r="J66" s="137">
         <f>SUM(C57:I57)</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="16.5" customHeight="1" s="82">
-      <c r="A67" s="149" t="n"/>
-      <c r="B67" s="60" t="inlineStr">
+    <row r="67" ht="16.5" customHeight="1" s="78">
+      <c r="A67" s="88" t="n"/>
+      <c r="B67" s="59" t="inlineStr">
         <is>
           <t>상해 종수술비(1-3종)</t>
         </is>
       </c>
-      <c r="C67" s="136" t="n"/>
-      <c r="D67" s="136" t="n"/>
-      <c r="E67" s="136" t="n"/>
-      <c r="F67" s="137" t="n"/>
-      <c r="G67" s="136" t="n"/>
-      <c r="H67" s="136" t="n"/>
-      <c r="I67" s="136" t="n"/>
-      <c r="J67" s="122" t="n"/>
-    </row>
-    <row r="68" ht="17.25" customHeight="1" s="82">
-      <c r="A68" s="149" t="n"/>
-      <c r="B68" s="60" t="inlineStr">
+      <c r="C67" s="155" t="n"/>
+      <c r="D67" s="155" t="n"/>
+      <c r="E67" s="155" t="n"/>
+      <c r="F67" s="156" t="n"/>
+      <c r="G67" s="155" t="n"/>
+      <c r="H67" s="155" t="n"/>
+      <c r="I67" s="155" t="n"/>
+      <c r="J67" s="137" t="n"/>
+    </row>
+    <row r="68" ht="17.25" customHeight="1" s="78">
+      <c r="A68" s="88" t="n"/>
+      <c r="B68" s="59" t="inlineStr">
         <is>
           <t>상해 종수술비(1-5종)</t>
         </is>
       </c>
-      <c r="C68" s="136" t="n"/>
-      <c r="D68" s="136" t="n"/>
-      <c r="E68" s="136" t="n"/>
-      <c r="F68" s="137" t="n"/>
-      <c r="G68" s="136" t="n"/>
-      <c r="H68" s="136" t="n"/>
-      <c r="I68" s="136" t="n"/>
-      <c r="J68" s="122" t="inlineStr">
+      <c r="C68" s="155" t="n"/>
+      <c r="D68" s="155" t="n"/>
+      <c r="E68" s="155" t="n"/>
+      <c r="F68" s="156" t="n"/>
+      <c r="G68" s="155" t="n"/>
+      <c r="H68" s="155" t="n"/>
+      <c r="I68" s="155" t="n"/>
+      <c r="J68" s="137" t="inlineStr">
         <is>
           <t>/ / / / /</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="16.5" customHeight="1" s="82">
-      <c r="A69" s="149" t="n"/>
-      <c r="B69" s="60" t="inlineStr">
+    <row r="69" ht="16.5" customHeight="1" s="78">
+      <c r="A69" s="88" t="n"/>
+      <c r="B69" s="59" t="inlineStr">
         <is>
           <t>상해 종수술비(1-8종)</t>
         </is>
       </c>
-      <c r="C69" s="136" t="n"/>
-      <c r="D69" s="136" t="n"/>
-      <c r="E69" s="136" t="n"/>
-      <c r="F69" s="137" t="n"/>
-      <c r="G69" s="136" t="n"/>
-      <c r="H69" s="136" t="n"/>
-      <c r="I69" s="136" t="n"/>
-      <c r="J69" s="122" t="n"/>
-    </row>
-    <row r="70" ht="16.5" customHeight="1" s="82">
-      <c r="A70" s="149" t="n"/>
-      <c r="B70" s="60" t="inlineStr">
+      <c r="C69" s="155" t="n"/>
+      <c r="D69" s="155" t="n"/>
+      <c r="E69" s="155" t="n"/>
+      <c r="F69" s="156" t="n"/>
+      <c r="G69" s="155" t="n"/>
+      <c r="H69" s="155" t="n"/>
+      <c r="I69" s="155" t="n"/>
+      <c r="J69" s="137" t="n"/>
+    </row>
+    <row r="70" ht="16.5" customHeight="1" s="78">
+      <c r="A70" s="88" t="n"/>
+      <c r="B70" s="59" t="inlineStr">
         <is>
           <t>창상봉합술</t>
         </is>
       </c>
-      <c r="C70" s="121" t="n"/>
-      <c r="D70" s="121" t="n"/>
-      <c r="E70" s="121" t="n"/>
-      <c r="F70" s="121" t="n"/>
-      <c r="G70" s="121" t="n"/>
-      <c r="H70" s="121" t="n"/>
-      <c r="I70" s="121" t="n"/>
-      <c r="J70" s="122">
+      <c r="C70" s="136" t="n"/>
+      <c r="D70" s="136" t="n"/>
+      <c r="E70" s="136" t="n"/>
+      <c r="F70" s="157" t="n"/>
+      <c r="G70" s="136" t="n"/>
+      <c r="H70" s="136" t="n"/>
+      <c r="I70" s="136" t="n"/>
+      <c r="J70" s="137">
         <f>SUM(C59:I59)</f>
         <v/>
       </c>
     </row>
-    <row r="71" ht="16.5" customHeight="1" s="82">
-      <c r="A71" s="149" t="n"/>
-      <c r="B71" s="60" t="inlineStr">
+    <row r="71" ht="16.5" customHeight="1" s="78">
+      <c r="A71" s="88" t="n"/>
+      <c r="B71" s="59" t="inlineStr">
         <is>
           <t>골절수술비</t>
         </is>
       </c>
-      <c r="C71" s="121" t="n"/>
-      <c r="D71" s="121" t="n"/>
-      <c r="E71" s="121" t="n"/>
-      <c r="F71" s="121" t="n"/>
-      <c r="G71" s="121" t="n"/>
-      <c r="H71" s="121" t="n"/>
-      <c r="I71" s="121" t="n"/>
-      <c r="J71" s="122">
+      <c r="C71" s="136" t="n"/>
+      <c r="D71" s="136" t="n"/>
+      <c r="E71" s="136" t="n"/>
+      <c r="F71" s="157" t="n"/>
+      <c r="G71" s="136" t="n"/>
+      <c r="H71" s="136" t="n"/>
+      <c r="I71" s="136" t="n"/>
+      <c r="J71" s="137">
         <f>SUM(C60:I60)</f>
         <v/>
       </c>
     </row>
-    <row r="72" ht="16.5" customHeight="1" s="82">
-      <c r="A72" s="149" t="n"/>
-      <c r="B72" s="69" t="inlineStr">
+    <row r="72" ht="16.5" customHeight="1" s="78">
+      <c r="A72" s="88" t="n"/>
+      <c r="B72" s="66" t="inlineStr">
         <is>
           <t>5대골절수술비</t>
         </is>
       </c>
-      <c r="C72" s="121" t="n"/>
-      <c r="D72" s="121" t="n"/>
-      <c r="E72" s="121" t="n"/>
-      <c r="F72" s="121" t="n"/>
-      <c r="G72" s="121" t="n"/>
-      <c r="H72" s="121" t="n"/>
-      <c r="I72" s="121" t="n"/>
-      <c r="J72" s="122">
+      <c r="C72" s="136" t="n"/>
+      <c r="D72" s="136" t="n"/>
+      <c r="E72" s="136" t="n"/>
+      <c r="F72" s="157" t="n"/>
+      <c r="G72" s="136" t="n"/>
+      <c r="H72" s="136" t="n"/>
+      <c r="I72" s="136" t="n"/>
+      <c r="J72" s="137">
         <f>SUM(C61:I61)</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="16.5" customHeight="1" s="82">
-      <c r="A73" s="149" t="n"/>
-      <c r="B73" s="57" t="inlineStr">
+    <row r="73" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A73" s="88" t="n"/>
+      <c r="B73" s="56" t="inlineStr">
         <is>
           <t>화상수술비</t>
         </is>
       </c>
-      <c r="C73" s="117" t="n"/>
-      <c r="D73" s="117" t="n"/>
-      <c r="E73" s="117" t="n"/>
-      <c r="F73" s="117" t="n"/>
-      <c r="G73" s="117" t="n"/>
-      <c r="H73" s="117" t="n"/>
-      <c r="I73" s="117" t="n"/>
-      <c r="J73" s="118">
+      <c r="C73" s="132" t="n"/>
+      <c r="D73" s="132" t="n"/>
+      <c r="E73" s="132" t="n"/>
+      <c r="F73" s="158" t="n"/>
+      <c r="G73" s="132" t="n"/>
+      <c r="H73" s="132" t="n"/>
+      <c r="I73" s="132" t="n"/>
+      <c r="J73" s="133">
         <f>SUM(C62:I62)</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="16.5" customHeight="1" s="82">
-      <c r="A74" s="149" t="n"/>
-      <c r="B74" s="65" t="inlineStr">
+    <row r="74" ht="16.5" customHeight="1" s="78">
+      <c r="A74" s="88" t="n"/>
+      <c r="B74" s="64" t="inlineStr">
         <is>
           <t>질병수술비</t>
         </is>
       </c>
-      <c r="C74" s="136" t="n"/>
-      <c r="D74" s="136" t="n"/>
-      <c r="E74" s="136" t="n"/>
-      <c r="F74" s="136" t="n"/>
-      <c r="G74" s="136" t="n"/>
-      <c r="H74" s="136" t="n"/>
-      <c r="I74" s="138" t="n"/>
-      <c r="J74" s="116">
+      <c r="C74" s="155" t="n"/>
+      <c r="D74" s="155" t="n"/>
+      <c r="E74" s="155" t="n"/>
+      <c r="F74" s="159" t="n"/>
+      <c r="G74" s="155" t="n"/>
+      <c r="H74" s="155" t="n"/>
+      <c r="I74" s="160" t="n"/>
+      <c r="J74" s="131">
         <f>SUM(C63:I63)</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="16.5" customHeight="1" s="82">
-      <c r="A75" s="149" t="n"/>
-      <c r="B75" s="60" t="inlineStr">
+    <row r="75" ht="16.5" customHeight="1" s="78">
+      <c r="A75" s="88" t="n"/>
+      <c r="B75" s="59" t="inlineStr">
         <is>
           <t>질병 종수술비(1-3종)</t>
         </is>
       </c>
-      <c r="C75" s="121" t="n"/>
-      <c r="D75" s="121" t="n"/>
-      <c r="E75" s="121" t="n"/>
-      <c r="F75" s="139" t="n"/>
-      <c r="G75" s="121" t="n"/>
-      <c r="H75" s="121" t="n"/>
-      <c r="I75" s="121" t="n"/>
-      <c r="J75" s="122" t="n"/>
-    </row>
-    <row r="76" ht="17.25" customHeight="1" s="82">
-      <c r="A76" s="149" t="n"/>
-      <c r="B76" s="60" t="inlineStr">
+      <c r="C75" s="136" t="n"/>
+      <c r="D75" s="136" t="n"/>
+      <c r="E75" s="136" t="n"/>
+      <c r="F75" s="161" t="n"/>
+      <c r="G75" s="136" t="n"/>
+      <c r="H75" s="136" t="n"/>
+      <c r="I75" s="136" t="n"/>
+      <c r="J75" s="137" t="n"/>
+    </row>
+    <row r="76" ht="17.25" customHeight="1" s="78">
+      <c r="A76" s="88" t="n"/>
+      <c r="B76" s="59" t="inlineStr">
         <is>
           <t>질병 종수술비(1-5종)</t>
         </is>
       </c>
-      <c r="C76" s="121" t="n"/>
-      <c r="D76" s="121" t="n"/>
-      <c r="E76" s="121" t="n"/>
-      <c r="F76" s="139" t="n"/>
-      <c r="G76" s="121" t="n"/>
-      <c r="H76" s="121" t="n"/>
-      <c r="I76" s="121" t="n"/>
-      <c r="J76" s="122" t="inlineStr">
+      <c r="C76" s="136" t="n"/>
+      <c r="D76" s="136" t="n"/>
+      <c r="E76" s="136" t="n"/>
+      <c r="F76" s="161" t="n"/>
+      <c r="G76" s="136" t="n"/>
+      <c r="H76" s="136" t="n"/>
+      <c r="I76" s="136" t="n"/>
+      <c r="J76" s="137" t="inlineStr">
         <is>
           <t>/ / / / /</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="16.5" customHeight="1" s="82">
-      <c r="A77" s="149" t="n"/>
-      <c r="B77" s="60" t="inlineStr">
+    <row r="77" ht="16.5" customHeight="1" s="78">
+      <c r="A77" s="88" t="n"/>
+      <c r="B77" s="59" t="inlineStr">
         <is>
           <t>질병 종수술비(1-8종)</t>
         </is>
       </c>
-      <c r="C77" s="121" t="n"/>
-      <c r="D77" s="121" t="n"/>
-      <c r="E77" s="121" t="n"/>
-      <c r="F77" s="139" t="n"/>
-      <c r="G77" s="121" t="n"/>
-      <c r="H77" s="121" t="n"/>
-      <c r="I77" s="121" t="n"/>
-      <c r="J77" s="122" t="n"/>
-    </row>
-    <row r="78" ht="16.5" customHeight="1" s="82">
-      <c r="A78" s="149" t="n"/>
-      <c r="B78" s="72" t="inlineStr">
+      <c r="C77" s="136" t="n"/>
+      <c r="D77" s="136" t="n"/>
+      <c r="E77" s="136" t="n"/>
+      <c r="F77" s="161" t="n"/>
+      <c r="G77" s="136" t="n"/>
+      <c r="H77" s="136" t="n"/>
+      <c r="I77" s="136" t="n"/>
+      <c r="J77" s="137" t="n"/>
+    </row>
+    <row r="78" ht="16.5" customHeight="1" s="78">
+      <c r="A78" s="88" t="n"/>
+      <c r="B78" s="68" t="inlineStr">
         <is>
           <t>뇌혈관수술비</t>
         </is>
       </c>
-      <c r="C78" s="140" t="n"/>
-      <c r="D78" s="140" t="n"/>
-      <c r="E78" s="140" t="n"/>
-      <c r="F78" s="140" t="n"/>
-      <c r="G78" s="140" t="n"/>
-      <c r="H78" s="140" t="n"/>
-      <c r="I78" s="140" t="n"/>
-      <c r="J78" s="122">
+      <c r="C78" s="162" t="n"/>
+      <c r="D78" s="162" t="n"/>
+      <c r="E78" s="162" t="n"/>
+      <c r="F78" s="162" t="n"/>
+      <c r="G78" s="162" t="n"/>
+      <c r="H78" s="162" t="n"/>
+      <c r="I78" s="162" t="n"/>
+      <c r="J78" s="137">
         <f>SUM(C65:I65)</f>
         <v/>
       </c>
     </row>
-    <row r="79" ht="17.25" customHeight="1" s="82">
-      <c r="A79" s="149" t="n"/>
-      <c r="B79" s="72" t="inlineStr">
+    <row r="79" ht="17.25" customHeight="1" s="78">
+      <c r="A79" s="88" t="n"/>
+      <c r="B79" s="68" t="inlineStr">
         <is>
           <t>허혈성수술비</t>
         </is>
       </c>
-      <c r="C79" s="140" t="n"/>
-      <c r="D79" s="140" t="n"/>
-      <c r="E79" s="140" t="n"/>
-      <c r="F79" s="140" t="n"/>
-      <c r="G79" s="140" t="n"/>
-      <c r="H79" s="140" t="n"/>
-      <c r="I79" s="140" t="n"/>
-      <c r="J79" s="122">
+      <c r="C79" s="162" t="n"/>
+      <c r="D79" s="162" t="n"/>
+      <c r="E79" s="162" t="n"/>
+      <c r="F79" s="162" t="n"/>
+      <c r="G79" s="162" t="n"/>
+      <c r="H79" s="162" t="n"/>
+      <c r="I79" s="162" t="n"/>
+      <c r="J79" s="137">
         <f>SUM(C66:I66)</f>
         <v/>
       </c>
     </row>
-    <row r="80" ht="17.25" customHeight="1" s="82">
-      <c r="A80" s="149" t="n"/>
-      <c r="B80" s="72" t="inlineStr">
+    <row r="80" ht="17.25" customHeight="1" s="78">
+      <c r="A80" s="88" t="n"/>
+      <c r="B80" s="68" t="inlineStr">
         <is>
           <t>심장수술비</t>
         </is>
       </c>
-      <c r="C80" s="140" t="n"/>
-      <c r="D80" s="140" t="n"/>
-      <c r="E80" s="140" t="n"/>
-      <c r="F80" s="140" t="n"/>
-      <c r="G80" s="140" t="n"/>
-      <c r="H80" s="140" t="n"/>
-      <c r="I80" s="140" t="n"/>
-      <c r="J80" s="122">
+      <c r="C80" s="162" t="n"/>
+      <c r="D80" s="162" t="n"/>
+      <c r="E80" s="162" t="n"/>
+      <c r="F80" s="162" t="n"/>
+      <c r="G80" s="162" t="n"/>
+      <c r="H80" s="162" t="n"/>
+      <c r="I80" s="162" t="n"/>
+      <c r="J80" s="137">
         <f>SUM(C67:I67)</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="17.25" customHeight="1" s="82">
-      <c r="A81" s="149" t="n"/>
-      <c r="B81" s="61" t="inlineStr">
+    <row r="81" ht="17.25" customHeight="1" s="78" thickBot="1">
+      <c r="A81" s="88" t="n"/>
+      <c r="B81" s="60" t="inlineStr">
         <is>
           <t>120대수술비</t>
         </is>
       </c>
-      <c r="C81" s="140" t="n"/>
-      <c r="D81" s="140" t="n"/>
-      <c r="E81" s="140" t="n"/>
-      <c r="F81" s="140" t="n"/>
-      <c r="G81" s="140" t="n"/>
-      <c r="H81" s="140" t="n"/>
-      <c r="I81" s="140" t="n"/>
-      <c r="J81" s="141">
+      <c r="C81" s="162" t="n"/>
+      <c r="D81" s="162" t="n"/>
+      <c r="E81" s="162" t="n"/>
+      <c r="F81" s="162" t="n"/>
+      <c r="G81" s="162" t="n"/>
+      <c r="H81" s="162" t="n"/>
+      <c r="I81" s="162" t="n"/>
+      <c r="J81" s="163">
         <f>SUM(C68:I68)</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="16.5" customHeight="1" s="82">
-      <c r="A82" s="149" t="n"/>
-      <c r="B82" s="73" t="inlineStr">
+    <row r="82" ht="16.5" customHeight="1" s="78">
+      <c r="A82" s="88" t="n"/>
+      <c r="B82" s="69" t="inlineStr">
         <is>
           <t>5대기관 수술비 관혈</t>
         </is>
       </c>
-      <c r="C82" s="123" t="n"/>
-      <c r="D82" s="123" t="n"/>
-      <c r="E82" s="123" t="n"/>
-      <c r="F82" s="123" t="n"/>
-      <c r="G82" s="123" t="n"/>
-      <c r="H82" s="123" t="n"/>
-      <c r="I82" s="123" t="n"/>
-      <c r="J82" s="120">
+      <c r="C82" s="138" t="n"/>
+      <c r="D82" s="138" t="n"/>
+      <c r="E82" s="138" t="n"/>
+      <c r="F82" s="138" t="n"/>
+      <c r="G82" s="138" t="n"/>
+      <c r="H82" s="138" t="n"/>
+      <c r="I82" s="138" t="n"/>
+      <c r="J82" s="135">
         <f>SUM(C69:I69)</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="17.25" customHeight="1" s="82">
-      <c r="A83" s="149" t="n"/>
-      <c r="B83" s="74" t="inlineStr">
+    <row r="83" ht="17.25" customHeight="1" s="78" thickBot="1">
+      <c r="A83" s="89" t="n"/>
+      <c r="B83" s="70" t="inlineStr">
         <is>
           <t>5대기관 수술비 비관혈</t>
         </is>
       </c>
-      <c r="C83" s="117" t="n"/>
-      <c r="D83" s="117" t="n"/>
-      <c r="E83" s="117" t="n"/>
-      <c r="F83" s="117" t="n"/>
-      <c r="G83" s="117" t="n"/>
-      <c r="H83" s="117" t="n"/>
-      <c r="I83" s="117" t="n"/>
-      <c r="J83" s="118">
+      <c r="C83" s="132" t="n"/>
+      <c r="D83" s="132" t="n"/>
+      <c r="E83" s="132" t="n"/>
+      <c r="F83" s="132" t="n"/>
+      <c r="G83" s="132" t="n"/>
+      <c r="H83" s="132" t="n"/>
+      <c r="I83" s="132" t="n"/>
+      <c r="J83" s="133">
         <f>SUM(C70:I70)</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="16.5" customHeight="1" s="82">
-      <c r="A84" s="150" t="inlineStr">
+    <row r="84" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A84" s="93" t="inlineStr">
         <is>
           <t>운전</t>
         </is>
@@ -3034,193 +3096,193 @@
           <t>대인</t>
         </is>
       </c>
-      <c r="C84" s="102" t="n"/>
-      <c r="D84" s="102" t="n"/>
-      <c r="E84" s="102" t="n"/>
-      <c r="F84" s="102" t="n"/>
-      <c r="G84" s="102" t="n"/>
-      <c r="H84" s="102" t="n"/>
-      <c r="I84" s="102" t="n"/>
-      <c r="J84" s="120">
+      <c r="C84" s="117" t="n"/>
+      <c r="D84" s="117" t="n"/>
+      <c r="E84" s="117" t="n"/>
+      <c r="F84" s="117" t="n"/>
+      <c r="G84" s="117" t="n"/>
+      <c r="H84" s="117" t="n"/>
+      <c r="I84" s="117" t="n"/>
+      <c r="J84" s="135">
         <f>SUM(C71:I71)</f>
         <v/>
       </c>
     </row>
-    <row r="85" ht="17.25" customHeight="1" s="82">
-      <c r="A85" s="149" t="n"/>
+    <row r="85" ht="17.25" customHeight="1" s="78">
+      <c r="A85" s="92" t="n"/>
       <c r="B85" s="31" t="inlineStr">
         <is>
           <t>대물</t>
         </is>
       </c>
-      <c r="C85" s="130" t="n"/>
-      <c r="D85" s="130" t="n"/>
-      <c r="E85" s="130" t="n"/>
-      <c r="F85" s="130" t="n"/>
-      <c r="G85" s="130" t="n"/>
-      <c r="H85" s="130" t="n"/>
-      <c r="I85" s="130" t="n"/>
-      <c r="J85" s="122">
+      <c r="C85" s="145" t="n"/>
+      <c r="D85" s="145" t="n"/>
+      <c r="E85" s="145" t="n"/>
+      <c r="F85" s="145" t="n"/>
+      <c r="G85" s="145" t="n"/>
+      <c r="H85" s="145" t="n"/>
+      <c r="I85" s="145" t="n"/>
+      <c r="J85" s="137">
         <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="16.5" customHeight="1" s="82">
-      <c r="A86" s="149" t="n"/>
+    <row r="86" ht="16.5" customHeight="1" s="78">
+      <c r="A86" s="92" t="n"/>
       <c r="B86" s="31" t="inlineStr">
         <is>
           <t>합의금</t>
         </is>
       </c>
-      <c r="C86" s="130" t="n"/>
-      <c r="D86" s="130" t="n"/>
-      <c r="E86" s="130" t="n"/>
-      <c r="F86" s="130" t="n"/>
-      <c r="G86" s="130" t="n"/>
-      <c r="H86" s="130" t="n"/>
-      <c r="I86" s="130" t="n"/>
-      <c r="J86" s="122">
+      <c r="C86" s="145" t="n"/>
+      <c r="D86" s="145" t="n"/>
+      <c r="E86" s="145" t="n"/>
+      <c r="F86" s="145" t="n"/>
+      <c r="G86" s="145" t="n"/>
+      <c r="H86" s="145" t="n"/>
+      <c r="I86" s="145" t="n"/>
+      <c r="J86" s="137">
         <f>SUM(C73:I73)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="16.5" customHeight="1" s="82">
-      <c r="A87" s="149" t="n"/>
-      <c r="B87" s="66" t="inlineStr">
+    <row r="87" ht="16.5" customHeight="1" s="78">
+      <c r="A87" s="92" t="n"/>
+      <c r="B87" s="65" t="inlineStr">
         <is>
           <t>6주미만</t>
         </is>
       </c>
-      <c r="C87" s="130" t="n"/>
-      <c r="D87" s="130" t="n"/>
-      <c r="E87" s="130" t="n"/>
-      <c r="F87" s="130" t="n"/>
-      <c r="G87" s="130" t="n"/>
-      <c r="H87" s="130" t="n"/>
-      <c r="I87" s="130" t="n"/>
-      <c r="J87" s="122">
+      <c r="C87" s="145" t="n"/>
+      <c r="D87" s="145" t="n"/>
+      <c r="E87" s="145" t="n"/>
+      <c r="F87" s="145" t="n"/>
+      <c r="G87" s="145" t="n"/>
+      <c r="H87" s="145" t="n"/>
+      <c r="I87" s="145" t="n"/>
+      <c r="J87" s="137">
         <f>SUM(C74:I74)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="17.25" customHeight="1" s="82">
-      <c r="A88" s="149" t="n"/>
+    <row r="88" ht="17.25" customHeight="1" s="78">
+      <c r="A88" s="92" t="n"/>
       <c r="B88" s="31" t="inlineStr">
         <is>
           <t>변호사</t>
         </is>
       </c>
-      <c r="C88" s="130" t="n"/>
-      <c r="D88" s="130" t="n"/>
-      <c r="E88" s="130" t="n"/>
-      <c r="F88" s="130" t="n"/>
-      <c r="G88" s="130" t="n"/>
-      <c r="H88" s="130" t="n"/>
-      <c r="I88" s="130" t="n"/>
-      <c r="J88" s="122">
+      <c r="C88" s="145" t="n"/>
+      <c r="D88" s="145" t="n"/>
+      <c r="E88" s="145" t="n"/>
+      <c r="F88" s="145" t="n"/>
+      <c r="G88" s="145" t="n"/>
+      <c r="H88" s="145" t="n"/>
+      <c r="I88" s="145" t="n"/>
+      <c r="J88" s="137">
         <f>SUM(C75:I75)</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="17.25" customHeight="1" s="82">
-      <c r="A89" s="151" t="n"/>
+    <row r="89" ht="17.25" customHeight="1" s="78">
+      <c r="A89" s="94" t="n"/>
       <c r="B89" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C89" s="142" t="n"/>
-      <c r="D89" s="142" t="n"/>
-      <c r="E89" s="142" t="n"/>
-      <c r="F89" s="142" t="n"/>
-      <c r="G89" s="142" t="n"/>
-      <c r="H89" s="142" t="n"/>
-      <c r="I89" s="142" t="n"/>
-      <c r="J89" s="118">
+      <c r="C89" s="164" t="n"/>
+      <c r="D89" s="164" t="n"/>
+      <c r="E89" s="164" t="n"/>
+      <c r="F89" s="164" t="n"/>
+      <c r="G89" s="164" t="n"/>
+      <c r="H89" s="164" t="n"/>
+      <c r="I89" s="164" t="n"/>
+      <c r="J89" s="133">
         <f>SUM(C76:I76)</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="150" t="inlineStr">
+      <c r="A90" s="93" t="inlineStr">
         <is>
           <t>골절</t>
         </is>
       </c>
-      <c r="B90" s="65" t="inlineStr">
+      <c r="B90" s="64" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C90" s="136" t="n"/>
-      <c r="D90" s="136" t="n"/>
-      <c r="E90" s="136" t="n"/>
-      <c r="F90" s="136" t="n"/>
-      <c r="G90" s="136" t="n"/>
-      <c r="H90" s="136" t="n"/>
-      <c r="I90" s="136" t="n"/>
-      <c r="J90" s="116">
+      <c r="C90" s="155" t="n"/>
+      <c r="D90" s="155" t="n"/>
+      <c r="E90" s="155" t="n"/>
+      <c r="F90" s="155" t="n"/>
+      <c r="G90" s="155" t="n"/>
+      <c r="H90" s="155" t="n"/>
+      <c r="I90" s="155" t="n"/>
+      <c r="J90" s="131">
         <f>SUM(C77:I77)</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="149" t="n"/>
-      <c r="B91" s="60" t="inlineStr">
+      <c r="A91" s="92" t="n"/>
+      <c r="B91" s="59" t="inlineStr">
         <is>
           <t>골절(치아파절제외)</t>
         </is>
       </c>
-      <c r="C91" s="121" t="n"/>
-      <c r="D91" s="121" t="n"/>
-      <c r="E91" s="121" t="n"/>
-      <c r="F91" s="121" t="n"/>
-      <c r="G91" s="121" t="n"/>
-      <c r="H91" s="121" t="n"/>
-      <c r="I91" s="121" t="n"/>
-      <c r="J91" s="122">
+      <c r="C91" s="136" t="n"/>
+      <c r="D91" s="136" t="n"/>
+      <c r="E91" s="136" t="n"/>
+      <c r="F91" s="136" t="n"/>
+      <c r="G91" s="136" t="n"/>
+      <c r="H91" s="136" t="n"/>
+      <c r="I91" s="136" t="n"/>
+      <c r="J91" s="137">
         <f>SUM(C78:I78)</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="151" t="n"/>
-      <c r="B92" s="74" t="inlineStr">
+      <c r="A92" s="94" t="n"/>
+      <c r="B92" s="70" t="inlineStr">
         <is>
           <t>5대골절진단비</t>
         </is>
       </c>
-      <c r="C92" s="117" t="n"/>
-      <c r="D92" s="117" t="n"/>
-      <c r="E92" s="117" t="n"/>
-      <c r="F92" s="117" t="n"/>
-      <c r="G92" s="117" t="n"/>
-      <c r="H92" s="117" t="n"/>
-      <c r="I92" s="117" t="n"/>
-      <c r="J92" s="118">
+      <c r="C92" s="132" t="n"/>
+      <c r="D92" s="132" t="n"/>
+      <c r="E92" s="132" t="n"/>
+      <c r="F92" s="132" t="n"/>
+      <c r="G92" s="132" t="n"/>
+      <c r="H92" s="132" t="n"/>
+      <c r="I92" s="132" t="n"/>
+      <c r="J92" s="133">
         <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="99" t="inlineStr">
+      <c r="A93" s="95" t="inlineStr">
         <is>
           <t>응급실</t>
         </is>
       </c>
-      <c r="B93" s="64" t="inlineStr">
+      <c r="B93" s="63" t="inlineStr">
         <is>
           <t>응급실(응급)</t>
         </is>
       </c>
-      <c r="C93" s="113" t="n"/>
-      <c r="D93" s="113" t="n"/>
-      <c r="E93" s="113" t="n"/>
-      <c r="F93" s="113" t="n"/>
-      <c r="G93" s="113" t="n"/>
-      <c r="H93" s="113" t="n"/>
-      <c r="I93" s="113" t="n"/>
-      <c r="J93" s="114">
+      <c r="C93" s="128" t="n"/>
+      <c r="D93" s="128" t="n"/>
+      <c r="E93" s="128" t="n"/>
+      <c r="F93" s="128" t="n"/>
+      <c r="G93" s="128" t="n"/>
+      <c r="H93" s="128" t="n"/>
+      <c r="I93" s="128" t="n"/>
+      <c r="J93" s="129">
         <f>SUM(C80:I80)</f>
         <v/>
       </c>
@@ -3236,17 +3298,17 @@
           <t>독감</t>
         </is>
       </c>
-      <c r="C94" s="123" t="n"/>
-      <c r="D94" s="123" t="n"/>
-      <c r="E94" s="123" t="n"/>
-      <c r="F94" s="123" t="n"/>
-      <c r="G94" s="123" t="n"/>
-      <c r="H94" s="123" t="n"/>
-      <c r="I94" s="123" t="n"/>
-      <c r="J94" s="124" t="n"/>
-    </row>
-    <row r="95" s="82">
-      <c r="A95" s="150" t="inlineStr">
+      <c r="C94" s="138" t="n"/>
+      <c r="D94" s="138" t="n"/>
+      <c r="E94" s="138" t="n"/>
+      <c r="F94" s="138" t="n"/>
+      <c r="G94" s="138" t="n"/>
+      <c r="H94" s="138" t="n"/>
+      <c r="I94" s="138" t="n"/>
+      <c r="J94" s="139" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="93" t="inlineStr">
         <is>
           <t>화상</t>
         </is>
@@ -3256,171 +3318,171 @@
           <t>화상진단비</t>
         </is>
       </c>
-      <c r="C95" s="119" t="n"/>
-      <c r="D95" s="119" t="n"/>
-      <c r="E95" s="119" t="n"/>
-      <c r="F95" s="119" t="n"/>
-      <c r="G95" s="119" t="n"/>
-      <c r="H95" s="119" t="n"/>
-      <c r="I95" s="119" t="n"/>
-      <c r="J95" s="120">
+      <c r="C95" s="134" t="n"/>
+      <c r="D95" s="134" t="n"/>
+      <c r="E95" s="134" t="n"/>
+      <c r="F95" s="134" t="n"/>
+      <c r="G95" s="134" t="n"/>
+      <c r="H95" s="134" t="n"/>
+      <c r="I95" s="134" t="n"/>
+      <c r="J95" s="135">
         <f>SUM(C82:I82)</f>
         <v/>
       </c>
     </row>
-    <row r="96" s="82">
-      <c r="A96" s="151" t="n"/>
+    <row r="96">
+      <c r="A96" s="94" t="n"/>
       <c r="B96" s="25" t="inlineStr">
         <is>
           <t>중증화상진단비</t>
         </is>
       </c>
-      <c r="C96" s="117" t="n"/>
-      <c r="D96" s="117" t="n"/>
-      <c r="E96" s="117" t="n"/>
-      <c r="F96" s="117" t="n"/>
-      <c r="G96" s="117" t="n"/>
-      <c r="H96" s="117" t="n"/>
-      <c r="I96" s="117" t="n"/>
-      <c r="J96" s="118">
+      <c r="C96" s="132" t="n"/>
+      <c r="D96" s="132" t="n"/>
+      <c r="E96" s="132" t="n"/>
+      <c r="F96" s="132" t="n"/>
+      <c r="G96" s="132" t="n"/>
+      <c r="H96" s="132" t="n"/>
+      <c r="I96" s="132" t="n"/>
+      <c r="J96" s="133">
         <f>SUM(C83:I83)</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="150" t="inlineStr">
+      <c r="A97" s="93" t="inlineStr">
         <is>
           <t>깁스</t>
         </is>
       </c>
-      <c r="B97" s="95" t="inlineStr">
+      <c r="B97" s="90" t="inlineStr">
         <is>
           <t>반깁스</t>
         </is>
       </c>
-      <c r="C97" s="119" t="n"/>
-      <c r="D97" s="119" t="n"/>
-      <c r="E97" s="119" t="n"/>
-      <c r="F97" s="119" t="n"/>
-      <c r="G97" s="119" t="n"/>
-      <c r="H97" s="119" t="n"/>
-      <c r="I97" s="119" t="n"/>
-      <c r="J97" s="120">
+      <c r="C97" s="134" t="n"/>
+      <c r="D97" s="134" t="n"/>
+      <c r="E97" s="134" t="n"/>
+      <c r="F97" s="134" t="n"/>
+      <c r="G97" s="134" t="n"/>
+      <c r="H97" s="134" t="n"/>
+      <c r="I97" s="134" t="n"/>
+      <c r="J97" s="135">
         <f>SUM(C84:I84)</f>
         <v/>
       </c>
     </row>
-    <row r="98" s="82">
-      <c r="A98" s="151" t="n"/>
-      <c r="B98" s="57" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="94" t="n"/>
+      <c r="B98" s="56" t="inlineStr">
         <is>
           <t>깁스진단비</t>
         </is>
       </c>
-      <c r="C98" s="117" t="n"/>
-      <c r="D98" s="117" t="n"/>
-      <c r="E98" s="117" t="n"/>
-      <c r="F98" s="117" t="n"/>
-      <c r="G98" s="117" t="n"/>
-      <c r="H98" s="117" t="n"/>
-      <c r="I98" s="117" t="n"/>
-      <c r="J98" s="118">
+      <c r="C98" s="132" t="n"/>
+      <c r="D98" s="132" t="n"/>
+      <c r="E98" s="132" t="n"/>
+      <c r="F98" s="132" t="n"/>
+      <c r="G98" s="132" t="n"/>
+      <c r="H98" s="132" t="n"/>
+      <c r="I98" s="132" t="n"/>
+      <c r="J98" s="133">
         <f>SUM(C85:I85)</f>
         <v/>
       </c>
     </row>
-    <row r="99" s="82">
-      <c r="A99" s="150" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="93" t="inlineStr">
         <is>
           <t>실손</t>
         </is>
       </c>
-      <c r="B99" s="95" t="inlineStr">
+      <c r="B99" s="90" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="C99" s="143" t="n"/>
-      <c r="D99" s="143" t="n"/>
-      <c r="E99" s="143" t="n"/>
-      <c r="F99" s="143" t="n"/>
-      <c r="G99" s="143" t="n"/>
-      <c r="H99" s="143" t="n"/>
-      <c r="I99" s="143" t="n"/>
-      <c r="J99" s="120">
+      <c r="C99" s="165" t="n"/>
+      <c r="D99" s="165" t="n"/>
+      <c r="E99" s="165" t="n"/>
+      <c r="F99" s="165" t="n"/>
+      <c r="G99" s="165" t="n"/>
+      <c r="H99" s="165" t="n"/>
+      <c r="I99" s="165" t="n"/>
+      <c r="J99" s="135">
         <f>SUM(C86:I86)</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="149" t="n"/>
-      <c r="B100" s="60" t="inlineStr">
+      <c r="A100" s="92" t="n"/>
+      <c r="B100" s="59" t="inlineStr">
         <is>
           <t>통원</t>
         </is>
       </c>
-      <c r="C100" s="144" t="n"/>
-      <c r="D100" s="144" t="n"/>
-      <c r="E100" s="144" t="n"/>
-      <c r="F100" s="144" t="n"/>
-      <c r="G100" s="144" t="n"/>
-      <c r="H100" s="144" t="n"/>
-      <c r="I100" s="144" t="n"/>
-      <c r="J100" s="122">
+      <c r="C100" s="166" t="n"/>
+      <c r="D100" s="166" t="n"/>
+      <c r="E100" s="166" t="n"/>
+      <c r="F100" s="166" t="n"/>
+      <c r="G100" s="166" t="n"/>
+      <c r="H100" s="166" t="n"/>
+      <c r="I100" s="166" t="n"/>
+      <c r="J100" s="137">
         <f>SUM(C87:I87)</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="149" t="n"/>
-      <c r="B101" s="22" t="inlineStr">
+      <c r="A101" s="92" t="n"/>
+      <c r="B101" s="59" t="inlineStr">
         <is>
           <t>약값</t>
         </is>
       </c>
-      <c r="C101" s="115" t="n"/>
-      <c r="D101" s="115" t="n"/>
-      <c r="E101" s="115" t="n"/>
-      <c r="F101" s="115" t="n"/>
-      <c r="G101" s="115" t="n"/>
-      <c r="H101" s="115" t="n"/>
-      <c r="I101" s="145" t="n"/>
-      <c r="J101" s="122">
+      <c r="C101" s="136" t="n"/>
+      <c r="D101" s="136" t="n"/>
+      <c r="E101" s="136" t="n"/>
+      <c r="F101" s="136" t="n"/>
+      <c r="G101" s="136" t="n"/>
+      <c r="H101" s="136" t="n"/>
+      <c r="I101" s="166" t="n"/>
+      <c r="J101" s="137">
         <f>SUM(C88:I88)</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="149" t="n"/>
-      <c r="B102" s="22" t="inlineStr">
+      <c r="A102" s="92" t="n"/>
+      <c r="B102" s="59" t="inlineStr">
         <is>
           <t>MRI/도수치료/비급여주사</t>
         </is>
       </c>
-      <c r="C102" s="115" t="n"/>
-      <c r="D102" s="115" t="n"/>
-      <c r="E102" s="115" t="n"/>
-      <c r="F102" s="115" t="n"/>
-      <c r="G102" s="115" t="n"/>
-      <c r="H102" s="115" t="n"/>
-      <c r="I102" s="145" t="n"/>
-      <c r="J102" s="122" t="n"/>
+      <c r="C102" s="136" t="n"/>
+      <c r="D102" s="136" t="n"/>
+      <c r="E102" s="136" t="n"/>
+      <c r="F102" s="136" t="n"/>
+      <c r="G102" s="136" t="n"/>
+      <c r="H102" s="136" t="n"/>
+      <c r="I102" s="166" t="n"/>
+      <c r="J102" s="131" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="151" t="n"/>
+      <c r="A103" s="94" t="n"/>
       <c r="B103" s="22" t="inlineStr">
         <is>
           <t>상해의료비</t>
         </is>
       </c>
-      <c r="C103" s="115" t="n"/>
-      <c r="D103" s="115" t="n"/>
-      <c r="E103" s="115" t="n"/>
-      <c r="F103" s="115" t="n"/>
-      <c r="G103" s="115" t="n"/>
-      <c r="H103" s="115" t="n"/>
-      <c r="I103" s="145" t="n"/>
-      <c r="J103" s="122" t="n"/>
+      <c r="C103" s="130" t="n"/>
+      <c r="D103" s="130" t="n"/>
+      <c r="E103" s="130" t="n"/>
+      <c r="F103" s="130" t="n"/>
+      <c r="G103" s="130" t="n"/>
+      <c r="H103" s="130" t="n"/>
+      <c r="I103" s="167" t="n"/>
+      <c r="J103" s="137" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="87" t="inlineStr">
@@ -3428,19 +3490,19 @@
           <t>일배책</t>
         </is>
       </c>
-      <c r="B104" s="79" t="inlineStr">
+      <c r="B104" s="75" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C104" s="146" t="n"/>
-      <c r="D104" s="146" t="n"/>
-      <c r="E104" s="146" t="n"/>
-      <c r="F104" s="146" t="n"/>
-      <c r="G104" s="146" t="n"/>
-      <c r="H104" s="146" t="n"/>
-      <c r="I104" s="146" t="n"/>
-      <c r="J104" s="147">
+      <c r="C104" s="168" t="n"/>
+      <c r="D104" s="168" t="n"/>
+      <c r="E104" s="168" t="n"/>
+      <c r="F104" s="168" t="n"/>
+      <c r="G104" s="168" t="n"/>
+      <c r="H104" s="168" t="n"/>
+      <c r="I104" s="168" t="n"/>
+      <c r="J104" s="169">
         <f>SUM(C89:I89)</f>
         <v/>
       </c>
@@ -3455,8 +3517,8 @@
     <mergeCell ref="A15:A29"/>
     <mergeCell ref="A52:A64"/>
     <mergeCell ref="A39:A51"/>
+    <mergeCell ref="A90:A92"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A90:A92"/>
     <mergeCell ref="A99:A103"/>
     <mergeCell ref="A95:A96"/>
     <mergeCell ref="A11:A14"/>
@@ -3479,156 +3541,156 @@
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="17.4"/>
   <cols>
-    <col width="5" customWidth="1" style="82" min="1" max="1"/>
-    <col width="110" customWidth="1" style="82" min="2" max="2"/>
+    <col width="5" customWidth="1" style="78" min="1" max="1"/>
+    <col width="110" customWidth="1" style="78" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1" s="82">
-      <c r="A1" s="83" t="inlineStr">
+    <row r="1" ht="20.1" customHeight="1" s="78">
+      <c r="A1" s="79" t="inlineStr">
         <is>
           <t>바름 보장분석 법칙 v2 — 이 표본에 내장 (2026.06.09)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="17.1" customHeight="1" s="82">
+    <row r="3" ht="17.1" customHeight="1" s="78">
       <c r="A3" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="84" t="inlineStr">
+      <c r="B3" s="80" t="inlineStr">
         <is>
           <t>폼 무변형: 이 표본을 열어 값만 채운다. 새 워크북·행삭제·카테고리축소 금지. 추가만(그룹 안 행삽입), 표 밖 금지.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17.1" customHeight="1" s="82">
+    <row r="4" ht="17.1" customHeight="1" s="78">
       <c r="A4" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="84" t="inlineStr">
+      <c r="B4" s="80" t="inlineStr">
         <is>
           <t>새 고객 입력 시 이전 고객 값 전부 zero화(이 표본에서 새로 시작).</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="17.1" customHeight="1" s="82">
+    <row r="5" ht="17.1" customHeight="1" s="78">
       <c r="A5" s="0" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
+      <c r="B5" s="80" t="inlineStr">
         <is>
           <t>열=계약(최대 50). 행=담보(15구분·82행). 끝열=합계.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="17.1" customHeight="1" s="82">
+    <row r="6" ht="17.1" customHeight="1" s="78">
       <c r="A6" s="0" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="84" t="inlineStr">
+      <c r="B6" s="80" t="inlineStr">
         <is>
           <t>합계 = 세로(계약별) SUM. 4페이지 한장보장 값을 합계칸 직박음 금지(눈속임). 계약별 칸을 채워야 합계가 산다.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.1" customHeight="1" s="82">
+    <row r="7" ht="17.1" customHeight="1" s="78">
       <c r="A7" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B7" s="84" t="inlineStr">
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>계약별 대조 필수: A담보가 B회사 칸으로 가면 안 됨.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="17.1" customHeight="1" s="82">
+    <row r="8" ht="17.1" customHeight="1" s="78">
       <c r="A8" s="0" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="85" t="inlineStr">
+      <c r="B8" s="81" t="inlineStr">
         <is>
           <t>1~5종 수술비 = 질병/상해 각 1행, 슬래시 가로표기 "20/50/100/500/1000", 합계도 종별.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="17.1" customHeight="1" s="82">
+    <row r="9" ht="17.1" customHeight="1" s="78">
       <c r="A9" s="0" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B9" s="84" t="inlineStr">
+      <c r="B9" s="80" t="inlineStr">
         <is>
           <t>갱신/비갱신: ①갱신형명시→갱신 ②운전자→비갱신 ③9999→비갱신 ④총회차240초과→비갱신 ⑤납입년수≠보장년수→비갱신.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="17.1" customHeight="1" s="82">
+    <row r="10" ht="17.1" customHeight="1" s="78">
       <c r="A10" s="0" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B10" s="84" t="inlineStr">
+      <c r="B10" s="80" t="inlineStr">
         <is>
           <t>색: 갱신=파랑 / 비갱신=검정 / 미가입=빨강. 구분셀=연두. 헤더 갱신블루·비갱신레드·완납진녹.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="17.1" customHeight="1" s="82">
+    <row r="11" ht="17.1" customHeight="1" s="78">
       <c r="A11" s="0" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B11" s="84" t="inlineStr">
+      <c r="B11" s="80" t="inlineStr">
         <is>
           <t>심장=담보명 직행(허혈성→허혈성칸, 전파금지). 불확정은 기재+[확인].</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="17.1" customHeight="1" s="82">
+    <row r="12" ht="17.1" customHeight="1" s="78">
       <c r="A12" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" s="85" t="inlineStr">
+      <c r="B12" s="81" t="inlineStr">
         <is>
           <t>9999(생보)=종신 → 일반사망(종신)+상해사망. 손보 질병사망=80세칸.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="17.1" customHeight="1" s="82">
+    <row r="13" ht="17.1" customHeight="1" s="78">
       <c r="A13" s="0" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B13" s="84" t="inlineStr">
+      <c r="B13" s="80" t="inlineStr">
         <is>
           <t>추측 금지: 모르면 빈칸+[확인]. 채우는 게 최악, 비우고 메모가 차선, 확정 기재가 최선. 자동천장 95%.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="17.1" customHeight="1" s="82">
+    <row r="14" ht="17.1" customHeight="1" s="78">
       <c r="A14" s="0" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B14" s="84" t="inlineStr">
+      <c r="B14" s="80" t="inlineStr">
         <is>
           <t>엑셀=원천, PPT는 완성 엑셀만 읽음(PDF→엑셀→PPT). 제출 전 렌더검수 통과한 것만.</t>
         </is>
@@ -3638,4 +3700,1748 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
+  <cols>
+    <col width="12" customWidth="1" style="78" min="1" max="1"/>
+    <col width="34" customWidth="1" style="78" min="2" max="2"/>
+    <col width="40" customWidth="1" style="78" min="3" max="3"/>
+    <col width="26" customWidth="1" style="78" min="4" max="4"/>
+    <col width="30" customWidth="1" style="78" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.2" customHeight="1" s="78">
+      <c r="A1" s="83" t="inlineStr">
+        <is>
+          <t>★ 이 시트가 지침 체크봇의 정본이다. 여기에 행을 추가하면 앱이 매 분석마다 자동으로 검사한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>사용법 : 구분=케이스 / 조항 / 담보명(리포트에 인쇄된 그대로) / 기대행(마스터 B열 담보명 · 기재금지면 빈칸) — 행 추가만 하면 된다. 코드 수정 불필요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>구분=커버리지허용 : 마스터 라벨이 자기 행으로 안 돌아오는 것이 정상인 행(라벨≠담보명 설계분). 담보명 칸에 라벨을 적는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="84" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>조항</t>
+        </is>
+      </c>
+      <c r="C5" s="84" t="inlineStr">
+        <is>
+          <t>담보명</t>
+        </is>
+      </c>
+      <c r="D5" s="84" t="inlineStr">
+        <is>
+          <t>기대행(빈칸=기재금지)</t>
+        </is>
+      </c>
+      <c r="E5" s="84" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>2대질병입원일당</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>특정질병입원일당</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>3대질병입원일당</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>질병입원일당(1-180)</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>질병일당</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>질병일당</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>질병일당</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>질병입원</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>질병일당</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>상해입원일당(1-180)</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>상해일당</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>재해입원일당</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>상해일당</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>종합병원 질병입원일당</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>종합병원 질병입원일당</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>상급병원 질병입원일당</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>교통상해입원일당</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>암직접치료입원일당</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>암일당</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>입원급여금</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>질병일당</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 일당 계열 배정(v212·v303·v305)</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>간호간병통합서비스사용 질병입원일당</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>간호통합병동</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>갱신형 유사암진단비</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>유사암(갑.기.경.제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>소액암진단</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>유사암(갑.기.경.제)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>갱신형 갑상선암(초기제외)진단비</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>갑상샘암치료보험금</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>상피내암치료보험금</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B25" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t>갱신형 유사암수술비</t>
+        </is>
+      </c>
+      <c r="D25" s="0" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B26" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C26" s="0" t="inlineStr">
+        <is>
+          <t>암진단비(유사암제외)</t>
+        </is>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>일반암</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C27" s="0" t="inlineStr">
+        <is>
+          <t>16대특정암진단비</t>
+        </is>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>고액암</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>일반암직접치료비</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>암수술</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t>치매진단</t>
+        </is>
+      </c>
+      <c r="D29" s="0" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B30" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t>치매진단(경증)</t>
+        </is>
+      </c>
+      <c r="D30" s="0" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>§8.3 심장·부정맥(v217·단독담보 원칙)</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>심장부정맥고주파·냉각절제술보장</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>§8.3 심장·부정맥(v217·단독담보 원칙)</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>부정맥진단비</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>§8.3 심장·부정맥(v217·단독담보 원칙)</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>기타심장부정맥(I49)진단비</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>§8.3 심장·부정맥(v217·단독담보 원칙)</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>허혈성심장질환진단비</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t>허혈성 진단비</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>§8.3 심장·부정맥(v217·단독담보 원칙)</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>주요심뇌5대혈관수술비</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>§8.3 심장·부정맥(v217·단독담보 원칙)</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>심뇌혈관수술비</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t>뇌혈관수술비</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>§8.1 사망·후유장해(v222·v300·v302)</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>상해후유장해(20%이상)</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>§8.1 사망·후유장해(v222·v300·v302)</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>상해후유장해(50%이상)</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>§8.1 사망·후유장해(v222·v300·v302)</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>상해후유장해(3%이상)</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>상해후유3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>§8.1 사망·후유장해(v222·v300·v302)</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>재해장해연금</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>§8.1 사망·후유장해(v222·v300·v302)</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>재해후유장해3%</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>상해후유3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>§8.1 사망·후유장해(v222·v300·v302)</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>교통상해사망</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>교통상해사망</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>§8.1 사망·후유장해(v222·v300·v302)</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>대중교통상해사망</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>교통상해사망</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>§8.1 사망·후유장해(v222·v300·v302)</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>상해사망</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>상해사망</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>§8.6 운전자(v198·v301·v302)</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>타인사망교통사고처리지원금</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t>합의금</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>§8.6 운전자(v198·v301·v302)</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>교통사고처리지원금(중상해포함)</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t>합의금</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>§8.6 운전자(v198·v301·v302)</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>자동차사고부상치료비(14급)</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t>자부상</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>§8.6 운전자(v198·v301·v302)</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>교통사고 벌금(대인)</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>대인</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>§8.6 운전자(v198·v301·v302)</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>교통사고 벌금(대물)</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t>대물</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>§8.6 운전자(v198·v301·v302)</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>변호사선임비용</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>변호사</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>§8.6 운전자(v198·v301·v302)</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>6주미만 진단위로금</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>6주미만</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 골절·화상·기타(v301·v38c)</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>중증화상진단비</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="inlineStr">
+        <is>
+          <t>중증화상진단비</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 골절·화상·기타(v301·v38c)</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>화상진단비</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="inlineStr">
+        <is>
+          <t>화상진단비</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 골절·화상·기타(v301·v38c)</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>중대한화상및부식진단비</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="inlineStr">
+        <is>
+          <t>중증화상진단비</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 골절·화상·기타(v301·v38c)</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>골절진단비(치아파절제외)</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="inlineStr">
+        <is>
+          <t>골절(치아파절제외)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 골절·화상·기타(v301·v38c)</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>골절진단비</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="inlineStr">
+        <is>
+          <t>골절(치아파절포함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 골절·화상·기타(v301·v38c)</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>일상생활배상책임</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="inlineStr">
+        <is>
+          <t>일상배상책임</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>§8.7 골절·화상·기타(v301·v38c)</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>응급실내원비</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="inlineStr">
+        <is>
+          <t>응급실(응급)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>§8.5 수술·재해=상해(v304)</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>재해수술일당</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="inlineStr">
+        <is>
+          <t>상해수술일당</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>§8.5 수술·재해=상해(v304)</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>재해종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="inlineStr">
+        <is>
+          <t>상해 종수술비(1-5종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B61" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>120대수술비</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>MRI/도수치료/비급여주사</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>대인</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>상해 종수술비(1-3종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>상해 종수술비(1-8종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>암일당</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>약값</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>염증</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>일반암</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>입원</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>중대한 뇌출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>중대한CI적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-3종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-8종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B75" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C75" s="0" t="inlineStr">
+        <is>
+          <t>통원</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B76" s="0" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C76" s="0" t="inlineStr">
+        <is>
+          <t>항암방사선약물</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
+  <cols>
+    <col width="6" customWidth="1" style="78" min="1" max="1"/>
+    <col width="74" customWidth="1" style="78" min="2" max="2"/>
+    <col width="38" customWidth="1" style="78" min="3" max="3"/>
+    <col width="44" customWidth="1" style="78" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19.2" customHeight="1" s="78">
+      <c r="A1" s="83" t="inlineStr">
+        <is>
+          <t>★ 이 시트가 「관점」의 정본이다. 지침을 어떻게 읽을지를 여기서 고정한다. 앱이 매 분석마다 확인사항 시트 하단에 이 원문을 그대로 출력한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>사용법 : 지점장이 B열에 원칙을 문장으로 적는다. Claude는 이 문장을 요약·재구성하지 않고 그대로 인용해야 한다. 행 추가만 하면 되고 코드 수정은 필요 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="84" t="inlineStr">
+        <is>
+          <t>원칙 (지점장 원문 — 그대로 쓴다)</t>
+        </is>
+      </c>
+      <c r="C4" s="84" t="inlineStr">
+        <is>
+          <t>위반하면</t>
+        </is>
+      </c>
+      <c r="D4" s="84" t="inlineStr">
+        <is>
+          <t>근거·사례</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31.95" customHeight="1" s="78">
+      <c r="A5" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="81" t="inlineStr">
+        <is>
+          <t>지점장이 준 자료는 문구·코드를 그대로 쓴다. 요약·재구성하거나 해설 주석을 덧붙이지 않는다.</t>
+        </is>
+      </c>
+      <c r="C5" s="81" t="inlineStr">
+        <is>
+          <t>최종본과 달라 보여 같은 매핑을 반복해 틀린다</t>
+        </is>
+      </c>
+      <c r="D5" s="81" t="inlineStr">
+        <is>
+          <t>정본 관리 3원칙 ① · 2026.07.18 심장 매핑 4회 오류</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="31.95" customHeight="1" s="78">
+      <c r="A6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="81" t="inlineStr">
+        <is>
+          <t>지침에 없으면 추측하지 않는다 — 빈칸으로 두고 [확인]큐로 보낸다.</t>
+        </is>
+      </c>
+      <c r="C6" s="81" t="inlineStr">
+        <is>
+          <t>내 판단이 정본인 것처럼 산출물에 박힌다</t>
+        </is>
+      </c>
+      <c r="D6" s="81" t="inlineStr">
+        <is>
+          <t>§0 "모르면 빈칸+[확인], 추측 금지"</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="31.95" customHeight="1" s="78">
+      <c r="A7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="81" t="inlineStr">
+        <is>
+          <t>범위를 넓히려면 먼저 물어본다. 지점장이 두 개를 말했으면 두 개만 넣는다.</t>
+        </is>
+      </c>
+      <c r="C7" s="81" t="inlineStr">
+        <is>
+          <t>"나는 그걸 말한 적이 없다" — 임의 확장</t>
+        </is>
+      </c>
+      <c r="D7" s="81" t="inlineStr">
+        <is>
+          <t>(0f) 상해·재해 외에 교통·외래·대중교통까지 확장</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="31.95" customHeight="1" s="78">
+      <c r="A8" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="81" t="inlineStr">
+        <is>
+          <t>지침이 바뀌면 옛 내용을 남기지 말고 지운다. 세트로 내려온 지시는 전부 폐기·교체한다.</t>
+        </is>
+      </c>
+      <c r="C8" s="81" t="inlineStr">
+        <is>
+          <t>옛 규칙이 살아남아 그대로 나간다</t>
+        </is>
+      </c>
+      <c r="D8" s="81" t="inlineStr">
+        <is>
+          <t>정본 관리 3원칙 ② · 빈맥 규칙이 4곳에 잔존</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="31.95" customHeight="1" s="78">
+      <c r="A9" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="81" t="inlineStr">
+        <is>
+          <t>같은 데이터가 여러 곳에 있다 — 전수 수정하고 마지막에 옛 문구 잔재를 스캔한다.</t>
+        </is>
+      </c>
+      <c r="C9" s="81" t="inlineStr">
+        <is>
+          <t>반쪽 수정 — 한 곳만 고쳐 불일치가 남는다</t>
+        </is>
+      </c>
+      <c r="D9" s="81" t="inlineStr">
+        <is>
+          <t>정본 관리 3원칙 ③ · v210 색 규칙 3군데</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="31.95" customHeight="1" s="78">
+      <c r="A10" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="81" t="inlineStr">
+        <is>
+          <t>규칙 두 개가 같은 값을 만지면 나중 것이 앞 것을 죽인다. 새 규칙 전에 같은 셀을 쓰는 기존 규칙을 확인한다.</t>
+        </is>
+      </c>
+      <c r="C10" s="81" t="inlineStr">
+        <is>
+          <t>조용히 겹쳐 박히거나 앞 규칙이 무효가 된다</t>
+        </is>
+      </c>
+      <c r="D10" s="81" t="inlineStr">
+        <is>
+          <t>v245가 v240을 되돌림 · v266 중복 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="31.95" customHeight="1" s="78">
+      <c r="A11" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="81" t="inlineStr">
+        <is>
+          <t>직접 열어본 것만 "~이다"라고 쓴다. 안 본 것은 "가설"이라 명시한다. 측정하지 않은 수치는 말하지 않는다.</t>
+        </is>
+      </c>
+      <c r="C11" s="81" t="inlineStr">
+        <is>
+          <t>틀린 단정이 사실로 굳는다</t>
+        </is>
+      </c>
+      <c r="D11" s="81" t="inlineStr">
+        <is>
+          <t>(0a) · 2026.07.31 "v307은 존재하지 않는다" 오단정</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="31.95" customHeight="1" s="78">
+      <c r="A12" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="81" t="inlineStr">
+        <is>
+          <t>고장난 기능은 고치는 것이다 — 선택지로 만들어 지점장께 결정을 넘기지 않는다.</t>
+        </is>
+      </c>
+      <c r="C12" s="81" t="inlineStr">
+        <is>
+          <t>보고가 아니라 결정 위임이 된다</t>
+        </is>
+      </c>
+      <c r="D12" s="81" t="inlineStr">
+        <is>
+          <t>(0f) ci_sebu를 3선택지로 포장</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="31.95" customHeight="1" s="78">
+      <c r="A13" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="81" t="inlineStr">
+        <is>
+          <t>못 한 검증은 "못 했다"고 쓴다. 결과물만 올리지 않고 실행 과정을 보여준다.</t>
+        </is>
+      </c>
+      <c r="C13" s="81" t="inlineStr">
+        <is>
+          <t>"지침 돌렸다"는 말만 남고 실제로 안 돌아간다</t>
+        </is>
+      </c>
+      <c r="D13" s="81" t="inlineStr">
+        <is>
+          <t>(0e) "왜 결과물만 올리냐"</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="31.95" customHeight="1" s="78">
+      <c r="A14" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="81" t="inlineStr">
+        <is>
+          <t>규칙 하나를 고치면 2열(롯데)·3열(KB) 두 경로를 반드시 다 돌린다.</t>
+        </is>
+      </c>
+      <c r="C14" s="81" t="inlineStr">
+        <is>
+          <t>한 경로만 고쳐 다른 경로가 조용히 깨진다</t>
+        </is>
+      </c>
+      <c r="D14" s="81" t="inlineStr">
+        <is>
+          <t>제출 전 체크리스트 ⑨</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+</worksheet>
 </file>
--- a/master.xlsx
+++ b/master.xlsx
@@ -135,7 +135,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -213,8 +213,14 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="55">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -747,19 +753,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -881,20 +874,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right/>
-      <top/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -904,7 +897,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1112,7 +1105,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1136,7 +1129,7 @@
     <xf numFmtId="164" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1147,45 +1140,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="10" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1204,22 +1165,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1300,6 +1299,12 @@
     <xf numFmtId="164" fontId="5" fillId="8" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1330,7 +1335,7 @@
     <xf numFmtId="164" fontId="5" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1384,7 +1389,7 @@
     <xf numFmtId="164" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1510,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="78" min="1" max="1"/>
@@ -1524,15 +1529,15 @@
   </cols>
   <sheetData>
     <row r="1" ht="38.25" customHeight="1" s="78">
-      <c r="A1" s="98" t="n"/>
-      <c r="B1" s="99" t="n"/>
-      <c r="C1" s="115" t="n"/>
-      <c r="D1" s="115" t="n"/>
-      <c r="E1" s="115" t="n"/>
-      <c r="F1" s="115" t="n"/>
-      <c r="G1" s="115" t="n"/>
-      <c r="H1" s="115" t="n"/>
-      <c r="I1" s="116" t="n"/>
+      <c r="A1" s="112" t="n"/>
+      <c r="B1" s="113" t="n"/>
+      <c r="C1" s="117" t="n"/>
+      <c r="D1" s="117" t="n"/>
+      <c r="E1" s="117" t="n"/>
+      <c r="F1" s="117" t="n"/>
+      <c r="G1" s="117" t="n"/>
+      <c r="H1" s="117" t="n"/>
+      <c r="I1" s="118" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
           <t>합계</t>
@@ -1540,83 +1545,83 @@
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" s="78">
-      <c r="A2" s="90" t="inlineStr">
+      <c r="A2" s="104" t="inlineStr">
         <is>
           <t>보험료</t>
         </is>
       </c>
-      <c r="B2" s="91" t="n"/>
-      <c r="C2" s="117" t="n"/>
-      <c r="D2" s="117" t="n"/>
-      <c r="E2" s="117" t="n"/>
-      <c r="F2" s="117" t="n"/>
-      <c r="G2" s="117" t="n"/>
-      <c r="H2" s="117" t="n"/>
-      <c r="I2" s="117" t="n"/>
-      <c r="J2" s="118">
+      <c r="B2" s="105" t="n"/>
+      <c r="C2" s="119" t="n"/>
+      <c r="D2" s="119" t="n"/>
+      <c r="E2" s="119" t="n"/>
+      <c r="F2" s="119" t="n"/>
+      <c r="G2" s="119" t="n"/>
+      <c r="H2" s="119" t="n"/>
+      <c r="I2" s="119" t="n"/>
+      <c r="J2" s="120">
         <f>SUM(C2:I2)</f>
         <v/>
       </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" s="78">
-      <c r="A3" s="85" t="inlineStr">
+      <c r="A3" s="99" t="inlineStr">
         <is>
           <t>가입년일</t>
         </is>
       </c>
-      <c r="B3" s="86" t="n"/>
-      <c r="C3" s="119" t="n"/>
-      <c r="D3" s="119" t="n"/>
-      <c r="E3" s="119" t="n"/>
-      <c r="F3" s="119" t="n"/>
-      <c r="G3" s="119" t="n"/>
-      <c r="H3" s="119" t="n"/>
-      <c r="I3" s="119" t="n"/>
-      <c r="J3" s="120">
+      <c r="B3" s="100" t="n"/>
+      <c r="C3" s="121" t="n"/>
+      <c r="D3" s="121" t="n"/>
+      <c r="E3" s="121" t="n"/>
+      <c r="F3" s="121" t="n"/>
+      <c r="G3" s="121" t="n"/>
+      <c r="H3" s="121" t="n"/>
+      <c r="I3" s="121" t="n"/>
+      <c r="J3" s="122">
         <f>SUM(C3:I3)</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="16.5" customHeight="1" s="78">
-      <c r="A4" s="85" t="inlineStr">
+      <c r="A4" s="99" t="inlineStr">
         <is>
           <t>만기일자</t>
         </is>
       </c>
-      <c r="B4" s="86" t="n"/>
-      <c r="C4" s="121" t="n"/>
-      <c r="D4" s="121" t="n"/>
-      <c r="E4" s="121" t="n"/>
-      <c r="F4" s="121" t="n"/>
-      <c r="G4" s="121" t="n"/>
-      <c r="H4" s="121" t="n"/>
-      <c r="I4" s="121" t="n"/>
-      <c r="J4" s="120">
+      <c r="B4" s="100" t="n"/>
+      <c r="C4" s="123" t="n"/>
+      <c r="D4" s="123" t="n"/>
+      <c r="E4" s="123" t="n"/>
+      <c r="F4" s="123" t="n"/>
+      <c r="G4" s="123" t="n"/>
+      <c r="H4" s="123" t="n"/>
+      <c r="I4" s="123" t="n"/>
+      <c r="J4" s="122">
         <f>SUM(C4:I4)</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="17.25" customHeight="1" s="78">
-      <c r="A5" s="96" t="inlineStr">
+      <c r="A5" s="110" t="inlineStr">
         <is>
           <t>총납입기간</t>
         </is>
       </c>
-      <c r="B5" s="97" t="n"/>
-      <c r="C5" s="122" t="n"/>
-      <c r="D5" s="122" t="n"/>
-      <c r="E5" s="122" t="n"/>
-      <c r="F5" s="122" t="n"/>
-      <c r="G5" s="122" t="n"/>
-      <c r="H5" s="122" t="n"/>
-      <c r="I5" s="122" t="n"/>
-      <c r="J5" s="123">
+      <c r="B5" s="111" t="n"/>
+      <c r="C5" s="124" t="n"/>
+      <c r="D5" s="124" t="n"/>
+      <c r="E5" s="124" t="n"/>
+      <c r="F5" s="124" t="n"/>
+      <c r="G5" s="124" t="n"/>
+      <c r="H5" s="124" t="n"/>
+      <c r="I5" s="124" t="n"/>
+      <c r="J5" s="125">
         <f>SUM(C5:I5)</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="78">
-      <c r="A6" s="87" t="inlineStr">
+      <c r="A6" s="101" t="inlineStr">
         <is>
           <t>사망</t>
         </is>
@@ -1626,96 +1631,96 @@
           <t>일반사망</t>
         </is>
       </c>
-      <c r="C6" s="124" t="n"/>
-      <c r="D6" s="124" t="n"/>
-      <c r="E6" s="124" t="n"/>
-      <c r="F6" s="124" t="n"/>
-      <c r="G6" s="124" t="n"/>
-      <c r="H6" s="124" t="n"/>
-      <c r="I6" s="124" t="n"/>
-      <c r="J6" s="125">
+      <c r="C6" s="126" t="n"/>
+      <c r="D6" s="126" t="n"/>
+      <c r="E6" s="126" t="n"/>
+      <c r="F6" s="126" t="n"/>
+      <c r="G6" s="126" t="n"/>
+      <c r="H6" s="126" t="n"/>
+      <c r="I6" s="126" t="n"/>
+      <c r="J6" s="127">
         <f>SUM(C6:I6)</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1" s="78">
-      <c r="A7" s="88" t="n"/>
+      <c r="A7" s="102" t="n"/>
       <c r="B7" s="16" t="inlineStr">
         <is>
           <t>중대한CI적용</t>
         </is>
       </c>
-      <c r="C7" s="126" t="n"/>
-      <c r="D7" s="126" t="n"/>
-      <c r="E7" s="126" t="n"/>
-      <c r="F7" s="126" t="n"/>
-      <c r="G7" s="126" t="n"/>
-      <c r="H7" s="126" t="n"/>
-      <c r="I7" s="126" t="n"/>
-      <c r="J7" s="127">
+      <c r="C7" s="128" t="n"/>
+      <c r="D7" s="128" t="n"/>
+      <c r="E7" s="128" t="n"/>
+      <c r="F7" s="128" t="n"/>
+      <c r="G7" s="128" t="n"/>
+      <c r="H7" s="128" t="n"/>
+      <c r="I7" s="128" t="n"/>
+      <c r="J7" s="129">
         <f>SUM(C7:I7)</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="17.25" customHeight="1" s="78">
-      <c r="A8" s="88" t="n"/>
+      <c r="A8" s="102" t="n"/>
       <c r="B8" s="19" t="inlineStr">
         <is>
           <t>질병사망(80세)</t>
         </is>
       </c>
-      <c r="C8" s="128" t="n"/>
-      <c r="D8" s="128" t="n"/>
-      <c r="E8" s="128" t="n"/>
-      <c r="F8" s="128" t="n"/>
-      <c r="G8" s="128" t="n"/>
-      <c r="H8" s="128" t="n"/>
-      <c r="I8" s="128" t="n"/>
-      <c r="J8" s="129">
+      <c r="C8" s="130" t="n"/>
+      <c r="D8" s="130" t="n"/>
+      <c r="E8" s="130" t="n"/>
+      <c r="F8" s="130" t="n"/>
+      <c r="G8" s="130" t="n"/>
+      <c r="H8" s="130" t="n"/>
+      <c r="I8" s="130" t="n"/>
+      <c r="J8" s="131">
         <f>SUM(C8:I8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="78">
-      <c r="A9" s="88" t="n"/>
+      <c r="A9" s="102" t="n"/>
       <c r="B9" s="22" t="inlineStr">
         <is>
           <t>교통상해사망</t>
         </is>
       </c>
-      <c r="C9" s="130" t="n"/>
-      <c r="D9" s="130" t="n"/>
-      <c r="E9" s="130" t="n"/>
-      <c r="F9" s="130" t="n"/>
-      <c r="G9" s="130" t="n"/>
-      <c r="H9" s="130" t="n"/>
-      <c r="I9" s="130" t="n"/>
-      <c r="J9" s="131">
+      <c r="C9" s="132" t="n"/>
+      <c r="D9" s="132" t="n"/>
+      <c r="E9" s="132" t="n"/>
+      <c r="F9" s="132" t="n"/>
+      <c r="G9" s="132" t="n"/>
+      <c r="H9" s="132" t="n"/>
+      <c r="I9" s="132" t="n"/>
+      <c r="J9" s="133">
         <f>SUM(C9:I9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="17.25" customHeight="1" s="78">
-      <c r="A10" s="89" t="n"/>
+      <c r="A10" s="103" t="n"/>
       <c r="B10" s="25" t="inlineStr">
         <is>
           <t>상해사망</t>
         </is>
       </c>
-      <c r="C10" s="132" t="n"/>
-      <c r="D10" s="132" t="n"/>
-      <c r="E10" s="132" t="n"/>
-      <c r="F10" s="132" t="n"/>
-      <c r="G10" s="132" t="n"/>
-      <c r="H10" s="132" t="n"/>
-      <c r="I10" s="132" t="n"/>
-      <c r="J10" s="133">
+      <c r="C10" s="134" t="n"/>
+      <c r="D10" s="134" t="n"/>
+      <c r="E10" s="134" t="n"/>
+      <c r="F10" s="134" t="n"/>
+      <c r="G10" s="134" t="n"/>
+      <c r="H10" s="134" t="n"/>
+      <c r="I10" s="134" t="n"/>
+      <c r="J10" s="135">
         <f>SUM(C10:I10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="78">
-      <c r="A11" s="87" t="inlineStr">
+      <c r="A11" s="101" t="inlineStr">
         <is>
           <t>후유장애</t>
         </is>
@@ -1725,77 +1730,77 @@
           <t>상해후유3%</t>
         </is>
       </c>
-      <c r="C11" s="134" t="n"/>
-      <c r="D11" s="134" t="n"/>
-      <c r="E11" s="134" t="n"/>
-      <c r="F11" s="134" t="n"/>
-      <c r="G11" s="134" t="n"/>
-      <c r="H11" s="134" t="n"/>
-      <c r="I11" s="134" t="n"/>
-      <c r="J11" s="135">
+      <c r="C11" s="136" t="n"/>
+      <c r="D11" s="136" t="n"/>
+      <c r="E11" s="136" t="n"/>
+      <c r="F11" s="136" t="n"/>
+      <c r="G11" s="136" t="n"/>
+      <c r="H11" s="136" t="n"/>
+      <c r="I11" s="136" t="n"/>
+      <c r="J11" s="137">
         <f>SUM(C11:I11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="78">
-      <c r="A12" s="88" t="n"/>
+      <c r="A12" s="102" t="n"/>
       <c r="B12" s="31" t="inlineStr">
         <is>
           <t>상해후유80%</t>
         </is>
       </c>
-      <c r="C12" s="136" t="n"/>
-      <c r="D12" s="136" t="n"/>
-      <c r="E12" s="136" t="n"/>
-      <c r="F12" s="136" t="n"/>
-      <c r="G12" s="136" t="n"/>
-      <c r="H12" s="136" t="n"/>
-      <c r="I12" s="136" t="n"/>
-      <c r="J12" s="137">
+      <c r="C12" s="138" t="n"/>
+      <c r="D12" s="138" t="n"/>
+      <c r="E12" s="138" t="n"/>
+      <c r="F12" s="138" t="n"/>
+      <c r="G12" s="138" t="n"/>
+      <c r="H12" s="138" t="n"/>
+      <c r="I12" s="138" t="n"/>
+      <c r="J12" s="139">
         <f>SUM(C12:I12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="78">
-      <c r="A13" s="88" t="n"/>
+      <c r="A13" s="102" t="n"/>
       <c r="B13" s="31" t="inlineStr">
         <is>
           <t>질병후유3%</t>
         </is>
       </c>
-      <c r="C13" s="136" t="n"/>
-      <c r="D13" s="136" t="n"/>
-      <c r="E13" s="136" t="n"/>
-      <c r="F13" s="136" t="n"/>
-      <c r="G13" s="136" t="n"/>
-      <c r="H13" s="136" t="n"/>
-      <c r="I13" s="136" t="n"/>
-      <c r="J13" s="137">
+      <c r="C13" s="138" t="n"/>
+      <c r="D13" s="138" t="n"/>
+      <c r="E13" s="138" t="n"/>
+      <c r="F13" s="138" t="n"/>
+      <c r="G13" s="138" t="n"/>
+      <c r="H13" s="138" t="n"/>
+      <c r="I13" s="138" t="n"/>
+      <c r="J13" s="139">
         <f>SUM(C13:I13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" s="78">
-      <c r="A14" s="89" t="n"/>
+      <c r="A14" s="103" t="n"/>
       <c r="B14" s="25" t="inlineStr">
         <is>
           <t>질병후유80%</t>
         </is>
       </c>
-      <c r="C14" s="132" t="n"/>
-      <c r="D14" s="132" t="n"/>
-      <c r="E14" s="132" t="n"/>
-      <c r="F14" s="132" t="n"/>
-      <c r="G14" s="132" t="n"/>
-      <c r="H14" s="132" t="n"/>
-      <c r="I14" s="132" t="n"/>
-      <c r="J14" s="137">
+      <c r="C14" s="134" t="n"/>
+      <c r="D14" s="134" t="n"/>
+      <c r="E14" s="134" t="n"/>
+      <c r="F14" s="134" t="n"/>
+      <c r="G14" s="134" t="n"/>
+      <c r="H14" s="134" t="n"/>
+      <c r="I14" s="134" t="n"/>
+      <c r="J14" s="139">
         <f>SUM(C14:I14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1" s="78">
-      <c r="A15" s="87" t="inlineStr">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>암</t>
         </is>
@@ -1805,284 +1810,277 @@
           <t>고액암</t>
         </is>
       </c>
-      <c r="C15" s="138" t="n"/>
-      <c r="D15" s="138" t="n"/>
-      <c r="E15" s="138" t="n"/>
-      <c r="F15" s="138" t="n"/>
-      <c r="G15" s="138" t="n"/>
-      <c r="H15" s="138" t="n"/>
-      <c r="I15" s="138" t="n"/>
-      <c r="J15" s="139">
+      <c r="C15" s="140" t="n"/>
+      <c r="D15" s="140" t="n"/>
+      <c r="E15" s="140" t="n"/>
+      <c r="F15" s="140" t="n"/>
+      <c r="G15" s="140" t="n"/>
+      <c r="H15" s="140" t="n"/>
+      <c r="I15" s="140" t="n"/>
+      <c r="J15" s="141">
         <f>SUM(C15:I15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="78">
-      <c r="A16" s="88" t="n"/>
+      <c r="A16" s="102" t="n"/>
       <c r="B16" s="13" t="inlineStr">
         <is>
+          <t>통합암</t>
+        </is>
+      </c>
+      <c r="C16" s="142" t="n"/>
+      <c r="D16" s="142" t="n"/>
+      <c r="E16" s="142" t="n"/>
+      <c r="F16" s="142" t="n"/>
+      <c r="G16" s="142" t="n"/>
+      <c r="H16" s="142" t="n"/>
+      <c r="I16" s="142" t="n"/>
+      <c r="J16" s="127">
+        <f>SUM(C16:I16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" s="78">
+      <c r="A17" s="102" t="n"/>
+      <c r="B17" s="114" t="inlineStr">
+        <is>
           <t>일반암</t>
         </is>
       </c>
-      <c r="C16" s="140" t="n"/>
-      <c r="D16" s="140" t="n"/>
-      <c r="E16" s="140" t="n"/>
-      <c r="F16" s="140" t="n"/>
-      <c r="G16" s="140" t="n"/>
-      <c r="H16" s="140" t="n"/>
-      <c r="I16" s="140" t="n"/>
-      <c r="J16" s="125">
-        <f>SUM(C16:I16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="17.25" customHeight="1" s="78">
-      <c r="A17" s="88" t="n"/>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="C17" s="143" t="n"/>
+      <c r="D17" s="143" t="n"/>
+      <c r="E17" s="143" t="n"/>
+      <c r="F17" s="143" t="n"/>
+      <c r="G17" s="143" t="n"/>
+      <c r="H17" s="143" t="n"/>
+      <c r="I17" s="143" t="n"/>
+      <c r="J17" s="144">
+        <f>SUM(C15:I15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="17.25" customHeight="1" s="78" thickBot="1">
+      <c r="A18" s="102" t="n"/>
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>중대한 암</t>
         </is>
       </c>
-      <c r="C17" s="141" t="n"/>
-      <c r="D17" s="141" t="n"/>
-      <c r="E17" s="141" t="n"/>
-      <c r="F17" s="141" t="n"/>
-      <c r="G17" s="141" t="n"/>
-      <c r="H17" s="141" t="n"/>
-      <c r="I17" s="141" t="n"/>
-      <c r="J17" s="127">
-        <f>SUM(C17:I17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" s="78">
-      <c r="A18" s="88" t="n"/>
-      <c r="B18" s="40" t="inlineStr">
+      <c r="C18" s="145" t="n"/>
+      <c r="D18" s="145" t="n"/>
+      <c r="E18" s="145" t="n"/>
+      <c r="F18" s="145" t="n"/>
+      <c r="G18" s="145" t="n"/>
+      <c r="H18" s="145" t="n"/>
+      <c r="I18" s="145" t="n"/>
+      <c r="J18" s="129">
+        <f>SUM(C18:I18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" s="78">
+      <c r="A19" s="102" t="n"/>
+      <c r="B19" s="40" t="inlineStr">
         <is>
           <t>유사암(갑.기.경.제)</t>
         </is>
       </c>
-      <c r="C18" s="142" t="n"/>
-      <c r="D18" s="142" t="n"/>
-      <c r="E18" s="142" t="n"/>
-      <c r="F18" s="142" t="n"/>
-      <c r="G18" s="142" t="n"/>
-      <c r="H18" s="142" t="n"/>
-      <c r="I18" s="142" t="n"/>
-      <c r="J18" s="131">
-        <f>SUM(C18:I18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" s="78">
-      <c r="A19" s="88" t="n"/>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="C19" s="146" t="n"/>
+      <c r="D19" s="146" t="n"/>
+      <c r="E19" s="146" t="n"/>
+      <c r="F19" s="146" t="n"/>
+      <c r="G19" s="146" t="n"/>
+      <c r="H19" s="146" t="n"/>
+      <c r="I19" s="146" t="n"/>
+      <c r="J19" s="133">
+        <f>SUM(C19:I19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16.5" customHeight="1" s="78">
+      <c r="A20" s="102" t="n"/>
+      <c r="B20" s="40" t="inlineStr">
         <is>
           <t>통합전이암</t>
         </is>
       </c>
-      <c r="C19" s="142" t="n"/>
-      <c r="D19" s="142" t="n"/>
-      <c r="E19" s="142" t="n"/>
-      <c r="F19" s="142" t="n"/>
-      <c r="G19" s="142" t="n"/>
-      <c r="H19" s="142" t="n"/>
-      <c r="I19" s="142" t="n"/>
-      <c r="J19" s="131" t="n"/>
-    </row>
-    <row r="20" ht="16.5" customHeight="1" s="78">
-      <c r="A20" s="88" t="n"/>
-      <c r="B20" s="42" t="inlineStr">
+      <c r="C20" s="146" t="n"/>
+      <c r="D20" s="146" t="n"/>
+      <c r="E20" s="146" t="n"/>
+      <c r="F20" s="146" t="n"/>
+      <c r="G20" s="146" t="n"/>
+      <c r="H20" s="146" t="n"/>
+      <c r="I20" s="146" t="n"/>
+      <c r="J20" s="133" t="n"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1" s="78">
+      <c r="A21" s="102" t="n"/>
+      <c r="B21" s="42" t="inlineStr">
         <is>
           <t>암주요치료비</t>
         </is>
       </c>
-      <c r="C20" s="143" t="n"/>
-      <c r="D20" s="143" t="n"/>
-      <c r="E20" s="143" t="n"/>
-      <c r="F20" s="143" t="n"/>
-      <c r="G20" s="143" t="n"/>
-      <c r="H20" s="143" t="n"/>
-      <c r="I20" s="142" t="n"/>
-      <c r="J20" s="131" t="n"/>
-    </row>
-    <row r="21" ht="16.5" customHeight="1" s="78">
-      <c r="A21" s="88" t="n"/>
-      <c r="B21" s="42" t="inlineStr">
+      <c r="C21" s="147" t="n"/>
+      <c r="D21" s="147" t="n"/>
+      <c r="E21" s="147" t="n"/>
+      <c r="F21" s="147" t="n"/>
+      <c r="G21" s="147" t="n"/>
+      <c r="H21" s="147" t="n"/>
+      <c r="I21" s="146" t="n"/>
+      <c r="J21" s="133" t="n"/>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" s="78">
+      <c r="A22" s="102" t="n"/>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>10억 플랜</t>
+        </is>
+      </c>
+      <c r="C22" s="147" t="n"/>
+      <c r="D22" s="147" t="n"/>
+      <c r="E22" s="147" t="n"/>
+      <c r="F22" s="147" t="n"/>
+      <c r="G22" s="147" t="n"/>
+      <c r="H22" s="147" t="n"/>
+      <c r="I22" s="146" t="n"/>
+      <c r="J22" s="133" t="n"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="78">
+      <c r="A23" s="102" t="n"/>
+      <c r="B23" s="42" t="inlineStr">
         <is>
           <t>하이클래스(암)</t>
         </is>
       </c>
-      <c r="C21" s="142" t="n"/>
-      <c r="D21" s="142" t="n"/>
-      <c r="E21" s="142" t="n"/>
-      <c r="F21" s="142" t="n"/>
-      <c r="G21" s="142" t="n"/>
-      <c r="H21" s="142" t="n"/>
-      <c r="I21" s="142" t="n"/>
-      <c r="J21" s="137">
-        <f>SUM(C20:I20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="16.5" customHeight="1" s="78">
-      <c r="A22" s="88" t="n"/>
-      <c r="B22" s="42" t="inlineStr">
+      <c r="C23" s="146" t="n"/>
+      <c r="D23" s="146" t="n"/>
+      <c r="E23" s="146" t="n"/>
+      <c r="F23" s="146" t="n"/>
+      <c r="G23" s="146" t="n"/>
+      <c r="H23" s="146" t="n"/>
+      <c r="I23" s="146" t="n"/>
+      <c r="J23" s="139">
+        <f>SUM(C21:I21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16.5" customHeight="1" s="78">
+      <c r="A24" s="102" t="n"/>
+      <c r="B24" s="42" t="inlineStr">
         <is>
           <t>중입자치료비</t>
         </is>
       </c>
-      <c r="C22" s="143" t="n"/>
-      <c r="D22" s="143" t="n"/>
-      <c r="E22" s="143" t="n"/>
-      <c r="F22" s="143" t="n"/>
-      <c r="G22" s="143" t="n"/>
-      <c r="H22" s="143" t="n"/>
-      <c r="I22" s="142" t="n"/>
-      <c r="J22" s="131">
-        <f>SUM(C21:I21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" s="78">
-      <c r="A23" s="88" t="n"/>
-      <c r="B23" s="42" t="inlineStr">
+      <c r="C24" s="147" t="n"/>
+      <c r="D24" s="147" t="n"/>
+      <c r="E24" s="147" t="n"/>
+      <c r="F24" s="147" t="n"/>
+      <c r="G24" s="147" t="n"/>
+      <c r="H24" s="147" t="n"/>
+      <c r="I24" s="146" t="n"/>
+      <c r="J24" s="133">
+        <f>SUM(C23:I23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" s="78">
+      <c r="A25" s="102" t="n"/>
+      <c r="B25" s="42" t="inlineStr">
         <is>
           <t>표적항암치료비</t>
         </is>
       </c>
-      <c r="C23" s="143" t="n"/>
-      <c r="D23" s="143" t="n"/>
-      <c r="E23" s="143" t="n"/>
-      <c r="F23" s="143" t="n"/>
-      <c r="G23" s="143" t="n"/>
-      <c r="H23" s="143" t="n"/>
-      <c r="I23" s="142" t="n"/>
-      <c r="J23" s="131" t="n"/>
-    </row>
-    <row r="24" ht="16.5" customHeight="1" s="78">
-      <c r="A24" s="88" t="n"/>
-      <c r="B24" s="44" t="inlineStr">
+      <c r="C25" s="147" t="n"/>
+      <c r="D25" s="147" t="n"/>
+      <c r="E25" s="147" t="n"/>
+      <c r="F25" s="147" t="n"/>
+      <c r="G25" s="147" t="n"/>
+      <c r="H25" s="147" t="n"/>
+      <c r="I25" s="146" t="n"/>
+      <c r="J25" s="133" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="78">
+      <c r="A26" s="102" t="n"/>
+      <c r="B26" s="44" t="inlineStr">
         <is>
           <t>양성자치료</t>
         </is>
       </c>
-      <c r="C24" s="144" t="n"/>
-      <c r="D24" s="144" t="n"/>
-      <c r="E24" s="144" t="n"/>
-      <c r="F24" s="144" t="n"/>
-      <c r="G24" s="144" t="n"/>
-      <c r="H24" s="144" t="n"/>
-      <c r="I24" s="145" t="n"/>
-      <c r="J24" s="137">
-        <f>SUM(C23:I23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16.5" customHeight="1" s="78">
-      <c r="A25" s="88" t="n"/>
-      <c r="B25" s="44" t="inlineStr">
+      <c r="C26" s="148" t="n"/>
+      <c r="D26" s="148" t="n"/>
+      <c r="E26" s="148" t="n"/>
+      <c r="F26" s="148" t="n"/>
+      <c r="G26" s="148" t="n"/>
+      <c r="H26" s="148" t="n"/>
+      <c r="I26" s="149" t="n"/>
+      <c r="J26" s="139">
+        <f>SUM(C25:I25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" s="78">
+      <c r="A27" s="102" t="n"/>
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>세기조절치료</t>
         </is>
       </c>
-      <c r="C25" s="144" t="n"/>
-      <c r="D25" s="144" t="n"/>
-      <c r="E25" s="144" t="n"/>
-      <c r="F25" s="144" t="n"/>
-      <c r="G25" s="144" t="n"/>
-      <c r="H25" s="144" t="n"/>
-      <c r="I25" s="145" t="n"/>
-      <c r="J25" s="137">
-        <f>SUM(C24:I24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16.5" customHeight="1" s="78">
-      <c r="A26" s="88" t="n"/>
-      <c r="B26" s="44" t="inlineStr">
+      <c r="C27" s="148" t="n"/>
+      <c r="D27" s="148" t="n"/>
+      <c r="E27" s="148" t="n"/>
+      <c r="F27" s="148" t="n"/>
+      <c r="G27" s="148" t="n"/>
+      <c r="H27" s="148" t="n"/>
+      <c r="I27" s="149" t="n"/>
+      <c r="J27" s="139">
+        <f>SUM(C26:I26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" s="78">
+      <c r="A28" s="102" t="n"/>
+      <c r="B28" s="44" t="inlineStr">
         <is>
           <t>다빈치로봇수술비</t>
         </is>
       </c>
-      <c r="C26" s="144" t="n"/>
-      <c r="D26" s="144" t="n"/>
-      <c r="E26" s="144" t="n"/>
-      <c r="F26" s="144" t="n"/>
-      <c r="G26" s="144" t="n"/>
-      <c r="H26" s="144" t="n"/>
-      <c r="I26" s="145" t="n"/>
-      <c r="J26" s="137">
-        <f>SUM(C25:I25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" s="78">
-      <c r="A27" s="88" t="n"/>
-      <c r="B27" s="44" t="inlineStr">
+      <c r="C28" s="148" t="n"/>
+      <c r="D28" s="148" t="n"/>
+      <c r="E28" s="148" t="n"/>
+      <c r="F28" s="148" t="n"/>
+      <c r="G28" s="148" t="n"/>
+      <c r="H28" s="148" t="n"/>
+      <c r="I28" s="149" t="n"/>
+      <c r="J28" s="139">
+        <f>SUM(C27:I27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" s="78">
+      <c r="A29" s="102" t="n"/>
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>암수술</t>
         </is>
       </c>
-      <c r="C27" s="145" t="n"/>
-      <c r="D27" s="145" t="n"/>
-      <c r="E27" s="145" t="n"/>
-      <c r="F27" s="145" t="n"/>
-      <c r="G27" s="145" t="n"/>
-      <c r="H27" s="145" t="n"/>
-      <c r="I27" s="145" t="n"/>
-      <c r="J27" s="137">
-        <f>SUM(C26:I26)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="17.25" customHeight="1" s="78">
-      <c r="A28" s="88" t="n"/>
-      <c r="B28" s="31" t="inlineStr">
+      <c r="C29" s="149" t="n"/>
+      <c r="D29" s="149" t="n"/>
+      <c r="E29" s="149" t="n"/>
+      <c r="F29" s="149" t="n"/>
+      <c r="G29" s="149" t="n"/>
+      <c r="H29" s="149" t="n"/>
+      <c r="I29" s="149" t="n"/>
+      <c r="J29" s="139">
+        <f>SUM(C28:I28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="17.25" customHeight="1" s="78">
+      <c r="A30" s="102" t="n"/>
+      <c r="B30" s="31" t="inlineStr">
         <is>
           <t>암일당</t>
-        </is>
-      </c>
-      <c r="C28" s="136" t="n"/>
-      <c r="D28" s="136" t="n"/>
-      <c r="E28" s="136" t="n"/>
-      <c r="F28" s="136" t="n"/>
-      <c r="G28" s="136" t="n"/>
-      <c r="H28" s="136" t="n"/>
-      <c r="I28" s="136" t="n"/>
-      <c r="J28" s="137">
-        <f>SUM(C27:I27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="17.25" customHeight="1" s="78">
-      <c r="A29" s="89" t="n"/>
-      <c r="B29" s="25" t="inlineStr">
-        <is>
-          <t>항암방사선약물</t>
-        </is>
-      </c>
-      <c r="C29" s="132" t="n"/>
-      <c r="D29" s="132" t="n"/>
-      <c r="E29" s="132" t="n"/>
-      <c r="F29" s="132" t="n"/>
-      <c r="G29" s="132" t="n"/>
-      <c r="H29" s="132" t="n"/>
-      <c r="I29" s="132" t="n"/>
-      <c r="J29" s="133">
-        <f>SUM(C28:I28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16.5" customHeight="1" s="78">
-      <c r="A30" s="87" t="inlineStr">
-        <is>
-          <t>뇌혈관</t>
-        </is>
-      </c>
-      <c r="B30" s="34" t="inlineStr">
-        <is>
-          <t>뇌혈관진단비</t>
         </is>
       </c>
       <c r="C30" s="138" t="n"/>
@@ -2098,86 +2096,90 @@
       </c>
     </row>
     <row r="31" ht="17.25" customHeight="1" s="78">
-      <c r="A31" s="88" t="n"/>
-      <c r="B31" s="47" t="inlineStr">
+      <c r="A31" s="103" t="n"/>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>항암방사선약물</t>
+        </is>
+      </c>
+      <c r="C31" s="134" t="n"/>
+      <c r="D31" s="134" t="n"/>
+      <c r="E31" s="134" t="n"/>
+      <c r="F31" s="134" t="n"/>
+      <c r="G31" s="134" t="n"/>
+      <c r="H31" s="134" t="n"/>
+      <c r="I31" s="134" t="n"/>
+      <c r="J31" s="135">
+        <f>SUM(C30:I30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" s="78">
+      <c r="A32" s="101" t="inlineStr">
+        <is>
+          <t>뇌혈관</t>
+        </is>
+      </c>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>뇌혈관진단비</t>
+        </is>
+      </c>
+      <c r="C32" s="140" t="n"/>
+      <c r="D32" s="140" t="n"/>
+      <c r="E32" s="140" t="n"/>
+      <c r="F32" s="140" t="n"/>
+      <c r="G32" s="140" t="n"/>
+      <c r="H32" s="140" t="n"/>
+      <c r="I32" s="140" t="n"/>
+      <c r="J32" s="141">
+        <f>SUM(C31:I31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="17.25" customHeight="1" s="78">
+      <c r="A33" s="102" t="n"/>
+      <c r="B33" s="47" t="inlineStr">
         <is>
           <t>뇌졸증진단비</t>
         </is>
       </c>
-      <c r="C31" s="146" t="n"/>
-      <c r="D31" s="146" t="n"/>
-      <c r="E31" s="146" t="n"/>
-      <c r="F31" s="146" t="n"/>
-      <c r="G31" s="146" t="n"/>
-      <c r="H31" s="146" t="n"/>
-      <c r="I31" s="146" t="n"/>
-      <c r="J31" s="147">
-        <f>SUM(C30:I30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A32" s="88" t="n"/>
-      <c r="B32" s="50" t="inlineStr">
+      <c r="C33" s="150" t="n"/>
+      <c r="D33" s="150" t="n"/>
+      <c r="E33" s="150" t="n"/>
+      <c r="F33" s="150" t="n"/>
+      <c r="G33" s="150" t="n"/>
+      <c r="H33" s="150" t="n"/>
+      <c r="I33" s="150" t="n"/>
+      <c r="J33" s="151">
+        <f>SUM(C32:I32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A34" s="102" t="n"/>
+      <c r="B34" s="50" t="inlineStr">
         <is>
           <t>중대한 뇌졸증</t>
         </is>
       </c>
-      <c r="C32" s="141" t="n"/>
-      <c r="D32" s="141" t="n"/>
-      <c r="E32" s="141" t="n"/>
-      <c r="F32" s="141" t="n"/>
-      <c r="G32" s="141" t="n"/>
-      <c r="H32" s="141" t="n"/>
-      <c r="I32" s="141" t="n"/>
-      <c r="J32" s="148">
-        <f>SUM(C31:I31)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16.5" customHeight="1" s="78">
-      <c r="A33" s="88" t="n"/>
-      <c r="B33" s="109" t="inlineStr">
-        <is>
-          <t>뇌출혈진단비</t>
-        </is>
-      </c>
-      <c r="C33" s="149" t="n"/>
-      <c r="D33" s="149" t="n"/>
-      <c r="E33" s="149" t="n"/>
-      <c r="F33" s="149" t="n"/>
-      <c r="G33" s="149" t="n"/>
-      <c r="H33" s="149" t="n"/>
-      <c r="I33" s="149" t="n"/>
-      <c r="J33" s="150">
-        <f>SUM(C32:I32)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A34" s="88" t="n"/>
-      <c r="B34" s="112" t="inlineStr">
-        <is>
-          <t>중대한 뇌출혈</t>
-        </is>
-      </c>
-      <c r="C34" s="151" t="n"/>
-      <c r="D34" s="151" t="n"/>
-      <c r="E34" s="151" t="n"/>
-      <c r="F34" s="151" t="n"/>
-      <c r="G34" s="151" t="n"/>
-      <c r="H34" s="151" t="n"/>
-      <c r="I34" s="151" t="n"/>
+      <c r="C34" s="145" t="n"/>
+      <c r="D34" s="145" t="n"/>
+      <c r="E34" s="145" t="n"/>
+      <c r="F34" s="145" t="n"/>
+      <c r="G34" s="145" t="n"/>
+      <c r="H34" s="145" t="n"/>
+      <c r="I34" s="145" t="n"/>
       <c r="J34" s="152">
         <f>SUM(C33:I33)</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="78">
-      <c r="A35" s="88" t="n"/>
-      <c r="B35" s="52" t="inlineStr">
-        <is>
-          <t>외상성뇌출혈</t>
+      <c r="A35" s="102" t="n"/>
+      <c r="B35" s="93" t="inlineStr">
+        <is>
+          <t>뇌출혈진단비</t>
         </is>
       </c>
       <c r="C35" s="153" t="n"/>
@@ -2187,1345 +2189,1386 @@
       <c r="G35" s="153" t="n"/>
       <c r="H35" s="153" t="n"/>
       <c r="I35" s="153" t="n"/>
-      <c r="J35" s="131">
-        <f>SUM(C33:I33)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" s="78">
-      <c r="A36" s="88" t="n"/>
-      <c r="B36" s="54" t="inlineStr">
+      <c r="J35" s="154">
+        <f>SUM(C34:I34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A36" s="102" t="n"/>
+      <c r="B36" s="96" t="inlineStr">
+        <is>
+          <t>중대한 뇌출혈</t>
+        </is>
+      </c>
+      <c r="C36" s="155" t="n"/>
+      <c r="D36" s="155" t="n"/>
+      <c r="E36" s="155" t="n"/>
+      <c r="F36" s="155" t="n"/>
+      <c r="G36" s="155" t="n"/>
+      <c r="H36" s="155" t="n"/>
+      <c r="I36" s="155" t="n"/>
+      <c r="J36" s="156">
+        <f>SUM(C35:I35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" s="78">
+      <c r="A37" s="102" t="n"/>
+      <c r="B37" s="52" t="inlineStr">
+        <is>
+          <t>외상성뇌출혈</t>
+        </is>
+      </c>
+      <c r="C37" s="157" t="n"/>
+      <c r="D37" s="157" t="n"/>
+      <c r="E37" s="157" t="n"/>
+      <c r="F37" s="157" t="n"/>
+      <c r="G37" s="157" t="n"/>
+      <c r="H37" s="157" t="n"/>
+      <c r="I37" s="157" t="n"/>
+      <c r="J37" s="133">
+        <f>SUM(C35:I35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" s="78">
+      <c r="A38" s="102" t="n"/>
+      <c r="B38" s="54" t="inlineStr">
         <is>
           <t>산정특례뇌혈관</t>
         </is>
       </c>
-      <c r="C36" s="154" t="n"/>
-      <c r="D36" s="154" t="n"/>
-      <c r="E36" s="154" t="n"/>
-      <c r="F36" s="154" t="n"/>
-      <c r="G36" s="154" t="n"/>
-      <c r="H36" s="154" t="n"/>
-      <c r="I36" s="154" t="n"/>
-      <c r="J36" s="137">
-        <f>SUM(C34:I34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16.5" customHeight="1" s="78">
-      <c r="A37" s="88" t="n"/>
-      <c r="B37" s="54" t="inlineStr">
+      <c r="C38" s="158" t="n"/>
+      <c r="D38" s="158" t="n"/>
+      <c r="E38" s="158" t="n"/>
+      <c r="F38" s="158" t="n"/>
+      <c r="G38" s="158" t="n"/>
+      <c r="H38" s="158" t="n"/>
+      <c r="I38" s="158" t="n"/>
+      <c r="J38" s="139">
+        <f>SUM(C36:I36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" s="78">
+      <c r="A39" s="102" t="n"/>
+      <c r="B39" s="54" t="inlineStr">
         <is>
           <t>2대 주요치료비</t>
         </is>
       </c>
-      <c r="C37" s="154" t="n"/>
-      <c r="D37" s="154" t="n"/>
-      <c r="E37" s="154" t="n"/>
-      <c r="F37" s="154" t="n"/>
-      <c r="G37" s="154" t="n"/>
-      <c r="H37" s="154" t="n"/>
-      <c r="I37" s="154" t="n"/>
-      <c r="J37" s="137" t="n"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A38" s="89" t="n"/>
-      <c r="B38" s="56" t="inlineStr">
+      <c r="C39" s="158" t="n"/>
+      <c r="D39" s="158" t="n"/>
+      <c r="E39" s="158" t="n"/>
+      <c r="F39" s="158" t="n"/>
+      <c r="G39" s="158" t="n"/>
+      <c r="H39" s="158" t="n"/>
+      <c r="I39" s="158" t="n"/>
+      <c r="J39" s="139">
+        <f>SUM(C37:I37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A40" s="103" t="n"/>
+      <c r="B40" s="56" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C38" s="132" t="n"/>
-      <c r="D38" s="132" t="n"/>
-      <c r="E38" s="132" t="n"/>
-      <c r="F38" s="132" t="n"/>
-      <c r="G38" s="132" t="n"/>
-      <c r="H38" s="132" t="n"/>
-      <c r="I38" s="132" t="n"/>
-      <c r="J38" s="133">
-        <f>SUM(C35:I35)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A39" s="87" t="inlineStr">
+      <c r="C40" s="134" t="n"/>
+      <c r="D40" s="134" t="n"/>
+      <c r="E40" s="134" t="n"/>
+      <c r="F40" s="134" t="n"/>
+      <c r="G40" s="134" t="n"/>
+      <c r="H40" s="134" t="n"/>
+      <c r="I40" s="134" t="n"/>
+      <c r="J40" s="135">
+        <f>SUM(C37:I37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A41" s="101" t="inlineStr">
         <is>
           <t>심장</t>
         </is>
       </c>
-      <c r="B39" s="28" t="inlineStr">
+      <c r="B41" s="28" t="inlineStr">
         <is>
           <t>협심증</t>
         </is>
       </c>
-      <c r="C39" s="117" t="n"/>
-      <c r="D39" s="117" t="n"/>
-      <c r="E39" s="117" t="n"/>
-      <c r="F39" s="117" t="n"/>
-      <c r="G39" s="117" t="n"/>
-      <c r="H39" s="117" t="n"/>
-      <c r="I39" s="117" t="n"/>
-      <c r="J39" s="135">
-        <f>SUM(C36:I36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" s="78">
-      <c r="A40" s="88" t="n"/>
-      <c r="B40" s="31" t="inlineStr">
+      <c r="C41" s="119" t="n"/>
+      <c r="D41" s="119" t="n"/>
+      <c r="E41" s="119" t="n"/>
+      <c r="F41" s="119" t="n"/>
+      <c r="G41" s="119" t="n"/>
+      <c r="H41" s="119" t="n"/>
+      <c r="I41" s="119" t="n"/>
+      <c r="J41" s="137">
+        <f>SUM(C38:I38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16.5" customHeight="1" s="78">
+      <c r="A42" s="102" t="n"/>
+      <c r="B42" s="31" t="inlineStr">
         <is>
           <t>심부전</t>
         </is>
       </c>
-      <c r="C40" s="145" t="n"/>
-      <c r="D40" s="145" t="n"/>
-      <c r="E40" s="145" t="n"/>
-      <c r="F40" s="145" t="n"/>
-      <c r="G40" s="145" t="n"/>
-      <c r="H40" s="145" t="n"/>
-      <c r="I40" s="145" t="n"/>
-      <c r="J40" s="137">
-        <f>SUM(C37:I37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="17.25" customHeight="1" s="78">
-      <c r="A41" s="88" t="n"/>
-      <c r="B41" s="31" t="inlineStr">
+      <c r="C42" s="149" t="n"/>
+      <c r="D42" s="149" t="n"/>
+      <c r="E42" s="149" t="n"/>
+      <c r="F42" s="149" t="n"/>
+      <c r="G42" s="149" t="n"/>
+      <c r="H42" s="149" t="n"/>
+      <c r="I42" s="149" t="n"/>
+      <c r="J42" s="139">
+        <f>SUM(C39:I39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="17.25" customHeight="1" s="78">
+      <c r="A43" s="102" t="n"/>
+      <c r="B43" s="31" t="inlineStr">
         <is>
           <t>빈맥</t>
         </is>
       </c>
-      <c r="C41" s="145" t="n"/>
-      <c r="D41" s="145" t="n"/>
-      <c r="E41" s="145" t="n"/>
-      <c r="F41" s="145" t="n"/>
-      <c r="G41" s="145" t="n"/>
-      <c r="H41" s="145" t="n"/>
-      <c r="I41" s="145" t="n"/>
-      <c r="J41" s="137" t="n"/>
-    </row>
-    <row r="42" ht="16.5" customHeight="1" s="78">
-      <c r="A42" s="88" t="n"/>
-      <c r="B42" s="31" t="inlineStr">
+      <c r="C43" s="149" t="n"/>
+      <c r="D43" s="149" t="n"/>
+      <c r="E43" s="149" t="n"/>
+      <c r="F43" s="149" t="n"/>
+      <c r="G43" s="149" t="n"/>
+      <c r="H43" s="149" t="n"/>
+      <c r="I43" s="149" t="n"/>
+      <c r="J43" s="139" t="n"/>
+    </row>
+    <row r="44" ht="16.5" customHeight="1" s="78">
+      <c r="A44" s="102" t="n"/>
+      <c r="B44" s="31" t="inlineStr">
         <is>
           <t>염증</t>
         </is>
       </c>
-      <c r="C42" s="145" t="n"/>
-      <c r="D42" s="145" t="n"/>
-      <c r="E42" s="145" t="n"/>
-      <c r="F42" s="145" t="n"/>
-      <c r="G42" s="145" t="n"/>
-      <c r="H42" s="145" t="n"/>
-      <c r="I42" s="145" t="n"/>
-      <c r="J42" s="137">
-        <f>SUM(C38:I38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16.5" customHeight="1" s="78">
-      <c r="A43" s="88" t="n"/>
-      <c r="B43" s="40" t="inlineStr">
+      <c r="C44" s="149" t="n"/>
+      <c r="D44" s="149" t="n"/>
+      <c r="E44" s="149" t="n"/>
+      <c r="F44" s="149" t="n"/>
+      <c r="G44" s="149" t="n"/>
+      <c r="H44" s="149" t="n"/>
+      <c r="I44" s="149" t="n"/>
+      <c r="J44" s="139">
+        <f>SUM(C40:I40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="16.5" customHeight="1" s="78">
+      <c r="A45" s="102" t="n"/>
+      <c r="B45" s="40" t="inlineStr">
         <is>
           <t>부정맥</t>
         </is>
       </c>
-      <c r="C43" s="155" t="n"/>
-      <c r="D43" s="155" t="n"/>
-      <c r="E43" s="155" t="n"/>
-      <c r="F43" s="155" t="n"/>
-      <c r="G43" s="155" t="n"/>
-      <c r="H43" s="155" t="n"/>
-      <c r="I43" s="155" t="n"/>
-      <c r="J43" s="137">
-        <f>SUM(C39:I39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="17.25" customHeight="1" s="78">
-      <c r="A44" s="88" t="n"/>
-      <c r="B44" s="59" t="inlineStr">
+      <c r="C45" s="159" t="n"/>
+      <c r="D45" s="159" t="n"/>
+      <c r="E45" s="159" t="n"/>
+      <c r="F45" s="159" t="n"/>
+      <c r="G45" s="159" t="n"/>
+      <c r="H45" s="159" t="n"/>
+      <c r="I45" s="159" t="n"/>
+      <c r="J45" s="139">
+        <f>SUM(C41:I41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="17.25" customHeight="1" s="78">
+      <c r="A46" s="102" t="n"/>
+      <c r="B46" s="59" t="inlineStr">
         <is>
           <t>심근병증</t>
         </is>
       </c>
-      <c r="C44" s="106" t="n"/>
-      <c r="D44" s="106" t="n"/>
-      <c r="E44" s="106" t="n"/>
-      <c r="F44" s="106" t="n"/>
-      <c r="G44" s="106" t="n"/>
-      <c r="H44" s="106" t="n"/>
-      <c r="I44" s="106" t="n"/>
-      <c r="J44" s="108" t="n"/>
-    </row>
-    <row r="45" ht="17.25" customHeight="1" s="78">
-      <c r="A45" s="88" t="n"/>
-      <c r="B45" s="40" t="inlineStr">
+      <c r="C46" s="90" t="n"/>
+      <c r="D46" s="90" t="n"/>
+      <c r="E46" s="90" t="n"/>
+      <c r="F46" s="90" t="n"/>
+      <c r="G46" s="90" t="n"/>
+      <c r="H46" s="90" t="n"/>
+      <c r="I46" s="90" t="n"/>
+      <c r="J46" s="92" t="n"/>
+    </row>
+    <row r="47" ht="17.25" customHeight="1" s="78">
+      <c r="A47" s="102" t="n"/>
+      <c r="B47" s="40" t="inlineStr">
         <is>
           <t>심장판막</t>
         </is>
       </c>
-      <c r="C45" s="107" t="n"/>
-      <c r="D45" s="106" t="n"/>
-      <c r="E45" s="106" t="n"/>
-      <c r="F45" s="106" t="n"/>
-      <c r="G45" s="106" t="n"/>
-      <c r="H45" s="106" t="n"/>
-      <c r="I45" s="106" t="n"/>
-      <c r="J45" s="108" t="n"/>
-    </row>
-    <row r="46" ht="16.5" customHeight="1" s="78">
-      <c r="A46" s="88" t="n"/>
-      <c r="B46" s="59" t="inlineStr">
+      <c r="C47" s="91" t="n"/>
+      <c r="D47" s="90" t="n"/>
+      <c r="E47" s="90" t="n"/>
+      <c r="F47" s="90" t="n"/>
+      <c r="G47" s="90" t="n"/>
+      <c r="H47" s="90" t="n"/>
+      <c r="I47" s="90" t="n"/>
+      <c r="J47" s="92" t="n"/>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" s="78">
+      <c r="A48" s="102" t="n"/>
+      <c r="B48" s="59" t="inlineStr">
         <is>
           <t>산정특례심장</t>
         </is>
       </c>
-      <c r="C46" s="136" t="n"/>
-      <c r="D46" s="136" t="n"/>
-      <c r="E46" s="136" t="n"/>
-      <c r="F46" s="136" t="n"/>
-      <c r="G46" s="136" t="n"/>
-      <c r="H46" s="136" t="n"/>
-      <c r="I46" s="136" t="n"/>
-      <c r="J46" s="137">
-        <f>SUM(C40:I40)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="16.5" customHeight="1" s="78">
-      <c r="A47" s="88" t="n"/>
-      <c r="B47" s="66" t="inlineStr">
+      <c r="C48" s="138" t="n"/>
+      <c r="D48" s="138" t="n"/>
+      <c r="E48" s="138" t="n"/>
+      <c r="F48" s="138" t="n"/>
+      <c r="G48" s="138" t="n"/>
+      <c r="H48" s="138" t="n"/>
+      <c r="I48" s="138" t="n"/>
+      <c r="J48" s="139">
+        <f>SUM(C42:I42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" s="78">
+      <c r="A49" s="102" t="n"/>
+      <c r="B49" s="66" t="inlineStr">
         <is>
           <t>2대 주요치료비</t>
         </is>
       </c>
-      <c r="C47" s="136" t="n"/>
-      <c r="D47" s="136" t="n"/>
-      <c r="E47" s="136" t="n"/>
-      <c r="F47" s="136" t="n"/>
-      <c r="G47" s="136" t="n"/>
-      <c r="H47" s="136" t="n"/>
-      <c r="I47" s="136" t="n"/>
-      <c r="J47" s="137">
-        <f>SUM(C41:I41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A48" s="88" t="n"/>
-      <c r="B48" s="82" t="inlineStr">
+      <c r="C49" s="138" t="n"/>
+      <c r="D49" s="138" t="n"/>
+      <c r="E49" s="138" t="n"/>
+      <c r="F49" s="138" t="n"/>
+      <c r="G49" s="138" t="n"/>
+      <c r="H49" s="138" t="n"/>
+      <c r="I49" s="138" t="n"/>
+      <c r="J49" s="139">
+        <f>SUM(C43:I43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A50" s="102" t="n"/>
+      <c r="B50" s="82" t="inlineStr">
         <is>
           <t>허혈성 진단비</t>
         </is>
       </c>
-      <c r="C48" s="130" t="n"/>
-      <c r="D48" s="130" t="n"/>
-      <c r="E48" s="130" t="n"/>
-      <c r="F48" s="130" t="n"/>
-      <c r="G48" s="130" t="n"/>
-      <c r="H48" s="130" t="n"/>
-      <c r="I48" s="130" t="n"/>
-      <c r="J48" s="137">
-        <f>SUM(C42:I42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="16.5" customHeight="1" s="78">
-      <c r="A49" s="88" t="n"/>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="C50" s="132" t="n"/>
+      <c r="D50" s="132" t="n"/>
+      <c r="E50" s="132" t="n"/>
+      <c r="F50" s="132" t="n"/>
+      <c r="G50" s="132" t="n"/>
+      <c r="H50" s="132" t="n"/>
+      <c r="I50" s="132" t="n"/>
+      <c r="J50" s="139">
+        <f>SUM(C44:I44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="16.5" customHeight="1" s="78">
+      <c r="A51" s="102" t="n"/>
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>급성심근경색</t>
         </is>
       </c>
-      <c r="C49" s="140" t="n"/>
-      <c r="D49" s="140" t="n"/>
-      <c r="E49" s="140" t="n"/>
-      <c r="F49" s="140" t="n"/>
-      <c r="G49" s="140" t="n"/>
-      <c r="H49" s="140" t="n"/>
-      <c r="I49" s="140" t="n"/>
-      <c r="J49" s="125">
-        <f>SUM(C42:I42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A50" s="88" t="n"/>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="C51" s="142" t="n"/>
+      <c r="D51" s="142" t="n"/>
+      <c r="E51" s="142" t="n"/>
+      <c r="F51" s="142" t="n"/>
+      <c r="G51" s="142" t="n"/>
+      <c r="H51" s="142" t="n"/>
+      <c r="I51" s="142" t="n"/>
+      <c r="J51" s="127">
+        <f>SUM(C44:I44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A52" s="102" t="n"/>
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>중대한 급성심근</t>
         </is>
       </c>
-      <c r="C50" s="126" t="n"/>
-      <c r="D50" s="126" t="n"/>
-      <c r="E50" s="126" t="n"/>
-      <c r="F50" s="126" t="n"/>
-      <c r="G50" s="126" t="n"/>
-      <c r="H50" s="126" t="n"/>
-      <c r="I50" s="126" t="n"/>
-      <c r="J50" s="148">
-        <f>SUM(C44:I44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A51" s="89" t="n"/>
-      <c r="B51" s="63" t="inlineStr">
+      <c r="C52" s="128" t="n"/>
+      <c r="D52" s="128" t="n"/>
+      <c r="E52" s="128" t="n"/>
+      <c r="F52" s="128" t="n"/>
+      <c r="G52" s="128" t="n"/>
+      <c r="H52" s="128" t="n"/>
+      <c r="I52" s="128" t="n"/>
+      <c r="J52" s="152">
+        <f>SUM(C46:I46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A53" s="103" t="n"/>
+      <c r="B53" s="63" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C51" s="128" t="n"/>
-      <c r="D51" s="128" t="n"/>
-      <c r="E51" s="128" t="n"/>
-      <c r="F51" s="128" t="n"/>
-      <c r="G51" s="128" t="n"/>
-      <c r="H51" s="128" t="n"/>
-      <c r="I51" s="128" t="n"/>
-      <c r="J51" s="129">
-        <f>SUM(C45:I45)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A52" s="95" t="inlineStr">
+      <c r="C53" s="130" t="n"/>
+      <c r="D53" s="130" t="n"/>
+      <c r="E53" s="130" t="n"/>
+      <c r="F53" s="130" t="n"/>
+      <c r="G53" s="130" t="n"/>
+      <c r="H53" s="130" t="n"/>
+      <c r="I53" s="130" t="n"/>
+      <c r="J53" s="131">
+        <f>SUM(C47:I47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A54" s="109" t="inlineStr">
         <is>
           <t>일당</t>
         </is>
       </c>
-      <c r="B52" s="90" t="inlineStr">
+      <c r="B54" s="104" t="inlineStr">
         <is>
           <t>질병일당</t>
         </is>
       </c>
-      <c r="C52" s="134" t="n"/>
-      <c r="D52" s="134" t="n"/>
-      <c r="E52" s="134" t="n"/>
-      <c r="F52" s="134" t="n"/>
-      <c r="G52" s="134" t="n"/>
-      <c r="H52" s="134" t="n"/>
-      <c r="I52" s="134" t="n"/>
-      <c r="J52" s="135">
-        <f>SUM(C46:I46)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="16.5" customHeight="1" s="78">
-      <c r="A53" s="88" t="n"/>
-      <c r="B53" s="64" t="inlineStr">
-        <is>
-          <t>질병수술일당</t>
-        </is>
-      </c>
-      <c r="C53" s="155" t="n"/>
-      <c r="D53" s="155" t="n"/>
-      <c r="E53" s="155" t="n"/>
-      <c r="F53" s="155" t="n"/>
-      <c r="G53" s="155" t="n"/>
-      <c r="H53" s="155" t="n"/>
-      <c r="I53" s="155" t="n"/>
-      <c r="J53" s="137">
-        <f>SUM(C47:I47)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="16.5" customHeight="1" s="78">
-      <c r="A54" s="88" t="n"/>
-      <c r="B54" s="64" t="inlineStr">
-        <is>
-          <t>종합병원 질병입원일당</t>
-        </is>
-      </c>
-      <c r="C54" s="155" t="n"/>
-      <c r="D54" s="155" t="n"/>
-      <c r="E54" s="155" t="n"/>
-      <c r="F54" s="155" t="n"/>
-      <c r="G54" s="155" t="n"/>
-      <c r="H54" s="155" t="n"/>
-      <c r="I54" s="155" t="n"/>
+      <c r="C54" s="136" t="n"/>
+      <c r="D54" s="136" t="n"/>
+      <c r="E54" s="136" t="n"/>
+      <c r="F54" s="136" t="n"/>
+      <c r="G54" s="136" t="n"/>
+      <c r="H54" s="136" t="n"/>
+      <c r="I54" s="136" t="n"/>
       <c r="J54" s="137">
         <f>SUM(C48:I48)</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" s="78">
-      <c r="A55" s="88" t="n"/>
+      <c r="A55" s="102" t="n"/>
       <c r="B55" s="64" t="inlineStr">
         <is>
+          <t>질병수술일당</t>
+        </is>
+      </c>
+      <c r="C55" s="159" t="n"/>
+      <c r="D55" s="159" t="n"/>
+      <c r="E55" s="159" t="n"/>
+      <c r="F55" s="159" t="n"/>
+      <c r="G55" s="159" t="n"/>
+      <c r="H55" s="159" t="n"/>
+      <c r="I55" s="159" t="n"/>
+      <c r="J55" s="139">
+        <f>SUM(C49:I49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="16.5" customHeight="1" s="78">
+      <c r="A56" s="102" t="n"/>
+      <c r="B56" s="64" t="inlineStr">
+        <is>
+          <t>종합병원 질병입원일당</t>
+        </is>
+      </c>
+      <c r="C56" s="159" t="n"/>
+      <c r="D56" s="159" t="n"/>
+      <c r="E56" s="159" t="n"/>
+      <c r="F56" s="159" t="n"/>
+      <c r="G56" s="159" t="n"/>
+      <c r="H56" s="159" t="n"/>
+      <c r="I56" s="159" t="n"/>
+      <c r="J56" s="139">
+        <f>SUM(C50:I50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="16.5" customHeight="1" s="78">
+      <c r="A57" s="102" t="n"/>
+      <c r="B57" s="64" t="inlineStr">
+        <is>
           <t>종합병원 상해입원일당</t>
         </is>
       </c>
-      <c r="C55" s="155" t="n"/>
-      <c r="D55" s="155" t="n"/>
-      <c r="E55" s="155" t="n"/>
-      <c r="F55" s="155" t="n"/>
-      <c r="G55" s="155" t="n"/>
-      <c r="H55" s="155" t="n"/>
-      <c r="I55" s="155" t="n"/>
-      <c r="J55" s="137" t="n"/>
-    </row>
-    <row r="56" ht="16.5" customHeight="1" s="78">
-      <c r="A56" s="88" t="n"/>
-      <c r="B56" s="59" t="inlineStr">
+      <c r="C57" s="159" t="n"/>
+      <c r="D57" s="159" t="n"/>
+      <c r="E57" s="159" t="n"/>
+      <c r="F57" s="159" t="n"/>
+      <c r="G57" s="159" t="n"/>
+      <c r="H57" s="159" t="n"/>
+      <c r="I57" s="159" t="n"/>
+      <c r="J57" s="139" t="n"/>
+    </row>
+    <row r="58" ht="16.5" customHeight="1" s="78">
+      <c r="A58" s="102" t="n"/>
+      <c r="B58" s="59" t="inlineStr">
         <is>
           <t>상해일당</t>
         </is>
       </c>
-      <c r="C56" s="136" t="n"/>
-      <c r="D56" s="136" t="n"/>
-      <c r="E56" s="136" t="n"/>
-      <c r="F56" s="136" t="n"/>
-      <c r="G56" s="136" t="n"/>
-      <c r="H56" s="136" t="n"/>
-      <c r="I56" s="136" t="n"/>
-      <c r="J56" s="137">
-        <f>SUM(C49:I49)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" ht="16.5" customHeight="1" s="78">
-      <c r="A57" s="88" t="n"/>
-      <c r="B57" s="59" t="inlineStr">
+      <c r="C58" s="138" t="n"/>
+      <c r="D58" s="138" t="n"/>
+      <c r="E58" s="138" t="n"/>
+      <c r="F58" s="138" t="n"/>
+      <c r="G58" s="138" t="n"/>
+      <c r="H58" s="138" t="n"/>
+      <c r="I58" s="138" t="n"/>
+      <c r="J58" s="139">
+        <f>SUM(C51:I51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="16.5" customHeight="1" s="78">
+      <c r="A59" s="102" t="n"/>
+      <c r="B59" s="59" t="inlineStr">
         <is>
           <t>상해수술일당</t>
         </is>
       </c>
-      <c r="C57" s="136" t="n"/>
-      <c r="D57" s="136" t="n"/>
-      <c r="E57" s="136" t="n"/>
-      <c r="F57" s="136" t="n"/>
-      <c r="G57" s="136" t="n"/>
-      <c r="H57" s="136" t="n"/>
-      <c r="I57" s="136" t="n"/>
-      <c r="J57" s="137" t="n"/>
-    </row>
-    <row r="58" ht="16.5" customHeight="1" s="78">
-      <c r="A58" s="88" t="n"/>
-      <c r="B58" s="31" t="inlineStr">
+      <c r="C59" s="138" t="n"/>
+      <c r="D59" s="138" t="n"/>
+      <c r="E59" s="138" t="n"/>
+      <c r="F59" s="138" t="n"/>
+      <c r="G59" s="138" t="n"/>
+      <c r="H59" s="138" t="n"/>
+      <c r="I59" s="138" t="n"/>
+      <c r="J59" s="139" t="n"/>
+    </row>
+    <row r="60" ht="16.5" customHeight="1" s="78">
+      <c r="A60" s="102" t="n"/>
+      <c r="B60" s="31" t="inlineStr">
         <is>
           <t>간병인</t>
         </is>
       </c>
-      <c r="C58" s="136" t="n"/>
-      <c r="D58" s="136" t="n"/>
-      <c r="E58" s="136" t="n"/>
-      <c r="F58" s="136" t="n"/>
-      <c r="G58" s="136" t="n"/>
-      <c r="H58" s="136" t="n"/>
-      <c r="I58" s="136" t="n"/>
-      <c r="J58" s="137">
-        <f>SUM(C50:I50)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="16.5" customHeight="1" s="78">
-      <c r="A59" s="88" t="n"/>
-      <c r="B59" s="31" t="inlineStr">
+      <c r="C60" s="138" t="n"/>
+      <c r="D60" s="138" t="n"/>
+      <c r="E60" s="138" t="n"/>
+      <c r="F60" s="138" t="n"/>
+      <c r="G60" s="138" t="n"/>
+      <c r="H60" s="138" t="n"/>
+      <c r="I60" s="138" t="n"/>
+      <c r="J60" s="139">
+        <f>SUM(C52:I52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="16.5" customHeight="1" s="78">
+      <c r="A61" s="102" t="n"/>
+      <c r="B61" s="31" t="inlineStr">
         <is>
           <t>간병인지원일당</t>
         </is>
       </c>
-      <c r="C59" s="136" t="n"/>
-      <c r="D59" s="136" t="n"/>
-      <c r="E59" s="136" t="n"/>
-      <c r="F59" s="136" t="n"/>
-      <c r="G59" s="136" t="n"/>
-      <c r="H59" s="136" t="n"/>
-      <c r="I59" s="136" t="n"/>
-      <c r="J59" s="137" t="n"/>
-    </row>
-    <row r="60" ht="16.5" customHeight="1" s="78">
-      <c r="A60" s="88" t="n"/>
-      <c r="B60" s="31" t="inlineStr">
+      <c r="C61" s="138" t="n"/>
+      <c r="D61" s="138" t="n"/>
+      <c r="E61" s="138" t="n"/>
+      <c r="F61" s="138" t="n"/>
+      <c r="G61" s="138" t="n"/>
+      <c r="H61" s="138" t="n"/>
+      <c r="I61" s="138" t="n"/>
+      <c r="J61" s="139" t="n"/>
+    </row>
+    <row r="62" ht="16.5" customHeight="1" s="78">
+      <c r="A62" s="102" t="n"/>
+      <c r="B62" s="31" t="inlineStr">
         <is>
           <t>간호통합병동</t>
         </is>
       </c>
-      <c r="C60" s="136" t="n"/>
-      <c r="D60" s="136" t="n"/>
-      <c r="E60" s="136" t="n"/>
-      <c r="F60" s="136" t="n"/>
-      <c r="G60" s="136" t="n"/>
-      <c r="H60" s="136" t="n"/>
-      <c r="I60" s="136" t="n"/>
-      <c r="J60" s="137">
-        <f>SUM(C51:I51)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="16.5" customHeight="1" s="78">
-      <c r="A61" s="88" t="n"/>
-      <c r="B61" s="65" t="inlineStr">
+      <c r="C62" s="138" t="n"/>
+      <c r="D62" s="138" t="n"/>
+      <c r="E62" s="138" t="n"/>
+      <c r="F62" s="138" t="n"/>
+      <c r="G62" s="138" t="n"/>
+      <c r="H62" s="138" t="n"/>
+      <c r="I62" s="138" t="n"/>
+      <c r="J62" s="139">
+        <f>SUM(C53:I53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" ht="16.5" customHeight="1" s="78">
+      <c r="A63" s="102" t="n"/>
+      <c r="B63" s="65" t="inlineStr">
         <is>
           <t>1인실 종합병원</t>
         </is>
       </c>
-      <c r="C61" s="136" t="n"/>
-      <c r="D61" s="136" t="n"/>
-      <c r="E61" s="136" t="n"/>
-      <c r="F61" s="136" t="n"/>
-      <c r="G61" s="136" t="n"/>
-      <c r="H61" s="136" t="n"/>
-      <c r="I61" s="136" t="n"/>
-      <c r="J61" s="137">
-        <f>SUM(C52:I52)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62" ht="17.25" customHeight="1" s="78">
-      <c r="A62" s="88" t="n"/>
-      <c r="B62" s="65" t="inlineStr">
+      <c r="C63" s="138" t="n"/>
+      <c r="D63" s="138" t="n"/>
+      <c r="E63" s="138" t="n"/>
+      <c r="F63" s="138" t="n"/>
+      <c r="G63" s="138" t="n"/>
+      <c r="H63" s="138" t="n"/>
+      <c r="I63" s="138" t="n"/>
+      <c r="J63" s="139">
+        <f>SUM(C54:I54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" ht="17.25" customHeight="1" s="78">
+      <c r="A64" s="102" t="n"/>
+      <c r="B64" s="65" t="inlineStr">
         <is>
           <t>1인실 상급병원</t>
         </is>
       </c>
-      <c r="C62" s="136" t="n"/>
-      <c r="D62" s="136" t="n"/>
-      <c r="E62" s="136" t="n"/>
-      <c r="F62" s="136" t="n"/>
-      <c r="G62" s="136" t="n"/>
-      <c r="H62" s="136" t="n"/>
-      <c r="I62" s="136" t="n"/>
-      <c r="J62" s="137">
-        <f>SUM(C53:I53)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63" ht="17.25" customHeight="1" s="78">
-      <c r="A63" s="88" t="n"/>
-      <c r="B63" s="31" t="inlineStr">
+      <c r="C64" s="138" t="n"/>
+      <c r="D64" s="138" t="n"/>
+      <c r="E64" s="138" t="n"/>
+      <c r="F64" s="138" t="n"/>
+      <c r="G64" s="138" t="n"/>
+      <c r="H64" s="138" t="n"/>
+      <c r="I64" s="138" t="n"/>
+      <c r="J64" s="139">
+        <f>SUM(C55:I55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="17.25" customHeight="1" s="78">
+      <c r="A65" s="102" t="n"/>
+      <c r="B65" s="31" t="inlineStr">
         <is>
           <t>질병중환자실</t>
         </is>
       </c>
-      <c r="C63" s="136" t="n"/>
-      <c r="D63" s="136" t="n"/>
-      <c r="E63" s="136" t="n"/>
-      <c r="F63" s="136" t="n"/>
-      <c r="G63" s="136" t="n"/>
-      <c r="H63" s="136" t="n"/>
-      <c r="I63" s="136" t="n"/>
-      <c r="J63" s="137">
-        <f>SUM(C54:I54)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A64" s="89" t="n"/>
-      <c r="B64" s="25" t="inlineStr">
+      <c r="C65" s="138" t="n"/>
+      <c r="D65" s="138" t="n"/>
+      <c r="E65" s="138" t="n"/>
+      <c r="F65" s="138" t="n"/>
+      <c r="G65" s="138" t="n"/>
+      <c r="H65" s="138" t="n"/>
+      <c r="I65" s="138" t="n"/>
+      <c r="J65" s="139">
+        <f>SUM(C56:I56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A66" s="103" t="n"/>
+      <c r="B66" s="25" t="inlineStr">
         <is>
           <t>상해중환자실</t>
         </is>
       </c>
-      <c r="C64" s="132" t="n"/>
-      <c r="D64" s="132" t="n"/>
-      <c r="E64" s="132" t="n"/>
-      <c r="F64" s="132" t="n"/>
-      <c r="G64" s="132" t="n"/>
-      <c r="H64" s="132" t="n"/>
-      <c r="I64" s="132" t="n"/>
-      <c r="J64" s="133">
-        <f>SUM(C55:I55)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65" ht="16.5" customHeight="1" s="78">
-      <c r="A65" s="87" t="inlineStr">
+      <c r="C66" s="134" t="n"/>
+      <c r="D66" s="134" t="n"/>
+      <c r="E66" s="134" t="n"/>
+      <c r="F66" s="134" t="n"/>
+      <c r="G66" s="134" t="n"/>
+      <c r="H66" s="134" t="n"/>
+      <c r="I66" s="134" t="n"/>
+      <c r="J66" s="135">
+        <f>SUM(C57:I57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16.5" customHeight="1" s="78">
+      <c r="A67" s="101" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B65" s="90" t="inlineStr">
+      <c r="B67" s="104" t="inlineStr">
         <is>
           <t>상해수술비</t>
         </is>
       </c>
-      <c r="C65" s="134" t="n"/>
-      <c r="D65" s="134" t="n"/>
-      <c r="E65" s="134" t="n"/>
-      <c r="F65" s="134" t="n"/>
-      <c r="G65" s="134" t="n"/>
-      <c r="H65" s="134" t="n"/>
-      <c r="I65" s="134" t="n"/>
-      <c r="J65" s="135">
-        <f>SUM(C56:I56)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" ht="16.5" customHeight="1" s="78">
-      <c r="A66" s="88" t="n"/>
-      <c r="B66" s="64" t="inlineStr">
+      <c r="C67" s="136" t="n"/>
+      <c r="D67" s="136" t="n"/>
+      <c r="E67" s="136" t="n"/>
+      <c r="F67" s="136" t="n"/>
+      <c r="G67" s="136" t="n"/>
+      <c r="H67" s="136" t="n"/>
+      <c r="I67" s="136" t="n"/>
+      <c r="J67" s="137">
+        <f>SUM(C58:I58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="16.5" customHeight="1" s="78">
+      <c r="A68" s="102" t="n"/>
+      <c r="B68" s="64" t="inlineStr">
         <is>
           <t>중대한상해수술비</t>
         </is>
       </c>
-      <c r="C66" s="155" t="n"/>
-      <c r="D66" s="155" t="n"/>
-      <c r="E66" s="155" t="n"/>
-      <c r="F66" s="155" t="n"/>
-      <c r="G66" s="155" t="n"/>
-      <c r="H66" s="155" t="n"/>
-      <c r="I66" s="155" t="n"/>
-      <c r="J66" s="137">
-        <f>SUM(C57:I57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16.5" customHeight="1" s="78">
-      <c r="A67" s="88" t="n"/>
-      <c r="B67" s="59" t="inlineStr">
+      <c r="C68" s="159" t="n"/>
+      <c r="D68" s="159" t="n"/>
+      <c r="E68" s="159" t="n"/>
+      <c r="F68" s="159" t="n"/>
+      <c r="G68" s="159" t="n"/>
+      <c r="H68" s="159" t="n"/>
+      <c r="I68" s="159" t="n"/>
+      <c r="J68" s="139">
+        <f>SUM(C59:I59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" ht="16.5" customHeight="1" s="78">
+      <c r="A69" s="102" t="n"/>
+      <c r="B69" s="59" t="inlineStr">
         <is>
           <t>상해 종수술비(1-3종)</t>
         </is>
       </c>
-      <c r="C67" s="155" t="n"/>
-      <c r="D67" s="155" t="n"/>
-      <c r="E67" s="155" t="n"/>
-      <c r="F67" s="156" t="n"/>
-      <c r="G67" s="155" t="n"/>
-      <c r="H67" s="155" t="n"/>
-      <c r="I67" s="155" t="n"/>
-      <c r="J67" s="137" t="n"/>
-    </row>
-    <row r="68" ht="17.25" customHeight="1" s="78">
-      <c r="A68" s="88" t="n"/>
-      <c r="B68" s="59" t="inlineStr">
+      <c r="C69" s="159" t="n"/>
+      <c r="D69" s="159" t="n"/>
+      <c r="E69" s="159" t="n"/>
+      <c r="F69" s="160" t="n"/>
+      <c r="G69" s="159" t="n"/>
+      <c r="H69" s="159" t="n"/>
+      <c r="I69" s="159" t="n"/>
+      <c r="J69" s="139" t="n"/>
+    </row>
+    <row r="70" ht="17.25" customHeight="1" s="78">
+      <c r="A70" s="102" t="n"/>
+      <c r="B70" s="59" t="inlineStr">
         <is>
           <t>상해 종수술비(1-5종)</t>
         </is>
       </c>
-      <c r="C68" s="155" t="n"/>
-      <c r="D68" s="155" t="n"/>
-      <c r="E68" s="155" t="n"/>
-      <c r="F68" s="156" t="n"/>
-      <c r="G68" s="155" t="n"/>
-      <c r="H68" s="155" t="n"/>
-      <c r="I68" s="155" t="n"/>
-      <c r="J68" s="137" t="inlineStr">
+      <c r="C70" s="159" t="n"/>
+      <c r="D70" s="159" t="n"/>
+      <c r="E70" s="159" t="n"/>
+      <c r="F70" s="160" t="n"/>
+      <c r="G70" s="159" t="n"/>
+      <c r="H70" s="159" t="n"/>
+      <c r="I70" s="159" t="n"/>
+      <c r="J70" s="139" t="inlineStr">
         <is>
           <t>/ / / / /</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="16.5" customHeight="1" s="78">
-      <c r="A69" s="88" t="n"/>
-      <c r="B69" s="59" t="inlineStr">
+    <row r="71" ht="16.5" customHeight="1" s="78">
+      <c r="A71" s="102" t="n"/>
+      <c r="B71" s="59" t="inlineStr">
         <is>
           <t>상해 종수술비(1-8종)</t>
         </is>
       </c>
-      <c r="C69" s="155" t="n"/>
-      <c r="D69" s="155" t="n"/>
-      <c r="E69" s="155" t="n"/>
-      <c r="F69" s="156" t="n"/>
-      <c r="G69" s="155" t="n"/>
-      <c r="H69" s="155" t="n"/>
-      <c r="I69" s="155" t="n"/>
-      <c r="J69" s="137" t="n"/>
-    </row>
-    <row r="70" ht="16.5" customHeight="1" s="78">
-      <c r="A70" s="88" t="n"/>
-      <c r="B70" s="59" t="inlineStr">
+      <c r="C71" s="159" t="n"/>
+      <c r="D71" s="159" t="n"/>
+      <c r="E71" s="159" t="n"/>
+      <c r="F71" s="160" t="n"/>
+      <c r="G71" s="159" t="n"/>
+      <c r="H71" s="159" t="n"/>
+      <c r="I71" s="159" t="n"/>
+      <c r="J71" s="139" t="n"/>
+    </row>
+    <row r="72" ht="16.5" customHeight="1" s="78">
+      <c r="A72" s="102" t="n"/>
+      <c r="B72" s="59" t="inlineStr">
         <is>
           <t>창상봉합술</t>
         </is>
       </c>
-      <c r="C70" s="136" t="n"/>
-      <c r="D70" s="136" t="n"/>
-      <c r="E70" s="136" t="n"/>
-      <c r="F70" s="157" t="n"/>
-      <c r="G70" s="136" t="n"/>
-      <c r="H70" s="136" t="n"/>
-      <c r="I70" s="136" t="n"/>
-      <c r="J70" s="137">
-        <f>SUM(C59:I59)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" ht="16.5" customHeight="1" s="78">
-      <c r="A71" s="88" t="n"/>
-      <c r="B71" s="59" t="inlineStr">
+      <c r="C72" s="138" t="n"/>
+      <c r="D72" s="138" t="n"/>
+      <c r="E72" s="138" t="n"/>
+      <c r="F72" s="161" t="n"/>
+      <c r="G72" s="138" t="n"/>
+      <c r="H72" s="138" t="n"/>
+      <c r="I72" s="138" t="n"/>
+      <c r="J72" s="139">
+        <f>SUM(C61:I61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="16.5" customHeight="1" s="78">
+      <c r="A73" s="102" t="n"/>
+      <c r="B73" s="59" t="inlineStr">
         <is>
           <t>골절수술비</t>
         </is>
       </c>
-      <c r="C71" s="136" t="n"/>
-      <c r="D71" s="136" t="n"/>
-      <c r="E71" s="136" t="n"/>
-      <c r="F71" s="157" t="n"/>
-      <c r="G71" s="136" t="n"/>
-      <c r="H71" s="136" t="n"/>
-      <c r="I71" s="136" t="n"/>
-      <c r="J71" s="137">
-        <f>SUM(C60:I60)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" ht="16.5" customHeight="1" s="78">
-      <c r="A72" s="88" t="n"/>
-      <c r="B72" s="66" t="inlineStr">
+      <c r="C73" s="138" t="n"/>
+      <c r="D73" s="138" t="n"/>
+      <c r="E73" s="138" t="n"/>
+      <c r="F73" s="161" t="n"/>
+      <c r="G73" s="138" t="n"/>
+      <c r="H73" s="138" t="n"/>
+      <c r="I73" s="138" t="n"/>
+      <c r="J73" s="139">
+        <f>SUM(C62:I62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="16.5" customHeight="1" s="78">
+      <c r="A74" s="102" t="n"/>
+      <c r="B74" s="66" t="inlineStr">
         <is>
           <t>5대골절수술비</t>
         </is>
       </c>
-      <c r="C72" s="136" t="n"/>
-      <c r="D72" s="136" t="n"/>
-      <c r="E72" s="136" t="n"/>
-      <c r="F72" s="157" t="n"/>
-      <c r="G72" s="136" t="n"/>
-      <c r="H72" s="136" t="n"/>
-      <c r="I72" s="136" t="n"/>
-      <c r="J72" s="137">
-        <f>SUM(C61:I61)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A73" s="88" t="n"/>
-      <c r="B73" s="56" t="inlineStr">
+      <c r="C74" s="138" t="n"/>
+      <c r="D74" s="138" t="n"/>
+      <c r="E74" s="138" t="n"/>
+      <c r="F74" s="161" t="n"/>
+      <c r="G74" s="138" t="n"/>
+      <c r="H74" s="138" t="n"/>
+      <c r="I74" s="138" t="n"/>
+      <c r="J74" s="139">
+        <f>SUM(C63:I63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A75" s="102" t="n"/>
+      <c r="B75" s="56" t="inlineStr">
         <is>
           <t>화상수술비</t>
         </is>
       </c>
-      <c r="C73" s="132" t="n"/>
-      <c r="D73" s="132" t="n"/>
-      <c r="E73" s="132" t="n"/>
-      <c r="F73" s="158" t="n"/>
-      <c r="G73" s="132" t="n"/>
-      <c r="H73" s="132" t="n"/>
-      <c r="I73" s="132" t="n"/>
-      <c r="J73" s="133">
-        <f>SUM(C62:I62)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" ht="16.5" customHeight="1" s="78">
-      <c r="A74" s="88" t="n"/>
-      <c r="B74" s="64" t="inlineStr">
+      <c r="C75" s="134" t="n"/>
+      <c r="D75" s="134" t="n"/>
+      <c r="E75" s="134" t="n"/>
+      <c r="F75" s="162" t="n"/>
+      <c r="G75" s="134" t="n"/>
+      <c r="H75" s="134" t="n"/>
+      <c r="I75" s="134" t="n"/>
+      <c r="J75" s="135">
+        <f>SUM(C64:I64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="16.5" customHeight="1" s="78">
+      <c r="A76" s="102" t="n"/>
+      <c r="B76" s="64" t="inlineStr">
         <is>
           <t>질병수술비</t>
         </is>
       </c>
-      <c r="C74" s="155" t="n"/>
-      <c r="D74" s="155" t="n"/>
-      <c r="E74" s="155" t="n"/>
-      <c r="F74" s="159" t="n"/>
-      <c r="G74" s="155" t="n"/>
-      <c r="H74" s="155" t="n"/>
-      <c r="I74" s="160" t="n"/>
-      <c r="J74" s="131">
-        <f>SUM(C63:I63)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" ht="16.5" customHeight="1" s="78">
-      <c r="A75" s="88" t="n"/>
-      <c r="B75" s="59" t="inlineStr">
+      <c r="C76" s="159" t="n"/>
+      <c r="D76" s="159" t="n"/>
+      <c r="E76" s="159" t="n"/>
+      <c r="F76" s="163" t="n"/>
+      <c r="G76" s="159" t="n"/>
+      <c r="H76" s="159" t="n"/>
+      <c r="I76" s="164" t="n"/>
+      <c r="J76" s="133">
+        <f>SUM(C65:I65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="16.5" customHeight="1" s="78">
+      <c r="A77" s="102" t="n"/>
+      <c r="B77" s="59" t="inlineStr">
         <is>
           <t>질병 종수술비(1-3종)</t>
         </is>
       </c>
-      <c r="C75" s="136" t="n"/>
-      <c r="D75" s="136" t="n"/>
-      <c r="E75" s="136" t="n"/>
-      <c r="F75" s="161" t="n"/>
-      <c r="G75" s="136" t="n"/>
-      <c r="H75" s="136" t="n"/>
-      <c r="I75" s="136" t="n"/>
-      <c r="J75" s="137" t="n"/>
-    </row>
-    <row r="76" ht="17.25" customHeight="1" s="78">
-      <c r="A76" s="88" t="n"/>
-      <c r="B76" s="59" t="inlineStr">
+      <c r="C77" s="138" t="n"/>
+      <c r="D77" s="138" t="n"/>
+      <c r="E77" s="138" t="n"/>
+      <c r="F77" s="165" t="n"/>
+      <c r="G77" s="138" t="n"/>
+      <c r="H77" s="138" t="n"/>
+      <c r="I77" s="138" t="n"/>
+      <c r="J77" s="139" t="n"/>
+    </row>
+    <row r="78" ht="17.25" customHeight="1" s="78">
+      <c r="A78" s="102" t="n"/>
+      <c r="B78" s="59" t="inlineStr">
         <is>
           <t>질병 종수술비(1-5종)</t>
         </is>
       </c>
-      <c r="C76" s="136" t="n"/>
-      <c r="D76" s="136" t="n"/>
-      <c r="E76" s="136" t="n"/>
-      <c r="F76" s="161" t="n"/>
-      <c r="G76" s="136" t="n"/>
-      <c r="H76" s="136" t="n"/>
-      <c r="I76" s="136" t="n"/>
-      <c r="J76" s="137" t="inlineStr">
+      <c r="C78" s="138" t="n"/>
+      <c r="D78" s="138" t="n"/>
+      <c r="E78" s="138" t="n"/>
+      <c r="F78" s="165" t="n"/>
+      <c r="G78" s="138" t="n"/>
+      <c r="H78" s="138" t="n"/>
+      <c r="I78" s="138" t="n"/>
+      <c r="J78" s="139" t="inlineStr">
         <is>
           <t>/ / / / /</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="16.5" customHeight="1" s="78">
-      <c r="A77" s="88" t="n"/>
-      <c r="B77" s="59" t="inlineStr">
+    <row r="79" ht="16.5" customHeight="1" s="78">
+      <c r="A79" s="102" t="n"/>
+      <c r="B79" s="59" t="inlineStr">
         <is>
           <t>질병 종수술비(1-8종)</t>
         </is>
       </c>
-      <c r="C77" s="136" t="n"/>
-      <c r="D77" s="136" t="n"/>
-      <c r="E77" s="136" t="n"/>
-      <c r="F77" s="161" t="n"/>
-      <c r="G77" s="136" t="n"/>
-      <c r="H77" s="136" t="n"/>
-      <c r="I77" s="136" t="n"/>
-      <c r="J77" s="137" t="n"/>
-    </row>
-    <row r="78" ht="16.5" customHeight="1" s="78">
-      <c r="A78" s="88" t="n"/>
-      <c r="B78" s="68" t="inlineStr">
+      <c r="C79" s="138" t="n"/>
+      <c r="D79" s="138" t="n"/>
+      <c r="E79" s="138" t="n"/>
+      <c r="F79" s="165" t="n"/>
+      <c r="G79" s="138" t="n"/>
+      <c r="H79" s="138" t="n"/>
+      <c r="I79" s="138" t="n"/>
+      <c r="J79" s="139" t="n"/>
+    </row>
+    <row r="80" ht="16.5" customHeight="1" s="78">
+      <c r="A80" s="102" t="n"/>
+      <c r="B80" s="68" t="inlineStr">
         <is>
           <t>뇌혈관수술비</t>
         </is>
       </c>
-      <c r="C78" s="162" t="n"/>
-      <c r="D78" s="162" t="n"/>
-      <c r="E78" s="162" t="n"/>
-      <c r="F78" s="162" t="n"/>
-      <c r="G78" s="162" t="n"/>
-      <c r="H78" s="162" t="n"/>
-      <c r="I78" s="162" t="n"/>
-      <c r="J78" s="137">
-        <f>SUM(C65:I65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="17.25" customHeight="1" s="78">
-      <c r="A79" s="88" t="n"/>
-      <c r="B79" s="68" t="inlineStr">
+      <c r="C80" s="166" t="n"/>
+      <c r="D80" s="166" t="n"/>
+      <c r="E80" s="166" t="n"/>
+      <c r="F80" s="166" t="n"/>
+      <c r="G80" s="166" t="n"/>
+      <c r="H80" s="166" t="n"/>
+      <c r="I80" s="166" t="n"/>
+      <c r="J80" s="139">
+        <f>SUM(C67:I67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="17.25" customHeight="1" s="78">
+      <c r="A81" s="102" t="n"/>
+      <c r="B81" s="68" t="inlineStr">
         <is>
           <t>허혈성수술비</t>
         </is>
       </c>
-      <c r="C79" s="162" t="n"/>
-      <c r="D79" s="162" t="n"/>
-      <c r="E79" s="162" t="n"/>
-      <c r="F79" s="162" t="n"/>
-      <c r="G79" s="162" t="n"/>
-      <c r="H79" s="162" t="n"/>
-      <c r="I79" s="162" t="n"/>
-      <c r="J79" s="137">
-        <f>SUM(C66:I66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" ht="17.25" customHeight="1" s="78">
-      <c r="A80" s="88" t="n"/>
-      <c r="B80" s="68" t="inlineStr">
+      <c r="C81" s="166" t="n"/>
+      <c r="D81" s="166" t="n"/>
+      <c r="E81" s="166" t="n"/>
+      <c r="F81" s="166" t="n"/>
+      <c r="G81" s="166" t="n"/>
+      <c r="H81" s="166" t="n"/>
+      <c r="I81" s="166" t="n"/>
+      <c r="J81" s="139">
+        <f>SUM(C68:I68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="17.25" customHeight="1" s="78">
+      <c r="A82" s="102" t="n"/>
+      <c r="B82" s="68" t="inlineStr">
         <is>
           <t>심장수술비</t>
         </is>
       </c>
-      <c r="C80" s="162" t="n"/>
-      <c r="D80" s="162" t="n"/>
-      <c r="E80" s="162" t="n"/>
-      <c r="F80" s="162" t="n"/>
-      <c r="G80" s="162" t="n"/>
-      <c r="H80" s="162" t="n"/>
-      <c r="I80" s="162" t="n"/>
-      <c r="J80" s="137">
-        <f>SUM(C67:I67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="17.25" customHeight="1" s="78" thickBot="1">
-      <c r="A81" s="88" t="n"/>
-      <c r="B81" s="60" t="inlineStr">
+      <c r="C82" s="166" t="n"/>
+      <c r="D82" s="166" t="n"/>
+      <c r="E82" s="166" t="n"/>
+      <c r="F82" s="166" t="n"/>
+      <c r="G82" s="166" t="n"/>
+      <c r="H82" s="166" t="n"/>
+      <c r="I82" s="166" t="n"/>
+      <c r="J82" s="139">
+        <f>SUM(C69:I69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="17.25" customHeight="1" s="78" thickBot="1">
+      <c r="A83" s="102" t="n"/>
+      <c r="B83" s="60" t="inlineStr">
         <is>
           <t>120대수술비</t>
         </is>
       </c>
-      <c r="C81" s="162" t="n"/>
-      <c r="D81" s="162" t="n"/>
-      <c r="E81" s="162" t="n"/>
-      <c r="F81" s="162" t="n"/>
-      <c r="G81" s="162" t="n"/>
-      <c r="H81" s="162" t="n"/>
-      <c r="I81" s="162" t="n"/>
-      <c r="J81" s="163">
-        <f>SUM(C68:I68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" ht="16.5" customHeight="1" s="78">
-      <c r="A82" s="88" t="n"/>
-      <c r="B82" s="69" t="inlineStr">
+      <c r="C83" s="166" t="n"/>
+      <c r="D83" s="166" t="n"/>
+      <c r="E83" s="166" t="n"/>
+      <c r="F83" s="166" t="n"/>
+      <c r="G83" s="166" t="n"/>
+      <c r="H83" s="166" t="n"/>
+      <c r="I83" s="166" t="n"/>
+      <c r="J83" s="167">
+        <f>SUM(C70:I70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="16.5" customHeight="1" s="78">
+      <c r="A84" s="102" t="n"/>
+      <c r="B84" s="69" t="inlineStr">
         <is>
           <t>5대기관 수술비 관혈</t>
         </is>
       </c>
-      <c r="C82" s="138" t="n"/>
-      <c r="D82" s="138" t="n"/>
-      <c r="E82" s="138" t="n"/>
-      <c r="F82" s="138" t="n"/>
-      <c r="G82" s="138" t="n"/>
-      <c r="H82" s="138" t="n"/>
-      <c r="I82" s="138" t="n"/>
-      <c r="J82" s="135">
-        <f>SUM(C69:I69)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" ht="17.25" customHeight="1" s="78" thickBot="1">
-      <c r="A83" s="89" t="n"/>
-      <c r="B83" s="70" t="inlineStr">
+      <c r="C84" s="140" t="n"/>
+      <c r="D84" s="140" t="n"/>
+      <c r="E84" s="140" t="n"/>
+      <c r="F84" s="140" t="n"/>
+      <c r="G84" s="140" t="n"/>
+      <c r="H84" s="140" t="n"/>
+      <c r="I84" s="140" t="n"/>
+      <c r="J84" s="137">
+        <f>SUM(C71:I71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="17.25" customHeight="1" s="78" thickBot="1">
+      <c r="A85" s="103" t="n"/>
+      <c r="B85" s="70" t="inlineStr">
         <is>
           <t>5대기관 수술비 비관혈</t>
         </is>
       </c>
-      <c r="C83" s="132" t="n"/>
-      <c r="D83" s="132" t="n"/>
-      <c r="E83" s="132" t="n"/>
-      <c r="F83" s="132" t="n"/>
-      <c r="G83" s="132" t="n"/>
-      <c r="H83" s="132" t="n"/>
-      <c r="I83" s="132" t="n"/>
-      <c r="J83" s="133">
-        <f>SUM(C70:I70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A84" s="93" t="inlineStr">
+      <c r="C85" s="134" t="n"/>
+      <c r="D85" s="134" t="n"/>
+      <c r="E85" s="134" t="n"/>
+      <c r="F85" s="134" t="n"/>
+      <c r="G85" s="134" t="n"/>
+      <c r="H85" s="134" t="n"/>
+      <c r="I85" s="134" t="n"/>
+      <c r="J85" s="135">
+        <f>SUM(C72:I72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A86" s="106" t="inlineStr">
         <is>
           <t>운전</t>
         </is>
       </c>
-      <c r="B84" s="28" t="inlineStr">
+      <c r="B86" s="28" t="inlineStr">
         <is>
           <t>대인</t>
         </is>
       </c>
-      <c r="C84" s="117" t="n"/>
-      <c r="D84" s="117" t="n"/>
-      <c r="E84" s="117" t="n"/>
-      <c r="F84" s="117" t="n"/>
-      <c r="G84" s="117" t="n"/>
-      <c r="H84" s="117" t="n"/>
-      <c r="I84" s="117" t="n"/>
-      <c r="J84" s="135">
-        <f>SUM(C71:I71)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="17.25" customHeight="1" s="78">
-      <c r="A85" s="92" t="n"/>
-      <c r="B85" s="31" t="inlineStr">
-        <is>
-          <t>대물</t>
-        </is>
-      </c>
-      <c r="C85" s="145" t="n"/>
-      <c r="D85" s="145" t="n"/>
-      <c r="E85" s="145" t="n"/>
-      <c r="F85" s="145" t="n"/>
-      <c r="G85" s="145" t="n"/>
-      <c r="H85" s="145" t="n"/>
-      <c r="I85" s="145" t="n"/>
-      <c r="J85" s="137">
-        <f>SUM(C72:I72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" ht="16.5" customHeight="1" s="78">
-      <c r="A86" s="92" t="n"/>
-      <c r="B86" s="31" t="inlineStr">
-        <is>
-          <t>합의금</t>
-        </is>
-      </c>
-      <c r="C86" s="145" t="n"/>
-      <c r="D86" s="145" t="n"/>
-      <c r="E86" s="145" t="n"/>
-      <c r="F86" s="145" t="n"/>
-      <c r="G86" s="145" t="n"/>
-      <c r="H86" s="145" t="n"/>
-      <c r="I86" s="145" t="n"/>
+      <c r="C86" s="119" t="n"/>
+      <c r="D86" s="119" t="n"/>
+      <c r="E86" s="119" t="n"/>
+      <c r="F86" s="119" t="n"/>
+      <c r="G86" s="119" t="n"/>
+      <c r="H86" s="119" t="n"/>
+      <c r="I86" s="119" t="n"/>
       <c r="J86" s="137">
         <f>SUM(C73:I73)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="16.5" customHeight="1" s="78">
-      <c r="A87" s="92" t="n"/>
-      <c r="B87" s="65" t="inlineStr">
+    <row r="87" ht="17.25" customHeight="1" s="78">
+      <c r="A87" s="107" t="n"/>
+      <c r="B87" s="31" t="inlineStr">
+        <is>
+          <t>대물</t>
+        </is>
+      </c>
+      <c r="C87" s="149" t="n"/>
+      <c r="D87" s="149" t="n"/>
+      <c r="E87" s="149" t="n"/>
+      <c r="F87" s="149" t="n"/>
+      <c r="G87" s="149" t="n"/>
+      <c r="H87" s="149" t="n"/>
+      <c r="I87" s="149" t="n"/>
+      <c r="J87" s="139">
+        <f>SUM(C74:I74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="16.5" customHeight="1" s="78">
+      <c r="A88" s="107" t="n"/>
+      <c r="B88" s="31" t="inlineStr">
+        <is>
+          <t>합의금</t>
+        </is>
+      </c>
+      <c r="C88" s="149" t="n"/>
+      <c r="D88" s="149" t="n"/>
+      <c r="E88" s="149" t="n"/>
+      <c r="F88" s="149" t="n"/>
+      <c r="G88" s="149" t="n"/>
+      <c r="H88" s="149" t="n"/>
+      <c r="I88" s="149" t="n"/>
+      <c r="J88" s="139">
+        <f>SUM(C75:I75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="16.5" customHeight="1" s="78">
+      <c r="A89" s="107" t="n"/>
+      <c r="B89" s="65" t="inlineStr">
         <is>
           <t>6주미만</t>
         </is>
       </c>
-      <c r="C87" s="145" t="n"/>
-      <c r="D87" s="145" t="n"/>
-      <c r="E87" s="145" t="n"/>
-      <c r="F87" s="145" t="n"/>
-      <c r="G87" s="145" t="n"/>
-      <c r="H87" s="145" t="n"/>
-      <c r="I87" s="145" t="n"/>
-      <c r="J87" s="137">
-        <f>SUM(C74:I74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="17.25" customHeight="1" s="78">
-      <c r="A88" s="92" t="n"/>
-      <c r="B88" s="31" t="inlineStr">
+      <c r="C89" s="149" t="n"/>
+      <c r="D89" s="149" t="n"/>
+      <c r="E89" s="149" t="n"/>
+      <c r="F89" s="149" t="n"/>
+      <c r="G89" s="149" t="n"/>
+      <c r="H89" s="149" t="n"/>
+      <c r="I89" s="149" t="n"/>
+      <c r="J89" s="139">
+        <f>SUM(C76:I76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="17.25" customHeight="1" s="78">
+      <c r="A90" s="107" t="n"/>
+      <c r="B90" s="31" t="inlineStr">
         <is>
           <t>변호사</t>
         </is>
       </c>
-      <c r="C88" s="145" t="n"/>
-      <c r="D88" s="145" t="n"/>
-      <c r="E88" s="145" t="n"/>
-      <c r="F88" s="145" t="n"/>
-      <c r="G88" s="145" t="n"/>
-      <c r="H88" s="145" t="n"/>
-      <c r="I88" s="145" t="n"/>
-      <c r="J88" s="137">
-        <f>SUM(C75:I75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="17.25" customHeight="1" s="78">
-      <c r="A89" s="94" t="n"/>
-      <c r="B89" s="25" t="inlineStr">
+      <c r="C90" s="149" t="n"/>
+      <c r="D90" s="149" t="n"/>
+      <c r="E90" s="149" t="n"/>
+      <c r="F90" s="149" t="n"/>
+      <c r="G90" s="149" t="n"/>
+      <c r="H90" s="149" t="n"/>
+      <c r="I90" s="149" t="n"/>
+      <c r="J90" s="139">
+        <f>SUM(C77:I77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="17.25" customHeight="1" s="78">
+      <c r="A91" s="108" t="n"/>
+      <c r="B91" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C89" s="164" t="n"/>
-      <c r="D89" s="164" t="n"/>
-      <c r="E89" s="164" t="n"/>
-      <c r="F89" s="164" t="n"/>
-      <c r="G89" s="164" t="n"/>
-      <c r="H89" s="164" t="n"/>
-      <c r="I89" s="164" t="n"/>
-      <c r="J89" s="133">
-        <f>SUM(C76:I76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="93" t="inlineStr">
+      <c r="C91" s="168" t="n"/>
+      <c r="D91" s="168" t="n"/>
+      <c r="E91" s="168" t="n"/>
+      <c r="F91" s="168" t="n"/>
+      <c r="G91" s="168" t="n"/>
+      <c r="H91" s="168" t="n"/>
+      <c r="I91" s="168" t="n"/>
+      <c r="J91" s="135">
+        <f>SUM(C78:I78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="106" t="inlineStr">
         <is>
           <t>골절</t>
         </is>
       </c>
-      <c r="B90" s="64" t="inlineStr">
+      <c r="B92" s="64" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C90" s="155" t="n"/>
-      <c r="D90" s="155" t="n"/>
-      <c r="E90" s="155" t="n"/>
-      <c r="F90" s="155" t="n"/>
-      <c r="G90" s="155" t="n"/>
-      <c r="H90" s="155" t="n"/>
-      <c r="I90" s="155" t="n"/>
-      <c r="J90" s="131">
-        <f>SUM(C77:I77)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="92" t="n"/>
-      <c r="B91" s="59" t="inlineStr">
-        <is>
-          <t>골절(치아파절제외)</t>
-        </is>
-      </c>
-      <c r="C91" s="136" t="n"/>
-      <c r="D91" s="136" t="n"/>
-      <c r="E91" s="136" t="n"/>
-      <c r="F91" s="136" t="n"/>
-      <c r="G91" s="136" t="n"/>
-      <c r="H91" s="136" t="n"/>
-      <c r="I91" s="136" t="n"/>
-      <c r="J91" s="137">
-        <f>SUM(C78:I78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="94" t="n"/>
-      <c r="B92" s="70" t="inlineStr">
-        <is>
-          <t>5대골절진단비</t>
-        </is>
-      </c>
-      <c r="C92" s="132" t="n"/>
-      <c r="D92" s="132" t="n"/>
-      <c r="E92" s="132" t="n"/>
-      <c r="F92" s="132" t="n"/>
-      <c r="G92" s="132" t="n"/>
-      <c r="H92" s="132" t="n"/>
-      <c r="I92" s="132" t="n"/>
+      <c r="C92" s="159" t="n"/>
+      <c r="D92" s="159" t="n"/>
+      <c r="E92" s="159" t="n"/>
+      <c r="F92" s="159" t="n"/>
+      <c r="G92" s="159" t="n"/>
+      <c r="H92" s="159" t="n"/>
+      <c r="I92" s="159" t="n"/>
       <c r="J92" s="133">
         <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="95" t="inlineStr">
+      <c r="A93" s="107" t="n"/>
+      <c r="B93" s="59" t="inlineStr">
+        <is>
+          <t>골절(치아파절제외)</t>
+        </is>
+      </c>
+      <c r="C93" s="138" t="n"/>
+      <c r="D93" s="138" t="n"/>
+      <c r="E93" s="138" t="n"/>
+      <c r="F93" s="138" t="n"/>
+      <c r="G93" s="138" t="n"/>
+      <c r="H93" s="138" t="n"/>
+      <c r="I93" s="138" t="n"/>
+      <c r="J93" s="139">
+        <f>SUM(C80:I80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="108" t="n"/>
+      <c r="B94" s="70" t="inlineStr">
+        <is>
+          <t>5대골절진단비</t>
+        </is>
+      </c>
+      <c r="C94" s="134" t="n"/>
+      <c r="D94" s="134" t="n"/>
+      <c r="E94" s="134" t="n"/>
+      <c r="F94" s="134" t="n"/>
+      <c r="G94" s="134" t="n"/>
+      <c r="H94" s="134" t="n"/>
+      <c r="I94" s="134" t="n"/>
+      <c r="J94" s="135">
+        <f>SUM(C81:I81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="109" t="inlineStr">
         <is>
           <t>응급실</t>
         </is>
       </c>
-      <c r="B93" s="63" t="inlineStr">
+      <c r="B95" s="63" t="inlineStr">
         <is>
           <t>응급실(응급)</t>
         </is>
       </c>
-      <c r="C93" s="128" t="n"/>
-      <c r="D93" s="128" t="n"/>
-      <c r="E93" s="128" t="n"/>
-      <c r="F93" s="128" t="n"/>
-      <c r="G93" s="128" t="n"/>
-      <c r="H93" s="128" t="n"/>
-      <c r="I93" s="128" t="n"/>
-      <c r="J93" s="129">
-        <f>SUM(C80:I80)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="87" t="inlineStr">
+      <c r="C95" s="130" t="n"/>
+      <c r="D95" s="130" t="n"/>
+      <c r="E95" s="130" t="n"/>
+      <c r="F95" s="130" t="n"/>
+      <c r="G95" s="130" t="n"/>
+      <c r="H95" s="130" t="n"/>
+      <c r="I95" s="130" t="n"/>
+      <c r="J95" s="131">
+        <f>SUM(C82:I82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="101" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="B94" s="34" t="inlineStr">
+      <c r="B96" s="34" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="C94" s="138" t="n"/>
-      <c r="D94" s="138" t="n"/>
-      <c r="E94" s="138" t="n"/>
-      <c r="F94" s="138" t="n"/>
-      <c r="G94" s="138" t="n"/>
-      <c r="H94" s="138" t="n"/>
-      <c r="I94" s="138" t="n"/>
-      <c r="J94" s="139" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="93" t="inlineStr">
+      <c r="C96" s="140" t="n"/>
+      <c r="D96" s="140" t="n"/>
+      <c r="E96" s="140" t="n"/>
+      <c r="F96" s="140" t="n"/>
+      <c r="G96" s="140" t="n"/>
+      <c r="H96" s="140" t="n"/>
+      <c r="I96" s="140" t="n"/>
+      <c r="J96" s="141" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="106" t="inlineStr">
         <is>
           <t>화상</t>
         </is>
       </c>
-      <c r="B95" s="28" t="inlineStr">
+      <c r="B97" s="28" t="inlineStr">
         <is>
           <t>화상진단비</t>
         </is>
       </c>
-      <c r="C95" s="134" t="n"/>
-      <c r="D95" s="134" t="n"/>
-      <c r="E95" s="134" t="n"/>
-      <c r="F95" s="134" t="n"/>
-      <c r="G95" s="134" t="n"/>
-      <c r="H95" s="134" t="n"/>
-      <c r="I95" s="134" t="n"/>
-      <c r="J95" s="135">
-        <f>SUM(C82:I82)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="94" t="n"/>
-      <c r="B96" s="25" t="inlineStr">
+      <c r="C97" s="136" t="n"/>
+      <c r="D97" s="136" t="n"/>
+      <c r="E97" s="136" t="n"/>
+      <c r="F97" s="136" t="n"/>
+      <c r="G97" s="136" t="n"/>
+      <c r="H97" s="136" t="n"/>
+      <c r="I97" s="136" t="n"/>
+      <c r="J97" s="137">
+        <f>SUM(C84:I84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="108" t="n"/>
+      <c r="B98" s="25" t="inlineStr">
         <is>
           <t>중증화상진단비</t>
         </is>
       </c>
-      <c r="C96" s="132" t="n"/>
-      <c r="D96" s="132" t="n"/>
-      <c r="E96" s="132" t="n"/>
-      <c r="F96" s="132" t="n"/>
-      <c r="G96" s="132" t="n"/>
-      <c r="H96" s="132" t="n"/>
-      <c r="I96" s="132" t="n"/>
-      <c r="J96" s="133">
-        <f>SUM(C83:I83)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="93" t="inlineStr">
+      <c r="C98" s="134" t="n"/>
+      <c r="D98" s="134" t="n"/>
+      <c r="E98" s="134" t="n"/>
+      <c r="F98" s="134" t="n"/>
+      <c r="G98" s="134" t="n"/>
+      <c r="H98" s="134" t="n"/>
+      <c r="I98" s="134" t="n"/>
+      <c r="J98" s="135">
+        <f>SUM(C85:I85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="106" t="inlineStr">
         <is>
           <t>깁스</t>
         </is>
       </c>
-      <c r="B97" s="90" t="inlineStr">
+      <c r="B99" s="104" t="inlineStr">
         <is>
           <t>반깁스</t>
         </is>
       </c>
-      <c r="C97" s="134" t="n"/>
-      <c r="D97" s="134" t="n"/>
-      <c r="E97" s="134" t="n"/>
-      <c r="F97" s="134" t="n"/>
-      <c r="G97" s="134" t="n"/>
-      <c r="H97" s="134" t="n"/>
-      <c r="I97" s="134" t="n"/>
-      <c r="J97" s="135">
-        <f>SUM(C84:I84)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="94" t="n"/>
-      <c r="B98" s="56" t="inlineStr">
+      <c r="C99" s="136" t="n"/>
+      <c r="D99" s="136" t="n"/>
+      <c r="E99" s="136" t="n"/>
+      <c r="F99" s="136" t="n"/>
+      <c r="G99" s="136" t="n"/>
+      <c r="H99" s="136" t="n"/>
+      <c r="I99" s="136" t="n"/>
+      <c r="J99" s="137">
+        <f>SUM(C86:I86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="108" t="n"/>
+      <c r="B100" s="56" t="inlineStr">
         <is>
           <t>깁스진단비</t>
         </is>
       </c>
-      <c r="C98" s="132" t="n"/>
-      <c r="D98" s="132" t="n"/>
-      <c r="E98" s="132" t="n"/>
-      <c r="F98" s="132" t="n"/>
-      <c r="G98" s="132" t="n"/>
-      <c r="H98" s="132" t="n"/>
-      <c r="I98" s="132" t="n"/>
-      <c r="J98" s="133">
-        <f>SUM(C85:I85)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="93" t="inlineStr">
+      <c r="C100" s="134" t="n"/>
+      <c r="D100" s="134" t="n"/>
+      <c r="E100" s="134" t="n"/>
+      <c r="F100" s="134" t="n"/>
+      <c r="G100" s="134" t="n"/>
+      <c r="H100" s="134" t="n"/>
+      <c r="I100" s="134" t="n"/>
+      <c r="J100" s="135">
+        <f>SUM(C87:I87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="106" t="inlineStr">
         <is>
           <t>실손</t>
         </is>
       </c>
-      <c r="B99" s="90" t="inlineStr">
+      <c r="B101" s="104" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="C99" s="165" t="n"/>
-      <c r="D99" s="165" t="n"/>
-      <c r="E99" s="165" t="n"/>
-      <c r="F99" s="165" t="n"/>
-      <c r="G99" s="165" t="n"/>
-      <c r="H99" s="165" t="n"/>
-      <c r="I99" s="165" t="n"/>
-      <c r="J99" s="135">
-        <f>SUM(C86:I86)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="92" t="n"/>
-      <c r="B100" s="59" t="inlineStr">
-        <is>
-          <t>통원</t>
-        </is>
-      </c>
-      <c r="C100" s="166" t="n"/>
-      <c r="D100" s="166" t="n"/>
-      <c r="E100" s="166" t="n"/>
-      <c r="F100" s="166" t="n"/>
-      <c r="G100" s="166" t="n"/>
-      <c r="H100" s="166" t="n"/>
-      <c r="I100" s="166" t="n"/>
-      <c r="J100" s="137">
-        <f>SUM(C87:I87)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="92" t="n"/>
-      <c r="B101" s="59" t="inlineStr">
-        <is>
-          <t>약값</t>
-        </is>
-      </c>
-      <c r="C101" s="136" t="n"/>
-      <c r="D101" s="136" t="n"/>
-      <c r="E101" s="136" t="n"/>
-      <c r="F101" s="136" t="n"/>
-      <c r="G101" s="136" t="n"/>
-      <c r="H101" s="136" t="n"/>
-      <c r="I101" s="166" t="n"/>
+      <c r="C101" s="169" t="n"/>
+      <c r="D101" s="169" t="n"/>
+      <c r="E101" s="169" t="n"/>
+      <c r="F101" s="169" t="n"/>
+      <c r="G101" s="169" t="n"/>
+      <c r="H101" s="169" t="n"/>
+      <c r="I101" s="169" t="n"/>
       <c r="J101" s="137">
         <f>SUM(C88:I88)</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="92" t="n"/>
+      <c r="A102" s="107" t="n"/>
       <c r="B102" s="59" t="inlineStr">
         <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="C102" s="170" t="n"/>
+      <c r="D102" s="170" t="n"/>
+      <c r="E102" s="170" t="n"/>
+      <c r="F102" s="170" t="n"/>
+      <c r="G102" s="170" t="n"/>
+      <c r="H102" s="170" t="n"/>
+      <c r="I102" s="170" t="n"/>
+      <c r="J102" s="139">
+        <f>SUM(C89:I89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="107" t="n"/>
+      <c r="B103" s="59" t="inlineStr">
+        <is>
+          <t>약값</t>
+        </is>
+      </c>
+      <c r="C103" s="138" t="n"/>
+      <c r="D103" s="138" t="n"/>
+      <c r="E103" s="138" t="n"/>
+      <c r="F103" s="138" t="n"/>
+      <c r="G103" s="138" t="n"/>
+      <c r="H103" s="138" t="n"/>
+      <c r="I103" s="170" t="n"/>
+      <c r="J103" s="139">
+        <f>SUM(C90:I90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="107" t="n"/>
+      <c r="B104" s="59" t="inlineStr">
+        <is>
           <t>MRI/도수치료/비급여주사</t>
         </is>
       </c>
-      <c r="C102" s="136" t="n"/>
-      <c r="D102" s="136" t="n"/>
-      <c r="E102" s="136" t="n"/>
-      <c r="F102" s="136" t="n"/>
-      <c r="G102" s="136" t="n"/>
-      <c r="H102" s="136" t="n"/>
-      <c r="I102" s="166" t="n"/>
-      <c r="J102" s="131" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="94" t="n"/>
-      <c r="B103" s="22" t="inlineStr">
+      <c r="C104" s="138" t="n"/>
+      <c r="D104" s="138" t="n"/>
+      <c r="E104" s="138" t="n"/>
+      <c r="F104" s="138" t="n"/>
+      <c r="G104" s="138" t="n"/>
+      <c r="H104" s="138" t="n"/>
+      <c r="I104" s="170" t="n"/>
+      <c r="J104" s="133" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="108" t="n"/>
+      <c r="B105" s="22" t="inlineStr">
         <is>
           <t>상해의료비</t>
         </is>
       </c>
-      <c r="C103" s="130" t="n"/>
-      <c r="D103" s="130" t="n"/>
-      <c r="E103" s="130" t="n"/>
-      <c r="F103" s="130" t="n"/>
-      <c r="G103" s="130" t="n"/>
-      <c r="H103" s="130" t="n"/>
-      <c r="I103" s="167" t="n"/>
-      <c r="J103" s="137" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="87" t="inlineStr">
+      <c r="C105" s="132" t="n"/>
+      <c r="D105" s="132" t="n"/>
+      <c r="E105" s="132" t="n"/>
+      <c r="F105" s="132" t="n"/>
+      <c r="G105" s="132" t="n"/>
+      <c r="H105" s="132" t="n"/>
+      <c r="I105" s="171" t="n"/>
+      <c r="J105" s="139" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="101" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B104" s="75" t="inlineStr">
+      <c r="B106" s="75" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C104" s="168" t="n"/>
-      <c r="D104" s="168" t="n"/>
-      <c r="E104" s="168" t="n"/>
-      <c r="F104" s="168" t="n"/>
-      <c r="G104" s="168" t="n"/>
-      <c r="H104" s="168" t="n"/>
-      <c r="I104" s="168" t="n"/>
-      <c r="J104" s="169">
-        <f>SUM(C89:I89)</f>
+      <c r="C106" s="172" t="n"/>
+      <c r="D106" s="172" t="n"/>
+      <c r="E106" s="172" t="n"/>
+      <c r="F106" s="172" t="n"/>
+      <c r="G106" s="172" t="n"/>
+      <c r="H106" s="172" t="n"/>
+      <c r="I106" s="172" t="n"/>
+      <c r="J106" s="173">
+        <f>SUM(C91:I91)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A30:A38"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A65:A83"/>
-    <mergeCell ref="A84:A89"/>
-    <mergeCell ref="A15:A29"/>
-    <mergeCell ref="A52:A64"/>
-    <mergeCell ref="A39:A51"/>
-    <mergeCell ref="A90:A92"/>
+    <mergeCell ref="A101:A105"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A86:A91"/>
+    <mergeCell ref="A15:A31"/>
+    <mergeCell ref="A92:A94"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A99:A103"/>
-    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="A99:A100"/>
     <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A54:A66"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A41:A53"/>
     <mergeCell ref="A97:A98"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A67:A85"/>
+    <mergeCell ref="A32:A40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>
@@ -3708,7 +3751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="12" customWidth="1" style="78" min="1" max="1"/>
@@ -5181,6 +5224,94 @@
       <c r="C76" s="0" t="inlineStr">
         <is>
           <t>항암방사선약물</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>통합암진단비</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="inlineStr">
+        <is>
+          <t>통합암</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>통합전이암진단비</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="inlineStr">
+        <is>
+          <t>통합전이암</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B79" s="0" t="inlineStr">
+        <is>
+          <t>§8.2 암·유사암(v248·v197·v227)</t>
+        </is>
+      </c>
+      <c r="C79" s="0" t="inlineStr">
+        <is>
+          <t>플래티넘 건강 리셋월렛II</t>
+        </is>
+      </c>
+      <c r="D79" s="0" t="inlineStr">
+        <is>
+          <t>10억 플랜</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>커버리지허용</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>라벨≠담보명 설계분</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>10억 플랜</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>담보명은 흥국 리셋월렛II — 라벨로는 자기 행 복귀 안 됨(정상)</t>
         </is>
       </c>
     </row>

--- a/master.xlsx
+++ b/master.xlsx
@@ -3075,7 +3075,7 @@
       <c r="A83" s="102" t="n"/>
       <c r="B83" s="60" t="inlineStr">
         <is>
-          <t>120대수술비</t>
+          <t>n대수술비</t>
         </is>
       </c>
       <c r="C83" s="166" t="n"/>
@@ -5294,22 +5294,22 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="0" t="inlineStr">
         <is>
           <t>커버리지허용</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>라벨≠담보명 설계분</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="0" t="inlineStr">
         <is>
           <t>10억 플랜</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="0" t="inlineStr">
         <is>
           <t>담보명은 흥국 리셋월렛II — 라벨로는 자기 행 복귀 안 됨(정상)</t>
         </is>

--- a/master.xlsx
+++ b/master.xlsx
@@ -135,7 +135,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -219,6 +219,11 @@
         <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="54">
     <border>
@@ -897,7 +902,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1390,6 +1395,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2177,38 +2200,38 @@
     </row>
     <row r="35" ht="16.5" customHeight="1" s="78">
       <c r="A35" s="102" t="n"/>
-      <c r="B35" s="93" t="inlineStr">
+      <c r="B35" s="174" t="inlineStr">
         <is>
           <t>뇌출혈진단비</t>
         </is>
       </c>
-      <c r="C35" s="153" t="n"/>
-      <c r="D35" s="153" t="n"/>
-      <c r="E35" s="153" t="n"/>
-      <c r="F35" s="153" t="n"/>
-      <c r="G35" s="153" t="n"/>
-      <c r="H35" s="153" t="n"/>
-      <c r="I35" s="153" t="n"/>
-      <c r="J35" s="154">
+      <c r="C35" s="175" t="n"/>
+      <c r="D35" s="175" t="n"/>
+      <c r="E35" s="175" t="n"/>
+      <c r="F35" s="175" t="n"/>
+      <c r="G35" s="175" t="n"/>
+      <c r="H35" s="175" t="n"/>
+      <c r="I35" s="175" t="n"/>
+      <c r="J35" s="176">
         <f>SUM(C34:I34)</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A36" s="102" t="n"/>
-      <c r="B36" s="96" t="inlineStr">
+      <c r="B36" s="177" t="inlineStr">
         <is>
           <t>중대한 뇌출혈</t>
         </is>
       </c>
-      <c r="C36" s="155" t="n"/>
-      <c r="D36" s="155" t="n"/>
-      <c r="E36" s="155" t="n"/>
-      <c r="F36" s="155" t="n"/>
-      <c r="G36" s="155" t="n"/>
-      <c r="H36" s="155" t="n"/>
-      <c r="I36" s="155" t="n"/>
-      <c r="J36" s="156">
+      <c r="C36" s="178" t="n"/>
+      <c r="D36" s="178" t="n"/>
+      <c r="E36" s="178" t="n"/>
+      <c r="F36" s="178" t="n"/>
+      <c r="G36" s="178" t="n"/>
+      <c r="H36" s="178" t="n"/>
+      <c r="I36" s="178" t="n"/>
+      <c r="J36" s="179">
         <f>SUM(C35:I35)</f>
         <v/>
       </c>

--- a/master.xlsx
+++ b/master.xlsx
@@ -3269,7 +3269,7 @@
         <v/>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="16.5" customHeight="1" s="78">
       <c r="A92" s="106" t="inlineStr">
         <is>
           <t>골절</t>
@@ -3292,7 +3292,7 @@
         <v/>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="16.5" customHeight="1" s="78">
       <c r="A93" s="107" t="n"/>
       <c r="B93" s="59" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v/>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="16.5" customHeight="1" s="78">
       <c r="A94" s="108" t="n"/>
       <c r="B94" s="70" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v/>
       </c>
     </row>
-    <row r="95">
+    <row r="95" ht="16.5" customHeight="1" s="78">
       <c r="A95" s="109" t="inlineStr">
         <is>
           <t>응급실</t>
@@ -3353,7 +3353,7 @@
         <v/>
       </c>
     </row>
-    <row r="96">
+    <row r="96" ht="16.5" customHeight="1" s="78">
       <c r="A96" s="101" t="inlineStr">
         <is>
           <t>독감</t>
@@ -3373,7 +3373,7 @@
       <c r="I96" s="140" t="n"/>
       <c r="J96" s="141" t="n"/>
     </row>
-    <row r="97">
+    <row r="97" ht="16.5" customHeight="1" s="78">
       <c r="A97" s="106" t="inlineStr">
         <is>
           <t>화상</t>
@@ -3396,7 +3396,7 @@
         <v/>
       </c>
     </row>
-    <row r="98">
+    <row r="98" ht="16.5" customHeight="1" s="78">
       <c r="A98" s="108" t="n"/>
       <c r="B98" s="25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
     </row>
-    <row r="99">
+    <row r="99" ht="16.5" customHeight="1" s="78">
       <c r="A99" s="106" t="inlineStr">
         <is>
           <t>깁스</t>
@@ -3438,7 +3438,7 @@
         <v/>
       </c>
     </row>
-    <row r="100">
+    <row r="100" ht="16.5" customHeight="1" s="78">
       <c r="A100" s="108" t="n"/>
       <c r="B100" s="56" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v/>
       </c>
     </row>
-    <row r="101">
+    <row r="101" ht="16.5" customHeight="1" s="78">
       <c r="A101" s="106" t="inlineStr">
         <is>
           <t>실손</t>
@@ -3480,7 +3480,7 @@
         <v/>
       </c>
     </row>
-    <row r="102">
+    <row r="102" ht="16.5" customHeight="1" s="78">
       <c r="A102" s="107" t="n"/>
       <c r="B102" s="59" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v/>
       </c>
     </row>
-    <row r="103">
+    <row r="103" ht="16.5" customHeight="1" s="78">
       <c r="A103" s="107" t="n"/>
       <c r="B103" s="59" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v/>
       </c>
     </row>
-    <row r="104">
+    <row r="104" ht="16.5" customHeight="1" s="78">
       <c r="A104" s="107" t="n"/>
       <c r="B104" s="59" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       <c r="I104" s="170" t="n"/>
       <c r="J104" s="133" t="n"/>
     </row>
-    <row r="105">
+    <row r="105" ht="16.5" customHeight="1" s="78">
       <c r="A105" s="108" t="n"/>
       <c r="B105" s="22" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
       <c r="I105" s="171" t="n"/>
       <c r="J105" s="139" t="n"/>
     </row>
-    <row r="106">
+    <row r="106" ht="16.5" customHeight="1" s="78">
       <c r="A106" s="101" t="inlineStr">
         <is>
           <t>일배책</t>

--- a/master.xlsx
+++ b/master.xlsx
@@ -1538,7 +1538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="78" min="1" max="1"/>
@@ -2689,7 +2689,7 @@
       <c r="A61" s="102" t="n"/>
       <c r="B61" s="31" t="inlineStr">
         <is>
-          <t>간병인지원일당</t>
+          <t>간병인질병일당(요양병원)</t>
         </is>
       </c>
       <c r="C61" s="138" t="n"/>
@@ -2705,7 +2705,7 @@
       <c r="A62" s="102" t="n"/>
       <c r="B62" s="31" t="inlineStr">
         <is>
-          <t>간호통합병동</t>
+          <t>간병인상해일당(요양병원)</t>
         </is>
       </c>
       <c r="C62" s="138" t="n"/>
@@ -2715,16 +2715,13 @@
       <c r="G62" s="138" t="n"/>
       <c r="H62" s="138" t="n"/>
       <c r="I62" s="138" t="n"/>
-      <c r="J62" s="139">
-        <f>SUM(C53:I53)</f>
-        <v/>
-      </c>
+      <c r="J62" s="139" t="n"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" s="78">
       <c r="A63" s="102" t="n"/>
-      <c r="B63" s="65" t="inlineStr">
-        <is>
-          <t>1인실 종합병원</t>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>간병인지원일당</t>
         </is>
       </c>
       <c r="C63" s="138" t="n"/>
@@ -2734,16 +2731,13 @@
       <c r="G63" s="138" t="n"/>
       <c r="H63" s="138" t="n"/>
       <c r="I63" s="138" t="n"/>
-      <c r="J63" s="139">
-        <f>SUM(C54:I54)</f>
-        <v/>
-      </c>
+      <c r="J63" s="139" t="n"/>
     </row>
     <row r="64" ht="17.25" customHeight="1" s="78">
       <c r="A64" s="102" t="n"/>
-      <c r="B64" s="65" t="inlineStr">
-        <is>
-          <t>1인실 상급병원</t>
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>간호통합병동</t>
         </is>
       </c>
       <c r="C64" s="138" t="n"/>
@@ -2754,15 +2748,15 @@
       <c r="H64" s="138" t="n"/>
       <c r="I64" s="138" t="n"/>
       <c r="J64" s="139">
-        <f>SUM(C55:I55)</f>
+        <f>SUM(C53:I53)</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="17.25" customHeight="1" s="78">
       <c r="A65" s="102" t="n"/>
-      <c r="B65" s="31" t="inlineStr">
-        <is>
-          <t>질병중환자실</t>
+      <c r="B65" s="65" t="inlineStr">
+        <is>
+          <t>1인실 종합병원</t>
         </is>
       </c>
       <c r="C65" s="138" t="n"/>
@@ -2773,112 +2767,110 @@
       <c r="H65" s="138" t="n"/>
       <c r="I65" s="138" t="n"/>
       <c r="J65" s="139">
+        <f>SUM(C54:I54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A66" s="102" t="n"/>
+      <c r="B66" s="65" t="inlineStr">
+        <is>
+          <t>1인실 상급병원</t>
+        </is>
+      </c>
+      <c r="C66" s="138" t="n"/>
+      <c r="D66" s="138" t="n"/>
+      <c r="E66" s="138" t="n"/>
+      <c r="F66" s="138" t="n"/>
+      <c r="G66" s="138" t="n"/>
+      <c r="H66" s="138" t="n"/>
+      <c r="I66" s="138" t="n"/>
+      <c r="J66" s="139">
+        <f>SUM(C55:I55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16.5" customHeight="1" s="78">
+      <c r="A67" s="103" t="n"/>
+      <c r="B67" s="31" t="inlineStr">
+        <is>
+          <t>질병중환자실</t>
+        </is>
+      </c>
+      <c r="C67" s="138" t="n"/>
+      <c r="D67" s="138" t="n"/>
+      <c r="E67" s="138" t="n"/>
+      <c r="F67" s="138" t="n"/>
+      <c r="G67" s="138" t="n"/>
+      <c r="H67" s="138" t="n"/>
+      <c r="I67" s="138" t="n"/>
+      <c r="J67" s="139">
         <f>SUM(C56:I56)</f>
         <v/>
       </c>
     </row>
-    <row r="66" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A66" s="103" t="n"/>
-      <c r="B66" s="25" t="inlineStr">
+    <row r="68" ht="16.5" customHeight="1" s="78">
+      <c r="A68" s="103" t="n"/>
+      <c r="B68" s="25" t="inlineStr">
         <is>
           <t>상해중환자실</t>
         </is>
       </c>
-      <c r="C66" s="134" t="n"/>
-      <c r="D66" s="134" t="n"/>
-      <c r="E66" s="134" t="n"/>
-      <c r="F66" s="134" t="n"/>
-      <c r="G66" s="134" t="n"/>
-      <c r="H66" s="134" t="n"/>
-      <c r="I66" s="134" t="n"/>
-      <c r="J66" s="135">
+      <c r="C68" s="134" t="n"/>
+      <c r="D68" s="134" t="n"/>
+      <c r="E68" s="134" t="n"/>
+      <c r="F68" s="134" t="n"/>
+      <c r="G68" s="134" t="n"/>
+      <c r="H68" s="134" t="n"/>
+      <c r="I68" s="134" t="n"/>
+      <c r="J68" s="135">
         <f>SUM(C57:I57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16.5" customHeight="1" s="78">
-      <c r="A67" s="101" t="inlineStr">
-        <is>
-          <t>수술</t>
-        </is>
-      </c>
-      <c r="B67" s="104" t="inlineStr">
-        <is>
-          <t>상해수술비</t>
-        </is>
-      </c>
-      <c r="C67" s="136" t="n"/>
-      <c r="D67" s="136" t="n"/>
-      <c r="E67" s="136" t="n"/>
-      <c r="F67" s="136" t="n"/>
-      <c r="G67" s="136" t="n"/>
-      <c r="H67" s="136" t="n"/>
-      <c r="I67" s="136" t="n"/>
-      <c r="J67" s="137">
-        <f>SUM(C58:I58)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="16.5" customHeight="1" s="78">
-      <c r="A68" s="102" t="n"/>
-      <c r="B68" s="64" t="inlineStr">
-        <is>
-          <t>중대한상해수술비</t>
-        </is>
-      </c>
-      <c r="C68" s="159" t="n"/>
-      <c r="D68" s="159" t="n"/>
-      <c r="E68" s="159" t="n"/>
-      <c r="F68" s="159" t="n"/>
-      <c r="G68" s="159" t="n"/>
-      <c r="H68" s="159" t="n"/>
-      <c r="I68" s="159" t="n"/>
-      <c r="J68" s="139">
-        <f>SUM(C59:I59)</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="78">
       <c r="A69" s="102" t="n"/>
-      <c r="B69" s="59" t="inlineStr">
-        <is>
-          <t>상해 종수술비(1-3종)</t>
-        </is>
-      </c>
-      <c r="C69" s="159" t="n"/>
-      <c r="D69" s="159" t="n"/>
-      <c r="E69" s="159" t="n"/>
-      <c r="F69" s="160" t="n"/>
-      <c r="G69" s="159" t="n"/>
-      <c r="H69" s="159" t="n"/>
-      <c r="I69" s="159" t="n"/>
-      <c r="J69" s="139" t="n"/>
+      <c r="B69" s="104" t="inlineStr">
+        <is>
+          <t>상해수술비</t>
+        </is>
+      </c>
+      <c r="C69" s="136" t="n"/>
+      <c r="D69" s="136" t="n"/>
+      <c r="E69" s="136" t="n"/>
+      <c r="F69" s="136" t="n"/>
+      <c r="G69" s="136" t="n"/>
+      <c r="H69" s="136" t="n"/>
+      <c r="I69" s="136" t="n"/>
+      <c r="J69" s="137">
+        <f>SUM(C58:I58)</f>
+        <v/>
+      </c>
     </row>
     <row r="70" ht="17.25" customHeight="1" s="78">
       <c r="A70" s="102" t="n"/>
-      <c r="B70" s="59" t="inlineStr">
-        <is>
-          <t>상해 종수술비(1-5종)</t>
+      <c r="B70" s="64" t="inlineStr">
+        <is>
+          <t>중대한상해수술비</t>
         </is>
       </c>
       <c r="C70" s="159" t="n"/>
       <c r="D70" s="159" t="n"/>
       <c r="E70" s="159" t="n"/>
-      <c r="F70" s="160" t="n"/>
+      <c r="F70" s="159" t="n"/>
       <c r="G70" s="159" t="n"/>
       <c r="H70" s="159" t="n"/>
       <c r="I70" s="159" t="n"/>
-      <c r="J70" s="139" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="J70" s="139">
+        <f>SUM(C59:I59)</f>
+        <v/>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="78">
       <c r="A71" s="102" t="n"/>
       <c r="B71" s="59" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-8종)</t>
+          <t>상해 종수술비(1-3종)</t>
         </is>
       </c>
       <c r="C71" s="159" t="n"/>
@@ -2894,45 +2886,43 @@
       <c r="A72" s="102" t="n"/>
       <c r="B72" s="59" t="inlineStr">
         <is>
-          <t>창상봉합술</t>
-        </is>
-      </c>
-      <c r="C72" s="138" t="n"/>
-      <c r="D72" s="138" t="n"/>
-      <c r="E72" s="138" t="n"/>
-      <c r="F72" s="161" t="n"/>
-      <c r="G72" s="138" t="n"/>
-      <c r="H72" s="138" t="n"/>
-      <c r="I72" s="138" t="n"/>
-      <c r="J72" s="139">
-        <f>SUM(C61:I61)</f>
-        <v/>
+          <t>상해 종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="C72" s="159" t="n"/>
+      <c r="D72" s="159" t="n"/>
+      <c r="E72" s="159" t="n"/>
+      <c r="F72" s="160" t="n"/>
+      <c r="G72" s="159" t="n"/>
+      <c r="H72" s="159" t="n"/>
+      <c r="I72" s="159" t="n"/>
+      <c r="J72" s="139" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="78">
       <c r="A73" s="102" t="n"/>
       <c r="B73" s="59" t="inlineStr">
         <is>
-          <t>골절수술비</t>
-        </is>
-      </c>
-      <c r="C73" s="138" t="n"/>
-      <c r="D73" s="138" t="n"/>
-      <c r="E73" s="138" t="n"/>
-      <c r="F73" s="161" t="n"/>
-      <c r="G73" s="138" t="n"/>
-      <c r="H73" s="138" t="n"/>
-      <c r="I73" s="138" t="n"/>
-      <c r="J73" s="139">
-        <f>SUM(C62:I62)</f>
-        <v/>
-      </c>
+          <t>상해 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C73" s="159" t="n"/>
+      <c r="D73" s="159" t="n"/>
+      <c r="E73" s="159" t="n"/>
+      <c r="F73" s="160" t="n"/>
+      <c r="G73" s="159" t="n"/>
+      <c r="H73" s="159" t="n"/>
+      <c r="I73" s="159" t="n"/>
+      <c r="J73" s="139" t="n"/>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="78">
       <c r="A74" s="102" t="n"/>
-      <c r="B74" s="66" t="inlineStr">
-        <is>
-          <t>5대골절수술비</t>
+      <c r="B74" s="59" t="inlineStr">
+        <is>
+          <t>창상봉합술</t>
         </is>
       </c>
       <c r="C74" s="138" t="n"/>
@@ -2943,89 +2933,91 @@
       <c r="H74" s="138" t="n"/>
       <c r="I74" s="138" t="n"/>
       <c r="J74" s="139">
-        <f>SUM(C63:I63)</f>
+        <f>SUM(C61:I61)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A75" s="102" t="n"/>
-      <c r="B75" s="56" t="inlineStr">
-        <is>
-          <t>화상수술비</t>
-        </is>
-      </c>
-      <c r="C75" s="134" t="n"/>
-      <c r="D75" s="134" t="n"/>
-      <c r="E75" s="134" t="n"/>
-      <c r="F75" s="162" t="n"/>
-      <c r="G75" s="134" t="n"/>
-      <c r="H75" s="134" t="n"/>
-      <c r="I75" s="134" t="n"/>
-      <c r="J75" s="135">
-        <f>SUM(C64:I64)</f>
+      <c r="B75" s="59" t="inlineStr">
+        <is>
+          <t>골절수술비</t>
+        </is>
+      </c>
+      <c r="C75" s="138" t="n"/>
+      <c r="D75" s="138" t="n"/>
+      <c r="E75" s="138" t="n"/>
+      <c r="F75" s="161" t="n"/>
+      <c r="G75" s="138" t="n"/>
+      <c r="H75" s="138" t="n"/>
+      <c r="I75" s="138" t="n"/>
+      <c r="J75" s="139">
+        <f>SUM(C62:I62)</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16.5" customHeight="1" s="78">
       <c r="A76" s="102" t="n"/>
-      <c r="B76" s="64" t="inlineStr">
-        <is>
-          <t>질병수술비</t>
-        </is>
-      </c>
-      <c r="C76" s="159" t="n"/>
-      <c r="D76" s="159" t="n"/>
-      <c r="E76" s="159" t="n"/>
-      <c r="F76" s="163" t="n"/>
-      <c r="G76" s="159" t="n"/>
-      <c r="H76" s="159" t="n"/>
-      <c r="I76" s="164" t="n"/>
-      <c r="J76" s="133">
-        <f>SUM(C65:I65)</f>
+      <c r="B76" s="66" t="inlineStr">
+        <is>
+          <t>5대골절수술비</t>
+        </is>
+      </c>
+      <c r="C76" s="138" t="n"/>
+      <c r="D76" s="138" t="n"/>
+      <c r="E76" s="138" t="n"/>
+      <c r="F76" s="161" t="n"/>
+      <c r="G76" s="138" t="n"/>
+      <c r="H76" s="138" t="n"/>
+      <c r="I76" s="138" t="n"/>
+      <c r="J76" s="139">
+        <f>SUM(C63:I63)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="78">
       <c r="A77" s="102" t="n"/>
-      <c r="B77" s="59" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-3종)</t>
-        </is>
-      </c>
-      <c r="C77" s="138" t="n"/>
-      <c r="D77" s="138" t="n"/>
-      <c r="E77" s="138" t="n"/>
-      <c r="F77" s="165" t="n"/>
-      <c r="G77" s="138" t="n"/>
-      <c r="H77" s="138" t="n"/>
-      <c r="I77" s="138" t="n"/>
-      <c r="J77" s="139" t="n"/>
+      <c r="B77" s="56" t="inlineStr">
+        <is>
+          <t>화상수술비</t>
+        </is>
+      </c>
+      <c r="C77" s="134" t="n"/>
+      <c r="D77" s="134" t="n"/>
+      <c r="E77" s="134" t="n"/>
+      <c r="F77" s="162" t="n"/>
+      <c r="G77" s="134" t="n"/>
+      <c r="H77" s="134" t="n"/>
+      <c r="I77" s="134" t="n"/>
+      <c r="J77" s="135">
+        <f>SUM(C64:I64)</f>
+        <v/>
+      </c>
     </row>
     <row r="78" ht="17.25" customHeight="1" s="78">
       <c r="A78" s="102" t="n"/>
-      <c r="B78" s="59" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-5종)</t>
-        </is>
-      </c>
-      <c r="C78" s="138" t="n"/>
-      <c r="D78" s="138" t="n"/>
-      <c r="E78" s="138" t="n"/>
-      <c r="F78" s="165" t="n"/>
-      <c r="G78" s="138" t="n"/>
-      <c r="H78" s="138" t="n"/>
-      <c r="I78" s="138" t="n"/>
-      <c r="J78" s="139" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="B78" s="64" t="inlineStr">
+        <is>
+          <t>질병수술비</t>
+        </is>
+      </c>
+      <c r="C78" s="159" t="n"/>
+      <c r="D78" s="159" t="n"/>
+      <c r="E78" s="159" t="n"/>
+      <c r="F78" s="163" t="n"/>
+      <c r="G78" s="159" t="n"/>
+      <c r="H78" s="159" t="n"/>
+      <c r="I78" s="164" t="n"/>
+      <c r="J78" s="133">
+        <f>SUM(C65:I65)</f>
+        <v/>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1" s="78">
       <c r="A79" s="102" t="n"/>
       <c r="B79" s="59" t="inlineStr">
         <is>
-          <t>질병 종수술비(1-8종)</t>
+          <t>질병 종수술비(1-3종)</t>
         </is>
       </c>
       <c r="C79" s="138" t="n"/>
@@ -3039,47 +3031,45 @@
     </row>
     <row r="80" ht="16.5" customHeight="1" s="78">
       <c r="A80" s="102" t="n"/>
-      <c r="B80" s="68" t="inlineStr">
-        <is>
-          <t>뇌혈관수술비</t>
-        </is>
-      </c>
-      <c r="C80" s="166" t="n"/>
-      <c r="D80" s="166" t="n"/>
-      <c r="E80" s="166" t="n"/>
-      <c r="F80" s="166" t="n"/>
-      <c r="G80" s="166" t="n"/>
-      <c r="H80" s="166" t="n"/>
-      <c r="I80" s="166" t="n"/>
-      <c r="J80" s="139">
-        <f>SUM(C67:I67)</f>
-        <v/>
+      <c r="B80" s="59" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="C80" s="138" t="n"/>
+      <c r="D80" s="138" t="n"/>
+      <c r="E80" s="138" t="n"/>
+      <c r="F80" s="165" t="n"/>
+      <c r="G80" s="138" t="n"/>
+      <c r="H80" s="138" t="n"/>
+      <c r="I80" s="138" t="n"/>
+      <c r="J80" s="139" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="81" ht="17.25" customHeight="1" s="78">
       <c r="A81" s="102" t="n"/>
-      <c r="B81" s="68" t="inlineStr">
-        <is>
-          <t>허혈성수술비</t>
-        </is>
-      </c>
-      <c r="C81" s="166" t="n"/>
-      <c r="D81" s="166" t="n"/>
-      <c r="E81" s="166" t="n"/>
-      <c r="F81" s="166" t="n"/>
-      <c r="G81" s="166" t="n"/>
-      <c r="H81" s="166" t="n"/>
-      <c r="I81" s="166" t="n"/>
-      <c r="J81" s="139">
-        <f>SUM(C68:I68)</f>
-        <v/>
-      </c>
+      <c r="B81" s="59" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C81" s="138" t="n"/>
+      <c r="D81" s="138" t="n"/>
+      <c r="E81" s="138" t="n"/>
+      <c r="F81" s="165" t="n"/>
+      <c r="G81" s="138" t="n"/>
+      <c r="H81" s="138" t="n"/>
+      <c r="I81" s="138" t="n"/>
+      <c r="J81" s="139" t="n"/>
     </row>
     <row r="82" ht="17.25" customHeight="1" s="78">
       <c r="A82" s="102" t="n"/>
       <c r="B82" s="68" t="inlineStr">
         <is>
-          <t>심장수술비</t>
+          <t>뇌혈관수술비</t>
         </is>
       </c>
       <c r="C82" s="166" t="n"/>
@@ -3090,15 +3080,15 @@
       <c r="H82" s="166" t="n"/>
       <c r="I82" s="166" t="n"/>
       <c r="J82" s="139">
-        <f>SUM(C69:I69)</f>
+        <f>SUM(C67:I67)</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="17.25" customHeight="1" s="78" thickBot="1">
       <c r="A83" s="102" t="n"/>
-      <c r="B83" s="60" t="inlineStr">
-        <is>
-          <t>n대수술비</t>
+      <c r="B83" s="68" t="inlineStr">
+        <is>
+          <t>허혈성수술비</t>
         </is>
       </c>
       <c r="C83" s="166" t="n"/>
@@ -3108,115 +3098,111 @@
       <c r="G83" s="166" t="n"/>
       <c r="H83" s="166" t="n"/>
       <c r="I83" s="166" t="n"/>
-      <c r="J83" s="167">
-        <f>SUM(C70:I70)</f>
+      <c r="J83" s="139">
+        <f>SUM(C68:I68)</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="78">
       <c r="A84" s="102" t="n"/>
-      <c r="B84" s="69" t="inlineStr">
+      <c r="B84" s="68" t="inlineStr">
+        <is>
+          <t>심장수술비</t>
+        </is>
+      </c>
+      <c r="C84" s="166" t="n"/>
+      <c r="D84" s="166" t="n"/>
+      <c r="E84" s="166" t="n"/>
+      <c r="F84" s="166" t="n"/>
+      <c r="G84" s="166" t="n"/>
+      <c r="H84" s="166" t="n"/>
+      <c r="I84" s="166" t="n"/>
+      <c r="J84" s="139">
+        <f>SUM(C69:I69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="17.25" customHeight="1" s="78" thickBot="1">
+      <c r="A85" s="102" t="n"/>
+      <c r="B85" s="60" t="inlineStr">
+        <is>
+          <t>n대수술비</t>
+        </is>
+      </c>
+      <c r="C85" s="166" t="n"/>
+      <c r="D85" s="166" t="n"/>
+      <c r="E85" s="166" t="n"/>
+      <c r="F85" s="166" t="n"/>
+      <c r="G85" s="166" t="n"/>
+      <c r="H85" s="166" t="n"/>
+      <c r="I85" s="166" t="n"/>
+      <c r="J85" s="167">
+        <f>SUM(C70:I70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A86" s="103" t="n"/>
+      <c r="B86" s="69" t="inlineStr">
         <is>
           <t>5대기관 수술비 관혈</t>
         </is>
       </c>
-      <c r="C84" s="140" t="n"/>
-      <c r="D84" s="140" t="n"/>
-      <c r="E84" s="140" t="n"/>
-      <c r="F84" s="140" t="n"/>
-      <c r="G84" s="140" t="n"/>
-      <c r="H84" s="140" t="n"/>
-      <c r="I84" s="140" t="n"/>
-      <c r="J84" s="137">
+      <c r="C86" s="140" t="n"/>
+      <c r="D86" s="140" t="n"/>
+      <c r="E86" s="140" t="n"/>
+      <c r="F86" s="140" t="n"/>
+      <c r="G86" s="140" t="n"/>
+      <c r="H86" s="140" t="n"/>
+      <c r="I86" s="140" t="n"/>
+      <c r="J86" s="137">
         <f>SUM(C71:I71)</f>
         <v/>
       </c>
     </row>
-    <row r="85" ht="17.25" customHeight="1" s="78" thickBot="1">
-      <c r="A85" s="103" t="n"/>
-      <c r="B85" s="70" t="inlineStr">
+    <row r="87" ht="17.25" customHeight="1" s="78">
+      <c r="A87" s="103" t="n"/>
+      <c r="B87" s="70" t="inlineStr">
         <is>
           <t>5대기관 수술비 비관혈</t>
         </is>
       </c>
-      <c r="C85" s="134" t="n"/>
-      <c r="D85" s="134" t="n"/>
-      <c r="E85" s="134" t="n"/>
-      <c r="F85" s="134" t="n"/>
-      <c r="G85" s="134" t="n"/>
-      <c r="H85" s="134" t="n"/>
-      <c r="I85" s="134" t="n"/>
-      <c r="J85" s="135">
+      <c r="C87" s="134" t="n"/>
+      <c r="D87" s="134" t="n"/>
+      <c r="E87" s="134" t="n"/>
+      <c r="F87" s="134" t="n"/>
+      <c r="G87" s="134" t="n"/>
+      <c r="H87" s="134" t="n"/>
+      <c r="I87" s="134" t="n"/>
+      <c r="J87" s="135">
         <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A86" s="106" t="inlineStr">
-        <is>
-          <t>운전</t>
-        </is>
-      </c>
-      <c r="B86" s="28" t="inlineStr">
+    <row r="88" ht="16.5" customHeight="1" s="78">
+      <c r="A88" s="102" t="n"/>
+      <c r="B88" s="28" t="inlineStr">
         <is>
           <t>대인</t>
         </is>
       </c>
-      <c r="C86" s="119" t="n"/>
-      <c r="D86" s="119" t="n"/>
-      <c r="E86" s="119" t="n"/>
-      <c r="F86" s="119" t="n"/>
-      <c r="G86" s="119" t="n"/>
-      <c r="H86" s="119" t="n"/>
-      <c r="I86" s="119" t="n"/>
-      <c r="J86" s="137">
+      <c r="C88" s="119" t="n"/>
+      <c r="D88" s="119" t="n"/>
+      <c r="E88" s="119" t="n"/>
+      <c r="F88" s="119" t="n"/>
+      <c r="G88" s="119" t="n"/>
+      <c r="H88" s="119" t="n"/>
+      <c r="I88" s="119" t="n"/>
+      <c r="J88" s="137">
         <f>SUM(C73:I73)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="17.25" customHeight="1" s="78">
-      <c r="A87" s="107" t="n"/>
-      <c r="B87" s="31" t="inlineStr">
+    <row r="89" ht="16.5" customHeight="1" s="78">
+      <c r="A89" s="102" t="n"/>
+      <c r="B89" s="31" t="inlineStr">
         <is>
           <t>대물</t>
-        </is>
-      </c>
-      <c r="C87" s="149" t="n"/>
-      <c r="D87" s="149" t="n"/>
-      <c r="E87" s="149" t="n"/>
-      <c r="F87" s="149" t="n"/>
-      <c r="G87" s="149" t="n"/>
-      <c r="H87" s="149" t="n"/>
-      <c r="I87" s="149" t="n"/>
-      <c r="J87" s="139">
-        <f>SUM(C74:I74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="16.5" customHeight="1" s="78">
-      <c r="A88" s="107" t="n"/>
-      <c r="B88" s="31" t="inlineStr">
-        <is>
-          <t>합의금</t>
-        </is>
-      </c>
-      <c r="C88" s="149" t="n"/>
-      <c r="D88" s="149" t="n"/>
-      <c r="E88" s="149" t="n"/>
-      <c r="F88" s="149" t="n"/>
-      <c r="G88" s="149" t="n"/>
-      <c r="H88" s="149" t="n"/>
-      <c r="I88" s="149" t="n"/>
-      <c r="J88" s="139">
-        <f>SUM(C75:I75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="16.5" customHeight="1" s="78">
-      <c r="A89" s="107" t="n"/>
-      <c r="B89" s="65" t="inlineStr">
-        <is>
-          <t>6주미만</t>
         </is>
       </c>
       <c r="C89" s="149" t="n"/>
@@ -3227,15 +3213,15 @@
       <c r="H89" s="149" t="n"/>
       <c r="I89" s="149" t="n"/>
       <c r="J89" s="139">
-        <f>SUM(C76:I76)</f>
+        <f>SUM(C74:I74)</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="17.25" customHeight="1" s="78">
-      <c r="A90" s="107" t="n"/>
+      <c r="A90" s="102" t="n"/>
       <c r="B90" s="31" t="inlineStr">
         <is>
-          <t>변호사</t>
+          <t>합의금</t>
         </is>
       </c>
       <c r="C90" s="149" t="n"/>
@@ -3246,184 +3232,172 @@
       <c r="H90" s="149" t="n"/>
       <c r="I90" s="149" t="n"/>
       <c r="J90" s="139">
+        <f>SUM(C75:I75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="17.25" customHeight="1" s="78">
+      <c r="A91" s="102" t="n"/>
+      <c r="B91" s="65" t="inlineStr">
+        <is>
+          <t>6주미만</t>
+        </is>
+      </c>
+      <c r="C91" s="149" t="n"/>
+      <c r="D91" s="149" t="n"/>
+      <c r="E91" s="149" t="n"/>
+      <c r="F91" s="149" t="n"/>
+      <c r="G91" s="149" t="n"/>
+      <c r="H91" s="149" t="n"/>
+      <c r="I91" s="149" t="n"/>
+      <c r="J91" s="139">
+        <f>SUM(C76:I76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="16.5" customHeight="1" s="78">
+      <c r="A92" s="103" t="n"/>
+      <c r="B92" s="31" t="inlineStr">
+        <is>
+          <t>변호사</t>
+        </is>
+      </c>
+      <c r="C92" s="149" t="n"/>
+      <c r="D92" s="149" t="n"/>
+      <c r="E92" s="149" t="n"/>
+      <c r="F92" s="149" t="n"/>
+      <c r="G92" s="149" t="n"/>
+      <c r="H92" s="149" t="n"/>
+      <c r="I92" s="149" t="n"/>
+      <c r="J92" s="139">
         <f>SUM(C77:I77)</f>
         <v/>
       </c>
     </row>
-    <row r="91" ht="17.25" customHeight="1" s="78">
-      <c r="A91" s="108" t="n"/>
-      <c r="B91" s="25" t="inlineStr">
+    <row r="93" ht="16.5" customHeight="1" s="78">
+      <c r="A93" s="108" t="n"/>
+      <c r="B93" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C91" s="168" t="n"/>
-      <c r="D91" s="168" t="n"/>
-      <c r="E91" s="168" t="n"/>
-      <c r="F91" s="168" t="n"/>
-      <c r="G91" s="168" t="n"/>
-      <c r="H91" s="168" t="n"/>
-      <c r="I91" s="168" t="n"/>
-      <c r="J91" s="135">
+      <c r="C93" s="168" t="n"/>
+      <c r="D93" s="168" t="n"/>
+      <c r="E93" s="168" t="n"/>
+      <c r="F93" s="168" t="n"/>
+      <c r="G93" s="168" t="n"/>
+      <c r="H93" s="168" t="n"/>
+      <c r="I93" s="168" t="n"/>
+      <c r="J93" s="135">
         <f>SUM(C78:I78)</f>
         <v/>
       </c>
     </row>
-    <row r="92" ht="16.5" customHeight="1" s="78">
-      <c r="A92" s="106" t="inlineStr">
-        <is>
-          <t>골절</t>
-        </is>
-      </c>
-      <c r="B92" s="64" t="inlineStr">
+    <row r="94" ht="16.5" customHeight="1" s="78">
+      <c r="A94" s="107" t="n"/>
+      <c r="B94" s="64" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C92" s="159" t="n"/>
-      <c r="D92" s="159" t="n"/>
-      <c r="E92" s="159" t="n"/>
-      <c r="F92" s="159" t="n"/>
-      <c r="G92" s="159" t="n"/>
-      <c r="H92" s="159" t="n"/>
-      <c r="I92" s="159" t="n"/>
-      <c r="J92" s="133">
+      <c r="C94" s="159" t="n"/>
+      <c r="D94" s="159" t="n"/>
+      <c r="E94" s="159" t="n"/>
+      <c r="F94" s="159" t="n"/>
+      <c r="G94" s="159" t="n"/>
+      <c r="H94" s="159" t="n"/>
+      <c r="I94" s="159" t="n"/>
+      <c r="J94" s="133">
         <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
-    <row r="93" ht="16.5" customHeight="1" s="78">
-      <c r="A93" s="107" t="n"/>
-      <c r="B93" s="59" t="inlineStr">
+    <row r="95" ht="16.5" customHeight="1" s="78">
+      <c r="A95" s="108" t="n"/>
+      <c r="B95" s="59" t="inlineStr">
         <is>
           <t>골절(치아파절제외)</t>
         </is>
       </c>
-      <c r="C93" s="138" t="n"/>
-      <c r="D93" s="138" t="n"/>
-      <c r="E93" s="138" t="n"/>
-      <c r="F93" s="138" t="n"/>
-      <c r="G93" s="138" t="n"/>
-      <c r="H93" s="138" t="n"/>
-      <c r="I93" s="138" t="n"/>
-      <c r="J93" s="139">
+      <c r="C95" s="138" t="n"/>
+      <c r="D95" s="138" t="n"/>
+      <c r="E95" s="138" t="n"/>
+      <c r="F95" s="138" t="n"/>
+      <c r="G95" s="138" t="n"/>
+      <c r="H95" s="138" t="n"/>
+      <c r="I95" s="138" t="n"/>
+      <c r="J95" s="139">
         <f>SUM(C80:I80)</f>
         <v/>
       </c>
     </row>
-    <row r="94" ht="16.5" customHeight="1" s="78">
-      <c r="A94" s="108" t="n"/>
-      <c r="B94" s="70" t="inlineStr">
+    <row r="96" ht="16.5" customHeight="1" s="78">
+      <c r="A96" s="108" t="n"/>
+      <c r="B96" s="70" t="inlineStr">
         <is>
           <t>5대골절진단비</t>
         </is>
       </c>
-      <c r="C94" s="134" t="n"/>
-      <c r="D94" s="134" t="n"/>
-      <c r="E94" s="134" t="n"/>
-      <c r="F94" s="134" t="n"/>
-      <c r="G94" s="134" t="n"/>
-      <c r="H94" s="134" t="n"/>
-      <c r="I94" s="134" t="n"/>
-      <c r="J94" s="135">
+      <c r="C96" s="134" t="n"/>
+      <c r="D96" s="134" t="n"/>
+      <c r="E96" s="134" t="n"/>
+      <c r="F96" s="134" t="n"/>
+      <c r="G96" s="134" t="n"/>
+      <c r="H96" s="134" t="n"/>
+      <c r="I96" s="134" t="n"/>
+      <c r="J96" s="135">
         <f>SUM(C81:I81)</f>
         <v/>
       </c>
     </row>
-    <row r="95" ht="16.5" customHeight="1" s="78">
-      <c r="A95" s="109" t="inlineStr">
+    <row r="97" ht="16.5" customHeight="1" s="78">
+      <c r="A97" s="109" t="inlineStr">
         <is>
           <t>응급실</t>
         </is>
       </c>
-      <c r="B95" s="63" t="inlineStr">
+      <c r="B97" s="63" t="inlineStr">
         <is>
           <t>응급실(응급)</t>
         </is>
       </c>
-      <c r="C95" s="130" t="n"/>
-      <c r="D95" s="130" t="n"/>
-      <c r="E95" s="130" t="n"/>
-      <c r="F95" s="130" t="n"/>
-      <c r="G95" s="130" t="n"/>
-      <c r="H95" s="130" t="n"/>
-      <c r="I95" s="130" t="n"/>
-      <c r="J95" s="131">
+      <c r="C97" s="130" t="n"/>
+      <c r="D97" s="130" t="n"/>
+      <c r="E97" s="130" t="n"/>
+      <c r="F97" s="130" t="n"/>
+      <c r="G97" s="130" t="n"/>
+      <c r="H97" s="130" t="n"/>
+      <c r="I97" s="130" t="n"/>
+      <c r="J97" s="131">
         <f>SUM(C82:I82)</f>
         <v/>
       </c>
     </row>
-    <row r="96" ht="16.5" customHeight="1" s="78">
-      <c r="A96" s="101" t="inlineStr">
+    <row r="98" ht="16.5" customHeight="1" s="78">
+      <c r="A98" s="101" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="B96" s="34" t="inlineStr">
+      <c r="B98" s="34" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="C96" s="140" t="n"/>
-      <c r="D96" s="140" t="n"/>
-      <c r="E96" s="140" t="n"/>
-      <c r="F96" s="140" t="n"/>
-      <c r="G96" s="140" t="n"/>
-      <c r="H96" s="140" t="n"/>
-      <c r="I96" s="140" t="n"/>
-      <c r="J96" s="141" t="n"/>
-    </row>
-    <row r="97" ht="16.5" customHeight="1" s="78">
-      <c r="A97" s="106" t="inlineStr">
-        <is>
-          <t>화상</t>
-        </is>
-      </c>
-      <c r="B97" s="28" t="inlineStr">
+      <c r="C98" s="140" t="n"/>
+      <c r="D98" s="140" t="n"/>
+      <c r="E98" s="140" t="n"/>
+      <c r="F98" s="140" t="n"/>
+      <c r="G98" s="140" t="n"/>
+      <c r="H98" s="140" t="n"/>
+      <c r="I98" s="140" t="n"/>
+      <c r="J98" s="141" t="n"/>
+    </row>
+    <row r="99" ht="16.5" customHeight="1" s="78">
+      <c r="A99" s="103" t="n"/>
+      <c r="B99" s="28" t="inlineStr">
         <is>
           <t>화상진단비</t>
-        </is>
-      </c>
-      <c r="C97" s="136" t="n"/>
-      <c r="D97" s="136" t="n"/>
-      <c r="E97" s="136" t="n"/>
-      <c r="F97" s="136" t="n"/>
-      <c r="G97" s="136" t="n"/>
-      <c r="H97" s="136" t="n"/>
-      <c r="I97" s="136" t="n"/>
-      <c r="J97" s="137">
-        <f>SUM(C84:I84)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98" ht="16.5" customHeight="1" s="78">
-      <c r="A98" s="108" t="n"/>
-      <c r="B98" s="25" t="inlineStr">
-        <is>
-          <t>중증화상진단비</t>
-        </is>
-      </c>
-      <c r="C98" s="134" t="n"/>
-      <c r="D98" s="134" t="n"/>
-      <c r="E98" s="134" t="n"/>
-      <c r="F98" s="134" t="n"/>
-      <c r="G98" s="134" t="n"/>
-      <c r="H98" s="134" t="n"/>
-      <c r="I98" s="134" t="n"/>
-      <c r="J98" s="135">
-        <f>SUM(C85:I85)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="16.5" customHeight="1" s="78">
-      <c r="A99" s="106" t="inlineStr">
-        <is>
-          <t>깁스</t>
-        </is>
-      </c>
-      <c r="B99" s="104" t="inlineStr">
-        <is>
-          <t>반깁스</t>
         </is>
       </c>
       <c r="C99" s="136" t="n"/>
@@ -3434,15 +3408,15 @@
       <c r="H99" s="136" t="n"/>
       <c r="I99" s="136" t="n"/>
       <c r="J99" s="137">
-        <f>SUM(C86:I86)</f>
+        <f>SUM(C84:I84)</f>
         <v/>
       </c>
     </row>
     <row r="100" ht="16.5" customHeight="1" s="78">
       <c r="A100" s="108" t="n"/>
-      <c r="B100" s="56" t="inlineStr">
-        <is>
-          <t>깁스진단비</t>
+      <c r="B100" s="25" t="inlineStr">
+        <is>
+          <t>중증화상진단비</t>
         </is>
       </c>
       <c r="C100" s="134" t="n"/>
@@ -3453,68 +3427,64 @@
       <c r="H100" s="134" t="n"/>
       <c r="I100" s="134" t="n"/>
       <c r="J100" s="135">
+        <f>SUM(C85:I85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="16.5" customHeight="1" s="78">
+      <c r="A101" s="108" t="n"/>
+      <c r="B101" s="104" t="inlineStr">
+        <is>
+          <t>반깁스</t>
+        </is>
+      </c>
+      <c r="C101" s="136" t="n"/>
+      <c r="D101" s="136" t="n"/>
+      <c r="E101" s="136" t="n"/>
+      <c r="F101" s="136" t="n"/>
+      <c r="G101" s="136" t="n"/>
+      <c r="H101" s="136" t="n"/>
+      <c r="I101" s="136" t="n"/>
+      <c r="J101" s="137">
+        <f>SUM(C86:I86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" ht="16.5" customHeight="1" s="78">
+      <c r="A102" s="108" t="n"/>
+      <c r="B102" s="56" t="inlineStr">
+        <is>
+          <t>깁스진단비</t>
+        </is>
+      </c>
+      <c r="C102" s="134" t="n"/>
+      <c r="D102" s="134" t="n"/>
+      <c r="E102" s="134" t="n"/>
+      <c r="F102" s="134" t="n"/>
+      <c r="G102" s="134" t="n"/>
+      <c r="H102" s="134" t="n"/>
+      <c r="I102" s="134" t="n"/>
+      <c r="J102" s="135">
         <f>SUM(C87:I87)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" ht="16.5" customHeight="1" s="78">
-      <c r="A101" s="106" t="inlineStr">
-        <is>
-          <t>실손</t>
-        </is>
-      </c>
-      <c r="B101" s="104" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="C101" s="169" t="n"/>
-      <c r="D101" s="169" t="n"/>
-      <c r="E101" s="169" t="n"/>
-      <c r="F101" s="169" t="n"/>
-      <c r="G101" s="169" t="n"/>
-      <c r="H101" s="169" t="n"/>
-      <c r="I101" s="169" t="n"/>
-      <c r="J101" s="137">
-        <f>SUM(C88:I88)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" ht="16.5" customHeight="1" s="78">
-      <c r="A102" s="107" t="n"/>
-      <c r="B102" s="59" t="inlineStr">
-        <is>
-          <t>통원</t>
-        </is>
-      </c>
-      <c r="C102" s="170" t="n"/>
-      <c r="D102" s="170" t="n"/>
-      <c r="E102" s="170" t="n"/>
-      <c r="F102" s="170" t="n"/>
-      <c r="G102" s="170" t="n"/>
-      <c r="H102" s="170" t="n"/>
-      <c r="I102" s="170" t="n"/>
-      <c r="J102" s="139">
-        <f>SUM(C89:I89)</f>
         <v/>
       </c>
     </row>
     <row r="103" ht="16.5" customHeight="1" s="78">
       <c r="A103" s="107" t="n"/>
-      <c r="B103" s="59" t="inlineStr">
-        <is>
-          <t>약값</t>
-        </is>
-      </c>
-      <c r="C103" s="138" t="n"/>
-      <c r="D103" s="138" t="n"/>
-      <c r="E103" s="138" t="n"/>
-      <c r="F103" s="138" t="n"/>
-      <c r="G103" s="138" t="n"/>
-      <c r="H103" s="138" t="n"/>
-      <c r="I103" s="170" t="n"/>
-      <c r="J103" s="139">
-        <f>SUM(C90:I90)</f>
+      <c r="B103" s="104" t="inlineStr">
+        <is>
+          <t>입원</t>
+        </is>
+      </c>
+      <c r="C103" s="169" t="n"/>
+      <c r="D103" s="169" t="n"/>
+      <c r="E103" s="169" t="n"/>
+      <c r="F103" s="169" t="n"/>
+      <c r="G103" s="169" t="n"/>
+      <c r="H103" s="169" t="n"/>
+      <c r="I103" s="169" t="n"/>
+      <c r="J103" s="137">
+        <f>SUM(C88:I88)</f>
         <v/>
       </c>
     </row>
@@ -3522,53 +3492,91 @@
       <c r="A104" s="107" t="n"/>
       <c r="B104" s="59" t="inlineStr">
         <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="C104" s="170" t="n"/>
+      <c r="D104" s="170" t="n"/>
+      <c r="E104" s="170" t="n"/>
+      <c r="F104" s="170" t="n"/>
+      <c r="G104" s="170" t="n"/>
+      <c r="H104" s="170" t="n"/>
+      <c r="I104" s="170" t="n"/>
+      <c r="J104" s="139">
+        <f>SUM(C89:I89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" ht="16.5" customHeight="1" s="78">
+      <c r="A105" s="107" t="n"/>
+      <c r="B105" s="59" t="inlineStr">
+        <is>
+          <t>약값</t>
+        </is>
+      </c>
+      <c r="C105" s="138" t="n"/>
+      <c r="D105" s="138" t="n"/>
+      <c r="E105" s="138" t="n"/>
+      <c r="F105" s="138" t="n"/>
+      <c r="G105" s="138" t="n"/>
+      <c r="H105" s="138" t="n"/>
+      <c r="I105" s="170" t="n"/>
+      <c r="J105" s="139">
+        <f>SUM(C90:I90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="16.5" customHeight="1" s="78">
+      <c r="A106" s="108" t="n"/>
+      <c r="B106" s="59" t="inlineStr">
+        <is>
           <t>MRI/도수치료/비급여주사</t>
         </is>
       </c>
-      <c r="C104" s="138" t="n"/>
-      <c r="D104" s="138" t="n"/>
-      <c r="E104" s="138" t="n"/>
-      <c r="F104" s="138" t="n"/>
-      <c r="G104" s="138" t="n"/>
-      <c r="H104" s="138" t="n"/>
-      <c r="I104" s="170" t="n"/>
-      <c r="J104" s="133" t="n"/>
-    </row>
-    <row r="105" ht="16.5" customHeight="1" s="78">
-      <c r="A105" s="108" t="n"/>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="C106" s="138" t="n"/>
+      <c r="D106" s="138" t="n"/>
+      <c r="E106" s="138" t="n"/>
+      <c r="F106" s="138" t="n"/>
+      <c r="G106" s="138" t="n"/>
+      <c r="H106" s="138" t="n"/>
+      <c r="I106" s="170" t="n"/>
+      <c r="J106" s="133" t="n"/>
+    </row>
+    <row r="107" ht="16.5" customHeight="1" s="78">
+      <c r="A107" s="108" t="n"/>
+      <c r="B107" s="22" t="inlineStr">
         <is>
           <t>상해의료비</t>
         </is>
       </c>
-      <c r="C105" s="132" t="n"/>
-      <c r="D105" s="132" t="n"/>
-      <c r="E105" s="132" t="n"/>
-      <c r="F105" s="132" t="n"/>
-      <c r="G105" s="132" t="n"/>
-      <c r="H105" s="132" t="n"/>
-      <c r="I105" s="171" t="n"/>
-      <c r="J105" s="139" t="n"/>
-    </row>
-    <row r="106" ht="16.5" customHeight="1" s="78">
-      <c r="A106" s="101" t="inlineStr">
+      <c r="C107" s="132" t="n"/>
+      <c r="D107" s="132" t="n"/>
+      <c r="E107" s="132" t="n"/>
+      <c r="F107" s="132" t="n"/>
+      <c r="G107" s="132" t="n"/>
+      <c r="H107" s="132" t="n"/>
+      <c r="I107" s="171" t="n"/>
+      <c r="J107" s="139" t="n"/>
+    </row>
+    <row r="108" ht="16.5" customHeight="1" s="78">
+      <c r="A108" s="101" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B106" s="75" t="inlineStr">
+      <c r="B108" s="75" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C106" s="172" t="n"/>
-      <c r="D106" s="172" t="n"/>
-      <c r="E106" s="172" t="n"/>
-      <c r="F106" s="172" t="n"/>
-      <c r="G106" s="172" t="n"/>
-      <c r="H106" s="172" t="n"/>
-      <c r="I106" s="172" t="n"/>
-      <c r="J106" s="173">
+      <c r="C108" s="172" t="n"/>
+      <c r="D108" s="172" t="n"/>
+      <c r="E108" s="172" t="n"/>
+      <c r="F108" s="172" t="n"/>
+      <c r="G108" s="172" t="n"/>
+      <c r="H108" s="172" t="n"/>
+      <c r="I108" s="172" t="n"/>
+      <c r="J108" s="173">
         <f>SUM(C91:I91)</f>
         <v/>
       </c>

--- a/master.xlsx
+++ b/master.xlsx
@@ -135,7 +135,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -219,11 +219,6 @@
         <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="54">
     <border>
@@ -902,7 +897,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1395,24 +1390,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1538,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="78" min="1" max="1"/>
@@ -2200,38 +2177,38 @@
     </row>
     <row r="35" ht="16.5" customHeight="1" s="78">
       <c r="A35" s="102" t="n"/>
-      <c r="B35" s="174" t="inlineStr">
+      <c r="B35" s="93" t="inlineStr">
         <is>
           <t>뇌출혈진단비</t>
         </is>
       </c>
-      <c r="C35" s="175" t="n"/>
-      <c r="D35" s="175" t="n"/>
-      <c r="E35" s="175" t="n"/>
-      <c r="F35" s="175" t="n"/>
-      <c r="G35" s="175" t="n"/>
-      <c r="H35" s="175" t="n"/>
-      <c r="I35" s="175" t="n"/>
-      <c r="J35" s="176">
+      <c r="C35" s="153" t="n"/>
+      <c r="D35" s="153" t="n"/>
+      <c r="E35" s="153" t="n"/>
+      <c r="F35" s="153" t="n"/>
+      <c r="G35" s="153" t="n"/>
+      <c r="H35" s="153" t="n"/>
+      <c r="I35" s="153" t="n"/>
+      <c r="J35" s="154">
         <f>SUM(C34:I34)</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A36" s="102" t="n"/>
-      <c r="B36" s="177" t="inlineStr">
+      <c r="B36" s="96" t="inlineStr">
         <is>
           <t>중대한 뇌출혈</t>
         </is>
       </c>
-      <c r="C36" s="178" t="n"/>
-      <c r="D36" s="178" t="n"/>
-      <c r="E36" s="178" t="n"/>
-      <c r="F36" s="178" t="n"/>
-      <c r="G36" s="178" t="n"/>
-      <c r="H36" s="178" t="n"/>
-      <c r="I36" s="178" t="n"/>
-      <c r="J36" s="179">
+      <c r="C36" s="155" t="n"/>
+      <c r="D36" s="155" t="n"/>
+      <c r="E36" s="155" t="n"/>
+      <c r="F36" s="155" t="n"/>
+      <c r="G36" s="155" t="n"/>
+      <c r="H36" s="155" t="n"/>
+      <c r="I36" s="155" t="n"/>
+      <c r="J36" s="156">
         <f>SUM(C35:I35)</f>
         <v/>
       </c>
@@ -2689,7 +2666,7 @@
       <c r="A61" s="102" t="n"/>
       <c r="B61" s="31" t="inlineStr">
         <is>
-          <t>간병인질병일당(요양병원)</t>
+          <t>간병인지원일당</t>
         </is>
       </c>
       <c r="C61" s="138" t="n"/>
@@ -2705,7 +2682,7 @@
       <c r="A62" s="102" t="n"/>
       <c r="B62" s="31" t="inlineStr">
         <is>
-          <t>간병인상해일당(요양병원)</t>
+          <t>간호통합병동</t>
         </is>
       </c>
       <c r="C62" s="138" t="n"/>
@@ -2715,13 +2692,16 @@
       <c r="G62" s="138" t="n"/>
       <c r="H62" s="138" t="n"/>
       <c r="I62" s="138" t="n"/>
-      <c r="J62" s="139" t="n"/>
+      <c r="J62" s="139">
+        <f>SUM(C53:I53)</f>
+        <v/>
+      </c>
     </row>
     <row r="63" ht="16.5" customHeight="1" s="78">
       <c r="A63" s="102" t="n"/>
-      <c r="B63" s="31" t="inlineStr">
-        <is>
-          <t>간병인지원일당</t>
+      <c r="B63" s="65" t="inlineStr">
+        <is>
+          <t>1인실 종합병원</t>
         </is>
       </c>
       <c r="C63" s="138" t="n"/>
@@ -2731,13 +2711,16 @@
       <c r="G63" s="138" t="n"/>
       <c r="H63" s="138" t="n"/>
       <c r="I63" s="138" t="n"/>
-      <c r="J63" s="139" t="n"/>
+      <c r="J63" s="139">
+        <f>SUM(C54:I54)</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="17.25" customHeight="1" s="78">
       <c r="A64" s="102" t="n"/>
-      <c r="B64" s="31" t="inlineStr">
-        <is>
-          <t>간호통합병동</t>
+      <c r="B64" s="65" t="inlineStr">
+        <is>
+          <t>1인실 상급병원</t>
         </is>
       </c>
       <c r="C64" s="138" t="n"/>
@@ -2748,15 +2731,15 @@
       <c r="H64" s="138" t="n"/>
       <c r="I64" s="138" t="n"/>
       <c r="J64" s="139">
-        <f>SUM(C53:I53)</f>
+        <f>SUM(C55:I55)</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="17.25" customHeight="1" s="78">
       <c r="A65" s="102" t="n"/>
-      <c r="B65" s="65" t="inlineStr">
-        <is>
-          <t>1인실 종합병원</t>
+      <c r="B65" s="31" t="inlineStr">
+        <is>
+          <t>질병중환자실</t>
         </is>
       </c>
       <c r="C65" s="138" t="n"/>
@@ -2767,110 +2750,112 @@
       <c r="H65" s="138" t="n"/>
       <c r="I65" s="138" t="n"/>
       <c r="J65" s="139">
-        <f>SUM(C54:I54)</f>
+        <f>SUM(C56:I56)</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A66" s="102" t="n"/>
-      <c r="B66" s="65" t="inlineStr">
-        <is>
-          <t>1인실 상급병원</t>
-        </is>
-      </c>
-      <c r="C66" s="138" t="n"/>
-      <c r="D66" s="138" t="n"/>
-      <c r="E66" s="138" t="n"/>
-      <c r="F66" s="138" t="n"/>
-      <c r="G66" s="138" t="n"/>
-      <c r="H66" s="138" t="n"/>
-      <c r="I66" s="138" t="n"/>
-      <c r="J66" s="139">
-        <f>SUM(C55:I55)</f>
+      <c r="A66" s="103" t="n"/>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>상해중환자실</t>
+        </is>
+      </c>
+      <c r="C66" s="134" t="n"/>
+      <c r="D66" s="134" t="n"/>
+      <c r="E66" s="134" t="n"/>
+      <c r="F66" s="134" t="n"/>
+      <c r="G66" s="134" t="n"/>
+      <c r="H66" s="134" t="n"/>
+      <c r="I66" s="134" t="n"/>
+      <c r="J66" s="135">
+        <f>SUM(C57:I57)</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" s="78">
-      <c r="A67" s="103" t="n"/>
-      <c r="B67" s="31" t="inlineStr">
-        <is>
-          <t>질병중환자실</t>
-        </is>
-      </c>
-      <c r="C67" s="138" t="n"/>
-      <c r="D67" s="138" t="n"/>
-      <c r="E67" s="138" t="n"/>
-      <c r="F67" s="138" t="n"/>
-      <c r="G67" s="138" t="n"/>
-      <c r="H67" s="138" t="n"/>
-      <c r="I67" s="138" t="n"/>
-      <c r="J67" s="139">
-        <f>SUM(C56:I56)</f>
+      <c r="A67" s="101" t="inlineStr">
+        <is>
+          <t>수술</t>
+        </is>
+      </c>
+      <c r="B67" s="104" t="inlineStr">
+        <is>
+          <t>상해수술비</t>
+        </is>
+      </c>
+      <c r="C67" s="136" t="n"/>
+      <c r="D67" s="136" t="n"/>
+      <c r="E67" s="136" t="n"/>
+      <c r="F67" s="136" t="n"/>
+      <c r="G67" s="136" t="n"/>
+      <c r="H67" s="136" t="n"/>
+      <c r="I67" s="136" t="n"/>
+      <c r="J67" s="137">
+        <f>SUM(C58:I58)</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="16.5" customHeight="1" s="78">
-      <c r="A68" s="103" t="n"/>
-      <c r="B68" s="25" t="inlineStr">
-        <is>
-          <t>상해중환자실</t>
-        </is>
-      </c>
-      <c r="C68" s="134" t="n"/>
-      <c r="D68" s="134" t="n"/>
-      <c r="E68" s="134" t="n"/>
-      <c r="F68" s="134" t="n"/>
-      <c r="G68" s="134" t="n"/>
-      <c r="H68" s="134" t="n"/>
-      <c r="I68" s="134" t="n"/>
-      <c r="J68" s="135">
-        <f>SUM(C57:I57)</f>
+      <c r="A68" s="102" t="n"/>
+      <c r="B68" s="64" t="inlineStr">
+        <is>
+          <t>중대한상해수술비</t>
+        </is>
+      </c>
+      <c r="C68" s="159" t="n"/>
+      <c r="D68" s="159" t="n"/>
+      <c r="E68" s="159" t="n"/>
+      <c r="F68" s="159" t="n"/>
+      <c r="G68" s="159" t="n"/>
+      <c r="H68" s="159" t="n"/>
+      <c r="I68" s="159" t="n"/>
+      <c r="J68" s="139">
+        <f>SUM(C59:I59)</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="78">
       <c r="A69" s="102" t="n"/>
-      <c r="B69" s="104" t="inlineStr">
-        <is>
-          <t>상해수술비</t>
-        </is>
-      </c>
-      <c r="C69" s="136" t="n"/>
-      <c r="D69" s="136" t="n"/>
-      <c r="E69" s="136" t="n"/>
-      <c r="F69" s="136" t="n"/>
-      <c r="G69" s="136" t="n"/>
-      <c r="H69" s="136" t="n"/>
-      <c r="I69" s="136" t="n"/>
-      <c r="J69" s="137">
-        <f>SUM(C58:I58)</f>
-        <v/>
-      </c>
+      <c r="B69" s="59" t="inlineStr">
+        <is>
+          <t>상해 종수술비(1-3종)</t>
+        </is>
+      </c>
+      <c r="C69" s="159" t="n"/>
+      <c r="D69" s="159" t="n"/>
+      <c r="E69" s="159" t="n"/>
+      <c r="F69" s="160" t="n"/>
+      <c r="G69" s="159" t="n"/>
+      <c r="H69" s="159" t="n"/>
+      <c r="I69" s="159" t="n"/>
+      <c r="J69" s="139" t="n"/>
     </row>
     <row r="70" ht="17.25" customHeight="1" s="78">
       <c r="A70" s="102" t="n"/>
-      <c r="B70" s="64" t="inlineStr">
-        <is>
-          <t>중대한상해수술비</t>
+      <c r="B70" s="59" t="inlineStr">
+        <is>
+          <t>상해 종수술비(1-5종)</t>
         </is>
       </c>
       <c r="C70" s="159" t="n"/>
       <c r="D70" s="159" t="n"/>
       <c r="E70" s="159" t="n"/>
-      <c r="F70" s="159" t="n"/>
+      <c r="F70" s="160" t="n"/>
       <c r="G70" s="159" t="n"/>
       <c r="H70" s="159" t="n"/>
       <c r="I70" s="159" t="n"/>
-      <c r="J70" s="139">
-        <f>SUM(C59:I59)</f>
-        <v/>
+      <c r="J70" s="139" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="78">
       <c r="A71" s="102" t="n"/>
       <c r="B71" s="59" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-3종)</t>
+          <t>상해 종수술비(1-8종)</t>
         </is>
       </c>
       <c r="C71" s="159" t="n"/>
@@ -2886,43 +2871,45 @@
       <c r="A72" s="102" t="n"/>
       <c r="B72" s="59" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-5종)</t>
-        </is>
-      </c>
-      <c r="C72" s="159" t="n"/>
-      <c r="D72" s="159" t="n"/>
-      <c r="E72" s="159" t="n"/>
-      <c r="F72" s="160" t="n"/>
-      <c r="G72" s="159" t="n"/>
-      <c r="H72" s="159" t="n"/>
-      <c r="I72" s="159" t="n"/>
-      <c r="J72" s="139" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+          <t>창상봉합술</t>
+        </is>
+      </c>
+      <c r="C72" s="138" t="n"/>
+      <c r="D72" s="138" t="n"/>
+      <c r="E72" s="138" t="n"/>
+      <c r="F72" s="161" t="n"/>
+      <c r="G72" s="138" t="n"/>
+      <c r="H72" s="138" t="n"/>
+      <c r="I72" s="138" t="n"/>
+      <c r="J72" s="139">
+        <f>SUM(C61:I61)</f>
+        <v/>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="78">
       <c r="A73" s="102" t="n"/>
       <c r="B73" s="59" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-8종)</t>
-        </is>
-      </c>
-      <c r="C73" s="159" t="n"/>
-      <c r="D73" s="159" t="n"/>
-      <c r="E73" s="159" t="n"/>
-      <c r="F73" s="160" t="n"/>
-      <c r="G73" s="159" t="n"/>
-      <c r="H73" s="159" t="n"/>
-      <c r="I73" s="159" t="n"/>
-      <c r="J73" s="139" t="n"/>
+          <t>골절수술비</t>
+        </is>
+      </c>
+      <c r="C73" s="138" t="n"/>
+      <c r="D73" s="138" t="n"/>
+      <c r="E73" s="138" t="n"/>
+      <c r="F73" s="161" t="n"/>
+      <c r="G73" s="138" t="n"/>
+      <c r="H73" s="138" t="n"/>
+      <c r="I73" s="138" t="n"/>
+      <c r="J73" s="139">
+        <f>SUM(C62:I62)</f>
+        <v/>
+      </c>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="78">
       <c r="A74" s="102" t="n"/>
-      <c r="B74" s="59" t="inlineStr">
-        <is>
-          <t>창상봉합술</t>
+      <c r="B74" s="66" t="inlineStr">
+        <is>
+          <t>5대골절수술비</t>
         </is>
       </c>
       <c r="C74" s="138" t="n"/>
@@ -2933,91 +2920,89 @@
       <c r="H74" s="138" t="n"/>
       <c r="I74" s="138" t="n"/>
       <c r="J74" s="139">
-        <f>SUM(C61:I61)</f>
+        <f>SUM(C63:I63)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A75" s="102" t="n"/>
-      <c r="B75" s="59" t="inlineStr">
-        <is>
-          <t>골절수술비</t>
-        </is>
-      </c>
-      <c r="C75" s="138" t="n"/>
-      <c r="D75" s="138" t="n"/>
-      <c r="E75" s="138" t="n"/>
-      <c r="F75" s="161" t="n"/>
-      <c r="G75" s="138" t="n"/>
-      <c r="H75" s="138" t="n"/>
-      <c r="I75" s="138" t="n"/>
-      <c r="J75" s="139">
-        <f>SUM(C62:I62)</f>
+      <c r="B75" s="56" t="inlineStr">
+        <is>
+          <t>화상수술비</t>
+        </is>
+      </c>
+      <c r="C75" s="134" t="n"/>
+      <c r="D75" s="134" t="n"/>
+      <c r="E75" s="134" t="n"/>
+      <c r="F75" s="162" t="n"/>
+      <c r="G75" s="134" t="n"/>
+      <c r="H75" s="134" t="n"/>
+      <c r="I75" s="134" t="n"/>
+      <c r="J75" s="135">
+        <f>SUM(C64:I64)</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16.5" customHeight="1" s="78">
       <c r="A76" s="102" t="n"/>
-      <c r="B76" s="66" t="inlineStr">
-        <is>
-          <t>5대골절수술비</t>
-        </is>
-      </c>
-      <c r="C76" s="138" t="n"/>
-      <c r="D76" s="138" t="n"/>
-      <c r="E76" s="138" t="n"/>
-      <c r="F76" s="161" t="n"/>
-      <c r="G76" s="138" t="n"/>
-      <c r="H76" s="138" t="n"/>
-      <c r="I76" s="138" t="n"/>
-      <c r="J76" s="139">
-        <f>SUM(C63:I63)</f>
+      <c r="B76" s="64" t="inlineStr">
+        <is>
+          <t>질병수술비</t>
+        </is>
+      </c>
+      <c r="C76" s="159" t="n"/>
+      <c r="D76" s="159" t="n"/>
+      <c r="E76" s="159" t="n"/>
+      <c r="F76" s="163" t="n"/>
+      <c r="G76" s="159" t="n"/>
+      <c r="H76" s="159" t="n"/>
+      <c r="I76" s="164" t="n"/>
+      <c r="J76" s="133">
+        <f>SUM(C65:I65)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="78">
       <c r="A77" s="102" t="n"/>
-      <c r="B77" s="56" t="inlineStr">
-        <is>
-          <t>화상수술비</t>
-        </is>
-      </c>
-      <c r="C77" s="134" t="n"/>
-      <c r="D77" s="134" t="n"/>
-      <c r="E77" s="134" t="n"/>
-      <c r="F77" s="162" t="n"/>
-      <c r="G77" s="134" t="n"/>
-      <c r="H77" s="134" t="n"/>
-      <c r="I77" s="134" t="n"/>
-      <c r="J77" s="135">
-        <f>SUM(C64:I64)</f>
-        <v/>
-      </c>
+      <c r="B77" s="59" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-3종)</t>
+        </is>
+      </c>
+      <c r="C77" s="138" t="n"/>
+      <c r="D77" s="138" t="n"/>
+      <c r="E77" s="138" t="n"/>
+      <c r="F77" s="165" t="n"/>
+      <c r="G77" s="138" t="n"/>
+      <c r="H77" s="138" t="n"/>
+      <c r="I77" s="138" t="n"/>
+      <c r="J77" s="139" t="n"/>
     </row>
     <row r="78" ht="17.25" customHeight="1" s="78">
       <c r="A78" s="102" t="n"/>
-      <c r="B78" s="64" t="inlineStr">
-        <is>
-          <t>질병수술비</t>
-        </is>
-      </c>
-      <c r="C78" s="159" t="n"/>
-      <c r="D78" s="159" t="n"/>
-      <c r="E78" s="159" t="n"/>
-      <c r="F78" s="163" t="n"/>
-      <c r="G78" s="159" t="n"/>
-      <c r="H78" s="159" t="n"/>
-      <c r="I78" s="164" t="n"/>
-      <c r="J78" s="133">
-        <f>SUM(C65:I65)</f>
-        <v/>
+      <c r="B78" s="59" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="C78" s="138" t="n"/>
+      <c r="D78" s="138" t="n"/>
+      <c r="E78" s="138" t="n"/>
+      <c r="F78" s="165" t="n"/>
+      <c r="G78" s="138" t="n"/>
+      <c r="H78" s="138" t="n"/>
+      <c r="I78" s="138" t="n"/>
+      <c r="J78" s="139" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1" s="78">
       <c r="A79" s="102" t="n"/>
       <c r="B79" s="59" t="inlineStr">
         <is>
-          <t>질병 종수술비(1-3종)</t>
+          <t>질병 종수술비(1-8종)</t>
         </is>
       </c>
       <c r="C79" s="138" t="n"/>
@@ -3031,45 +3016,47 @@
     </row>
     <row r="80" ht="16.5" customHeight="1" s="78">
       <c r="A80" s="102" t="n"/>
-      <c r="B80" s="59" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-5종)</t>
-        </is>
-      </c>
-      <c r="C80" s="138" t="n"/>
-      <c r="D80" s="138" t="n"/>
-      <c r="E80" s="138" t="n"/>
-      <c r="F80" s="165" t="n"/>
-      <c r="G80" s="138" t="n"/>
-      <c r="H80" s="138" t="n"/>
-      <c r="I80" s="138" t="n"/>
-      <c r="J80" s="139" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="B80" s="68" t="inlineStr">
+        <is>
+          <t>뇌혈관수술비</t>
+        </is>
+      </c>
+      <c r="C80" s="166" t="n"/>
+      <c r="D80" s="166" t="n"/>
+      <c r="E80" s="166" t="n"/>
+      <c r="F80" s="166" t="n"/>
+      <c r="G80" s="166" t="n"/>
+      <c r="H80" s="166" t="n"/>
+      <c r="I80" s="166" t="n"/>
+      <c r="J80" s="139">
+        <f>SUM(C67:I67)</f>
+        <v/>
       </c>
     </row>
     <row r="81" ht="17.25" customHeight="1" s="78">
       <c r="A81" s="102" t="n"/>
-      <c r="B81" s="59" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-8종)</t>
-        </is>
-      </c>
-      <c r="C81" s="138" t="n"/>
-      <c r="D81" s="138" t="n"/>
-      <c r="E81" s="138" t="n"/>
-      <c r="F81" s="165" t="n"/>
-      <c r="G81" s="138" t="n"/>
-      <c r="H81" s="138" t="n"/>
-      <c r="I81" s="138" t="n"/>
-      <c r="J81" s="139" t="n"/>
+      <c r="B81" s="68" t="inlineStr">
+        <is>
+          <t>허혈성수술비</t>
+        </is>
+      </c>
+      <c r="C81" s="166" t="n"/>
+      <c r="D81" s="166" t="n"/>
+      <c r="E81" s="166" t="n"/>
+      <c r="F81" s="166" t="n"/>
+      <c r="G81" s="166" t="n"/>
+      <c r="H81" s="166" t="n"/>
+      <c r="I81" s="166" t="n"/>
+      <c r="J81" s="139">
+        <f>SUM(C68:I68)</f>
+        <v/>
+      </c>
     </row>
     <row r="82" ht="17.25" customHeight="1" s="78">
       <c r="A82" s="102" t="n"/>
       <c r="B82" s="68" t="inlineStr">
         <is>
-          <t>뇌혈관수술비</t>
+          <t>심장수술비</t>
         </is>
       </c>
       <c r="C82" s="166" t="n"/>
@@ -3080,15 +3067,15 @@
       <c r="H82" s="166" t="n"/>
       <c r="I82" s="166" t="n"/>
       <c r="J82" s="139">
-        <f>SUM(C67:I67)</f>
+        <f>SUM(C69:I69)</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="17.25" customHeight="1" s="78" thickBot="1">
       <c r="A83" s="102" t="n"/>
-      <c r="B83" s="68" t="inlineStr">
-        <is>
-          <t>허혈성수술비</t>
+      <c r="B83" s="60" t="inlineStr">
+        <is>
+          <t>120대수술비</t>
         </is>
       </c>
       <c r="C83" s="166" t="n"/>
@@ -3098,111 +3085,115 @@
       <c r="G83" s="166" t="n"/>
       <c r="H83" s="166" t="n"/>
       <c r="I83" s="166" t="n"/>
-      <c r="J83" s="139">
-        <f>SUM(C68:I68)</f>
+      <c r="J83" s="167">
+        <f>SUM(C70:I70)</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="78">
       <c r="A84" s="102" t="n"/>
-      <c r="B84" s="68" t="inlineStr">
-        <is>
-          <t>심장수술비</t>
-        </is>
-      </c>
-      <c r="C84" s="166" t="n"/>
-      <c r="D84" s="166" t="n"/>
-      <c r="E84" s="166" t="n"/>
-      <c r="F84" s="166" t="n"/>
-      <c r="G84" s="166" t="n"/>
-      <c r="H84" s="166" t="n"/>
-      <c r="I84" s="166" t="n"/>
-      <c r="J84" s="139">
-        <f>SUM(C69:I69)</f>
+      <c r="B84" s="69" t="inlineStr">
+        <is>
+          <t>5대기관 수술비 관혈</t>
+        </is>
+      </c>
+      <c r="C84" s="140" t="n"/>
+      <c r="D84" s="140" t="n"/>
+      <c r="E84" s="140" t="n"/>
+      <c r="F84" s="140" t="n"/>
+      <c r="G84" s="140" t="n"/>
+      <c r="H84" s="140" t="n"/>
+      <c r="I84" s="140" t="n"/>
+      <c r="J84" s="137">
+        <f>SUM(C71:I71)</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="17.25" customHeight="1" s="78" thickBot="1">
-      <c r="A85" s="102" t="n"/>
-      <c r="B85" s="60" t="inlineStr">
-        <is>
-          <t>n대수술비</t>
-        </is>
-      </c>
-      <c r="C85" s="166" t="n"/>
-      <c r="D85" s="166" t="n"/>
-      <c r="E85" s="166" t="n"/>
-      <c r="F85" s="166" t="n"/>
-      <c r="G85" s="166" t="n"/>
-      <c r="H85" s="166" t="n"/>
-      <c r="I85" s="166" t="n"/>
-      <c r="J85" s="167">
-        <f>SUM(C70:I70)</f>
+      <c r="A85" s="103" t="n"/>
+      <c r="B85" s="70" t="inlineStr">
+        <is>
+          <t>5대기관 수술비 비관혈</t>
+        </is>
+      </c>
+      <c r="C85" s="134" t="n"/>
+      <c r="D85" s="134" t="n"/>
+      <c r="E85" s="134" t="n"/>
+      <c r="F85" s="134" t="n"/>
+      <c r="G85" s="134" t="n"/>
+      <c r="H85" s="134" t="n"/>
+      <c r="I85" s="134" t="n"/>
+      <c r="J85" s="135">
+        <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A86" s="103" t="n"/>
-      <c r="B86" s="69" t="inlineStr">
-        <is>
-          <t>5대기관 수술비 관혈</t>
-        </is>
-      </c>
-      <c r="C86" s="140" t="n"/>
-      <c r="D86" s="140" t="n"/>
-      <c r="E86" s="140" t="n"/>
-      <c r="F86" s="140" t="n"/>
-      <c r="G86" s="140" t="n"/>
-      <c r="H86" s="140" t="n"/>
-      <c r="I86" s="140" t="n"/>
+      <c r="A86" s="106" t="inlineStr">
+        <is>
+          <t>운전</t>
+        </is>
+      </c>
+      <c r="B86" s="28" t="inlineStr">
+        <is>
+          <t>대인</t>
+        </is>
+      </c>
+      <c r="C86" s="119" t="n"/>
+      <c r="D86" s="119" t="n"/>
+      <c r="E86" s="119" t="n"/>
+      <c r="F86" s="119" t="n"/>
+      <c r="G86" s="119" t="n"/>
+      <c r="H86" s="119" t="n"/>
+      <c r="I86" s="119" t="n"/>
       <c r="J86" s="137">
-        <f>SUM(C71:I71)</f>
+        <f>SUM(C73:I73)</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="17.25" customHeight="1" s="78">
-      <c r="A87" s="103" t="n"/>
-      <c r="B87" s="70" t="inlineStr">
-        <is>
-          <t>5대기관 수술비 비관혈</t>
-        </is>
-      </c>
-      <c r="C87" s="134" t="n"/>
-      <c r="D87" s="134" t="n"/>
-      <c r="E87" s="134" t="n"/>
-      <c r="F87" s="134" t="n"/>
-      <c r="G87" s="134" t="n"/>
-      <c r="H87" s="134" t="n"/>
-      <c r="I87" s="134" t="n"/>
-      <c r="J87" s="135">
-        <f>SUM(C72:I72)</f>
+      <c r="A87" s="107" t="n"/>
+      <c r="B87" s="31" t="inlineStr">
+        <is>
+          <t>대물</t>
+        </is>
+      </c>
+      <c r="C87" s="149" t="n"/>
+      <c r="D87" s="149" t="n"/>
+      <c r="E87" s="149" t="n"/>
+      <c r="F87" s="149" t="n"/>
+      <c r="G87" s="149" t="n"/>
+      <c r="H87" s="149" t="n"/>
+      <c r="I87" s="149" t="n"/>
+      <c r="J87" s="139">
+        <f>SUM(C74:I74)</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16.5" customHeight="1" s="78">
-      <c r="A88" s="102" t="n"/>
-      <c r="B88" s="28" t="inlineStr">
-        <is>
-          <t>대인</t>
-        </is>
-      </c>
-      <c r="C88" s="119" t="n"/>
-      <c r="D88" s="119" t="n"/>
-      <c r="E88" s="119" t="n"/>
-      <c r="F88" s="119" t="n"/>
-      <c r="G88" s="119" t="n"/>
-      <c r="H88" s="119" t="n"/>
-      <c r="I88" s="119" t="n"/>
-      <c r="J88" s="137">
-        <f>SUM(C73:I73)</f>
+      <c r="A88" s="107" t="n"/>
+      <c r="B88" s="31" t="inlineStr">
+        <is>
+          <t>합의금</t>
+        </is>
+      </c>
+      <c r="C88" s="149" t="n"/>
+      <c r="D88" s="149" t="n"/>
+      <c r="E88" s="149" t="n"/>
+      <c r="F88" s="149" t="n"/>
+      <c r="G88" s="149" t="n"/>
+      <c r="H88" s="149" t="n"/>
+      <c r="I88" s="149" t="n"/>
+      <c r="J88" s="139">
+        <f>SUM(C75:I75)</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16.5" customHeight="1" s="78">
-      <c r="A89" s="102" t="n"/>
-      <c r="B89" s="31" t="inlineStr">
-        <is>
-          <t>대물</t>
+      <c r="A89" s="107" t="n"/>
+      <c r="B89" s="65" t="inlineStr">
+        <is>
+          <t>6주미만</t>
         </is>
       </c>
       <c r="C89" s="149" t="n"/>
@@ -3213,15 +3204,15 @@
       <c r="H89" s="149" t="n"/>
       <c r="I89" s="149" t="n"/>
       <c r="J89" s="139">
-        <f>SUM(C74:I74)</f>
+        <f>SUM(C76:I76)</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="17.25" customHeight="1" s="78">
-      <c r="A90" s="102" t="n"/>
+      <c r="A90" s="107" t="n"/>
       <c r="B90" s="31" t="inlineStr">
         <is>
-          <t>합의금</t>
+          <t>변호사</t>
         </is>
       </c>
       <c r="C90" s="149" t="n"/>
@@ -3232,172 +3223,184 @@
       <c r="H90" s="149" t="n"/>
       <c r="I90" s="149" t="n"/>
       <c r="J90" s="139">
-        <f>SUM(C75:I75)</f>
+        <f>SUM(C77:I77)</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="17.25" customHeight="1" s="78">
-      <c r="A91" s="102" t="n"/>
-      <c r="B91" s="65" t="inlineStr">
-        <is>
-          <t>6주미만</t>
-        </is>
-      </c>
-      <c r="C91" s="149" t="n"/>
-      <c r="D91" s="149" t="n"/>
-      <c r="E91" s="149" t="n"/>
-      <c r="F91" s="149" t="n"/>
-      <c r="G91" s="149" t="n"/>
-      <c r="H91" s="149" t="n"/>
-      <c r="I91" s="149" t="n"/>
-      <c r="J91" s="139">
-        <f>SUM(C76:I76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="16.5" customHeight="1" s="78">
-      <c r="A92" s="103" t="n"/>
-      <c r="B92" s="31" t="inlineStr">
-        <is>
-          <t>변호사</t>
-        </is>
-      </c>
-      <c r="C92" s="149" t="n"/>
-      <c r="D92" s="149" t="n"/>
-      <c r="E92" s="149" t="n"/>
-      <c r="F92" s="149" t="n"/>
-      <c r="G92" s="149" t="n"/>
-      <c r="H92" s="149" t="n"/>
-      <c r="I92" s="149" t="n"/>
-      <c r="J92" s="139">
-        <f>SUM(C77:I77)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="16.5" customHeight="1" s="78">
-      <c r="A93" s="108" t="n"/>
-      <c r="B93" s="25" t="inlineStr">
+      <c r="A91" s="108" t="n"/>
+      <c r="B91" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C93" s="168" t="n"/>
-      <c r="D93" s="168" t="n"/>
-      <c r="E93" s="168" t="n"/>
-      <c r="F93" s="168" t="n"/>
-      <c r="G93" s="168" t="n"/>
-      <c r="H93" s="168" t="n"/>
-      <c r="I93" s="168" t="n"/>
-      <c r="J93" s="135">
+      <c r="C91" s="168" t="n"/>
+      <c r="D91" s="168" t="n"/>
+      <c r="E91" s="168" t="n"/>
+      <c r="F91" s="168" t="n"/>
+      <c r="G91" s="168" t="n"/>
+      <c r="H91" s="168" t="n"/>
+      <c r="I91" s="168" t="n"/>
+      <c r="J91" s="135">
         <f>SUM(C78:I78)</f>
         <v/>
       </c>
     </row>
-    <row r="94" ht="16.5" customHeight="1" s="78">
-      <c r="A94" s="107" t="n"/>
-      <c r="B94" s="64" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="106" t="inlineStr">
+        <is>
+          <t>골절</t>
+        </is>
+      </c>
+      <c r="B92" s="64" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C94" s="159" t="n"/>
-      <c r="D94" s="159" t="n"/>
-      <c r="E94" s="159" t="n"/>
-      <c r="F94" s="159" t="n"/>
-      <c r="G94" s="159" t="n"/>
-      <c r="H94" s="159" t="n"/>
-      <c r="I94" s="159" t="n"/>
-      <c r="J94" s="133">
+      <c r="C92" s="159" t="n"/>
+      <c r="D92" s="159" t="n"/>
+      <c r="E92" s="159" t="n"/>
+      <c r="F92" s="159" t="n"/>
+      <c r="G92" s="159" t="n"/>
+      <c r="H92" s="159" t="n"/>
+      <c r="I92" s="159" t="n"/>
+      <c r="J92" s="133">
         <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
-    <row r="95" ht="16.5" customHeight="1" s="78">
-      <c r="A95" s="108" t="n"/>
-      <c r="B95" s="59" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="107" t="n"/>
+      <c r="B93" s="59" t="inlineStr">
         <is>
           <t>골절(치아파절제외)</t>
         </is>
       </c>
-      <c r="C95" s="138" t="n"/>
-      <c r="D95" s="138" t="n"/>
-      <c r="E95" s="138" t="n"/>
-      <c r="F95" s="138" t="n"/>
-      <c r="G95" s="138" t="n"/>
-      <c r="H95" s="138" t="n"/>
-      <c r="I95" s="138" t="n"/>
-      <c r="J95" s="139">
+      <c r="C93" s="138" t="n"/>
+      <c r="D93" s="138" t="n"/>
+      <c r="E93" s="138" t="n"/>
+      <c r="F93" s="138" t="n"/>
+      <c r="G93" s="138" t="n"/>
+      <c r="H93" s="138" t="n"/>
+      <c r="I93" s="138" t="n"/>
+      <c r="J93" s="139">
         <f>SUM(C80:I80)</f>
         <v/>
       </c>
     </row>
-    <row r="96" ht="16.5" customHeight="1" s="78">
-      <c r="A96" s="108" t="n"/>
-      <c r="B96" s="70" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="108" t="n"/>
+      <c r="B94" s="70" t="inlineStr">
         <is>
           <t>5대골절진단비</t>
         </is>
       </c>
-      <c r="C96" s="134" t="n"/>
-      <c r="D96" s="134" t="n"/>
-      <c r="E96" s="134" t="n"/>
-      <c r="F96" s="134" t="n"/>
-      <c r="G96" s="134" t="n"/>
-      <c r="H96" s="134" t="n"/>
-      <c r="I96" s="134" t="n"/>
-      <c r="J96" s="135">
+      <c r="C94" s="134" t="n"/>
+      <c r="D94" s="134" t="n"/>
+      <c r="E94" s="134" t="n"/>
+      <c r="F94" s="134" t="n"/>
+      <c r="G94" s="134" t="n"/>
+      <c r="H94" s="134" t="n"/>
+      <c r="I94" s="134" t="n"/>
+      <c r="J94" s="135">
         <f>SUM(C81:I81)</f>
         <v/>
       </c>
     </row>
-    <row r="97" ht="16.5" customHeight="1" s="78">
-      <c r="A97" s="109" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="109" t="inlineStr">
         <is>
           <t>응급실</t>
         </is>
       </c>
-      <c r="B97" s="63" t="inlineStr">
+      <c r="B95" s="63" t="inlineStr">
         <is>
           <t>응급실(응급)</t>
         </is>
       </c>
-      <c r="C97" s="130" t="n"/>
-      <c r="D97" s="130" t="n"/>
-      <c r="E97" s="130" t="n"/>
-      <c r="F97" s="130" t="n"/>
-      <c r="G97" s="130" t="n"/>
-      <c r="H97" s="130" t="n"/>
-      <c r="I97" s="130" t="n"/>
-      <c r="J97" s="131">
+      <c r="C95" s="130" t="n"/>
+      <c r="D95" s="130" t="n"/>
+      <c r="E95" s="130" t="n"/>
+      <c r="F95" s="130" t="n"/>
+      <c r="G95" s="130" t="n"/>
+      <c r="H95" s="130" t="n"/>
+      <c r="I95" s="130" t="n"/>
+      <c r="J95" s="131">
         <f>SUM(C82:I82)</f>
         <v/>
       </c>
     </row>
-    <row r="98" ht="16.5" customHeight="1" s="78">
-      <c r="A98" s="101" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="101" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="B98" s="34" t="inlineStr">
+      <c r="B96" s="34" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="C98" s="140" t="n"/>
-      <c r="D98" s="140" t="n"/>
-      <c r="E98" s="140" t="n"/>
-      <c r="F98" s="140" t="n"/>
-      <c r="G98" s="140" t="n"/>
-      <c r="H98" s="140" t="n"/>
-      <c r="I98" s="140" t="n"/>
-      <c r="J98" s="141" t="n"/>
-    </row>
-    <row r="99" ht="16.5" customHeight="1" s="78">
-      <c r="A99" s="103" t="n"/>
-      <c r="B99" s="28" t="inlineStr">
+      <c r="C96" s="140" t="n"/>
+      <c r="D96" s="140" t="n"/>
+      <c r="E96" s="140" t="n"/>
+      <c r="F96" s="140" t="n"/>
+      <c r="G96" s="140" t="n"/>
+      <c r="H96" s="140" t="n"/>
+      <c r="I96" s="140" t="n"/>
+      <c r="J96" s="141" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="106" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B97" s="28" t="inlineStr">
         <is>
           <t>화상진단비</t>
+        </is>
+      </c>
+      <c r="C97" s="136" t="n"/>
+      <c r="D97" s="136" t="n"/>
+      <c r="E97" s="136" t="n"/>
+      <c r="F97" s="136" t="n"/>
+      <c r="G97" s="136" t="n"/>
+      <c r="H97" s="136" t="n"/>
+      <c r="I97" s="136" t="n"/>
+      <c r="J97" s="137">
+        <f>SUM(C84:I84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="108" t="n"/>
+      <c r="B98" s="25" t="inlineStr">
+        <is>
+          <t>중증화상진단비</t>
+        </is>
+      </c>
+      <c r="C98" s="134" t="n"/>
+      <c r="D98" s="134" t="n"/>
+      <c r="E98" s="134" t="n"/>
+      <c r="F98" s="134" t="n"/>
+      <c r="G98" s="134" t="n"/>
+      <c r="H98" s="134" t="n"/>
+      <c r="I98" s="134" t="n"/>
+      <c r="J98" s="135">
+        <f>SUM(C85:I85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="106" t="inlineStr">
+        <is>
+          <t>깁스</t>
+        </is>
+      </c>
+      <c r="B99" s="104" t="inlineStr">
+        <is>
+          <t>반깁스</t>
         </is>
       </c>
       <c r="C99" s="136" t="n"/>
@@ -3408,15 +3411,15 @@
       <c r="H99" s="136" t="n"/>
       <c r="I99" s="136" t="n"/>
       <c r="J99" s="137">
-        <f>SUM(C84:I84)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" ht="16.5" customHeight="1" s="78">
+        <f>SUM(C86:I86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
       <c r="A100" s="108" t="n"/>
-      <c r="B100" s="25" t="inlineStr">
-        <is>
-          <t>중증화상진단비</t>
+      <c r="B100" s="56" t="inlineStr">
+        <is>
+          <t>깁스진단비</t>
         </is>
       </c>
       <c r="C100" s="134" t="n"/>
@@ -3427,156 +3430,122 @@
       <c r="H100" s="134" t="n"/>
       <c r="I100" s="134" t="n"/>
       <c r="J100" s="135">
-        <f>SUM(C85:I85)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" ht="16.5" customHeight="1" s="78">
-      <c r="A101" s="108" t="n"/>
+        <f>SUM(C87:I87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="106" t="inlineStr">
+        <is>
+          <t>실손</t>
+        </is>
+      </c>
       <c r="B101" s="104" t="inlineStr">
         <is>
-          <t>반깁스</t>
-        </is>
-      </c>
-      <c r="C101" s="136" t="n"/>
-      <c r="D101" s="136" t="n"/>
-      <c r="E101" s="136" t="n"/>
-      <c r="F101" s="136" t="n"/>
-      <c r="G101" s="136" t="n"/>
-      <c r="H101" s="136" t="n"/>
-      <c r="I101" s="136" t="n"/>
+          <t>입원</t>
+        </is>
+      </c>
+      <c r="C101" s="169" t="n"/>
+      <c r="D101" s="169" t="n"/>
+      <c r="E101" s="169" t="n"/>
+      <c r="F101" s="169" t="n"/>
+      <c r="G101" s="169" t="n"/>
+      <c r="H101" s="169" t="n"/>
+      <c r="I101" s="169" t="n"/>
       <c r="J101" s="137">
-        <f>SUM(C86:I86)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102" ht="16.5" customHeight="1" s="78">
-      <c r="A102" s="108" t="n"/>
-      <c r="B102" s="56" t="inlineStr">
-        <is>
-          <t>깁스진단비</t>
-        </is>
-      </c>
-      <c r="C102" s="134" t="n"/>
-      <c r="D102" s="134" t="n"/>
-      <c r="E102" s="134" t="n"/>
-      <c r="F102" s="134" t="n"/>
-      <c r="G102" s="134" t="n"/>
-      <c r="H102" s="134" t="n"/>
-      <c r="I102" s="134" t="n"/>
-      <c r="J102" s="135">
-        <f>SUM(C87:I87)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103" ht="16.5" customHeight="1" s="78">
+        <f>SUM(C88:I88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="107" t="n"/>
+      <c r="B102" s="59" t="inlineStr">
+        <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="C102" s="170" t="n"/>
+      <c r="D102" s="170" t="n"/>
+      <c r="E102" s="170" t="n"/>
+      <c r="F102" s="170" t="n"/>
+      <c r="G102" s="170" t="n"/>
+      <c r="H102" s="170" t="n"/>
+      <c r="I102" s="170" t="n"/>
+      <c r="J102" s="139">
+        <f>SUM(C89:I89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
       <c r="A103" s="107" t="n"/>
-      <c r="B103" s="104" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="C103" s="169" t="n"/>
-      <c r="D103" s="169" t="n"/>
-      <c r="E103" s="169" t="n"/>
-      <c r="F103" s="169" t="n"/>
-      <c r="G103" s="169" t="n"/>
-      <c r="H103" s="169" t="n"/>
-      <c r="I103" s="169" t="n"/>
-      <c r="J103" s="137">
-        <f>SUM(C88:I88)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" ht="16.5" customHeight="1" s="78">
+      <c r="B103" s="59" t="inlineStr">
+        <is>
+          <t>약값</t>
+        </is>
+      </c>
+      <c r="C103" s="138" t="n"/>
+      <c r="D103" s="138" t="n"/>
+      <c r="E103" s="138" t="n"/>
+      <c r="F103" s="138" t="n"/>
+      <c r="G103" s="138" t="n"/>
+      <c r="H103" s="138" t="n"/>
+      <c r="I103" s="170" t="n"/>
+      <c r="J103" s="139">
+        <f>SUM(C90:I90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
       <c r="A104" s="107" t="n"/>
       <c r="B104" s="59" t="inlineStr">
         <is>
-          <t>통원</t>
-        </is>
-      </c>
-      <c r="C104" s="170" t="n"/>
-      <c r="D104" s="170" t="n"/>
-      <c r="E104" s="170" t="n"/>
-      <c r="F104" s="170" t="n"/>
-      <c r="G104" s="170" t="n"/>
-      <c r="H104" s="170" t="n"/>
+          <t>MRI/도수치료/비급여주사</t>
+        </is>
+      </c>
+      <c r="C104" s="138" t="n"/>
+      <c r="D104" s="138" t="n"/>
+      <c r="E104" s="138" t="n"/>
+      <c r="F104" s="138" t="n"/>
+      <c r="G104" s="138" t="n"/>
+      <c r="H104" s="138" t="n"/>
       <c r="I104" s="170" t="n"/>
-      <c r="J104" s="139">
-        <f>SUM(C89:I89)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" ht="16.5" customHeight="1" s="78">
-      <c r="A105" s="107" t="n"/>
-      <c r="B105" s="59" t="inlineStr">
-        <is>
-          <t>약값</t>
-        </is>
-      </c>
-      <c r="C105" s="138" t="n"/>
-      <c r="D105" s="138" t="n"/>
-      <c r="E105" s="138" t="n"/>
-      <c r="F105" s="138" t="n"/>
-      <c r="G105" s="138" t="n"/>
-      <c r="H105" s="138" t="n"/>
-      <c r="I105" s="170" t="n"/>
-      <c r="J105" s="139">
-        <f>SUM(C90:I90)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106" ht="16.5" customHeight="1" s="78">
-      <c r="A106" s="108" t="n"/>
-      <c r="B106" s="59" t="inlineStr">
-        <is>
-          <t>MRI/도수치료/비급여주사</t>
-        </is>
-      </c>
-      <c r="C106" s="138" t="n"/>
-      <c r="D106" s="138" t="n"/>
-      <c r="E106" s="138" t="n"/>
-      <c r="F106" s="138" t="n"/>
-      <c r="G106" s="138" t="n"/>
-      <c r="H106" s="138" t="n"/>
-      <c r="I106" s="170" t="n"/>
-      <c r="J106" s="133" t="n"/>
-    </row>
-    <row r="107" ht="16.5" customHeight="1" s="78">
-      <c r="A107" s="108" t="n"/>
-      <c r="B107" s="22" t="inlineStr">
+      <c r="J104" s="133" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="108" t="n"/>
+      <c r="B105" s="22" t="inlineStr">
         <is>
           <t>상해의료비</t>
         </is>
       </c>
-      <c r="C107" s="132" t="n"/>
-      <c r="D107" s="132" t="n"/>
-      <c r="E107" s="132" t="n"/>
-      <c r="F107" s="132" t="n"/>
-      <c r="G107" s="132" t="n"/>
-      <c r="H107" s="132" t="n"/>
-      <c r="I107" s="171" t="n"/>
-      <c r="J107" s="139" t="n"/>
-    </row>
-    <row r="108" ht="16.5" customHeight="1" s="78">
-      <c r="A108" s="101" t="inlineStr">
+      <c r="C105" s="132" t="n"/>
+      <c r="D105" s="132" t="n"/>
+      <c r="E105" s="132" t="n"/>
+      <c r="F105" s="132" t="n"/>
+      <c r="G105" s="132" t="n"/>
+      <c r="H105" s="132" t="n"/>
+      <c r="I105" s="171" t="n"/>
+      <c r="J105" s="139" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="101" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B108" s="75" t="inlineStr">
+      <c r="B106" s="75" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C108" s="172" t="n"/>
-      <c r="D108" s="172" t="n"/>
-      <c r="E108" s="172" t="n"/>
-      <c r="F108" s="172" t="n"/>
-      <c r="G108" s="172" t="n"/>
-      <c r="H108" s="172" t="n"/>
-      <c r="I108" s="172" t="n"/>
-      <c r="J108" s="173">
+      <c r="C106" s="172" t="n"/>
+      <c r="D106" s="172" t="n"/>
+      <c r="E106" s="172" t="n"/>
+      <c r="F106" s="172" t="n"/>
+      <c r="G106" s="172" t="n"/>
+      <c r="H106" s="172" t="n"/>
+      <c r="I106" s="172" t="n"/>
+      <c r="J106" s="173">
         <f>SUM(C91:I91)</f>
         <v/>
       </c>
@@ -5325,22 +5294,22 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="0" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>커버리지허용</t>
         </is>
       </c>
-      <c r="B80" s="0" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>라벨≠담보명 설계분</t>
         </is>
       </c>
-      <c r="C80" s="0" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>10억 플랜</t>
         </is>
       </c>
-      <c r="E80" s="0" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>담보명은 흥국 리셋월렛II — 라벨로는 자기 행 복귀 안 됨(정상)</t>
         </is>

--- a/master.xlsx
+++ b/master.xlsx
@@ -135,7 +135,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -219,6 +219,11 @@
         <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="54">
     <border>
@@ -897,7 +902,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1390,6 +1395,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="15" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1515,7 +1538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="78" min="1" max="1"/>
@@ -2177,38 +2200,38 @@
     </row>
     <row r="35" ht="16.5" customHeight="1" s="78">
       <c r="A35" s="102" t="n"/>
-      <c r="B35" s="93" t="inlineStr">
+      <c r="B35" s="174" t="inlineStr">
         <is>
           <t>뇌출혈진단비</t>
         </is>
       </c>
-      <c r="C35" s="153" t="n"/>
-      <c r="D35" s="153" t="n"/>
-      <c r="E35" s="153" t="n"/>
-      <c r="F35" s="153" t="n"/>
-      <c r="G35" s="153" t="n"/>
-      <c r="H35" s="153" t="n"/>
-      <c r="I35" s="153" t="n"/>
-      <c r="J35" s="154">
+      <c r="C35" s="175" t="n"/>
+      <c r="D35" s="175" t="n"/>
+      <c r="E35" s="175" t="n"/>
+      <c r="F35" s="175" t="n"/>
+      <c r="G35" s="175" t="n"/>
+      <c r="H35" s="175" t="n"/>
+      <c r="I35" s="175" t="n"/>
+      <c r="J35" s="176">
         <f>SUM(C34:I34)</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A36" s="102" t="n"/>
-      <c r="B36" s="96" t="inlineStr">
+      <c r="B36" s="177" t="inlineStr">
         <is>
           <t>중대한 뇌출혈</t>
         </is>
       </c>
-      <c r="C36" s="155" t="n"/>
-      <c r="D36" s="155" t="n"/>
-      <c r="E36" s="155" t="n"/>
-      <c r="F36" s="155" t="n"/>
-      <c r="G36" s="155" t="n"/>
-      <c r="H36" s="155" t="n"/>
-      <c r="I36" s="155" t="n"/>
-      <c r="J36" s="156">
+      <c r="C36" s="178" t="n"/>
+      <c r="D36" s="178" t="n"/>
+      <c r="E36" s="178" t="n"/>
+      <c r="F36" s="178" t="n"/>
+      <c r="G36" s="178" t="n"/>
+      <c r="H36" s="178" t="n"/>
+      <c r="I36" s="178" t="n"/>
+      <c r="J36" s="179">
         <f>SUM(C35:I35)</f>
         <v/>
       </c>
@@ -2666,7 +2689,7 @@
       <c r="A61" s="102" t="n"/>
       <c r="B61" s="31" t="inlineStr">
         <is>
-          <t>간병인지원일당</t>
+          <t>간병인질병일당(요양병원)</t>
         </is>
       </c>
       <c r="C61" s="138" t="n"/>
@@ -2682,7 +2705,7 @@
       <c r="A62" s="102" t="n"/>
       <c r="B62" s="31" t="inlineStr">
         <is>
-          <t>간호통합병동</t>
+          <t>간병인상해일당(요양병원)</t>
         </is>
       </c>
       <c r="C62" s="138" t="n"/>
@@ -2692,16 +2715,13 @@
       <c r="G62" s="138" t="n"/>
       <c r="H62" s="138" t="n"/>
       <c r="I62" s="138" t="n"/>
-      <c r="J62" s="139">
-        <f>SUM(C53:I53)</f>
-        <v/>
-      </c>
+      <c r="J62" s="139" t="n"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" s="78">
       <c r="A63" s="102" t="n"/>
-      <c r="B63" s="65" t="inlineStr">
-        <is>
-          <t>1인실 종합병원</t>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>간병인지원일당</t>
         </is>
       </c>
       <c r="C63" s="138" t="n"/>
@@ -2711,16 +2731,13 @@
       <c r="G63" s="138" t="n"/>
       <c r="H63" s="138" t="n"/>
       <c r="I63" s="138" t="n"/>
-      <c r="J63" s="139">
-        <f>SUM(C54:I54)</f>
-        <v/>
-      </c>
+      <c r="J63" s="139" t="n"/>
     </row>
     <row r="64" ht="17.25" customHeight="1" s="78">
       <c r="A64" s="102" t="n"/>
-      <c r="B64" s="65" t="inlineStr">
-        <is>
-          <t>1인실 상급병원</t>
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>간호통합병동</t>
         </is>
       </c>
       <c r="C64" s="138" t="n"/>
@@ -2731,15 +2748,15 @@
       <c r="H64" s="138" t="n"/>
       <c r="I64" s="138" t="n"/>
       <c r="J64" s="139">
-        <f>SUM(C55:I55)</f>
+        <f>SUM(C53:I53)</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="17.25" customHeight="1" s="78">
       <c r="A65" s="102" t="n"/>
-      <c r="B65" s="31" t="inlineStr">
-        <is>
-          <t>질병중환자실</t>
+      <c r="B65" s="65" t="inlineStr">
+        <is>
+          <t>1인실 종합병원</t>
         </is>
       </c>
       <c r="C65" s="138" t="n"/>
@@ -2750,112 +2767,110 @@
       <c r="H65" s="138" t="n"/>
       <c r="I65" s="138" t="n"/>
       <c r="J65" s="139">
+        <f>SUM(C54:I54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A66" s="102" t="n"/>
+      <c r="B66" s="65" t="inlineStr">
+        <is>
+          <t>1인실 상급병원</t>
+        </is>
+      </c>
+      <c r="C66" s="138" t="n"/>
+      <c r="D66" s="138" t="n"/>
+      <c r="E66" s="138" t="n"/>
+      <c r="F66" s="138" t="n"/>
+      <c r="G66" s="138" t="n"/>
+      <c r="H66" s="138" t="n"/>
+      <c r="I66" s="138" t="n"/>
+      <c r="J66" s="139">
+        <f>SUM(C55:I55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="16.5" customHeight="1" s="78">
+      <c r="A67" s="103" t="n"/>
+      <c r="B67" s="31" t="inlineStr">
+        <is>
+          <t>질병중환자실</t>
+        </is>
+      </c>
+      <c r="C67" s="138" t="n"/>
+      <c r="D67" s="138" t="n"/>
+      <c r="E67" s="138" t="n"/>
+      <c r="F67" s="138" t="n"/>
+      <c r="G67" s="138" t="n"/>
+      <c r="H67" s="138" t="n"/>
+      <c r="I67" s="138" t="n"/>
+      <c r="J67" s="139">
         <f>SUM(C56:I56)</f>
         <v/>
       </c>
     </row>
-    <row r="66" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A66" s="103" t="n"/>
-      <c r="B66" s="25" t="inlineStr">
+    <row r="68" ht="16.5" customHeight="1" s="78">
+      <c r="A68" s="103" t="n"/>
+      <c r="B68" s="25" t="inlineStr">
         <is>
           <t>상해중환자실</t>
         </is>
       </c>
-      <c r="C66" s="134" t="n"/>
-      <c r="D66" s="134" t="n"/>
-      <c r="E66" s="134" t="n"/>
-      <c r="F66" s="134" t="n"/>
-      <c r="G66" s="134" t="n"/>
-      <c r="H66" s="134" t="n"/>
-      <c r="I66" s="134" t="n"/>
-      <c r="J66" s="135">
+      <c r="C68" s="134" t="n"/>
+      <c r="D68" s="134" t="n"/>
+      <c r="E68" s="134" t="n"/>
+      <c r="F68" s="134" t="n"/>
+      <c r="G68" s="134" t="n"/>
+      <c r="H68" s="134" t="n"/>
+      <c r="I68" s="134" t="n"/>
+      <c r="J68" s="135">
         <f>SUM(C57:I57)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" ht="16.5" customHeight="1" s="78">
-      <c r="A67" s="101" t="inlineStr">
-        <is>
-          <t>수술</t>
-        </is>
-      </c>
-      <c r="B67" s="104" t="inlineStr">
-        <is>
-          <t>상해수술비</t>
-        </is>
-      </c>
-      <c r="C67" s="136" t="n"/>
-      <c r="D67" s="136" t="n"/>
-      <c r="E67" s="136" t="n"/>
-      <c r="F67" s="136" t="n"/>
-      <c r="G67" s="136" t="n"/>
-      <c r="H67" s="136" t="n"/>
-      <c r="I67" s="136" t="n"/>
-      <c r="J67" s="137">
-        <f>SUM(C58:I58)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" ht="16.5" customHeight="1" s="78">
-      <c r="A68" s="102" t="n"/>
-      <c r="B68" s="64" t="inlineStr">
-        <is>
-          <t>중대한상해수술비</t>
-        </is>
-      </c>
-      <c r="C68" s="159" t="n"/>
-      <c r="D68" s="159" t="n"/>
-      <c r="E68" s="159" t="n"/>
-      <c r="F68" s="159" t="n"/>
-      <c r="G68" s="159" t="n"/>
-      <c r="H68" s="159" t="n"/>
-      <c r="I68" s="159" t="n"/>
-      <c r="J68" s="139">
-        <f>SUM(C59:I59)</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="78">
       <c r="A69" s="102" t="n"/>
-      <c r="B69" s="59" t="inlineStr">
-        <is>
-          <t>상해 종수술비(1-3종)</t>
-        </is>
-      </c>
-      <c r="C69" s="159" t="n"/>
-      <c r="D69" s="159" t="n"/>
-      <c r="E69" s="159" t="n"/>
-      <c r="F69" s="160" t="n"/>
-      <c r="G69" s="159" t="n"/>
-      <c r="H69" s="159" t="n"/>
-      <c r="I69" s="159" t="n"/>
-      <c r="J69" s="139" t="n"/>
+      <c r="B69" s="104" t="inlineStr">
+        <is>
+          <t>상해수술비</t>
+        </is>
+      </c>
+      <c r="C69" s="136" t="n"/>
+      <c r="D69" s="136" t="n"/>
+      <c r="E69" s="136" t="n"/>
+      <c r="F69" s="136" t="n"/>
+      <c r="G69" s="136" t="n"/>
+      <c r="H69" s="136" t="n"/>
+      <c r="I69" s="136" t="n"/>
+      <c r="J69" s="137">
+        <f>SUM(C58:I58)</f>
+        <v/>
+      </c>
     </row>
     <row r="70" ht="17.25" customHeight="1" s="78">
       <c r="A70" s="102" t="n"/>
-      <c r="B70" s="59" t="inlineStr">
-        <is>
-          <t>상해 종수술비(1-5종)</t>
+      <c r="B70" s="64" t="inlineStr">
+        <is>
+          <t>중대한상해수술비</t>
         </is>
       </c>
       <c r="C70" s="159" t="n"/>
       <c r="D70" s="159" t="n"/>
       <c r="E70" s="159" t="n"/>
-      <c r="F70" s="160" t="n"/>
+      <c r="F70" s="159" t="n"/>
       <c r="G70" s="159" t="n"/>
       <c r="H70" s="159" t="n"/>
       <c r="I70" s="159" t="n"/>
-      <c r="J70" s="139" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="J70" s="139">
+        <f>SUM(C59:I59)</f>
+        <v/>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="78">
       <c r="A71" s="102" t="n"/>
       <c r="B71" s="59" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-8종)</t>
+          <t>상해 종수술비(1-3종)</t>
         </is>
       </c>
       <c r="C71" s="159" t="n"/>
@@ -2871,45 +2886,43 @@
       <c r="A72" s="102" t="n"/>
       <c r="B72" s="59" t="inlineStr">
         <is>
-          <t>창상봉합술</t>
-        </is>
-      </c>
-      <c r="C72" s="138" t="n"/>
-      <c r="D72" s="138" t="n"/>
-      <c r="E72" s="138" t="n"/>
-      <c r="F72" s="161" t="n"/>
-      <c r="G72" s="138" t="n"/>
-      <c r="H72" s="138" t="n"/>
-      <c r="I72" s="138" t="n"/>
-      <c r="J72" s="139">
-        <f>SUM(C61:I61)</f>
-        <v/>
+          <t>상해 종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="C72" s="159" t="n"/>
+      <c r="D72" s="159" t="n"/>
+      <c r="E72" s="159" t="n"/>
+      <c r="F72" s="160" t="n"/>
+      <c r="G72" s="159" t="n"/>
+      <c r="H72" s="159" t="n"/>
+      <c r="I72" s="159" t="n"/>
+      <c r="J72" s="139" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="78">
       <c r="A73" s="102" t="n"/>
       <c r="B73" s="59" t="inlineStr">
         <is>
-          <t>골절수술비</t>
-        </is>
-      </c>
-      <c r="C73" s="138" t="n"/>
-      <c r="D73" s="138" t="n"/>
-      <c r="E73" s="138" t="n"/>
-      <c r="F73" s="161" t="n"/>
-      <c r="G73" s="138" t="n"/>
-      <c r="H73" s="138" t="n"/>
-      <c r="I73" s="138" t="n"/>
-      <c r="J73" s="139">
-        <f>SUM(C62:I62)</f>
-        <v/>
-      </c>
+          <t>상해 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C73" s="159" t="n"/>
+      <c r="D73" s="159" t="n"/>
+      <c r="E73" s="159" t="n"/>
+      <c r="F73" s="160" t="n"/>
+      <c r="G73" s="159" t="n"/>
+      <c r="H73" s="159" t="n"/>
+      <c r="I73" s="159" t="n"/>
+      <c r="J73" s="139" t="n"/>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="78">
       <c r="A74" s="102" t="n"/>
-      <c r="B74" s="66" t="inlineStr">
-        <is>
-          <t>5대골절수술비</t>
+      <c r="B74" s="59" t="inlineStr">
+        <is>
+          <t>창상봉합술</t>
         </is>
       </c>
       <c r="C74" s="138" t="n"/>
@@ -2920,89 +2933,91 @@
       <c r="H74" s="138" t="n"/>
       <c r="I74" s="138" t="n"/>
       <c r="J74" s="139">
-        <f>SUM(C63:I63)</f>
+        <f>SUM(C61:I61)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A75" s="102" t="n"/>
-      <c r="B75" s="56" t="inlineStr">
-        <is>
-          <t>화상수술비</t>
-        </is>
-      </c>
-      <c r="C75" s="134" t="n"/>
-      <c r="D75" s="134" t="n"/>
-      <c r="E75" s="134" t="n"/>
-      <c r="F75" s="162" t="n"/>
-      <c r="G75" s="134" t="n"/>
-      <c r="H75" s="134" t="n"/>
-      <c r="I75" s="134" t="n"/>
-      <c r="J75" s="135">
-        <f>SUM(C64:I64)</f>
+      <c r="B75" s="59" t="inlineStr">
+        <is>
+          <t>골절수술비</t>
+        </is>
+      </c>
+      <c r="C75" s="138" t="n"/>
+      <c r="D75" s="138" t="n"/>
+      <c r="E75" s="138" t="n"/>
+      <c r="F75" s="161" t="n"/>
+      <c r="G75" s="138" t="n"/>
+      <c r="H75" s="138" t="n"/>
+      <c r="I75" s="138" t="n"/>
+      <c r="J75" s="139">
+        <f>SUM(C62:I62)</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16.5" customHeight="1" s="78">
       <c r="A76" s="102" t="n"/>
-      <c r="B76" s="64" t="inlineStr">
-        <is>
-          <t>질병수술비</t>
-        </is>
-      </c>
-      <c r="C76" s="159" t="n"/>
-      <c r="D76" s="159" t="n"/>
-      <c r="E76" s="159" t="n"/>
-      <c r="F76" s="163" t="n"/>
-      <c r="G76" s="159" t="n"/>
-      <c r="H76" s="159" t="n"/>
-      <c r="I76" s="164" t="n"/>
-      <c r="J76" s="133">
-        <f>SUM(C65:I65)</f>
+      <c r="B76" s="66" t="inlineStr">
+        <is>
+          <t>5대골절수술비</t>
+        </is>
+      </c>
+      <c r="C76" s="138" t="n"/>
+      <c r="D76" s="138" t="n"/>
+      <c r="E76" s="138" t="n"/>
+      <c r="F76" s="161" t="n"/>
+      <c r="G76" s="138" t="n"/>
+      <c r="H76" s="138" t="n"/>
+      <c r="I76" s="138" t="n"/>
+      <c r="J76" s="139">
+        <f>SUM(C63:I63)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="78">
       <c r="A77" s="102" t="n"/>
-      <c r="B77" s="59" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-3종)</t>
-        </is>
-      </c>
-      <c r="C77" s="138" t="n"/>
-      <c r="D77" s="138" t="n"/>
-      <c r="E77" s="138" t="n"/>
-      <c r="F77" s="165" t="n"/>
-      <c r="G77" s="138" t="n"/>
-      <c r="H77" s="138" t="n"/>
-      <c r="I77" s="138" t="n"/>
-      <c r="J77" s="139" t="n"/>
+      <c r="B77" s="56" t="inlineStr">
+        <is>
+          <t>화상수술비</t>
+        </is>
+      </c>
+      <c r="C77" s="134" t="n"/>
+      <c r="D77" s="134" t="n"/>
+      <c r="E77" s="134" t="n"/>
+      <c r="F77" s="162" t="n"/>
+      <c r="G77" s="134" t="n"/>
+      <c r="H77" s="134" t="n"/>
+      <c r="I77" s="134" t="n"/>
+      <c r="J77" s="135">
+        <f>SUM(C64:I64)</f>
+        <v/>
+      </c>
     </row>
     <row r="78" ht="17.25" customHeight="1" s="78">
       <c r="A78" s="102" t="n"/>
-      <c r="B78" s="59" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-5종)</t>
-        </is>
-      </c>
-      <c r="C78" s="138" t="n"/>
-      <c r="D78" s="138" t="n"/>
-      <c r="E78" s="138" t="n"/>
-      <c r="F78" s="165" t="n"/>
-      <c r="G78" s="138" t="n"/>
-      <c r="H78" s="138" t="n"/>
-      <c r="I78" s="138" t="n"/>
-      <c r="J78" s="139" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="B78" s="64" t="inlineStr">
+        <is>
+          <t>질병수술비</t>
+        </is>
+      </c>
+      <c r="C78" s="159" t="n"/>
+      <c r="D78" s="159" t="n"/>
+      <c r="E78" s="159" t="n"/>
+      <c r="F78" s="163" t="n"/>
+      <c r="G78" s="159" t="n"/>
+      <c r="H78" s="159" t="n"/>
+      <c r="I78" s="164" t="n"/>
+      <c r="J78" s="133">
+        <f>SUM(C65:I65)</f>
+        <v/>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1" s="78">
       <c r="A79" s="102" t="n"/>
       <c r="B79" s="59" t="inlineStr">
         <is>
-          <t>질병 종수술비(1-8종)</t>
+          <t>질병 종수술비(1-3종)</t>
         </is>
       </c>
       <c r="C79" s="138" t="n"/>
@@ -3016,47 +3031,45 @@
     </row>
     <row r="80" ht="16.5" customHeight="1" s="78">
       <c r="A80" s="102" t="n"/>
-      <c r="B80" s="68" t="inlineStr">
-        <is>
-          <t>뇌혈관수술비</t>
-        </is>
-      </c>
-      <c r="C80" s="166" t="n"/>
-      <c r="D80" s="166" t="n"/>
-      <c r="E80" s="166" t="n"/>
-      <c r="F80" s="166" t="n"/>
-      <c r="G80" s="166" t="n"/>
-      <c r="H80" s="166" t="n"/>
-      <c r="I80" s="166" t="n"/>
-      <c r="J80" s="139">
-        <f>SUM(C67:I67)</f>
-        <v/>
+      <c r="B80" s="59" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="C80" s="138" t="n"/>
+      <c r="D80" s="138" t="n"/>
+      <c r="E80" s="138" t="n"/>
+      <c r="F80" s="165" t="n"/>
+      <c r="G80" s="138" t="n"/>
+      <c r="H80" s="138" t="n"/>
+      <c r="I80" s="138" t="n"/>
+      <c r="J80" s="139" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="81" ht="17.25" customHeight="1" s="78">
       <c r="A81" s="102" t="n"/>
-      <c r="B81" s="68" t="inlineStr">
-        <is>
-          <t>허혈성수술비</t>
-        </is>
-      </c>
-      <c r="C81" s="166" t="n"/>
-      <c r="D81" s="166" t="n"/>
-      <c r="E81" s="166" t="n"/>
-      <c r="F81" s="166" t="n"/>
-      <c r="G81" s="166" t="n"/>
-      <c r="H81" s="166" t="n"/>
-      <c r="I81" s="166" t="n"/>
-      <c r="J81" s="139">
-        <f>SUM(C68:I68)</f>
-        <v/>
-      </c>
+      <c r="B81" s="59" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-8종)</t>
+        </is>
+      </c>
+      <c r="C81" s="138" t="n"/>
+      <c r="D81" s="138" t="n"/>
+      <c r="E81" s="138" t="n"/>
+      <c r="F81" s="165" t="n"/>
+      <c r="G81" s="138" t="n"/>
+      <c r="H81" s="138" t="n"/>
+      <c r="I81" s="138" t="n"/>
+      <c r="J81" s="139" t="n"/>
     </row>
     <row r="82" ht="17.25" customHeight="1" s="78">
       <c r="A82" s="102" t="n"/>
       <c r="B82" s="68" t="inlineStr">
         <is>
-          <t>심장수술비</t>
+          <t>뇌혈관수술비</t>
         </is>
       </c>
       <c r="C82" s="166" t="n"/>
@@ -3067,15 +3080,15 @@
       <c r="H82" s="166" t="n"/>
       <c r="I82" s="166" t="n"/>
       <c r="J82" s="139">
-        <f>SUM(C69:I69)</f>
+        <f>SUM(C67:I67)</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="17.25" customHeight="1" s="78" thickBot="1">
       <c r="A83" s="102" t="n"/>
-      <c r="B83" s="60" t="inlineStr">
-        <is>
-          <t>120대수술비</t>
+      <c r="B83" s="68" t="inlineStr">
+        <is>
+          <t>허혈성수술비</t>
         </is>
       </c>
       <c r="C83" s="166" t="n"/>
@@ -3085,115 +3098,111 @@
       <c r="G83" s="166" t="n"/>
       <c r="H83" s="166" t="n"/>
       <c r="I83" s="166" t="n"/>
-      <c r="J83" s="167">
-        <f>SUM(C70:I70)</f>
+      <c r="J83" s="139">
+        <f>SUM(C68:I68)</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="78">
       <c r="A84" s="102" t="n"/>
-      <c r="B84" s="69" t="inlineStr">
+      <c r="B84" s="68" t="inlineStr">
+        <is>
+          <t>심장수술비</t>
+        </is>
+      </c>
+      <c r="C84" s="166" t="n"/>
+      <c r="D84" s="166" t="n"/>
+      <c r="E84" s="166" t="n"/>
+      <c r="F84" s="166" t="n"/>
+      <c r="G84" s="166" t="n"/>
+      <c r="H84" s="166" t="n"/>
+      <c r="I84" s="166" t="n"/>
+      <c r="J84" s="139">
+        <f>SUM(C69:I69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="17.25" customHeight="1" s="78" thickBot="1">
+      <c r="A85" s="102" t="n"/>
+      <c r="B85" s="60" t="inlineStr">
+        <is>
+          <t>n대수술비</t>
+        </is>
+      </c>
+      <c r="C85" s="166" t="n"/>
+      <c r="D85" s="166" t="n"/>
+      <c r="E85" s="166" t="n"/>
+      <c r="F85" s="166" t="n"/>
+      <c r="G85" s="166" t="n"/>
+      <c r="H85" s="166" t="n"/>
+      <c r="I85" s="166" t="n"/>
+      <c r="J85" s="167">
+        <f>SUM(C70:I70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="16.5" customHeight="1" s="78" thickBot="1">
+      <c r="A86" s="103" t="n"/>
+      <c r="B86" s="69" t="inlineStr">
         <is>
           <t>5대기관 수술비 관혈</t>
         </is>
       </c>
-      <c r="C84" s="140" t="n"/>
-      <c r="D84" s="140" t="n"/>
-      <c r="E84" s="140" t="n"/>
-      <c r="F84" s="140" t="n"/>
-      <c r="G84" s="140" t="n"/>
-      <c r="H84" s="140" t="n"/>
-      <c r="I84" s="140" t="n"/>
-      <c r="J84" s="137">
+      <c r="C86" s="140" t="n"/>
+      <c r="D86" s="140" t="n"/>
+      <c r="E86" s="140" t="n"/>
+      <c r="F86" s="140" t="n"/>
+      <c r="G86" s="140" t="n"/>
+      <c r="H86" s="140" t="n"/>
+      <c r="I86" s="140" t="n"/>
+      <c r="J86" s="137">
         <f>SUM(C71:I71)</f>
         <v/>
       </c>
     </row>
-    <row r="85" ht="17.25" customHeight="1" s="78" thickBot="1">
-      <c r="A85" s="103" t="n"/>
-      <c r="B85" s="70" t="inlineStr">
+    <row r="87" ht="17.25" customHeight="1" s="78">
+      <c r="A87" s="103" t="n"/>
+      <c r="B87" s="70" t="inlineStr">
         <is>
           <t>5대기관 수술비 비관혈</t>
         </is>
       </c>
-      <c r="C85" s="134" t="n"/>
-      <c r="D85" s="134" t="n"/>
-      <c r="E85" s="134" t="n"/>
-      <c r="F85" s="134" t="n"/>
-      <c r="G85" s="134" t="n"/>
-      <c r="H85" s="134" t="n"/>
-      <c r="I85" s="134" t="n"/>
-      <c r="J85" s="135">
+      <c r="C87" s="134" t="n"/>
+      <c r="D87" s="134" t="n"/>
+      <c r="E87" s="134" t="n"/>
+      <c r="F87" s="134" t="n"/>
+      <c r="G87" s="134" t="n"/>
+      <c r="H87" s="134" t="n"/>
+      <c r="I87" s="134" t="n"/>
+      <c r="J87" s="135">
         <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A86" s="106" t="inlineStr">
-        <is>
-          <t>운전</t>
-        </is>
-      </c>
-      <c r="B86" s="28" t="inlineStr">
+    <row r="88" ht="16.5" customHeight="1" s="78">
+      <c r="A88" s="102" t="n"/>
+      <c r="B88" s="28" t="inlineStr">
         <is>
           <t>대인</t>
         </is>
       </c>
-      <c r="C86" s="119" t="n"/>
-      <c r="D86" s="119" t="n"/>
-      <c r="E86" s="119" t="n"/>
-      <c r="F86" s="119" t="n"/>
-      <c r="G86" s="119" t="n"/>
-      <c r="H86" s="119" t="n"/>
-      <c r="I86" s="119" t="n"/>
-      <c r="J86" s="137">
+      <c r="C88" s="119" t="n"/>
+      <c r="D88" s="119" t="n"/>
+      <c r="E88" s="119" t="n"/>
+      <c r="F88" s="119" t="n"/>
+      <c r="G88" s="119" t="n"/>
+      <c r="H88" s="119" t="n"/>
+      <c r="I88" s="119" t="n"/>
+      <c r="J88" s="137">
         <f>SUM(C73:I73)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="17.25" customHeight="1" s="78">
-      <c r="A87" s="107" t="n"/>
-      <c r="B87" s="31" t="inlineStr">
+    <row r="89" ht="16.5" customHeight="1" s="78">
+      <c r="A89" s="102" t="n"/>
+      <c r="B89" s="31" t="inlineStr">
         <is>
           <t>대물</t>
-        </is>
-      </c>
-      <c r="C87" s="149" t="n"/>
-      <c r="D87" s="149" t="n"/>
-      <c r="E87" s="149" t="n"/>
-      <c r="F87" s="149" t="n"/>
-      <c r="G87" s="149" t="n"/>
-      <c r="H87" s="149" t="n"/>
-      <c r="I87" s="149" t="n"/>
-      <c r="J87" s="139">
-        <f>SUM(C74:I74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="16.5" customHeight="1" s="78">
-      <c r="A88" s="107" t="n"/>
-      <c r="B88" s="31" t="inlineStr">
-        <is>
-          <t>합의금</t>
-        </is>
-      </c>
-      <c r="C88" s="149" t="n"/>
-      <c r="D88" s="149" t="n"/>
-      <c r="E88" s="149" t="n"/>
-      <c r="F88" s="149" t="n"/>
-      <c r="G88" s="149" t="n"/>
-      <c r="H88" s="149" t="n"/>
-      <c r="I88" s="149" t="n"/>
-      <c r="J88" s="139">
-        <f>SUM(C75:I75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="16.5" customHeight="1" s="78">
-      <c r="A89" s="107" t="n"/>
-      <c r="B89" s="65" t="inlineStr">
-        <is>
-          <t>6주미만</t>
         </is>
       </c>
       <c r="C89" s="149" t="n"/>
@@ -3204,15 +3213,15 @@
       <c r="H89" s="149" t="n"/>
       <c r="I89" s="149" t="n"/>
       <c r="J89" s="139">
-        <f>SUM(C76:I76)</f>
+        <f>SUM(C74:I74)</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="17.25" customHeight="1" s="78">
-      <c r="A90" s="107" t="n"/>
+      <c r="A90" s="102" t="n"/>
       <c r="B90" s="31" t="inlineStr">
         <is>
-          <t>변호사</t>
+          <t>합의금</t>
         </is>
       </c>
       <c r="C90" s="149" t="n"/>
@@ -3223,184 +3232,172 @@
       <c r="H90" s="149" t="n"/>
       <c r="I90" s="149" t="n"/>
       <c r="J90" s="139">
+        <f>SUM(C75:I75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="17.25" customHeight="1" s="78">
+      <c r="A91" s="102" t="n"/>
+      <c r="B91" s="65" t="inlineStr">
+        <is>
+          <t>6주미만</t>
+        </is>
+      </c>
+      <c r="C91" s="149" t="n"/>
+      <c r="D91" s="149" t="n"/>
+      <c r="E91" s="149" t="n"/>
+      <c r="F91" s="149" t="n"/>
+      <c r="G91" s="149" t="n"/>
+      <c r="H91" s="149" t="n"/>
+      <c r="I91" s="149" t="n"/>
+      <c r="J91" s="139">
+        <f>SUM(C76:I76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="16.5" customHeight="1" s="78">
+      <c r="A92" s="103" t="n"/>
+      <c r="B92" s="31" t="inlineStr">
+        <is>
+          <t>변호사</t>
+        </is>
+      </c>
+      <c r="C92" s="149" t="n"/>
+      <c r="D92" s="149" t="n"/>
+      <c r="E92" s="149" t="n"/>
+      <c r="F92" s="149" t="n"/>
+      <c r="G92" s="149" t="n"/>
+      <c r="H92" s="149" t="n"/>
+      <c r="I92" s="149" t="n"/>
+      <c r="J92" s="139">
         <f>SUM(C77:I77)</f>
         <v/>
       </c>
     </row>
-    <row r="91" ht="17.25" customHeight="1" s="78">
-      <c r="A91" s="108" t="n"/>
-      <c r="B91" s="25" t="inlineStr">
+    <row r="93" ht="16.5" customHeight="1" s="78">
+      <c r="A93" s="108" t="n"/>
+      <c r="B93" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C91" s="168" t="n"/>
-      <c r="D91" s="168" t="n"/>
-      <c r="E91" s="168" t="n"/>
-      <c r="F91" s="168" t="n"/>
-      <c r="G91" s="168" t="n"/>
-      <c r="H91" s="168" t="n"/>
-      <c r="I91" s="168" t="n"/>
-      <c r="J91" s="135">
+      <c r="C93" s="168" t="n"/>
+      <c r="D93" s="168" t="n"/>
+      <c r="E93" s="168" t="n"/>
+      <c r="F93" s="168" t="n"/>
+      <c r="G93" s="168" t="n"/>
+      <c r="H93" s="168" t="n"/>
+      <c r="I93" s="168" t="n"/>
+      <c r="J93" s="135">
         <f>SUM(C78:I78)</f>
         <v/>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="106" t="inlineStr">
-        <is>
-          <t>골절</t>
-        </is>
-      </c>
-      <c r="B92" s="64" t="inlineStr">
+    <row r="94" ht="16.5" customHeight="1" s="78">
+      <c r="A94" s="107" t="n"/>
+      <c r="B94" s="64" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C92" s="159" t="n"/>
-      <c r="D92" s="159" t="n"/>
-      <c r="E92" s="159" t="n"/>
-      <c r="F92" s="159" t="n"/>
-      <c r="G92" s="159" t="n"/>
-      <c r="H92" s="159" t="n"/>
-      <c r="I92" s="159" t="n"/>
-      <c r="J92" s="133">
+      <c r="C94" s="159" t="n"/>
+      <c r="D94" s="159" t="n"/>
+      <c r="E94" s="159" t="n"/>
+      <c r="F94" s="159" t="n"/>
+      <c r="G94" s="159" t="n"/>
+      <c r="H94" s="159" t="n"/>
+      <c r="I94" s="159" t="n"/>
+      <c r="J94" s="133">
         <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="107" t="n"/>
-      <c r="B93" s="59" t="inlineStr">
+    <row r="95" ht="16.5" customHeight="1" s="78">
+      <c r="A95" s="108" t="n"/>
+      <c r="B95" s="59" t="inlineStr">
         <is>
           <t>골절(치아파절제외)</t>
         </is>
       </c>
-      <c r="C93" s="138" t="n"/>
-      <c r="D93" s="138" t="n"/>
-      <c r="E93" s="138" t="n"/>
-      <c r="F93" s="138" t="n"/>
-      <c r="G93" s="138" t="n"/>
-      <c r="H93" s="138" t="n"/>
-      <c r="I93" s="138" t="n"/>
-      <c r="J93" s="139">
+      <c r="C95" s="138" t="n"/>
+      <c r="D95" s="138" t="n"/>
+      <c r="E95" s="138" t="n"/>
+      <c r="F95" s="138" t="n"/>
+      <c r="G95" s="138" t="n"/>
+      <c r="H95" s="138" t="n"/>
+      <c r="I95" s="138" t="n"/>
+      <c r="J95" s="139">
         <f>SUM(C80:I80)</f>
         <v/>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="108" t="n"/>
-      <c r="B94" s="70" t="inlineStr">
+    <row r="96" ht="16.5" customHeight="1" s="78">
+      <c r="A96" s="108" t="n"/>
+      <c r="B96" s="70" t="inlineStr">
         <is>
           <t>5대골절진단비</t>
         </is>
       </c>
-      <c r="C94" s="134" t="n"/>
-      <c r="D94" s="134" t="n"/>
-      <c r="E94" s="134" t="n"/>
-      <c r="F94" s="134" t="n"/>
-      <c r="G94" s="134" t="n"/>
-      <c r="H94" s="134" t="n"/>
-      <c r="I94" s="134" t="n"/>
-      <c r="J94" s="135">
+      <c r="C96" s="134" t="n"/>
+      <c r="D96" s="134" t="n"/>
+      <c r="E96" s="134" t="n"/>
+      <c r="F96" s="134" t="n"/>
+      <c r="G96" s="134" t="n"/>
+      <c r="H96" s="134" t="n"/>
+      <c r="I96" s="134" t="n"/>
+      <c r="J96" s="135">
         <f>SUM(C81:I81)</f>
         <v/>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="109" t="inlineStr">
+    <row r="97" ht="16.5" customHeight="1" s="78">
+      <c r="A97" s="109" t="inlineStr">
         <is>
           <t>응급실</t>
         </is>
       </c>
-      <c r="B95" s="63" t="inlineStr">
+      <c r="B97" s="63" t="inlineStr">
         <is>
           <t>응급실(응급)</t>
         </is>
       </c>
-      <c r="C95" s="130" t="n"/>
-      <c r="D95" s="130" t="n"/>
-      <c r="E95" s="130" t="n"/>
-      <c r="F95" s="130" t="n"/>
-      <c r="G95" s="130" t="n"/>
-      <c r="H95" s="130" t="n"/>
-      <c r="I95" s="130" t="n"/>
-      <c r="J95" s="131">
+      <c r="C97" s="130" t="n"/>
+      <c r="D97" s="130" t="n"/>
+      <c r="E97" s="130" t="n"/>
+      <c r="F97" s="130" t="n"/>
+      <c r="G97" s="130" t="n"/>
+      <c r="H97" s="130" t="n"/>
+      <c r="I97" s="130" t="n"/>
+      <c r="J97" s="131">
         <f>SUM(C82:I82)</f>
         <v/>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="101" t="inlineStr">
+    <row r="98" ht="16.5" customHeight="1" s="78">
+      <c r="A98" s="101" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="B96" s="34" t="inlineStr">
+      <c r="B98" s="34" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
       </c>
-      <c r="C96" s="140" t="n"/>
-      <c r="D96" s="140" t="n"/>
-      <c r="E96" s="140" t="n"/>
-      <c r="F96" s="140" t="n"/>
-      <c r="G96" s="140" t="n"/>
-      <c r="H96" s="140" t="n"/>
-      <c r="I96" s="140" t="n"/>
-      <c r="J96" s="141" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="106" t="inlineStr">
-        <is>
-          <t>화상</t>
-        </is>
-      </c>
-      <c r="B97" s="28" t="inlineStr">
+      <c r="C98" s="140" t="n"/>
+      <c r="D98" s="140" t="n"/>
+      <c r="E98" s="140" t="n"/>
+      <c r="F98" s="140" t="n"/>
+      <c r="G98" s="140" t="n"/>
+      <c r="H98" s="140" t="n"/>
+      <c r="I98" s="140" t="n"/>
+      <c r="J98" s="141" t="n"/>
+    </row>
+    <row r="99" ht="16.5" customHeight="1" s="78">
+      <c r="A99" s="103" t="n"/>
+      <c r="B99" s="28" t="inlineStr">
         <is>
           <t>화상진단비</t>
-        </is>
-      </c>
-      <c r="C97" s="136" t="n"/>
-      <c r="D97" s="136" t="n"/>
-      <c r="E97" s="136" t="n"/>
-      <c r="F97" s="136" t="n"/>
-      <c r="G97" s="136" t="n"/>
-      <c r="H97" s="136" t="n"/>
-      <c r="I97" s="136" t="n"/>
-      <c r="J97" s="137">
-        <f>SUM(C84:I84)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="108" t="n"/>
-      <c r="B98" s="25" t="inlineStr">
-        <is>
-          <t>중증화상진단비</t>
-        </is>
-      </c>
-      <c r="C98" s="134" t="n"/>
-      <c r="D98" s="134" t="n"/>
-      <c r="E98" s="134" t="n"/>
-      <c r="F98" s="134" t="n"/>
-      <c r="G98" s="134" t="n"/>
-      <c r="H98" s="134" t="n"/>
-      <c r="I98" s="134" t="n"/>
-      <c r="J98" s="135">
-        <f>SUM(C85:I85)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="106" t="inlineStr">
-        <is>
-          <t>깁스</t>
-        </is>
-      </c>
-      <c r="B99" s="104" t="inlineStr">
-        <is>
-          <t>반깁스</t>
         </is>
       </c>
       <c r="C99" s="136" t="n"/>
@@ -3411,15 +3408,15 @@
       <c r="H99" s="136" t="n"/>
       <c r="I99" s="136" t="n"/>
       <c r="J99" s="137">
-        <f>SUM(C86:I86)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
+        <f>SUM(C84:I84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="16.5" customHeight="1" s="78">
       <c r="A100" s="108" t="n"/>
-      <c r="B100" s="56" t="inlineStr">
-        <is>
-          <t>깁스진단비</t>
+      <c r="B100" s="25" t="inlineStr">
+        <is>
+          <t>중증화상진단비</t>
         </is>
       </c>
       <c r="C100" s="134" t="n"/>
@@ -3430,122 +3427,156 @@
       <c r="H100" s="134" t="n"/>
       <c r="I100" s="134" t="n"/>
       <c r="J100" s="135">
+        <f>SUM(C85:I85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="16.5" customHeight="1" s="78">
+      <c r="A101" s="108" t="n"/>
+      <c r="B101" s="104" t="inlineStr">
+        <is>
+          <t>반깁스</t>
+        </is>
+      </c>
+      <c r="C101" s="136" t="n"/>
+      <c r="D101" s="136" t="n"/>
+      <c r="E101" s="136" t="n"/>
+      <c r="F101" s="136" t="n"/>
+      <c r="G101" s="136" t="n"/>
+      <c r="H101" s="136" t="n"/>
+      <c r="I101" s="136" t="n"/>
+      <c r="J101" s="137">
+        <f>SUM(C86:I86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" ht="16.5" customHeight="1" s="78">
+      <c r="A102" s="108" t="n"/>
+      <c r="B102" s="56" t="inlineStr">
+        <is>
+          <t>깁스진단비</t>
+        </is>
+      </c>
+      <c r="C102" s="134" t="n"/>
+      <c r="D102" s="134" t="n"/>
+      <c r="E102" s="134" t="n"/>
+      <c r="F102" s="134" t="n"/>
+      <c r="G102" s="134" t="n"/>
+      <c r="H102" s="134" t="n"/>
+      <c r="I102" s="134" t="n"/>
+      <c r="J102" s="135">
         <f>SUM(C87:I87)</f>
         <v/>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="106" t="inlineStr">
-        <is>
-          <t>실손</t>
-        </is>
-      </c>
-      <c r="B101" s="104" t="inlineStr">
+    <row r="103" ht="16.5" customHeight="1" s="78">
+      <c r="A103" s="107" t="n"/>
+      <c r="B103" s="104" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="C101" s="169" t="n"/>
-      <c r="D101" s="169" t="n"/>
-      <c r="E101" s="169" t="n"/>
-      <c r="F101" s="169" t="n"/>
-      <c r="G101" s="169" t="n"/>
-      <c r="H101" s="169" t="n"/>
-      <c r="I101" s="169" t="n"/>
-      <c r="J101" s="137">
+      <c r="C103" s="169" t="n"/>
+      <c r="D103" s="169" t="n"/>
+      <c r="E103" s="169" t="n"/>
+      <c r="F103" s="169" t="n"/>
+      <c r="G103" s="169" t="n"/>
+      <c r="H103" s="169" t="n"/>
+      <c r="I103" s="169" t="n"/>
+      <c r="J103" s="137">
         <f>SUM(C88:I88)</f>
         <v/>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="107" t="n"/>
-      <c r="B102" s="59" t="inlineStr">
-        <is>
-          <t>통원</t>
-        </is>
-      </c>
-      <c r="C102" s="170" t="n"/>
-      <c r="D102" s="170" t="n"/>
-      <c r="E102" s="170" t="n"/>
-      <c r="F102" s="170" t="n"/>
-      <c r="G102" s="170" t="n"/>
-      <c r="H102" s="170" t="n"/>
-      <c r="I102" s="170" t="n"/>
-      <c r="J102" s="139">
-        <f>SUM(C89:I89)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="107" t="n"/>
-      <c r="B103" s="59" t="inlineStr">
-        <is>
-          <t>약값</t>
-        </is>
-      </c>
-      <c r="C103" s="138" t="n"/>
-      <c r="D103" s="138" t="n"/>
-      <c r="E103" s="138" t="n"/>
-      <c r="F103" s="138" t="n"/>
-      <c r="G103" s="138" t="n"/>
-      <c r="H103" s="138" t="n"/>
-      <c r="I103" s="170" t="n"/>
-      <c r="J103" s="139">
-        <f>SUM(C90:I90)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104">
+    <row r="104" ht="16.5" customHeight="1" s="78">
       <c r="A104" s="107" t="n"/>
       <c r="B104" s="59" t="inlineStr">
         <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="C104" s="170" t="n"/>
+      <c r="D104" s="170" t="n"/>
+      <c r="E104" s="170" t="n"/>
+      <c r="F104" s="170" t="n"/>
+      <c r="G104" s="170" t="n"/>
+      <c r="H104" s="170" t="n"/>
+      <c r="I104" s="170" t="n"/>
+      <c r="J104" s="139">
+        <f>SUM(C89:I89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" ht="16.5" customHeight="1" s="78">
+      <c r="A105" s="107" t="n"/>
+      <c r="B105" s="59" t="inlineStr">
+        <is>
+          <t>약값</t>
+        </is>
+      </c>
+      <c r="C105" s="138" t="n"/>
+      <c r="D105" s="138" t="n"/>
+      <c r="E105" s="138" t="n"/>
+      <c r="F105" s="138" t="n"/>
+      <c r="G105" s="138" t="n"/>
+      <c r="H105" s="138" t="n"/>
+      <c r="I105" s="170" t="n"/>
+      <c r="J105" s="139">
+        <f>SUM(C90:I90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="16.5" customHeight="1" s="78">
+      <c r="A106" s="108" t="n"/>
+      <c r="B106" s="59" t="inlineStr">
+        <is>
           <t>MRI/도수치료/비급여주사</t>
         </is>
       </c>
-      <c r="C104" s="138" t="n"/>
-      <c r="D104" s="138" t="n"/>
-      <c r="E104" s="138" t="n"/>
-      <c r="F104" s="138" t="n"/>
-      <c r="G104" s="138" t="n"/>
-      <c r="H104" s="138" t="n"/>
-      <c r="I104" s="170" t="n"/>
-      <c r="J104" s="133" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="108" t="n"/>
-      <c r="B105" s="22" t="inlineStr">
+      <c r="C106" s="138" t="n"/>
+      <c r="D106" s="138" t="n"/>
+      <c r="E106" s="138" t="n"/>
+      <c r="F106" s="138" t="n"/>
+      <c r="G106" s="138" t="n"/>
+      <c r="H106" s="138" t="n"/>
+      <c r="I106" s="170" t="n"/>
+      <c r="J106" s="133" t="n"/>
+    </row>
+    <row r="107" ht="16.5" customHeight="1" s="78">
+      <c r="A107" s="108" t="n"/>
+      <c r="B107" s="22" t="inlineStr">
         <is>
           <t>상해의료비</t>
         </is>
       </c>
-      <c r="C105" s="132" t="n"/>
-      <c r="D105" s="132" t="n"/>
-      <c r="E105" s="132" t="n"/>
-      <c r="F105" s="132" t="n"/>
-      <c r="G105" s="132" t="n"/>
-      <c r="H105" s="132" t="n"/>
-      <c r="I105" s="171" t="n"/>
-      <c r="J105" s="139" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="101" t="inlineStr">
+      <c r="C107" s="132" t="n"/>
+      <c r="D107" s="132" t="n"/>
+      <c r="E107" s="132" t="n"/>
+      <c r="F107" s="132" t="n"/>
+      <c r="G107" s="132" t="n"/>
+      <c r="H107" s="132" t="n"/>
+      <c r="I107" s="171" t="n"/>
+      <c r="J107" s="139" t="n"/>
+    </row>
+    <row r="108" ht="16.5" customHeight="1" s="78">
+      <c r="A108" s="101" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B106" s="75" t="inlineStr">
+      <c r="B108" s="75" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C106" s="172" t="n"/>
-      <c r="D106" s="172" t="n"/>
-      <c r="E106" s="172" t="n"/>
-      <c r="F106" s="172" t="n"/>
-      <c r="G106" s="172" t="n"/>
-      <c r="H106" s="172" t="n"/>
-      <c r="I106" s="172" t="n"/>
-      <c r="J106" s="173">
+      <c r="C108" s="172" t="n"/>
+      <c r="D108" s="172" t="n"/>
+      <c r="E108" s="172" t="n"/>
+      <c r="F108" s="172" t="n"/>
+      <c r="G108" s="172" t="n"/>
+      <c r="H108" s="172" t="n"/>
+      <c r="I108" s="172" t="n"/>
+      <c r="J108" s="173">
         <f>SUM(C91:I91)</f>
         <v/>
       </c>
@@ -5294,22 +5325,22 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="0" t="inlineStr">
         <is>
           <t>커버리지허용</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>라벨≠담보명 설계분</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="0" t="inlineStr">
         <is>
           <t>10억 플랜</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E80" s="0" t="inlineStr">
         <is>
           <t>담보명은 흥국 리셋월렛II — 라벨로는 자기 행 복귀 안 됨(정상)</t>
         </is>

--- a/master.xlsx
+++ b/master.xlsx
@@ -1538,7 +1538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
   <cols>
     <col width="6.5" customWidth="1" style="78" min="1" max="1"/>
@@ -2555,7 +2555,7 @@
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A54" s="109" t="inlineStr">
+      <c r="A54" s="101" t="inlineStr">
         <is>
           <t>일당</t>
         </is>
@@ -2689,7 +2689,7 @@
       <c r="A61" s="102" t="n"/>
       <c r="B61" s="31" t="inlineStr">
         <is>
-          <t>간병인질병일당(요양병원)</t>
+          <t>간병인지원일당</t>
         </is>
       </c>
       <c r="C61" s="138" t="n"/>
@@ -2705,7 +2705,7 @@
       <c r="A62" s="102" t="n"/>
       <c r="B62" s="31" t="inlineStr">
         <is>
-          <t>간병인상해일당(요양병원)</t>
+          <t>간호통합병동</t>
         </is>
       </c>
       <c r="C62" s="138" t="n"/>
@@ -2715,13 +2715,16 @@
       <c r="G62" s="138" t="n"/>
       <c r="H62" s="138" t="n"/>
       <c r="I62" s="138" t="n"/>
-      <c r="J62" s="139" t="n"/>
+      <c r="J62" s="139">
+        <f>SUM(C53:I53)</f>
+        <v/>
+      </c>
     </row>
     <row r="63" ht="16.5" customHeight="1" s="78">
       <c r="A63" s="102" t="n"/>
-      <c r="B63" s="31" t="inlineStr">
-        <is>
-          <t>간병인지원일당</t>
+      <c r="B63" s="65" t="inlineStr">
+        <is>
+          <t>1인실 종합병원</t>
         </is>
       </c>
       <c r="C63" s="138" t="n"/>
@@ -2731,13 +2734,16 @@
       <c r="G63" s="138" t="n"/>
       <c r="H63" s="138" t="n"/>
       <c r="I63" s="138" t="n"/>
-      <c r="J63" s="139" t="n"/>
+      <c r="J63" s="139">
+        <f>SUM(C54:I54)</f>
+        <v/>
+      </c>
     </row>
     <row r="64" ht="17.25" customHeight="1" s="78">
       <c r="A64" s="102" t="n"/>
-      <c r="B64" s="31" t="inlineStr">
-        <is>
-          <t>간호통합병동</t>
+      <c r="B64" s="65" t="inlineStr">
+        <is>
+          <t>1인실 상급병원</t>
         </is>
       </c>
       <c r="C64" s="138" t="n"/>
@@ -2748,15 +2754,15 @@
       <c r="H64" s="138" t="n"/>
       <c r="I64" s="138" t="n"/>
       <c r="J64" s="139">
-        <f>SUM(C53:I53)</f>
+        <f>SUM(C55:I55)</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="17.25" customHeight="1" s="78">
       <c r="A65" s="102" t="n"/>
-      <c r="B65" s="65" t="inlineStr">
-        <is>
-          <t>1인실 종합병원</t>
+      <c r="B65" s="31" t="inlineStr">
+        <is>
+          <t>질병중환자실</t>
         </is>
       </c>
       <c r="C65" s="138" t="n"/>
@@ -2767,110 +2773,112 @@
       <c r="H65" s="138" t="n"/>
       <c r="I65" s="138" t="n"/>
       <c r="J65" s="139">
-        <f>SUM(C54:I54)</f>
+        <f>SUM(C56:I56)</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A66" s="102" t="n"/>
-      <c r="B66" s="65" t="inlineStr">
-        <is>
-          <t>1인실 상급병원</t>
-        </is>
-      </c>
-      <c r="C66" s="138" t="n"/>
-      <c r="D66" s="138" t="n"/>
-      <c r="E66" s="138" t="n"/>
-      <c r="F66" s="138" t="n"/>
-      <c r="G66" s="138" t="n"/>
-      <c r="H66" s="138" t="n"/>
-      <c r="I66" s="138" t="n"/>
-      <c r="J66" s="139">
-        <f>SUM(C55:I55)</f>
+      <c r="A66" s="103" t="n"/>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>상해중환자실</t>
+        </is>
+      </c>
+      <c r="C66" s="134" t="n"/>
+      <c r="D66" s="134" t="n"/>
+      <c r="E66" s="134" t="n"/>
+      <c r="F66" s="134" t="n"/>
+      <c r="G66" s="134" t="n"/>
+      <c r="H66" s="134" t="n"/>
+      <c r="I66" s="134" t="n"/>
+      <c r="J66" s="135">
+        <f>SUM(C57:I57)</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" s="78">
-      <c r="A67" s="103" t="n"/>
-      <c r="B67" s="31" t="inlineStr">
-        <is>
-          <t>질병중환자실</t>
-        </is>
-      </c>
-      <c r="C67" s="138" t="n"/>
-      <c r="D67" s="138" t="n"/>
-      <c r="E67" s="138" t="n"/>
-      <c r="F67" s="138" t="n"/>
-      <c r="G67" s="138" t="n"/>
-      <c r="H67" s="138" t="n"/>
-      <c r="I67" s="138" t="n"/>
-      <c r="J67" s="139">
-        <f>SUM(C56:I56)</f>
+      <c r="A67" s="101" t="inlineStr">
+        <is>
+          <t>수술</t>
+        </is>
+      </c>
+      <c r="B67" s="104" t="inlineStr">
+        <is>
+          <t>상해수술비</t>
+        </is>
+      </c>
+      <c r="C67" s="136" t="n"/>
+      <c r="D67" s="136" t="n"/>
+      <c r="E67" s="136" t="n"/>
+      <c r="F67" s="136" t="n"/>
+      <c r="G67" s="136" t="n"/>
+      <c r="H67" s="136" t="n"/>
+      <c r="I67" s="136" t="n"/>
+      <c r="J67" s="137">
+        <f>SUM(C58:I58)</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="16.5" customHeight="1" s="78">
-      <c r="A68" s="103" t="n"/>
-      <c r="B68" s="25" t="inlineStr">
-        <is>
-          <t>상해중환자실</t>
-        </is>
-      </c>
-      <c r="C68" s="134" t="n"/>
-      <c r="D68" s="134" t="n"/>
-      <c r="E68" s="134" t="n"/>
-      <c r="F68" s="134" t="n"/>
-      <c r="G68" s="134" t="n"/>
-      <c r="H68" s="134" t="n"/>
-      <c r="I68" s="134" t="n"/>
-      <c r="J68" s="135">
-        <f>SUM(C57:I57)</f>
+      <c r="A68" s="102" t="n"/>
+      <c r="B68" s="64" t="inlineStr">
+        <is>
+          <t>중대한상해수술비</t>
+        </is>
+      </c>
+      <c r="C68" s="159" t="n"/>
+      <c r="D68" s="159" t="n"/>
+      <c r="E68" s="159" t="n"/>
+      <c r="F68" s="159" t="n"/>
+      <c r="G68" s="159" t="n"/>
+      <c r="H68" s="159" t="n"/>
+      <c r="I68" s="159" t="n"/>
+      <c r="J68" s="139">
+        <f>SUM(C59:I59)</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" s="78">
       <c r="A69" s="102" t="n"/>
-      <c r="B69" s="104" t="inlineStr">
-        <is>
-          <t>상해수술비</t>
-        </is>
-      </c>
-      <c r="C69" s="136" t="n"/>
-      <c r="D69" s="136" t="n"/>
-      <c r="E69" s="136" t="n"/>
-      <c r="F69" s="136" t="n"/>
-      <c r="G69" s="136" t="n"/>
-      <c r="H69" s="136" t="n"/>
-      <c r="I69" s="136" t="n"/>
-      <c r="J69" s="137">
-        <f>SUM(C58:I58)</f>
-        <v/>
-      </c>
+      <c r="B69" s="59" t="inlineStr">
+        <is>
+          <t>상해 종수술비(1-3종)</t>
+        </is>
+      </c>
+      <c r="C69" s="159" t="n"/>
+      <c r="D69" s="159" t="n"/>
+      <c r="E69" s="159" t="n"/>
+      <c r="F69" s="160" t="n"/>
+      <c r="G69" s="159" t="n"/>
+      <c r="H69" s="159" t="n"/>
+      <c r="I69" s="159" t="n"/>
+      <c r="J69" s="139" t="n"/>
     </row>
     <row r="70" ht="17.25" customHeight="1" s="78">
       <c r="A70" s="102" t="n"/>
-      <c r="B70" s="64" t="inlineStr">
-        <is>
-          <t>중대한상해수술비</t>
+      <c r="B70" s="59" t="inlineStr">
+        <is>
+          <t>상해 종수술비(1-5종)</t>
         </is>
       </c>
       <c r="C70" s="159" t="n"/>
       <c r="D70" s="159" t="n"/>
       <c r="E70" s="159" t="n"/>
-      <c r="F70" s="159" t="n"/>
+      <c r="F70" s="160" t="n"/>
       <c r="G70" s="159" t="n"/>
       <c r="H70" s="159" t="n"/>
       <c r="I70" s="159" t="n"/>
-      <c r="J70" s="139">
-        <f>SUM(C59:I59)</f>
-        <v/>
+      <c r="J70" s="139" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" s="78">
       <c r="A71" s="102" t="n"/>
       <c r="B71" s="59" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-3종)</t>
+          <t>상해 종수술비(1-8종)</t>
         </is>
       </c>
       <c r="C71" s="159" t="n"/>
@@ -2886,43 +2894,45 @@
       <c r="A72" s="102" t="n"/>
       <c r="B72" s="59" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-5종)</t>
-        </is>
-      </c>
-      <c r="C72" s="159" t="n"/>
-      <c r="D72" s="159" t="n"/>
-      <c r="E72" s="159" t="n"/>
-      <c r="F72" s="160" t="n"/>
-      <c r="G72" s="159" t="n"/>
-      <c r="H72" s="159" t="n"/>
-      <c r="I72" s="159" t="n"/>
-      <c r="J72" s="139" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+          <t>창상봉합술</t>
+        </is>
+      </c>
+      <c r="C72" s="138" t="n"/>
+      <c r="D72" s="138" t="n"/>
+      <c r="E72" s="138" t="n"/>
+      <c r="F72" s="161" t="n"/>
+      <c r="G72" s="138" t="n"/>
+      <c r="H72" s="138" t="n"/>
+      <c r="I72" s="138" t="n"/>
+      <c r="J72" s="139">
+        <f>SUM(C61:I61)</f>
+        <v/>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" s="78">
       <c r="A73" s="102" t="n"/>
       <c r="B73" s="59" t="inlineStr">
         <is>
-          <t>상해 종수술비(1-8종)</t>
-        </is>
-      </c>
-      <c r="C73" s="159" t="n"/>
-      <c r="D73" s="159" t="n"/>
-      <c r="E73" s="159" t="n"/>
-      <c r="F73" s="160" t="n"/>
-      <c r="G73" s="159" t="n"/>
-      <c r="H73" s="159" t="n"/>
-      <c r="I73" s="159" t="n"/>
-      <c r="J73" s="139" t="n"/>
+          <t>골절수술비</t>
+        </is>
+      </c>
+      <c r="C73" s="138" t="n"/>
+      <c r="D73" s="138" t="n"/>
+      <c r="E73" s="138" t="n"/>
+      <c r="F73" s="161" t="n"/>
+      <c r="G73" s="138" t="n"/>
+      <c r="H73" s="138" t="n"/>
+      <c r="I73" s="138" t="n"/>
+      <c r="J73" s="139">
+        <f>SUM(C62:I62)</f>
+        <v/>
+      </c>
     </row>
     <row r="74" ht="16.5" customHeight="1" s="78">
       <c r="A74" s="102" t="n"/>
-      <c r="B74" s="59" t="inlineStr">
-        <is>
-          <t>창상봉합술</t>
+      <c r="B74" s="66" t="inlineStr">
+        <is>
+          <t>5대골절수술비</t>
         </is>
       </c>
       <c r="C74" s="138" t="n"/>
@@ -2933,91 +2943,89 @@
       <c r="H74" s="138" t="n"/>
       <c r="I74" s="138" t="n"/>
       <c r="J74" s="139">
-        <f>SUM(C61:I61)</f>
+        <f>SUM(C63:I63)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="16.5" customHeight="1" s="78" thickBot="1">
       <c r="A75" s="102" t="n"/>
-      <c r="B75" s="59" t="inlineStr">
-        <is>
-          <t>골절수술비</t>
-        </is>
-      </c>
-      <c r="C75" s="138" t="n"/>
-      <c r="D75" s="138" t="n"/>
-      <c r="E75" s="138" t="n"/>
-      <c r="F75" s="161" t="n"/>
-      <c r="G75" s="138" t="n"/>
-      <c r="H75" s="138" t="n"/>
-      <c r="I75" s="138" t="n"/>
-      <c r="J75" s="139">
-        <f>SUM(C62:I62)</f>
+      <c r="B75" s="56" t="inlineStr">
+        <is>
+          <t>화상수술비</t>
+        </is>
+      </c>
+      <c r="C75" s="134" t="n"/>
+      <c r="D75" s="134" t="n"/>
+      <c r="E75" s="134" t="n"/>
+      <c r="F75" s="162" t="n"/>
+      <c r="G75" s="134" t="n"/>
+      <c r="H75" s="134" t="n"/>
+      <c r="I75" s="134" t="n"/>
+      <c r="J75" s="135">
+        <f>SUM(C64:I64)</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="16.5" customHeight="1" s="78">
       <c r="A76" s="102" t="n"/>
-      <c r="B76" s="66" t="inlineStr">
-        <is>
-          <t>5대골절수술비</t>
-        </is>
-      </c>
-      <c r="C76" s="138" t="n"/>
-      <c r="D76" s="138" t="n"/>
-      <c r="E76" s="138" t="n"/>
-      <c r="F76" s="161" t="n"/>
-      <c r="G76" s="138" t="n"/>
-      <c r="H76" s="138" t="n"/>
-      <c r="I76" s="138" t="n"/>
-      <c r="J76" s="139">
-        <f>SUM(C63:I63)</f>
+      <c r="B76" s="64" t="inlineStr">
+        <is>
+          <t>질병수술비</t>
+        </is>
+      </c>
+      <c r="C76" s="159" t="n"/>
+      <c r="D76" s="159" t="n"/>
+      <c r="E76" s="159" t="n"/>
+      <c r="F76" s="163" t="n"/>
+      <c r="G76" s="159" t="n"/>
+      <c r="H76" s="159" t="n"/>
+      <c r="I76" s="164" t="n"/>
+      <c r="J76" s="133">
+        <f>SUM(C65:I65)</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="16.5" customHeight="1" s="78">
       <c r="A77" s="102" t="n"/>
-      <c r="B77" s="56" t="inlineStr">
-        <is>
-          <t>화상수술비</t>
-        </is>
-      </c>
-      <c r="C77" s="134" t="n"/>
-      <c r="D77" s="134" t="n"/>
-      <c r="E77" s="134" t="n"/>
-      <c r="F77" s="162" t="n"/>
-      <c r="G77" s="134" t="n"/>
-      <c r="H77" s="134" t="n"/>
-      <c r="I77" s="134" t="n"/>
-      <c r="J77" s="135">
-        <f>SUM(C64:I64)</f>
-        <v/>
-      </c>
+      <c r="B77" s="59" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-3종)</t>
+        </is>
+      </c>
+      <c r="C77" s="138" t="n"/>
+      <c r="D77" s="138" t="n"/>
+      <c r="E77" s="138" t="n"/>
+      <c r="F77" s="165" t="n"/>
+      <c r="G77" s="138" t="n"/>
+      <c r="H77" s="138" t="n"/>
+      <c r="I77" s="138" t="n"/>
+      <c r="J77" s="139" t="n"/>
     </row>
     <row r="78" ht="17.25" customHeight="1" s="78">
       <c r="A78" s="102" t="n"/>
-      <c r="B78" s="64" t="inlineStr">
-        <is>
-          <t>질병수술비</t>
-        </is>
-      </c>
-      <c r="C78" s="159" t="n"/>
-      <c r="D78" s="159" t="n"/>
-      <c r="E78" s="159" t="n"/>
-      <c r="F78" s="163" t="n"/>
-      <c r="G78" s="159" t="n"/>
-      <c r="H78" s="159" t="n"/>
-      <c r="I78" s="164" t="n"/>
-      <c r="J78" s="133">
-        <f>SUM(C65:I65)</f>
-        <v/>
+      <c r="B78" s="59" t="inlineStr">
+        <is>
+          <t>질병 종수술비(1-5종)</t>
+        </is>
+      </c>
+      <c r="C78" s="138" t="n"/>
+      <c r="D78" s="138" t="n"/>
+      <c r="E78" s="138" t="n"/>
+      <c r="F78" s="165" t="n"/>
+      <c r="G78" s="138" t="n"/>
+      <c r="H78" s="138" t="n"/>
+      <c r="I78" s="138" t="n"/>
+      <c r="J78" s="139" t="inlineStr">
+        <is>
+          <t>/ / / / /</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="16.5" customHeight="1" s="78">
       <c r="A79" s="102" t="n"/>
       <c r="B79" s="59" t="inlineStr">
         <is>
-          <t>질병 종수술비(1-3종)</t>
+          <t>질병 종수술비(1-8종)</t>
         </is>
       </c>
       <c r="C79" s="138" t="n"/>
@@ -3031,45 +3039,47 @@
     </row>
     <row r="80" ht="16.5" customHeight="1" s="78">
       <c r="A80" s="102" t="n"/>
-      <c r="B80" s="59" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-5종)</t>
-        </is>
-      </c>
-      <c r="C80" s="138" t="n"/>
-      <c r="D80" s="138" t="n"/>
-      <c r="E80" s="138" t="n"/>
-      <c r="F80" s="165" t="n"/>
-      <c r="G80" s="138" t="n"/>
-      <c r="H80" s="138" t="n"/>
-      <c r="I80" s="138" t="n"/>
-      <c r="J80" s="139" t="inlineStr">
-        <is>
-          <t>/ / / / /</t>
-        </is>
+      <c r="B80" s="68" t="inlineStr">
+        <is>
+          <t>뇌혈관수술비</t>
+        </is>
+      </c>
+      <c r="C80" s="166" t="n"/>
+      <c r="D80" s="166" t="n"/>
+      <c r="E80" s="166" t="n"/>
+      <c r="F80" s="166" t="n"/>
+      <c r="G80" s="166" t="n"/>
+      <c r="H80" s="166" t="n"/>
+      <c r="I80" s="166" t="n"/>
+      <c r="J80" s="139">
+        <f>SUM(C67:I67)</f>
+        <v/>
       </c>
     </row>
     <row r="81" ht="17.25" customHeight="1" s="78">
       <c r="A81" s="102" t="n"/>
-      <c r="B81" s="59" t="inlineStr">
-        <is>
-          <t>질병 종수술비(1-8종)</t>
-        </is>
-      </c>
-      <c r="C81" s="138" t="n"/>
-      <c r="D81" s="138" t="n"/>
-      <c r="E81" s="138" t="n"/>
-      <c r="F81" s="165" t="n"/>
-      <c r="G81" s="138" t="n"/>
-      <c r="H81" s="138" t="n"/>
-      <c r="I81" s="138" t="n"/>
-      <c r="J81" s="139" t="n"/>
+      <c r="B81" s="68" t="inlineStr">
+        <is>
+          <t>허혈성수술비</t>
+        </is>
+      </c>
+      <c r="C81" s="166" t="n"/>
+      <c r="D81" s="166" t="n"/>
+      <c r="E81" s="166" t="n"/>
+      <c r="F81" s="166" t="n"/>
+      <c r="G81" s="166" t="n"/>
+      <c r="H81" s="166" t="n"/>
+      <c r="I81" s="166" t="n"/>
+      <c r="J81" s="139">
+        <f>SUM(C68:I68)</f>
+        <v/>
+      </c>
     </row>
     <row r="82" ht="17.25" customHeight="1" s="78">
       <c r="A82" s="102" t="n"/>
       <c r="B82" s="68" t="inlineStr">
         <is>
-          <t>뇌혈관수술비</t>
+          <t>심장수술비</t>
         </is>
       </c>
       <c r="C82" s="166" t="n"/>
@@ -3080,15 +3090,15 @@
       <c r="H82" s="166" t="n"/>
       <c r="I82" s="166" t="n"/>
       <c r="J82" s="139">
-        <f>SUM(C67:I67)</f>
+        <f>SUM(C69:I69)</f>
         <v/>
       </c>
     </row>
     <row r="83" ht="17.25" customHeight="1" s="78" thickBot="1">
       <c r="A83" s="102" t="n"/>
-      <c r="B83" s="68" t="inlineStr">
-        <is>
-          <t>허혈성수술비</t>
+      <c r="B83" s="60" t="inlineStr">
+        <is>
+          <t>n대수술비</t>
         </is>
       </c>
       <c r="C83" s="166" t="n"/>
@@ -3098,111 +3108,115 @@
       <c r="G83" s="166" t="n"/>
       <c r="H83" s="166" t="n"/>
       <c r="I83" s="166" t="n"/>
-      <c r="J83" s="139">
-        <f>SUM(C68:I68)</f>
+      <c r="J83" s="167">
+        <f>SUM(C70:I70)</f>
         <v/>
       </c>
     </row>
     <row r="84" ht="16.5" customHeight="1" s="78">
       <c r="A84" s="102" t="n"/>
-      <c r="B84" s="68" t="inlineStr">
-        <is>
-          <t>심장수술비</t>
-        </is>
-      </c>
-      <c r="C84" s="166" t="n"/>
-      <c r="D84" s="166" t="n"/>
-      <c r="E84" s="166" t="n"/>
-      <c r="F84" s="166" t="n"/>
-      <c r="G84" s="166" t="n"/>
-      <c r="H84" s="166" t="n"/>
-      <c r="I84" s="166" t="n"/>
-      <c r="J84" s="139">
-        <f>SUM(C69:I69)</f>
+      <c r="B84" s="69" t="inlineStr">
+        <is>
+          <t>5대기관 수술비 관혈</t>
+        </is>
+      </c>
+      <c r="C84" s="140" t="n"/>
+      <c r="D84" s="140" t="n"/>
+      <c r="E84" s="140" t="n"/>
+      <c r="F84" s="140" t="n"/>
+      <c r="G84" s="140" t="n"/>
+      <c r="H84" s="140" t="n"/>
+      <c r="I84" s="140" t="n"/>
+      <c r="J84" s="137">
+        <f>SUM(C71:I71)</f>
         <v/>
       </c>
     </row>
     <row r="85" ht="17.25" customHeight="1" s="78" thickBot="1">
-      <c r="A85" s="102" t="n"/>
-      <c r="B85" s="60" t="inlineStr">
-        <is>
-          <t>n대수술비</t>
-        </is>
-      </c>
-      <c r="C85" s="166" t="n"/>
-      <c r="D85" s="166" t="n"/>
-      <c r="E85" s="166" t="n"/>
-      <c r="F85" s="166" t="n"/>
-      <c r="G85" s="166" t="n"/>
-      <c r="H85" s="166" t="n"/>
-      <c r="I85" s="166" t="n"/>
-      <c r="J85" s="167">
-        <f>SUM(C70:I70)</f>
+      <c r="A85" s="103" t="n"/>
+      <c r="B85" s="70" t="inlineStr">
+        <is>
+          <t>5대기관 수술비 비관혈</t>
+        </is>
+      </c>
+      <c r="C85" s="134" t="n"/>
+      <c r="D85" s="134" t="n"/>
+      <c r="E85" s="134" t="n"/>
+      <c r="F85" s="134" t="n"/>
+      <c r="G85" s="134" t="n"/>
+      <c r="H85" s="134" t="n"/>
+      <c r="I85" s="134" t="n"/>
+      <c r="J85" s="135">
+        <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
     <row r="86" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A86" s="103" t="n"/>
-      <c r="B86" s="69" t="inlineStr">
-        <is>
-          <t>5대기관 수술비 관혈</t>
-        </is>
-      </c>
-      <c r="C86" s="140" t="n"/>
-      <c r="D86" s="140" t="n"/>
-      <c r="E86" s="140" t="n"/>
-      <c r="F86" s="140" t="n"/>
-      <c r="G86" s="140" t="n"/>
-      <c r="H86" s="140" t="n"/>
-      <c r="I86" s="140" t="n"/>
+      <c r="A86" s="101" t="inlineStr">
+        <is>
+          <t>운전</t>
+        </is>
+      </c>
+      <c r="B86" s="28" t="inlineStr">
+        <is>
+          <t>대인</t>
+        </is>
+      </c>
+      <c r="C86" s="119" t="n"/>
+      <c r="D86" s="119" t="n"/>
+      <c r="E86" s="119" t="n"/>
+      <c r="F86" s="119" t="n"/>
+      <c r="G86" s="119" t="n"/>
+      <c r="H86" s="119" t="n"/>
+      <c r="I86" s="119" t="n"/>
       <c r="J86" s="137">
-        <f>SUM(C71:I71)</f>
+        <f>SUM(C73:I73)</f>
         <v/>
       </c>
     </row>
     <row r="87" ht="17.25" customHeight="1" s="78">
-      <c r="A87" s="103" t="n"/>
-      <c r="B87" s="70" t="inlineStr">
-        <is>
-          <t>5대기관 수술비 비관혈</t>
-        </is>
-      </c>
-      <c r="C87" s="134" t="n"/>
-      <c r="D87" s="134" t="n"/>
-      <c r="E87" s="134" t="n"/>
-      <c r="F87" s="134" t="n"/>
-      <c r="G87" s="134" t="n"/>
-      <c r="H87" s="134" t="n"/>
-      <c r="I87" s="134" t="n"/>
-      <c r="J87" s="135">
-        <f>SUM(C72:I72)</f>
+      <c r="A87" s="102" t="n"/>
+      <c r="B87" s="31" t="inlineStr">
+        <is>
+          <t>대물</t>
+        </is>
+      </c>
+      <c r="C87" s="149" t="n"/>
+      <c r="D87" s="149" t="n"/>
+      <c r="E87" s="149" t="n"/>
+      <c r="F87" s="149" t="n"/>
+      <c r="G87" s="149" t="n"/>
+      <c r="H87" s="149" t="n"/>
+      <c r="I87" s="149" t="n"/>
+      <c r="J87" s="139">
+        <f>SUM(C74:I74)</f>
         <v/>
       </c>
     </row>
     <row r="88" ht="16.5" customHeight="1" s="78">
       <c r="A88" s="102" t="n"/>
-      <c r="B88" s="28" t="inlineStr">
-        <is>
-          <t>대인</t>
-        </is>
-      </c>
-      <c r="C88" s="119" t="n"/>
-      <c r="D88" s="119" t="n"/>
-      <c r="E88" s="119" t="n"/>
-      <c r="F88" s="119" t="n"/>
-      <c r="G88" s="119" t="n"/>
-      <c r="H88" s="119" t="n"/>
-      <c r="I88" s="119" t="n"/>
-      <c r="J88" s="137">
-        <f>SUM(C73:I73)</f>
+      <c r="B88" s="31" t="inlineStr">
+        <is>
+          <t>합의금</t>
+        </is>
+      </c>
+      <c r="C88" s="149" t="n"/>
+      <c r="D88" s="149" t="n"/>
+      <c r="E88" s="149" t="n"/>
+      <c r="F88" s="149" t="n"/>
+      <c r="G88" s="149" t="n"/>
+      <c r="H88" s="149" t="n"/>
+      <c r="I88" s="149" t="n"/>
+      <c r="J88" s="139">
+        <f>SUM(C75:I75)</f>
         <v/>
       </c>
     </row>
     <row r="89" ht="16.5" customHeight="1" s="78">
       <c r="A89" s="102" t="n"/>
-      <c r="B89" s="31" t="inlineStr">
-        <is>
-          <t>대물</t>
+      <c r="B89" s="65" t="inlineStr">
+        <is>
+          <t>6주미만</t>
         </is>
       </c>
       <c r="C89" s="149" t="n"/>
@@ -3213,7 +3227,7 @@
       <c r="H89" s="149" t="n"/>
       <c r="I89" s="149" t="n"/>
       <c r="J89" s="139">
-        <f>SUM(C74:I74)</f>
+        <f>SUM(C76:I76)</f>
         <v/>
       </c>
     </row>
@@ -3221,7 +3235,7 @@
       <c r="A90" s="102" t="n"/>
       <c r="B90" s="31" t="inlineStr">
         <is>
-          <t>합의금</t>
+          <t>변호사</t>
         </is>
       </c>
       <c r="C90" s="149" t="n"/>
@@ -3232,172 +3246,184 @@
       <c r="H90" s="149" t="n"/>
       <c r="I90" s="149" t="n"/>
       <c r="J90" s="139">
-        <f>SUM(C75:I75)</f>
+        <f>SUM(C77:I77)</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="17.25" customHeight="1" s="78">
-      <c r="A91" s="102" t="n"/>
-      <c r="B91" s="65" t="inlineStr">
-        <is>
-          <t>6주미만</t>
-        </is>
-      </c>
-      <c r="C91" s="149" t="n"/>
-      <c r="D91" s="149" t="n"/>
-      <c r="E91" s="149" t="n"/>
-      <c r="F91" s="149" t="n"/>
-      <c r="G91" s="149" t="n"/>
-      <c r="H91" s="149" t="n"/>
-      <c r="I91" s="149" t="n"/>
-      <c r="J91" s="139">
-        <f>SUM(C76:I76)</f>
+      <c r="A91" s="103" t="n"/>
+      <c r="B91" s="25" t="inlineStr">
+        <is>
+          <t>자부상</t>
+        </is>
+      </c>
+      <c r="C91" s="168" t="n"/>
+      <c r="D91" s="168" t="n"/>
+      <c r="E91" s="168" t="n"/>
+      <c r="F91" s="168" t="n"/>
+      <c r="G91" s="168" t="n"/>
+      <c r="H91" s="168" t="n"/>
+      <c r="I91" s="168" t="n"/>
+      <c r="J91" s="135">
+        <f>SUM(C78:I78)</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="16.5" customHeight="1" s="78">
-      <c r="A92" s="103" t="n"/>
-      <c r="B92" s="31" t="inlineStr">
-        <is>
-          <t>변호사</t>
-        </is>
-      </c>
-      <c r="C92" s="149" t="n"/>
-      <c r="D92" s="149" t="n"/>
-      <c r="E92" s="149" t="n"/>
-      <c r="F92" s="149" t="n"/>
-      <c r="G92" s="149" t="n"/>
-      <c r="H92" s="149" t="n"/>
-      <c r="I92" s="149" t="n"/>
-      <c r="J92" s="139">
-        <f>SUM(C77:I77)</f>
+      <c r="A92" s="101" t="inlineStr">
+        <is>
+          <t>골절</t>
+        </is>
+      </c>
+      <c r="B92" s="64" t="inlineStr">
+        <is>
+          <t>골절(치아파절포함)</t>
+        </is>
+      </c>
+      <c r="C92" s="159" t="n"/>
+      <c r="D92" s="159" t="n"/>
+      <c r="E92" s="159" t="n"/>
+      <c r="F92" s="159" t="n"/>
+      <c r="G92" s="159" t="n"/>
+      <c r="H92" s="159" t="n"/>
+      <c r="I92" s="159" t="n"/>
+      <c r="J92" s="133">
+        <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="16.5" customHeight="1" s="78">
-      <c r="A93" s="108" t="n"/>
-      <c r="B93" s="25" t="inlineStr">
-        <is>
-          <t>자부상</t>
-        </is>
-      </c>
-      <c r="C93" s="168" t="n"/>
-      <c r="D93" s="168" t="n"/>
-      <c r="E93" s="168" t="n"/>
-      <c r="F93" s="168" t="n"/>
-      <c r="G93" s="168" t="n"/>
-      <c r="H93" s="168" t="n"/>
-      <c r="I93" s="168" t="n"/>
-      <c r="J93" s="135">
-        <f>SUM(C78:I78)</f>
+      <c r="A93" s="102" t="n"/>
+      <c r="B93" s="59" t="inlineStr">
+        <is>
+          <t>골절(치아파절제외)</t>
+        </is>
+      </c>
+      <c r="C93" s="138" t="n"/>
+      <c r="D93" s="138" t="n"/>
+      <c r="E93" s="138" t="n"/>
+      <c r="F93" s="138" t="n"/>
+      <c r="G93" s="138" t="n"/>
+      <c r="H93" s="138" t="n"/>
+      <c r="I93" s="138" t="n"/>
+      <c r="J93" s="139">
+        <f>SUM(C80:I80)</f>
         <v/>
       </c>
     </row>
     <row r="94" ht="16.5" customHeight="1" s="78">
-      <c r="A94" s="107" t="n"/>
-      <c r="B94" s="64" t="inlineStr">
-        <is>
-          <t>골절(치아파절포함)</t>
-        </is>
-      </c>
-      <c r="C94" s="159" t="n"/>
-      <c r="D94" s="159" t="n"/>
-      <c r="E94" s="159" t="n"/>
-      <c r="F94" s="159" t="n"/>
-      <c r="G94" s="159" t="n"/>
-      <c r="H94" s="159" t="n"/>
-      <c r="I94" s="159" t="n"/>
-      <c r="J94" s="133">
-        <f>SUM(C79:I79)</f>
+      <c r="A94" s="103" t="n"/>
+      <c r="B94" s="70" t="inlineStr">
+        <is>
+          <t>5대골절진단비</t>
+        </is>
+      </c>
+      <c r="C94" s="134" t="n"/>
+      <c r="D94" s="134" t="n"/>
+      <c r="E94" s="134" t="n"/>
+      <c r="F94" s="134" t="n"/>
+      <c r="G94" s="134" t="n"/>
+      <c r="H94" s="134" t="n"/>
+      <c r="I94" s="134" t="n"/>
+      <c r="J94" s="135">
+        <f>SUM(C81:I81)</f>
         <v/>
       </c>
     </row>
     <row r="95" ht="16.5" customHeight="1" s="78">
-      <c r="A95" s="108" t="n"/>
-      <c r="B95" s="59" t="inlineStr">
-        <is>
-          <t>골절(치아파절제외)</t>
-        </is>
-      </c>
-      <c r="C95" s="138" t="n"/>
-      <c r="D95" s="138" t="n"/>
-      <c r="E95" s="138" t="n"/>
-      <c r="F95" s="138" t="n"/>
-      <c r="G95" s="138" t="n"/>
-      <c r="H95" s="138" t="n"/>
-      <c r="I95" s="138" t="n"/>
-      <c r="J95" s="139">
-        <f>SUM(C80:I80)</f>
+      <c r="A95" s="101" t="inlineStr">
+        <is>
+          <t>응급실</t>
+        </is>
+      </c>
+      <c r="B95" s="63" t="inlineStr">
+        <is>
+          <t>응급실(응급)</t>
+        </is>
+      </c>
+      <c r="C95" s="130" t="n"/>
+      <c r="D95" s="130" t="n"/>
+      <c r="E95" s="130" t="n"/>
+      <c r="F95" s="130" t="n"/>
+      <c r="G95" s="130" t="n"/>
+      <c r="H95" s="130" t="n"/>
+      <c r="I95" s="130" t="n"/>
+      <c r="J95" s="131">
+        <f>SUM(C82:I82)</f>
         <v/>
       </c>
     </row>
     <row r="96" ht="16.5" customHeight="1" s="78">
-      <c r="A96" s="108" t="n"/>
-      <c r="B96" s="70" t="inlineStr">
-        <is>
-          <t>5대골절진단비</t>
-        </is>
-      </c>
-      <c r="C96" s="134" t="n"/>
-      <c r="D96" s="134" t="n"/>
-      <c r="E96" s="134" t="n"/>
-      <c r="F96" s="134" t="n"/>
-      <c r="G96" s="134" t="n"/>
-      <c r="H96" s="134" t="n"/>
-      <c r="I96" s="134" t="n"/>
-      <c r="J96" s="135">
-        <f>SUM(C81:I81)</f>
-        <v/>
-      </c>
+      <c r="A96" s="101" t="inlineStr">
+        <is>
+          <t>독감</t>
+        </is>
+      </c>
+      <c r="B96" s="34" t="inlineStr">
+        <is>
+          <t>독감</t>
+        </is>
+      </c>
+      <c r="C96" s="140" t="n"/>
+      <c r="D96" s="140" t="n"/>
+      <c r="E96" s="140" t="n"/>
+      <c r="F96" s="140" t="n"/>
+      <c r="G96" s="140" t="n"/>
+      <c r="H96" s="140" t="n"/>
+      <c r="I96" s="140" t="n"/>
+      <c r="J96" s="141" t="n"/>
     </row>
     <row r="97" ht="16.5" customHeight="1" s="78">
-      <c r="A97" s="109" t="inlineStr">
-        <is>
-          <t>응급실</t>
-        </is>
-      </c>
-      <c r="B97" s="63" t="inlineStr">
-        <is>
-          <t>응급실(응급)</t>
-        </is>
-      </c>
-      <c r="C97" s="130" t="n"/>
-      <c r="D97" s="130" t="n"/>
-      <c r="E97" s="130" t="n"/>
-      <c r="F97" s="130" t="n"/>
-      <c r="G97" s="130" t="n"/>
-      <c r="H97" s="130" t="n"/>
-      <c r="I97" s="130" t="n"/>
-      <c r="J97" s="131">
-        <f>SUM(C82:I82)</f>
+      <c r="A97" s="101" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B97" s="28" t="inlineStr">
+        <is>
+          <t>화상진단비</t>
+        </is>
+      </c>
+      <c r="C97" s="136" t="n"/>
+      <c r="D97" s="136" t="n"/>
+      <c r="E97" s="136" t="n"/>
+      <c r="F97" s="136" t="n"/>
+      <c r="G97" s="136" t="n"/>
+      <c r="H97" s="136" t="n"/>
+      <c r="I97" s="136" t="n"/>
+      <c r="J97" s="137">
+        <f>SUM(C84:I84)</f>
         <v/>
       </c>
     </row>
     <row r="98" ht="16.5" customHeight="1" s="78">
-      <c r="A98" s="101" t="inlineStr">
-        <is>
-          <t>독감</t>
-        </is>
-      </c>
-      <c r="B98" s="34" t="inlineStr">
-        <is>
-          <t>독감</t>
-        </is>
-      </c>
-      <c r="C98" s="140" t="n"/>
-      <c r="D98" s="140" t="n"/>
-      <c r="E98" s="140" t="n"/>
-      <c r="F98" s="140" t="n"/>
-      <c r="G98" s="140" t="n"/>
-      <c r="H98" s="140" t="n"/>
-      <c r="I98" s="140" t="n"/>
-      <c r="J98" s="141" t="n"/>
+      <c r="A98" s="103" t="n"/>
+      <c r="B98" s="25" t="inlineStr">
+        <is>
+          <t>중증화상진단비</t>
+        </is>
+      </c>
+      <c r="C98" s="134" t="n"/>
+      <c r="D98" s="134" t="n"/>
+      <c r="E98" s="134" t="n"/>
+      <c r="F98" s="134" t="n"/>
+      <c r="G98" s="134" t="n"/>
+      <c r="H98" s="134" t="n"/>
+      <c r="I98" s="134" t="n"/>
+      <c r="J98" s="135">
+        <f>SUM(C85:I85)</f>
+        <v/>
+      </c>
     </row>
     <row r="99" ht="16.5" customHeight="1" s="78">
-      <c r="A99" s="103" t="n"/>
-      <c r="B99" s="28" t="inlineStr">
-        <is>
-          <t>화상진단비</t>
+      <c r="A99" s="101" t="inlineStr">
+        <is>
+          <t>깁스</t>
+        </is>
+      </c>
+      <c r="B99" s="104" t="inlineStr">
+        <is>
+          <t>반깁스</t>
         </is>
       </c>
       <c r="C99" s="136" t="n"/>
@@ -3408,15 +3434,15 @@
       <c r="H99" s="136" t="n"/>
       <c r="I99" s="136" t="n"/>
       <c r="J99" s="137">
-        <f>SUM(C84:I84)</f>
+        <f>SUM(C86:I86)</f>
         <v/>
       </c>
     </row>
     <row r="100" ht="16.5" customHeight="1" s="78">
-      <c r="A100" s="108" t="n"/>
-      <c r="B100" s="25" t="inlineStr">
-        <is>
-          <t>중증화상진단비</t>
+      <c r="A100" s="103" t="n"/>
+      <c r="B100" s="56" t="inlineStr">
+        <is>
+          <t>깁스진단비</t>
         </is>
       </c>
       <c r="C100" s="134" t="n"/>
@@ -3427,179 +3453,147 @@
       <c r="H100" s="134" t="n"/>
       <c r="I100" s="134" t="n"/>
       <c r="J100" s="135">
-        <f>SUM(C85:I85)</f>
+        <f>SUM(C87:I87)</f>
         <v/>
       </c>
     </row>
     <row r="101" ht="16.5" customHeight="1" s="78">
-      <c r="A101" s="108" t="n"/>
+      <c r="A101" s="101" t="inlineStr">
+        <is>
+          <t>실손</t>
+        </is>
+      </c>
       <c r="B101" s="104" t="inlineStr">
         <is>
-          <t>반깁스</t>
-        </is>
-      </c>
-      <c r="C101" s="136" t="n"/>
-      <c r="D101" s="136" t="n"/>
-      <c r="E101" s="136" t="n"/>
-      <c r="F101" s="136" t="n"/>
-      <c r="G101" s="136" t="n"/>
-      <c r="H101" s="136" t="n"/>
-      <c r="I101" s="136" t="n"/>
+          <t>입원</t>
+        </is>
+      </c>
+      <c r="C101" s="169" t="n"/>
+      <c r="D101" s="169" t="n"/>
+      <c r="E101" s="169" t="n"/>
+      <c r="F101" s="169" t="n"/>
+      <c r="G101" s="169" t="n"/>
+      <c r="H101" s="169" t="n"/>
+      <c r="I101" s="169" t="n"/>
       <c r="J101" s="137">
-        <f>SUM(C86:I86)</f>
+        <f>SUM(C88:I88)</f>
         <v/>
       </c>
     </row>
     <row r="102" ht="16.5" customHeight="1" s="78">
-      <c r="A102" s="108" t="n"/>
-      <c r="B102" s="56" t="inlineStr">
-        <is>
-          <t>깁스진단비</t>
-        </is>
-      </c>
-      <c r="C102" s="134" t="n"/>
-      <c r="D102" s="134" t="n"/>
-      <c r="E102" s="134" t="n"/>
-      <c r="F102" s="134" t="n"/>
-      <c r="G102" s="134" t="n"/>
-      <c r="H102" s="134" t="n"/>
-      <c r="I102" s="134" t="n"/>
-      <c r="J102" s="135">
-        <f>SUM(C87:I87)</f>
+      <c r="A102" s="102" t="n"/>
+      <c r="B102" s="59" t="inlineStr">
+        <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="C102" s="170" t="n"/>
+      <c r="D102" s="170" t="n"/>
+      <c r="E102" s="170" t="n"/>
+      <c r="F102" s="170" t="n"/>
+      <c r="G102" s="170" t="n"/>
+      <c r="H102" s="170" t="n"/>
+      <c r="I102" s="170" t="n"/>
+      <c r="J102" s="139">
+        <f>SUM(C89:I89)</f>
         <v/>
       </c>
     </row>
     <row r="103" ht="16.5" customHeight="1" s="78">
-      <c r="A103" s="107" t="n"/>
-      <c r="B103" s="104" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="C103" s="169" t="n"/>
-      <c r="D103" s="169" t="n"/>
-      <c r="E103" s="169" t="n"/>
-      <c r="F103" s="169" t="n"/>
-      <c r="G103" s="169" t="n"/>
-      <c r="H103" s="169" t="n"/>
-      <c r="I103" s="169" t="n"/>
-      <c r="J103" s="137">
-        <f>SUM(C88:I88)</f>
+      <c r="A103" s="102" t="n"/>
+      <c r="B103" s="59" t="inlineStr">
+        <is>
+          <t>약값</t>
+        </is>
+      </c>
+      <c r="C103" s="138" t="n"/>
+      <c r="D103" s="138" t="n"/>
+      <c r="E103" s="138" t="n"/>
+      <c r="F103" s="138" t="n"/>
+      <c r="G103" s="138" t="n"/>
+      <c r="H103" s="138" t="n"/>
+      <c r="I103" s="170" t="n"/>
+      <c r="J103" s="139">
+        <f>SUM(C90:I90)</f>
         <v/>
       </c>
     </row>
     <row r="104" ht="16.5" customHeight="1" s="78">
-      <c r="A104" s="107" t="n"/>
+      <c r="A104" s="102" t="n"/>
       <c r="B104" s="59" t="inlineStr">
         <is>
-          <t>통원</t>
-        </is>
-      </c>
-      <c r="C104" s="170" t="n"/>
-      <c r="D104" s="170" t="n"/>
-      <c r="E104" s="170" t="n"/>
-      <c r="F104" s="170" t="n"/>
-      <c r="G104" s="170" t="n"/>
-      <c r="H104" s="170" t="n"/>
+          <t>MRI/도수치료/비급여주사</t>
+        </is>
+      </c>
+      <c r="C104" s="138" t="n"/>
+      <c r="D104" s="138" t="n"/>
+      <c r="E104" s="138" t="n"/>
+      <c r="F104" s="138" t="n"/>
+      <c r="G104" s="138" t="n"/>
+      <c r="H104" s="138" t="n"/>
       <c r="I104" s="170" t="n"/>
-      <c r="J104" s="139">
-        <f>SUM(C89:I89)</f>
-        <v/>
-      </c>
+      <c r="J104" s="133" t="n"/>
     </row>
     <row r="105" ht="16.5" customHeight="1" s="78">
-      <c r="A105" s="107" t="n"/>
-      <c r="B105" s="59" t="inlineStr">
-        <is>
-          <t>약값</t>
-        </is>
-      </c>
-      <c r="C105" s="138" t="n"/>
-      <c r="D105" s="138" t="n"/>
-      <c r="E105" s="138" t="n"/>
-      <c r="F105" s="138" t="n"/>
-      <c r="G105" s="138" t="n"/>
-      <c r="H105" s="138" t="n"/>
-      <c r="I105" s="170" t="n"/>
-      <c r="J105" s="139">
-        <f>SUM(C90:I90)</f>
-        <v/>
-      </c>
+      <c r="A105" s="103" t="n"/>
+      <c r="B105" s="22" t="inlineStr">
+        <is>
+          <t>상해의료비</t>
+        </is>
+      </c>
+      <c r="C105" s="132" t="n"/>
+      <c r="D105" s="132" t="n"/>
+      <c r="E105" s="132" t="n"/>
+      <c r="F105" s="132" t="n"/>
+      <c r="G105" s="132" t="n"/>
+      <c r="H105" s="132" t="n"/>
+      <c r="I105" s="171" t="n"/>
+      <c r="J105" s="139" t="n"/>
     </row>
     <row r="106" ht="16.5" customHeight="1" s="78">
-      <c r="A106" s="108" t="n"/>
-      <c r="B106" s="59" t="inlineStr">
-        <is>
-          <t>MRI/도수치료/비급여주사</t>
-        </is>
-      </c>
-      <c r="C106" s="138" t="n"/>
-      <c r="D106" s="138" t="n"/>
-      <c r="E106" s="138" t="n"/>
-      <c r="F106" s="138" t="n"/>
-      <c r="G106" s="138" t="n"/>
-      <c r="H106" s="138" t="n"/>
-      <c r="I106" s="170" t="n"/>
-      <c r="J106" s="133" t="n"/>
-    </row>
-    <row r="107" ht="16.5" customHeight="1" s="78">
-      <c r="A107" s="108" t="n"/>
-      <c r="B107" s="22" t="inlineStr">
-        <is>
-          <t>상해의료비</t>
-        </is>
-      </c>
-      <c r="C107" s="132" t="n"/>
-      <c r="D107" s="132" t="n"/>
-      <c r="E107" s="132" t="n"/>
-      <c r="F107" s="132" t="n"/>
-      <c r="G107" s="132" t="n"/>
-      <c r="H107" s="132" t="n"/>
-      <c r="I107" s="171" t="n"/>
-      <c r="J107" s="139" t="n"/>
-    </row>
-    <row r="108" ht="16.5" customHeight="1" s="78">
-      <c r="A108" s="101" t="inlineStr">
+      <c r="A106" s="101" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B108" s="75" t="inlineStr">
+      <c r="B106" s="75" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C108" s="172" t="n"/>
-      <c r="D108" s="172" t="n"/>
-      <c r="E108" s="172" t="n"/>
-      <c r="F108" s="172" t="n"/>
-      <c r="G108" s="172" t="n"/>
-      <c r="H108" s="172" t="n"/>
-      <c r="I108" s="172" t="n"/>
-      <c r="J108" s="173">
+      <c r="C106" s="172" t="n"/>
+      <c r="D106" s="172" t="n"/>
+      <c r="E106" s="172" t="n"/>
+      <c r="F106" s="172" t="n"/>
+      <c r="G106" s="172" t="n"/>
+      <c r="H106" s="172" t="n"/>
+      <c r="I106" s="172" t="n"/>
+      <c r="J106" s="173">
         <f>SUM(C91:I91)</f>
         <v/>
       </c>
     </row>
+    <row r="107" ht="16.5" customHeight="1" s="78"/>
+    <row r="108" ht="16.5" customHeight="1" s="78"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A101:A105"/>
-    <mergeCell ref="A6:A10"/>
     <mergeCell ref="A86:A91"/>
     <mergeCell ref="A15:A31"/>
-    <mergeCell ref="A92:A94"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A41:A53"/>
     <mergeCell ref="A54:A66"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A41:A53"/>
+    <mergeCell ref="A11:A14"/>
     <mergeCell ref="A97:A98"/>
-    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A67:A85"/>
     <mergeCell ref="A32:A40"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>

--- a/master.xlsx
+++ b/master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1170" yWindow="855" windowWidth="20100" windowHeight="15345" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="보장분석" sheetId="1" state="visible" r:id="rId1"/>
@@ -135,7 +135,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -209,12 +209,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor rgb="FFC0C0C0"/>
       </patternFill>
@@ -225,7 +219,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -819,26 +813,6 @@
       </right>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -879,20 +853,33 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right/>
-      <top/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -902,7 +889,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1072,9 +1059,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1170,62 +1154,57 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="48" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="8" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="14" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1307,7 +1286,7 @@
     <xf numFmtId="164" fontId="5" fillId="8" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="14" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="13" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1334,16 +1313,16 @@
     <xf numFmtId="164" fontId="5" fillId="8" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="13" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="14" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1395,24 +1374,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="15" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1420,7 +1381,74 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1539,112 +1567,112 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J106"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col width="6.5" customWidth="1" style="78" min="1" max="1"/>
-    <col width="17.3984375" customWidth="1" style="78" min="2" max="2"/>
-    <col width="14.5" customWidth="1" style="78" min="3" max="7"/>
-    <col width="16.5" customWidth="1" style="78" min="8" max="8"/>
-    <col width="14.5" customWidth="1" style="78" min="9" max="9"/>
-    <col width="22.8984375" customWidth="1" style="78" min="10" max="10"/>
-    <col width="1.5" customWidth="1" style="78" min="11" max="11"/>
-    <col width="11.3984375" customWidth="1" style="78" min="12" max="18"/>
+    <col width="6.5" customWidth="1" style="77" min="1" max="1"/>
+    <col width="17.375" customWidth="1" style="77" min="2" max="2"/>
+    <col width="14.5" customWidth="1" style="77" min="3" max="7"/>
+    <col width="16.5" customWidth="1" style="77" min="8" max="8"/>
+    <col width="14.5" customWidth="1" style="77" min="9" max="9"/>
+    <col width="22.875" customWidth="1" style="77" min="10" max="10"/>
+    <col width="1.5" customWidth="1" style="77" min="11" max="11"/>
+    <col width="11.375" customWidth="1" style="77" min="12" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38.25" customHeight="1" s="78">
-      <c r="A1" s="112" t="n"/>
-      <c r="B1" s="113" t="n"/>
-      <c r="C1" s="117" t="n"/>
-      <c r="D1" s="117" t="n"/>
-      <c r="E1" s="117" t="n"/>
-      <c r="F1" s="117" t="n"/>
-      <c r="G1" s="117" t="n"/>
-      <c r="H1" s="117" t="n"/>
-      <c r="I1" s="118" t="n"/>
+    <row r="1" ht="38.25" customHeight="1" s="77">
+      <c r="A1" s="102" t="n"/>
+      <c r="B1" s="103" t="n"/>
+      <c r="C1" s="113" t="n"/>
+      <c r="D1" s="113" t="n"/>
+      <c r="E1" s="113" t="n"/>
+      <c r="F1" s="113" t="n"/>
+      <c r="G1" s="113" t="n"/>
+      <c r="H1" s="113" t="n"/>
+      <c r="I1" s="114" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="78">
-      <c r="A2" s="104" t="inlineStr">
+    <row r="2" ht="16.5" customHeight="1" s="77">
+      <c r="A2" s="109" t="inlineStr">
         <is>
           <t>보험료</t>
         </is>
       </c>
-      <c r="B2" s="105" t="n"/>
-      <c r="C2" s="119" t="n"/>
-      <c r="D2" s="119" t="n"/>
-      <c r="E2" s="119" t="n"/>
-      <c r="F2" s="119" t="n"/>
-      <c r="G2" s="119" t="n"/>
-      <c r="H2" s="119" t="n"/>
-      <c r="I2" s="119" t="n"/>
-      <c r="J2" s="120">
+      <c r="B2" s="110" t="n"/>
+      <c r="C2" s="115" t="n"/>
+      <c r="D2" s="115" t="n"/>
+      <c r="E2" s="115" t="n"/>
+      <c r="F2" s="115" t="n"/>
+      <c r="G2" s="115" t="n"/>
+      <c r="H2" s="115" t="n"/>
+      <c r="I2" s="115" t="n"/>
+      <c r="J2" s="116">
         <f>SUM(C2:I2)</f>
         <v/>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="78">
-      <c r="A3" s="99" t="inlineStr">
+    <row r="3" ht="16.5" customHeight="1" s="77">
+      <c r="A3" s="107" t="inlineStr">
         <is>
           <t>가입년일</t>
         </is>
       </c>
-      <c r="B3" s="100" t="n"/>
-      <c r="C3" s="121" t="n"/>
-      <c r="D3" s="121" t="n"/>
-      <c r="E3" s="121" t="n"/>
-      <c r="F3" s="121" t="n"/>
-      <c r="G3" s="121" t="n"/>
-      <c r="H3" s="121" t="n"/>
-      <c r="I3" s="121" t="n"/>
-      <c r="J3" s="122">
+      <c r="B3" s="108" t="n"/>
+      <c r="C3" s="117" t="n"/>
+      <c r="D3" s="117" t="n"/>
+      <c r="E3" s="117" t="n"/>
+      <c r="F3" s="117" t="n"/>
+      <c r="G3" s="117" t="n"/>
+      <c r="H3" s="117" t="n"/>
+      <c r="I3" s="117" t="n"/>
+      <c r="J3" s="118">
         <f>SUM(C3:I3)</f>
         <v/>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="78">
-      <c r="A4" s="99" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="77">
+      <c r="A4" s="107" t="inlineStr">
         <is>
           <t>만기일자</t>
         </is>
       </c>
-      <c r="B4" s="100" t="n"/>
-      <c r="C4" s="123" t="n"/>
-      <c r="D4" s="123" t="n"/>
-      <c r="E4" s="123" t="n"/>
-      <c r="F4" s="123" t="n"/>
-      <c r="G4" s="123" t="n"/>
-      <c r="H4" s="123" t="n"/>
-      <c r="I4" s="123" t="n"/>
-      <c r="J4" s="122">
+      <c r="B4" s="108" t="n"/>
+      <c r="C4" s="119" t="n"/>
+      <c r="D4" s="119" t="n"/>
+      <c r="E4" s="119" t="n"/>
+      <c r="F4" s="119" t="n"/>
+      <c r="G4" s="119" t="n"/>
+      <c r="H4" s="119" t="n"/>
+      <c r="I4" s="119" t="n"/>
+      <c r="J4" s="118">
         <f>SUM(C4:I4)</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1" s="78">
-      <c r="A5" s="110" t="inlineStr">
+    <row r="5" ht="17.25" customHeight="1" s="77">
+      <c r="A5" s="111" t="inlineStr">
         <is>
           <t>총납입기간</t>
         </is>
       </c>
-      <c r="B5" s="111" t="n"/>
-      <c r="C5" s="124" t="n"/>
-      <c r="D5" s="124" t="n"/>
-      <c r="E5" s="124" t="n"/>
-      <c r="F5" s="124" t="n"/>
-      <c r="G5" s="124" t="n"/>
-      <c r="H5" s="124" t="n"/>
-      <c r="I5" s="124" t="n"/>
-      <c r="J5" s="125">
+      <c r="B5" s="112" t="n"/>
+      <c r="C5" s="120" t="n"/>
+      <c r="D5" s="120" t="n"/>
+      <c r="E5" s="120" t="n"/>
+      <c r="F5" s="120" t="n"/>
+      <c r="G5" s="120" t="n"/>
+      <c r="H5" s="120" t="n"/>
+      <c r="I5" s="120" t="n"/>
+      <c r="J5" s="121">
         <f>SUM(C5:I5)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1" s="78">
-      <c r="A6" s="101" t="inlineStr">
+    <row r="6" ht="16.5" customHeight="1" s="77">
+      <c r="A6" s="104" t="inlineStr">
         <is>
           <t>사망</t>
         </is>
@@ -1654,96 +1682,96 @@
           <t>일반사망</t>
         </is>
       </c>
-      <c r="C6" s="126" t="n"/>
-      <c r="D6" s="126" t="n"/>
-      <c r="E6" s="126" t="n"/>
-      <c r="F6" s="126" t="n"/>
-      <c r="G6" s="126" t="n"/>
-      <c r="H6" s="126" t="n"/>
-      <c r="I6" s="126" t="n"/>
-      <c r="J6" s="127">
+      <c r="C6" s="122" t="n"/>
+      <c r="D6" s="122" t="n"/>
+      <c r="E6" s="122" t="n"/>
+      <c r="F6" s="122" t="n"/>
+      <c r="G6" s="122" t="n"/>
+      <c r="H6" s="122" t="n"/>
+      <c r="I6" s="122" t="n"/>
+      <c r="J6" s="123">
         <f>SUM(C6:I6)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" s="78">
-      <c r="A7" s="102" t="n"/>
+    <row r="7" ht="17.25" customHeight="1" s="77">
+      <c r="A7" s="105" t="n"/>
       <c r="B7" s="16" t="inlineStr">
         <is>
           <t>중대한CI적용</t>
         </is>
       </c>
-      <c r="C7" s="128" t="n"/>
-      <c r="D7" s="128" t="n"/>
-      <c r="E7" s="128" t="n"/>
-      <c r="F7" s="128" t="n"/>
-      <c r="G7" s="128" t="n"/>
-      <c r="H7" s="128" t="n"/>
-      <c r="I7" s="128" t="n"/>
-      <c r="J7" s="129">
+      <c r="C7" s="124" t="n"/>
+      <c r="D7" s="124" t="n"/>
+      <c r="E7" s="124" t="n"/>
+      <c r="F7" s="124" t="n"/>
+      <c r="G7" s="124" t="n"/>
+      <c r="H7" s="124" t="n"/>
+      <c r="I7" s="124" t="n"/>
+      <c r="J7" s="125">
         <f>SUM(C7:I7)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1" s="78">
-      <c r="A8" s="102" t="n"/>
+    <row r="8" ht="17.25" customHeight="1" s="77">
+      <c r="A8" s="105" t="n"/>
       <c r="B8" s="19" t="inlineStr">
         <is>
           <t>질병사망(80세)</t>
         </is>
       </c>
-      <c r="C8" s="130" t="n"/>
-      <c r="D8" s="130" t="n"/>
-      <c r="E8" s="130" t="n"/>
-      <c r="F8" s="130" t="n"/>
-      <c r="G8" s="130" t="n"/>
-      <c r="H8" s="130" t="n"/>
-      <c r="I8" s="130" t="n"/>
-      <c r="J8" s="131">
+      <c r="C8" s="126" t="n"/>
+      <c r="D8" s="126" t="n"/>
+      <c r="E8" s="126" t="n"/>
+      <c r="F8" s="126" t="n"/>
+      <c r="G8" s="126" t="n"/>
+      <c r="H8" s="126" t="n"/>
+      <c r="I8" s="126" t="n"/>
+      <c r="J8" s="127">
         <f>SUM(C8:I8)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1" s="78">
-      <c r="A9" s="102" t="n"/>
+    <row r="9" ht="16.5" customHeight="1" s="77">
+      <c r="A9" s="105" t="n"/>
       <c r="B9" s="22" t="inlineStr">
         <is>
           <t>교통상해사망</t>
         </is>
       </c>
-      <c r="C9" s="132" t="n"/>
-      <c r="D9" s="132" t="n"/>
-      <c r="E9" s="132" t="n"/>
-      <c r="F9" s="132" t="n"/>
-      <c r="G9" s="132" t="n"/>
-      <c r="H9" s="132" t="n"/>
-      <c r="I9" s="132" t="n"/>
-      <c r="J9" s="133">
+      <c r="C9" s="128" t="n"/>
+      <c r="D9" s="128" t="n"/>
+      <c r="E9" s="128" t="n"/>
+      <c r="F9" s="128" t="n"/>
+      <c r="G9" s="128" t="n"/>
+      <c r="H9" s="128" t="n"/>
+      <c r="I9" s="128" t="n"/>
+      <c r="J9" s="129">
         <f>SUM(C9:I9)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1" s="78">
-      <c r="A10" s="103" t="n"/>
+    <row r="10" ht="17.25" customHeight="1" s="77">
+      <c r="A10" s="106" t="n"/>
       <c r="B10" s="25" t="inlineStr">
         <is>
           <t>상해사망</t>
         </is>
       </c>
-      <c r="C10" s="134" t="n"/>
-      <c r="D10" s="134" t="n"/>
-      <c r="E10" s="134" t="n"/>
-      <c r="F10" s="134" t="n"/>
-      <c r="G10" s="134" t="n"/>
-      <c r="H10" s="134" t="n"/>
-      <c r="I10" s="134" t="n"/>
-      <c r="J10" s="135">
+      <c r="C10" s="130" t="n"/>
+      <c r="D10" s="130" t="n"/>
+      <c r="E10" s="130" t="n"/>
+      <c r="F10" s="130" t="n"/>
+      <c r="G10" s="130" t="n"/>
+      <c r="H10" s="130" t="n"/>
+      <c r="I10" s="130" t="n"/>
+      <c r="J10" s="131">
         <f>SUM(C10:I10)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1" s="78">
-      <c r="A11" s="101" t="inlineStr">
+    <row r="11" ht="16.5" customHeight="1" s="77">
+      <c r="A11" s="104" t="inlineStr">
         <is>
           <t>후유장애</t>
         </is>
@@ -1753,77 +1781,77 @@
           <t>상해후유3%</t>
         </is>
       </c>
-      <c r="C11" s="136" t="n"/>
-      <c r="D11" s="136" t="n"/>
-      <c r="E11" s="136" t="n"/>
-      <c r="F11" s="136" t="n"/>
-      <c r="G11" s="136" t="n"/>
-      <c r="H11" s="136" t="n"/>
-      <c r="I11" s="136" t="n"/>
-      <c r="J11" s="137">
+      <c r="C11" s="132" t="n"/>
+      <c r="D11" s="132" t="n"/>
+      <c r="E11" s="132" t="n"/>
+      <c r="F11" s="132" t="n"/>
+      <c r="G11" s="132" t="n"/>
+      <c r="H11" s="132" t="n"/>
+      <c r="I11" s="132" t="n"/>
+      <c r="J11" s="133">
         <f>SUM(C11:I11)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1" s="78">
-      <c r="A12" s="102" t="n"/>
+    <row r="12" ht="16.5" customHeight="1" s="77">
+      <c r="A12" s="105" t="n"/>
       <c r="B12" s="31" t="inlineStr">
         <is>
           <t>상해후유80%</t>
         </is>
       </c>
-      <c r="C12" s="138" t="n"/>
-      <c r="D12" s="138" t="n"/>
-      <c r="E12" s="138" t="n"/>
-      <c r="F12" s="138" t="n"/>
-      <c r="G12" s="138" t="n"/>
-      <c r="H12" s="138" t="n"/>
-      <c r="I12" s="138" t="n"/>
-      <c r="J12" s="139">
+      <c r="C12" s="134" t="n"/>
+      <c r="D12" s="134" t="n"/>
+      <c r="E12" s="134" t="n"/>
+      <c r="F12" s="134" t="n"/>
+      <c r="G12" s="134" t="n"/>
+      <c r="H12" s="134" t="n"/>
+      <c r="I12" s="134" t="n"/>
+      <c r="J12" s="135">
         <f>SUM(C12:I12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" s="78">
-      <c r="A13" s="102" t="n"/>
+    <row r="13" ht="16.5" customHeight="1" s="77">
+      <c r="A13" s="105" t="n"/>
       <c r="B13" s="31" t="inlineStr">
         <is>
           <t>질병후유3%</t>
         </is>
       </c>
-      <c r="C13" s="138" t="n"/>
-      <c r="D13" s="138" t="n"/>
-      <c r="E13" s="138" t="n"/>
-      <c r="F13" s="138" t="n"/>
-      <c r="G13" s="138" t="n"/>
-      <c r="H13" s="138" t="n"/>
-      <c r="I13" s="138" t="n"/>
-      <c r="J13" s="139">
+      <c r="C13" s="134" t="n"/>
+      <c r="D13" s="134" t="n"/>
+      <c r="E13" s="134" t="n"/>
+      <c r="F13" s="134" t="n"/>
+      <c r="G13" s="134" t="n"/>
+      <c r="H13" s="134" t="n"/>
+      <c r="I13" s="134" t="n"/>
+      <c r="J13" s="135">
         <f>SUM(C13:I13)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1" s="78">
-      <c r="A14" s="103" t="n"/>
+    <row r="14" ht="17.25" customHeight="1" s="77">
+      <c r="A14" s="106" t="n"/>
       <c r="B14" s="25" t="inlineStr">
         <is>
           <t>질병후유80%</t>
         </is>
       </c>
-      <c r="C14" s="134" t="n"/>
-      <c r="D14" s="134" t="n"/>
-      <c r="E14" s="134" t="n"/>
-      <c r="F14" s="134" t="n"/>
-      <c r="G14" s="134" t="n"/>
-      <c r="H14" s="134" t="n"/>
-      <c r="I14" s="134" t="n"/>
-      <c r="J14" s="139">
+      <c r="C14" s="130" t="n"/>
+      <c r="D14" s="130" t="n"/>
+      <c r="E14" s="130" t="n"/>
+      <c r="F14" s="130" t="n"/>
+      <c r="G14" s="130" t="n"/>
+      <c r="H14" s="130" t="n"/>
+      <c r="I14" s="130" t="n"/>
+      <c r="J14" s="135">
         <f>SUM(C14:I14)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1" s="78">
-      <c r="A15" s="101" t="inlineStr">
+    <row r="15" ht="17.25" customHeight="1" s="77">
+      <c r="A15" s="104" t="inlineStr">
         <is>
           <t>암</t>
         </is>
@@ -1833,312 +1861,312 @@
           <t>고액암</t>
         </is>
       </c>
-      <c r="C15" s="140" t="n"/>
-      <c r="D15" s="140" t="n"/>
-      <c r="E15" s="140" t="n"/>
-      <c r="F15" s="140" t="n"/>
-      <c r="G15" s="140" t="n"/>
-      <c r="H15" s="140" t="n"/>
-      <c r="I15" s="140" t="n"/>
-      <c r="J15" s="141">
+      <c r="C15" s="136" t="n"/>
+      <c r="D15" s="136" t="n"/>
+      <c r="E15" s="136" t="n"/>
+      <c r="F15" s="136" t="n"/>
+      <c r="G15" s="136" t="n"/>
+      <c r="H15" s="136" t="n"/>
+      <c r="I15" s="136" t="n"/>
+      <c r="J15" s="137">
         <f>SUM(C15:I15)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" s="78">
-      <c r="A16" s="102" t="n"/>
+    <row r="16" ht="16.5" customHeight="1" s="77">
+      <c r="A16" s="105" t="n"/>
       <c r="B16" s="13" t="inlineStr">
         <is>
           <t>통합암</t>
         </is>
       </c>
-      <c r="C16" s="142" t="n"/>
-      <c r="D16" s="142" t="n"/>
-      <c r="E16" s="142" t="n"/>
-      <c r="F16" s="142" t="n"/>
-      <c r="G16" s="142" t="n"/>
-      <c r="H16" s="142" t="n"/>
-      <c r="I16" s="142" t="n"/>
-      <c r="J16" s="127">
+      <c r="C16" s="138" t="n"/>
+      <c r="D16" s="138" t="n"/>
+      <c r="E16" s="138" t="n"/>
+      <c r="F16" s="138" t="n"/>
+      <c r="G16" s="138" t="n"/>
+      <c r="H16" s="138" t="n"/>
+      <c r="I16" s="138" t="n"/>
+      <c r="J16" s="123">
         <f>SUM(C16:I16)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" s="78">
-      <c r="A17" s="102" t="n"/>
-      <c r="B17" s="114" t="inlineStr">
+    <row r="17" ht="16.5" customHeight="1" s="77">
+      <c r="A17" s="105" t="n"/>
+      <c r="B17" s="92" t="inlineStr">
         <is>
           <t>일반암</t>
         </is>
       </c>
-      <c r="C17" s="143" t="n"/>
-      <c r="D17" s="143" t="n"/>
-      <c r="E17" s="143" t="n"/>
-      <c r="F17" s="143" t="n"/>
-      <c r="G17" s="143" t="n"/>
-      <c r="H17" s="143" t="n"/>
-      <c r="I17" s="143" t="n"/>
-      <c r="J17" s="144">
+      <c r="C17" s="139" t="n"/>
+      <c r="D17" s="139" t="n"/>
+      <c r="E17" s="139" t="n"/>
+      <c r="F17" s="139" t="n"/>
+      <c r="G17" s="139" t="n"/>
+      <c r="H17" s="139" t="n"/>
+      <c r="I17" s="139" t="n"/>
+      <c r="J17" s="140">
         <f>SUM(C15:I15)</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="17.25" customHeight="1" s="78" thickBot="1">
-      <c r="A18" s="102" t="n"/>
+    <row r="18" ht="17.25" customHeight="1" s="77" thickBot="1">
+      <c r="A18" s="105" t="n"/>
       <c r="B18" s="38" t="inlineStr">
         <is>
           <t>중대한 암</t>
         </is>
       </c>
-      <c r="C18" s="145" t="n"/>
-      <c r="D18" s="145" t="n"/>
-      <c r="E18" s="145" t="n"/>
-      <c r="F18" s="145" t="n"/>
-      <c r="G18" s="145" t="n"/>
-      <c r="H18" s="145" t="n"/>
-      <c r="I18" s="145" t="n"/>
-      <c r="J18" s="129">
+      <c r="C18" s="141" t="n"/>
+      <c r="D18" s="141" t="n"/>
+      <c r="E18" s="141" t="n"/>
+      <c r="F18" s="141" t="n"/>
+      <c r="G18" s="141" t="n"/>
+      <c r="H18" s="141" t="n"/>
+      <c r="I18" s="141" t="n"/>
+      <c r="J18" s="125">
         <f>SUM(C18:I18)</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1" s="78">
-      <c r="A19" s="102" t="n"/>
+    <row r="19" ht="16.5" customHeight="1" s="77">
+      <c r="A19" s="105" t="n"/>
       <c r="B19" s="40" t="inlineStr">
         <is>
           <t>유사암(갑.기.경.제)</t>
         </is>
       </c>
-      <c r="C19" s="146" t="n"/>
-      <c r="D19" s="146" t="n"/>
-      <c r="E19" s="146" t="n"/>
-      <c r="F19" s="146" t="n"/>
-      <c r="G19" s="146" t="n"/>
-      <c r="H19" s="146" t="n"/>
-      <c r="I19" s="146" t="n"/>
-      <c r="J19" s="133">
+      <c r="C19" s="142" t="n"/>
+      <c r="D19" s="142" t="n"/>
+      <c r="E19" s="142" t="n"/>
+      <c r="F19" s="142" t="n"/>
+      <c r="G19" s="142" t="n"/>
+      <c r="H19" s="142" t="n"/>
+      <c r="I19" s="142" t="n"/>
+      <c r="J19" s="129">
         <f>SUM(C19:I19)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1" s="78">
-      <c r="A20" s="102" t="n"/>
+    <row r="20" ht="16.5" customHeight="1" s="77">
+      <c r="A20" s="105" t="n"/>
       <c r="B20" s="40" t="inlineStr">
         <is>
           <t>통합전이암</t>
         </is>
       </c>
-      <c r="C20" s="146" t="n"/>
-      <c r="D20" s="146" t="n"/>
-      <c r="E20" s="146" t="n"/>
-      <c r="F20" s="146" t="n"/>
-      <c r="G20" s="146" t="n"/>
-      <c r="H20" s="146" t="n"/>
-      <c r="I20" s="146" t="n"/>
-      <c r="J20" s="133" t="n"/>
-    </row>
-    <row r="21" ht="16.5" customHeight="1" s="78">
-      <c r="A21" s="102" t="n"/>
+      <c r="C20" s="142" t="n"/>
+      <c r="D20" s="142" t="n"/>
+      <c r="E20" s="142" t="n"/>
+      <c r="F20" s="142" t="n"/>
+      <c r="G20" s="142" t="n"/>
+      <c r="H20" s="142" t="n"/>
+      <c r="I20" s="142" t="n"/>
+      <c r="J20" s="129" t="n"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1" s="77">
+      <c r="A21" s="105" t="n"/>
       <c r="B21" s="42" t="inlineStr">
         <is>
           <t>암주요치료비</t>
         </is>
       </c>
-      <c r="C21" s="147" t="n"/>
-      <c r="D21" s="147" t="n"/>
-      <c r="E21" s="147" t="n"/>
-      <c r="F21" s="147" t="n"/>
-      <c r="G21" s="147" t="n"/>
-      <c r="H21" s="147" t="n"/>
-      <c r="I21" s="146" t="n"/>
-      <c r="J21" s="133" t="n"/>
-    </row>
-    <row r="22" ht="16.5" customHeight="1" s="78">
-      <c r="A22" s="102" t="n"/>
+      <c r="C21" s="143" t="n"/>
+      <c r="D21" s="143" t="n"/>
+      <c r="E21" s="143" t="n"/>
+      <c r="F21" s="143" t="n"/>
+      <c r="G21" s="143" t="n"/>
+      <c r="H21" s="143" t="n"/>
+      <c r="I21" s="142" t="n"/>
+      <c r="J21" s="129" t="n"/>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" s="77">
+      <c r="A22" s="105" t="n"/>
       <c r="B22" s="42" t="inlineStr">
         <is>
           <t>10억 플랜</t>
         </is>
       </c>
-      <c r="C22" s="147" t="n"/>
-      <c r="D22" s="147" t="n"/>
-      <c r="E22" s="147" t="n"/>
-      <c r="F22" s="147" t="n"/>
-      <c r="G22" s="147" t="n"/>
-      <c r="H22" s="147" t="n"/>
-      <c r="I22" s="146" t="n"/>
-      <c r="J22" s="133" t="n"/>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" s="78">
-      <c r="A23" s="102" t="n"/>
+      <c r="C22" s="143" t="n"/>
+      <c r="D22" s="143" t="n"/>
+      <c r="E22" s="143" t="n"/>
+      <c r="F22" s="143" t="n"/>
+      <c r="G22" s="143" t="n"/>
+      <c r="H22" s="143" t="n"/>
+      <c r="I22" s="142" t="n"/>
+      <c r="J22" s="129" t="n"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" s="77">
+      <c r="A23" s="105" t="n"/>
       <c r="B23" s="42" t="inlineStr">
         <is>
           <t>하이클래스(암)</t>
         </is>
       </c>
-      <c r="C23" s="146" t="n"/>
-      <c r="D23" s="146" t="n"/>
-      <c r="E23" s="146" t="n"/>
-      <c r="F23" s="146" t="n"/>
-      <c r="G23" s="146" t="n"/>
-      <c r="H23" s="146" t="n"/>
-      <c r="I23" s="146" t="n"/>
-      <c r="J23" s="139">
+      <c r="C23" s="142" t="n"/>
+      <c r="D23" s="142" t="n"/>
+      <c r="E23" s="142" t="n"/>
+      <c r="F23" s="142" t="n"/>
+      <c r="G23" s="142" t="n"/>
+      <c r="H23" s="142" t="n"/>
+      <c r="I23" s="142" t="n"/>
+      <c r="J23" s="135">
         <f>SUM(C21:I21)</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1" s="78">
-      <c r="A24" s="102" t="n"/>
+    <row r="24" ht="16.5" customHeight="1" s="77">
+      <c r="A24" s="105" t="n"/>
       <c r="B24" s="42" t="inlineStr">
         <is>
           <t>중입자치료비</t>
         </is>
       </c>
-      <c r="C24" s="147" t="n"/>
-      <c r="D24" s="147" t="n"/>
-      <c r="E24" s="147" t="n"/>
-      <c r="F24" s="147" t="n"/>
-      <c r="G24" s="147" t="n"/>
-      <c r="H24" s="147" t="n"/>
-      <c r="I24" s="146" t="n"/>
-      <c r="J24" s="133">
+      <c r="C24" s="143" t="n"/>
+      <c r="D24" s="143" t="n"/>
+      <c r="E24" s="143" t="n"/>
+      <c r="F24" s="143" t="n"/>
+      <c r="G24" s="143" t="n"/>
+      <c r="H24" s="143" t="n"/>
+      <c r="I24" s="142" t="n"/>
+      <c r="J24" s="129">
         <f>SUM(C23:I23)</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1" s="78">
-      <c r="A25" s="102" t="n"/>
+    <row r="25" ht="16.5" customHeight="1" s="77">
+      <c r="A25" s="105" t="n"/>
       <c r="B25" s="42" t="inlineStr">
         <is>
           <t>표적항암치료비</t>
         </is>
       </c>
-      <c r="C25" s="147" t="n"/>
-      <c r="D25" s="147" t="n"/>
-      <c r="E25" s="147" t="n"/>
-      <c r="F25" s="147" t="n"/>
-      <c r="G25" s="147" t="n"/>
-      <c r="H25" s="147" t="n"/>
-      <c r="I25" s="146" t="n"/>
-      <c r="J25" s="133" t="n"/>
-    </row>
-    <row r="26" ht="16.5" customHeight="1" s="78">
-      <c r="A26" s="102" t="n"/>
+      <c r="C25" s="143" t="n"/>
+      <c r="D25" s="143" t="n"/>
+      <c r="E25" s="143" t="n"/>
+      <c r="F25" s="143" t="n"/>
+      <c r="G25" s="143" t="n"/>
+      <c r="H25" s="143" t="n"/>
+      <c r="I25" s="142" t="n"/>
+      <c r="J25" s="129" t="n"/>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" s="77">
+      <c r="A26" s="105" t="n"/>
       <c r="B26" s="44" t="inlineStr">
         <is>
           <t>양성자치료</t>
         </is>
       </c>
-      <c r="C26" s="148" t="n"/>
-      <c r="D26" s="148" t="n"/>
-      <c r="E26" s="148" t="n"/>
-      <c r="F26" s="148" t="n"/>
-      <c r="G26" s="148" t="n"/>
-      <c r="H26" s="148" t="n"/>
-      <c r="I26" s="149" t="n"/>
-      <c r="J26" s="139">
+      <c r="C26" s="144" t="n"/>
+      <c r="D26" s="144" t="n"/>
+      <c r="E26" s="144" t="n"/>
+      <c r="F26" s="144" t="n"/>
+      <c r="G26" s="144" t="n"/>
+      <c r="H26" s="144" t="n"/>
+      <c r="I26" s="145" t="n"/>
+      <c r="J26" s="135">
         <f>SUM(C25:I25)</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="78">
-      <c r="A27" s="102" t="n"/>
+    <row r="27" ht="16.5" customHeight="1" s="77">
+      <c r="A27" s="105" t="n"/>
       <c r="B27" s="44" t="inlineStr">
         <is>
           <t>세기조절치료</t>
         </is>
       </c>
-      <c r="C27" s="148" t="n"/>
-      <c r="D27" s="148" t="n"/>
-      <c r="E27" s="148" t="n"/>
-      <c r="F27" s="148" t="n"/>
-      <c r="G27" s="148" t="n"/>
-      <c r="H27" s="148" t="n"/>
-      <c r="I27" s="149" t="n"/>
-      <c r="J27" s="139">
+      <c r="C27" s="144" t="n"/>
+      <c r="D27" s="144" t="n"/>
+      <c r="E27" s="144" t="n"/>
+      <c r="F27" s="144" t="n"/>
+      <c r="G27" s="144" t="n"/>
+      <c r="H27" s="144" t="n"/>
+      <c r="I27" s="145" t="n"/>
+      <c r="J27" s="135">
         <f>SUM(C26:I26)</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" s="78">
-      <c r="A28" s="102" t="n"/>
+    <row r="28" ht="16.5" customHeight="1" s="77">
+      <c r="A28" s="105" t="n"/>
       <c r="B28" s="44" t="inlineStr">
         <is>
           <t>다빈치로봇수술비</t>
         </is>
       </c>
-      <c r="C28" s="148" t="n"/>
-      <c r="D28" s="148" t="n"/>
-      <c r="E28" s="148" t="n"/>
-      <c r="F28" s="148" t="n"/>
-      <c r="G28" s="148" t="n"/>
-      <c r="H28" s="148" t="n"/>
-      <c r="I28" s="149" t="n"/>
-      <c r="J28" s="139">
+      <c r="C28" s="144" t="n"/>
+      <c r="D28" s="144" t="n"/>
+      <c r="E28" s="144" t="n"/>
+      <c r="F28" s="144" t="n"/>
+      <c r="G28" s="144" t="n"/>
+      <c r="H28" s="144" t="n"/>
+      <c r="I28" s="145" t="n"/>
+      <c r="J28" s="135">
         <f>SUM(C27:I27)</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" s="78">
-      <c r="A29" s="102" t="n"/>
+    <row r="29" ht="16.5" customHeight="1" s="77">
+      <c r="A29" s="105" t="n"/>
       <c r="B29" s="44" t="inlineStr">
         <is>
           <t>암수술</t>
         </is>
       </c>
-      <c r="C29" s="149" t="n"/>
-      <c r="D29" s="149" t="n"/>
-      <c r="E29" s="149" t="n"/>
-      <c r="F29" s="149" t="n"/>
-      <c r="G29" s="149" t="n"/>
-      <c r="H29" s="149" t="n"/>
-      <c r="I29" s="149" t="n"/>
-      <c r="J29" s="139">
+      <c r="C29" s="145" t="n"/>
+      <c r="D29" s="145" t="n"/>
+      <c r="E29" s="145" t="n"/>
+      <c r="F29" s="145" t="n"/>
+      <c r="G29" s="145" t="n"/>
+      <c r="H29" s="145" t="n"/>
+      <c r="I29" s="145" t="n"/>
+      <c r="J29" s="135">
         <f>SUM(C28:I28)</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1" s="78">
-      <c r="A30" s="102" t="n"/>
+    <row r="30" ht="17.25" customHeight="1" s="77">
+      <c r="A30" s="105" t="n"/>
       <c r="B30" s="31" t="inlineStr">
         <is>
           <t>암일당</t>
         </is>
       </c>
-      <c r="C30" s="138" t="n"/>
-      <c r="D30" s="138" t="n"/>
-      <c r="E30" s="138" t="n"/>
-      <c r="F30" s="138" t="n"/>
-      <c r="G30" s="138" t="n"/>
-      <c r="H30" s="138" t="n"/>
-      <c r="I30" s="138" t="n"/>
-      <c r="J30" s="139">
+      <c r="C30" s="134" t="n"/>
+      <c r="D30" s="134" t="n"/>
+      <c r="E30" s="134" t="n"/>
+      <c r="F30" s="134" t="n"/>
+      <c r="G30" s="134" t="n"/>
+      <c r="H30" s="134" t="n"/>
+      <c r="I30" s="134" t="n"/>
+      <c r="J30" s="135">
         <f>SUM(C29:I29)</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="17.25" customHeight="1" s="78">
-      <c r="A31" s="103" t="n"/>
+    <row r="31" ht="17.25" customHeight="1" s="77">
+      <c r="A31" s="106" t="n"/>
       <c r="B31" s="25" t="inlineStr">
         <is>
           <t>항암방사선약물</t>
         </is>
       </c>
-      <c r="C31" s="134" t="n"/>
-      <c r="D31" s="134" t="n"/>
-      <c r="E31" s="134" t="n"/>
-      <c r="F31" s="134" t="n"/>
-      <c r="G31" s="134" t="n"/>
-      <c r="H31" s="134" t="n"/>
-      <c r="I31" s="134" t="n"/>
-      <c r="J31" s="135">
+      <c r="C31" s="130" t="n"/>
+      <c r="D31" s="130" t="n"/>
+      <c r="E31" s="130" t="n"/>
+      <c r="F31" s="130" t="n"/>
+      <c r="G31" s="130" t="n"/>
+      <c r="H31" s="130" t="n"/>
+      <c r="I31" s="130" t="n"/>
+      <c r="J31" s="131">
         <f>SUM(C30:I30)</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" s="78">
-      <c r="A32" s="101" t="inlineStr">
+    <row r="32" ht="16.5" customHeight="1" s="77">
+      <c r="A32" s="104" t="inlineStr">
         <is>
           <t>뇌혈관</t>
         </is>
@@ -2148,172 +2176,172 @@
           <t>뇌혈관진단비</t>
         </is>
       </c>
-      <c r="C32" s="140" t="n"/>
-      <c r="D32" s="140" t="n"/>
-      <c r="E32" s="140" t="n"/>
-      <c r="F32" s="140" t="n"/>
-      <c r="G32" s="140" t="n"/>
-      <c r="H32" s="140" t="n"/>
-      <c r="I32" s="140" t="n"/>
-      <c r="J32" s="141">
+      <c r="C32" s="136" t="n"/>
+      <c r="D32" s="136" t="n"/>
+      <c r="E32" s="136" t="n"/>
+      <c r="F32" s="136" t="n"/>
+      <c r="G32" s="136" t="n"/>
+      <c r="H32" s="136" t="n"/>
+      <c r="I32" s="136" t="n"/>
+      <c r="J32" s="137">
         <f>SUM(C31:I31)</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="17.25" customHeight="1" s="78">
-      <c r="A33" s="102" t="n"/>
+    <row r="33" ht="17.25" customHeight="1" s="77">
+      <c r="A33" s="105" t="n"/>
       <c r="B33" s="47" t="inlineStr">
         <is>
           <t>뇌졸증진단비</t>
         </is>
       </c>
-      <c r="C33" s="150" t="n"/>
-      <c r="D33" s="150" t="n"/>
-      <c r="E33" s="150" t="n"/>
-      <c r="F33" s="150" t="n"/>
-      <c r="G33" s="150" t="n"/>
-      <c r="H33" s="150" t="n"/>
-      <c r="I33" s="150" t="n"/>
-      <c r="J33" s="151">
+      <c r="C33" s="146" t="n"/>
+      <c r="D33" s="146" t="n"/>
+      <c r="E33" s="146" t="n"/>
+      <c r="F33" s="146" t="n"/>
+      <c r="G33" s="146" t="n"/>
+      <c r="H33" s="146" t="n"/>
+      <c r="I33" s="146" t="n"/>
+      <c r="J33" s="147">
         <f>SUM(C32:I32)</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A34" s="102" t="n"/>
+    <row r="34" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A34" s="105" t="n"/>
       <c r="B34" s="50" t="inlineStr">
         <is>
           <t>중대한 뇌졸증</t>
         </is>
       </c>
-      <c r="C34" s="145" t="n"/>
-      <c r="D34" s="145" t="n"/>
-      <c r="E34" s="145" t="n"/>
-      <c r="F34" s="145" t="n"/>
-      <c r="G34" s="145" t="n"/>
-      <c r="H34" s="145" t="n"/>
-      <c r="I34" s="145" t="n"/>
-      <c r="J34" s="152">
+      <c r="C34" s="141" t="n"/>
+      <c r="D34" s="141" t="n"/>
+      <c r="E34" s="141" t="n"/>
+      <c r="F34" s="141" t="n"/>
+      <c r="G34" s="141" t="n"/>
+      <c r="H34" s="141" t="n"/>
+      <c r="I34" s="141" t="n"/>
+      <c r="J34" s="148">
         <f>SUM(C33:I33)</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" s="78">
-      <c r="A35" s="102" t="n"/>
-      <c r="B35" s="174" t="inlineStr">
+    <row r="35" ht="16.5" customHeight="1" s="77">
+      <c r="A35" s="105" t="n"/>
+      <c r="B35" s="95" t="inlineStr">
         <is>
           <t>뇌출혈진단비</t>
         </is>
       </c>
-      <c r="C35" s="175" t="n"/>
-      <c r="D35" s="175" t="n"/>
-      <c r="E35" s="175" t="n"/>
-      <c r="F35" s="175" t="n"/>
-      <c r="G35" s="175" t="n"/>
-      <c r="H35" s="175" t="n"/>
-      <c r="I35" s="175" t="n"/>
-      <c r="J35" s="176">
+      <c r="C35" s="149" t="n"/>
+      <c r="D35" s="149" t="n"/>
+      <c r="E35" s="149" t="n"/>
+      <c r="F35" s="149" t="n"/>
+      <c r="G35" s="149" t="n"/>
+      <c r="H35" s="149" t="n"/>
+      <c r="I35" s="149" t="n"/>
+      <c r="J35" s="150">
         <f>SUM(C34:I34)</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A36" s="102" t="n"/>
-      <c r="B36" s="177" t="inlineStr">
+    <row r="36" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A36" s="105" t="n"/>
+      <c r="B36" s="98" t="inlineStr">
         <is>
           <t>중대한 뇌출혈</t>
         </is>
       </c>
-      <c r="C36" s="178" t="n"/>
-      <c r="D36" s="178" t="n"/>
-      <c r="E36" s="178" t="n"/>
-      <c r="F36" s="178" t="n"/>
-      <c r="G36" s="178" t="n"/>
-      <c r="H36" s="178" t="n"/>
-      <c r="I36" s="178" t="n"/>
-      <c r="J36" s="179">
+      <c r="C36" s="151" t="n"/>
+      <c r="D36" s="151" t="n"/>
+      <c r="E36" s="151" t="n"/>
+      <c r="F36" s="151" t="n"/>
+      <c r="G36" s="151" t="n"/>
+      <c r="H36" s="151" t="n"/>
+      <c r="I36" s="151" t="n"/>
+      <c r="J36" s="152">
         <f>SUM(C35:I35)</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" s="78">
-      <c r="A37" s="102" t="n"/>
+    <row r="37" ht="16.5" customHeight="1" s="77">
+      <c r="A37" s="105" t="n"/>
       <c r="B37" s="52" t="inlineStr">
         <is>
           <t>외상성뇌출혈</t>
         </is>
       </c>
-      <c r="C37" s="157" t="n"/>
-      <c r="D37" s="157" t="n"/>
-      <c r="E37" s="157" t="n"/>
-      <c r="F37" s="157" t="n"/>
-      <c r="G37" s="157" t="n"/>
-      <c r="H37" s="157" t="n"/>
-      <c r="I37" s="157" t="n"/>
-      <c r="J37" s="133">
+      <c r="C37" s="153" t="n"/>
+      <c r="D37" s="153" t="n"/>
+      <c r="E37" s="153" t="n"/>
+      <c r="F37" s="153" t="n"/>
+      <c r="G37" s="153" t="n"/>
+      <c r="H37" s="153" t="n"/>
+      <c r="I37" s="153" t="n"/>
+      <c r="J37" s="129">
         <f>SUM(C35:I35)</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" s="78">
-      <c r="A38" s="102" t="n"/>
+    <row r="38" ht="16.5" customHeight="1" s="77">
+      <c r="A38" s="105" t="n"/>
       <c r="B38" s="54" t="inlineStr">
         <is>
           <t>산정특례뇌혈관</t>
         </is>
       </c>
-      <c r="C38" s="158" t="n"/>
-      <c r="D38" s="158" t="n"/>
-      <c r="E38" s="158" t="n"/>
-      <c r="F38" s="158" t="n"/>
-      <c r="G38" s="158" t="n"/>
-      <c r="H38" s="158" t="n"/>
-      <c r="I38" s="158" t="n"/>
-      <c r="J38" s="139">
+      <c r="C38" s="154" t="n"/>
+      <c r="D38" s="154" t="n"/>
+      <c r="E38" s="154" t="n"/>
+      <c r="F38" s="154" t="n"/>
+      <c r="G38" s="154" t="n"/>
+      <c r="H38" s="154" t="n"/>
+      <c r="I38" s="154" t="n"/>
+      <c r="J38" s="135">
         <f>SUM(C36:I36)</f>
         <v/>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" s="78">
-      <c r="A39" s="102" t="n"/>
+    <row r="39" ht="16.5" customHeight="1" s="77">
+      <c r="A39" s="105" t="n"/>
       <c r="B39" s="54" t="inlineStr">
         <is>
           <t>2대 주요치료비</t>
         </is>
       </c>
-      <c r="C39" s="158" t="n"/>
-      <c r="D39" s="158" t="n"/>
-      <c r="E39" s="158" t="n"/>
-      <c r="F39" s="158" t="n"/>
-      <c r="G39" s="158" t="n"/>
-      <c r="H39" s="158" t="n"/>
-      <c r="I39" s="158" t="n"/>
-      <c r="J39" s="139">
+      <c r="C39" s="154" t="n"/>
+      <c r="D39" s="154" t="n"/>
+      <c r="E39" s="154" t="n"/>
+      <c r="F39" s="154" t="n"/>
+      <c r="G39" s="154" t="n"/>
+      <c r="H39" s="154" t="n"/>
+      <c r="I39" s="154" t="n"/>
+      <c r="J39" s="135">
         <f>SUM(C37:I37)</f>
         <v/>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A40" s="103" t="n"/>
+    <row r="40" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A40" s="106" t="n"/>
       <c r="B40" s="56" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C40" s="134" t="n"/>
-      <c r="D40" s="134" t="n"/>
-      <c r="E40" s="134" t="n"/>
-      <c r="F40" s="134" t="n"/>
-      <c r="G40" s="134" t="n"/>
-      <c r="H40" s="134" t="n"/>
-      <c r="I40" s="134" t="n"/>
-      <c r="J40" s="135">
+      <c r="C40" s="130" t="n"/>
+      <c r="D40" s="130" t="n"/>
+      <c r="E40" s="130" t="n"/>
+      <c r="F40" s="130" t="n"/>
+      <c r="G40" s="130" t="n"/>
+      <c r="H40" s="130" t="n"/>
+      <c r="I40" s="130" t="n"/>
+      <c r="J40" s="131">
         <f>SUM(C37:I37)</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A41" s="101" t="inlineStr">
+    <row r="41" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A41" s="104" t="inlineStr">
         <is>
           <t>심장</t>
         </is>
@@ -2323,147 +2351,147 @@
           <t>협심증</t>
         </is>
       </c>
-      <c r="C41" s="119" t="n"/>
-      <c r="D41" s="119" t="n"/>
-      <c r="E41" s="119" t="n"/>
-      <c r="F41" s="119" t="n"/>
-      <c r="G41" s="119" t="n"/>
-      <c r="H41" s="119" t="n"/>
-      <c r="I41" s="119" t="n"/>
-      <c r="J41" s="137">
+      <c r="C41" s="115" t="n"/>
+      <c r="D41" s="115" t="n"/>
+      <c r="E41" s="115" t="n"/>
+      <c r="F41" s="115" t="n"/>
+      <c r="G41" s="115" t="n"/>
+      <c r="H41" s="115" t="n"/>
+      <c r="I41" s="115" t="n"/>
+      <c r="J41" s="133">
         <f>SUM(C38:I38)</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="16.5" customHeight="1" s="78">
-      <c r="A42" s="102" t="n"/>
+    <row r="42" ht="16.5" customHeight="1" s="77">
+      <c r="A42" s="105" t="n"/>
       <c r="B42" s="31" t="inlineStr">
         <is>
           <t>심부전</t>
         </is>
       </c>
-      <c r="C42" s="149" t="n"/>
-      <c r="D42" s="149" t="n"/>
-      <c r="E42" s="149" t="n"/>
-      <c r="F42" s="149" t="n"/>
-      <c r="G42" s="149" t="n"/>
-      <c r="H42" s="149" t="n"/>
-      <c r="I42" s="149" t="n"/>
-      <c r="J42" s="139">
+      <c r="C42" s="145" t="n"/>
+      <c r="D42" s="145" t="n"/>
+      <c r="E42" s="145" t="n"/>
+      <c r="F42" s="145" t="n"/>
+      <c r="G42" s="145" t="n"/>
+      <c r="H42" s="145" t="n"/>
+      <c r="I42" s="145" t="n"/>
+      <c r="J42" s="135">
         <f>SUM(C39:I39)</f>
         <v/>
       </c>
     </row>
-    <row r="43" ht="17.25" customHeight="1" s="78">
-      <c r="A43" s="102" t="n"/>
+    <row r="43" ht="17.25" customHeight="1" s="77">
+      <c r="A43" s="105" t="n"/>
       <c r="B43" s="31" t="inlineStr">
         <is>
           <t>빈맥</t>
         </is>
       </c>
-      <c r="C43" s="149" t="n"/>
-      <c r="D43" s="149" t="n"/>
-      <c r="E43" s="149" t="n"/>
-      <c r="F43" s="149" t="n"/>
-      <c r="G43" s="149" t="n"/>
-      <c r="H43" s="149" t="n"/>
-      <c r="I43" s="149" t="n"/>
-      <c r="J43" s="139" t="n"/>
-    </row>
-    <row r="44" ht="16.5" customHeight="1" s="78">
-      <c r="A44" s="102" t="n"/>
+      <c r="C43" s="145" t="n"/>
+      <c r="D43" s="145" t="n"/>
+      <c r="E43" s="145" t="n"/>
+      <c r="F43" s="145" t="n"/>
+      <c r="G43" s="145" t="n"/>
+      <c r="H43" s="145" t="n"/>
+      <c r="I43" s="145" t="n"/>
+      <c r="J43" s="135" t="n"/>
+    </row>
+    <row r="44" ht="16.5" customHeight="1" s="77">
+      <c r="A44" s="105" t="n"/>
       <c r="B44" s="31" t="inlineStr">
         <is>
           <t>염증</t>
         </is>
       </c>
-      <c r="C44" s="149" t="n"/>
-      <c r="D44" s="149" t="n"/>
-      <c r="E44" s="149" t="n"/>
-      <c r="F44" s="149" t="n"/>
-      <c r="G44" s="149" t="n"/>
-      <c r="H44" s="149" t="n"/>
-      <c r="I44" s="149" t="n"/>
-      <c r="J44" s="139">
+      <c r="C44" s="145" t="n"/>
+      <c r="D44" s="145" t="n"/>
+      <c r="E44" s="145" t="n"/>
+      <c r="F44" s="145" t="n"/>
+      <c r="G44" s="145" t="n"/>
+      <c r="H44" s="145" t="n"/>
+      <c r="I44" s="145" t="n"/>
+      <c r="J44" s="135">
         <f>SUM(C40:I40)</f>
         <v/>
       </c>
     </row>
-    <row r="45" ht="16.5" customHeight="1" s="78">
-      <c r="A45" s="102" t="n"/>
+    <row r="45" ht="16.5" customHeight="1" s="77">
+      <c r="A45" s="105" t="n"/>
       <c r="B45" s="40" t="inlineStr">
         <is>
           <t>부정맥</t>
         </is>
       </c>
-      <c r="C45" s="159" t="n"/>
-      <c r="D45" s="159" t="n"/>
-      <c r="E45" s="159" t="n"/>
-      <c r="F45" s="159" t="n"/>
-      <c r="G45" s="159" t="n"/>
-      <c r="H45" s="159" t="n"/>
-      <c r="I45" s="159" t="n"/>
-      <c r="J45" s="139">
+      <c r="C45" s="155" t="n"/>
+      <c r="D45" s="155" t="n"/>
+      <c r="E45" s="155" t="n"/>
+      <c r="F45" s="155" t="n"/>
+      <c r="G45" s="155" t="n"/>
+      <c r="H45" s="155" t="n"/>
+      <c r="I45" s="155" t="n"/>
+      <c r="J45" s="135">
         <f>SUM(C41:I41)</f>
         <v/>
       </c>
     </row>
-    <row r="46" ht="17.25" customHeight="1" s="78">
-      <c r="A46" s="102" t="n"/>
-      <c r="B46" s="59" t="inlineStr">
+    <row r="46" ht="17.25" customHeight="1" s="77">
+      <c r="A46" s="105" t="n"/>
+      <c r="B46" s="58" t="inlineStr">
         <is>
           <t>심근병증</t>
         </is>
       </c>
-      <c r="C46" s="90" t="n"/>
-      <c r="D46" s="90" t="n"/>
-      <c r="E46" s="90" t="n"/>
-      <c r="F46" s="90" t="n"/>
-      <c r="G46" s="90" t="n"/>
-      <c r="H46" s="90" t="n"/>
-      <c r="I46" s="90" t="n"/>
-      <c r="J46" s="92" t="n"/>
-    </row>
-    <row r="47" ht="17.25" customHeight="1" s="78">
-      <c r="A47" s="102" t="n"/>
+      <c r="C46" s="89" t="n"/>
+      <c r="D46" s="89" t="n"/>
+      <c r="E46" s="89" t="n"/>
+      <c r="F46" s="89" t="n"/>
+      <c r="G46" s="89" t="n"/>
+      <c r="H46" s="89" t="n"/>
+      <c r="I46" s="89" t="n"/>
+      <c r="J46" s="91" t="n"/>
+    </row>
+    <row r="47" ht="17.25" customHeight="1" s="77">
+      <c r="A47" s="105" t="n"/>
       <c r="B47" s="40" t="inlineStr">
         <is>
           <t>심장판막</t>
         </is>
       </c>
-      <c r="C47" s="91" t="n"/>
-      <c r="D47" s="90" t="n"/>
-      <c r="E47" s="90" t="n"/>
-      <c r="F47" s="90" t="n"/>
-      <c r="G47" s="90" t="n"/>
-      <c r="H47" s="90" t="n"/>
-      <c r="I47" s="90" t="n"/>
-      <c r="J47" s="92" t="n"/>
-    </row>
-    <row r="48" ht="16.5" customHeight="1" s="78">
-      <c r="A48" s="102" t="n"/>
-      <c r="B48" s="59" t="inlineStr">
-        <is>
-          <t>산정특례심장</t>
-        </is>
-      </c>
-      <c r="C48" s="138" t="n"/>
-      <c r="D48" s="138" t="n"/>
-      <c r="E48" s="138" t="n"/>
-      <c r="F48" s="138" t="n"/>
-      <c r="G48" s="138" t="n"/>
-      <c r="H48" s="138" t="n"/>
-      <c r="I48" s="138" t="n"/>
-      <c r="J48" s="139">
-        <f>SUM(C42:I42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="16.5" customHeight="1" s="78">
-      <c r="A49" s="102" t="n"/>
-      <c r="B49" s="66" t="inlineStr">
-        <is>
-          <t>2대 주요치료비</t>
+      <c r="C47" s="90" t="n"/>
+      <c r="D47" s="89" t="n"/>
+      <c r="E47" s="89" t="n"/>
+      <c r="F47" s="89" t="n"/>
+      <c r="G47" s="89" t="n"/>
+      <c r="H47" s="89" t="n"/>
+      <c r="I47" s="89" t="n"/>
+      <c r="J47" s="91" t="n"/>
+    </row>
+    <row r="48" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A48" s="105" t="n"/>
+      <c r="B48" s="81" t="inlineStr">
+        <is>
+          <t>허혈성 진단비</t>
+        </is>
+      </c>
+      <c r="C48" s="128" t="n"/>
+      <c r="D48" s="128" t="n"/>
+      <c r="E48" s="128" t="n"/>
+      <c r="F48" s="128" t="n"/>
+      <c r="G48" s="128" t="n"/>
+      <c r="H48" s="128" t="n"/>
+      <c r="I48" s="128" t="n"/>
+      <c r="J48" s="135">
+        <f>SUM(C44:I44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="16.5" customHeight="1" s="77">
+      <c r="A49" s="105" t="n"/>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>급성심근경색</t>
         </is>
       </c>
       <c r="C49" s="138" t="n"/>
@@ -2473,686 +2501,686 @@
       <c r="G49" s="138" t="n"/>
       <c r="H49" s="138" t="n"/>
       <c r="I49" s="138" t="n"/>
-      <c r="J49" s="139">
-        <f>SUM(C43:I43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A50" s="102" t="n"/>
-      <c r="B50" s="82" t="inlineStr">
-        <is>
-          <t>허혈성 진단비</t>
-        </is>
-      </c>
-      <c r="C50" s="132" t="n"/>
-      <c r="D50" s="132" t="n"/>
-      <c r="E50" s="132" t="n"/>
-      <c r="F50" s="132" t="n"/>
-      <c r="G50" s="132" t="n"/>
-      <c r="H50" s="132" t="n"/>
-      <c r="I50" s="132" t="n"/>
-      <c r="J50" s="139">
+      <c r="J49" s="123">
         <f>SUM(C44:I44)</f>
         <v/>
       </c>
     </row>
-    <row r="51" ht="16.5" customHeight="1" s="78">
-      <c r="A51" s="102" t="n"/>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>급성심근경색</t>
-        </is>
-      </c>
-      <c r="C51" s="142" t="n"/>
-      <c r="D51" s="142" t="n"/>
-      <c r="E51" s="142" t="n"/>
-      <c r="F51" s="142" t="n"/>
-      <c r="G51" s="142" t="n"/>
-      <c r="H51" s="142" t="n"/>
-      <c r="I51" s="142" t="n"/>
-      <c r="J51" s="127">
-        <f>SUM(C44:I44)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A52" s="102" t="n"/>
-      <c r="B52" s="16" t="inlineStr">
+    <row r="50" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A50" s="105" t="n"/>
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>중대한 급성심근</t>
         </is>
       </c>
-      <c r="C52" s="128" t="n"/>
-      <c r="D52" s="128" t="n"/>
-      <c r="E52" s="128" t="n"/>
-      <c r="F52" s="128" t="n"/>
-      <c r="G52" s="128" t="n"/>
-      <c r="H52" s="128" t="n"/>
-      <c r="I52" s="128" t="n"/>
-      <c r="J52" s="152">
+      <c r="C50" s="124" t="n"/>
+      <c r="D50" s="124" t="n"/>
+      <c r="E50" s="124" t="n"/>
+      <c r="F50" s="124" t="n"/>
+      <c r="G50" s="124" t="n"/>
+      <c r="H50" s="124" t="n"/>
+      <c r="I50" s="124" t="n"/>
+      <c r="J50" s="148">
         <f>SUM(C46:I46)</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A53" s="103" t="n"/>
-      <c r="B53" s="63" t="inlineStr">
+    <row r="51" ht="16.5" customHeight="1" s="77">
+      <c r="A51" s="105" t="n"/>
+      <c r="B51" s="54" t="inlineStr">
+        <is>
+          <t>2대 주요치료비</t>
+        </is>
+      </c>
+      <c r="C51" s="154" t="n"/>
+      <c r="D51" s="154" t="n"/>
+      <c r="E51" s="154" t="n"/>
+      <c r="F51" s="154" t="n"/>
+      <c r="G51" s="154" t="n"/>
+      <c r="H51" s="154" t="n"/>
+      <c r="I51" s="154" t="n"/>
+      <c r="J51" s="135">
+        <f>SUM(C49:I49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="16.5" customHeight="1" s="77">
+      <c r="A52" s="105" t="n"/>
+      <c r="B52" s="101" t="inlineStr">
+        <is>
+          <t>산정특례심장</t>
+        </is>
+      </c>
+      <c r="C52" s="145" t="n"/>
+      <c r="D52" s="145" t="n"/>
+      <c r="E52" s="145" t="n"/>
+      <c r="F52" s="145" t="n"/>
+      <c r="G52" s="145" t="n"/>
+      <c r="H52" s="145" t="n"/>
+      <c r="I52" s="145" t="n"/>
+      <c r="J52" s="135">
+        <f>SUM(C50:I50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A53" s="106" t="n"/>
+      <c r="B53" s="62" t="inlineStr">
         <is>
           <t>혈전용해치료비</t>
         </is>
       </c>
-      <c r="C53" s="130" t="n"/>
-      <c r="D53" s="130" t="n"/>
-      <c r="E53" s="130" t="n"/>
-      <c r="F53" s="130" t="n"/>
-      <c r="G53" s="130" t="n"/>
-      <c r="H53" s="130" t="n"/>
-      <c r="I53" s="130" t="n"/>
-      <c r="J53" s="131">
+      <c r="C53" s="126" t="n"/>
+      <c r="D53" s="126" t="n"/>
+      <c r="E53" s="126" t="n"/>
+      <c r="F53" s="126" t="n"/>
+      <c r="G53" s="126" t="n"/>
+      <c r="H53" s="126" t="n"/>
+      <c r="I53" s="126" t="n"/>
+      <c r="J53" s="127">
         <f>SUM(C47:I47)</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A54" s="101" t="inlineStr">
+    <row r="54" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A54" s="104" t="inlineStr">
         <is>
           <t>일당</t>
         </is>
       </c>
-      <c r="B54" s="104" t="inlineStr">
+      <c r="B54" s="109" t="inlineStr">
         <is>
           <t>질병일당</t>
         </is>
       </c>
-      <c r="C54" s="136" t="n"/>
-      <c r="D54" s="136" t="n"/>
-      <c r="E54" s="136" t="n"/>
-      <c r="F54" s="136" t="n"/>
-      <c r="G54" s="136" t="n"/>
-      <c r="H54" s="136" t="n"/>
-      <c r="I54" s="136" t="n"/>
-      <c r="J54" s="137">
+      <c r="C54" s="132" t="n"/>
+      <c r="D54" s="132" t="n"/>
+      <c r="E54" s="132" t="n"/>
+      <c r="F54" s="132" t="n"/>
+      <c r="G54" s="132" t="n"/>
+      <c r="H54" s="132" t="n"/>
+      <c r="I54" s="132" t="n"/>
+      <c r="J54" s="133">
+        <f>SUM(#REF!)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="16.5" customHeight="1" s="77">
+      <c r="A55" s="105" t="n"/>
+      <c r="B55" s="63" t="inlineStr">
+        <is>
+          <t>질병수술일당</t>
+        </is>
+      </c>
+      <c r="C55" s="155" t="n"/>
+      <c r="D55" s="155" t="n"/>
+      <c r="E55" s="155" t="n"/>
+      <c r="F55" s="155" t="n"/>
+      <c r="G55" s="155" t="n"/>
+      <c r="H55" s="155" t="n"/>
+      <c r="I55" s="155" t="n"/>
+      <c r="J55" s="135">
+        <f>SUM(#REF!)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="16.5" customHeight="1" s="77">
+      <c r="A56" s="105" t="n"/>
+      <c r="B56" s="63" t="inlineStr">
+        <is>
+          <t>종합병원 질병입원일당</t>
+        </is>
+      </c>
+      <c r="C56" s="155" t="n"/>
+      <c r="D56" s="155" t="n"/>
+      <c r="E56" s="155" t="n"/>
+      <c r="F56" s="155" t="n"/>
+      <c r="G56" s="155" t="n"/>
+      <c r="H56" s="155" t="n"/>
+      <c r="I56" s="155" t="n"/>
+      <c r="J56" s="135">
         <f>SUM(C48:I48)</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="16.5" customHeight="1" s="78">
-      <c r="A55" s="102" t="n"/>
-      <c r="B55" s="64" t="inlineStr">
-        <is>
-          <t>질병수술일당</t>
-        </is>
-      </c>
-      <c r="C55" s="159" t="n"/>
-      <c r="D55" s="159" t="n"/>
-      <c r="E55" s="159" t="n"/>
-      <c r="F55" s="159" t="n"/>
-      <c r="G55" s="159" t="n"/>
-      <c r="H55" s="159" t="n"/>
-      <c r="I55" s="159" t="n"/>
-      <c r="J55" s="139">
+    <row r="57" ht="16.5" customHeight="1" s="77">
+      <c r="A57" s="105" t="n"/>
+      <c r="B57" s="63" t="inlineStr">
+        <is>
+          <t>종합병원 상해입원일당</t>
+        </is>
+      </c>
+      <c r="C57" s="155" t="n"/>
+      <c r="D57" s="155" t="n"/>
+      <c r="E57" s="155" t="n"/>
+      <c r="F57" s="155" t="n"/>
+      <c r="G57" s="155" t="n"/>
+      <c r="H57" s="155" t="n"/>
+      <c r="I57" s="155" t="n"/>
+      <c r="J57" s="135" t="n"/>
+    </row>
+    <row r="58" ht="16.5" customHeight="1" s="77">
+      <c r="A58" s="105" t="n"/>
+      <c r="B58" s="58" t="inlineStr">
+        <is>
+          <t>상해일당</t>
+        </is>
+      </c>
+      <c r="C58" s="134" t="n"/>
+      <c r="D58" s="134" t="n"/>
+      <c r="E58" s="134" t="n"/>
+      <c r="F58" s="134" t="n"/>
+      <c r="G58" s="134" t="n"/>
+      <c r="H58" s="134" t="n"/>
+      <c r="I58" s="134" t="n"/>
+      <c r="J58" s="135">
         <f>SUM(C49:I49)</f>
         <v/>
       </c>
     </row>
-    <row r="56" ht="16.5" customHeight="1" s="78">
-      <c r="A56" s="102" t="n"/>
-      <c r="B56" s="64" t="inlineStr">
-        <is>
-          <t>종합병원 질병입원일당</t>
-        </is>
-      </c>
-      <c r="C56" s="159" t="n"/>
-      <c r="D56" s="159" t="n"/>
-      <c r="E56" s="159" t="n"/>
-      <c r="F56" s="159" t="n"/>
-      <c r="G56" s="159" t="n"/>
-      <c r="H56" s="159" t="n"/>
-      <c r="I56" s="159" t="n"/>
-      <c r="J56" s="139">
+    <row r="59" ht="16.5" customHeight="1" s="77">
+      <c r="A59" s="105" t="n"/>
+      <c r="B59" s="58" t="inlineStr">
+        <is>
+          <t>상해수술일당</t>
+        </is>
+      </c>
+      <c r="C59" s="134" t="n"/>
+      <c r="D59" s="134" t="n"/>
+      <c r="E59" s="134" t="n"/>
+      <c r="F59" s="134" t="n"/>
+      <c r="G59" s="134" t="n"/>
+      <c r="H59" s="134" t="n"/>
+      <c r="I59" s="134" t="n"/>
+      <c r="J59" s="135" t="n"/>
+    </row>
+    <row r="60" ht="16.5" customHeight="1" s="77">
+      <c r="A60" s="105" t="n"/>
+      <c r="B60" s="31" t="inlineStr">
+        <is>
+          <t>간병인</t>
+        </is>
+      </c>
+      <c r="C60" s="134" t="n"/>
+      <c r="D60" s="134" t="n"/>
+      <c r="E60" s="134" t="n"/>
+      <c r="F60" s="134" t="n"/>
+      <c r="G60" s="134" t="n"/>
+      <c r="H60" s="134" t="n"/>
+      <c r="I60" s="134" t="n"/>
+      <c r="J60" s="135">
         <f>SUM(C50:I50)</f>
         <v/>
       </c>
     </row>
-    <row r="57" ht="16.5" customHeight="1" s="78">
-      <c r="A57" s="102" t="n"/>
-      <c r="B57" s="64" t="inlineStr">
-        <is>
-          <t>종합병원 상해입원일당</t>
-        </is>
-      </c>
-      <c r="C57" s="159" t="n"/>
-      <c r="D57" s="159" t="n"/>
-      <c r="E57" s="159" t="n"/>
-      <c r="F57" s="159" t="n"/>
-      <c r="G57" s="159" t="n"/>
-      <c r="H57" s="159" t="n"/>
-      <c r="I57" s="159" t="n"/>
-      <c r="J57" s="139" t="n"/>
-    </row>
-    <row r="58" ht="16.5" customHeight="1" s="78">
-      <c r="A58" s="102" t="n"/>
-      <c r="B58" s="59" t="inlineStr">
-        <is>
-          <t>상해일당</t>
-        </is>
-      </c>
-      <c r="C58" s="138" t="n"/>
-      <c r="D58" s="138" t="n"/>
-      <c r="E58" s="138" t="n"/>
-      <c r="F58" s="138" t="n"/>
-      <c r="G58" s="138" t="n"/>
-      <c r="H58" s="138" t="n"/>
-      <c r="I58" s="138" t="n"/>
-      <c r="J58" s="139">
-        <f>SUM(C51:I51)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" ht="16.5" customHeight="1" s="78">
-      <c r="A59" s="102" t="n"/>
-      <c r="B59" s="59" t="inlineStr">
-        <is>
-          <t>상해수술일당</t>
-        </is>
-      </c>
-      <c r="C59" s="138" t="n"/>
-      <c r="D59" s="138" t="n"/>
-      <c r="E59" s="138" t="n"/>
-      <c r="F59" s="138" t="n"/>
-      <c r="G59" s="138" t="n"/>
-      <c r="H59" s="138" t="n"/>
-      <c r="I59" s="138" t="n"/>
-      <c r="J59" s="139" t="n"/>
-    </row>
-    <row r="60" ht="16.5" customHeight="1" s="78">
-      <c r="A60" s="102" t="n"/>
-      <c r="B60" s="31" t="inlineStr">
-        <is>
-          <t>간병인</t>
-        </is>
-      </c>
-      <c r="C60" s="138" t="n"/>
-      <c r="D60" s="138" t="n"/>
-      <c r="E60" s="138" t="n"/>
-      <c r="F60" s="138" t="n"/>
-      <c r="G60" s="138" t="n"/>
-      <c r="H60" s="138" t="n"/>
-      <c r="I60" s="138" t="n"/>
-      <c r="J60" s="139">
-        <f>SUM(C52:I52)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61" ht="16.5" customHeight="1" s="78">
-      <c r="A61" s="102" t="n"/>
+    <row r="61" ht="16.5" customHeight="1" s="77">
+      <c r="A61" s="105" t="n"/>
       <c r="B61" s="31" t="inlineStr">
         <is>
           <t>간병인지원일당</t>
         </is>
       </c>
-      <c r="C61" s="138" t="n"/>
-      <c r="D61" s="138" t="n"/>
-      <c r="E61" s="138" t="n"/>
-      <c r="F61" s="138" t="n"/>
-      <c r="G61" s="138" t="n"/>
-      <c r="H61" s="138" t="n"/>
-      <c r="I61" s="138" t="n"/>
-      <c r="J61" s="139" t="n"/>
-    </row>
-    <row r="62" ht="16.5" customHeight="1" s="78">
-      <c r="A62" s="102" t="n"/>
+      <c r="C61" s="134" t="n"/>
+      <c r="D61" s="134" t="n"/>
+      <c r="E61" s="134" t="n"/>
+      <c r="F61" s="134" t="n"/>
+      <c r="G61" s="134" t="n"/>
+      <c r="H61" s="134" t="n"/>
+      <c r="I61" s="134" t="n"/>
+      <c r="J61" s="135" t="n"/>
+    </row>
+    <row r="62" ht="16.5" customHeight="1" s="77">
+      <c r="A62" s="105" t="n"/>
       <c r="B62" s="31" t="inlineStr">
         <is>
           <t>간호통합병동</t>
         </is>
       </c>
-      <c r="C62" s="138" t="n"/>
-      <c r="D62" s="138" t="n"/>
-      <c r="E62" s="138" t="n"/>
-      <c r="F62" s="138" t="n"/>
-      <c r="G62" s="138" t="n"/>
-      <c r="H62" s="138" t="n"/>
-      <c r="I62" s="138" t="n"/>
-      <c r="J62" s="139">
+      <c r="C62" s="134" t="n"/>
+      <c r="D62" s="134" t="n"/>
+      <c r="E62" s="134" t="n"/>
+      <c r="F62" s="134" t="n"/>
+      <c r="G62" s="134" t="n"/>
+      <c r="H62" s="134" t="n"/>
+      <c r="I62" s="134" t="n"/>
+      <c r="J62" s="135">
         <f>SUM(C53:I53)</f>
         <v/>
       </c>
     </row>
-    <row r="63" ht="16.5" customHeight="1" s="78">
-      <c r="A63" s="102" t="n"/>
-      <c r="B63" s="65" t="inlineStr">
+    <row r="63" ht="16.5" customHeight="1" s="77">
+      <c r="A63" s="105" t="n"/>
+      <c r="B63" s="64" t="inlineStr">
         <is>
           <t>1인실 종합병원</t>
         </is>
       </c>
-      <c r="C63" s="138" t="n"/>
-      <c r="D63" s="138" t="n"/>
-      <c r="E63" s="138" t="n"/>
-      <c r="F63" s="138" t="n"/>
-      <c r="G63" s="138" t="n"/>
-      <c r="H63" s="138" t="n"/>
-      <c r="I63" s="138" t="n"/>
-      <c r="J63" s="139">
+      <c r="C63" s="134" t="n"/>
+      <c r="D63" s="134" t="n"/>
+      <c r="E63" s="134" t="n"/>
+      <c r="F63" s="134" t="n"/>
+      <c r="G63" s="134" t="n"/>
+      <c r="H63" s="134" t="n"/>
+      <c r="I63" s="134" t="n"/>
+      <c r="J63" s="135">
         <f>SUM(C54:I54)</f>
         <v/>
       </c>
     </row>
-    <row r="64" ht="17.25" customHeight="1" s="78">
-      <c r="A64" s="102" t="n"/>
-      <c r="B64" s="65" t="inlineStr">
+    <row r="64" ht="17.25" customHeight="1" s="77">
+      <c r="A64" s="105" t="n"/>
+      <c r="B64" s="64" t="inlineStr">
         <is>
           <t>1인실 상급병원</t>
         </is>
       </c>
-      <c r="C64" s="138" t="n"/>
-      <c r="D64" s="138" t="n"/>
-      <c r="E64" s="138" t="n"/>
-      <c r="F64" s="138" t="n"/>
-      <c r="G64" s="138" t="n"/>
-      <c r="H64" s="138" t="n"/>
-      <c r="I64" s="138" t="n"/>
-      <c r="J64" s="139">
+      <c r="C64" s="134" t="n"/>
+      <c r="D64" s="134" t="n"/>
+      <c r="E64" s="134" t="n"/>
+      <c r="F64" s="134" t="n"/>
+      <c r="G64" s="134" t="n"/>
+      <c r="H64" s="134" t="n"/>
+      <c r="I64" s="134" t="n"/>
+      <c r="J64" s="135">
         <f>SUM(C55:I55)</f>
         <v/>
       </c>
     </row>
-    <row r="65" ht="17.25" customHeight="1" s="78">
-      <c r="A65" s="102" t="n"/>
+    <row r="65" ht="17.25" customHeight="1" s="77">
+      <c r="A65" s="105" t="n"/>
       <c r="B65" s="31" t="inlineStr">
         <is>
           <t>질병중환자실</t>
         </is>
       </c>
-      <c r="C65" s="138" t="n"/>
-      <c r="D65" s="138" t="n"/>
-      <c r="E65" s="138" t="n"/>
-      <c r="F65" s="138" t="n"/>
-      <c r="G65" s="138" t="n"/>
-      <c r="H65" s="138" t="n"/>
-      <c r="I65" s="138" t="n"/>
-      <c r="J65" s="139">
+      <c r="C65" s="134" t="n"/>
+      <c r="D65" s="134" t="n"/>
+      <c r="E65" s="134" t="n"/>
+      <c r="F65" s="134" t="n"/>
+      <c r="G65" s="134" t="n"/>
+      <c r="H65" s="134" t="n"/>
+      <c r="I65" s="134" t="n"/>
+      <c r="J65" s="135">
         <f>SUM(C56:I56)</f>
         <v/>
       </c>
     </row>
-    <row r="66" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A66" s="103" t="n"/>
+    <row r="66" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A66" s="106" t="n"/>
       <c r="B66" s="25" t="inlineStr">
         <is>
           <t>상해중환자실</t>
         </is>
       </c>
-      <c r="C66" s="134" t="n"/>
-      <c r="D66" s="134" t="n"/>
-      <c r="E66" s="134" t="n"/>
-      <c r="F66" s="134" t="n"/>
-      <c r="G66" s="134" t="n"/>
-      <c r="H66" s="134" t="n"/>
-      <c r="I66" s="134" t="n"/>
-      <c r="J66" s="135">
+      <c r="C66" s="130" t="n"/>
+      <c r="D66" s="130" t="n"/>
+      <c r="E66" s="130" t="n"/>
+      <c r="F66" s="130" t="n"/>
+      <c r="G66" s="130" t="n"/>
+      <c r="H66" s="130" t="n"/>
+      <c r="I66" s="130" t="n"/>
+      <c r="J66" s="131">
         <f>SUM(C57:I57)</f>
         <v/>
       </c>
     </row>
-    <row r="67" ht="16.5" customHeight="1" s="78">
-      <c r="A67" s="101" t="inlineStr">
+    <row r="67" ht="16.5" customHeight="1" s="77">
+      <c r="A67" s="104" t="inlineStr">
         <is>
           <t>수술</t>
         </is>
       </c>
-      <c r="B67" s="104" t="inlineStr">
+      <c r="B67" s="109" t="inlineStr">
         <is>
           <t>상해수술비</t>
         </is>
       </c>
-      <c r="C67" s="136" t="n"/>
-      <c r="D67" s="136" t="n"/>
-      <c r="E67" s="136" t="n"/>
-      <c r="F67" s="136" t="n"/>
-      <c r="G67" s="136" t="n"/>
-      <c r="H67" s="136" t="n"/>
-      <c r="I67" s="136" t="n"/>
-      <c r="J67" s="137">
+      <c r="C67" s="132" t="n"/>
+      <c r="D67" s="132" t="n"/>
+      <c r="E67" s="132" t="n"/>
+      <c r="F67" s="132" t="n"/>
+      <c r="G67" s="132" t="n"/>
+      <c r="H67" s="132" t="n"/>
+      <c r="I67" s="132" t="n"/>
+      <c r="J67" s="133">
         <f>SUM(C58:I58)</f>
         <v/>
       </c>
     </row>
-    <row r="68" ht="16.5" customHeight="1" s="78">
-      <c r="A68" s="102" t="n"/>
-      <c r="B68" s="64" t="inlineStr">
+    <row r="68" ht="16.5" customHeight="1" s="77">
+      <c r="A68" s="105" t="n"/>
+      <c r="B68" s="63" t="inlineStr">
         <is>
           <t>중대한상해수술비</t>
         </is>
       </c>
-      <c r="C68" s="159" t="n"/>
-      <c r="D68" s="159" t="n"/>
-      <c r="E68" s="159" t="n"/>
-      <c r="F68" s="159" t="n"/>
-      <c r="G68" s="159" t="n"/>
-      <c r="H68" s="159" t="n"/>
-      <c r="I68" s="159" t="n"/>
-      <c r="J68" s="139">
+      <c r="C68" s="155" t="n"/>
+      <c r="D68" s="155" t="n"/>
+      <c r="E68" s="155" t="n"/>
+      <c r="F68" s="155" t="n"/>
+      <c r="G68" s="155" t="n"/>
+      <c r="H68" s="155" t="n"/>
+      <c r="I68" s="155" t="n"/>
+      <c r="J68" s="135">
         <f>SUM(C59:I59)</f>
         <v/>
       </c>
     </row>
-    <row r="69" ht="16.5" customHeight="1" s="78">
-      <c r="A69" s="102" t="n"/>
-      <c r="B69" s="59" t="inlineStr">
+    <row r="69" ht="16.5" customHeight="1" s="77">
+      <c r="A69" s="105" t="n"/>
+      <c r="B69" s="58" t="inlineStr">
         <is>
           <t>상해 종수술비(1-3종)</t>
         </is>
       </c>
-      <c r="C69" s="159" t="n"/>
-      <c r="D69" s="159" t="n"/>
-      <c r="E69" s="159" t="n"/>
-      <c r="F69" s="160" t="n"/>
-      <c r="G69" s="159" t="n"/>
-      <c r="H69" s="159" t="n"/>
-      <c r="I69" s="159" t="n"/>
-      <c r="J69" s="139" t="n"/>
-    </row>
-    <row r="70" ht="17.25" customHeight="1" s="78">
-      <c r="A70" s="102" t="n"/>
-      <c r="B70" s="59" t="inlineStr">
+      <c r="C69" s="155" t="n"/>
+      <c r="D69" s="155" t="n"/>
+      <c r="E69" s="155" t="n"/>
+      <c r="F69" s="156" t="n"/>
+      <c r="G69" s="155" t="n"/>
+      <c r="H69" s="155" t="n"/>
+      <c r="I69" s="155" t="n"/>
+      <c r="J69" s="135" t="n"/>
+    </row>
+    <row r="70" ht="17.25" customHeight="1" s="77">
+      <c r="A70" s="105" t="n"/>
+      <c r="B70" s="58" t="inlineStr">
         <is>
           <t>상해 종수술비(1-5종)</t>
         </is>
       </c>
-      <c r="C70" s="159" t="n"/>
-      <c r="D70" s="159" t="n"/>
-      <c r="E70" s="159" t="n"/>
-      <c r="F70" s="160" t="n"/>
-      <c r="G70" s="159" t="n"/>
-      <c r="H70" s="159" t="n"/>
-      <c r="I70" s="159" t="n"/>
-      <c r="J70" s="139" t="inlineStr">
+      <c r="C70" s="155" t="n"/>
+      <c r="D70" s="155" t="n"/>
+      <c r="E70" s="155" t="n"/>
+      <c r="F70" s="156" t="n"/>
+      <c r="G70" s="155" t="n"/>
+      <c r="H70" s="155" t="n"/>
+      <c r="I70" s="155" t="n"/>
+      <c r="J70" s="135" t="inlineStr">
         <is>
           <t>/ / / / /</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="16.5" customHeight="1" s="78">
-      <c r="A71" s="102" t="n"/>
-      <c r="B71" s="59" t="inlineStr">
+    <row r="71" ht="16.5" customHeight="1" s="77">
+      <c r="A71" s="105" t="n"/>
+      <c r="B71" s="58" t="inlineStr">
         <is>
           <t>상해 종수술비(1-8종)</t>
         </is>
       </c>
-      <c r="C71" s="159" t="n"/>
-      <c r="D71" s="159" t="n"/>
-      <c r="E71" s="159" t="n"/>
-      <c r="F71" s="160" t="n"/>
-      <c r="G71" s="159" t="n"/>
-      <c r="H71" s="159" t="n"/>
-      <c r="I71" s="159" t="n"/>
-      <c r="J71" s="139" t="n"/>
-    </row>
-    <row r="72" ht="16.5" customHeight="1" s="78">
-      <c r="A72" s="102" t="n"/>
-      <c r="B72" s="59" t="inlineStr">
+      <c r="C71" s="155" t="n"/>
+      <c r="D71" s="155" t="n"/>
+      <c r="E71" s="155" t="n"/>
+      <c r="F71" s="156" t="n"/>
+      <c r="G71" s="155" t="n"/>
+      <c r="H71" s="155" t="n"/>
+      <c r="I71" s="155" t="n"/>
+      <c r="J71" s="135" t="n"/>
+    </row>
+    <row r="72" ht="16.5" customHeight="1" s="77">
+      <c r="A72" s="105" t="n"/>
+      <c r="B72" s="58" t="inlineStr">
         <is>
           <t>창상봉합술</t>
         </is>
       </c>
-      <c r="C72" s="138" t="n"/>
-      <c r="D72" s="138" t="n"/>
-      <c r="E72" s="138" t="n"/>
-      <c r="F72" s="161" t="n"/>
-      <c r="G72" s="138" t="n"/>
-      <c r="H72" s="138" t="n"/>
-      <c r="I72" s="138" t="n"/>
-      <c r="J72" s="139">
+      <c r="C72" s="134" t="n"/>
+      <c r="D72" s="134" t="n"/>
+      <c r="E72" s="134" t="n"/>
+      <c r="F72" s="157" t="n"/>
+      <c r="G72" s="134" t="n"/>
+      <c r="H72" s="134" t="n"/>
+      <c r="I72" s="134" t="n"/>
+      <c r="J72" s="135">
         <f>SUM(C61:I61)</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="16.5" customHeight="1" s="78">
-      <c r="A73" s="102" t="n"/>
-      <c r="B73" s="59" t="inlineStr">
+    <row r="73" ht="16.5" customHeight="1" s="77">
+      <c r="A73" s="105" t="n"/>
+      <c r="B73" s="58" t="inlineStr">
         <is>
           <t>골절수술비</t>
         </is>
       </c>
-      <c r="C73" s="138" t="n"/>
-      <c r="D73" s="138" t="n"/>
-      <c r="E73" s="138" t="n"/>
-      <c r="F73" s="161" t="n"/>
-      <c r="G73" s="138" t="n"/>
-      <c r="H73" s="138" t="n"/>
-      <c r="I73" s="138" t="n"/>
-      <c r="J73" s="139">
+      <c r="C73" s="134" t="n"/>
+      <c r="D73" s="134" t="n"/>
+      <c r="E73" s="134" t="n"/>
+      <c r="F73" s="157" t="n"/>
+      <c r="G73" s="134" t="n"/>
+      <c r="H73" s="134" t="n"/>
+      <c r="I73" s="134" t="n"/>
+      <c r="J73" s="135">
         <f>SUM(C62:I62)</f>
         <v/>
       </c>
     </row>
-    <row r="74" ht="16.5" customHeight="1" s="78">
-      <c r="A74" s="102" t="n"/>
-      <c r="B74" s="66" t="inlineStr">
+    <row r="74" ht="16.5" customHeight="1" s="77">
+      <c r="A74" s="105" t="n"/>
+      <c r="B74" s="65" t="inlineStr">
         <is>
           <t>5대골절수술비</t>
         </is>
       </c>
-      <c r="C74" s="138" t="n"/>
-      <c r="D74" s="138" t="n"/>
-      <c r="E74" s="138" t="n"/>
-      <c r="F74" s="161" t="n"/>
-      <c r="G74" s="138" t="n"/>
-      <c r="H74" s="138" t="n"/>
-      <c r="I74" s="138" t="n"/>
-      <c r="J74" s="139">
+      <c r="C74" s="134" t="n"/>
+      <c r="D74" s="134" t="n"/>
+      <c r="E74" s="134" t="n"/>
+      <c r="F74" s="157" t="n"/>
+      <c r="G74" s="134" t="n"/>
+      <c r="H74" s="134" t="n"/>
+      <c r="I74" s="134" t="n"/>
+      <c r="J74" s="135">
         <f>SUM(C63:I63)</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A75" s="102" t="n"/>
+    <row r="75" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A75" s="105" t="n"/>
       <c r="B75" s="56" t="inlineStr">
         <is>
           <t>화상수술비</t>
         </is>
       </c>
-      <c r="C75" s="134" t="n"/>
-      <c r="D75" s="134" t="n"/>
-      <c r="E75" s="134" t="n"/>
-      <c r="F75" s="162" t="n"/>
-      <c r="G75" s="134" t="n"/>
-      <c r="H75" s="134" t="n"/>
-      <c r="I75" s="134" t="n"/>
-      <c r="J75" s="135">
+      <c r="C75" s="130" t="n"/>
+      <c r="D75" s="130" t="n"/>
+      <c r="E75" s="130" t="n"/>
+      <c r="F75" s="158" t="n"/>
+      <c r="G75" s="130" t="n"/>
+      <c r="H75" s="130" t="n"/>
+      <c r="I75" s="130" t="n"/>
+      <c r="J75" s="131">
         <f>SUM(C64:I64)</f>
         <v/>
       </c>
     </row>
-    <row r="76" ht="16.5" customHeight="1" s="78">
-      <c r="A76" s="102" t="n"/>
-      <c r="B76" s="64" t="inlineStr">
+    <row r="76" ht="16.5" customHeight="1" s="77">
+      <c r="A76" s="105" t="n"/>
+      <c r="B76" s="63" t="inlineStr">
         <is>
           <t>질병수술비</t>
         </is>
       </c>
-      <c r="C76" s="159" t="n"/>
-      <c r="D76" s="159" t="n"/>
-      <c r="E76" s="159" t="n"/>
-      <c r="F76" s="163" t="n"/>
-      <c r="G76" s="159" t="n"/>
-      <c r="H76" s="159" t="n"/>
-      <c r="I76" s="164" t="n"/>
-      <c r="J76" s="133">
+      <c r="C76" s="155" t="n"/>
+      <c r="D76" s="155" t="n"/>
+      <c r="E76" s="155" t="n"/>
+      <c r="F76" s="159" t="n"/>
+      <c r="G76" s="155" t="n"/>
+      <c r="H76" s="155" t="n"/>
+      <c r="I76" s="160" t="n"/>
+      <c r="J76" s="129">
         <f>SUM(C65:I65)</f>
         <v/>
       </c>
     </row>
-    <row r="77" ht="16.5" customHeight="1" s="78">
-      <c r="A77" s="102" t="n"/>
-      <c r="B77" s="59" t="inlineStr">
+    <row r="77" ht="16.5" customHeight="1" s="77">
+      <c r="A77" s="105" t="n"/>
+      <c r="B77" s="58" t="inlineStr">
         <is>
           <t>질병 종수술비(1-3종)</t>
         </is>
       </c>
-      <c r="C77" s="138" t="n"/>
-      <c r="D77" s="138" t="n"/>
-      <c r="E77" s="138" t="n"/>
-      <c r="F77" s="165" t="n"/>
-      <c r="G77" s="138" t="n"/>
-      <c r="H77" s="138" t="n"/>
-      <c r="I77" s="138" t="n"/>
-      <c r="J77" s="139" t="n"/>
-    </row>
-    <row r="78" ht="17.25" customHeight="1" s="78">
-      <c r="A78" s="102" t="n"/>
-      <c r="B78" s="59" t="inlineStr">
+      <c r="C77" s="134" t="n"/>
+      <c r="D77" s="134" t="n"/>
+      <c r="E77" s="134" t="n"/>
+      <c r="F77" s="161" t="n"/>
+      <c r="G77" s="134" t="n"/>
+      <c r="H77" s="134" t="n"/>
+      <c r="I77" s="134" t="n"/>
+      <c r="J77" s="135" t="n"/>
+    </row>
+    <row r="78" ht="17.25" customHeight="1" s="77">
+      <c r="A78" s="105" t="n"/>
+      <c r="B78" s="58" t="inlineStr">
         <is>
           <t>질병 종수술비(1-5종)</t>
         </is>
       </c>
-      <c r="C78" s="138" t="n"/>
-      <c r="D78" s="138" t="n"/>
-      <c r="E78" s="138" t="n"/>
-      <c r="F78" s="165" t="n"/>
-      <c r="G78" s="138" t="n"/>
-      <c r="H78" s="138" t="n"/>
-      <c r="I78" s="138" t="n"/>
-      <c r="J78" s="139" t="inlineStr">
+      <c r="C78" s="134" t="n"/>
+      <c r="D78" s="134" t="n"/>
+      <c r="E78" s="134" t="n"/>
+      <c r="F78" s="161" t="n"/>
+      <c r="G78" s="134" t="n"/>
+      <c r="H78" s="134" t="n"/>
+      <c r="I78" s="134" t="n"/>
+      <c r="J78" s="135" t="inlineStr">
         <is>
           <t>/ / / / /</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="16.5" customHeight="1" s="78">
-      <c r="A79" s="102" t="n"/>
-      <c r="B79" s="59" t="inlineStr">
+    <row r="79" ht="16.5" customHeight="1" s="77">
+      <c r="A79" s="105" t="n"/>
+      <c r="B79" s="58" t="inlineStr">
         <is>
           <t>질병 종수술비(1-8종)</t>
         </is>
       </c>
-      <c r="C79" s="138" t="n"/>
-      <c r="D79" s="138" t="n"/>
-      <c r="E79" s="138" t="n"/>
-      <c r="F79" s="165" t="n"/>
-      <c r="G79" s="138" t="n"/>
-      <c r="H79" s="138" t="n"/>
-      <c r="I79" s="138" t="n"/>
-      <c r="J79" s="139" t="n"/>
-    </row>
-    <row r="80" ht="16.5" customHeight="1" s="78">
-      <c r="A80" s="102" t="n"/>
-      <c r="B80" s="68" t="inlineStr">
+      <c r="C79" s="134" t="n"/>
+      <c r="D79" s="134" t="n"/>
+      <c r="E79" s="134" t="n"/>
+      <c r="F79" s="161" t="n"/>
+      <c r="G79" s="134" t="n"/>
+      <c r="H79" s="134" t="n"/>
+      <c r="I79" s="134" t="n"/>
+      <c r="J79" s="135" t="n"/>
+    </row>
+    <row r="80" ht="16.5" customHeight="1" s="77">
+      <c r="A80" s="105" t="n"/>
+      <c r="B80" s="67" t="inlineStr">
         <is>
           <t>뇌혈관수술비</t>
         </is>
       </c>
-      <c r="C80" s="166" t="n"/>
-      <c r="D80" s="166" t="n"/>
-      <c r="E80" s="166" t="n"/>
-      <c r="F80" s="166" t="n"/>
-      <c r="G80" s="166" t="n"/>
-      <c r="H80" s="166" t="n"/>
-      <c r="I80" s="166" t="n"/>
-      <c r="J80" s="139">
+      <c r="C80" s="162" t="n"/>
+      <c r="D80" s="162" t="n"/>
+      <c r="E80" s="162" t="n"/>
+      <c r="F80" s="162" t="n"/>
+      <c r="G80" s="162" t="n"/>
+      <c r="H80" s="162" t="n"/>
+      <c r="I80" s="162" t="n"/>
+      <c r="J80" s="135">
         <f>SUM(C67:I67)</f>
         <v/>
       </c>
     </row>
-    <row r="81" ht="17.25" customHeight="1" s="78">
-      <c r="A81" s="102" t="n"/>
-      <c r="B81" s="68" t="inlineStr">
+    <row r="81" ht="17.25" customHeight="1" s="77">
+      <c r="A81" s="105" t="n"/>
+      <c r="B81" s="67" t="inlineStr">
         <is>
           <t>허혈성수술비</t>
         </is>
       </c>
-      <c r="C81" s="166" t="n"/>
-      <c r="D81" s="166" t="n"/>
-      <c r="E81" s="166" t="n"/>
-      <c r="F81" s="166" t="n"/>
-      <c r="G81" s="166" t="n"/>
-      <c r="H81" s="166" t="n"/>
-      <c r="I81" s="166" t="n"/>
-      <c r="J81" s="139">
+      <c r="C81" s="162" t="n"/>
+      <c r="D81" s="162" t="n"/>
+      <c r="E81" s="162" t="n"/>
+      <c r="F81" s="162" t="n"/>
+      <c r="G81" s="162" t="n"/>
+      <c r="H81" s="162" t="n"/>
+      <c r="I81" s="162" t="n"/>
+      <c r="J81" s="135">
         <f>SUM(C68:I68)</f>
         <v/>
       </c>
     </row>
-    <row r="82" ht="17.25" customHeight="1" s="78">
-      <c r="A82" s="102" t="n"/>
-      <c r="B82" s="68" t="inlineStr">
+    <row r="82" ht="17.25" customHeight="1" s="77">
+      <c r="A82" s="105" t="n"/>
+      <c r="B82" s="67" t="inlineStr">
         <is>
           <t>심장수술비</t>
         </is>
       </c>
-      <c r="C82" s="166" t="n"/>
-      <c r="D82" s="166" t="n"/>
-      <c r="E82" s="166" t="n"/>
-      <c r="F82" s="166" t="n"/>
-      <c r="G82" s="166" t="n"/>
-      <c r="H82" s="166" t="n"/>
-      <c r="I82" s="166" t="n"/>
-      <c r="J82" s="139">
+      <c r="C82" s="162" t="n"/>
+      <c r="D82" s="162" t="n"/>
+      <c r="E82" s="162" t="n"/>
+      <c r="F82" s="162" t="n"/>
+      <c r="G82" s="162" t="n"/>
+      <c r="H82" s="162" t="n"/>
+      <c r="I82" s="162" t="n"/>
+      <c r="J82" s="135">
         <f>SUM(C69:I69)</f>
         <v/>
       </c>
     </row>
-    <row r="83" ht="17.25" customHeight="1" s="78" thickBot="1">
-      <c r="A83" s="102" t="n"/>
-      <c r="B83" s="60" t="inlineStr">
+    <row r="83" ht="17.25" customHeight="1" s="77" thickBot="1">
+      <c r="A83" s="105" t="n"/>
+      <c r="B83" s="59" t="inlineStr">
         <is>
           <t>n대수술비</t>
         </is>
       </c>
-      <c r="C83" s="166" t="n"/>
-      <c r="D83" s="166" t="n"/>
-      <c r="E83" s="166" t="n"/>
-      <c r="F83" s="166" t="n"/>
-      <c r="G83" s="166" t="n"/>
-      <c r="H83" s="166" t="n"/>
-      <c r="I83" s="166" t="n"/>
-      <c r="J83" s="167">
+      <c r="C83" s="162" t="n"/>
+      <c r="D83" s="162" t="n"/>
+      <c r="E83" s="162" t="n"/>
+      <c r="F83" s="162" t="n"/>
+      <c r="G83" s="162" t="n"/>
+      <c r="H83" s="162" t="n"/>
+      <c r="I83" s="162" t="n"/>
+      <c r="J83" s="163">
         <f>SUM(C70:I70)</f>
         <v/>
       </c>
     </row>
-    <row r="84" ht="16.5" customHeight="1" s="78">
-      <c r="A84" s="102" t="n"/>
-      <c r="B84" s="69" t="inlineStr">
+    <row r="84" ht="16.5" customHeight="1" s="77">
+      <c r="A84" s="105" t="n"/>
+      <c r="B84" s="68" t="inlineStr">
         <is>
           <t>5대기관 수술비 관혈</t>
         </is>
       </c>
-      <c r="C84" s="140" t="n"/>
-      <c r="D84" s="140" t="n"/>
-      <c r="E84" s="140" t="n"/>
-      <c r="F84" s="140" t="n"/>
-      <c r="G84" s="140" t="n"/>
-      <c r="H84" s="140" t="n"/>
-      <c r="I84" s="140" t="n"/>
-      <c r="J84" s="137">
+      <c r="C84" s="136" t="n"/>
+      <c r="D84" s="136" t="n"/>
+      <c r="E84" s="136" t="n"/>
+      <c r="F84" s="136" t="n"/>
+      <c r="G84" s="136" t="n"/>
+      <c r="H84" s="136" t="n"/>
+      <c r="I84" s="136" t="n"/>
+      <c r="J84" s="133">
         <f>SUM(C71:I71)</f>
         <v/>
       </c>
     </row>
-    <row r="85" ht="17.25" customHeight="1" s="78" thickBot="1">
-      <c r="A85" s="103" t="n"/>
-      <c r="B85" s="70" t="inlineStr">
+    <row r="85" ht="17.25" customHeight="1" s="77" thickBot="1">
+      <c r="A85" s="106" t="n"/>
+      <c r="B85" s="69" t="inlineStr">
         <is>
           <t>5대기관 수술비 비관혈</t>
         </is>
       </c>
-      <c r="C85" s="134" t="n"/>
-      <c r="D85" s="134" t="n"/>
-      <c r="E85" s="134" t="n"/>
-      <c r="F85" s="134" t="n"/>
-      <c r="G85" s="134" t="n"/>
-      <c r="H85" s="134" t="n"/>
-      <c r="I85" s="134" t="n"/>
-      <c r="J85" s="135">
+      <c r="C85" s="130" t="n"/>
+      <c r="D85" s="130" t="n"/>
+      <c r="E85" s="130" t="n"/>
+      <c r="F85" s="130" t="n"/>
+      <c r="G85" s="130" t="n"/>
+      <c r="H85" s="130" t="n"/>
+      <c r="I85" s="130" t="n"/>
+      <c r="J85" s="131">
         <f>SUM(C72:I72)</f>
         <v/>
       </c>
     </row>
-    <row r="86" ht="16.5" customHeight="1" s="78" thickBot="1">
-      <c r="A86" s="101" t="inlineStr">
+    <row r="86" ht="16.5" customHeight="1" s="77" thickBot="1">
+      <c r="A86" s="104" t="inlineStr">
         <is>
           <t>운전</t>
         </is>
@@ -3162,199 +3190,199 @@
           <t>대인</t>
         </is>
       </c>
-      <c r="C86" s="119" t="n"/>
-      <c r="D86" s="119" t="n"/>
-      <c r="E86" s="119" t="n"/>
-      <c r="F86" s="119" t="n"/>
-      <c r="G86" s="119" t="n"/>
-      <c r="H86" s="119" t="n"/>
-      <c r="I86" s="119" t="n"/>
-      <c r="J86" s="137">
+      <c r="C86" s="115" t="n"/>
+      <c r="D86" s="115" t="n"/>
+      <c r="E86" s="115" t="n"/>
+      <c r="F86" s="115" t="n"/>
+      <c r="G86" s="115" t="n"/>
+      <c r="H86" s="115" t="n"/>
+      <c r="I86" s="115" t="n"/>
+      <c r="J86" s="133">
         <f>SUM(C73:I73)</f>
         <v/>
       </c>
     </row>
-    <row r="87" ht="17.25" customHeight="1" s="78">
-      <c r="A87" s="102" t="n"/>
+    <row r="87" ht="17.25" customHeight="1" s="77">
+      <c r="A87" s="105" t="n"/>
       <c r="B87" s="31" t="inlineStr">
         <is>
           <t>대물</t>
         </is>
       </c>
-      <c r="C87" s="149" t="n"/>
-      <c r="D87" s="149" t="n"/>
-      <c r="E87" s="149" t="n"/>
-      <c r="F87" s="149" t="n"/>
-      <c r="G87" s="149" t="n"/>
-      <c r="H87" s="149" t="n"/>
-      <c r="I87" s="149" t="n"/>
-      <c r="J87" s="139">
+      <c r="C87" s="145" t="n"/>
+      <c r="D87" s="145" t="n"/>
+      <c r="E87" s="145" t="n"/>
+      <c r="F87" s="145" t="n"/>
+      <c r="G87" s="145" t="n"/>
+      <c r="H87" s="145" t="n"/>
+      <c r="I87" s="145" t="n"/>
+      <c r="J87" s="135">
         <f>SUM(C74:I74)</f>
         <v/>
       </c>
     </row>
-    <row r="88" ht="16.5" customHeight="1" s="78">
-      <c r="A88" s="102" t="n"/>
+    <row r="88" ht="16.5" customHeight="1" s="77">
+      <c r="A88" s="105" t="n"/>
       <c r="B88" s="31" t="inlineStr">
         <is>
           <t>합의금</t>
         </is>
       </c>
-      <c r="C88" s="149" t="n"/>
-      <c r="D88" s="149" t="n"/>
-      <c r="E88" s="149" t="n"/>
-      <c r="F88" s="149" t="n"/>
-      <c r="G88" s="149" t="n"/>
-      <c r="H88" s="149" t="n"/>
-      <c r="I88" s="149" t="n"/>
-      <c r="J88" s="139">
+      <c r="C88" s="145" t="n"/>
+      <c r="D88" s="145" t="n"/>
+      <c r="E88" s="145" t="n"/>
+      <c r="F88" s="145" t="n"/>
+      <c r="G88" s="145" t="n"/>
+      <c r="H88" s="145" t="n"/>
+      <c r="I88" s="145" t="n"/>
+      <c r="J88" s="135">
         <f>SUM(C75:I75)</f>
         <v/>
       </c>
     </row>
-    <row r="89" ht="16.5" customHeight="1" s="78">
-      <c r="A89" s="102" t="n"/>
-      <c r="B89" s="65" t="inlineStr">
+    <row r="89" ht="16.5" customHeight="1" s="77">
+      <c r="A89" s="105" t="n"/>
+      <c r="B89" s="64" t="inlineStr">
         <is>
           <t>6주미만</t>
         </is>
       </c>
-      <c r="C89" s="149" t="n"/>
-      <c r="D89" s="149" t="n"/>
-      <c r="E89" s="149" t="n"/>
-      <c r="F89" s="149" t="n"/>
-      <c r="G89" s="149" t="n"/>
-      <c r="H89" s="149" t="n"/>
-      <c r="I89" s="149" t="n"/>
-      <c r="J89" s="139">
+      <c r="C89" s="145" t="n"/>
+      <c r="D89" s="145" t="n"/>
+      <c r="E89" s="145" t="n"/>
+      <c r="F89" s="145" t="n"/>
+      <c r="G89" s="145" t="n"/>
+      <c r="H89" s="145" t="n"/>
+      <c r="I89" s="145" t="n"/>
+      <c r="J89" s="135">
         <f>SUM(C76:I76)</f>
         <v/>
       </c>
     </row>
-    <row r="90" ht="17.25" customHeight="1" s="78">
-      <c r="A90" s="102" t="n"/>
+    <row r="90" ht="17.25" customHeight="1" s="77">
+      <c r="A90" s="105" t="n"/>
       <c r="B90" s="31" t="inlineStr">
         <is>
           <t>변호사</t>
         </is>
       </c>
-      <c r="C90" s="149" t="n"/>
-      <c r="D90" s="149" t="n"/>
-      <c r="E90" s="149" t="n"/>
-      <c r="F90" s="149" t="n"/>
-      <c r="G90" s="149" t="n"/>
-      <c r="H90" s="149" t="n"/>
-      <c r="I90" s="149" t="n"/>
-      <c r="J90" s="139">
+      <c r="C90" s="145" t="n"/>
+      <c r="D90" s="145" t="n"/>
+      <c r="E90" s="145" t="n"/>
+      <c r="F90" s="145" t="n"/>
+      <c r="G90" s="145" t="n"/>
+      <c r="H90" s="145" t="n"/>
+      <c r="I90" s="145" t="n"/>
+      <c r="J90" s="135">
         <f>SUM(C77:I77)</f>
         <v/>
       </c>
     </row>
-    <row r="91" ht="17.25" customHeight="1" s="78">
-      <c r="A91" s="103" t="n"/>
+    <row r="91" ht="17.25" customHeight="1" s="77">
+      <c r="A91" s="106" t="n"/>
       <c r="B91" s="25" t="inlineStr">
         <is>
           <t>자부상</t>
         </is>
       </c>
-      <c r="C91" s="168" t="n"/>
-      <c r="D91" s="168" t="n"/>
-      <c r="E91" s="168" t="n"/>
-      <c r="F91" s="168" t="n"/>
-      <c r="G91" s="168" t="n"/>
-      <c r="H91" s="168" t="n"/>
-      <c r="I91" s="168" t="n"/>
-      <c r="J91" s="135">
+      <c r="C91" s="164" t="n"/>
+      <c r="D91" s="164" t="n"/>
+      <c r="E91" s="164" t="n"/>
+      <c r="F91" s="164" t="n"/>
+      <c r="G91" s="164" t="n"/>
+      <c r="H91" s="164" t="n"/>
+      <c r="I91" s="164" t="n"/>
+      <c r="J91" s="131">
         <f>SUM(C78:I78)</f>
         <v/>
       </c>
     </row>
-    <row r="92" ht="16.5" customHeight="1" s="78">
-      <c r="A92" s="101" t="inlineStr">
+    <row r="92" ht="16.5" customHeight="1" s="77">
+      <c r="A92" s="104" t="inlineStr">
         <is>
           <t>골절</t>
         </is>
       </c>
-      <c r="B92" s="64" t="inlineStr">
+      <c r="B92" s="63" t="inlineStr">
         <is>
           <t>골절(치아파절포함)</t>
         </is>
       </c>
-      <c r="C92" s="159" t="n"/>
-      <c r="D92" s="159" t="n"/>
-      <c r="E92" s="159" t="n"/>
-      <c r="F92" s="159" t="n"/>
-      <c r="G92" s="159" t="n"/>
-      <c r="H92" s="159" t="n"/>
-      <c r="I92" s="159" t="n"/>
-      <c r="J92" s="133">
+      <c r="C92" s="155" t="n"/>
+      <c r="D92" s="155" t="n"/>
+      <c r="E92" s="155" t="n"/>
+      <c r="F92" s="155" t="n"/>
+      <c r="G92" s="155" t="n"/>
+      <c r="H92" s="155" t="n"/>
+      <c r="I92" s="155" t="n"/>
+      <c r="J92" s="129">
         <f>SUM(C79:I79)</f>
         <v/>
       </c>
     </row>
-    <row r="93" ht="16.5" customHeight="1" s="78">
-      <c r="A93" s="102" t="n"/>
-      <c r="B93" s="59" t="inlineStr">
+    <row r="93" ht="16.5" customHeight="1" s="77">
+      <c r="A93" s="105" t="n"/>
+      <c r="B93" s="58" t="inlineStr">
         <is>
           <t>골절(치아파절제외)</t>
         </is>
       </c>
-      <c r="C93" s="138" t="n"/>
-      <c r="D93" s="138" t="n"/>
-      <c r="E93" s="138" t="n"/>
-      <c r="F93" s="138" t="n"/>
-      <c r="G93" s="138" t="n"/>
-      <c r="H93" s="138" t="n"/>
-      <c r="I93" s="138" t="n"/>
-      <c r="J93" s="139">
+      <c r="C93" s="134" t="n"/>
+      <c r="D93" s="134" t="n"/>
+      <c r="E93" s="134" t="n"/>
+      <c r="F93" s="134" t="n"/>
+      <c r="G93" s="134" t="n"/>
+      <c r="H93" s="134" t="n"/>
+      <c r="I93" s="134" t="n"/>
+      <c r="J93" s="135">
         <f>SUM(C80:I80)</f>
         <v/>
       </c>
     </row>
-    <row r="94" ht="16.5" customHeight="1" s="78">
-      <c r="A94" s="103" t="n"/>
-      <c r="B94" s="70" t="inlineStr">
+    <row r="94" ht="16.5" customHeight="1" s="77">
+      <c r="A94" s="106" t="n"/>
+      <c r="B94" s="69" t="inlineStr">
         <is>
           <t>5대골절진단비</t>
         </is>
       </c>
-      <c r="C94" s="134" t="n"/>
-      <c r="D94" s="134" t="n"/>
-      <c r="E94" s="134" t="n"/>
-      <c r="F94" s="134" t="n"/>
-      <c r="G94" s="134" t="n"/>
-      <c r="H94" s="134" t="n"/>
-      <c r="I94" s="134" t="n"/>
-      <c r="J94" s="135">
+      <c r="C94" s="130" t="n"/>
+      <c r="D94" s="130" t="n"/>
+      <c r="E94" s="130" t="n"/>
+      <c r="F94" s="130" t="n"/>
+      <c r="G94" s="130" t="n"/>
+      <c r="H94" s="130" t="n"/>
+      <c r="I94" s="130" t="n"/>
+      <c r="J94" s="131">
         <f>SUM(C81:I81)</f>
         <v/>
       </c>
     </row>
-    <row r="95" ht="16.5" customHeight="1" s="78">
-      <c r="A95" s="101" t="inlineStr">
+    <row r="95" ht="16.5" customHeight="1" s="77">
+      <c r="A95" s="104" t="inlineStr">
         <is>
           <t>응급실</t>
         </is>
       </c>
-      <c r="B95" s="63" t="inlineStr">
+      <c r="B95" s="62" t="inlineStr">
         <is>
           <t>응급실(응급)</t>
         </is>
       </c>
-      <c r="C95" s="130" t="n"/>
-      <c r="D95" s="130" t="n"/>
-      <c r="E95" s="130" t="n"/>
-      <c r="F95" s="130" t="n"/>
-      <c r="G95" s="130" t="n"/>
-      <c r="H95" s="130" t="n"/>
-      <c r="I95" s="130" t="n"/>
-      <c r="J95" s="131">
+      <c r="C95" s="126" t="n"/>
+      <c r="D95" s="126" t="n"/>
+      <c r="E95" s="126" t="n"/>
+      <c r="F95" s="126" t="n"/>
+      <c r="G95" s="126" t="n"/>
+      <c r="H95" s="126" t="n"/>
+      <c r="I95" s="126" t="n"/>
+      <c r="J95" s="127">
         <f>SUM(C82:I82)</f>
         <v/>
       </c>
     </row>
-    <row r="96" ht="16.5" customHeight="1" s="78">
-      <c r="A96" s="101" t="inlineStr">
+    <row r="96" ht="16.5" customHeight="1" s="77">
+      <c r="A96" s="104" t="inlineStr">
         <is>
           <t>독감</t>
         </is>
@@ -3364,17 +3392,17 @@
           <t>독감</t>
         </is>
       </c>
-      <c r="C96" s="140" t="n"/>
-      <c r="D96" s="140" t="n"/>
-      <c r="E96" s="140" t="n"/>
-      <c r="F96" s="140" t="n"/>
-      <c r="G96" s="140" t="n"/>
-      <c r="H96" s="140" t="n"/>
-      <c r="I96" s="140" t="n"/>
-      <c r="J96" s="141" t="n"/>
-    </row>
-    <row r="97" ht="16.5" customHeight="1" s="78">
-      <c r="A97" s="101" t="inlineStr">
+      <c r="C96" s="136" t="n"/>
+      <c r="D96" s="136" t="n"/>
+      <c r="E96" s="136" t="n"/>
+      <c r="F96" s="136" t="n"/>
+      <c r="G96" s="136" t="n"/>
+      <c r="H96" s="136" t="n"/>
+      <c r="I96" s="136" t="n"/>
+      <c r="J96" s="137" t="n"/>
+    </row>
+    <row r="97" ht="16.5" customHeight="1" s="77">
+      <c r="A97" s="104" t="inlineStr">
         <is>
           <t>화상</t>
         </is>
@@ -3384,216 +3412,216 @@
           <t>화상진단비</t>
         </is>
       </c>
-      <c r="C97" s="136" t="n"/>
-      <c r="D97" s="136" t="n"/>
-      <c r="E97" s="136" t="n"/>
-      <c r="F97" s="136" t="n"/>
-      <c r="G97" s="136" t="n"/>
-      <c r="H97" s="136" t="n"/>
-      <c r="I97" s="136" t="n"/>
-      <c r="J97" s="137">
+      <c r="C97" s="132" t="n"/>
+      <c r="D97" s="132" t="n"/>
+      <c r="E97" s="132" t="n"/>
+      <c r="F97" s="132" t="n"/>
+      <c r="G97" s="132" t="n"/>
+      <c r="H97" s="132" t="n"/>
+      <c r="I97" s="132" t="n"/>
+      <c r="J97" s="133">
         <f>SUM(C84:I84)</f>
         <v/>
       </c>
     </row>
-    <row r="98" ht="16.5" customHeight="1" s="78">
-      <c r="A98" s="103" t="n"/>
+    <row r="98" ht="16.5" customHeight="1" s="77">
+      <c r="A98" s="106" t="n"/>
       <c r="B98" s="25" t="inlineStr">
         <is>
           <t>중증화상진단비</t>
         </is>
       </c>
-      <c r="C98" s="134" t="n"/>
-      <c r="D98" s="134" t="n"/>
-      <c r="E98" s="134" t="n"/>
-      <c r="F98" s="134" t="n"/>
-      <c r="G98" s="134" t="n"/>
-      <c r="H98" s="134" t="n"/>
-      <c r="I98" s="134" t="n"/>
-      <c r="J98" s="135">
+      <c r="C98" s="130" t="n"/>
+      <c r="D98" s="130" t="n"/>
+      <c r="E98" s="130" t="n"/>
+      <c r="F98" s="130" t="n"/>
+      <c r="G98" s="130" t="n"/>
+      <c r="H98" s="130" t="n"/>
+      <c r="I98" s="130" t="n"/>
+      <c r="J98" s="131">
         <f>SUM(C85:I85)</f>
         <v/>
       </c>
     </row>
-    <row r="99" ht="16.5" customHeight="1" s="78">
-      <c r="A99" s="101" t="inlineStr">
+    <row r="99" ht="16.5" customHeight="1" s="77">
+      <c r="A99" s="104" t="inlineStr">
         <is>
           <t>깁스</t>
         </is>
       </c>
-      <c r="B99" s="104" t="inlineStr">
+      <c r="B99" s="109" t="inlineStr">
         <is>
           <t>반깁스</t>
         </is>
       </c>
-      <c r="C99" s="136" t="n"/>
-      <c r="D99" s="136" t="n"/>
-      <c r="E99" s="136" t="n"/>
-      <c r="F99" s="136" t="n"/>
-      <c r="G99" s="136" t="n"/>
-      <c r="H99" s="136" t="n"/>
-      <c r="I99" s="136" t="n"/>
-      <c r="J99" s="137">
+      <c r="C99" s="132" t="n"/>
+      <c r="D99" s="132" t="n"/>
+      <c r="E99" s="132" t="n"/>
+      <c r="F99" s="132" t="n"/>
+      <c r="G99" s="132" t="n"/>
+      <c r="H99" s="132" t="n"/>
+      <c r="I99" s="132" t="n"/>
+      <c r="J99" s="133">
         <f>SUM(C86:I86)</f>
         <v/>
       </c>
     </row>
-    <row r="100" ht="16.5" customHeight="1" s="78">
-      <c r="A100" s="103" t="n"/>
+    <row r="100" ht="16.5" customHeight="1" s="77">
+      <c r="A100" s="106" t="n"/>
       <c r="B100" s="56" t="inlineStr">
         <is>
           <t>깁스진단비</t>
         </is>
       </c>
-      <c r="C100" s="134" t="n"/>
-      <c r="D100" s="134" t="n"/>
-      <c r="E100" s="134" t="n"/>
-      <c r="F100" s="134" t="n"/>
-      <c r="G100" s="134" t="n"/>
-      <c r="H100" s="134" t="n"/>
-      <c r="I100" s="134" t="n"/>
-      <c r="J100" s="135">
+      <c r="C100" s="130" t="n"/>
+      <c r="D100" s="130" t="n"/>
+      <c r="E100" s="130" t="n"/>
+      <c r="F100" s="130" t="n"/>
+      <c r="G100" s="130" t="n"/>
+      <c r="H100" s="130" t="n"/>
+      <c r="I100" s="130" t="n"/>
+      <c r="J100" s="131">
         <f>SUM(C87:I87)</f>
         <v/>
       </c>
     </row>
-    <row r="101" ht="16.5" customHeight="1" s="78">
-      <c r="A101" s="101" t="inlineStr">
+    <row r="101" ht="16.5" customHeight="1" s="77">
+      <c r="A101" s="104" t="inlineStr">
         <is>
           <t>실손</t>
         </is>
       </c>
-      <c r="B101" s="104" t="inlineStr">
+      <c r="B101" s="109" t="inlineStr">
         <is>
           <t>입원</t>
         </is>
       </c>
-      <c r="C101" s="169" t="n"/>
-      <c r="D101" s="169" t="n"/>
-      <c r="E101" s="169" t="n"/>
-      <c r="F101" s="169" t="n"/>
-      <c r="G101" s="169" t="n"/>
-      <c r="H101" s="169" t="n"/>
-      <c r="I101" s="169" t="n"/>
-      <c r="J101" s="137">
+      <c r="C101" s="165" t="n"/>
+      <c r="D101" s="165" t="n"/>
+      <c r="E101" s="165" t="n"/>
+      <c r="F101" s="165" t="n"/>
+      <c r="G101" s="165" t="n"/>
+      <c r="H101" s="165" t="n"/>
+      <c r="I101" s="165" t="n"/>
+      <c r="J101" s="133">
         <f>SUM(C88:I88)</f>
         <v/>
       </c>
     </row>
-    <row r="102" ht="16.5" customHeight="1" s="78">
-      <c r="A102" s="102" t="n"/>
-      <c r="B102" s="59" t="inlineStr">
+    <row r="102" ht="16.5" customHeight="1" s="77">
+      <c r="A102" s="105" t="n"/>
+      <c r="B102" s="58" t="inlineStr">
         <is>
           <t>통원</t>
         </is>
       </c>
-      <c r="C102" s="170" t="n"/>
-      <c r="D102" s="170" t="n"/>
-      <c r="E102" s="170" t="n"/>
-      <c r="F102" s="170" t="n"/>
-      <c r="G102" s="170" t="n"/>
-      <c r="H102" s="170" t="n"/>
-      <c r="I102" s="170" t="n"/>
-      <c r="J102" s="139">
+      <c r="C102" s="166" t="n"/>
+      <c r="D102" s="166" t="n"/>
+      <c r="E102" s="166" t="n"/>
+      <c r="F102" s="166" t="n"/>
+      <c r="G102" s="166" t="n"/>
+      <c r="H102" s="166" t="n"/>
+      <c r="I102" s="166" t="n"/>
+      <c r="J102" s="135">
         <f>SUM(C89:I89)</f>
         <v/>
       </c>
     </row>
-    <row r="103" ht="16.5" customHeight="1" s="78">
-      <c r="A103" s="102" t="n"/>
-      <c r="B103" s="59" t="inlineStr">
+    <row r="103" ht="16.5" customHeight="1" s="77">
+      <c r="A103" s="105" t="n"/>
+      <c r="B103" s="58" t="inlineStr">
         <is>
           <t>약값</t>
         </is>
       </c>
-      <c r="C103" s="138" t="n"/>
-      <c r="D103" s="138" t="n"/>
-      <c r="E103" s="138" t="n"/>
-      <c r="F103" s="138" t="n"/>
-      <c r="G103" s="138" t="n"/>
-      <c r="H103" s="138" t="n"/>
-      <c r="I103" s="170" t="n"/>
-      <c r="J103" s="139">
+      <c r="C103" s="134" t="n"/>
+      <c r="D103" s="134" t="n"/>
+      <c r="E103" s="134" t="n"/>
+      <c r="F103" s="134" t="n"/>
+      <c r="G103" s="134" t="n"/>
+      <c r="H103" s="134" t="n"/>
+      <c r="I103" s="166" t="n"/>
+      <c r="J103" s="135">
         <f>SUM(C90:I90)</f>
         <v/>
       </c>
     </row>
-    <row r="104" ht="16.5" customHeight="1" s="78">
-      <c r="A104" s="102" t="n"/>
-      <c r="B104" s="59" t="inlineStr">
+    <row r="104" ht="16.5" customHeight="1" s="77">
+      <c r="A104" s="105" t="n"/>
+      <c r="B104" s="58" t="inlineStr">
         <is>
           <t>MRI/도수치료/비급여주사</t>
         </is>
       </c>
-      <c r="C104" s="138" t="n"/>
-      <c r="D104" s="138" t="n"/>
-      <c r="E104" s="138" t="n"/>
-      <c r="F104" s="138" t="n"/>
-      <c r="G104" s="138" t="n"/>
-      <c r="H104" s="138" t="n"/>
-      <c r="I104" s="170" t="n"/>
-      <c r="J104" s="133" t="n"/>
-    </row>
-    <row r="105" ht="16.5" customHeight="1" s="78">
-      <c r="A105" s="103" t="n"/>
+      <c r="C104" s="134" t="n"/>
+      <c r="D104" s="134" t="n"/>
+      <c r="E104" s="134" t="n"/>
+      <c r="F104" s="134" t="n"/>
+      <c r="G104" s="134" t="n"/>
+      <c r="H104" s="134" t="n"/>
+      <c r="I104" s="166" t="n"/>
+      <c r="J104" s="129" t="n"/>
+    </row>
+    <row r="105" ht="16.5" customHeight="1" s="77">
+      <c r="A105" s="106" t="n"/>
       <c r="B105" s="22" t="inlineStr">
         <is>
           <t>상해의료비</t>
         </is>
       </c>
-      <c r="C105" s="132" t="n"/>
-      <c r="D105" s="132" t="n"/>
-      <c r="E105" s="132" t="n"/>
-      <c r="F105" s="132" t="n"/>
-      <c r="G105" s="132" t="n"/>
-      <c r="H105" s="132" t="n"/>
-      <c r="I105" s="171" t="n"/>
-      <c r="J105" s="139" t="n"/>
-    </row>
-    <row r="106" ht="16.5" customHeight="1" s="78">
-      <c r="A106" s="101" t="inlineStr">
+      <c r="C105" s="128" t="n"/>
+      <c r="D105" s="128" t="n"/>
+      <c r="E105" s="128" t="n"/>
+      <c r="F105" s="128" t="n"/>
+      <c r="G105" s="128" t="n"/>
+      <c r="H105" s="128" t="n"/>
+      <c r="I105" s="167" t="n"/>
+      <c r="J105" s="135" t="n"/>
+    </row>
+    <row r="106" ht="16.5" customHeight="1" s="77">
+      <c r="A106" s="104" t="inlineStr">
         <is>
           <t>일배책</t>
         </is>
       </c>
-      <c r="B106" s="75" t="inlineStr">
+      <c r="B106" s="74" t="inlineStr">
         <is>
           <t>일상배상책임</t>
         </is>
       </c>
-      <c r="C106" s="172" t="n"/>
-      <c r="D106" s="172" t="n"/>
-      <c r="E106" s="172" t="n"/>
-      <c r="F106" s="172" t="n"/>
-      <c r="G106" s="172" t="n"/>
-      <c r="H106" s="172" t="n"/>
-      <c r="I106" s="172" t="n"/>
-      <c r="J106" s="173">
+      <c r="C106" s="168" t="n"/>
+      <c r="D106" s="168" t="n"/>
+      <c r="E106" s="168" t="n"/>
+      <c r="F106" s="168" t="n"/>
+      <c r="G106" s="168" t="n"/>
+      <c r="H106" s="168" t="n"/>
+      <c r="I106" s="168" t="n"/>
+      <c r="J106" s="169">
         <f>SUM(C91:I91)</f>
         <v/>
       </c>
     </row>
-    <row r="107" ht="16.5" customHeight="1" s="78"/>
-    <row r="108" ht="16.5" customHeight="1" s="78"/>
+    <row r="107" ht="16.5" customHeight="1" s="77"/>
+    <row r="108" ht="16.5" customHeight="1" s="77"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A101:A105"/>
+    <mergeCell ref="A32:A40"/>
     <mergeCell ref="A86:A91"/>
     <mergeCell ref="A15:A31"/>
+    <mergeCell ref="A92:A94"/>
     <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A99:A100"/>
     <mergeCell ref="A41:A53"/>
     <mergeCell ref="A54:A66"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A67:A85"/>
-    <mergeCell ref="A32:A40"/>
-    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A6:A10"/>
-    <mergeCell ref="A92:A94"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="8" horizontalDpi="300" verticalDpi="300"/>
@@ -3607,158 +3635,158 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="17.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5" defaultRowHeight="16.5"/>
   <cols>
-    <col width="5" customWidth="1" style="78" min="1" max="1"/>
-    <col width="110" customWidth="1" style="78" min="2" max="2"/>
+    <col width="5" customWidth="1" style="77" min="1" max="1"/>
+    <col width="110" customWidth="1" style="77" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1" s="78">
-      <c r="A1" s="79" t="inlineStr">
+    <row r="1" ht="20.1" customHeight="1" s="77">
+      <c r="A1" s="78" t="inlineStr">
         <is>
           <t>바름 보장분석 법칙 v2 — 이 표본에 내장 (2026.06.09)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="17.1" customHeight="1" s="78">
+    <row r="3" ht="17.1" customHeight="1" s="77">
       <c r="A3" s="0" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B3" s="80" t="inlineStr">
+      <c r="B3" s="79" t="inlineStr">
         <is>
           <t>폼 무변형: 이 표본을 열어 값만 채운다. 새 워크북·행삭제·카테고리축소 금지. 추가만(그룹 안 행삽입), 표 밖 금지.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="17.1" customHeight="1" s="78">
+    <row r="4" ht="17.1" customHeight="1" s="77">
       <c r="A4" s="0" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B4" s="80" t="inlineStr">
+      <c r="B4" s="79" t="inlineStr">
         <is>
           <t>새 고객 입력 시 이전 고객 값 전부 zero화(이 표본에서 새로 시작).</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="17.1" customHeight="1" s="78">
+    <row r="5" ht="17.1" customHeight="1" s="77">
       <c r="A5" s="0" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B5" s="80" t="inlineStr">
+      <c r="B5" s="79" t="inlineStr">
         <is>
           <t>열=계약(최대 50). 행=담보(15구분·82행). 끝열=합계.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="17.1" customHeight="1" s="78">
+    <row r="6" ht="17.1" customHeight="1" s="77">
       <c r="A6" s="0" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B6" s="80" t="inlineStr">
+      <c r="B6" s="79" t="inlineStr">
         <is>
           <t>합계 = 세로(계약별) SUM. 4페이지 한장보장 값을 합계칸 직박음 금지(눈속임). 계약별 칸을 채워야 합계가 산다.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="17.1" customHeight="1" s="78">
+    <row r="7" ht="17.1" customHeight="1" s="77">
       <c r="A7" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B7" s="80" t="inlineStr">
+      <c r="B7" s="79" t="inlineStr">
         <is>
           <t>계약별 대조 필수: A담보가 B회사 칸으로 가면 안 됨.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="17.1" customHeight="1" s="78">
+    <row r="8" ht="17.1" customHeight="1" s="77">
       <c r="A8" s="0" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="81" t="inlineStr">
+      <c r="B8" s="80" t="inlineStr">
         <is>
           <t>1~5종 수술비 = 질병/상해 각 1행, 슬래시 가로표기 "20/50/100/500/1000", 합계도 종별.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="17.1" customHeight="1" s="78">
+    <row r="9" ht="17.1" customHeight="1" s="77">
       <c r="A9" s="0" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B9" s="80" t="inlineStr">
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>갱신/비갱신: ①갱신형명시→갱신 ②운전자→비갱신 ③9999→비갱신 ④총회차240초과→비갱신 ⑤납입년수≠보장년수→비갱신.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="17.1" customHeight="1" s="78">
+    <row r="10" ht="17.1" customHeight="1" s="77">
       <c r="A10" s="0" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B10" s="80" t="inlineStr">
+      <c r="B10" s="79" t="inlineStr">
         <is>
           <t>색: 갱신=파랑 / 비갱신=검정 / 미가입=빨강. 구분셀=연두. 헤더 갱신블루·비갱신레드·완납진녹.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="17.1" customHeight="1" s="78">
+    <row r="11" ht="17.1" customHeight="1" s="77">
       <c r="A11" s="0" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B11" s="80" t="inlineStr">
+      <c r="B11" s="79" t="inlineStr">
         <is>
           <t>심장=담보명 직행(허혈성→허혈성칸, 전파금지). 불확정은 기재+[확인].</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="17.1" customHeight="1" s="78">
+    <row r="12" ht="17.1" customHeight="1" s="77">
       <c r="A12" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" s="81" t="inlineStr">
+      <c r="B12" s="80" t="inlineStr">
         <is>
           <t>9999(생보)=종신 → 일반사망(종신)+상해사망. 손보 질병사망=80세칸.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="17.1" customHeight="1" s="78">
+    <row r="13" ht="17.1" customHeight="1" s="77">
       <c r="A13" s="0" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B13" s="80" t="inlineStr">
+      <c r="B13" s="79" t="inlineStr">
         <is>
           <t>추측 금지: 모르면 빈칸+[확인]. 채우는 게 최악, 비우고 메모가 차선, 확정 기재가 최선. 자동천장 95%.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="17.1" customHeight="1" s="78">
+    <row r="14" ht="17.1" customHeight="1" s="77">
       <c r="A14" s="0" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B14" s="80" t="inlineStr">
+      <c r="B14" s="79" t="inlineStr">
         <is>
           <t>엑셀=원천, PPT는 완성 엑셀만 읽음(PDF→엑셀→PPT). 제출 전 렌더검수 통과한 것만.</t>
         </is>
@@ -3777,17 +3805,17 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E80"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="12" customWidth="1" style="78" min="1" max="1"/>
-    <col width="34" customWidth="1" style="78" min="2" max="2"/>
-    <col width="40" customWidth="1" style="78" min="3" max="3"/>
-    <col width="26" customWidth="1" style="78" min="4" max="4"/>
-    <col width="30" customWidth="1" style="78" min="5" max="5"/>
+    <col width="12" customWidth="1" style="77" min="1" max="1"/>
+    <col width="34" customWidth="1" style="77" min="2" max="2"/>
+    <col width="40" customWidth="1" style="77" min="3" max="3"/>
+    <col width="26" customWidth="1" style="77" min="4" max="4"/>
+    <col width="30" customWidth="1" style="77" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.2" customHeight="1" s="78">
-      <c r="A1" s="83" t="inlineStr">
+    <row r="1" ht="19.15" customHeight="1" s="77">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>★ 이 시트가 지침 체크봇의 정본이다. 여기에 행을 추가하면 앱이 매 분석마다 자동으로 검사한다.</t>
         </is>
@@ -3808,27 +3836,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="84" t="inlineStr">
+      <c r="A5" s="83" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
       </c>
-      <c r="B5" s="84" t="inlineStr">
+      <c r="B5" s="83" t="inlineStr">
         <is>
           <t>조항</t>
         </is>
       </c>
-      <c r="C5" s="84" t="inlineStr">
+      <c r="C5" s="83" t="inlineStr">
         <is>
           <t>담보명</t>
         </is>
       </c>
-      <c r="D5" s="84" t="inlineStr">
+      <c r="D5" s="83" t="inlineStr">
         <is>
           <t>기대행(빈칸=기재금지)</t>
         </is>
       </c>
-      <c r="E5" s="84" t="inlineStr">
+      <c r="E5" s="83" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -5352,16 +5380,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="6" customWidth="1" style="78" min="1" max="1"/>
-    <col width="74" customWidth="1" style="78" min="2" max="2"/>
-    <col width="38" customWidth="1" style="78" min="3" max="3"/>
-    <col width="44" customWidth="1" style="78" min="4" max="4"/>
+    <col width="6" customWidth="1" style="77" min="1" max="1"/>
+    <col width="74" customWidth="1" style="77" min="2" max="2"/>
+    <col width="38" customWidth="1" style="77" min="3" max="3"/>
+    <col width="44" customWidth="1" style="77" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.2" customHeight="1" s="78">
-      <c r="A1" s="83" t="inlineStr">
+    <row r="1" ht="19.15" customHeight="1" s="77">
+      <c r="A1" s="82" t="inlineStr">
         <is>
           <t>★ 이 시트가 「관점」의 정본이다. 지침을 어떻게 읽을지를 여기서 고정한다. 앱이 매 분석마다 확인사항 시트 하단에 이 원문을 그대로 출력한다.</t>
         </is>
@@ -5375,222 +5403,222 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="84" t="inlineStr">
+      <c r="A4" s="83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B4" s="84" t="inlineStr">
+      <c r="B4" s="83" t="inlineStr">
         <is>
           <t>원칙 (지점장 원문 — 그대로 쓴다)</t>
         </is>
       </c>
-      <c r="C4" s="84" t="inlineStr">
+      <c r="C4" s="83" t="inlineStr">
         <is>
           <t>위반하면</t>
         </is>
       </c>
-      <c r="D4" s="84" t="inlineStr">
+      <c r="D4" s="83" t="inlineStr">
         <is>
           <t>근거·사례</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="31.95" customHeight="1" s="78">
+    <row r="5" ht="31.9" customHeight="1" s="77">
       <c r="A5" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="81" t="inlineStr">
+      <c r="B5" s="80" t="inlineStr">
         <is>
           <t>지점장이 준 자료는 문구·코드를 그대로 쓴다. 요약·재구성하거나 해설 주석을 덧붙이지 않는다.</t>
         </is>
       </c>
-      <c r="C5" s="81" t="inlineStr">
+      <c r="C5" s="80" t="inlineStr">
         <is>
           <t>최종본과 달라 보여 같은 매핑을 반복해 틀린다</t>
         </is>
       </c>
-      <c r="D5" s="81" t="inlineStr">
+      <c r="D5" s="80" t="inlineStr">
         <is>
           <t>정본 관리 3원칙 ① · 2026.07.18 심장 매핑 4회 오류</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="31.95" customHeight="1" s="78">
+    <row r="6" ht="31.9" customHeight="1" s="77">
       <c r="A6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="81" t="inlineStr">
+      <c r="B6" s="80" t="inlineStr">
         <is>
           <t>지침에 없으면 추측하지 않는다 — 빈칸으로 두고 [확인]큐로 보낸다.</t>
         </is>
       </c>
-      <c r="C6" s="81" t="inlineStr">
+      <c r="C6" s="80" t="inlineStr">
         <is>
           <t>내 판단이 정본인 것처럼 산출물에 박힌다</t>
         </is>
       </c>
-      <c r="D6" s="81" t="inlineStr">
+      <c r="D6" s="80" t="inlineStr">
         <is>
           <t>§0 "모르면 빈칸+[확인], 추측 금지"</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="31.95" customHeight="1" s="78">
+    <row r="7" ht="31.9" customHeight="1" s="77">
       <c r="A7" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="81" t="inlineStr">
+      <c r="B7" s="80" t="inlineStr">
         <is>
           <t>범위를 넓히려면 먼저 물어본다. 지점장이 두 개를 말했으면 두 개만 넣는다.</t>
         </is>
       </c>
-      <c r="C7" s="81" t="inlineStr">
+      <c r="C7" s="80" t="inlineStr">
         <is>
           <t>"나는 그걸 말한 적이 없다" — 임의 확장</t>
         </is>
       </c>
-      <c r="D7" s="81" t="inlineStr">
+      <c r="D7" s="80" t="inlineStr">
         <is>
           <t>(0f) 상해·재해 외에 교통·외래·대중교통까지 확장</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="31.95" customHeight="1" s="78">
+    <row r="8" ht="31.9" customHeight="1" s="77">
       <c r="A8" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="81" t="inlineStr">
+      <c r="B8" s="80" t="inlineStr">
         <is>
           <t>지침이 바뀌면 옛 내용을 남기지 말고 지운다. 세트로 내려온 지시는 전부 폐기·교체한다.</t>
         </is>
       </c>
-      <c r="C8" s="81" t="inlineStr">
+      <c r="C8" s="80" t="inlineStr">
         <is>
           <t>옛 규칙이 살아남아 그대로 나간다</t>
         </is>
       </c>
-      <c r="D8" s="81" t="inlineStr">
+      <c r="D8" s="80" t="inlineStr">
         <is>
           <t>정본 관리 3원칙 ② · 빈맥 규칙이 4곳에 잔존</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="31.95" customHeight="1" s="78">
+    <row r="9" ht="31.9" customHeight="1" s="77">
       <c r="A9" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="81" t="inlineStr">
+      <c r="B9" s="80" t="inlineStr">
         <is>
           <t>같은 데이터가 여러 곳에 있다 — 전수 수정하고 마지막에 옛 문구 잔재를 스캔한다.</t>
         </is>
       </c>
-      <c r="C9" s="81" t="inlineStr">
+      <c r="C9" s="80" t="inlineStr">
         <is>
           <t>반쪽 수정 — 한 곳만 고쳐 불일치가 남는다</t>
         </is>
       </c>
-      <c r="D9" s="81" t="inlineStr">
+      <c r="D9" s="80" t="inlineStr">
         <is>
           <t>정본 관리 3원칙 ③ · v210 색 규칙 3군데</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="31.95" customHeight="1" s="78">
+    <row r="10" ht="31.9" customHeight="1" s="77">
       <c r="A10" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="81" t="inlineStr">
+      <c r="B10" s="80" t="inlineStr">
         <is>
           <t>규칙 두 개가 같은 값을 만지면 나중 것이 앞 것을 죽인다. 새 규칙 전에 같은 셀을 쓰는 기존 규칙을 확인한다.</t>
         </is>
       </c>
-      <c r="C10" s="81" t="inlineStr">
+      <c r="C10" s="80" t="inlineStr">
         <is>
           <t>조용히 겹쳐 박히거나 앞 규칙이 무효가 된다</t>
         </is>
       </c>
-      <c r="D10" s="81" t="inlineStr">
+      <c r="D10" s="80" t="inlineStr">
         <is>
           <t>v245가 v240을 되돌림 · v266 중복 적용</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="31.95" customHeight="1" s="78">
+    <row r="11" ht="31.9" customHeight="1" s="77">
       <c r="A11" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="81" t="inlineStr">
+      <c r="B11" s="80" t="inlineStr">
         <is>
           <t>직접 열어본 것만 "~이다"라고 쓴다. 안 본 것은 "가설"이라 명시한다. 측정하지 않은 수치는 말하지 않는다.</t>
         </is>
       </c>
-      <c r="C11" s="81" t="inlineStr">
+      <c r="C11" s="80" t="inlineStr">
         <is>
           <t>틀린 단정이 사실로 굳는다</t>
         </is>
       </c>
-      <c r="D11" s="81" t="inlineStr">
+      <c r="D11" s="80" t="inlineStr">
         <is>
           <t>(0a) · 2026.07.31 "v307은 존재하지 않는다" 오단정</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="31.95" customHeight="1" s="78">
+    <row r="12" ht="31.9" customHeight="1" s="77">
       <c r="A12" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="81" t="inlineStr">
+      <c r="B12" s="80" t="inlineStr">
         <is>
           <t>고장난 기능은 고치는 것이다 — 선택지로 만들어 지점장께 결정을 넘기지 않는다.</t>
         </is>
       </c>
-      <c r="C12" s="81" t="inlineStr">
+      <c r="C12" s="80" t="inlineStr">
         <is>
           <t>보고가 아니라 결정 위임이 된다</t>
         </is>
       </c>
-      <c r="D12" s="81" t="inlineStr">
+      <c r="D12" s="80" t="inlineStr">
         <is>
           <t>(0f) ci_sebu를 3선택지로 포장</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="31.95" customHeight="1" s="78">
+    <row r="13" ht="31.9" customHeight="1" s="77">
       <c r="A13" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="81" t="inlineStr">
+      <c r="B13" s="80" t="inlineStr">
         <is>
           <t>못 한 검증은 "못 했다"고 쓴다. 결과물만 올리지 않고 실행 과정을 보여준다.</t>
         </is>
       </c>
-      <c r="C13" s="81" t="inlineStr">
+      <c r="C13" s="80" t="inlineStr">
         <is>
           <t>"지침 돌렸다"는 말만 남고 실제로 안 돌아간다</t>
         </is>
       </c>
-      <c r="D13" s="81" t="inlineStr">
+      <c r="D13" s="80" t="inlineStr">
         <is>
           <t>(0e) "왜 결과물만 올리냐"</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="31.95" customHeight="1" s="78">
+    <row r="14" ht="31.9" customHeight="1" s="77">
       <c r="A14" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="81" t="inlineStr">
+      <c r="B14" s="80" t="inlineStr">
         <is>
           <t>규칙 하나를 고치면 2열(롯데)·3열(KB) 두 경로를 반드시 다 돌린다.</t>
         </is>
       </c>
-      <c r="C14" s="81" t="inlineStr">
+      <c r="C14" s="80" t="inlineStr">
         <is>
           <t>한 경로만 고쳐 다른 경로가 조용히 깨진다</t>
         </is>
       </c>
-      <c r="D14" s="81" t="inlineStr">
+      <c r="D14" s="80" t="inlineStr">
         <is>
           <t>제출 전 체크리스트 ⑨</t>
         </is>
